--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="1971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="1972">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,64 +44,64 @@
     <t xml:space="preserve">A2A.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774303913116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769300401210785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777431070804596</t>
+    <t xml:space="preserve">0.7743039727211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76930034160614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777431190013885</t>
   </si>
   <si>
     <t xml:space="preserve">0.772427618503571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.775554835796356</t>
+    <t xml:space="preserve">0.775554776191711</t>
   </si>
   <si>
     <t xml:space="preserve">0.73615175485611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.728020787239075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.708631992340088</t>
+    <t xml:space="preserve">0.728020846843719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.708631932735443</t>
   </si>
   <si>
     <t xml:space="preserve">0.701126575469971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.678610503673553</t>
+    <t xml:space="preserve">0.678610563278198</t>
   </si>
   <si>
     <t xml:space="preserve">0.686115801334381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662974298000336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.669854283332825</t>
+    <t xml:space="preserve">0.662974238395691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.66985422372818</t>
   </si>
   <si>
     <t xml:space="preserve">0.673606932163239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.661723375320435</t>
+    <t xml:space="preserve">0.661723434925079</t>
   </si>
   <si>
     <t xml:space="preserve">0.68986850976944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667352497577667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.688617646694183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689243078231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.676108539104462</t>
+    <t xml:space="preserve">0.667352437973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.688617587089539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689243197441101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.676108658313751</t>
   </si>
   <si>
     <t xml:space="preserve">0.671105086803436</t>
@@ -110,22 +110,22 @@
     <t xml:space="preserve">0.66672694683075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643585503101349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612313091754913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597927689552307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605745851993561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610749423503876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614189386367798</t>
+    <t xml:space="preserve">0.643585443496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612312972545624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597927749156952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605745911598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610749363899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614189445972443</t>
   </si>
   <si>
     <t xml:space="preserve">0.627323806285858</t>
@@ -137,43 +137,43 @@
     <t xml:space="preserve">0.624822020530701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646712720394135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.636080086231232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65671980381012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645461618900299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641083717346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647963464260101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.657345235347748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661097943782806</t>
+    <t xml:space="preserve">0.64671266078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.636080026626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.656719744205475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645461738109589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641083657741547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.647963643074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.657345294952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661098003387451</t>
   </si>
   <si>
     <t xml:space="preserve">0.672981441020966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666101574897766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.66485059261322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658596217632294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651716291904449</t>
+    <t xml:space="preserve">0.666101515293121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.664850652217865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658596158027649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651716351509094</t>
   </si>
   <si>
     <t xml:space="preserve">0.654843509197235</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">0.71301007270813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.692995727062225</t>
+    <t xml:space="preserve">0.692995846271515</t>
   </si>
   <si>
     <t xml:space="preserve">0.691119432449341</t>
@@ -197,52 +197,52 @@
     <t xml:space="preserve">0.697999358177185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696123003959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70300281047821</t>
+    <t xml:space="preserve">0.696123063564301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7030029296875</t>
   </si>
   <si>
     <t xml:space="preserve">0.692370355129242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.699250161647797</t>
+    <t xml:space="preserve">0.699250221252441</t>
   </si>
   <si>
     <t xml:space="preserve">0.714260935783386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714886367321014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.702377498149872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705504775047302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735526204109192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.740529716014862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74428254365921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748660504817963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.738028049468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750536859035492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754289567470551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768049418926239</t>
+    <t xml:space="preserve">0.714886486530304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.702377557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705504715442657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735526144504547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.740529775619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.744282484054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748660564422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.738027989864349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750536978244781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754289627075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768049478530884</t>
   </si>
   <si>
     <t xml:space="preserve">0.757416844367981</t>
@@ -251,82 +251,82 @@
     <t xml:space="preserve">0.766798496246338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.752413332462311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781183779239655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778056740760803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786187410354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77930760383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768674969673157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755540549755096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.760544061660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.764296770095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770551204681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7592933177948</t>
+    <t xml:space="preserve">0.752413272857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781183898448944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778056561946869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786187469959259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779307544231415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768674790859222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755540430545807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.760544240474701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76429682970047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770551145076752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759293079376221</t>
   </si>
   <si>
     <t xml:space="preserve">0.769925892353058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.761169493198395</t>
+    <t xml:space="preserve">0.76116955280304</t>
   </si>
   <si>
     <t xml:space="preserve">0.767424046993256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.747409760951996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751787841320038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754915058612823</t>
+    <t xml:space="preserve">0.747409701347351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751787781715393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754914999008179</t>
   </si>
   <si>
     <t xml:space="preserve">0.781809329986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801198124885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804950714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799321889877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785561978816986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796820104122162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791816592216492</t>
+    <t xml:space="preserve">0.801198184490204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804950833320618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79932177066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785561919212341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796820044517517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791816473007202</t>
   </si>
   <si>
     <t xml:space="preserve">0.801823616027832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.733649730682373</t>
+    <t xml:space="preserve">0.733649909496307</t>
   </si>
   <si>
     <t xml:space="preserve">0.725519061088562</t>
@@ -335,73 +335,73 @@
     <t xml:space="preserve">0.766306400299072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.759828686714172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750760078430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778613984584808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703473210334778</t>
+    <t xml:space="preserve">0.759828805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750760197639465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778613924980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703473150730133</t>
   </si>
   <si>
     <t xml:space="preserve">0.692461252212524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.705416560173035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.730031549930573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763067662715912</t>
+    <t xml:space="preserve">0.70541650056839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.730031609535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763067722320557</t>
   </si>
   <si>
     <t xml:space="preserve">0.762419939041138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769545257091522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75788539648056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742986798286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742339074611664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.758533418178558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77731841802597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77407968044281</t>
+    <t xml:space="preserve">0.769545197486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757885456085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742986857891083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742339193820953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758533358573914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77731853723526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774079620838165</t>
   </si>
   <si>
     <t xml:space="preserve">0.776022911071777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783796191215515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779909610748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79027384519577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789625942707062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794160306453705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805172264575958</t>
+    <t xml:space="preserve">0.783796072006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779909551143646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790273785591125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789626002311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79416024684906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805172502994537</t>
   </si>
   <si>
     <t xml:space="preserve">0.807763516902924</t>
@@ -410,25 +410,25 @@
     <t xml:space="preserve">0.822661936283112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817479968070984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820718765258789</t>
+    <t xml:space="preserve">0.817479848861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820718586444855</t>
   </si>
   <si>
     <t xml:space="preserve">0.822014391422272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809706747531891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814241051673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816184401512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804524660110474</t>
+    <t xml:space="preserve">0.809706807136536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814241111278534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816184341907501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804524600505829</t>
   </si>
   <si>
     <t xml:space="preserve">0.801285684108734</t>
@@ -437,100 +437,100 @@
     <t xml:space="preserve">0.812945544719696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801933586597443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786387264728546</t>
+    <t xml:space="preserve">0.801933646202087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786387205123901</t>
   </si>
   <si>
     <t xml:space="preserve">0.788330495357513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77148848772049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783148348331451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782500684261322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781852841377258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770193040370941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785091757774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795455873012543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811002314090729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794808149337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796103715896606</t>
+    <t xml:space="preserve">0.771488547325134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783148288726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782500565052032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781852781772614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770193099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785091638565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795456051826477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811002254486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794808089733124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796103656291962</t>
   </si>
   <si>
     <t xml:space="preserve">0.798694729804993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.802581369876862</t>
+    <t xml:space="preserve">0.802581310272217</t>
   </si>
   <si>
     <t xml:space="preserve">0.790921568870544</t>
   </si>
   <si>
-    <t xml:space="preserve">0.796751499176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799342393875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81035453081131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78055727481842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784443795681</t>
+    <t xml:space="preserve">0.796751320362091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799342513084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81035441160202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780557334423065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784443855285645</t>
   </si>
   <si>
     <t xml:space="preserve">0.785739362239838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.82719624042511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81359326839447</t>
+    <t xml:space="preserve">0.827196300029755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813593447208405</t>
   </si>
   <si>
     <t xml:space="preserve">0.80063796043396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.797399282455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803876876831055</t>
+    <t xml:space="preserve">0.7973992228508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803876996040344</t>
   </si>
   <si>
     <t xml:space="preserve">0.807115793228149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.761124312877655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770840883255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73132711648941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735861420631409</t>
+    <t xml:space="preserve">0.761124432086945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77084082365036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.731327056884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735861599445343</t>
   </si>
   <si>
     <t xml:space="preserve">0.720315158367157</t>
@@ -548,19 +548,19 @@
     <t xml:space="preserve">0.696995556354523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.709950923919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713837444782257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.711894094944</t>
+    <t xml:space="preserve">0.709950864315033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713837504386902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71189421415329</t>
   </si>
   <si>
     <t xml:space="preserve">0.707359790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.728736042976379</t>
+    <t xml:space="preserve">0.728736162185669</t>
   </si>
   <si>
     <t xml:space="preserve">0.715780794620514</t>
@@ -572,52 +572,52 @@
     <t xml:space="preserve">0.765010952949524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.7546466588974</t>
+    <t xml:space="preserve">0.754646718502045</t>
   </si>
   <si>
     <t xml:space="preserve">0.755294442176819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.787682712078094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776670813560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772136390209198</t>
+    <t xml:space="preserve">0.78768265247345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776670694351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772136449813843</t>
   </si>
   <si>
     <t xml:space="preserve">0.78703498840332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81683224439621</t>
+    <t xml:space="preserve">0.816832184791565</t>
   </si>
   <si>
     <t xml:space="preserve">0.819423198699951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799990296363831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824605345726013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838856041431427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831730902194977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832378506660461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840151846408844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848572671413422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841447234153748</t>
+    <t xml:space="preserve">0.799990236759186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824605226516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838856160640717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831730842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832378566265106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840151906013489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848572552204132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841447293758392</t>
   </si>
   <si>
     <t xml:space="preserve">0.844686031341553</t>
@@ -626,46 +626,46 @@
     <t xml:space="preserve">0.830435216426849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.798046886920929</t>
+    <t xml:space="preserve">0.798046946525574</t>
   </si>
   <si>
     <t xml:space="preserve">0.815536558628082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.82007110118866</t>
+    <t xml:space="preserve">0.82007098197937</t>
   </si>
   <si>
     <t xml:space="preserve">0.806467890739441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.811650097370148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836265087127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844038426876068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837560534477234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836912989616394</t>
+    <t xml:space="preserve">0.811650037765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83626514673233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844038307666779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837560594081879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836912870407104</t>
   </si>
   <si>
     <t xml:space="preserve">0.821366608142853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.828492045402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825900793075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829139769077301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84662926197052</t>
+    <t xml:space="preserve">0.828491985797882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825900912284851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829139590263367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84662938117981</t>
   </si>
   <si>
     <t xml:space="preserve">0.849220454692841</t>
@@ -674,187 +674,187 @@
     <t xml:space="preserve">0.864766895771027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867357790470123</t>
+    <t xml:space="preserve">0.867357850074768</t>
   </si>
   <si>
     <t xml:space="preserve">0.868005692958832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.870596706867218</t>
+    <t xml:space="preserve">0.870596647262573</t>
   </si>
   <si>
     <t xml:space="preserve">0.857641279697418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.865414500236511</t>
+    <t xml:space="preserve">0.865414559841156</t>
   </si>
   <si>
     <t xml:space="preserve">0.866710126399994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.853107035160065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855698049068451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858289241790771</t>
+    <t xml:space="preserve">0.853106915950775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85569816827774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858289361000061</t>
   </si>
   <si>
     <t xml:space="preserve">0.860232532024384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872540056705475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874483168125153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887438774108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893916189670563</t>
+    <t xml:space="preserve">0.872539877891541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874483346939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887438595294952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893916368484497</t>
   </si>
   <si>
     <t xml:space="preserve">0.892620742321014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912701368331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909462451934814</t>
+    <t xml:space="preserve">0.912701487541199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909462630748749</t>
   </si>
   <si>
     <t xml:space="preserve">0.908167123794556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919826745986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91853129863739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875778913497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877722024917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891972959041595</t>
+    <t xml:space="preserve">0.919826805591583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91853141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875778794288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877722144126892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.891972899436951</t>
   </si>
   <si>
     <t xml:space="preserve">0.884847581386566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895211696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884199857711792</t>
+    <t xml:space="preserve">0.895211815834045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884199738502502</t>
   </si>
   <si>
     <t xml:space="preserve">0.876426577568054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.862175703048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856346011161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882256507873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899098455905914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890677511692047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926952183246613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915292501449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917235732078552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966465830802917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95804488658905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965170323848724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961283683776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963227033615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94185084104538</t>
+    <t xml:space="preserve">0.862175762653351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856345891952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882256627082825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899098336696625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890677392482758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926952302455902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915292382240295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917235851287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966466069221497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958044946193695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965170562267303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961283802986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963227152824402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941850900650024</t>
   </si>
   <si>
     <t xml:space="preserve">0.941203057765961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958692908287048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982278347015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988308608531952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997019052505493</t>
+    <t xml:space="preserve">0.958692848682404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982278227806091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988308429718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997019171714783</t>
   </si>
   <si>
     <t xml:space="preserve">1.00036919116974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992998898029327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96820729970932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981608092784882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986298501491547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988978505134583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989648520946503</t>
+    <t xml:space="preserve">0.992998778820038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96820741891861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981608152389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986298263072968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988978624343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989648640155792</t>
   </si>
   <si>
     <t xml:space="preserve">0.97490781545639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999699175357819</t>
+    <t xml:space="preserve">0.999699294567108</t>
   </si>
   <si>
     <t xml:space="preserve">1.00505948066711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998359203338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997689068317413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00170934200287</t>
+    <t xml:space="preserve">0.998359262943268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997689127922058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00170946121216</t>
   </si>
   <si>
     <t xml:space="preserve">1.00706958770752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02047038078308</t>
+    <t xml:space="preserve">1.02047061920166</t>
   </si>
   <si>
     <t xml:space="preserve">1.02985107898712</t>
@@ -863,46 +863,46 @@
     <t xml:space="preserve">1.0177903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995009064674377</t>
+    <t xml:space="preserve">0.995008826255798</t>
   </si>
   <si>
     <t xml:space="preserve">0.999029219150543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.976917743682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.974237680435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970217406749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965527176856995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960836887359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961507022380829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964187145233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980268120765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978928089141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984958350658417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972897589206696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960166752338409</t>
+    <t xml:space="preserve">0.976917803287506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.974237740039825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970217347145081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965527236461639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96083676815033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96150678396225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964187204837799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980268061161041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978927969932556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984958291053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97289776802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960166931152344</t>
   </si>
   <si>
     <t xml:space="preserve">0.958826839923859</t>
@@ -914,25 +914,25 @@
     <t xml:space="preserve">0.955476582050323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949446201324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963517010211945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950116217136383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953466594219208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956816732883453</t>
+    <t xml:space="preserve">0.949446260929108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963517069816589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950116336345673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953466475009918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956816494464874</t>
   </si>
   <si>
     <t xml:space="preserve">0.958156764507294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952796459197998</t>
+    <t xml:space="preserve">0.952796399593353</t>
   </si>
   <si>
     <t xml:space="preserve">0.962176978588104</t>
@@ -941,79 +941,79 @@
     <t xml:space="preserve">0.944755852222443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931355178356171</t>
+    <t xml:space="preserve">0.931355237960815</t>
   </si>
   <si>
     <t xml:space="preserve">0.948106169700623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954136610031128</t>
+    <t xml:space="preserve">0.954136490821838</t>
   </si>
   <si>
     <t xml:space="preserve">0.957486748695374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939395606517792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946766078472137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934705436229706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928675055503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924654722213745</t>
+    <t xml:space="preserve">0.939395666122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946765959262848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934705376625061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92867511510849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924654901027679</t>
   </si>
   <si>
     <t xml:space="preserve">0.932695209980011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945426046848297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959496974945068</t>
+    <t xml:space="preserve">0.945426106452942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959496915340424</t>
   </si>
   <si>
     <t xml:space="preserve">0.973567605018616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978258073329926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993668913841248</t>
+    <t xml:space="preserve">0.978257954120636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993668854236603</t>
   </si>
   <si>
     <t xml:space="preserve">0.984288275241852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983618378639221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994338929653168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977587938308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980938076972961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972227573394775</t>
+    <t xml:space="preserve">0.983618319034576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994338870048523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977587878704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980938136577606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972227513790131</t>
   </si>
   <si>
     <t xml:space="preserve">0.96619725227356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969547510147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96887731552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971557557582855</t>
+    <t xml:space="preserve">0.969547390937805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968877375125885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971557438373566</t>
   </si>
   <si>
     <t xml:space="preserve">0.995678961277008</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">0.992328703403473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96686726808548</t>
+    <t xml:space="preserve">0.966867327690125</t>
   </si>
   <si>
     <t xml:space="preserve">1.02114045619965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01041972637177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01444005966187</t>
+    <t xml:space="preserve">1.01041984558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01444017887115</t>
   </si>
   <si>
     <t xml:space="preserve">1.02181053161621</t>
@@ -1040,10 +1040,10 @@
     <t xml:space="preserve">1.02382063865662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0285108089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03320133686066</t>
+    <t xml:space="preserve">1.02851092815399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03320121765137</t>
   </si>
   <si>
     <t xml:space="preserve">1.03923153877258</t>
@@ -1052,13 +1052,13 @@
     <t xml:space="preserve">1.0265007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05531251430511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05866277217865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04459190368652</t>
+    <t xml:space="preserve">1.05531239509583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05866265296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04459202289581</t>
   </si>
   <si>
     <t xml:space="preserve">1.05330240726471</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">1.0680433511734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0727334022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08613443374634</t>
+    <t xml:space="preserve">1.07273364067078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08613431453705</t>
   </si>
   <si>
     <t xml:space="preserve">1.0955148935318</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">1.08211410045624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05397248268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06000292301178</t>
+    <t xml:space="preserve">1.05397236347198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06000280380249</t>
   </si>
   <si>
     <t xml:space="preserve">1.04392182826996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04861223697662</t>
+    <t xml:space="preserve">1.04861211776733</t>
   </si>
   <si>
     <t xml:space="preserve">1.04660189151764</t>
@@ -1100,25 +1100,25 @@
     <t xml:space="preserve">1.03990149497986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04258167743683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01980030536652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.015780210495</t>
+    <t xml:space="preserve">1.04258179664612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01980042457581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01578009128571</t>
   </si>
   <si>
     <t xml:space="preserve">1.05196237564087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06737327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06603300571442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02449071407318</t>
+    <t xml:space="preserve">1.06737315654755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06603312492371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02449059486389</t>
   </si>
   <si>
     <t xml:space="preserve">1.01846027374268</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">1.02784085273743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05665266513824</t>
+    <t xml:space="preserve">1.05665254592896</t>
   </si>
   <si>
     <t xml:space="preserve">1.06134271621704</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">1.07943391799927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06938314437866</t>
+    <t xml:space="preserve">1.06938326358795</t>
   </si>
   <si>
     <t xml:space="preserve">1.05933272838593</t>
@@ -1151,19 +1151,19 @@
     <t xml:space="preserve">1.02683579921722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03588128089905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04191160202026</t>
+    <t xml:space="preserve">1.03588151931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04191172122955</t>
   </si>
   <si>
     <t xml:space="preserve">0.996349036693573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971222519874573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995343863964081</t>
+    <t xml:space="preserve">0.971222460269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995343923568726</t>
   </si>
   <si>
     <t xml:space="preserve">0.944420874118805</t>
@@ -1172,31 +1172,31 @@
     <t xml:space="preserve">0.953131496906281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941405773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959831953048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94643098115921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957821667194366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950451374053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936380445957184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967202365398407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991323709487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975577831268311</t>
+    <t xml:space="preserve">0.941405892372131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959831774234772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946431219577789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957821607589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950451254844666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936380505561829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967202305793762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991323590278625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975577712059021</t>
   </si>
   <si>
     <t xml:space="preserve">0.993333876132965</t>
@@ -1205,16 +1205,16 @@
     <t xml:space="preserve">1.00003409385681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00137436389923</t>
+    <t xml:space="preserve">1.00137448310852</t>
   </si>
   <si>
     <t xml:space="preserve">0.991658806800842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00673460960388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999364256858826</t>
+    <t xml:space="preserve">1.00673472881317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999364197254181</t>
   </si>
   <si>
     <t xml:space="preserve">1.04023659229279</t>
@@ -1229,25 +1229,25 @@
     <t xml:space="preserve">1.04961705207825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04995214939117</t>
+    <t xml:space="preserve">1.04995226860046</t>
   </si>
   <si>
     <t xml:space="preserve">1.06268286705017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07206344604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05832767486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06335306167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07407355308533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08043897151947</t>
+    <t xml:space="preserve">1.0720636844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05832755565643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06335294246674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07407367229462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08043885231018</t>
   </si>
   <si>
     <t xml:space="preserve">1.08546423912048</t>
@@ -1256,25 +1256,25 @@
     <t xml:space="preserve">1.09048974514008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09484481811523</t>
+    <t xml:space="preserve">1.09484469890594</t>
   </si>
   <si>
     <t xml:space="preserve">1.09819507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0985301733017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12198138237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11762630939484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11729109287262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10724055767059</t>
+    <t xml:space="preserve">1.09853005409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12198150157928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11762607097626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11729121208191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10724067687988</t>
   </si>
   <si>
     <t xml:space="preserve">1.10757565498352</t>
@@ -1286,25 +1286,25 @@
     <t xml:space="preserve">1.13002192974091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10992097854614</t>
+    <t xml:space="preserve">1.10992074012756</t>
   </si>
   <si>
     <t xml:space="preserve">1.11829626560211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05732274055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03387129306793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03895282745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05287504196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04208540916443</t>
+    <t xml:space="preserve">1.05732262134552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03387117385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03895270824432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05287528038025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04208528995514</t>
   </si>
   <si>
     <t xml:space="preserve">1.04730618000031</t>
@@ -1313,43 +1313,43 @@
     <t xml:space="preserve">1.02572667598724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00693166255951</t>
+    <t xml:space="preserve">1.00693154335022</t>
   </si>
   <si>
     <t xml:space="preserve">0.980827152729034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998926281929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01076018810272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00484323501587</t>
+    <t xml:space="preserve">0.998926043510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01076030731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00484335422516</t>
   </si>
   <si>
     <t xml:space="preserve">1.02920722961426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00936794281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00658333301544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999622285366058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968993306159973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01598107814789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02398645877838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03164374828339</t>
+    <t xml:space="preserve">1.00936782360077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00658357143402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999622344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968993127346039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01598119735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02398633956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0316436290741</t>
   </si>
   <si>
     <t xml:space="preserve">1.02851116657257</t>
@@ -1358,19 +1358,19 @@
     <t xml:space="preserve">1.01980972290039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04382574558258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04661011695862</t>
+    <t xml:space="preserve">1.04382562637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04661023616791</t>
   </si>
   <si>
     <t xml:space="preserve">1.02363836765289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02537870407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00588738918304</t>
+    <t xml:space="preserve">1.02537858486176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00588750839233</t>
   </si>
   <si>
     <t xml:space="preserve">1.01250052452087</t>
@@ -1379,34 +1379,34 @@
     <t xml:space="preserve">1.02120196819305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02642285823822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03373217582703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01389265060425</t>
+    <t xml:space="preserve">1.02642273902893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03373193740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01389276981354</t>
   </si>
   <si>
     <t xml:space="preserve">1.03860485553741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05113482475281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06122851371765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07236647605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06018435955048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06262063980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05600762367249</t>
+    <t xml:space="preserve">1.0511349439621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06122863292694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07236659526825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06018447875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06262075901031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05600774288177</t>
   </si>
   <si>
     <t xml:space="preserve">1.07375872135162</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">1.0786315202713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09290194511414</t>
+    <t xml:space="preserve">1.09290182590485</t>
   </si>
   <si>
     <t xml:space="preserve">1.09429407119751</t>
@@ -1430,19 +1430,19 @@
     <t xml:space="preserve">1.08420038223267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04835057258606</t>
+    <t xml:space="preserve">1.04835045337677</t>
   </si>
   <si>
     <t xml:space="preserve">1.06157660484314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07201838493347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07584702968597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07132232189178</t>
+    <t xml:space="preserve">1.07201826572418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07584726810455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0713222026825</t>
   </si>
   <si>
     <t xml:space="preserve">1.09394598007202</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">1.08106791973114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09011733531952</t>
+    <t xml:space="preserve">1.09011745452881</t>
   </si>
   <si>
     <t xml:space="preserve">1.08246004581451</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">1.12387895584106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10473597049713</t>
+    <t xml:space="preserve">1.10473585128784</t>
   </si>
   <si>
     <t xml:space="preserve">1.10612809658051</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">1.10821640491486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10960876941681</t>
+    <t xml:space="preserve">1.10960865020752</t>
   </si>
   <si>
     <t xml:space="preserve">1.08837711811066</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">1.07549893856049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06540536880493</t>
+    <t xml:space="preserve">1.06540524959564</t>
   </si>
   <si>
     <t xml:space="preserve">1.03338408470154</t>
@@ -1502,73 +1502,73 @@
     <t xml:space="preserve">1.04243338108063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02155005931854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03094744682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04173731803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05705177783966</t>
+    <t xml:space="preserve">1.02154994010925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03094756603241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04173743724823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05705189704895</t>
   </si>
   <si>
     <t xml:space="preserve">1.07897937297821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09220576286316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09116148948669</t>
+    <t xml:space="preserve">1.09220564365387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09116160869598</t>
   </si>
   <si>
     <t xml:space="preserve">1.08454847335815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08141601085663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0984708070755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09603428840637</t>
+    <t xml:space="preserve">1.08141589164734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09847068786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09603440761566</t>
   </si>
   <si>
     <t xml:space="preserve">1.07619512081146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07445466518402</t>
+    <t xml:space="preserve">1.07445478439331</t>
   </si>
   <si>
     <t xml:space="preserve">1.05879211425781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07758736610413</t>
+    <t xml:space="preserve">1.07758724689484</t>
   </si>
   <si>
     <t xml:space="preserve">1.06923389434814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04069316387177</t>
+    <t xml:space="preserve">1.04069328308105</t>
   </si>
   <si>
     <t xml:space="preserve">1.03199172019958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04452180862427</t>
+    <t xml:space="preserve">1.04452168941498</t>
   </si>
   <si>
     <t xml:space="preserve">1.04417371749878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05183100700378</t>
+    <t xml:space="preserve">1.05183112621307</t>
   </si>
   <si>
     <t xml:space="preserve">1.03616833686829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05844402313232</t>
+    <t xml:space="preserve">1.05844414234161</t>
   </si>
   <si>
     <t xml:space="preserve">1.03442811965942</t>
@@ -1577,100 +1577,100 @@
     <t xml:space="preserve">1.00310277938843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99161696434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00832366943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01424074172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01772153377533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01354467868805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993705451488495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988136351108551</t>
+    <t xml:space="preserve">0.991617023944855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00832378864288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01424062252045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01772117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01354455947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993705213069916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98813658952713</t>
   </si>
   <si>
     <t xml:space="preserve">0.97734671831131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00553929805756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986047983169556</t>
+    <t xml:space="preserve">1.00553941726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9860480427742</t>
   </si>
   <si>
     <t xml:space="preserve">0.989528715610504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992313086986542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98291540145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991965115070343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01319646835327</t>
+    <t xml:space="preserve">0.992313206195831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982915580272675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991965055465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01319658756256</t>
   </si>
   <si>
     <t xml:space="preserve">1.00414705276489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02050590515137</t>
+    <t xml:space="preserve">1.02050566673279</t>
   </si>
   <si>
     <t xml:space="preserve">1.0156329870224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03512418270111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0393009185791</t>
+    <t xml:space="preserve">1.0351243019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03930103778839</t>
   </si>
   <si>
     <t xml:space="preserve">1.05252707004547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05461537837982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03721272945404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02711892127991</t>
+    <t xml:space="preserve">1.05461549758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03721261024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0271190404892</t>
   </si>
   <si>
     <t xml:space="preserve">1.03999698162079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06610131263733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06088054180145</t>
+    <t xml:space="preserve">1.06610143184662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06088066101074</t>
   </si>
   <si>
     <t xml:space="preserve">1.04034519195557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03233993053436</t>
+    <t xml:space="preserve">1.03233981132507</t>
   </si>
   <si>
     <t xml:space="preserve">1.04278159141541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04347777366638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07410669326782</t>
+    <t xml:space="preserve">1.04347765445709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07410657405853</t>
   </si>
   <si>
     <t xml:space="preserve">1.10090720653534</t>
@@ -1679,10 +1679,10 @@
     <t xml:space="preserve">1.11761391162872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12701141834259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11378526687622</t>
+    <t xml:space="preserve">1.12701153755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1137855052948</t>
   </si>
   <si>
     <t xml:space="preserve">1.1064760684967</t>
@@ -1691,16 +1691,16 @@
     <t xml:space="preserve">1.12318289279938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13118827342987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1144814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08872509002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.094642162323</t>
+    <t xml:space="preserve">1.13118815422058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11448156833649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08872520923615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09464204311371</t>
   </si>
   <si>
     <t xml:space="preserve">1.11622166633606</t>
@@ -1709,28 +1709,28 @@
     <t xml:space="preserve">1.1183100938797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13501679897308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13675725460052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1381493806839</t>
+    <t xml:space="preserve">1.13501691818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13675701618195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13814949989319</t>
   </si>
   <si>
     <t xml:space="preserve">1.14302217960358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10403966903687</t>
+    <t xml:space="preserve">1.10403978824615</t>
   </si>
   <si>
     <t xml:space="preserve">1.10891258716583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09951496124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10195136070251</t>
+    <t xml:space="preserve">1.09951484203339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10195124149323</t>
   </si>
   <si>
     <t xml:space="preserve">1.09916687011719</t>
@@ -1742,19 +1742,19 @@
     <t xml:space="preserve">1.10578000545502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09185779094696</t>
+    <t xml:space="preserve">1.09185767173767</t>
   </si>
   <si>
     <t xml:space="preserve">1.07793533802032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08071970939636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08663690090179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06227266788483</t>
+    <t xml:space="preserve">1.08071994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08663666248322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06227278709412</t>
   </si>
   <si>
     <t xml:space="preserve">1.08280813694</t>
@@ -1763,22 +1763,22 @@
     <t xml:space="preserve">1.09742665290833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10021102428436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09777474403381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10369181632996</t>
+    <t xml:space="preserve">1.10021114349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09777462482452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10369169712067</t>
   </si>
   <si>
     <t xml:space="preserve">1.11100077629089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10543191432953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08594059944153</t>
+    <t xml:space="preserve">1.10543215274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08594071865082</t>
   </si>
   <si>
     <t xml:space="preserve">1.09568619728088</t>
@@ -1790,16 +1790,16 @@
     <t xml:space="preserve">1.11726582050323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12074649333954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10752010345459</t>
+    <t xml:space="preserve">1.12074661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10752034187317</t>
   </si>
   <si>
     <t xml:space="preserve">1.1103048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12179052829742</t>
+    <t xml:space="preserve">1.12179064750671</t>
   </si>
   <si>
     <t xml:space="preserve">1.11935424804688</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">1.13571298122406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13536500930786</t>
+    <t xml:space="preserve">1.13536489009857</t>
   </si>
   <si>
     <t xml:space="preserve">1.13084030151367</t>
@@ -1823,13 +1823,13 @@
     <t xml:space="preserve">1.06331694126129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05391931533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04626202583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05426740646362</t>
+    <t xml:space="preserve">1.05391943454742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04626214504242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05426728725433</t>
   </si>
   <si>
     <t xml:space="preserve">1.04869854450226</t>
@@ -1838,16 +1838,16 @@
     <t xml:space="preserve">1.02433443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0194616317749</t>
+    <t xml:space="preserve">1.01946151256561</t>
   </si>
   <si>
     <t xml:space="preserve">1.01632916927338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00379908084869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997882068157196</t>
+    <t xml:space="preserve">1.0037989616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997882187366486</t>
   </si>
   <si>
     <t xml:space="preserve">1.00727963447571</t>
@@ -1859,31 +1859,31 @@
     <t xml:space="preserve">1.07654309272766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08517634868622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09720540046692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09647631645203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0662214756012</t>
+    <t xml:space="preserve">1.08517646789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09720551967621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09647643566132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06622135639191</t>
   </si>
   <si>
     <t xml:space="preserve">1.08116674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07205379009247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06038916110992</t>
+    <t xml:space="preserve">1.07205367088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06038904190063</t>
   </si>
   <si>
     <t xml:space="preserve">1.05127608776093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06403434276581</t>
+    <t xml:space="preserve">1.06403422355652</t>
   </si>
   <si>
     <t xml:space="preserve">1.07168924808502</t>
@@ -1895,10 +1895,10 @@
     <t xml:space="preserve">1.0979346036911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0986635684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10449588298798</t>
+    <t xml:space="preserve">1.09866344928741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10449600219727</t>
   </si>
   <si>
     <t xml:space="preserve">1.10048627853394</t>
@@ -1907,19 +1907,19 @@
     <t xml:space="preserve">1.10230875015259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09574735164642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09829902648926</t>
+    <t xml:space="preserve">1.095747590065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09829914569855</t>
   </si>
   <si>
     <t xml:space="preserve">1.13219952583313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12563812732697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14021897315979</t>
+    <t xml:space="preserve">1.12563824653625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1402188539505</t>
   </si>
   <si>
     <t xml:space="preserve">1.14750933647156</t>
@@ -1928,49 +1928,49 @@
     <t xml:space="preserve">1.13584470748901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11944127082825</t>
+    <t xml:space="preserve">1.11944139003754</t>
   </si>
   <si>
     <t xml:space="preserve">1.11543154716492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10376691818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11251533031464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11069273948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13511574268341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15006101131439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15188360214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14787375926971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15261268615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16427731513977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1704740524292</t>
+    <t xml:space="preserve">1.10376703739166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11251544952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11069285869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13511562347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15006077289581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15188348293304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.147873878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15261256694794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16427719593048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17047417163849</t>
   </si>
   <si>
     <t xml:space="preserve">1.17156767845154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17229688167572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17849361896515</t>
+    <t xml:space="preserve">1.17229676246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17849373817444</t>
   </si>
   <si>
     <t xml:space="preserve">1.17484831809998</t>
@@ -1982,19 +1982,19 @@
     <t xml:space="preserve">1.16318368911743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16609966754913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17995166778564</t>
+    <t xml:space="preserve">1.16609978675842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17995154857635</t>
   </si>
   <si>
     <t xml:space="preserve">1.18469047546387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18104529380798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17120313644409</t>
+    <t xml:space="preserve">1.1810450553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17120325565338</t>
   </si>
   <si>
     <t xml:space="preserve">1.17375481128693</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">1.16209018230438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1668289899826</t>
+    <t xml:space="preserve">1.16682887077332</t>
   </si>
   <si>
     <t xml:space="preserve">1.16755795478821</t>
@@ -2042,19 +2042,19 @@
     <t xml:space="preserve">1.15297710895538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13985443115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13475108146667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16391277313232</t>
+    <t xml:space="preserve">1.13985455036163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13475120067596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16391265392303</t>
   </si>
   <si>
     <t xml:space="preserve">1.16938054561615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16573536396027</t>
+    <t xml:space="preserve">1.16573524475098</t>
   </si>
   <si>
     <t xml:space="preserve">1.16500627994537</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">1.18833565711975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20473897457123</t>
+    <t xml:space="preserve">1.20473885536194</t>
   </si>
   <si>
     <t xml:space="preserve">1.20036470890045</t>
@@ -2072,13 +2072,13 @@
     <t xml:space="preserve">1.18870007991791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17958724498749</t>
+    <t xml:space="preserve">1.1795871257782</t>
   </si>
   <si>
     <t xml:space="preserve">1.16464173793793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17922246456146</t>
+    <t xml:space="preserve">1.17922258377075</t>
   </si>
   <si>
     <t xml:space="preserve">1.18213880062103</t>
@@ -2087,28 +2087,28 @@
     <t xml:space="preserve">1.17630636692047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19599044322968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18979382514954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22551667690277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21567475795746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22770380973816</t>
+    <t xml:space="preserve">1.19599032402039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18979358673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22551679611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21567463874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22770369052887</t>
   </si>
   <si>
     <t xml:space="preserve">1.23207807540894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21421658992767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21166491508484</t>
+    <t xml:space="preserve">1.21421670913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21166479587555</t>
   </si>
   <si>
     <t xml:space="preserve">1.23134899139404</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">1.21603906154633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21931993961334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23791015148163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23462975025177</t>
+    <t xml:space="preserve">1.21931982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2379105091095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23462986946106</t>
   </si>
   <si>
     <t xml:space="preserve">1.22806835174561</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">1.22187149524689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22114241123199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22405850887299</t>
+    <t xml:space="preserve">1.22114229202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22405862808228</t>
   </si>
   <si>
     <t xml:space="preserve">1.23061990737915</t>
@@ -2150,10 +2150,10 @@
     <t xml:space="preserve">1.22843277454376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23645234107971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2287974357605</t>
+    <t xml:space="preserve">1.23645222187042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22879731655121</t>
   </si>
   <si>
     <t xml:space="preserve">1.22624564170837</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">1.27363324165344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27691411972046</t>
+    <t xml:space="preserve">1.27691400051117</t>
   </si>
   <si>
     <t xml:space="preserve">1.31154346466064</t>
@@ -2177,16 +2177,16 @@
     <t xml:space="preserve">1.30826270580292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31591761112213</t>
+    <t xml:space="preserve">1.31591749191284</t>
   </si>
   <si>
     <t xml:space="preserve">1.29331743717194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31518864631653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31445956230164</t>
+    <t xml:space="preserve">1.31518852710724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31445932388306</t>
   </si>
   <si>
     <t xml:space="preserve">1.30862724781036</t>
@@ -2195,19 +2195,19 @@
     <t xml:space="preserve">1.29732716083527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27873647212982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.288578748703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28420424461365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27727842330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27509117126465</t>
+    <t xml:space="preserve">1.27873659133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28857862949371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28420436382294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27727854251862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27509140968323</t>
   </si>
   <si>
     <t xml:space="preserve">1.26452040672302</t>
@@ -2216,40 +2216,40 @@
     <t xml:space="preserve">1.24884593486786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24665868282318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25249111652374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24520063400269</t>
+    <t xml:space="preserve">1.24665892124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25249099731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24520075321198</t>
   </si>
   <si>
     <t xml:space="preserve">1.24483621120453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19052278995514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1963552236557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19854211807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19343888759613</t>
+    <t xml:space="preserve">1.19052267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19635510444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19854235649109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19343876838684</t>
   </si>
   <si>
     <t xml:space="preserve">1.18068063259125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20218741893768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18906462192535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19270992279053</t>
+    <t xml:space="preserve">1.20218729972839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18906450271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19270980358124</t>
   </si>
   <si>
     <t xml:space="preserve">1.20656156539917</t>
@@ -2258,22 +2258,22 @@
     <t xml:space="preserve">1.20729064941406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22515225410461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24155557155609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23353612422943</t>
+    <t xml:space="preserve">1.22515201568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2415554523468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23353624343872</t>
   </si>
   <si>
     <t xml:space="preserve">1.2189553976059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21275854110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2083842754364</t>
+    <t xml:space="preserve">1.2127583026886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20838415622711</t>
   </si>
   <si>
     <t xml:space="preserve">1.25504279136658</t>
@@ -2285,10 +2285,10 @@
     <t xml:space="preserve">1.25941705703735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25650084018707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26852989196777</t>
+    <t xml:space="preserve">1.25650072097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26853001117706</t>
   </si>
   <si>
     <t xml:space="preserve">1.2998788356781</t>
@@ -2300,34 +2300,34 @@
     <t xml:space="preserve">1.29368197917938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29222393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30607545375824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3520051240921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34544384479523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33414375782013</t>
+    <t xml:space="preserve">1.2922238111496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30607569217682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35200536251068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34544372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33414351940155</t>
   </si>
   <si>
     <t xml:space="preserve">1.31409513950348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32247912883759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32940495014191</t>
+    <t xml:space="preserve">1.3224790096283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32940483093262</t>
   </si>
   <si>
     <t xml:space="preserve">1.34580826759338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33159208297729</t>
+    <t xml:space="preserve">1.33159196376801</t>
   </si>
   <si>
     <t xml:space="preserve">1.33013379573822</t>
@@ -2336,37 +2336,37 @@
     <t xml:space="preserve">1.34981799125671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34398567676544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3414341211319</t>
+    <t xml:space="preserve">1.34398579597473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34143424034119</t>
   </si>
   <si>
     <t xml:space="preserve">1.34945344924927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35893106460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36986660957336</t>
+    <t xml:space="preserve">1.35893094539642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36986649036407</t>
   </si>
   <si>
     <t xml:space="preserve">1.3822603225708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3603892326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34908902645111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26524937152863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25613629817963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13766717910767</t>
+    <t xml:space="preserve">1.36038911342621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34908890724182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26524949073792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25613641738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13766729831696</t>
   </si>
   <si>
     <t xml:space="preserve">1.15589332580566</t>
@@ -2375,109 +2375,109 @@
     <t xml:space="preserve">1.19708406925201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11579608917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996233522891998</t>
+    <t xml:space="preserve">1.11579620838165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996233463287354</t>
   </si>
   <si>
     <t xml:space="preserve">0.924787521362305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.905467987060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733049929141998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772782623767853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750546932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775334358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751276016235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754556715488434</t>
+    <t xml:space="preserve">0.905467927455902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733049988746643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772782683372498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750546872615814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775334239006042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751276075839996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754556596279144</t>
   </si>
   <si>
     <t xml:space="preserve">0.741433918476105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.729040265083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786270022392273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797205567359924</t>
+    <t xml:space="preserve">0.729040205478668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786269962787628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79720550775528</t>
   </si>
   <si>
     <t xml:space="preserve">0.793195843696594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778250455856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824544608592987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826002597808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816160559654236</t>
+    <t xml:space="preserve">0.778250396251678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824544489383698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826002657413483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816160619258881</t>
   </si>
   <si>
     <t xml:space="preserve">0.841677010059357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.836209118366241</t>
+    <t xml:space="preserve">0.836209177970886</t>
   </si>
   <si>
     <t xml:space="preserve">0.869015991687775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869744896888733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855164110660553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876670956611633</t>
+    <t xml:space="preserve">0.869745016098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855164170265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876670837402344</t>
   </si>
   <si>
     <t xml:space="preserve">0.889429152011871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.885783910751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.897448480129242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910935878753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911664843559265</t>
+    <t xml:space="preserve">0.885783970355988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.897448539733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910935819149017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91166478395462</t>
   </si>
   <si>
     <t xml:space="preserve">0.883961260318756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888335585594177</t>
+    <t xml:space="preserve">0.888335406780243</t>
   </si>
   <si>
     <t xml:space="preserve">0.879587173461914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89015805721283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906926095485687</t>
+    <t xml:space="preserve">0.890158116817474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906926035881042</t>
   </si>
   <si>
     <t xml:space="preserve">0.901458323001862</t>
@@ -2492,37 +2492,37 @@
     <t xml:space="preserve">0.872296571731567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.879951655864716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878128826618195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882138729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877764463424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914581060409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934265196323395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911300361156464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944332540035248</t>
+    <t xml:space="preserve">0.879951536655426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878128945827484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882138609886169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877764403820038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914581000804901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93426501750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911300182342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944332599639893</t>
   </si>
   <si>
     <t xml:space="preserve">0.902750670909882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.914020538330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910522997379303</t>
+    <t xml:space="preserve">0.914020419120789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910523056983948</t>
   </si>
   <si>
     <t xml:space="preserve">0.912854731082916</t>
@@ -2531,91 +2531,91 @@
     <t xml:space="preserve">0.946275532245636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971146941184998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950550377368927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971535563468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969592273235321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981639444828033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00573348999023</t>
+    <t xml:space="preserve">0.971146881580353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950550258159637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971535444259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969592332839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981639504432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00573360919952</t>
   </si>
   <si>
     <t xml:space="preserve">1.04265189170837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04342901706696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03060472011566</t>
+    <t xml:space="preserve">1.04342913627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03060483932495</t>
   </si>
   <si>
     <t xml:space="preserve">1.05236721038818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02710723876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01195132732391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960265636444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956379532814026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978141963481903</t>
+    <t xml:space="preserve">1.02710735797882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0119514465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960265576839447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956379473209381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978141903877258</t>
   </si>
   <si>
     <t xml:space="preserve">1.01156270503998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01778054237366</t>
+    <t xml:space="preserve">1.01778042316437</t>
   </si>
   <si>
     <t xml:space="preserve">1.00961971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01933491230011</t>
+    <t xml:space="preserve">1.0193350315094</t>
   </si>
   <si>
     <t xml:space="preserve">1.01467168331146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972312808036804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963763117790222</t>
+    <t xml:space="preserve">0.97231262922287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963763177394867</t>
   </si>
   <si>
     <t xml:space="preserve">0.977364838123322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979696393013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984359860420227</t>
+    <t xml:space="preserve">0.979696333408356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984359800815582</t>
   </si>
   <si>
     <t xml:space="preserve">0.999904274940491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996795475482941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993686497211456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98319399356842</t>
+    <t xml:space="preserve">0.996795415878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993686378002167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983193933963776</t>
   </si>
   <si>
     <t xml:space="preserve">0.98280531167984</t>
@@ -2624,16 +2624,16 @@
     <t xml:space="preserve">0.958322584629059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961431443691254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960654258728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973867237567902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973089873790741</t>
+    <t xml:space="preserve">0.961431562900543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960654199123383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973867177963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973089933395386</t>
   </si>
   <si>
     <t xml:space="preserve">0.985137045383453</t>
@@ -2642,34 +2642,34 @@
     <t xml:space="preserve">0.987857341766357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985525667667389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949773013591766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954436480998993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970758259296417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928788065910339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943166673183441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95599091053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959877133369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953659236431122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965317666530609</t>
+    <t xml:space="preserve">0.985525608062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949773132801056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954436421394348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970758199691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92878794670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943166613578796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955990970134735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959877014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953659296035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965317606925964</t>
   </si>
   <si>
     <t xml:space="preserve">0.982028067111969</t>
@@ -2681,76 +2681,76 @@
     <t xml:space="preserve">1.00612211227417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994852304458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979307770729065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989411771297455</t>
+    <t xml:space="preserve">0.994852244853973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979307889938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989411652088165</t>
   </si>
   <si>
     <t xml:space="preserve">0.987079977989197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.964929103851318</t>
+    <t xml:space="preserve">0.964929044246674</t>
   </si>
   <si>
     <t xml:space="preserve">0.96259731054306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958711326122284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96609491109848</t>
+    <t xml:space="preserve">0.958711266517639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966094970703125</t>
   </si>
   <si>
     <t xml:space="preserve">0.951327443122864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954047858715057</t>
+    <t xml:space="preserve">0.954047739505768</t>
   </si>
   <si>
     <t xml:space="preserve">0.975033044815063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968037962913513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937726140022278</t>
+    <t xml:space="preserve">0.968038022518158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937726080417633</t>
   </si>
   <si>
     <t xml:space="preserve">0.946664273738861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938503265380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94200074672699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933451235294342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971924066543579</t>
+    <t xml:space="preserve">0.938503205776215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942000806331635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933451175689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971924185752869</t>
   </si>
   <si>
     <t xml:space="preserve">0.94899582862854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953270614147186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9458869099617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929565131664276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931119680404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900807797908783</t>
+    <t xml:space="preserve">0.953270673751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945886850357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929565191268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931119620800018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900807738304138</t>
   </si>
   <si>
     <t xml:space="preserve">0.903528034687042</t>
@@ -2759,97 +2759,97 @@
     <t xml:space="preserve">0.904693841934204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89886462688446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878656625747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886428892612457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901584923267365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886040329933167</t>
+    <t xml:space="preserve">0.898864567279816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878656685352325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886428952217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90158486366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886040389537811</t>
   </si>
   <si>
     <t xml:space="preserve">0.840961158275604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830079913139343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848344802856445</t>
+    <t xml:space="preserve">0.830079793930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848344743251801</t>
   </si>
   <si>
     <t xml:space="preserve">0.860780358314514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872050166130066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898476004600525</t>
+    <t xml:space="preserve">0.872050225734711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898476123809814</t>
   </si>
   <si>
     <t xml:space="preserve">0.892646729946136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.881376922130585</t>
+    <t xml:space="preserve">0.881377041339874</t>
   </si>
   <si>
     <t xml:space="preserve">0.94277811050415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93928050994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955213665962219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95249342918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947441458702087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952104806900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95948851108551</t>
+    <t xml:space="preserve">0.939280450344086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955213606357574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95249330997467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947441399097443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952104866504669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959488451480865</t>
   </si>
   <si>
     <t xml:space="preserve">0.97619891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01700341701508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02205526828766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993297874927521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982416689395905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975421547889709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976587414741516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997184097766876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990966200828552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988245844841003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984748363494873</t>
+    <t xml:space="preserve">1.01700353622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02205538749695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993297934532166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982416749000549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975421607494354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976587474346161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997183978557587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990966081619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988245904445648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984748244285583</t>
   </si>
   <si>
     <t xml:space="preserve">0.995629668235779</t>
@@ -2858,16 +2858,16 @@
     <t xml:space="preserve">0.954825103282928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00651073455811</t>
+    <t xml:space="preserve">1.0065108537674</t>
   </si>
   <si>
     <t xml:space="preserve">1.01583755016327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0138943195343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03449082374573</t>
+    <t xml:space="preserve">1.01389443874359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03449094295502</t>
   </si>
   <si>
     <t xml:space="preserve">1.02399837970734</t>
@@ -2876,22 +2876,22 @@
     <t xml:space="preserve">1.04148602485657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03954291343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03487944602966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01428294181824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03759980201721</t>
+    <t xml:space="preserve">1.03954303264618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03487956523895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01428306102753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0375999212265</t>
   </si>
   <si>
     <t xml:space="preserve">1.03215932846069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02050089836121</t>
+    <t xml:space="preserve">1.02050077915192</t>
   </si>
   <si>
     <t xml:space="preserve">1.03099346160889</t>
@@ -2903,70 +2903,70 @@
     <t xml:space="preserve">1.0729638338089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04653799533844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05897355079651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0535329580307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06169390678406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04498362541199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10871636867523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1363080739975</t>
+    <t xml:space="preserve">1.04653811454773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0589736700058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05353307723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06169402599335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04498338699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10871624946594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13630795478821</t>
   </si>
   <si>
     <t xml:space="preserve">1.15418422222137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12853574752808</t>
+    <t xml:space="preserve">1.12853562831879</t>
   </si>
   <si>
     <t xml:space="preserve">1.13825082778931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14252591133118</t>
+    <t xml:space="preserve">1.1425256729126</t>
   </si>
   <si>
     <t xml:space="preserve">1.17516922950745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16195642948151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13863956928253</t>
+    <t xml:space="preserve">1.16195631027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13863968849182</t>
   </si>
   <si>
     <t xml:space="preserve">1.12154054641724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13475346565247</t>
+    <t xml:space="preserve">1.13475358486176</t>
   </si>
   <si>
     <t xml:space="preserve">1.12698113918304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11415684223175</t>
+    <t xml:space="preserve">1.11415696144104</t>
   </si>
   <si>
     <t xml:space="preserve">1.10366427898407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11221396923065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0931715965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08384490013123</t>
+    <t xml:space="preserve">1.11221385002136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09317171573639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08384501934052</t>
   </si>
   <si>
     <t xml:space="preserve">1.11493408679962</t>
@@ -2978,31 +2978,31 @@
     <t xml:space="preserve">1.07918155193329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08656525611877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07723844051361</t>
+    <t xml:space="preserve">1.08656513690948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0772385597229</t>
   </si>
   <si>
     <t xml:space="preserve">1.10832762718201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13086748123169</t>
+    <t xml:space="preserve">1.1308673620224</t>
   </si>
   <si>
     <t xml:space="preserve">1.15262973308563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14874362945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15496146678925</t>
+    <t xml:space="preserve">1.14874351024628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15496134757996</t>
   </si>
   <si>
     <t xml:space="preserve">1.16312229633331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14563465118408</t>
+    <t xml:space="preserve">1.14563453197479</t>
   </si>
   <si>
     <t xml:space="preserve">1.15301835536957</t>
@@ -3011,22 +3011,22 @@
     <t xml:space="preserve">1.14641189575195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17089450359344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18954801559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20470380783081</t>
+    <t xml:space="preserve">1.17089462280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18954813480377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20470404624939</t>
   </si>
   <si>
     <t xml:space="preserve">1.20664703845978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21558523178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2175281047821</t>
+    <t xml:space="preserve">1.21558511257172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21752822399139</t>
   </si>
   <si>
     <t xml:space="preserve">1.20625841617584</t>
@@ -3047,31 +3047,31 @@
     <t xml:space="preserve">1.19809758663177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21286475658417</t>
+    <t xml:space="preserve">1.21286487579346</t>
   </si>
   <si>
     <t xml:space="preserve">1.21597385406494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21325349807739</t>
+    <t xml:space="preserve">1.21325361728668</t>
   </si>
   <si>
     <t xml:space="preserve">1.20431530475616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21247613430023</t>
+    <t xml:space="preserve">1.21247625350952</t>
   </si>
   <si>
     <t xml:space="preserve">1.22685503959656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21403074264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2357931137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2381249666214</t>
+    <t xml:space="preserve">1.21403086185455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23579323291779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23812484741211</t>
   </si>
   <si>
     <t xml:space="preserve">1.23851346969604</t>
@@ -3083,37 +3083,37 @@
     <t xml:space="preserve">1.26105296611786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26455056667328</t>
+    <t xml:space="preserve">1.26455044746399</t>
   </si>
   <si>
     <t xml:space="preserve">1.27582037448883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26066434383392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26493918895721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27892935276031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30457782745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31779086589813</t>
+    <t xml:space="preserve">1.26066446304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26493942737579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27892923355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3045779466629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31779074668884</t>
   </si>
   <si>
     <t xml:space="preserve">1.29291939735413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29874861240387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3174022436142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33061504364014</t>
+    <t xml:space="preserve">1.29874849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31740212440491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33061492443085</t>
   </si>
   <si>
     <t xml:space="preserve">1.34693682193756</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">1.37258541584015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40067207813263</t>
+    <t xml:space="preserve">1.40067195892334</t>
   </si>
   <si>
     <t xml:space="preserve">1.37502765655518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38194763660431</t>
+    <t xml:space="preserve">1.38194751739502</t>
   </si>
   <si>
     <t xml:space="preserve">1.37787699699402</t>
@@ -3149,22 +3149,22 @@
     <t xml:space="preserve">1.391716837883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38438999652863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39456617832184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38886761665344</t>
+    <t xml:space="preserve">1.38438987731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39456629753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38886737823486</t>
   </si>
   <si>
     <t xml:space="preserve">1.41044127941132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42305994033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43323636054993</t>
+    <t xml:space="preserve">1.42306005954742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43323624134064</t>
   </si>
   <si>
     <t xml:space="preserve">1.45847368240356</t>
@@ -3179,10 +3179,10 @@
     <t xml:space="preserve">1.4491114616394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44951868057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45725250244141</t>
+    <t xml:space="preserve">1.44951856136322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4572526216507</t>
   </si>
   <si>
     <t xml:space="preserve">1.45765960216522</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">1.43120110034943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44300556182861</t>
+    <t xml:space="preserve">1.4430056810379</t>
   </si>
   <si>
     <t xml:space="preserve">1.44422686100006</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">1.42713057994843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41858243942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40352141857147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41288352012634</t>
+    <t xml:space="preserve">1.41858232021332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40352153778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41288375854492</t>
   </si>
   <si>
     <t xml:space="preserve">1.41695427894592</t>
@@ -3221,46 +3221,46 @@
     <t xml:space="preserve">1.41329061985016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43527173995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3795051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38072645664215</t>
+    <t xml:space="preserve">1.43527162075043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37950527667999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38072633743286</t>
   </si>
   <si>
     <t xml:space="preserve">1.39945089817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41736137866974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.403928399086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40148615837097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34734797477722</t>
+    <t xml:space="preserve">1.41736125946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40392851829529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40148627758026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34734785556793</t>
   </si>
   <si>
     <t xml:space="preserve">1.3591525554657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38316881656647</t>
+    <t xml:space="preserve">1.38316869735718</t>
   </si>
   <si>
     <t xml:space="preserve">1.395787358284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45114684104919</t>
+    <t xml:space="preserve">1.4511467218399</t>
   </si>
   <si>
     <t xml:space="preserve">1.47719812393188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47801232337952</t>
+    <t xml:space="preserve">1.47801244258881</t>
   </si>
   <si>
     <t xml:space="preserve">1.47394180297852</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">1.46824312210083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4796404838562</t>
+    <t xml:space="preserve">1.47964036464691</t>
   </si>
   <si>
     <t xml:space="preserve">1.49348032474518</t>
@@ -3296,22 +3296,22 @@
     <t xml:space="preserve">1.55006086826324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58262515068054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58669579029083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56593585014343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58384621143341</t>
+    <t xml:space="preserve">1.58262503147125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58669567108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56593596935272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5838463306427</t>
   </si>
   <si>
     <t xml:space="preserve">1.5549453496933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53215038776398</t>
+    <t xml:space="preserve">1.53215026855469</t>
   </si>
   <si>
     <t xml:space="preserve">1.52726578712463</t>
@@ -3329,16 +3329,16 @@
     <t xml:space="preserve">1.51912474632263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50650608539581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49755084514618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52238118648529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49307322502136</t>
+    <t xml:space="preserve">1.50650596618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49755072593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.522381067276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49307334423065</t>
   </si>
   <si>
     <t xml:space="preserve">1.51464712619781</t>
@@ -3347,10 +3347,10 @@
     <t xml:space="preserve">1.5162752866745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48615336418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48940968513489</t>
+    <t xml:space="preserve">1.48615348339081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48940980434418</t>
   </si>
   <si>
     <t xml:space="preserve">1.49063086509705</t>
@@ -3365,13 +3365,13 @@
     <t xml:space="preserve">1.46173012256622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46213710308075</t>
+    <t xml:space="preserve">1.46213722229004</t>
   </si>
   <si>
     <t xml:space="preserve">1.4837110042572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47882628440857</t>
+    <t xml:space="preserve">1.47882640361786</t>
   </si>
   <si>
     <t xml:space="preserve">1.48411810398102</t>
@@ -3383,13 +3383,13 @@
     <t xml:space="preserve">1.45562422275543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43812108039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44544792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44015634059906</t>
+    <t xml:space="preserve">1.43812096118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44544816017151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44015622138977</t>
   </si>
   <si>
     <t xml:space="preserve">1.45684540271759</t>
@@ -3398,13 +3398,13 @@
     <t xml:space="preserve">1.48737454414368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48533916473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5040637254715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46417248249054</t>
+    <t xml:space="preserve">1.48533928394318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50406360626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46417236328125</t>
   </si>
   <si>
     <t xml:space="preserve">1.4450409412384</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">1.49673676490784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50894832611084</t>
+    <t xml:space="preserve">1.50894844532013</t>
   </si>
   <si>
     <t xml:space="preserve">1.502028465271</t>
@@ -3431,10 +3431,10 @@
     <t xml:space="preserve">1.52970802783966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53662812709808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57407701015472</t>
+    <t xml:space="preserve">1.53662800788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57407712936401</t>
   </si>
   <si>
     <t xml:space="preserve">1.55698072910309</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">1.50732016563416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48004746437073</t>
+    <t xml:space="preserve">1.48004758358002</t>
   </si>
   <si>
     <t xml:space="preserve">1.49022388458252</t>
@@ -3464,22 +3464,22 @@
     <t xml:space="preserve">1.50040030479431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50121450424194</t>
+    <t xml:space="preserve">1.50121426582336</t>
   </si>
   <si>
     <t xml:space="preserve">1.51301884651184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51953172683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51546132564545</t>
+    <t xml:space="preserve">1.51953184604645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51546108722687</t>
   </si>
   <si>
     <t xml:space="preserve">1.3921240568161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4059636592865</t>
+    <t xml:space="preserve">1.40596377849579</t>
   </si>
   <si>
     <t xml:space="preserve">1.39538037776947</t>
@@ -3494,25 +3494,25 @@
     <t xml:space="preserve">1.43079400062561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45806670188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45440316200256</t>
+    <t xml:space="preserve">1.45806658267975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45440304279327</t>
   </si>
   <si>
     <t xml:space="preserve">1.45399618148804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42835164070129</t>
+    <t xml:space="preserve">1.42835175991058</t>
   </si>
   <si>
     <t xml:space="preserve">1.39130973815918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32699525356293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34531271457672</t>
+    <t xml:space="preserve">1.32699537277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34531283378601</t>
   </si>
   <si>
     <t xml:space="preserve">1.34775519371033</t>
@@ -3527,10 +3527,10 @@
     <t xml:space="preserve">1.39741563796997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40026497840881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40677797794342</t>
+    <t xml:space="preserve">1.4002650976181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40677785873413</t>
   </si>
   <si>
     <t xml:space="preserve">1.35548901557922</t>
@@ -3539,13 +3539,13 @@
     <t xml:space="preserve">1.35955965518951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35833847522736</t>
+    <t xml:space="preserve">1.35833835601807</t>
   </si>
   <si>
     <t xml:space="preserve">1.37462067604065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36770069599152</t>
+    <t xml:space="preserve">1.36770057678223</t>
   </si>
   <si>
     <t xml:space="preserve">1.35589623451233</t>
@@ -3554,34 +3554,34 @@
     <t xml:space="preserve">1.35263979434967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33310127258301</t>
+    <t xml:space="preserve">1.33310115337372</t>
   </si>
   <si>
     <t xml:space="preserve">1.32414591312408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3530467748642</t>
+    <t xml:space="preserve">1.35304665565491</t>
   </si>
   <si>
     <t xml:space="preserve">1.34164917469025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30664277076721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3326940536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36525845527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41532611846924</t>
+    <t xml:space="preserve">1.30664253234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33269393444061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3652583360672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41532588005066</t>
   </si>
   <si>
     <t xml:space="preserve">1.37380647659302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36729371547699</t>
+    <t xml:space="preserve">1.3672935962677</t>
   </si>
   <si>
     <t xml:space="preserve">1.37909817695618</t>
@@ -3596,19 +3596,19 @@
     <t xml:space="preserve">1.33513641357422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30949199199677</t>
+    <t xml:space="preserve">1.30949211120605</t>
   </si>
   <si>
     <t xml:space="preserve">1.28262650966644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30094397068024</t>
+    <t xml:space="preserve">1.30094385147095</t>
   </si>
   <si>
     <t xml:space="preserve">1.30542147159576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29036045074463</t>
+    <t xml:space="preserve">1.29036056995392</t>
   </si>
   <si>
     <t xml:space="preserve">1.26430904865265</t>
@@ -3617,28 +3617,28 @@
     <t xml:space="preserve">1.28913938999176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28425467014313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2818124294281</t>
+    <t xml:space="preserve">1.28425455093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28181219100952</t>
   </si>
   <si>
     <t xml:space="preserve">1.27652060985565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25413262844086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22889530658722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25046932697296</t>
+    <t xml:space="preserve">1.25413274765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22889542579651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25046920776367</t>
   </si>
   <si>
     <t xml:space="preserve">1.22482478618622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28140532970428</t>
+    <t xml:space="preserve">1.281405210495</t>
   </si>
   <si>
     <t xml:space="preserve">1.3001297712326</t>
@@ -3647,22 +3647,22 @@
     <t xml:space="preserve">1.25494682788849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2284882068634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19918048381805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18249118328094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20243680477142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25616788864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24639868736267</t>
+    <t xml:space="preserve">1.22848832607269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19918036460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18249106407166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20243692398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25616800785065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24639880657196</t>
   </si>
   <si>
     <t xml:space="preserve">1.2447704076767</t>
@@ -3671,16 +3671,16 @@
     <t xml:space="preserve">1.23093068599701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22238254547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22116148471832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21464836597443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23785042762756</t>
+    <t xml:space="preserve">1.22238266468048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22116136550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21464848518372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23785054683685</t>
   </si>
   <si>
     <t xml:space="preserve">1.2508761882782</t>
@@ -3689,43 +3689,43 @@
     <t xml:space="preserve">1.22563886642456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22808110713959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23540830612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25698220729828</t>
+    <t xml:space="preserve">1.22808122634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23540818691254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25698208808899</t>
   </si>
   <si>
     <t xml:space="preserve">1.27489244937897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25779604911804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26553022861481</t>
+    <t xml:space="preserve">1.25779616832733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26553010940552</t>
   </si>
   <si>
     <t xml:space="preserve">1.25942444801331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28751111030579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29768753051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2980945110321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33554351329803</t>
+    <t xml:space="preserve">1.28751122951508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29768741130829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29809439182281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33554327487946</t>
   </si>
   <si>
     <t xml:space="preserve">1.36281609535217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35223269462585</t>
+    <t xml:space="preserve">1.35223257541656</t>
   </si>
   <si>
     <t xml:space="preserve">1.3571172952652</t>
@@ -3734,10 +3734,10 @@
     <t xml:space="preserve">1.34856915473938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34409153461456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36485135555267</t>
+    <t xml:space="preserve">1.34409165382385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36485123634338</t>
   </si>
   <si>
     <t xml:space="preserve">1.33961391448975</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">1.32129657268524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3245530128479</t>
+    <t xml:space="preserve">1.32455289363861</t>
   </si>
   <si>
     <t xml:space="preserve">1.33432233333588</t>
@@ -3758,31 +3758,31 @@
     <t xml:space="preserve">1.34002101421356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32862341403961</t>
+    <t xml:space="preserve">1.3286235332489</t>
   </si>
   <si>
     <t xml:space="preserve">1.31193435192108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3164119720459</t>
+    <t xml:space="preserve">1.31641185283661</t>
   </si>
   <si>
     <t xml:space="preserve">1.35019731521606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34653377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34327733516693</t>
+    <t xml:space="preserve">1.34653401374817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34327745437622</t>
   </si>
   <si>
     <t xml:space="preserve">1.38561105728149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33147299289703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36037373542786</t>
+    <t xml:space="preserve">1.33147275447845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36037361621857</t>
   </si>
   <si>
     <t xml:space="preserve">1.34205627441406</t>
@@ -3803,10 +3803,10 @@
     <t xml:space="preserve">1.3631272315979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35796213150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34504961967468</t>
+    <t xml:space="preserve">1.35796225070953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34504973888397</t>
   </si>
   <si>
     <t xml:space="preserve">1.32998502254486</t>
@@ -3815,16 +3815,16 @@
     <t xml:space="preserve">1.31578135490417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30416023731232</t>
+    <t xml:space="preserve">1.30416011810303</t>
   </si>
   <si>
     <t xml:space="preserve">1.33041560649872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31018602848053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31233811378479</t>
+    <t xml:space="preserve">1.31018590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3123379945755</t>
   </si>
   <si>
     <t xml:space="preserve">1.270587682724</t>
@@ -3836,13 +3836,13 @@
     <t xml:space="preserve">1.14921045303345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11047303676605</t>
+    <t xml:space="preserve">1.11047291755676</t>
   </si>
   <si>
     <t xml:space="preserve">1.15050172805786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11563801765442</t>
+    <t xml:space="preserve">1.11563789844513</t>
   </si>
   <si>
     <t xml:space="preserve">1.15437543392181</t>
@@ -3857,10 +3857,10 @@
     <t xml:space="preserve">1.03945434093475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05581021308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10143423080444</t>
+    <t xml:space="preserve">1.05581033229828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10143435001373</t>
   </si>
   <si>
     <t xml:space="preserve">1.08593928813934</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">1.043328166008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06743144989014</t>
+    <t xml:space="preserve">1.06743133068085</t>
   </si>
   <si>
     <t xml:space="preserve">1.06614017486572</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">1.07130515575409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06915307044983</t>
+    <t xml:space="preserve">1.06915318965912</t>
   </si>
   <si>
     <t xml:space="preserve">1.02697229385376</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">1.00200819969177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02352905273438</t>
+    <t xml:space="preserve">1.02352893352509</t>
   </si>
   <si>
     <t xml:space="preserve">1.05365812778473</t>
@@ -3917,10 +3917,10 @@
     <t xml:space="preserve">1.03816306591034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02955496311188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0588231086731</t>
+    <t xml:space="preserve">1.02955484390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05882322788239</t>
   </si>
   <si>
     <t xml:space="preserve">1.08120477199554</t>
@@ -3929,16 +3929,16 @@
     <t xml:space="preserve">1.04203689098358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04978442192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07474863529205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09024345874786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06829226016998</t>
+    <t xml:space="preserve">1.04978430271149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07474851608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09024357795715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06829237937927</t>
   </si>
   <si>
     <t xml:space="preserve">1.08636963367462</t>
@@ -3959,10 +3959,10 @@
     <t xml:space="preserve">1.10100388526917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10272562503815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08292639255524</t>
+    <t xml:space="preserve">1.10272550582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08292651176453</t>
   </si>
   <si>
     <t xml:space="preserve">1.06097519397736</t>
@@ -3971,25 +3971,25 @@
     <t xml:space="preserve">1.06355774402618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05839264392853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0170726776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996843218803406</t>
+    <t xml:space="preserve">1.05839276313782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01707279682159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996843278408051</t>
   </si>
   <si>
     <t xml:space="preserve">0.999425709247589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.963701188564301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946914970874786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968435764312744</t>
+    <t xml:space="preserve">0.963701248168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946915090084076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968435704708099</t>
   </si>
   <si>
     <t xml:space="preserve">0.945623755455017</t>
@@ -3998,22 +3998,22 @@
     <t xml:space="preserve">0.932711243629456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939167499542236</t>
+    <t xml:space="preserve">0.939167439937592</t>
   </si>
   <si>
     <t xml:space="preserve">0.920229196548462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965422809123993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975322425365448</t>
+    <t xml:space="preserve">0.965422928333282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975322484970093</t>
   </si>
   <si>
     <t xml:space="preserve">0.952510416507721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.926254987716675</t>
+    <t xml:space="preserve">0.92625492811203</t>
   </si>
   <si>
     <t xml:space="preserve">0.930128753185272</t>
@@ -4022,10 +4022,10 @@
     <t xml:space="preserve">0.913342595100403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92195075750351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923242092132568</t>
+    <t xml:space="preserve">0.921950876712799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923242032527924</t>
   </si>
   <si>
     <t xml:space="preserve">0.912051260471344</t>
@@ -4034,10 +4034,10 @@
     <t xml:space="preserve">0.882783055305481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888808906078339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852567851543427</t>
+    <t xml:space="preserve">0.888808846473694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852567791938782</t>
   </si>
   <si>
     <t xml:space="preserve">0.86298394203186</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">0.85377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860659658908844</t>
+    <t xml:space="preserve">0.860659718513489</t>
   </si>
   <si>
     <t xml:space="preserve">0.879339694976807</t>
@@ -4055,19 +4055,19 @@
     <t xml:space="preserve">0.903442978858948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868579268455505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853256464004517</t>
+    <t xml:space="preserve">0.868579208850861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853256404399872</t>
   </si>
   <si>
     <t xml:space="preserve">0.8353511095047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.846541941165924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837244987487793</t>
+    <t xml:space="preserve">0.846542000770569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837245047092438</t>
   </si>
   <si>
     <t xml:space="preserve">0.820200502872467</t>
@@ -4085,22 +4085,22 @@
     <t xml:space="preserve">0.879770040512085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871161699295044</t>
+    <t xml:space="preserve">0.871161758899689</t>
   </si>
   <si>
     <t xml:space="preserve">0.896986782550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949497580528259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9482062458992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982209026813507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971018254756927</t>
+    <t xml:space="preserve">0.949497520923615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948206186294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982209086418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971018373966217</t>
   </si>
   <si>
     <t xml:space="preserve">0.965853273868561</t>
@@ -4112,25 +4112,25 @@
     <t xml:space="preserve">0.966283679008484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955092906951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972309589385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993830382823944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00459086894989</t>
+    <t xml:space="preserve">0.955092966556549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972309470176697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993830323219299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0045907497406</t>
   </si>
   <si>
     <t xml:space="preserve">1.01061654090881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11176419258118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11606848239899</t>
+    <t xml:space="preserve">1.11176431179047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1160683631897</t>
   </si>
   <si>
     <t xml:space="preserve">1.12295508384705</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">1.10616886615753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12682890892029</t>
+    <t xml:space="preserve">1.126828789711</t>
   </si>
   <si>
     <t xml:space="preserve">1.1220942735672</t>
@@ -4154,22 +4154,22 @@
     <t xml:space="preserve">1.11391639709473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13974130153656</t>
+    <t xml:space="preserve">1.13974118232727</t>
   </si>
   <si>
     <t xml:space="preserve">1.11865091323853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09928226470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11090338230133</t>
+    <t xml:space="preserve">1.09928214550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11090350151062</t>
   </si>
   <si>
     <t xml:space="preserve">1.12898087501526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13586747646332</t>
+    <t xml:space="preserve">1.13586759567261</t>
   </si>
   <si>
     <t xml:space="preserve">1.13027215003967</t>
@@ -4187,7 +4187,7 @@
     <t xml:space="preserve">1.12166380882263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1298416852951</t>
+    <t xml:space="preserve">1.12984180450439</t>
   </si>
   <si>
     <t xml:space="preserve">1.14490628242493</t>
@@ -4196,10 +4196,10 @@
     <t xml:space="preserve">1.11692929267883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0928258895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07603979110718</t>
+    <t xml:space="preserve">1.09282600879669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07603967189789</t>
   </si>
   <si>
     <t xml:space="preserve">1.08378720283508</t>
@@ -4208,46 +4208,46 @@
     <t xml:space="preserve">1.06958341598511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07173550128937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09971261024475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12467670440674</t>
+    <t xml:space="preserve">1.07173562049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09971272945404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12467682361603</t>
   </si>
   <si>
     <t xml:space="preserve">1.12553763389587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13888049125671</t>
+    <t xml:space="preserve">1.13888037204742</t>
   </si>
   <si>
     <t xml:space="preserve">1.14705836772919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18837821483612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19354343414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19827783107758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20043003559113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20516443252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21032965183258</t>
+    <t xml:space="preserve">1.18837833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19354331493378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19827771186829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20042991638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20516455173492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21032953262329</t>
   </si>
   <si>
     <t xml:space="preserve">1.17245292663574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15093219280243</t>
+    <t xml:space="preserve">1.15093207359314</t>
   </si>
   <si>
     <t xml:space="preserve">1.18192207813263</t>
@@ -4259,7 +4259,7 @@
     <t xml:space="preserve">1.20387327671051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20430374145508</t>
+    <t xml:space="preserve">1.20430386066437</t>
   </si>
   <si>
     <t xml:space="preserve">1.21119022369385</t>
@@ -4268,7 +4268,7 @@
     <t xml:space="preserve">1.19483458995819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18665659427643</t>
+    <t xml:space="preserve">1.18665671348572</t>
   </si>
   <si>
     <t xml:space="preserve">1.20989918708801</t>
@@ -4307,43 +4307,43 @@
     <t xml:space="preserve">1.18579590320587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18966960906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20215153694153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20129060745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16943991184235</t>
+    <t xml:space="preserve">1.18966948986053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20215165615082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20129084587097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16944003105164</t>
   </si>
   <si>
     <t xml:space="preserve">1.18364369869232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19784736633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18149161338806</t>
+    <t xml:space="preserve">1.1978474855423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18149149417877</t>
   </si>
   <si>
     <t xml:space="preserve">1.18493497371674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17503535747528</t>
+    <t xml:space="preserve">1.17503547668457</t>
   </si>
   <si>
     <t xml:space="preserve">1.16814875602722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15738832950592</t>
+    <t xml:space="preserve">1.15738821029663</t>
   </si>
   <si>
     <t xml:space="preserve">1.18278288841248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18321323394775</t>
+    <t xml:space="preserve">1.18321335315704</t>
   </si>
   <si>
     <t xml:space="preserve">1.25078856945038</t>
@@ -4358,7 +4358,7 @@
     <t xml:space="preserve">1.25294065475464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2395977973938</t>
+    <t xml:space="preserve">1.23959791660309</t>
   </si>
   <si>
     <t xml:space="preserve">1.23787605762482</t>
@@ -4367,13 +4367,13 @@
     <t xml:space="preserve">1.21678566932678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22496366500854</t>
+    <t xml:space="preserve">1.22496354579926</t>
   </si>
   <si>
     <t xml:space="preserve">1.25121903419495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26542270183563</t>
+    <t xml:space="preserve">1.26542282104492</t>
   </si>
   <si>
     <t xml:space="preserve">1.25853610038757</t>
@@ -4382,13 +4382,13 @@
     <t xml:space="preserve">1.26714444160461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29426062107086</t>
+    <t xml:space="preserve">1.29426074028015</t>
   </si>
   <si>
     <t xml:space="preserve">1.32869386672974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33256769180298</t>
+    <t xml:space="preserve">1.33256757259369</t>
   </si>
   <si>
     <t xml:space="preserve">1.33730220794678</t>
@@ -4400,13 +4400,13 @@
     <t xml:space="preserve">1.32137680053711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31922471523285</t>
+    <t xml:space="preserve">1.31922483444214</t>
   </si>
   <si>
     <t xml:space="preserve">1.35150599479675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33988475799561</t>
+    <t xml:space="preserve">1.33988463878632</t>
   </si>
   <si>
     <t xml:space="preserve">1.35279715061188</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">1.35968375205994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35236668586731</t>
+    <t xml:space="preserve">1.3523668050766</t>
   </si>
   <si>
     <t xml:space="preserve">1.36614012718201</t>
@@ -4427,10 +4427,10 @@
     <t xml:space="preserve">1.34332811832428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3678617477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36829209327698</t>
+    <t xml:space="preserve">1.36786162853241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36829221248627</t>
   </si>
   <si>
     <t xml:space="preserve">1.3880912065506</t>
@@ -4442,34 +4442,34 @@
     <t xml:space="preserve">1.39885175228119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4126250743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43113279342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4560968875885</t>
+    <t xml:space="preserve">1.41262495517731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4311329126358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45609700679779</t>
   </si>
   <si>
     <t xml:space="preserve">1.46728777885437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44877982139587</t>
+    <t xml:space="preserve">1.44877994060516</t>
   </si>
   <si>
     <t xml:space="preserve">1.43758916854858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37905251979828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41047275066376</t>
+    <t xml:space="preserve">1.37905263900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41047286987305</t>
   </si>
   <si>
     <t xml:space="preserve">1.42495942115784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42905950546265</t>
+    <t xml:space="preserve">1.42905938625336</t>
   </si>
   <si>
     <t xml:space="preserve">1.39261531829834</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">1.39079320430756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38532650470734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40719306468964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41038191318512</t>
+    <t xml:space="preserve">1.38532662391663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40719294548035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41038179397583</t>
   </si>
   <si>
     <t xml:space="preserve">1.4313371181488</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">1.45684790611267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4563924074173</t>
+    <t xml:space="preserve">1.45639228820801</t>
   </si>
   <si>
     <t xml:space="preserve">1.48235869407654</t>
@@ -4520,19 +4520,19 @@
     <t xml:space="preserve">1.50103628635406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50786936283112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51743614673615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50012505054474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50376951694489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4768922328949</t>
+    <t xml:space="preserve">1.50786948204041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51743602752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50012516975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50376963615417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47689211368561</t>
   </si>
   <si>
     <t xml:space="preserve">1.49784743785858</t>
@@ -4541,13 +4541,13 @@
     <t xml:space="preserve">1.49420297145844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50695836544037</t>
+    <t xml:space="preserve">1.50695848464966</t>
   </si>
   <si>
     <t xml:space="preserve">1.51652491092682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52563583850861</t>
+    <t xml:space="preserve">1.5256359577179</t>
   </si>
   <si>
     <t xml:space="preserve">1.5242692232132</t>
@@ -4571,7 +4571,7 @@
     <t xml:space="preserve">1.54112458229065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53975808620453</t>
+    <t xml:space="preserve">1.53975796699524</t>
   </si>
   <si>
     <t xml:space="preserve">1.52153599262238</t>
@@ -4583,7 +4583,7 @@
     <t xml:space="preserve">1.53064692020416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53383588790894</t>
+    <t xml:space="preserve">1.53383576869965</t>
   </si>
   <si>
     <t xml:space="preserve">1.53520238399506</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">1.54750227928162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55433559417725</t>
+    <t xml:space="preserve">1.55433547496796</t>
   </si>
   <si>
     <t xml:space="preserve">1.56435763835907</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">1.55160212516785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58121287822723</t>
+    <t xml:space="preserve">1.58121299743652</t>
   </si>
   <si>
     <t xml:space="preserve">1.57939076423645</t>
@@ -4613,10 +4613,10 @@
     <t xml:space="preserve">1.54249119758606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51470267772675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5110582113266</t>
+    <t xml:space="preserve">1.51470279693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51105833053589</t>
   </si>
   <si>
     <t xml:space="preserve">1.49921405315399</t>
@@ -4631,13 +4631,13 @@
     <t xml:space="preserve">1.54886901378632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56709098815918</t>
+    <t xml:space="preserve">1.56709086894989</t>
   </si>
   <si>
     <t xml:space="preserve">1.52335822582245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52836930751801</t>
+    <t xml:space="preserve">1.52836918830872</t>
   </si>
   <si>
     <t xml:space="preserve">1.54613566398621</t>
@@ -4649,37 +4649,37 @@
     <t xml:space="preserve">1.57210195064545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58349072933197</t>
+    <t xml:space="preserve">1.58349084854126</t>
   </si>
   <si>
     <t xml:space="preserve">1.58622407913208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60581278800964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59487950801849</t>
+    <t xml:space="preserve">1.60581266880035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5948793888092</t>
   </si>
   <si>
     <t xml:space="preserve">1.61219036579132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59214603900909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57984638214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56481313705444</t>
+    <t xml:space="preserve">1.59214615821838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57984626293182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56481325626373</t>
   </si>
   <si>
     <t xml:space="preserve">1.59123516082764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60034608840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61310148239136</t>
+    <t xml:space="preserve">1.60034596920013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61310136318207</t>
   </si>
   <si>
     <t xml:space="preserve">1.63041234016418</t>
@@ -4703,7 +4703,7 @@
     <t xml:space="preserve">1.70056700706482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6345123052597</t>
+    <t xml:space="preserve">1.63451242446899</t>
   </si>
   <si>
     <t xml:space="preserve">1.5994348526001</t>
@@ -4721,25 +4721,25 @@
     <t xml:space="preserve">1.51060271263123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53611361980438</t>
+    <t xml:space="preserve">1.53611350059509</t>
   </si>
   <si>
     <t xml:space="preserve">1.48828089237213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50285851955414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.521080493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55889093875885</t>
+    <t xml:space="preserve">1.50285840034485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52108037471771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55889105796814</t>
   </si>
   <si>
     <t xml:space="preserve">1.56800198554993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58440172672272</t>
+    <t xml:space="preserve">1.58440184593201</t>
   </si>
   <si>
     <t xml:space="preserve">1.57893526554108</t>
@@ -4754,10 +4754,10 @@
     <t xml:space="preserve">1.54659116268158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57756853103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57620203495026</t>
+    <t xml:space="preserve">1.57756865024567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57620191574097</t>
   </si>
   <si>
     <t xml:space="preserve">1.59761273860931</t>
@@ -4766,37 +4766,37 @@
     <t xml:space="preserve">1.60125720500946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61355710029602</t>
+    <t xml:space="preserve">1.61355698108673</t>
   </si>
   <si>
     <t xml:space="preserve">1.63724565505981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.633145570755</t>
+    <t xml:space="preserve">1.63314568996429</t>
   </si>
   <si>
     <t xml:space="preserve">1.63223457336426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62767899036407</t>
+    <t xml:space="preserve">1.62767910957336</t>
   </si>
   <si>
     <t xml:space="preserve">1.6167459487915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61765694618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63177907466888</t>
+    <t xml:space="preserve">1.61765706539154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63177895545959</t>
   </si>
   <si>
     <t xml:space="preserve">1.69601154327393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71742224693298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.761155128479</t>
+    <t xml:space="preserve">1.71742236614227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76115500926971</t>
   </si>
   <si>
     <t xml:space="preserve">1.7597883939743</t>
@@ -4826,7 +4826,7 @@
     <t xml:space="preserve">1.79031038284302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79759919643402</t>
+    <t xml:space="preserve">1.79759907722473</t>
   </si>
   <si>
     <t xml:space="preserve">1.79167699813843</t>
@@ -4835,7 +4835,7 @@
     <t xml:space="preserve">1.77709937095642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78256607055664</t>
+    <t xml:space="preserve">1.78256595134735</t>
   </si>
   <si>
     <t xml:space="preserve">1.77846598625183</t>
@@ -4844,16 +4844,16 @@
     <t xml:space="preserve">1.78211033344269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78712141513824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77618813514709</t>
+    <t xml:space="preserve">1.78712153434753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77618825435638</t>
   </si>
   <si>
     <t xml:space="preserve">1.74384427070618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77208840847015</t>
+    <t xml:space="preserve">1.77208828926086</t>
   </si>
   <si>
     <t xml:space="preserve">1.79805469512939</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">1.74019980430603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71377789974213</t>
+    <t xml:space="preserve">1.71377801895142</t>
   </si>
   <si>
     <t xml:space="preserve">1.6964670419693</t>
@@ -4886,10 +4886,10 @@
     <t xml:space="preserve">1.68280053138733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67778956890106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71651124954224</t>
+    <t xml:space="preserve">1.67778944969177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71651113033295</t>
   </si>
   <si>
     <t xml:space="preserve">1.72061121463776</t>
@@ -4898,10 +4898,10 @@
     <t xml:space="preserve">1.73792207241058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74247765541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74703299999237</t>
+    <t xml:space="preserve">1.74247753620148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74703311920166</t>
   </si>
   <si>
     <t xml:space="preserve">1.69692254066467</t>
@@ -4922,10 +4922,10 @@
     <t xml:space="preserve">1.64453434944153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66184520721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64225661754608</t>
+    <t xml:space="preserve">1.66184532642365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64225673675537</t>
   </si>
   <si>
     <t xml:space="preserve">1.59897947311401</t>
@@ -4934,7 +4934,7 @@
     <t xml:space="preserve">1.62995684146881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62859010696411</t>
+    <t xml:space="preserve">1.6285902261734</t>
   </si>
   <si>
     <t xml:space="preserve">1.66321194171906</t>
@@ -4943,10 +4943,10 @@
     <t xml:space="preserve">1.67687833309174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60307931900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56936872005463</t>
+    <t xml:space="preserve">1.60307943820953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56936860084534</t>
   </si>
   <si>
     <t xml:space="preserve">1.55296885967255</t>
@@ -4955,13 +4955,13 @@
     <t xml:space="preserve">1.5124249458313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51014733314514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49238073825836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48964750766754</t>
+    <t xml:space="preserve">1.51014721393585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49238085746765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48964738845825</t>
   </si>
   <si>
     <t xml:space="preserve">1.51698040962219</t>
@@ -4976,7 +4976,7 @@
     <t xml:space="preserve">1.55023562908173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55114662647247</t>
+    <t xml:space="preserve">1.55114674568176</t>
   </si>
   <si>
     <t xml:space="preserve">1.54066896438599</t>
@@ -4985,7 +4985,7 @@
     <t xml:space="preserve">1.53839135169983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52518045902252</t>
+    <t xml:space="preserve">1.52518033981323</t>
   </si>
   <si>
     <t xml:space="preserve">1.51288056373596</t>
@@ -5000,13 +5000,13 @@
     <t xml:space="preserve">1.58212411403656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59533500671387</t>
+    <t xml:space="preserve">1.59533512592316</t>
   </si>
   <si>
     <t xml:space="preserve">1.53748023509979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49602508544922</t>
+    <t xml:space="preserve">1.49602520465851</t>
   </si>
   <si>
     <t xml:space="preserve">1.50468063354492</t>
@@ -5015,13 +5015,13 @@
     <t xml:space="preserve">1.50149178504944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49556970596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47279214859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49283623695374</t>
+    <t xml:space="preserve">1.49556958675385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47279226779938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49283635616302</t>
   </si>
   <si>
     <t xml:space="preserve">1.52472484111786</t>
@@ -5033,7 +5033,7 @@
     <t xml:space="preserve">1.50422501564026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47370314598083</t>
+    <t xml:space="preserve">1.47370326519012</t>
   </si>
   <si>
     <t xml:space="preserve">1.50331389904022</t>
@@ -5042,7 +5042,7 @@
     <t xml:space="preserve">1.5051361322403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48418092727661</t>
+    <t xml:space="preserve">1.48418080806732</t>
   </si>
   <si>
     <t xml:space="preserve">1.49966955184937</t>
@@ -5051,7 +5051,7 @@
     <t xml:space="preserve">1.57574641704559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59624600410461</t>
+    <t xml:space="preserve">1.5962461233139</t>
   </si>
   <si>
     <t xml:space="preserve">1.65592312812805</t>
@@ -5066,19 +5066,19 @@
     <t xml:space="preserve">1.70694470405579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.690544962883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7142333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69464492797852</t>
+    <t xml:space="preserve">1.69054484367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71423351764679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69464480876923</t>
   </si>
   <si>
     <t xml:space="preserve">1.71241128444672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72380006313324</t>
+    <t xml:space="preserve">1.72379994392395</t>
   </si>
   <si>
     <t xml:space="preserve">1.74156641960144</t>
@@ -5087,7 +5087,7 @@
     <t xml:space="preserve">1.74794411659241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75341081619263</t>
+    <t xml:space="preserve">1.75341069698334</t>
   </si>
   <si>
     <t xml:space="preserve">1.7921324968338</t>
@@ -5102,7 +5102,7 @@
     <t xml:space="preserve">1.84497630596161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83586525917053</t>
+    <t xml:space="preserve">1.83586537837982</t>
   </si>
   <si>
     <t xml:space="preserve">1.84284818172455</t>
@@ -5925,6 +5925,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.25999999046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25300002098083</t>
   </si>
 </sst>
 </file>
@@ -70899,7 +70902,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6499189815</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>6874793</v>
@@ -70920,6 +70923,32 @@
         <v>1970</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6520486111</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>6152295</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>2.27500009536743</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>2.2409999370575</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>2.25300002098083</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1971</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="1972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1973" uniqueCount="1973">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765547692775726</t>
+    <t xml:space="preserve">0.765547752380371</t>
   </si>
   <si>
     <t xml:space="preserve">A2A.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.7743039727211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76930034160614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777431190013885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772427618503571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775554776191711</t>
+    <t xml:space="preserve">0.774304032325745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76930046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777431130409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772427558898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775554895401001</t>
   </si>
   <si>
     <t xml:space="preserve">0.73615175485611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.728020846843719</t>
+    <t xml:space="preserve">0.728020906448364</t>
   </si>
   <si>
     <t xml:space="preserve">0.708631932735443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.701126575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.678610563278198</t>
+    <t xml:space="preserve">0.701126635074615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678610444068909</t>
   </si>
   <si>
     <t xml:space="preserve">0.686115801334381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662974238395691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.66985422372818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.673606932163239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661723434925079</t>
+    <t xml:space="preserve">0.66297435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.66985410451889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.673606872558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661723375320435</t>
   </si>
   <si>
     <t xml:space="preserve">0.68986850976944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667352437973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.688617587089539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689243197441101</t>
+    <t xml:space="preserve">0.667352497577667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.688617646694183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689243078231812</t>
   </si>
   <si>
     <t xml:space="preserve">0.676108658313751</t>
@@ -110,25 +110,25 @@
     <t xml:space="preserve">0.66672694683075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643585443496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612312972545624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597927749156952</t>
+    <t xml:space="preserve">0.643585503101349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612313032150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597927808761597</t>
   </si>
   <si>
     <t xml:space="preserve">0.605745911598206</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610749363899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614189445972443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627323806285858</t>
+    <t xml:space="preserve">0.610749423503876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614189386367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627323865890503</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942094802856</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">0.645461738109589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641083657741547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647963643074036</t>
+    <t xml:space="preserve">0.641083717346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.647963404655457</t>
   </si>
   <si>
     <t xml:space="preserve">0.657345294952393</t>
@@ -161,64 +161,64 @@
     <t xml:space="preserve">0.661098003387451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672981441020966</t>
+    <t xml:space="preserve">0.67298150062561</t>
   </si>
   <si>
     <t xml:space="preserve">0.666101515293121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.664850652217865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658596158027649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651716351509094</t>
+    <t xml:space="preserve">0.66485059261322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658596217632294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651716232299805</t>
   </si>
   <si>
     <t xml:space="preserve">0.654843509197235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669228851795197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71301007270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692995846271515</t>
+    <t xml:space="preserve">0.669228792190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713010013103485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69299578666687</t>
   </si>
   <si>
     <t xml:space="preserve">0.691119432449341</t>
   </si>
   <si>
-    <t xml:space="preserve">0.694246649742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697999358177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696123063564301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7030029296875</t>
+    <t xml:space="preserve">0.694246768951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69799941778183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696122944355011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703002870082855</t>
   </si>
   <si>
     <t xml:space="preserve">0.692370355129242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.699250221252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714260935783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714886486530304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.702377557754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705504715442657</t>
+    <t xml:space="preserve">0.699250161647797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714260995388031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714886367321014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.702377498149872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705504775047302</t>
   </si>
   <si>
     <t xml:space="preserve">0.735526144504547</t>
@@ -227,19 +227,19 @@
     <t xml:space="preserve">0.740529775619507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.744282484054565</t>
+    <t xml:space="preserve">0.74428254365921</t>
   </si>
   <si>
     <t xml:space="preserve">0.748660564422607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.738027989864349</t>
+    <t xml:space="preserve">0.738028109073639</t>
   </si>
   <si>
     <t xml:space="preserve">0.750536978244781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.754289627075195</t>
+    <t xml:space="preserve">0.754289567470551</t>
   </si>
   <si>
     <t xml:space="preserve">0.768049478530884</t>
@@ -248,103 +248,103 @@
     <t xml:space="preserve">0.757416844367981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766798496246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.752413272857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781183898448944</t>
+    <t xml:space="preserve">0.766798555850983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.752413153648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781183779239655</t>
   </si>
   <si>
     <t xml:space="preserve">0.778056561946869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786187469959259</t>
+    <t xml:space="preserve">0.786187350749969</t>
   </si>
   <si>
     <t xml:space="preserve">0.779307544231415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.768674790859222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755540430545807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.760544240474701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76429682970047</t>
+    <t xml:space="preserve">0.768674969673157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755540549755096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.760544002056122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.764296770095825</t>
   </si>
   <si>
     <t xml:space="preserve">0.770551145076752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.759293079376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769925892353058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76116955280304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767424046993256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747409701347351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751787781715393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754914999008179</t>
+    <t xml:space="preserve">0.759293258190155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769925773143768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761169612407684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767423987388611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747409760951996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751787722110748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754915058612823</t>
   </si>
   <si>
     <t xml:space="preserve">0.781809329986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801198184490204</t>
+    <t xml:space="preserve">0.801198303699493</t>
   </si>
   <si>
     <t xml:space="preserve">0.804950833320618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79932177066803</t>
+    <t xml:space="preserve">0.799321889877319</t>
   </si>
   <si>
     <t xml:space="preserve">0.785561919212341</t>
   </si>
   <si>
-    <t xml:space="preserve">0.796820044517517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791816473007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801823616027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733649909496307</t>
+    <t xml:space="preserve">0.796820104122162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791816532611847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801823675632477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733649849891663</t>
   </si>
   <si>
     <t xml:space="preserve">0.725519061088562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766306400299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759828805923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750760197639465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778613924980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703473150730133</t>
+    <t xml:space="preserve">0.766306340694427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759828746318817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750760078430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778613984584808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703473210334778</t>
   </si>
   <si>
     <t xml:space="preserve">0.692461252212524</t>
@@ -356,28 +356,28 @@
     <t xml:space="preserve">0.730031609535217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.763067722320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762419939041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769545197486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757885456085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742986857891083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742339193820953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.758533358573914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77731853723526</t>
+    <t xml:space="preserve">0.763067603111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762419879436493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769545316696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757885634899139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742986917495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742339134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758533298969269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777318596839905</t>
   </si>
   <si>
     <t xml:space="preserve">0.774079620838165</t>
@@ -386,34 +386,34 @@
     <t xml:space="preserve">0.776022911071777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783796072006226</t>
+    <t xml:space="preserve">0.78379613161087</t>
   </si>
   <si>
     <t xml:space="preserve">0.779909551143646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.790273785591125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789626002311707</t>
+    <t xml:space="preserve">0.79027384519577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789626061916351</t>
   </si>
   <si>
     <t xml:space="preserve">0.79416024684906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805172502994537</t>
+    <t xml:space="preserve">0.805172383785248</t>
   </si>
   <si>
     <t xml:space="preserve">0.807763516902924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.822661936283112</t>
+    <t xml:space="preserve">0.822662055492401</t>
   </si>
   <si>
     <t xml:space="preserve">0.817479848861694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.820718586444855</t>
+    <t xml:space="preserve">0.820718705654144</t>
   </si>
   <si>
     <t xml:space="preserve">0.822014391422272</t>
@@ -425,34 +425,34 @@
     <t xml:space="preserve">0.814241111278534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.816184341907501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804524600505829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801285684108734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812945544719696</t>
+    <t xml:space="preserve">0.816184461116791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804524481296539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801285803318024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812945604324341</t>
   </si>
   <si>
     <t xml:space="preserve">0.801933646202087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786387205123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788330495357513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771488547325134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783148288726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782500565052032</t>
+    <t xml:space="preserve">0.786387264728546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788330435752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77148848772049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783148467540741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782500624656677</t>
   </si>
   <si>
     <t xml:space="preserve">0.781852781772614</t>
@@ -479,55 +479,55 @@
     <t xml:space="preserve">0.798694729804993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.802581310272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790921568870544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796751320362091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799342513084412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81035441160202</t>
+    <t xml:space="preserve">0.802581369876862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7909215092659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796751499176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799342393875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810354590415955</t>
   </si>
   <si>
     <t xml:space="preserve">0.780557334423065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784443855285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785739362239838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827196300029755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813593447208405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80063796043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7973992228508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803876996040344</t>
+    <t xml:space="preserve">0.784443795681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785739421844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827196359634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81359326839447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800638020038605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797399163246155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80387681722641</t>
   </si>
   <si>
     <t xml:space="preserve">0.807115793228149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.761124432086945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77084082365036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.731327056884766</t>
+    <t xml:space="preserve">0.76112425327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77084094285965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73132711648941</t>
   </si>
   <si>
     <t xml:space="preserve">0.735861599445343</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">0.720315158367157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.72161066532135</t>
+    <t xml:space="preserve">0.721610605716705</t>
   </si>
   <si>
     <t xml:space="preserve">0.719019591808319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696347832679749</t>
+    <t xml:space="preserve">0.696347892284393</t>
   </si>
   <si>
     <t xml:space="preserve">0.696995556354523</t>
@@ -551,94 +551,94 @@
     <t xml:space="preserve">0.709950864315033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.713837504386902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71189421415329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.707359790802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728736162185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715780794620514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722258388996124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765010952949524</t>
+    <t xml:space="preserve">0.713837444782257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.711894154548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.707359731197357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728736042976379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715780675411224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722258448600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765010893344879</t>
   </si>
   <si>
     <t xml:space="preserve">0.754646718502045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.755294442176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78768265247345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776670694351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772136449813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78703498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816832184791565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819423198699951</t>
+    <t xml:space="preserve">0.755294501781464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787682712078094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776670753955841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772136390209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787035048007965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81683212518692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819423139095306</t>
   </si>
   <si>
     <t xml:space="preserve">0.799990236759186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824605226516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838856160640717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831730842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832378566265106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840151906013489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848572552204132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841447293758392</t>
+    <t xml:space="preserve">0.824605286121368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838856101036072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831730723381042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832378447055817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840151846408844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848572611808777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841447234153748</t>
   </si>
   <si>
     <t xml:space="preserve">0.844686031341553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830435216426849</t>
+    <t xml:space="preserve">0.830435276031494</t>
   </si>
   <si>
     <t xml:space="preserve">0.798046946525574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.815536558628082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82007098197937</t>
+    <t xml:space="preserve">0.815536677837372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820071160793304</t>
   </si>
   <si>
     <t xml:space="preserve">0.806467890739441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.811650037765503</t>
+    <t xml:space="preserve">0.811649978160858</t>
   </si>
   <si>
     <t xml:space="preserve">0.83626514673233</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">0.844038307666779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837560594081879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836912870407104</t>
+    <t xml:space="preserve">0.837560534477234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836912930011749</t>
   </si>
   <si>
     <t xml:space="preserve">0.821366608142853</t>
@@ -659,112 +659,112 @@
     <t xml:space="preserve">0.828491985797882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825900912284851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829139590263367</t>
+    <t xml:space="preserve">0.825900793075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829139649868011</t>
   </si>
   <si>
     <t xml:space="preserve">0.84662938117981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849220454692841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864766895771027</t>
+    <t xml:space="preserve">0.84922057390213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864766836166382</t>
   </si>
   <si>
     <t xml:space="preserve">0.867357850074768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868005692958832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870596647262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857641279697418</t>
+    <t xml:space="preserve">0.868005752563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870596587657928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857641458511353</t>
   </si>
   <si>
     <t xml:space="preserve">0.865414559841156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866710126399994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853106915950775</t>
+    <t xml:space="preserve">0.866710186004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85310697555542</t>
   </si>
   <si>
     <t xml:space="preserve">0.85569816827774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858289361000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860232532024384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872539877891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874483346939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887438595294952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893916368484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892620742321014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912701487541199</t>
+    <t xml:space="preserve">0.858289122581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860232353210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872540056705475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874483287334442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887438774108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893916308879852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892620801925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912701427936554</t>
   </si>
   <si>
     <t xml:space="preserve">0.909462630748749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908167123794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919826805591583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91853141784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875778794288635</t>
+    <t xml:space="preserve">0.908167064189911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919826865196228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918531239032745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875778913497925</t>
   </si>
   <si>
     <t xml:space="preserve">0.877722144126892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.891972899436951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884847581386566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895211815834045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884199738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876426577568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862175762653351</t>
+    <t xml:space="preserve">0.891972959041595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884847521781921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895211756229401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884199798107147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876426517963409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862175703048706</t>
   </si>
   <si>
     <t xml:space="preserve">0.856345891952515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.882256627082825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899098336696625</t>
+    <t xml:space="preserve">0.88225656747818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89909839630127</t>
   </si>
   <si>
     <t xml:space="preserve">0.890677392482758</t>
@@ -773,40 +773,40 @@
     <t xml:space="preserve">0.926952302455902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.915292382240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917235851287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966466069221497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958044946193695</t>
+    <t xml:space="preserve">0.91529244184494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917235910892487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966465950012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958044826984406</t>
   </si>
   <si>
     <t xml:space="preserve">0.965170562267303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961283802986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963227152824402</t>
+    <t xml:space="preserve">0.96128386259079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963227093219757</t>
   </si>
   <si>
     <t xml:space="preserve">0.941850900650024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941203057765961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958692848682404</t>
+    <t xml:space="preserve">0.941202998161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958692908287048</t>
   </si>
   <si>
     <t xml:space="preserve">0.982278227806091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988308429718018</t>
+    <t xml:space="preserve">0.988308608531952</t>
   </si>
   <si>
     <t xml:space="preserve">0.997019171714783</t>
@@ -815,172 +815,172 @@
     <t xml:space="preserve">1.00036919116974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992998778820038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96820741891861</t>
+    <t xml:space="preserve">0.992998719215393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968207478523254</t>
   </si>
   <si>
     <t xml:space="preserve">0.981608152389526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986298263072968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988978624343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989648640155792</t>
+    <t xml:space="preserve">0.986298441886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988978564739227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989648759365082</t>
   </si>
   <si>
     <t xml:space="preserve">0.97490781545639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999699294567108</t>
+    <t xml:space="preserve">0.999699413776398</t>
   </si>
   <si>
     <t xml:space="preserve">1.00505948066711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998359262943268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997689127922058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00170946121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00706958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02047061920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02985107898712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0177903175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995008826255798</t>
+    <t xml:space="preserve">0.998359143733978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997689247131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00170934200287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00706946849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02047038078308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02985084056854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01779043674469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995009124279022</t>
   </si>
   <si>
     <t xml:space="preserve">0.999029219150543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.976917803287506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.974237740039825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970217347145081</t>
+    <t xml:space="preserve">0.976917862892151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.974237859249115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970217406749725</t>
   </si>
   <si>
     <t xml:space="preserve">0.965527236461639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96083676815033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96150678396225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964187204837799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980268061161041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978927969932556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984958291053772</t>
+    <t xml:space="preserve">0.960836946964264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961506903171539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96418708562851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980268180370331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978927850723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984958231449127</t>
   </si>
   <si>
     <t xml:space="preserve">0.97289776802063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960166931152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958826839923859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951456308364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955476582050323</t>
+    <t xml:space="preserve">0.960166752338409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958826780319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951456367969513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955476641654968</t>
   </si>
   <si>
     <t xml:space="preserve">0.949446260929108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.963517069816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950116336345673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953466475009918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956816494464874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958156764507294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952796399593353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962176978588104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944755852222443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931355237960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948106169700623</t>
+    <t xml:space="preserve">0.9635169506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950116276741028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953466534614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956816673278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958156824111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952796578407288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962176918983459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944755971431732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931355178356171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948106110095978</t>
   </si>
   <si>
     <t xml:space="preserve">0.954136490821838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957486748695374</t>
+    <t xml:space="preserve">0.957486629486084</t>
   </si>
   <si>
     <t xml:space="preserve">0.939395666122437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946765959262848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934705376625061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92867511510849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924654901027679</t>
+    <t xml:space="preserve">0.946766078472137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934705317020416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928675055503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92465478181839</t>
   </si>
   <si>
     <t xml:space="preserve">0.932695209980011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945426106452942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959496915340424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973567605018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978257954120636</t>
+    <t xml:space="preserve">0.945426166057587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959496796131134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973567724227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978258013725281</t>
   </si>
   <si>
     <t xml:space="preserve">0.993668854236603</t>
@@ -992,34 +992,34 @@
     <t xml:space="preserve">0.983618319034576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994338870048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977587878704071</t>
+    <t xml:space="preserve">0.994338929653168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977587819099426</t>
   </si>
   <si>
     <t xml:space="preserve">0.980938136577606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972227513790131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96619725227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969547390937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968877375125885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971557438373566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995678961277008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992328703403473</t>
+    <t xml:space="preserve">0.972227692604065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966197311878204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96954745054245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96887743473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97155749797821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995678901672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992328882217407</t>
   </si>
   <si>
     <t xml:space="preserve">0.966867327690125</t>
@@ -1031,16 +1031,16 @@
     <t xml:space="preserve">1.01041984558105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01444017887115</t>
+    <t xml:space="preserve">1.01443994045258</t>
   </si>
   <si>
     <t xml:space="preserve">1.02181053161621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02382063865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02851092815399</t>
+    <t xml:space="preserve">1.02382051944733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0285108089447</t>
   </si>
   <si>
     <t xml:space="preserve">1.03320121765137</t>
@@ -1049,28 +1049,28 @@
     <t xml:space="preserve">1.03923153877258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0265007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05531239509583</t>
+    <t xml:space="preserve">1.02650082111359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05531251430511</t>
   </si>
   <si>
     <t xml:space="preserve">1.05866265296936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04459202289581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05330240726471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0680433511734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07273364067078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08613431453705</t>
+    <t xml:space="preserve">1.04459190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05330228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06804323196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0727334022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08613443374634</t>
   </si>
   <si>
     <t xml:space="preserve">1.0955148935318</t>
@@ -1079,37 +1079,37 @@
     <t xml:space="preserve">1.08345425128937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08211410045624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05397236347198</t>
+    <t xml:space="preserve">1.08211421966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0539722442627</t>
   </si>
   <si>
     <t xml:space="preserve">1.06000280380249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04392182826996</t>
+    <t xml:space="preserve">1.04392170906067</t>
   </si>
   <si>
     <t xml:space="preserve">1.04861211776733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04660189151764</t>
+    <t xml:space="preserve">1.04660212993622</t>
   </si>
   <si>
     <t xml:space="preserve">1.03990149497986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04258179664612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01980042457581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01578009128571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05196237564087</t>
+    <t xml:space="preserve">1.04258167743683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01980030536652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.015780210495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05196249485016</t>
   </si>
   <si>
     <t xml:space="preserve">1.06737315654755</t>
@@ -1124,16 +1124,16 @@
     <t xml:space="preserve">1.01846027374268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02784085273743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05665254592896</t>
+    <t xml:space="preserve">1.02784097194672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05665266513824</t>
   </si>
   <si>
     <t xml:space="preserve">1.06134271621704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07742369174957</t>
+    <t xml:space="preserve">1.07742381095886</t>
   </si>
   <si>
     <t xml:space="preserve">1.07943391799927</t>
@@ -1142,103 +1142,103 @@
     <t xml:space="preserve">1.06938326358795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05933272838593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03856146335602</t>
+    <t xml:space="preserve">1.05933260917664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03856134414673</t>
   </si>
   <si>
     <t xml:space="preserve">1.02683579921722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03588151931763</t>
+    <t xml:space="preserve">1.03588128089905</t>
   </si>
   <si>
     <t xml:space="preserve">1.04191172122955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996349036693573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971222460269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995343923568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944420874118805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953131496906281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941405892372131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959831774234772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946431219577789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957821607589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950451254844666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936380505561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967202305793762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991323590278625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975577712059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993333876132965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00003409385681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00137448310852</t>
+    <t xml:space="preserve">0.996349096298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971222519874573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99534410238266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944420993328094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953131377696991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941405773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959831953048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946431279182434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957821786403656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950451195240021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936380624771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967202365398407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99132376909256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975577771663666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99333393573761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0000342130661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00137436389923</t>
   </si>
   <si>
     <t xml:space="preserve">0.991658806800842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00673472881317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999364197254181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04023659229279</t>
+    <t xml:space="preserve">1.00673460960388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999364137649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04023671150208</t>
   </si>
   <si>
     <t xml:space="preserve">1.04157662391663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04224669933319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04961705207825</t>
+    <t xml:space="preserve">1.04224681854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04961717128754</t>
   </si>
   <si>
     <t xml:space="preserve">1.04995226860046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06268286705017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0720636844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05832755565643</t>
+    <t xml:space="preserve">1.06268298625946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07206356525421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05832767486572</t>
   </si>
   <si>
     <t xml:space="preserve">1.06335294246674</t>
@@ -1247,19 +1247,19 @@
     <t xml:space="preserve">1.07407367229462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08043885231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08546423912048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09048974514008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09484469890594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09819507598877</t>
+    <t xml:space="preserve">1.08043897151947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08546435832977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09048962593079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09484481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09819495677948</t>
   </si>
   <si>
     <t xml:space="preserve">1.09853005409241</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">1.12198150157928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11762607097626</t>
+    <t xml:space="preserve">1.11762619018555</t>
   </si>
   <si>
     <t xml:space="preserve">1.11729121208191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10724067687988</t>
+    <t xml:space="preserve">1.10724055767059</t>
   </si>
   <si>
     <t xml:space="preserve">1.10757565498352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12265157699585</t>
+    <t xml:space="preserve">1.12265145778656</t>
   </si>
   <si>
     <t xml:space="preserve">1.13002192974091</t>
@@ -1298,28 +1298,28 @@
     <t xml:space="preserve">1.03387117385864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03895270824432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05287528038025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04208528995514</t>
+    <t xml:space="preserve">1.03895282745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05287516117096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04208552837372</t>
   </si>
   <si>
     <t xml:space="preserve">1.04730618000031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02572667598724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00693154335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980827152729034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998926043510437</t>
+    <t xml:space="preserve">1.02572679519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00693142414093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980827271938324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998926162719727</t>
   </si>
   <si>
     <t xml:space="preserve">1.01076030731201</t>
@@ -1328,46 +1328,46 @@
     <t xml:space="preserve">1.00484335422516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02920722961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00936782360077</t>
+    <t xml:space="preserve">1.02920734882355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00936806201935</t>
   </si>
   <si>
     <t xml:space="preserve">1.00658357143402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999622344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968993127346039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01598119735718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02398633956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0316436290741</t>
+    <t xml:space="preserve">0.999622285366058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968993246555328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01598107814789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02398645877838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03164374828339</t>
   </si>
   <si>
     <t xml:space="preserve">1.02851116657257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01980972290039</t>
+    <t xml:space="preserve">1.01980984210968</t>
   </si>
   <si>
     <t xml:space="preserve">1.04382562637329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04661023616791</t>
+    <t xml:space="preserve">1.04660999774933</t>
   </si>
   <si>
     <t xml:space="preserve">1.02363836765289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02537858486176</t>
+    <t xml:space="preserve">1.02537870407104</t>
   </si>
   <si>
     <t xml:space="preserve">1.00588750839233</t>
@@ -1376,28 +1376,28 @@
     <t xml:space="preserve">1.01250052452087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02120196819305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02642273902893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03373193740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01389276981354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03860485553741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0511349439621</t>
+    <t xml:space="preserve">1.02120208740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02642285823822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03373205661774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01389265060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0386049747467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05113482475281</t>
   </si>
   <si>
     <t xml:space="preserve">1.06122863292694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07236659526825</t>
+    <t xml:space="preserve">1.07236635684967</t>
   </si>
   <si>
     <t xml:space="preserve">1.06018447875977</t>
@@ -1406,46 +1406,46 @@
     <t xml:space="preserve">1.06262075901031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05600774288177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07375872135162</t>
+    <t xml:space="preserve">1.05600762367249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07375860214233</t>
   </si>
   <si>
     <t xml:space="preserve">1.06714558601379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0786315202713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09290182590485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09429407119751</t>
+    <t xml:space="preserve">1.07863140106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09290206432343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09429395198822</t>
   </si>
   <si>
     <t xml:space="preserve">1.10160326957703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08420038223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04835045337677</t>
+    <t xml:space="preserve">1.08420050144196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04835033416748</t>
   </si>
   <si>
     <t xml:space="preserve">1.06157660484314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07201826572418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07584726810455</t>
+    <t xml:space="preserve">1.07201838493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07584702968597</t>
   </si>
   <si>
     <t xml:space="preserve">1.0713222026825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09394598007202</t>
+    <t xml:space="preserve">1.09394609928131</t>
   </si>
   <si>
     <t xml:space="preserve">1.08106791973114</t>
@@ -1454,25 +1454,25 @@
     <t xml:space="preserve">1.09011745452881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08246004581451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10299563407898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12005043029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12387895584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10473585128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10612809658051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11134898662567</t>
+    <t xml:space="preserve">1.0824601650238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10299551486969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12005031108856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12387907505035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10473573207855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10612797737122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11134886741638</t>
   </si>
   <si>
     <t xml:space="preserve">1.10821640491486</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">1.10960865020752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08837711811066</t>
+    <t xml:space="preserve">1.08837723731995</t>
   </si>
   <si>
     <t xml:space="preserve">1.08802902698517</t>
@@ -1490,10 +1490,10 @@
     <t xml:space="preserve">1.08942127227783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07549893856049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06540524959564</t>
+    <t xml:space="preserve">1.0754988193512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06540536880493</t>
   </si>
   <si>
     <t xml:space="preserve">1.03338408470154</t>
@@ -1508,37 +1508,37 @@
     <t xml:space="preserve">1.03094756603241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04173743724823</t>
+    <t xml:space="preserve">1.04173731803894</t>
   </si>
   <si>
     <t xml:space="preserve">1.05705189704895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07897937297821</t>
+    <t xml:space="preserve">1.0789794921875</t>
   </si>
   <si>
     <t xml:space="preserve">1.09220564365387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09116160869598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08454847335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08141589164734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09847068786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09603440761566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07619512081146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07445478439331</t>
+    <t xml:space="preserve">1.09116148948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08454835414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08141601085663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0984708070755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09603428840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07619500160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07445466518402</t>
   </si>
   <si>
     <t xml:space="preserve">1.05879211425781</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">1.04417371749878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05183112621307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03616833686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05844414234161</t>
+    <t xml:space="preserve">1.05183100700378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03616845607758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05844402313232</t>
   </si>
   <si>
     <t xml:space="preserve">1.03442811965942</t>
@@ -1577,28 +1577,28 @@
     <t xml:space="preserve">1.00310277938843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991617023944855</t>
+    <t xml:space="preserve">0.99161696434021</t>
   </si>
   <si>
     <t xml:space="preserve">1.00832378864288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01424062252045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01772117614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01354455947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993705213069916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98813658952713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97734671831131</t>
+    <t xml:space="preserve">1.01424074172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01772141456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01354467868805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993705272674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988136351108551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977346658706665</t>
   </si>
   <si>
     <t xml:space="preserve">1.00553941726685</t>
@@ -1607,16 +1607,16 @@
     <t xml:space="preserve">0.9860480427742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989528715610504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992313206195831</t>
+    <t xml:space="preserve">0.98952853679657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992313146591187</t>
   </si>
   <si>
     <t xml:space="preserve">0.982915580272675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991965055465698</t>
+    <t xml:space="preserve">0.991964995861053</t>
   </si>
   <si>
     <t xml:space="preserve">1.01319658756256</t>
@@ -1625,37 +1625,37 @@
     <t xml:space="preserve">1.00414705276489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02050566673279</t>
+    <t xml:space="preserve">1.02050578594208</t>
   </si>
   <si>
     <t xml:space="preserve">1.0156329870224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0351243019104</t>
+    <t xml:space="preserve">1.03512418270111</t>
   </si>
   <si>
     <t xml:space="preserve">1.03930103778839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05252707004547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05461549758911</t>
+    <t xml:space="preserve">1.05252718925476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05461537837982</t>
   </si>
   <si>
     <t xml:space="preserve">1.03721261024475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0271190404892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03999698162079</t>
+    <t xml:space="preserve">1.02711892127991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03999710083008</t>
   </si>
   <si>
     <t xml:space="preserve">1.06610143184662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06088066101074</t>
+    <t xml:space="preserve">1.06088054180145</t>
   </si>
   <si>
     <t xml:space="preserve">1.04034519195557</t>
@@ -1664,25 +1664,25 @@
     <t xml:space="preserve">1.03233981132507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04278159141541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04347765445709</t>
+    <t xml:space="preserve">1.04278147220612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04347741603851</t>
   </si>
   <si>
     <t xml:space="preserve">1.07410657405853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10090720653534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11761391162872</t>
+    <t xml:space="preserve">1.10090708732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11761403083801</t>
   </si>
   <si>
     <t xml:space="preserve">1.12701153755188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1137855052948</t>
+    <t xml:space="preserve">1.11378538608551</t>
   </si>
   <si>
     <t xml:space="preserve">1.1064760684967</t>
@@ -1691,46 +1691,46 @@
     <t xml:space="preserve">1.12318289279938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13118815422058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11448156833649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08872520923615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09464204311371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11622166633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1183100938797</t>
+    <t xml:space="preserve">1.13118827342987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1144814491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08872509002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09464228153229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11622178554535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11831021308899</t>
   </si>
   <si>
     <t xml:space="preserve">1.13501691818237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13675701618195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13814949989319</t>
+    <t xml:space="preserve">1.13675713539124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13814926147461</t>
   </si>
   <si>
     <t xml:space="preserve">1.14302217960358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10403978824615</t>
+    <t xml:space="preserve">1.10403966903687</t>
   </si>
   <si>
     <t xml:space="preserve">1.10891258716583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09951484203339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10195124149323</t>
+    <t xml:space="preserve">1.09951496124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10195136070251</t>
   </si>
   <si>
     <t xml:space="preserve">1.09916687011719</t>
@@ -1739,70 +1739,70 @@
     <t xml:space="preserve">1.0949901342392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10578000545502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09185767173767</t>
+    <t xml:space="preserve">1.10578012466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09185779094696</t>
   </si>
   <si>
     <t xml:space="preserve">1.07793533802032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08071994781494</t>
+    <t xml:space="preserve">1.08071970939636</t>
   </si>
   <si>
     <t xml:space="preserve">1.08663666248322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06227278709412</t>
+    <t xml:space="preserve">1.06227290630341</t>
   </si>
   <si>
     <t xml:space="preserve">1.08280813694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09742665290833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10021114349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09777462482452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10369169712067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11100077629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10543215274811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08594071865082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09568619728088</t>
+    <t xml:space="preserve">1.09742677211761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10021102428436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09777474403381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10369157791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11100089550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10543191432953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08594048023224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09568643569946</t>
   </si>
   <si>
     <t xml:space="preserve">1.08907318115234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11726582050323</t>
+    <t xml:space="preserve">1.11726593971252</t>
   </si>
   <si>
     <t xml:space="preserve">1.12074661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10752034187317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1103048324585</t>
+    <t xml:space="preserve">1.10752010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11030471324921</t>
   </si>
   <si>
     <t xml:space="preserve">1.12179064750671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11935424804688</t>
+    <t xml:space="preserve">1.11935436725616</t>
   </si>
   <si>
     <t xml:space="preserve">1.13571298122406</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">1.13536489009857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13084030151367</t>
+    <t xml:space="preserve">1.13084006309509</t>
   </si>
   <si>
     <t xml:space="preserve">1.13223242759705</t>
@@ -1820,34 +1820,34 @@
     <t xml:space="preserve">1.14754700660706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06331694126129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05391943454742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04626214504242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05426728725433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04869854450226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02433443069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01946151256561</t>
+    <t xml:space="preserve">1.06331706047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05391919612885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04626190662384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05426752567291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04869842529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02433454990387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01946139335632</t>
   </si>
   <si>
     <t xml:space="preserve">1.01632916927338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0037989616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997882187366486</t>
+    <t xml:space="preserve">1.00379908084869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997882068157196</t>
   </si>
   <si>
     <t xml:space="preserve">1.00727963447571</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">1.02015781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07654309272766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08517646789551</t>
+    <t xml:space="preserve">1.07654297351837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08517634868622</t>
   </si>
   <si>
     <t xml:space="preserve">1.09720551967621</t>
@@ -1886,43 +1886,43 @@
     <t xml:space="preserve">1.06403422355652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07168924808502</t>
+    <t xml:space="preserve">1.07168912887573</t>
   </si>
   <si>
     <t xml:space="preserve">1.08043766021729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0979346036911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09866344928741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10449600219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10048627853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10230875015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.095747590065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09829914569855</t>
+    <t xml:space="preserve">1.09793448448181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0986635684967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10449588298798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10048615932465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10230886936188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09574735164642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09829902648926</t>
   </si>
   <si>
     <t xml:space="preserve">1.13219952583313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12563824653625</t>
+    <t xml:space="preserve">1.12563812732697</t>
   </si>
   <si>
     <t xml:space="preserve">1.1402188539505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14750933647156</t>
+    <t xml:space="preserve">1.14750945568085</t>
   </si>
   <si>
     <t xml:space="preserve">1.13584470748901</t>
@@ -1934,25 +1934,25 @@
     <t xml:space="preserve">1.11543154716492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10376703739166</t>
+    <t xml:space="preserve">1.10376679897308</t>
   </si>
   <si>
     <t xml:space="preserve">1.11251544952393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11069285869598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13511562347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15006077289581</t>
+    <t xml:space="preserve">1.11069273948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13511550426483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1500608921051</t>
   </si>
   <si>
     <t xml:space="preserve">1.15188348293304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.147873878479</t>
+    <t xml:space="preserve">1.14787375926971</t>
   </si>
   <si>
     <t xml:space="preserve">1.15261256694794</t>
@@ -1970,10 +1970,10 @@
     <t xml:space="preserve">1.17229676246643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17849373817444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17484831809998</t>
+    <t xml:space="preserve">1.17849349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17484843730927</t>
   </si>
   <si>
     <t xml:space="preserve">1.19161629676819</t>
@@ -1985,13 +1985,13 @@
     <t xml:space="preserve">1.16609978675842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17995154857635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18469047546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1810450553894</t>
+    <t xml:space="preserve">1.17995178699493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18469035625458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18104517459869</t>
   </si>
   <si>
     <t xml:space="preserve">1.17120325565338</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">1.14969646930695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15407061576843</t>
+    <t xml:space="preserve">1.15407073497772</t>
   </si>
   <si>
     <t xml:space="preserve">1.17083859443665</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">1.16209018230438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16682887077332</t>
+    <t xml:space="preserve">1.1668289899826</t>
   </si>
   <si>
     <t xml:space="preserve">1.16755795478821</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">1.13183498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12418007850647</t>
+    <t xml:space="preserve">1.12417995929718</t>
   </si>
   <si>
     <t xml:space="preserve">1.12782526016235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14277052879333</t>
+    <t xml:space="preserve">1.14277064800262</t>
   </si>
   <si>
     <t xml:space="preserve">1.16099655628204</t>
@@ -2045,34 +2045,34 @@
     <t xml:space="preserve">1.13985455036163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13475120067596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16391265392303</t>
+    <t xml:space="preserve">1.13475108146667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16391277313232</t>
   </si>
   <si>
     <t xml:space="preserve">1.16938054561615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16573524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16500627994537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18833565711975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20473885536194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20036470890045</t>
+    <t xml:space="preserve">1.16573536396027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16500639915466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18833541870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20473909378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20036482810974</t>
   </si>
   <si>
     <t xml:space="preserve">1.18870007991791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1795871257782</t>
+    <t xml:space="preserve">1.17958700656891</t>
   </si>
   <si>
     <t xml:space="preserve">1.16464173793793</t>
@@ -2084,61 +2084,61 @@
     <t xml:space="preserve">1.18213880062103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17630636692047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19599032402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18979358673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22551679611206</t>
+    <t xml:space="preserve">1.17630648612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19599044322968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18979370594025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22551667690277</t>
   </si>
   <si>
     <t xml:space="preserve">1.21567463874817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22770369052887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23207807540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21421670913696</t>
+    <t xml:space="preserve">1.22770392894745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23207819461823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21421647071838</t>
   </si>
   <si>
     <t xml:space="preserve">1.21166479587555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23134899139404</t>
+    <t xml:space="preserve">1.23134911060333</t>
   </si>
   <si>
     <t xml:space="preserve">1.23025548458099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21603906154633</t>
+    <t xml:space="preserve">1.21603918075562</t>
   </si>
   <si>
     <t xml:space="preserve">1.21931982040405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2379105091095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23462986946106</t>
+    <t xml:space="preserve">1.23791038990021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23462975025177</t>
   </si>
   <si>
     <t xml:space="preserve">1.22806835174561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21640360355377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22187149524689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22114229202271</t>
+    <t xml:space="preserve">1.21640348434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2218713760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22114241123199</t>
   </si>
   <si>
     <t xml:space="preserve">1.22405862808228</t>
@@ -2153,25 +2153,25 @@
     <t xml:space="preserve">1.23645222187042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22879731655121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22624564170837</t>
+    <t xml:space="preserve">1.2287974357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22624576091766</t>
   </si>
   <si>
     <t xml:space="preserve">1.27363324165344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27691400051117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31154346466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3133659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30972075462341</t>
+    <t xml:space="preserve">1.27691388130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31154334545135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31336605548859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30972063541412</t>
   </si>
   <si>
     <t xml:space="preserve">1.30826270580292</t>
@@ -2180,34 +2180,34 @@
     <t xml:space="preserve">1.31591749191284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29331743717194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31518852710724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31445932388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30862724781036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29732716083527</t>
+    <t xml:space="preserve">1.29331731796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31518864631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31445956230164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30862712860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29732704162598</t>
   </si>
   <si>
     <t xml:space="preserve">1.27873659133911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28857862949371</t>
+    <t xml:space="preserve">1.288578748703</t>
   </si>
   <si>
     <t xml:space="preserve">1.28420436382294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27727854251862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27509140968323</t>
+    <t xml:space="preserve">1.27727830410004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27509117126465</t>
   </si>
   <si>
     <t xml:space="preserve">1.26452040672302</t>
@@ -2216,13 +2216,13 @@
     <t xml:space="preserve">1.24884593486786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24665892124176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25249099731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24520075321198</t>
+    <t xml:space="preserve">1.24665880203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25249123573303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2452005147934</t>
   </si>
   <si>
     <t xml:space="preserve">1.24483621120453</t>
@@ -2231,40 +2231,40 @@
     <t xml:space="preserve">1.19052267074585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19635510444641</t>
+    <t xml:space="preserve">1.1963552236557</t>
   </si>
   <si>
     <t xml:space="preserve">1.19854235649109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19343876838684</t>
+    <t xml:space="preserve">1.19343888759613</t>
   </si>
   <si>
     <t xml:space="preserve">1.18068063259125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20218729972839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18906450271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19270980358124</t>
+    <t xml:space="preserve">1.20218741893768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18906474113464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19270992279053</t>
   </si>
   <si>
     <t xml:space="preserve">1.20656156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20729064941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22515201568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2415554523468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23353624343872</t>
+    <t xml:space="preserve">1.20729076862335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22515213489532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24155557155609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23353612422943</t>
   </si>
   <si>
     <t xml:space="preserve">1.2189553976059</t>
@@ -2273,10 +2273,10 @@
     <t xml:space="preserve">1.2127583026886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20838415622711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25504279136658</t>
+    <t xml:space="preserve">1.2083842754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25504267215729</t>
   </si>
   <si>
     <t xml:space="preserve">1.2506685256958</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">1.25941705703735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25650072097778</t>
+    <t xml:space="preserve">1.25650084018707</t>
   </si>
   <si>
     <t xml:space="preserve">1.26853001117706</t>
@@ -2294,61 +2294,61 @@
     <t xml:space="preserve">1.2998788356781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30315947532654</t>
+    <t xml:space="preserve">1.30315935611725</t>
   </si>
   <si>
     <t xml:space="preserve">1.29368197917938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2922238111496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30607569217682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35200536251068</t>
+    <t xml:space="preserve">1.29222393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30607545375824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3520051240921</t>
   </si>
   <si>
     <t xml:space="preserve">1.34544372558594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414351940155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31409513950348</t>
+    <t xml:space="preserve">1.33414363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31409502029419</t>
   </si>
   <si>
     <t xml:space="preserve">1.3224790096283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32940483093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34580826759338</t>
+    <t xml:space="preserve">1.32940495014191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34580838680267</t>
   </si>
   <si>
     <t xml:space="preserve">1.33159196376801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33013379573822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34981799125671</t>
+    <t xml:space="preserve">1.33013391494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.349818110466</t>
   </si>
   <si>
     <t xml:space="preserve">1.34398579597473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34143424034119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34945344924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35893094539642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36986649036407</t>
+    <t xml:space="preserve">1.34143400192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34945356845856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35893106460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36986660957336</t>
   </si>
   <si>
     <t xml:space="preserve">1.3822603225708</t>
@@ -2357,16 +2357,16 @@
     <t xml:space="preserve">1.36038911342621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34908890724182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26524949073792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25613641738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13766729831696</t>
+    <t xml:space="preserve">1.34908902645111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26524937152863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25613629817963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13766741752625</t>
   </si>
   <si>
     <t xml:space="preserve">1.15589332580566</t>
@@ -2378,13 +2378,13 @@
     <t xml:space="preserve">1.11579620838165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996233463287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924787521362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905467927455902</t>
+    <t xml:space="preserve">0.996233582496643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924787640571594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905468046665192</t>
   </si>
   <si>
     <t xml:space="preserve">0.733049988746643</t>
@@ -2393,16 +2393,16 @@
     <t xml:space="preserve">0.772782683372498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.750546872615814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775334239006042</t>
+    <t xml:space="preserve">0.750546991825104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775334358215332</t>
   </si>
   <si>
     <t xml:space="preserve">0.751276075839996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.754556596279144</t>
+    <t xml:space="preserve">0.754556655883789</t>
   </si>
   <si>
     <t xml:space="preserve">0.741433918476105</t>
@@ -2414,22 +2414,22 @@
     <t xml:space="preserve">0.786269962787628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79720550775528</t>
+    <t xml:space="preserve">0.797205567359924</t>
   </si>
   <si>
     <t xml:space="preserve">0.793195843696594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778250396251678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824544489383698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826002657413483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816160619258881</t>
+    <t xml:space="preserve">0.778250515460968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824544548988342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826002597808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816160500049591</t>
   </si>
   <si>
     <t xml:space="preserve">0.841677010059357</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">0.836209177970886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869015991687775</t>
+    <t xml:space="preserve">0.869016051292419</t>
   </si>
   <si>
     <t xml:space="preserve">0.869745016098022</t>
@@ -2447,100 +2447,100 @@
     <t xml:space="preserve">0.855164170265198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.876670837402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889429152011871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885783970355988</t>
+    <t xml:space="preserve">0.876670897006989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889429032802582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885783851146698</t>
   </si>
   <si>
     <t xml:space="preserve">0.897448539733887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910935819149017</t>
+    <t xml:space="preserve">0.910935938358307</t>
   </si>
   <si>
     <t xml:space="preserve">0.91166478395462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.883961260318756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888335406780243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879587173461914</t>
+    <t xml:space="preserve">0.883961200714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888335466384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879587233066559</t>
   </si>
   <si>
     <t xml:space="preserve">0.890158116817474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906926035881042</t>
+    <t xml:space="preserve">0.906926095485687</t>
   </si>
   <si>
     <t xml:space="preserve">0.901458323001862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89963561296463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905832529067993</t>
+    <t xml:space="preserve">0.899635672569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905832409858704</t>
   </si>
   <si>
     <t xml:space="preserve">0.872296571731567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.879951536655426</t>
+    <t xml:space="preserve">0.879951596260071</t>
   </si>
   <si>
     <t xml:space="preserve">0.878128945827484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.882138609886169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877764403820038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914581000804901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93426501750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911300182342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944332599639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902750670909882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914020419120789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910523056983948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912854731082916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946275532245636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971146881580353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950550258159637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971535444259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969592332839966</t>
+    <t xml:space="preserve">0.882138669490814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877764463424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914580941200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934265077114105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911300301551819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944332480430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902750730514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914020538330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910522937774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912854671478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946275472640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971147000789642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950550377368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971535503864288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9695925116539</t>
   </si>
   <si>
     <t xml:space="preserve">0.981639504432678</t>
@@ -2549,25 +2549,25 @@
     <t xml:space="preserve">1.00573360919952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04265189170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04342913627625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03060483932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05236721038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02710735797882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0119514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960265576839447</t>
+    <t xml:space="preserve">1.04265177249908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04342901706696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03060472011566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05236709117889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02710723876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01195132732391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960265755653381</t>
   </si>
   <si>
     <t xml:space="preserve">0.956379473209381</t>
@@ -2576,82 +2576,82 @@
     <t xml:space="preserve">0.978141903877258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01156270503998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01778042316437</t>
+    <t xml:space="preserve">1.01156282424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01778054237366</t>
   </si>
   <si>
     <t xml:space="preserve">1.00961971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0193350315094</t>
+    <t xml:space="preserve">1.01933491230011</t>
   </si>
   <si>
     <t xml:space="preserve">1.01467168331146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97231262922287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963763177394867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977364838123322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979696333408356</t>
+    <t xml:space="preserve">0.972312748432159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963763236999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977364778518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979696393013</t>
   </si>
   <si>
     <t xml:space="preserve">0.984359800815582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999904274940491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996795415878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993686378002167</t>
+    <t xml:space="preserve">0.999904453754425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996795535087585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993686556816101</t>
   </si>
   <si>
     <t xml:space="preserve">0.983193933963776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98280531167984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958322584629059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961431562900543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960654199123383</t>
+    <t xml:space="preserve">0.982805371284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958322644233704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961431503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960654258728027</t>
   </si>
   <si>
     <t xml:space="preserve">0.973867177963257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973089933395386</t>
+    <t xml:space="preserve">0.973089873790741</t>
   </si>
   <si>
     <t xml:space="preserve">0.985137045383453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987857341766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985525608062744</t>
+    <t xml:space="preserve">0.987857401371002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985525667667389</t>
   </si>
   <si>
     <t xml:space="preserve">0.949773132801056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954436421394348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970758199691772</t>
+    <t xml:space="preserve">0.954436480998993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970758259296417</t>
   </si>
   <si>
     <t xml:space="preserve">0.92878794670105</t>
@@ -2663,40 +2663,40 @@
     <t xml:space="preserve">0.955990970134735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959877014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953659296035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965317606925964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982028067111969</t>
+    <t xml:space="preserve">0.959877133369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953659236431122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965317726135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982028007507324</t>
   </si>
   <si>
     <t xml:space="preserve">1.01739192008972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00612211227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994852244853973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979307889938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989411652088165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987079977989197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964929044246674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96259731054306</t>
+    <t xml:space="preserve">1.00612223148346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994852423667908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979307770729065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989411771297455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987080156803131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964929103851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962597370147705</t>
   </si>
   <si>
     <t xml:space="preserve">0.958711266517639</t>
@@ -2705,10 +2705,10 @@
     <t xml:space="preserve">0.966094970703125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.951327443122864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954047739505768</t>
+    <t xml:space="preserve">0.951327502727509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954047858715057</t>
   </si>
   <si>
     <t xml:space="preserve">0.975033044815063</t>
@@ -2717,112 +2717,112 @@
     <t xml:space="preserve">0.968038022518158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937726080417633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946664273738861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938503205776215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942000806331635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933451175689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971924185752869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94899582862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953270673751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945886850357056</t>
+    <t xml:space="preserve">0.937726199626923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946664214134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938503324985504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94200074672699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933451354503632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971924126148224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948995888233185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953270614147186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945886969566345</t>
   </si>
   <si>
     <t xml:space="preserve">0.929565191268921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931119620800018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900807738304138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903528034687042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.904693841934204</t>
+    <t xml:space="preserve">0.931119561195374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900807678699493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903527975082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904693901538849</t>
   </si>
   <si>
     <t xml:space="preserve">0.898864567279816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878656685352325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886428952217102</t>
+    <t xml:space="preserve">0.878656625747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886428892612457</t>
   </si>
   <si>
     <t xml:space="preserve">0.90158486366272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.886040389537811</t>
+    <t xml:space="preserve">0.886040270328522</t>
   </si>
   <si>
     <t xml:space="preserve">0.840961158275604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830079793930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848344743251801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860780358314514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872050225734711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898476123809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892646729946136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.881377041339874</t>
+    <t xml:space="preserve">0.830079913139343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848344922065735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860780298709869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872050166130066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89847606420517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892646670341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.881376922130585</t>
   </si>
   <si>
     <t xml:space="preserve">0.94277811050415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939280450344086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955213606357574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95249330997467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947441399097443</t>
+    <t xml:space="preserve">0.939280569553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955213725566864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952493369579315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947441339492798</t>
   </si>
   <si>
     <t xml:space="preserve">0.952104866504669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959488451480865</t>
+    <t xml:space="preserve">0.95948851108551</t>
   </si>
   <si>
     <t xml:space="preserve">0.97619891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01700353622437</t>
+    <t xml:space="preserve">1.01700329780579</t>
   </si>
   <si>
     <t xml:space="preserve">1.02205538749695</t>
@@ -2834,22 +2834,22 @@
     <t xml:space="preserve">0.982416749000549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975421607494354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976587474346161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997183978557587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990966081619263</t>
+    <t xml:space="preserve">0.975421667098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976587533950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997184157371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990966260433197</t>
   </si>
   <si>
     <t xml:space="preserve">0.988245904445648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984748244285583</t>
+    <t xml:space="preserve">0.984748423099518</t>
   </si>
   <si>
     <t xml:space="preserve">0.995629668235779</t>
@@ -2861,13 +2861,13 @@
     <t xml:space="preserve">1.0065108537674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01583755016327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01389443874359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03449094295502</t>
+    <t xml:space="preserve">1.01583743095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0138943195343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03449082374573</t>
   </si>
   <si>
     <t xml:space="preserve">1.02399837970734</t>
@@ -2876,22 +2876,22 @@
     <t xml:space="preserve">1.04148602485657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03954303264618</t>
+    <t xml:space="preserve">1.03954291343689</t>
   </si>
   <si>
     <t xml:space="preserve">1.03487956523895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01428306102753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0375999212265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03215932846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02050077915192</t>
+    <t xml:space="preserve">1.01428294181824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03759980201721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0321592092514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02050089836121</t>
   </si>
   <si>
     <t xml:space="preserve">1.03099346160889</t>
@@ -2900,10 +2900,10 @@
     <t xml:space="preserve">1.06596875190735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0729638338089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04653811454773</t>
+    <t xml:space="preserve">1.07296371459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04653799533844</t>
   </si>
   <si>
     <t xml:space="preserve">1.0589736700058</t>
@@ -2921,25 +2921,25 @@
     <t xml:space="preserve">1.10871624946594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13630795478821</t>
+    <t xml:space="preserve">1.13630783557892</t>
   </si>
   <si>
     <t xml:space="preserve">1.15418422222137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12853562831879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13825082778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1425256729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17516922950745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16195631027222</t>
+    <t xml:space="preserve">1.12853574752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1382509469986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14252579212189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17516934871674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1619565486908</t>
   </si>
   <si>
     <t xml:space="preserve">1.13863968849182</t>
@@ -2948,16 +2948,16 @@
     <t xml:space="preserve">1.12154054641724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13475358486176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12698113918304</t>
+    <t xml:space="preserve">1.13475346565247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12698125839233</t>
   </si>
   <si>
     <t xml:space="preserve">1.11415696144104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10366427898407</t>
+    <t xml:space="preserve">1.10366415977478</t>
   </si>
   <si>
     <t xml:space="preserve">1.11221385002136</t>
@@ -2966,25 +2966,25 @@
     <t xml:space="preserve">1.09317171573639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08384501934052</t>
+    <t xml:space="preserve">1.08384490013123</t>
   </si>
   <si>
     <t xml:space="preserve">1.11493408679962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1071617603302</t>
+    <t xml:space="preserve">1.10716187953949</t>
   </si>
   <si>
     <t xml:space="preserve">1.07918155193329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08656513690948</t>
+    <t xml:space="preserve">1.08656525611877</t>
   </si>
   <si>
     <t xml:space="preserve">1.0772385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10832762718201</t>
+    <t xml:space="preserve">1.1083277463913</t>
   </si>
   <si>
     <t xml:space="preserve">1.1308673620224</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">1.15262973308563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14874351024628</t>
+    <t xml:space="preserve">1.14874362945557</t>
   </si>
   <si>
     <t xml:space="preserve">1.15496134757996</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">1.16312229633331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14563453197479</t>
+    <t xml:space="preserve">1.14563465118408</t>
   </si>
   <si>
     <t xml:space="preserve">1.15301835536957</t>
@@ -3011,13 +3011,13 @@
     <t xml:space="preserve">1.14641189575195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17089462280273</t>
+    <t xml:space="preserve">1.17089450359344</t>
   </si>
   <si>
     <t xml:space="preserve">1.18954813480377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20470404624939</t>
+    <t xml:space="preserve">1.2047039270401</t>
   </si>
   <si>
     <t xml:space="preserve">1.20664703845978</t>
@@ -3026,55 +3026,55 @@
     <t xml:space="preserve">1.21558511257172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21752822399139</t>
+    <t xml:space="preserve">1.2175281047821</t>
   </si>
   <si>
     <t xml:space="preserve">1.20625841617584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20392680168152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20859003067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22413468360901</t>
+    <t xml:space="preserve">1.20392668247223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20859014987946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2241348028183</t>
   </si>
   <si>
     <t xml:space="preserve">1.20975589752197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19809758663177</t>
+    <t xml:space="preserve">1.19809746742249</t>
   </si>
   <si>
     <t xml:space="preserve">1.21286487579346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21597385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21325361728668</t>
+    <t xml:space="preserve">1.21597373485565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2132533788681</t>
   </si>
   <si>
     <t xml:space="preserve">1.20431530475616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21247625350952</t>
+    <t xml:space="preserve">1.21247613430023</t>
   </si>
   <si>
     <t xml:space="preserve">1.22685503959656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21403086185455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23579323291779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23812484741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23851346969604</t>
+    <t xml:space="preserve">1.21403074264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2357931137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23812472820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23851335048676</t>
   </si>
   <si>
     <t xml:space="preserve">1.24278819561005</t>
@@ -3083,34 +3083,34 @@
     <t xml:space="preserve">1.26105296611786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26455044746399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27582037448883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26066446304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26493942737579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27892923355103</t>
+    <t xml:space="preserve">1.26455056667328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27582049369812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26066434383392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26493918895721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27892935276031</t>
   </si>
   <si>
     <t xml:space="preserve">1.3045779466629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31779074668884</t>
+    <t xml:space="preserve">1.31779086589813</t>
   </si>
   <si>
     <t xml:space="preserve">1.29291939735413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29874849319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31740212440491</t>
+    <t xml:space="preserve">1.29874861240387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3174022436142</t>
   </si>
   <si>
     <t xml:space="preserve">1.33061492443085</t>
@@ -3119,19 +3119,19 @@
     <t xml:space="preserve">1.34693682193756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34382772445679</t>
+    <t xml:space="preserve">1.34382784366608</t>
   </si>
   <si>
     <t xml:space="preserve">1.3484913110733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35121142864227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37258541584015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40067195892334</t>
+    <t xml:space="preserve">1.35121154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37258529663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40067207813263</t>
   </si>
   <si>
     <t xml:space="preserve">1.37502765655518</t>
@@ -3155,22 +3155,22 @@
     <t xml:space="preserve">1.39456629753113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38886737823486</t>
+    <t xml:space="preserve">1.38886749744415</t>
   </si>
   <si>
     <t xml:space="preserve">1.41044127941132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42306005954742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43323624134064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45847368240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43852806091309</t>
+    <t xml:space="preserve">1.42305994033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43323636054993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45847380161285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43852818012238</t>
   </si>
   <si>
     <t xml:space="preserve">1.43771398067474</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">1.44951856136322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4572526216507</t>
+    <t xml:space="preserve">1.45725250244141</t>
   </si>
   <si>
     <t xml:space="preserve">1.45765960216522</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">1.45521724224091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43120110034943</t>
+    <t xml:space="preserve">1.43120121955872</t>
   </si>
   <si>
     <t xml:space="preserve">1.4430056810379</t>
@@ -3203,10 +3203,10 @@
     <t xml:space="preserve">1.42713057994843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41858232021332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40352153778076</t>
+    <t xml:space="preserve">1.41858243942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40352141857147</t>
   </si>
   <si>
     <t xml:space="preserve">1.41288375854492</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">1.43527162075043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37950527667999</t>
+    <t xml:space="preserve">1.3795051574707</t>
   </si>
   <si>
     <t xml:space="preserve">1.38072633743286</t>
@@ -3233,19 +3233,19 @@
     <t xml:space="preserve">1.39945089817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41736125946045</t>
+    <t xml:space="preserve">1.41736137866974</t>
   </si>
   <si>
     <t xml:space="preserve">1.40392851829529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40148627758026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34734785556793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3591525554657</t>
+    <t xml:space="preserve">1.40148615837097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34734797477722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35915243625641</t>
   </si>
   <si>
     <t xml:space="preserve">1.38316869735718</t>
@@ -3254,28 +3254,28 @@
     <t xml:space="preserve">1.395787358284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4511467218399</t>
+    <t xml:space="preserve">1.45114684104919</t>
   </si>
   <si>
     <t xml:space="preserve">1.47719812393188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47801244258881</t>
+    <t xml:space="preserve">1.47801232337952</t>
   </si>
   <si>
     <t xml:space="preserve">1.47394180297852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47068536281586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47923338413239</t>
+    <t xml:space="preserve">1.47068524360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47923350334167</t>
   </si>
   <si>
     <t xml:space="preserve">1.46824312210083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47964036464691</t>
+    <t xml:space="preserve">1.4796404838562</t>
   </si>
   <si>
     <t xml:space="preserve">1.49348032474518</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">1.53866326808929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54069864749908</t>
+    <t xml:space="preserve">1.54069852828979</t>
   </si>
   <si>
     <t xml:space="preserve">1.55006086826324</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">1.58669567108154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56593596935272</t>
+    <t xml:space="preserve">1.56593573093414</t>
   </si>
   <si>
     <t xml:space="preserve">1.5838463306427</t>
@@ -3311,10 +3311,10 @@
     <t xml:space="preserve">1.5549453496933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53215026855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52726578712463</t>
+    <t xml:space="preserve">1.53215038776398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52726590633392</t>
   </si>
   <si>
     <t xml:space="preserve">1.52889394760132</t>
@@ -3326,16 +3326,16 @@
     <t xml:space="preserve">1.514240026474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51912474632263</t>
+    <t xml:space="preserve">1.51912462711334</t>
   </si>
   <si>
     <t xml:space="preserve">1.50650596618652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49755072593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.522381067276</t>
+    <t xml:space="preserve">1.49755084514618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52238118648529</t>
   </si>
   <si>
     <t xml:space="preserve">1.49307334423065</t>
@@ -3347,16 +3347,16 @@
     <t xml:space="preserve">1.5162752866745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48615348339081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48940980434418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49063086509705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42794466018677</t>
+    <t xml:space="preserve">1.48615336418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48940968513489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49063098430634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42794454097748</t>
   </si>
   <si>
     <t xml:space="preserve">1.45155382156372</t>
@@ -3377,37 +3377,37 @@
     <t xml:space="preserve">1.48411810398102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45643842220306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45562422275543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43812096118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44544816017151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44015622138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45684540271759</t>
+    <t xml:space="preserve">1.45643854141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45562434196472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43812108039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44544804096222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44015634059906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45684552192688</t>
   </si>
   <si>
     <t xml:space="preserve">1.48737454414368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48533928394318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50406360626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46417236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4450409412384</t>
+    <t xml:space="preserve">1.48533916473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5040637254715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46417248249054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44504082202911</t>
   </si>
   <si>
     <t xml:space="preserve">1.47475576400757</t>
@@ -3428,13 +3428,13 @@
     <t xml:space="preserve">1.50365662574768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52970802783966</t>
+    <t xml:space="preserve">1.52970814704895</t>
   </si>
   <si>
     <t xml:space="preserve">1.53662800788879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57407712936401</t>
+    <t xml:space="preserve">1.57407701015472</t>
   </si>
   <si>
     <t xml:space="preserve">1.55698072910309</t>
@@ -3473,64 +3473,64 @@
     <t xml:space="preserve">1.51953184604645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51546108722687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3921240568161</t>
+    <t xml:space="preserve">1.51546120643616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39212393760681</t>
   </si>
   <si>
     <t xml:space="preserve">1.40596377849579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39538037776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40637075901031</t>
+    <t xml:space="preserve">1.39538025856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4063708782196</t>
   </si>
   <si>
     <t xml:space="preserve">1.45196080207825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43079400062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45806658267975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45440304279327</t>
+    <t xml:space="preserve">1.4307941198349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45806670188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45440316200256</t>
   </si>
   <si>
     <t xml:space="preserve">1.45399618148804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42835175991058</t>
+    <t xml:space="preserve">1.42835187911987</t>
   </si>
   <si>
     <t xml:space="preserve">1.39130973815918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32699537277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34531283378601</t>
+    <t xml:space="preserve">1.32699525356293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34531271457672</t>
   </si>
   <si>
     <t xml:space="preserve">1.34775519371033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36810779571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37177121639252</t>
+    <t xml:space="preserve">1.36810767650604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37177109718323</t>
   </si>
   <si>
     <t xml:space="preserve">1.39741563796997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4002650976181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40677785873413</t>
+    <t xml:space="preserve">1.40026497840881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40677797794342</t>
   </si>
   <si>
     <t xml:space="preserve">1.35548901557922</t>
@@ -3542,16 +3542,16 @@
     <t xml:space="preserve">1.35833835601807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37462067604065</t>
+    <t xml:space="preserve">1.37462055683136</t>
   </si>
   <si>
     <t xml:space="preserve">1.36770057678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35589623451233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35263979434967</t>
+    <t xml:space="preserve">1.35589611530304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35263967514038</t>
   </si>
   <si>
     <t xml:space="preserve">1.33310115337372</t>
@@ -3566,19 +3566,19 @@
     <t xml:space="preserve">1.34164917469025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30664253234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33269393444061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3652583360672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41532588005066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37380647659302</t>
+    <t xml:space="preserve">1.30664265155792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3326940536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36525845527649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41532599925995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37380635738373</t>
   </si>
   <si>
     <t xml:space="preserve">1.3672935962677</t>
@@ -3593,16 +3593,16 @@
     <t xml:space="preserve">1.36973595619202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33513641357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30949211120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28262650966644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30094385147095</t>
+    <t xml:space="preserve">1.33513629436493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30949199199677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28262639045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30094397068024</t>
   </si>
   <si>
     <t xml:space="preserve">1.30542147159576</t>
@@ -3617,10 +3617,10 @@
     <t xml:space="preserve">1.28913938999176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28425455093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28181219100952</t>
+    <t xml:space="preserve">1.28425467014313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28181231021881</t>
   </si>
   <si>
     <t xml:space="preserve">1.27652060985565</t>
@@ -3635,43 +3635,43 @@
     <t xml:space="preserve">1.25046920776367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22482478618622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.281405210495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3001297712326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25494682788849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22848832607269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19918036460876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18249106407166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20243692398071</t>
+    <t xml:space="preserve">1.22482490539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28140532970428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30012989044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2549467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2284882068634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19918060302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18249130249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20243680477142</t>
   </si>
   <si>
     <t xml:space="preserve">1.25616800785065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24639880657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2447704076767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23093068599701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22238266468048</t>
+    <t xml:space="preserve">1.24639868736267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24477052688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23093056678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22238254547119</t>
   </si>
   <si>
     <t xml:space="preserve">1.22116136550903</t>
@@ -3683,7 +3683,7 @@
     <t xml:space="preserve">1.23785054683685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2508761882782</t>
+    <t xml:space="preserve">1.25087630748749</t>
   </si>
   <si>
     <t xml:space="preserve">1.22563886642456</t>
@@ -3698,34 +3698,34 @@
     <t xml:space="preserve">1.25698208808899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27489244937897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25779616832733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26553010940552</t>
+    <t xml:space="preserve">1.27489233016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25779604911804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26553022861481</t>
   </si>
   <si>
     <t xml:space="preserve">1.25942444801331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28751122951508</t>
+    <t xml:space="preserve">1.28751111030579</t>
   </si>
   <si>
     <t xml:space="preserve">1.29768741130829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29809439182281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33554327487946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36281609535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35223257541656</t>
+    <t xml:space="preserve">1.2980945110321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33554339408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36281597614288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35223269462585</t>
   </si>
   <si>
     <t xml:space="preserve">1.3571172952652</t>
@@ -3734,13 +3734,13 @@
     <t xml:space="preserve">1.34856915473938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34409165382385</t>
+    <t xml:space="preserve">1.34409153461456</t>
   </si>
   <si>
     <t xml:space="preserve">1.36485123634338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33961391448975</t>
+    <t xml:space="preserve">1.33961403369904</t>
   </si>
   <si>
     <t xml:space="preserve">1.32129657268524</t>
@@ -3749,10 +3749,10 @@
     <t xml:space="preserve">1.32455289363861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33432233333588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33106589317322</t>
+    <t xml:space="preserve">1.33432221412659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33106577396393</t>
   </si>
   <si>
     <t xml:space="preserve">1.34002101421356</t>
@@ -3770,19 +3770,19 @@
     <t xml:space="preserve">1.35019731521606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34653401374817</t>
+    <t xml:space="preserve">1.34653389453888</t>
   </si>
   <si>
     <t xml:space="preserve">1.34327745437622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38561105728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33147275447845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36037361621857</t>
+    <t xml:space="preserve">1.3856109380722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33147287368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36037373542786</t>
   </si>
   <si>
     <t xml:space="preserve">1.34205627441406</t>
@@ -3794,10 +3794,10 @@
     <t xml:space="preserve">1.36872255802155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37862205505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38507843017578</t>
+    <t xml:space="preserve">1.378622174263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38507831096649</t>
   </si>
   <si>
     <t xml:space="preserve">1.3631272315979</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">1.35796225070953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34504973888397</t>
+    <t xml:space="preserve">1.34504961967468</t>
   </si>
   <si>
     <t xml:space="preserve">1.32998502254486</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">1.270587682724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18708693981171</t>
+    <t xml:space="preserve">1.187087059021</t>
   </si>
   <si>
     <t xml:space="preserve">1.14921045303345</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">1.15050172805786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11563789844513</t>
+    <t xml:space="preserve">1.11563801765442</t>
   </si>
   <si>
     <t xml:space="preserve">1.15437543392181</t>
@@ -3851,19 +3851,19 @@
     <t xml:space="preserve">1.091104388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06570971012115</t>
+    <t xml:space="preserve">1.06570982933044</t>
   </si>
   <si>
     <t xml:space="preserve">1.03945434093475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05581033229828</t>
+    <t xml:space="preserve">1.05581021308899</t>
   </si>
   <si>
     <t xml:space="preserve">1.10143435001373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08593928813934</t>
+    <t xml:space="preserve">1.08593940734863</t>
   </si>
   <si>
     <t xml:space="preserve">1.09540855884552</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">1.0510755777359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07130515575409</t>
+    <t xml:space="preserve">1.07130527496338</t>
   </si>
   <si>
     <t xml:space="preserve">1.06915318965912</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">1.03601109981537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04074561595917</t>
+    <t xml:space="preserve">1.04074573516846</t>
   </si>
   <si>
     <t xml:space="preserve">1.05451893806458</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">1.02955484390259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05882322788239</t>
+    <t xml:space="preserve">1.0588231086731</t>
   </si>
   <si>
     <t xml:space="preserve">1.08120477199554</t>
@@ -3932,13 +3932,13 @@
     <t xml:space="preserve">1.04978430271149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07474851608276</t>
+    <t xml:space="preserve">1.07474839687347</t>
   </si>
   <si>
     <t xml:space="preserve">1.09024357795715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06829237937927</t>
+    <t xml:space="preserve">1.06829226016998</t>
   </si>
   <si>
     <t xml:space="preserve">1.08636963367462</t>
@@ -3959,16 +3959,16 @@
     <t xml:space="preserve">1.10100388526917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10272550582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08292651176453</t>
+    <t xml:space="preserve">1.10272562503815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08292639255524</t>
   </si>
   <si>
     <t xml:space="preserve">1.06097519397736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06355774402618</t>
+    <t xml:space="preserve">1.06355762481689</t>
   </si>
   <si>
     <t xml:space="preserve">1.05839276313782</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">1.01707279682159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996843278408051</t>
+    <t xml:space="preserve">0.996843218803406</t>
   </si>
   <si>
     <t xml:space="preserve">0.999425709247589</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">0.963701248168945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946915090084076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968435704708099</t>
+    <t xml:space="preserve">0.946915030479431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968435764312744</t>
   </si>
   <si>
     <t xml:space="preserve">0.945623755455017</t>
@@ -4001,22 +4001,22 @@
     <t xml:space="preserve">0.939167439937592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920229196548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965422928333282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975322484970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952510416507721</t>
+    <t xml:space="preserve">0.920229136943817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965422868728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975322425365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952510356903076</t>
   </si>
   <si>
     <t xml:space="preserve">0.92625492811203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930128753185272</t>
+    <t xml:space="preserve">0.930128812789917</t>
   </si>
   <si>
     <t xml:space="preserve">0.913342595100403</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">0.921950876712799</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923242032527924</t>
+    <t xml:space="preserve">0.923242092132568</t>
   </si>
   <si>
     <t xml:space="preserve">0.912051260471344</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">0.888808846473694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852567791938782</t>
+    <t xml:space="preserve">0.852567851543427</t>
   </si>
   <si>
     <t xml:space="preserve">0.86298394203186</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">0.85377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860659718513489</t>
+    <t xml:space="preserve">0.860659658908844</t>
   </si>
   <si>
     <t xml:space="preserve">0.879339694976807</t>
@@ -4073,10 +4073,10 @@
     <t xml:space="preserve">0.820200502872467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825882017612457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863844692707062</t>
+    <t xml:space="preserve">0.825881958007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863844633102417</t>
   </si>
   <si>
     <t xml:space="preserve">0.883643805980682</t>
@@ -4097,7 +4097,7 @@
     <t xml:space="preserve">0.948206186294556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982209086418152</t>
+    <t xml:space="preserve">0.982209146022797</t>
   </si>
   <si>
     <t xml:space="preserve">0.971018373966217</t>
@@ -4106,13 +4106,13 @@
     <t xml:space="preserve">0.965853273868561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966714143753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966283679008484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955092966556549</t>
+    <t xml:space="preserve">0.966714203357697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966283619403839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955092906951904</t>
   </si>
   <si>
     <t xml:space="preserve">0.972309470176697</t>
@@ -4121,13 +4121,13 @@
     <t xml:space="preserve">0.993830323219299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0045907497406</t>
+    <t xml:space="preserve">1.00459086894989</t>
   </si>
   <si>
     <t xml:space="preserve">1.01061654090881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11176431179047</t>
+    <t xml:space="preserve">1.11176419258118</t>
   </si>
   <si>
     <t xml:space="preserve">1.1160683631897</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">1.10616886615753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.126828789711</t>
+    <t xml:space="preserve">1.12682890892029</t>
   </si>
   <si>
     <t xml:space="preserve">1.1220942735672</t>
@@ -4148,16 +4148,16 @@
     <t xml:space="preserve">1.11822056770325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09669971466064</t>
+    <t xml:space="preserve">1.09669959545135</t>
   </si>
   <si>
     <t xml:space="preserve">1.11391639709473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13974118232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11865091323853</t>
+    <t xml:space="preserve">1.13974130153656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11865103244781</t>
   </si>
   <si>
     <t xml:space="preserve">1.09928214550018</t>
@@ -4169,7 +4169,7 @@
     <t xml:space="preserve">1.12898087501526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13586759567261</t>
+    <t xml:space="preserve">1.13586747646332</t>
   </si>
   <si>
     <t xml:space="preserve">1.13027215003967</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">1.11951184272766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12166380882263</t>
+    <t xml:space="preserve">1.12166392803192</t>
   </si>
   <si>
     <t xml:space="preserve">1.12984180450439</t>
@@ -4193,10 +4193,10 @@
     <t xml:space="preserve">1.14490628242493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11692929267883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09282600879669</t>
+    <t xml:space="preserve">1.11692917346954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0928258895874</t>
   </si>
   <si>
     <t xml:space="preserve">1.07603967189789</t>
@@ -4208,19 +4208,19 @@
     <t xml:space="preserve">1.06958341598511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07173562049866</t>
+    <t xml:space="preserve">1.07173550128937</t>
   </si>
   <si>
     <t xml:space="preserve">1.09971272945404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12467682361603</t>
+    <t xml:space="preserve">1.12467670440674</t>
   </si>
   <si>
     <t xml:space="preserve">1.12553763389587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13888037204742</t>
+    <t xml:space="preserve">1.13888049125671</t>
   </si>
   <si>
     <t xml:space="preserve">1.14705836772919</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">1.17245292663574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15093207359314</t>
+    <t xml:space="preserve">1.15093219280243</t>
   </si>
   <si>
     <t xml:space="preserve">1.18192207813263</t>
@@ -4259,10 +4259,10 @@
     <t xml:space="preserve">1.20387327671051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20430386066437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21119022369385</t>
+    <t xml:space="preserve">1.20430374145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21119034290314</t>
   </si>
   <si>
     <t xml:space="preserve">1.19483458995819</t>
@@ -4271,7 +4271,7 @@
     <t xml:space="preserve">1.18665671348572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20989918708801</t>
+    <t xml:space="preserve">1.20989906787872</t>
   </si>
   <si>
     <t xml:space="preserve">1.18794786930084</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">1.17632663249969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17675697803497</t>
+    <t xml:space="preserve">1.17675709724426</t>
   </si>
   <si>
     <t xml:space="preserve">1.19139122962952</t>
@@ -4301,19 +4301,19 @@
     <t xml:space="preserve">1.19225203990936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17976987361908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18579590320587</t>
+    <t xml:space="preserve">1.17976999282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18579578399658</t>
   </si>
   <si>
     <t xml:space="preserve">1.18966948986053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20215165615082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20129084587097</t>
+    <t xml:space="preserve">1.20215153694153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20129072666168</t>
   </si>
   <si>
     <t xml:space="preserve">1.16944003105164</t>
@@ -4346,10 +4346,10 @@
     <t xml:space="preserve">1.18321335315704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25078856945038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26240992546082</t>
+    <t xml:space="preserve">1.25078845024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26240980625153</t>
   </si>
   <si>
     <t xml:space="preserve">1.23658490180969</t>
@@ -4361,13 +4361,13 @@
     <t xml:space="preserve">1.23959791660309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23787605762482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21678566932678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22496354579926</t>
+    <t xml:space="preserve">1.23787617683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21678578853607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22496366500854</t>
   </si>
   <si>
     <t xml:space="preserve">1.25121903419495</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">1.26714444160461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29426074028015</t>
+    <t xml:space="preserve">1.29426062107086</t>
   </si>
   <si>
     <t xml:space="preserve">1.32869386672974</t>
@@ -4415,13 +4415,13 @@
     <t xml:space="preserve">1.35968375205994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3523668050766</t>
+    <t xml:space="preserve">1.35236668586731</t>
   </si>
   <si>
     <t xml:space="preserve">1.36614012718201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37733089923859</t>
+    <t xml:space="preserve">1.3773307800293</t>
   </si>
   <si>
     <t xml:space="preserve">1.34332811832428</t>
@@ -4430,13 +4430,13 @@
     <t xml:space="preserve">1.36786162853241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36829221248627</t>
+    <t xml:space="preserve">1.36829209327698</t>
   </si>
   <si>
     <t xml:space="preserve">1.3880912065506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40057337284088</t>
+    <t xml:space="preserve">1.40057325363159</t>
   </si>
   <si>
     <t xml:space="preserve">1.39885175228119</t>
@@ -4457,13 +4457,13 @@
     <t xml:space="preserve">1.44877994060516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43758916854858</t>
+    <t xml:space="preserve">1.43758904933929</t>
   </si>
   <si>
     <t xml:space="preserve">1.37905263900757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41047286987305</t>
+    <t xml:space="preserve">1.41047298908234</t>
   </si>
   <si>
     <t xml:space="preserve">1.42495942115784</t>
@@ -5928,6 +5928,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.25300002098083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27500009536743</t>
   </si>
 </sst>
 </file>
@@ -70928,7 +70931,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6520486111</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>6152295</v>
@@ -70949,6 +70952,32 @@
         <v>1971</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6496064815</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>11332647</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>2.29299998283386</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>2.24799990653992</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>2.25500011444092</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>2.27500009536743</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1972</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -44,91 +44,91 @@
     <t xml:space="preserve">A2A.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.7743039727211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769300401210785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77743124961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772427558898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775554835796356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73615175485611</t>
+    <t xml:space="preserve">0.774304032325745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769300282001495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777431190013885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772427499294281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775554776191711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73615163564682</t>
   </si>
   <si>
     <t xml:space="preserve">0.728020906448364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.708631992340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701126515865326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.678610503673553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.686115920543671</t>
+    <t xml:space="preserve">0.708631932735443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701126635074615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678610563278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.686115860939026</t>
   </si>
   <si>
     <t xml:space="preserve">0.662974298000336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669854283332825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.673606991767883</t>
+    <t xml:space="preserve">0.66985422372818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.673606932163239</t>
   </si>
   <si>
     <t xml:space="preserve">0.661723434925079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689868569374084</t>
+    <t xml:space="preserve">0.68986850976944</t>
   </si>
   <si>
     <t xml:space="preserve">0.667352497577667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688617587089539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689243137836456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.676108658313751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.671105086803436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.666726887226105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643585562705994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612312972545624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597927689552307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605745911598206</t>
+    <t xml:space="preserve">0.688617646694183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689243018627167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.676108717918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.671105027198792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.666727006435394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643585443496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612313032150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597927749156952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605745851993561</t>
   </si>
   <si>
     <t xml:space="preserve">0.610749423503876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614189326763153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627323865890503</t>
+    <t xml:space="preserve">0.614189386367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627323925495148</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942094802856</t>
@@ -137,40 +137,40 @@
     <t xml:space="preserve">0.624822080135345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646712720394135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.636079967021942</t>
+    <t xml:space="preserve">0.64671266078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.636080086231232</t>
   </si>
   <si>
     <t xml:space="preserve">0.656719744205475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645461738109589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641083598136902</t>
+    <t xml:space="preserve">0.645461678504944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641083717346191</t>
   </si>
   <si>
     <t xml:space="preserve">0.647963523864746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657345354557037</t>
+    <t xml:space="preserve">0.657345294952393</t>
   </si>
   <si>
     <t xml:space="preserve">0.661098003387451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672981441020966</t>
+    <t xml:space="preserve">0.67298150062561</t>
   </si>
   <si>
     <t xml:space="preserve">0.666101574897766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66485059261322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658596158027649</t>
+    <t xml:space="preserve">0.664850652217865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658596217632294</t>
   </si>
   <si>
     <t xml:space="preserve">0.651716291904449</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">0.654843509197235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669228792190552</t>
+    <t xml:space="preserve">0.669228911399841</t>
   </si>
   <si>
     <t xml:space="preserve">0.71301007270813</t>
@@ -188,28 +188,28 @@
     <t xml:space="preserve">0.69299578666687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.691119372844696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.694246649742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69799929857254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696123063564301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7030029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692370355129242</t>
+    <t xml:space="preserve">0.691119492053986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.694246590137482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69799941778183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696123003959656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.70300281047821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692370295524597</t>
   </si>
   <si>
     <t xml:space="preserve">0.699250280857086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714260995388031</t>
+    <t xml:space="preserve">0.714260935783386</t>
   </si>
   <si>
     <t xml:space="preserve">0.714886426925659</t>
@@ -218,40 +218,40 @@
     <t xml:space="preserve">0.702377438545227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.705504655838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735526204109192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.740529775619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74428254365921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748660683631897</t>
+    <t xml:space="preserve">0.705504715442657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735526084899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.740529716014862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.744282484054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748660624027252</t>
   </si>
   <si>
     <t xml:space="preserve">0.738027930259705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.750537097454071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754289627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768049597740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757416903972626</t>
+    <t xml:space="preserve">0.750536918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754289567470551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768049538135529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757416784763336</t>
   </si>
   <si>
     <t xml:space="preserve">0.766798436641693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.752413272857666</t>
+    <t xml:space="preserve">0.752413094043732</t>
   </si>
   <si>
     <t xml:space="preserve">0.781183838844299</t>
@@ -263,19 +263,19 @@
     <t xml:space="preserve">0.786187410354614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77930760383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768674850463867</t>
+    <t xml:space="preserve">0.77930748462677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768674969673157</t>
   </si>
   <si>
     <t xml:space="preserve">0.755540430545807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.760544121265411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.764296770095825</t>
+    <t xml:space="preserve">0.760544061660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76429682970047</t>
   </si>
   <si>
     <t xml:space="preserve">0.770551264286041</t>
@@ -284,19 +284,19 @@
     <t xml:space="preserve">0.75929319858551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769925713539124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.761169612407684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767424046993256</t>
+    <t xml:space="preserve">0.769925832748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76116955280304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767423987388611</t>
   </si>
   <si>
     <t xml:space="preserve">0.747409701347351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.751787841320038</t>
+    <t xml:space="preserve">0.751787900924683</t>
   </si>
   <si>
     <t xml:space="preserve">0.754915058612823</t>
@@ -305,82 +305,82 @@
     <t xml:space="preserve">0.781809329986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801198244094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804950773715973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799321830272675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78556215763092</t>
+    <t xml:space="preserve">0.801198124885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804950952529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79932177066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785562098026276</t>
   </si>
   <si>
     <t xml:space="preserve">0.796820163726807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791816473007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801823616027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733649849891663</t>
+    <t xml:space="preserve">0.791816532611847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801823556423187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733649790287018</t>
   </si>
   <si>
     <t xml:space="preserve">0.725519061088562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766306459903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759828805923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750760138034821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778614044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703473210334778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69246119260788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70541650056839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.730031609535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763067662715912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762419939041138</t>
+    <t xml:space="preserve">0.766306400299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759828746318817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750760078430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778614103794098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703473269939423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692461252212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705416560173035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.730031549930573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763067543506622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762419879436493</t>
   </si>
   <si>
     <t xml:space="preserve">0.769545257091522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.757885456085205</t>
+    <t xml:space="preserve">0.75788539648056</t>
   </si>
   <si>
     <t xml:space="preserve">0.742986857891083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.742339193820953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.758533358573914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777318596839905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77407968044281</t>
+    <t xml:space="preserve">0.742339074611664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758533298969269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777318477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774079620838165</t>
   </si>
   <si>
     <t xml:space="preserve">0.776022911071777</t>
@@ -392,49 +392,49 @@
     <t xml:space="preserve">0.779909551143646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.790273785591125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789626002311707</t>
+    <t xml:space="preserve">0.79027384519577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789625942707062</t>
   </si>
   <si>
     <t xml:space="preserve">0.79416024684906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805172443389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807763338088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.822661936283112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817479968070984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820718765258789</t>
+    <t xml:space="preserve">0.805172383785248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807763457298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.822662055492401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81747978925705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820718705654144</t>
   </si>
   <si>
     <t xml:space="preserve">0.822014272212982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809706807136536</t>
+    <t xml:space="preserve">0.809706747531891</t>
   </si>
   <si>
     <t xml:space="preserve">0.814241051673889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.816184520721436</t>
+    <t xml:space="preserve">0.816184401512146</t>
   </si>
   <si>
     <t xml:space="preserve">0.804524600505829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801285803318024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812945604324341</t>
+    <t xml:space="preserve">0.801285743713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812945544719696</t>
   </si>
   <si>
     <t xml:space="preserve">0.801933646202087</t>
@@ -446,46 +446,46 @@
     <t xml:space="preserve">0.788330495357513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77148848772049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783148348331451</t>
+    <t xml:space="preserve">0.771488606929779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783148407936096</t>
   </si>
   <si>
     <t xml:space="preserve">0.782500505447388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781852781772614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770192980766296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785091638565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795456051826477</t>
+    <t xml:space="preserve">0.781852841377258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770193040370941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785091698169708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795455992221832</t>
   </si>
   <si>
     <t xml:space="preserve">0.811002254486084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.794808149337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796103596687317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798694789409637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802581369876862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790921628475189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796751439571381</t>
+    <t xml:space="preserve">0.794808089733124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796103715896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798694670200348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802581250667572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7909215092659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796751379966736</t>
   </si>
   <si>
     <t xml:space="preserve">0.799342513084412</t>
@@ -497,34 +497,34 @@
     <t xml:space="preserve">0.780557334423065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784443974494934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785739362239838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827196359634399</t>
+    <t xml:space="preserve">0.784443795681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785739541053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827196419239044</t>
   </si>
   <si>
     <t xml:space="preserve">0.813593447208405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800637900829315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797399163246155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803876996040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807115733623505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7611243724823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770840883255005</t>
+    <t xml:space="preserve">0.80063807964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7973992228508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803876936435699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80711567401886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761124312877655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77084082365036</t>
   </si>
   <si>
     <t xml:space="preserve">0.73132711648941</t>
@@ -533,25 +533,25 @@
     <t xml:space="preserve">0.735861480236053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720315158367157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72161066532135</t>
+    <t xml:space="preserve">0.720315039157867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721610605716705</t>
   </si>
   <si>
     <t xml:space="preserve">0.719019532203674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696347773075104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696995556354523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.709950864315033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713837504386902</t>
+    <t xml:space="preserve">0.696347832679749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696995615959167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.709950923919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713837385177612</t>
   </si>
   <si>
     <t xml:space="preserve">0.711894154548645</t>
@@ -560,52 +560,52 @@
     <t xml:space="preserve">0.707359850406647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.728736042976379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715780735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722258508205414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765010952949524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754646718502045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755294442176819</t>
+    <t xml:space="preserve">0.728735983371735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715780794620514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722258329391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765010833740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7546466588974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755294382572174</t>
   </si>
   <si>
     <t xml:space="preserve">0.787682712078094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776670813560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772136390209198</t>
+    <t xml:space="preserve">0.776670634746552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772136330604553</t>
   </si>
   <si>
     <t xml:space="preserve">0.787034928798676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.816832184791565</t>
+    <t xml:space="preserve">0.81683224439621</t>
   </si>
   <si>
     <t xml:space="preserve">0.819423198699951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799990236759186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824605286121368</t>
+    <t xml:space="preserve">0.799990177154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824605345726013</t>
   </si>
   <si>
     <t xml:space="preserve">0.838856279850006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.831730902194977</t>
+    <t xml:space="preserve">0.831730723381042</t>
   </si>
   <si>
     <t xml:space="preserve">0.832378447055817</t>
@@ -614,31 +614,31 @@
     <t xml:space="preserve">0.840151607990265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.848572611808777</t>
+    <t xml:space="preserve">0.848572552204132</t>
   </si>
   <si>
     <t xml:space="preserve">0.841447293758392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.844686031341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830435216426849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798047006130219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815536618232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82007098197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806467950344086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811650097370148</t>
+    <t xml:space="preserve">0.844685912132263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830435156822205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798046946525574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815536558628082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820071041584015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806467890739441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811649978160858</t>
   </si>
   <si>
     <t xml:space="preserve">0.83626514673233</t>
@@ -647,25 +647,25 @@
     <t xml:space="preserve">0.844038307666779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837560594081879</t>
+    <t xml:space="preserve">0.837560713291168</t>
   </si>
   <si>
     <t xml:space="preserve">0.836912870407104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.821366488933563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828492105007172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825900793075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829139530658722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846629440784454</t>
+    <t xml:space="preserve">0.821366608142853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828492045402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825900912284851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829139649868011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846629321575165</t>
   </si>
   <si>
     <t xml:space="preserve">0.849220275878906</t>
@@ -674,82 +674,82 @@
     <t xml:space="preserve">0.864766836166382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867357850074768</t>
+    <t xml:space="preserve">0.867357730865479</t>
   </si>
   <si>
     <t xml:space="preserve">0.868005573749542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.870596766471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857641398906708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.865414500236511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866710186004639</t>
+    <t xml:space="preserve">0.870596647262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857641339302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.865414440631866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866710126399994</t>
   </si>
   <si>
     <t xml:space="preserve">0.853107035160065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855698049068451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858289062976837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860232472419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872540056705475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874483287334442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887438595294952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893916308879852</t>
+    <t xml:space="preserve">0.855697929859161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858289122581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860232353210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872539937496185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874483168125153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887438535690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893916189670563</t>
   </si>
   <si>
     <t xml:space="preserve">0.892620742321014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912701547145844</t>
+    <t xml:space="preserve">0.912701427936554</t>
   </si>
   <si>
     <t xml:space="preserve">0.909462571144104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9081671833992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919826805591583</t>
+    <t xml:space="preserve">0.908167123794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919826865196228</t>
   </si>
   <si>
     <t xml:space="preserve">0.91853141784668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.875778794288635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877722144126892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89197301864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884847521781921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895211696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884199857711792</t>
+    <t xml:space="preserve">0.87577885389328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877722024917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.891972839832306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884847462177277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895211637020111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884199738502502</t>
   </si>
   <si>
     <t xml:space="preserve">0.876426517963409</t>
@@ -758,100 +758,100 @@
     <t xml:space="preserve">0.862175643444061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85634583234787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88225644826889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89909839630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890677452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926952242851257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915292382240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917235732078552</t>
+    <t xml:space="preserve">0.856345891952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882256329059601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89909827709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890677273273468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926952302455902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915292501449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917235851287842</t>
   </si>
   <si>
     <t xml:space="preserve">0.966466069221497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958044946193695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965170502662659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961283802986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963227152824402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941851019859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941203057765961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958692848682404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982277989387512</t>
+    <t xml:space="preserve">0.95804500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965170562267303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96128386259079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963227272033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941850900650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941203117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958692908287048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982278108596802</t>
   </si>
   <si>
     <t xml:space="preserve">0.988308548927307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997019052505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00036931037903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992998778820038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96820729970932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981608271598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986298263072968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988978624343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989648520946503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97490793466568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999699294567108</t>
+    <t xml:space="preserve">0.997019290924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00036942958832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992998898029327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96820741891861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981608331203461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986298501491547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988978505134583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989648759365082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97490781545639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999699175357819</t>
   </si>
   <si>
     <t xml:space="preserve">1.00505948066711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998359203338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997689008712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00170934200287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0070698261261</t>
+    <t xml:space="preserve">0.998359084129333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997689068317413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00170946121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00706970691681</t>
   </si>
   <si>
     <t xml:space="preserve">1.02047038078308</t>
@@ -860,25 +860,25 @@
     <t xml:space="preserve">1.02985095977783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01779019832611</t>
+    <t xml:space="preserve">1.01779043674469</t>
   </si>
   <si>
     <t xml:space="preserve">0.995009064674377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999029099941254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976917803287506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.974237859249115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97021758556366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965527236461639</t>
+    <t xml:space="preserve">0.999029219150543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976917862892151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.974237680435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970217525959015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965527355670929</t>
   </si>
   <si>
     <t xml:space="preserve">0.960837006568909</t>
@@ -890,22 +890,22 @@
     <t xml:space="preserve">0.964187145233154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980268061161041</t>
+    <t xml:space="preserve">0.980268239974976</t>
   </si>
   <si>
     <t xml:space="preserve">0.978927969932556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984958410263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97289764881134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960166931152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958826720714569</t>
+    <t xml:space="preserve">0.984958350658417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972897708415985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960166871547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958826839923859</t>
   </si>
   <si>
     <t xml:space="preserve">0.951456308364868</t>
@@ -914,34 +914,34 @@
     <t xml:space="preserve">0.955476701259613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949446260929108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9635169506073</t>
+    <t xml:space="preserve">0.949446320533752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963517010211945</t>
   </si>
   <si>
     <t xml:space="preserve">0.950116336345673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953466534614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956816554069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958156883716583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952796399593353</t>
+    <t xml:space="preserve">0.953466475009918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956816732883453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958156764507294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952796459197998</t>
   </si>
   <si>
     <t xml:space="preserve">0.962176978588104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944755911827087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931355118751526</t>
+    <t xml:space="preserve">0.944756031036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93135529756546</t>
   </si>
   <si>
     <t xml:space="preserve">0.948106169700623</t>
@@ -953,88 +953,88 @@
     <t xml:space="preserve">0.957486748695374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939395725727081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946765959262848</t>
+    <t xml:space="preserve">0.939395666122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946766078472137</t>
   </si>
   <si>
     <t xml:space="preserve">0.934705436229706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.928675055503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924654841423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932695269584656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945425987243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959496796131134</t>
+    <t xml:space="preserve">0.928674936294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92465478181839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932695209980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945426166057587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959496974945068</t>
   </si>
   <si>
     <t xml:space="preserve">0.973567605018616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978257834911346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993668854236603</t>
+    <t xml:space="preserve">0.978258073329926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993669033050537</t>
   </si>
   <si>
     <t xml:space="preserve">0.984288394451141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983618319034576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994338870048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977587997913361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980938136577606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972227513790131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96619713306427</t>
+    <t xml:space="preserve">0.983618378639221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994338929653168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977587938308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980938196182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972227692604065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966197490692139</t>
   </si>
   <si>
     <t xml:space="preserve">0.969547510147095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968877375125885</t>
+    <t xml:space="preserve">0.968877553939819</t>
   </si>
   <si>
     <t xml:space="preserve">0.971557557582855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995678842067719</t>
+    <t xml:space="preserve">0.995678961277008</t>
   </si>
   <si>
     <t xml:space="preserve">0.992328703403473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966867327690125</t>
+    <t xml:space="preserve">0.96686726808548</t>
   </si>
   <si>
     <t xml:space="preserve">1.02114057540894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01041996479034</t>
+    <t xml:space="preserve">1.01041984558105</t>
   </si>
   <si>
     <t xml:space="preserve">1.01444017887115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0218106508255</t>
+    <t xml:space="preserve">1.02181041240692</t>
   </si>
   <si>
     <t xml:space="preserve">1.02382063865662</t>
@@ -1043,22 +1043,22 @@
     <t xml:space="preserve">1.0285108089447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03320121765137</t>
+    <t xml:space="preserve">1.03320109844208</t>
   </si>
   <si>
     <t xml:space="preserve">1.03923153877258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02650082111359</t>
+    <t xml:space="preserve">1.0265007019043</t>
   </si>
   <si>
     <t xml:space="preserve">1.05531251430511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05866265296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04459178447723</t>
+    <t xml:space="preserve">1.05866277217865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04459166526794</t>
   </si>
   <si>
     <t xml:space="preserve">1.05330240726471</t>
@@ -1067,25 +1067,25 @@
     <t xml:space="preserve">1.06804323196411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07273364067078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08613431453705</t>
+    <t xml:space="preserve">1.07273352146149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08613443374634</t>
   </si>
   <si>
     <t xml:space="preserve">1.0955148935318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08345401287079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08211410045624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05397236347198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0600026845932</t>
+    <t xml:space="preserve">1.08345425128937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08211421966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0539722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06000280380249</t>
   </si>
   <si>
     <t xml:space="preserve">1.04392170906067</t>
@@ -1094,46 +1094,46 @@
     <t xml:space="preserve">1.04861223697662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04660189151764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03990149497986</t>
+    <t xml:space="preserve">1.04660201072693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03990161418915</t>
   </si>
   <si>
     <t xml:space="preserve">1.04258179664612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01980042457581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01578009128571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05196225643158</t>
+    <t xml:space="preserve">1.01980018615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.015780210495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05196237564087</t>
   </si>
   <si>
     <t xml:space="preserve">1.06737327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.066033244133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02449071407318</t>
+    <t xml:space="preserve">1.06603300571442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02449083328247</t>
   </si>
   <si>
     <t xml:space="preserve">1.01846027374268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02784085273743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05665254592896</t>
+    <t xml:space="preserve">1.02784097194672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05665266513824</t>
   </si>
   <si>
     <t xml:space="preserve">1.06134283542633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07742369174957</t>
+    <t xml:space="preserve">1.07742381095886</t>
   </si>
   <si>
     <t xml:space="preserve">1.07943391799927</t>
@@ -1145,13 +1145,13 @@
     <t xml:space="preserve">1.05933272838593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0385617017746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02683591842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03588151931763</t>
+    <t xml:space="preserve">1.03856146335602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0268360376358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03588140010834</t>
   </si>
   <si>
     <t xml:space="preserve">1.04191172122955</t>
@@ -1163,64 +1163,64 @@
     <t xml:space="preserve">0.971222579479218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995343923568726</t>
+    <t xml:space="preserve">0.99534398317337</t>
   </si>
   <si>
     <t xml:space="preserve">0.944421052932739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95313161611557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941405832767487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959831774234772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94643098115921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957821726799011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950451195240021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936380326747894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967202305793762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991323709487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975577712059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993333756923676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00003409385681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00137448310852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991658806800842</t>
+    <t xml:space="preserve">0.953131496906281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941405713558197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959831953048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9464311003685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957821786403656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950451374053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936380445957184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967202425003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991323828697205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975577831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993333876132965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00003433227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00137436389923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991658866405487</t>
   </si>
   <si>
     <t xml:space="preserve">1.00673460960388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99936431646347</t>
+    <t xml:space="preserve">0.999364256858826</t>
   </si>
   <si>
     <t xml:space="preserve">1.04023659229279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04157674312592</t>
+    <t xml:space="preserve">1.04157662391663</t>
   </si>
   <si>
     <t xml:space="preserve">1.04224681854248</t>
@@ -1235,22 +1235,22 @@
     <t xml:space="preserve">1.06268298625946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0720636844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05832767486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06335294246674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07407355308533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08043885231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08546435832977</t>
+    <t xml:space="preserve">1.07206344604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05832779407501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06335306167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07407367229462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08043897151947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08546423912048</t>
   </si>
   <si>
     <t xml:space="preserve">1.09048962593079</t>
@@ -1259,16 +1259,16 @@
     <t xml:space="preserve">1.09484493732452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09819507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09853005409241</t>
+    <t xml:space="preserve">1.09819519519806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0985301733017</t>
   </si>
   <si>
     <t xml:space="preserve">1.12198150157928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11762607097626</t>
+    <t xml:space="preserve">1.11762619018555</t>
   </si>
   <si>
     <t xml:space="preserve">1.11729121208191</t>
@@ -1280,19 +1280,19 @@
     <t xml:space="preserve">1.10757565498352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12265157699585</t>
+    <t xml:space="preserve">1.12265145778656</t>
   </si>
   <si>
     <t xml:space="preserve">1.13002192974091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10992074012756</t>
+    <t xml:space="preserve">1.10992097854614</t>
   </si>
   <si>
     <t xml:space="preserve">1.11829626560211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05732274055481</t>
+    <t xml:space="preserve">1.05732262134552</t>
   </si>
   <si>
     <t xml:space="preserve">1.03387129306793</t>
@@ -1301,19 +1301,19 @@
     <t xml:space="preserve">1.03895282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05287528038025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04208528995514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04730629920959</t>
+    <t xml:space="preserve">1.05287516117096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04208552837372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04730618000031</t>
   </si>
   <si>
     <t xml:space="preserve">1.02572667598724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00693166255951</t>
+    <t xml:space="preserve">1.00693142414093</t>
   </si>
   <si>
     <t xml:space="preserve">0.980827152729034</t>
@@ -1325,31 +1325,31 @@
     <t xml:space="preserve">1.01076018810272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00484335422516</t>
+    <t xml:space="preserve">1.00484323501587</t>
   </si>
   <si>
     <t xml:space="preserve">1.02920734882355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00936782360077</t>
+    <t xml:space="preserve">1.00936806201935</t>
   </si>
   <si>
     <t xml:space="preserve">1.00658345222473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999622344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968993127346039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0159809589386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0239862203598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0316436290741</t>
+    <t xml:space="preserve">0.999622404575348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968993186950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01598107814789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02398645877838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03164374828339</t>
   </si>
   <si>
     <t xml:space="preserve">1.02851116657257</t>
@@ -1364,25 +1364,25 @@
     <t xml:space="preserve">1.04661011695862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0236382484436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02537858486176</t>
+    <t xml:space="preserve">1.02363836765289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02537870407104</t>
   </si>
   <si>
     <t xml:space="preserve">1.00588750839233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01250040531158</t>
+    <t xml:space="preserve">1.01250052452087</t>
   </si>
   <si>
     <t xml:space="preserve">1.02120184898376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02642285823822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03373205661774</t>
+    <t xml:space="preserve">1.02642273902893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03373217582703</t>
   </si>
   <si>
     <t xml:space="preserve">1.01389288902283</t>
@@ -1394,97 +1394,97 @@
     <t xml:space="preserve">1.0511349439621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06122863292694</t>
+    <t xml:space="preserve">1.06122851371765</t>
   </si>
   <si>
     <t xml:space="preserve">1.07236647605896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06018435955048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0626208782196</t>
+    <t xml:space="preserve">1.06018424034119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06262063980103</t>
   </si>
   <si>
     <t xml:space="preserve">1.05600762367249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07375884056091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06714570522308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07863140106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09290182590485</t>
+    <t xml:space="preserve">1.07375860214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0671454668045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0786315202713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09290194511414</t>
   </si>
   <si>
     <t xml:space="preserve">1.09429407119751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10160338878632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08420038223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04835057258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06157660484314</t>
+    <t xml:space="preserve">1.10160326957703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08420050144196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04835033416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06157672405243</t>
   </si>
   <si>
     <t xml:space="preserve">1.07201826572418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07584714889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0713222026825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09394598007202</t>
+    <t xml:space="preserve">1.07584702968597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07132232189178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09394609928131</t>
   </si>
   <si>
     <t xml:space="preserve">1.08106791973114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09011733531952</t>
+    <t xml:space="preserve">1.09011745452881</t>
   </si>
   <si>
     <t xml:space="preserve">1.08246004581451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1029953956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12005031108856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12387895584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10473585128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10612797737122</t>
+    <t xml:space="preserve">1.10299551486969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12005043029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12387907505035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10473573207855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10612809658051</t>
   </si>
   <si>
     <t xml:space="preserve">1.11134886741638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10821652412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10960876941681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08837711811066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08802902698517</t>
+    <t xml:space="preserve">1.10821640491486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10960865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08837723731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08802890777588</t>
   </si>
   <si>
     <t xml:space="preserve">1.08942127227783</t>
@@ -1493,31 +1493,31 @@
     <t xml:space="preserve">1.07549893856049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06540524959564</t>
+    <t xml:space="preserve">1.06540536880493</t>
   </si>
   <si>
     <t xml:space="preserve">1.03338408470154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04243350028992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02154994010925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03094744682312</t>
+    <t xml:space="preserve">1.04243338108063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02155005931854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03094732761383</t>
   </si>
   <si>
     <t xml:space="preserve">1.04173731803894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05705177783966</t>
+    <t xml:space="preserve">1.05705189704895</t>
   </si>
   <si>
     <t xml:space="preserve">1.0789794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09220588207245</t>
+    <t xml:space="preserve">1.09220576286316</t>
   </si>
   <si>
     <t xml:space="preserve">1.09116148948669</t>
@@ -1529,10 +1529,10 @@
     <t xml:space="preserve">1.08141601085663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09847068786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09603428840637</t>
+    <t xml:space="preserve">1.0984708070755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09603440761566</t>
   </si>
   <si>
     <t xml:space="preserve">1.07619500160217</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">1.07445478439331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0587922334671</t>
+    <t xml:space="preserve">1.05879211425781</t>
   </si>
   <si>
     <t xml:space="preserve">1.07758724689484</t>
@@ -1550,16 +1550,16 @@
     <t xml:space="preserve">1.06923389434814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04069328308105</t>
+    <t xml:space="preserve">1.04069316387177</t>
   </si>
   <si>
     <t xml:space="preserve">1.03199172019958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04452168941498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04417359828949</t>
+    <t xml:space="preserve">1.04452192783356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04417371749878</t>
   </si>
   <si>
     <t xml:space="preserve">1.05183112621307</t>
@@ -1577,37 +1577,37 @@
     <t xml:space="preserve">1.00310289859772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991617023944855</t>
+    <t xml:space="preserve">0.9916170835495</t>
   </si>
   <si>
     <t xml:space="preserve">1.00832378864288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01424074172974</t>
+    <t xml:space="preserve">1.01424098014832</t>
   </si>
   <si>
     <t xml:space="preserve">1.01772129535675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01354455947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993705451488495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988136470317841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97734659910202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00553941726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98604816198349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989528596401215</t>
+    <t xml:space="preserve">1.01354467868805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993705332279205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988136351108551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977346837520599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00553929805756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986047983169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989528715610504</t>
   </si>
   <si>
     <t xml:space="preserve">0.992313206195831</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">0.98291540145874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991965055465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01319658756256</t>
+    <t xml:space="preserve">0.991964995861053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01319646835327</t>
   </si>
   <si>
     <t xml:space="preserve">1.00414717197418</t>
@@ -1631,55 +1631,55 @@
     <t xml:space="preserve">1.0156329870224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0351243019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03930103778839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05252718925476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0546156167984</t>
+    <t xml:space="preserve">1.03512418270111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0393009185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05252707004547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05461537837982</t>
   </si>
   <si>
     <t xml:space="preserve">1.03721261024475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02711880207062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03999710083008</t>
+    <t xml:space="preserve">1.02711892127991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03999698162079</t>
   </si>
   <si>
     <t xml:space="preserve">1.06610143184662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06088066101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04034507274628</t>
+    <t xml:space="preserve">1.06088054180145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04034519195557</t>
   </si>
   <si>
     <t xml:space="preserve">1.03233981132507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04278147220612</t>
+    <t xml:space="preserve">1.04278171062469</t>
   </si>
   <si>
     <t xml:space="preserve">1.04347765445709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07410681247711</t>
+    <t xml:space="preserve">1.07410669326782</t>
   </si>
   <si>
     <t xml:space="preserve">1.10090732574463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11761403083801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12701153755188</t>
+    <t xml:space="preserve">1.11761391162872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12701141834259</t>
   </si>
   <si>
     <t xml:space="preserve">1.1137855052948</t>
@@ -1688,58 +1688,58 @@
     <t xml:space="preserve">1.1064760684967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12318289279938</t>
+    <t xml:space="preserve">1.12318301200867</t>
   </si>
   <si>
     <t xml:space="preserve">1.13118827342987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1144814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08872520923615</t>
+    <t xml:space="preserve">1.11448132991791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08872509002686</t>
   </si>
   <si>
     <t xml:space="preserve">1.094642162323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11622166633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1183100938797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13501691818237</t>
+    <t xml:space="preserve">1.11622178554535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11831021308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13501679897308</t>
   </si>
   <si>
     <t xml:space="preserve">1.13675713539124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13814926147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14302229881287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10403954982758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10891258716583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09951484203339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1019514799118</t>
+    <t xml:space="preserve">1.13814949989319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14302217960358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10403978824615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10891270637512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09951496124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10195124149323</t>
   </si>
   <si>
     <t xml:space="preserve">1.09916687011719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09499025344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10577988624573</t>
+    <t xml:space="preserve">1.0949901342392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10578012466431</t>
   </si>
   <si>
     <t xml:space="preserve">1.09185767173767</t>
@@ -1748,22 +1748,22 @@
     <t xml:space="preserve">1.07793521881104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08071982860565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0866367816925</t>
+    <t xml:space="preserve">1.08071970939636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08663690090179</t>
   </si>
   <si>
     <t xml:space="preserve">1.06227278709412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08280825614929</t>
+    <t xml:space="preserve">1.08280801773071</t>
   </si>
   <si>
     <t xml:space="preserve">1.09742665290833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10021114349365</t>
+    <t xml:space="preserve">1.10021090507507</t>
   </si>
   <si>
     <t xml:space="preserve">1.09777462482452</t>
@@ -1775,7 +1775,7 @@
     <t xml:space="preserve">1.11100089550018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10543203353882</t>
+    <t xml:space="preserve">1.10543191432953</t>
   </si>
   <si>
     <t xml:space="preserve">1.08594059944153</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">1.12074661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10752034187317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11030471324921</t>
+    <t xml:space="preserve">1.10752022266388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1103048324585</t>
   </si>
   <si>
     <t xml:space="preserve">1.12179064750671</t>
@@ -1808,49 +1808,49 @@
     <t xml:space="preserve">1.13571310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13536489009857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13084018230438</t>
+    <t xml:space="preserve">1.13536500930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13084006309509</t>
   </si>
   <si>
     <t xml:space="preserve">1.13223242759705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14754688739777</t>
+    <t xml:space="preserve">1.14754700660706</t>
   </si>
   <si>
     <t xml:space="preserve">1.063316822052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05391955375671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04626226425171</t>
+    <t xml:space="preserve">1.05391943454742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04626214504242</t>
   </si>
   <si>
     <t xml:space="preserve">1.05426740646362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04869842529297</t>
+    <t xml:space="preserve">1.04869854450226</t>
   </si>
   <si>
     <t xml:space="preserve">1.02433443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01946151256561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01632905006409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0037989616394</t>
+    <t xml:space="preserve">1.0194616317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01632916927338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00379908084869</t>
   </si>
   <si>
     <t xml:space="preserve">0.997882068157196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00727963447571</t>
+    <t xml:space="preserve">1.007279753685</t>
   </si>
   <si>
     <t xml:space="preserve">1.02015781402588</t>
@@ -1868,55 +1868,55 @@
     <t xml:space="preserve">1.09647643566132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06622135639191</t>
+    <t xml:space="preserve">1.0662214756012</t>
   </si>
   <si>
     <t xml:space="preserve">1.08116662502289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07205355167389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06038892269135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05127608776093</t>
+    <t xml:space="preserve">1.07205379009247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06038916110992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05127596855164</t>
   </si>
   <si>
     <t xml:space="preserve">1.06403422355652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07168924808502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.080437541008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09793472290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0986635684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10449600219727</t>
+    <t xml:space="preserve">1.07168912887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08043766021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0979346036911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09866344928741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10449588298798</t>
   </si>
   <si>
     <t xml:space="preserve">1.10048615932465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10230875015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09574747085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09829926490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13219952583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12563824653625</t>
+    <t xml:space="preserve">1.1023086309433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09574735164642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09829914569855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13219940662384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12563812732697</t>
   </si>
   <si>
     <t xml:space="preserve">1.14021897315979</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">1.14750933647156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13584470748901</t>
+    <t xml:space="preserve">1.1358448266983</t>
   </si>
   <si>
     <t xml:space="preserve">1.11944139003754</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">1.11543154716492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10376703739166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11251544952393</t>
+    <t xml:space="preserve">1.10376691818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11251533031464</t>
   </si>
   <si>
     <t xml:space="preserve">1.11069285869598</t>
@@ -1946,31 +1946,31 @@
     <t xml:space="preserve">1.13511562347412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1500608921051</t>
+    <t xml:space="preserve">1.15006101131439</t>
   </si>
   <si>
     <t xml:space="preserve">1.15188360214233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.147873878479</t>
+    <t xml:space="preserve">1.14787375926971</t>
   </si>
   <si>
     <t xml:space="preserve">1.15261256694794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16427719593048</t>
+    <t xml:space="preserve">1.16427731513977</t>
   </si>
   <si>
     <t xml:space="preserve">1.17047417163849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17156755924225</t>
+    <t xml:space="preserve">1.17156767845154</t>
   </si>
   <si>
     <t xml:space="preserve">1.17229676246643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17849361896515</t>
+    <t xml:space="preserve">1.17849349975586</t>
   </si>
   <si>
     <t xml:space="preserve">1.17484831809998</t>
@@ -1979,40 +1979,40 @@
     <t xml:space="preserve">1.19161629676819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16318380832672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16609978675842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17995154857635</t>
+    <t xml:space="preserve">1.16318356990814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16609966754913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17995166778564</t>
   </si>
   <si>
     <t xml:space="preserve">1.18469047546387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1810450553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17120325565338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17375493049622</t>
+    <t xml:space="preserve">1.18104517459869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17120313644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17375481128693</t>
   </si>
   <si>
     <t xml:space="preserve">1.14969646930695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15407061576843</t>
+    <t xml:space="preserve">1.15407073497772</t>
   </si>
   <si>
     <t xml:space="preserve">1.17083847522736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16209030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1668289899826</t>
+    <t xml:space="preserve">1.16209006309509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16682887077332</t>
   </si>
   <si>
     <t xml:space="preserve">1.16755795478821</t>
@@ -2024,28 +2024,28 @@
     <t xml:space="preserve">1.13183498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12417995929718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12782526016235</t>
+    <t xml:space="preserve">1.12418007850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12782537937164</t>
   </si>
   <si>
     <t xml:space="preserve">1.14277052879333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16099655628204</t>
+    <t xml:space="preserve">1.16099667549133</t>
   </si>
   <si>
     <t xml:space="preserve">1.14459323883057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15297734737396</t>
+    <t xml:space="preserve">1.15297722816467</t>
   </si>
   <si>
     <t xml:space="preserve">1.13985443115234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13475120067596</t>
+    <t xml:space="preserve">1.13475108146667</t>
   </si>
   <si>
     <t xml:space="preserve">1.16391277313232</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">1.16938054561615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16573524475098</t>
+    <t xml:space="preserve">1.16573548316956</t>
   </si>
   <si>
     <t xml:space="preserve">1.16500627994537</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">1.18833553791046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20473909378052</t>
+    <t xml:space="preserve">1.20473897457123</t>
   </si>
   <si>
     <t xml:space="preserve">1.20036482810974</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">1.18870007991791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17958724498749</t>
+    <t xml:space="preserve">1.1795871257782</t>
   </si>
   <si>
     <t xml:space="preserve">1.16464173793793</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">1.18979370594025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22551667690277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21567475795746</t>
+    <t xml:space="preserve">1.22551679611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21567463874817</t>
   </si>
   <si>
     <t xml:space="preserve">1.22770380973816</t>
@@ -2105,25 +2105,25 @@
     <t xml:space="preserve">1.23207807540894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21421670913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21166491508484</t>
+    <t xml:space="preserve">1.21421647071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21166479587555</t>
   </si>
   <si>
     <t xml:space="preserve">1.23134899139404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2302553653717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21603906154633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21931970119476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23791038990021</t>
+    <t xml:space="preserve">1.23025560379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2160392999649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21931993961334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23791027069092</t>
   </si>
   <si>
     <t xml:space="preserve">1.23462963104248</t>
@@ -2132,10 +2132,10 @@
     <t xml:space="preserve">1.22806835174561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21640372276306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22187149524689</t>
+    <t xml:space="preserve">1.21640360355377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2218713760376</t>
   </si>
   <si>
     <t xml:space="preserve">1.22114229202271</t>
@@ -2144,22 +2144,22 @@
     <t xml:space="preserve">1.22405862808228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23062002658844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22843265533447</t>
+    <t xml:space="preserve">1.23061990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22843277454376</t>
   </si>
   <si>
     <t xml:space="preserve">1.23645222187042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22879731655121</t>
+    <t xml:space="preserve">1.2287974357605</t>
   </si>
   <si>
     <t xml:space="preserve">1.22624576091766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27363336086273</t>
+    <t xml:space="preserve">1.27363324165344</t>
   </si>
   <si>
     <t xml:space="preserve">1.27691400051117</t>
@@ -2177,19 +2177,19 @@
     <t xml:space="preserve">1.30826270580292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31591749191284</t>
+    <t xml:space="preserve">1.31591761112213</t>
   </si>
   <si>
     <t xml:space="preserve">1.29331743717194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31518864631653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31445944309235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30862712860107</t>
+    <t xml:space="preserve">1.31518876552582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31445956230164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30862724781036</t>
   </si>
   <si>
     <t xml:space="preserve">1.29732704162598</t>
@@ -2198,22 +2198,22 @@
     <t xml:space="preserve">1.27873647212982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28857862949371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28420448303223</t>
+    <t xml:space="preserve">1.288578748703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28420436382294</t>
   </si>
   <si>
     <t xml:space="preserve">1.27727842330933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27509152889252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26452052593231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24884605407715</t>
+    <t xml:space="preserve">1.27509129047394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26452016830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24884593486786</t>
   </si>
   <si>
     <t xml:space="preserve">1.24665880203247</t>
@@ -2222,16 +2222,16 @@
     <t xml:space="preserve">1.25249123573303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24520063400269</t>
+    <t xml:space="preserve">1.2452005147934</t>
   </si>
   <si>
     <t xml:space="preserve">1.24483621120453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19052278995514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19635498523712</t>
+    <t xml:space="preserve">1.19052267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19635510444641</t>
   </si>
   <si>
     <t xml:space="preserve">1.1985422372818</t>
@@ -2240,46 +2240,46 @@
     <t xml:space="preserve">1.19343888759613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18068051338196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20218729972839</t>
+    <t xml:space="preserve">1.18068063259125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20218741893768</t>
   </si>
   <si>
     <t xml:space="preserve">1.18906462192535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19270980358124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20656168460846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20729064941406</t>
+    <t xml:space="preserve">1.19270992279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20656156539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20729076862335</t>
   </si>
   <si>
     <t xml:space="preserve">1.22515213489532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24155557155609</t>
+    <t xml:space="preserve">1.2415554523468</t>
   </si>
   <si>
     <t xml:space="preserve">1.23353612422943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2189553976059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2127583026886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20838415622711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25504279136658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2506685256958</t>
+    <t xml:space="preserve">1.21895527839661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21275854110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2083842754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25504267215729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25066864490509</t>
   </si>
   <si>
     <t xml:space="preserve">1.25941705703735</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">1.25650084018707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26853001117706</t>
+    <t xml:space="preserve">1.26852989196777</t>
   </si>
   <si>
     <t xml:space="preserve">1.2998788356781</t>
@@ -2297,49 +2297,49 @@
     <t xml:space="preserve">1.30315935611725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29368197917938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2922238111496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30607569217682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35200524330139</t>
+    <t xml:space="preserve">1.29368185997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29222393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30607557296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3520051240921</t>
   </si>
   <si>
     <t xml:space="preserve">1.34544372558594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414363861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3140949010849</t>
+    <t xml:space="preserve">1.33414375782013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31409502029419</t>
   </si>
   <si>
     <t xml:space="preserve">1.3224790096283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32940483093262</t>
+    <t xml:space="preserve">1.32940495014191</t>
   </si>
   <si>
     <t xml:space="preserve">1.34580826759338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33159196376801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33013379573822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.349818110466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34398579597473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34143400192261</t>
+    <t xml:space="preserve">1.33159208297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33013391494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34981799125671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34398567676544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3414341211319</t>
   </si>
   <si>
     <t xml:space="preserve">1.34945344924927</t>
@@ -2351,25 +2351,25 @@
     <t xml:space="preserve">1.36986649036407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3822603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3603892326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34908890724182</t>
+    <t xml:space="preserve">1.38226044178009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36038911342621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34908902645111</t>
   </si>
   <si>
     <t xml:space="preserve">1.26524937152863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25613641738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13766741752625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15589332580566</t>
+    <t xml:space="preserve">1.25613629817963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13766729831696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15589320659637</t>
   </si>
   <si>
     <t xml:space="preserve">1.19708406925201</t>
@@ -2378,31 +2378,31 @@
     <t xml:space="preserve">1.11579608917236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996233463287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924787521362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905467927455902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733049988746643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772782623767853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750546932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775334298610687</t>
+    <t xml:space="preserve">0.996233522891998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924787640571594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905467987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733049929141998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772782683372498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750546991825104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775334358215332</t>
   </si>
   <si>
     <t xml:space="preserve">0.751276016235352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.754556655883789</t>
+    <t xml:space="preserve">0.754556715488434</t>
   </si>
   <si>
     <t xml:space="preserve">0.741433918476105</t>
@@ -2411,70 +2411,70 @@
     <t xml:space="preserve">0.729040205478668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786269962787628</t>
+    <t xml:space="preserve">0.786270022392273</t>
   </si>
   <si>
     <t xml:space="preserve">0.797205567359924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.793195724487305</t>
+    <t xml:space="preserve">0.793195843696594</t>
   </si>
   <si>
     <t xml:space="preserve">0.778250455856323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824544429779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826002657413483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816160619258881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841677010059357</t>
+    <t xml:space="preserve">0.824544548988342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826002538204193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816160500049591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841676950454712</t>
   </si>
   <si>
     <t xml:space="preserve">0.836209118366241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869015991687775</t>
+    <t xml:space="preserve">0.869016051292419</t>
   </si>
   <si>
     <t xml:space="preserve">0.869745016098022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855164170265198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876670837402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889429032802582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885783910751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.897448599338531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910935819149017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911664724349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.883961141109467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888335525989532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879587113857269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890158116817474</t>
+    <t xml:space="preserve">0.855164110660553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876670956611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889429092407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885783970355988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.897448539733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910935878753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91166490316391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883961260318756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888335406780243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879587054252625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890158176422119</t>
   </si>
   <si>
     <t xml:space="preserve">0.906926035881042</t>
@@ -2483,43 +2483,43 @@
     <t xml:space="preserve">0.901458323001862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89963561296463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905832409858704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872296571731567</t>
+    <t xml:space="preserve">0.899635672569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905832529067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872296631336212</t>
   </si>
   <si>
     <t xml:space="preserve">0.879951596260071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878128945827484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882138729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877764344215393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914580941200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934265077114105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911300241947174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944332480430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902750730514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914020538330078</t>
+    <t xml:space="preserve">0.878128886222839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882138669490814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877764403820038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914581120014191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93426513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911300361156464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944332540035248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902750790119171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914020597934723</t>
   </si>
   <si>
     <t xml:space="preserve">0.910522997379303</t>
@@ -2531,31 +2531,31 @@
     <t xml:space="preserve">0.946275532245636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971146881580353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950550258159637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971535384654999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969592332839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981639504432678</t>
+    <t xml:space="preserve">0.971146941184998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950550377368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971535444259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969592392444611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981639444828033</t>
   </si>
   <si>
     <t xml:space="preserve">1.00573348999023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04265189170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04342901706696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03060483932495</t>
+    <t xml:space="preserve">1.04265177249908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04342913627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03060472011566</t>
   </si>
   <si>
     <t xml:space="preserve">1.05236721038818</t>
@@ -2564,73 +2564,73 @@
     <t xml:space="preserve">1.02710723876953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0119514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960265576839447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956379473209381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978141903877258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01156270503998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01778042316437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0096195936203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0193350315094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01467168331146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972312748432159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963763177394867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977364778518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979696333408356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984359800815582</t>
+    <t xml:space="preserve">1.01195132732391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960265755653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956379532814026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978141844272614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01156282424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01778054237366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00961971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01933491230011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01467156410217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972312688827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963763236999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977364718914032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979696393013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984359741210938</t>
   </si>
   <si>
     <t xml:space="preserve">0.999904274940491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996795415878296</t>
+    <t xml:space="preserve">0.996795475482941</t>
   </si>
   <si>
     <t xml:space="preserve">0.993686497211456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983193814754486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98280543088913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958322703838348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961431562900543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960654199123383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973867177963257</t>
+    <t xml:space="preserve">0.983193874359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982805371284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958322584629059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961431443691254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960654258728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973867237567902</t>
   </si>
   <si>
     <t xml:space="preserve">0.973089993000031</t>
@@ -2639,19 +2639,19 @@
     <t xml:space="preserve">0.985136926174164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987857222557068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985525608062744</t>
+    <t xml:space="preserve">0.987857341766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985525667667389</t>
   </si>
   <si>
     <t xml:space="preserve">0.949773132801056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954436540603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970758199691772</t>
+    <t xml:space="preserve">0.954436480998993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970758140087128</t>
   </si>
   <si>
     <t xml:space="preserve">0.92878794670105</t>
@@ -2660,16 +2660,16 @@
     <t xml:space="preserve">0.943166613578796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955990850925446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959877014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953659176826477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965317606925964</t>
+    <t xml:space="preserve">0.95599091053009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959877133369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953659236431122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965317666530609</t>
   </si>
   <si>
     <t xml:space="preserve">0.982028067111969</t>
@@ -2678,10 +2678,10 @@
     <t xml:space="preserve">1.01739192008972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00612211227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994852244853973</t>
+    <t xml:space="preserve">1.00612223148346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994852304458618</t>
   </si>
   <si>
     <t xml:space="preserve">0.979307770729065</t>
@@ -2690,43 +2690,43 @@
     <t xml:space="preserve">0.989411771297455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987079977989197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964929163455963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96259742975235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95871114730835</t>
+    <t xml:space="preserve">0.987080097198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964929103851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96259731054306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958711206912994</t>
   </si>
   <si>
     <t xml:space="preserve">0.96609491109848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.951327562332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954047739505768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975033044815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968038022518158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937726020812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946664273738861</t>
+    <t xml:space="preserve">0.951327443122864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954047858715057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975032985210419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968037962913513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937726140022278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946664154529572</t>
   </si>
   <si>
     <t xml:space="preserve">0.938503265380859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.942000865936279</t>
+    <t xml:space="preserve">0.942000806331635</t>
   </si>
   <si>
     <t xml:space="preserve">0.933451294898987</t>
@@ -2735,58 +2735,58 @@
     <t xml:space="preserve">0.971924066543579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94899582862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953270673751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945886969566345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929565072059631</t>
+    <t xml:space="preserve">0.94899594783783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953270614147186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9458869099617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929565131664276</t>
   </si>
   <si>
     <t xml:space="preserve">0.931119561195374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.900807797908783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903527975082397</t>
+    <t xml:space="preserve">0.900807678699493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903528034687042</t>
   </si>
   <si>
     <t xml:space="preserve">0.904693841934204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89886462688446</t>
+    <t xml:space="preserve">0.898864567279816</t>
   </si>
   <si>
     <t xml:space="preserve">0.878656625747681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.886429011821747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90158486366272</t>
+    <t xml:space="preserve">0.886428952217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901584923267365</t>
   </si>
   <si>
     <t xml:space="preserve">0.886040329933167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840961098670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830079734325409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848344743251801</t>
+    <t xml:space="preserve">0.840961158275604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830079972743988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84834486246109</t>
   </si>
   <si>
     <t xml:space="preserve">0.860780298709869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872050225734711</t>
+    <t xml:space="preserve">0.872050106525421</t>
   </si>
   <si>
     <t xml:space="preserve">0.89847606420517</t>
@@ -2795,49 +2795,49 @@
     <t xml:space="preserve">0.892646729946136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.881377041339874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942778050899506</t>
+    <t xml:space="preserve">0.88137686252594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942778170108795</t>
   </si>
   <si>
     <t xml:space="preserve">0.93928050994873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955213606357574</t>
+    <t xml:space="preserve">0.955213665962219</t>
   </si>
   <si>
     <t xml:space="preserve">0.95249330997467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947441399097443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95210474729538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959488570690155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97619903087616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01700353622437</t>
+    <t xml:space="preserve">0.947441458702087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952104806900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959488391876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97619891166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01700329780579</t>
   </si>
   <si>
     <t xml:space="preserve">1.02205526828766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993297815322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98241662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975421488285065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976587355136871</t>
+    <t xml:space="preserve">0.993297874927521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982416689395905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975421667098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976587533950806</t>
   </si>
   <si>
     <t xml:space="preserve">0.997183978557587</t>
@@ -2846,16 +2846,16 @@
     <t xml:space="preserve">0.990966200828552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988245785236359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984748244285583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995629668235779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954825103282928</t>
+    <t xml:space="preserve">0.988245844841003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984748363494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995629549026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954825222492218</t>
   </si>
   <si>
     <t xml:space="preserve">1.00651073455811</t>
@@ -2864,28 +2864,28 @@
     <t xml:space="preserve">1.01583755016327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01389443874359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03449106216431</t>
+    <t xml:space="preserve">1.0138943195343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03449082374573</t>
   </si>
   <si>
     <t xml:space="preserve">1.02399837970734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04148614406586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03954303264618</t>
+    <t xml:space="preserve">1.04148602485657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03954291343689</t>
   </si>
   <si>
     <t xml:space="preserve">1.03487956523895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01428306102753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03760004043579</t>
+    <t xml:space="preserve">1.01428294181824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03759980201721</t>
   </si>
   <si>
     <t xml:space="preserve">1.0321592092514</t>
@@ -2894,55 +2894,55 @@
     <t xml:space="preserve">1.02050077915192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03099346160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06596875190735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07296371459961</t>
+    <t xml:space="preserve">1.03099358081818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06596863269806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0729638338089</t>
   </si>
   <si>
     <t xml:space="preserve">1.04653811454773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05897378921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05353307723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06169402599335</t>
+    <t xml:space="preserve">1.0589736700058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0535329580307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06169390678406</t>
   </si>
   <si>
     <t xml:space="preserve">1.0449835062027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10871624946594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13630783557892</t>
+    <t xml:space="preserve">1.10871636867523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13630795478821</t>
   </si>
   <si>
     <t xml:space="preserve">1.15418422222137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12853562831879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13825082778931</t>
+    <t xml:space="preserve">1.12853574752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1382509469986</t>
   </si>
   <si>
     <t xml:space="preserve">1.14252579212189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17516934871674</t>
+    <t xml:space="preserve">1.17516922950745</t>
   </si>
   <si>
     <t xml:space="preserve">1.16195642948151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13863968849182</t>
+    <t xml:space="preserve">1.13863956928253</t>
   </si>
   <si>
     <t xml:space="preserve">1.12154054641724</t>
@@ -2963,16 +2963,16 @@
     <t xml:space="preserve">1.11221385002136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09317171573639</t>
+    <t xml:space="preserve">1.0931715965271</t>
   </si>
   <si>
     <t xml:space="preserve">1.08384501934052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11493420600891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1071617603302</t>
+    <t xml:space="preserve">1.11493408679962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10716187953949</t>
   </si>
   <si>
     <t xml:space="preserve">1.07918155193329</t>
@@ -2981,13 +2981,13 @@
     <t xml:space="preserve">1.08656525611877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07723867893219</t>
+    <t xml:space="preserve">1.0772385597229</t>
   </si>
   <si>
     <t xml:space="preserve">1.1083277463913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1308673620224</t>
+    <t xml:space="preserve">1.13086748123169</t>
   </si>
   <si>
     <t xml:space="preserve">1.15262961387634</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">1.15496134757996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16312229633331</t>
+    <t xml:space="preserve">1.1631224155426</t>
   </si>
   <si>
     <t xml:space="preserve">1.14563465118408</t>
@@ -3011,13 +3011,13 @@
     <t xml:space="preserve">1.14641189575195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17089462280273</t>
+    <t xml:space="preserve">1.17089450359344</t>
   </si>
   <si>
     <t xml:space="preserve">1.18954813480377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20470404624939</t>
+    <t xml:space="preserve">1.2047039270401</t>
   </si>
   <si>
     <t xml:space="preserve">1.20664703845978</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">1.21558511257172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21752834320068</t>
+    <t xml:space="preserve">1.2175281047821</t>
   </si>
   <si>
     <t xml:space="preserve">1.20625853538513</t>
@@ -3038,28 +3038,28 @@
     <t xml:space="preserve">1.20859003067017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2241348028183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20975601673126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19809770584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21286499500275</t>
+    <t xml:space="preserve">1.22413468360901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20975589752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19809746742249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21286487579346</t>
   </si>
   <si>
     <t xml:space="preserve">1.21597385406494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21325349807739</t>
+    <t xml:space="preserve">1.2132533788681</t>
   </si>
   <si>
     <t xml:space="preserve">1.20431530475616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21247625350952</t>
+    <t xml:space="preserve">1.21247613430023</t>
   </si>
   <si>
     <t xml:space="preserve">1.22685503959656</t>
@@ -3068,16 +3068,16 @@
     <t xml:space="preserve">1.21403074264526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23579323291779</t>
+    <t xml:space="preserve">1.2357931137085</t>
   </si>
   <si>
     <t xml:space="preserve">1.23812484741211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23851335048676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24278807640076</t>
+    <t xml:space="preserve">1.23851346969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24278819561005</t>
   </si>
   <si>
     <t xml:space="preserve">1.26105296611786</t>
@@ -3086,34 +3086,34 @@
     <t xml:space="preserve">1.26455056667328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27582037448883</t>
+    <t xml:space="preserve">1.27582049369812</t>
   </si>
   <si>
     <t xml:space="preserve">1.26066434383392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26493942737579</t>
+    <t xml:space="preserve">1.2649393081665</t>
   </si>
   <si>
     <t xml:space="preserve">1.27892935276031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30457782745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31779074668884</t>
+    <t xml:space="preserve">1.3045779466629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31779086589813</t>
   </si>
   <si>
     <t xml:space="preserve">1.29291939735413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29874849319458</t>
+    <t xml:space="preserve">1.29874873161316</t>
   </si>
   <si>
     <t xml:space="preserve">1.31740212440491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33061504364014</t>
+    <t xml:space="preserve">1.33061492443085</t>
   </si>
   <si>
     <t xml:space="preserve">1.34693682193756</t>
@@ -3122,22 +3122,22 @@
     <t xml:space="preserve">1.34382772445679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34849119186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35121154785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37258541584015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40067195892334</t>
+    <t xml:space="preserve">1.3484913110733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35121142864227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37258529663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40067207813263</t>
   </si>
   <si>
     <t xml:space="preserve">1.37502765655518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38194751739502</t>
+    <t xml:space="preserve">1.38194763660431</t>
   </si>
   <si>
     <t xml:space="preserve">1.37787699699402</t>
@@ -3146,25 +3146,25 @@
     <t xml:space="preserve">1.39497327804565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39171695709229</t>
+    <t xml:space="preserve">1.391716837883</t>
   </si>
   <si>
     <t xml:space="preserve">1.38438987731934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39456629753113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38886737823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41044127941132</t>
+    <t xml:space="preserve">1.39456617832184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38886749744415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41044116020203</t>
   </si>
   <si>
     <t xml:space="preserve">1.42306005954742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43323624134064</t>
+    <t xml:space="preserve">1.43323636054993</t>
   </si>
   <si>
     <t xml:space="preserve">1.45847368240356</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">1.43852806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43771409988403</t>
+    <t xml:space="preserve">1.43771398067474</t>
   </si>
   <si>
     <t xml:space="preserve">1.4491114616394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44951856136322</t>
+    <t xml:space="preserve">1.44951868057251</t>
   </si>
   <si>
     <t xml:space="preserve">1.45725250244141</t>
@@ -3197,16 +3197,16 @@
     <t xml:space="preserve">1.4430056810379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44422686100006</t>
+    <t xml:space="preserve">1.44422674179077</t>
   </si>
   <si>
     <t xml:space="preserve">1.42713057994843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41858232021332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40352153778076</t>
+    <t xml:space="preserve">1.41858243942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40352141857147</t>
   </si>
   <si>
     <t xml:space="preserve">1.41288363933563</t>
@@ -3218,16 +3218,16 @@
     <t xml:space="preserve">1.41898953914642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41329073905945</t>
+    <t xml:space="preserve">1.41329061985016</t>
   </si>
   <si>
     <t xml:space="preserve">1.43527162075043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37950527667999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38072633743286</t>
+    <t xml:space="preserve">1.3795051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38072645664215</t>
   </si>
   <si>
     <t xml:space="preserve">1.39945089817047</t>
@@ -3236,25 +3236,25 @@
     <t xml:space="preserve">1.41736125946045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.403928399086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40148627758026</t>
+    <t xml:space="preserve">1.40392851829529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40148615837097</t>
   </si>
   <si>
     <t xml:space="preserve">1.34734797477722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35915267467499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38316869735718</t>
+    <t xml:space="preserve">1.3591525554657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38316881656647</t>
   </si>
   <si>
     <t xml:space="preserve">1.395787358284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4511467218399</t>
+    <t xml:space="preserve">1.45114684104919</t>
   </si>
   <si>
     <t xml:space="preserve">1.47719812393188</t>
@@ -3272,31 +3272,31 @@
     <t xml:space="preserve">1.47923338413239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46824312210083</t>
+    <t xml:space="preserve">1.46824300289154</t>
   </si>
   <si>
     <t xml:space="preserve">1.47964036464691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49348032474518</t>
+    <t xml:space="preserve">1.49348020553589</t>
   </si>
   <si>
     <t xml:space="preserve">1.50691306591034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52360224723816</t>
+    <t xml:space="preserve">1.52360236644745</t>
   </si>
   <si>
     <t xml:space="preserve">1.53866338729858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54069864749908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55006074905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58262503147125</t>
+    <t xml:space="preserve">1.54069852828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55006086826324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58262515068054</t>
   </si>
   <si>
     <t xml:space="preserve">1.58669567108154</t>
@@ -3305,13 +3305,13 @@
     <t xml:space="preserve">1.56593596935272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58384621143341</t>
+    <t xml:space="preserve">1.5838463306427</t>
   </si>
   <si>
     <t xml:space="preserve">1.55494546890259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53215026855469</t>
+    <t xml:space="preserve">1.53215038776398</t>
   </si>
   <si>
     <t xml:space="preserve">1.52726578712463</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">1.52197408676147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51424014568329</t>
+    <t xml:space="preserve">1.514240026474</t>
   </si>
   <si>
     <t xml:space="preserve">1.51912474632263</t>
@@ -3335,25 +3335,25 @@
     <t xml:space="preserve">1.49755084514618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52238118648529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49307322502136</t>
+    <t xml:space="preserve">1.522381067276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49307334423065</t>
   </si>
   <si>
     <t xml:space="preserve">1.51464712619781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51627540588379</t>
+    <t xml:space="preserve">1.5162752866745</t>
   </si>
   <si>
     <t xml:space="preserve">1.48615336418152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48940980434418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49063098430634</t>
+    <t xml:space="preserve">1.48940968513489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49063086509705</t>
   </si>
   <si>
     <t xml:space="preserve">1.42794454097748</t>
@@ -3371,10 +3371,10 @@
     <t xml:space="preserve">1.4837110042572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47882640361786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48411810398102</t>
+    <t xml:space="preserve">1.47882628440857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48411822319031</t>
   </si>
   <si>
     <t xml:space="preserve">1.45643842220306</t>
@@ -3383,28 +3383,28 @@
     <t xml:space="preserve">1.45562422275543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43812096118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44544804096222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44015622138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45684552192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48737454414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48533928394318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5040637254715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46417236328125</t>
+    <t xml:space="preserve">1.43812108039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44544792175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44015634059906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45684540271759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48737442493439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48533916473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50406384468079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46417248249054</t>
   </si>
   <si>
     <t xml:space="preserve">1.44504082202911</t>
@@ -3419,13 +3419,13 @@
     <t xml:space="preserve">1.50894844532013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.502028465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48696744441986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50365662574768</t>
+    <t xml:space="preserve">1.50202858448029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48696756362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50365674495697</t>
   </si>
   <si>
     <t xml:space="preserve">1.52970802783966</t>
@@ -3434,28 +3434,28 @@
     <t xml:space="preserve">1.53662812709808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57407712936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55698072910309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55779469013214</t>
+    <t xml:space="preserve">1.57407701015472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5569806098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55779480934143</t>
   </si>
   <si>
     <t xml:space="preserve">1.50732016563416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48004758358002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49022388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49225914478302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.510169506073</t>
+    <t xml:space="preserve">1.48004746437073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49022376537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49225902557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51016938686371</t>
   </si>
   <si>
     <t xml:space="preserve">1.4776052236557</t>
@@ -3467,52 +3467,52 @@
     <t xml:space="preserve">1.50121426582336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51301896572113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51953172683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51546108722687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39212393760681</t>
+    <t xml:space="preserve">1.51301884651184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51953184604645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51546132564545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3921240568161</t>
   </si>
   <si>
     <t xml:space="preserve">1.40596377849579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39538037776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40637075901031</t>
+    <t xml:space="preserve">1.39538025856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40637063980103</t>
   </si>
   <si>
     <t xml:space="preserve">1.45196080207825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43079400062561</t>
+    <t xml:space="preserve">1.4307941198349</t>
   </si>
   <si>
     <t xml:space="preserve">1.45806670188904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45440304279327</t>
+    <t xml:space="preserve">1.45440316200256</t>
   </si>
   <si>
     <t xml:space="preserve">1.45399618148804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42835175991058</t>
+    <t xml:space="preserve">1.42835164070129</t>
   </si>
   <si>
     <t xml:space="preserve">1.39130973815918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32699525356293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34531283378601</t>
+    <t xml:space="preserve">1.32699537277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34531271457672</t>
   </si>
   <si>
     <t xml:space="preserve">1.34775519371033</t>
@@ -3539,16 +3539,16 @@
     <t xml:space="preserve">1.35955953598022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35833835601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37462067604065</t>
+    <t xml:space="preserve">1.35833847522736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37462055683136</t>
   </si>
   <si>
     <t xml:space="preserve">1.36770057678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35589635372162</t>
+    <t xml:space="preserve">1.35589611530304</t>
   </si>
   <si>
     <t xml:space="preserve">1.35263967514038</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">1.32414591312408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35304665565491</t>
+    <t xml:space="preserve">1.3530467748642</t>
   </si>
   <si>
     <t xml:space="preserve">1.34164929389954</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">1.3326940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36525845527649</t>
+    <t xml:space="preserve">1.36525857448578</t>
   </si>
   <si>
     <t xml:space="preserve">1.41532599925995</t>
@@ -3587,19 +3587,19 @@
     <t xml:space="preserve">1.37909817695618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37624895572662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36973583698273</t>
+    <t xml:space="preserve">1.37624883651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36973595619202</t>
   </si>
   <si>
     <t xml:space="preserve">1.33513641357422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30949211120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28262650966644</t>
+    <t xml:space="preserve">1.30949199199677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28262639045715</t>
   </si>
   <si>
     <t xml:space="preserve">1.30094397068024</t>
@@ -3617,67 +3617,67 @@
     <t xml:space="preserve">1.28913938999176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28425467014313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28181219100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27652060985565</t>
+    <t xml:space="preserve">1.28425478935242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28181231021881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27652072906494</t>
   </si>
   <si>
     <t xml:space="preserve">1.25413274765015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22889542579651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25046920776367</t>
+    <t xml:space="preserve">1.22889530658722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25046932697296</t>
   </si>
   <si>
     <t xml:space="preserve">1.22482478618622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28140532970428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3001297712326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25494682788849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22848832607269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19918036460876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18249118328094</t>
+    <t xml:space="preserve">1.28140544891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30012989044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2549467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2284882068634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19918048381805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18249130249023</t>
   </si>
   <si>
     <t xml:space="preserve">1.20243680477142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25616800785065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24639880657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24477052688599</t>
+    <t xml:space="preserve">1.25616788864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24639868736267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2447704076767</t>
   </si>
   <si>
     <t xml:space="preserve">1.23093068599701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22238266468048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22116124629974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21464836597443</t>
+    <t xml:space="preserve">1.22238254547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22116136550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21464860439301</t>
   </si>
   <si>
     <t xml:space="preserve">1.23785054683685</t>
@@ -3689,43 +3689,43 @@
     <t xml:space="preserve">1.22563886642456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22808110713959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23540818691254</t>
+    <t xml:space="preserve">1.22808122634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23540830612183</t>
   </si>
   <si>
     <t xml:space="preserve">1.25698208808899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27489244937897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25779616832733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26553010940552</t>
+    <t xml:space="preserve">1.27489233016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25779604911804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2655303478241</t>
   </si>
   <si>
     <t xml:space="preserve">1.25942444801331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28751122951508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29768753051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29809439182281</t>
+    <t xml:space="preserve">1.28751111030579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29768741130829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2980945110321</t>
   </si>
   <si>
     <t xml:space="preserve">1.33554339408875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36281609535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35223257541656</t>
+    <t xml:space="preserve">1.36281597614288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35223269462585</t>
   </si>
   <si>
     <t xml:space="preserve">1.35711741447449</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">1.34409153461456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36485123634338</t>
+    <t xml:space="preserve">1.36485135555267</t>
   </si>
   <si>
     <t xml:space="preserve">1.33961391448975</t>
@@ -3746,10 +3746,10 @@
     <t xml:space="preserve">1.32129657268524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3245530128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33432233333588</t>
+    <t xml:space="preserve">1.32455289363861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33432245254517</t>
   </si>
   <si>
     <t xml:space="preserve">1.33106589317322</t>
@@ -3758,19 +3758,19 @@
     <t xml:space="preserve">1.34002101421356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3286235332489</t>
+    <t xml:space="preserve">1.32862341403961</t>
   </si>
   <si>
     <t xml:space="preserve">1.31193435192108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31641185283661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35019731521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34653401374817</t>
+    <t xml:space="preserve">1.3164119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35019743442535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34653389453888</t>
   </si>
   <si>
     <t xml:space="preserve">1.34327745437622</t>
@@ -3779,34 +3779,34 @@
     <t xml:space="preserve">1.38561105728149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33147287368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36037361621857</t>
+    <t xml:space="preserve">1.33147299289703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36037373542786</t>
   </si>
   <si>
     <t xml:space="preserve">1.34205627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40272557735443</t>
+    <t xml:space="preserve">1.40272545814514</t>
   </si>
   <si>
     <t xml:space="preserve">1.36872255802155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37862205505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38507843017578</t>
+    <t xml:space="preserve">1.378622174263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38507831096649</t>
   </si>
   <si>
     <t xml:space="preserve">1.3631272315979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35796213150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34504973888397</t>
+    <t xml:space="preserve">1.35796225070953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34504961967468</t>
   </si>
   <si>
     <t xml:space="preserve">1.32998502254486</t>
@@ -3818,10 +3818,10 @@
     <t xml:space="preserve">1.30416011810303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33041548728943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31018602848053</t>
+    <t xml:space="preserve">1.33041560649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31018590927124</t>
   </si>
   <si>
     <t xml:space="preserve">1.3123379945755</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">1.270587682724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18708693981171</t>
+    <t xml:space="preserve">1.187087059021</t>
   </si>
   <si>
     <t xml:space="preserve">1.14921045303345</t>
@@ -3851,31 +3851,31 @@
     <t xml:space="preserve">1.091104388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06570971012115</t>
+    <t xml:space="preserve">1.06570982933044</t>
   </si>
   <si>
     <t xml:space="preserve">1.03945434093475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05581033229828</t>
+    <t xml:space="preserve">1.05581021308899</t>
   </si>
   <si>
     <t xml:space="preserve">1.10143435001373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08593928813934</t>
+    <t xml:space="preserve">1.08593940734863</t>
   </si>
   <si>
     <t xml:space="preserve">1.09540855884552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07517898082733</t>
+    <t xml:space="preserve">1.07517886161804</t>
   </si>
   <si>
     <t xml:space="preserve">1.043328166008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06743144989014</t>
+    <t xml:space="preserve">1.06743133068085</t>
   </si>
   <si>
     <t xml:space="preserve">1.06614017486572</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">1.0510755777359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07130515575409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06915307044983</t>
+    <t xml:space="preserve">1.07130527496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06915318965912</t>
   </si>
   <si>
     <t xml:space="preserve">1.02697229385376</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">1.03601109981537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04074561595917</t>
+    <t xml:space="preserve">1.04074573516846</t>
   </si>
   <si>
     <t xml:space="preserve">1.05451893806458</t>
@@ -3932,10 +3932,10 @@
     <t xml:space="preserve">1.04978430271149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07474851608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09024345874786</t>
+    <t xml:space="preserve">1.07474839687347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09024357795715</t>
   </si>
   <si>
     <t xml:space="preserve">1.06829226016998</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">1.08636963367462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07690072059631</t>
+    <t xml:space="preserve">1.07690060138702</t>
   </si>
   <si>
     <t xml:space="preserve">1.06786179542542</t>
@@ -3956,28 +3956,28 @@
     <t xml:space="preserve">1.11305546760559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10100400447845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10272550582886</t>
+    <t xml:space="preserve">1.10100388526917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10272562503815</t>
   </si>
   <si>
     <t xml:space="preserve">1.08292639255524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06097531318665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06355774402618</t>
+    <t xml:space="preserve">1.06097519397736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06355762481689</t>
   </si>
   <si>
     <t xml:space="preserve">1.05839276313782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0170726776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996843278408051</t>
+    <t xml:space="preserve">1.01707279682159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996843218803406</t>
   </si>
   <si>
     <t xml:space="preserve">0.999425709247589</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">0.963701248168945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946914970874786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968435704708099</t>
+    <t xml:space="preserve">0.946915030479431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968435764312744</t>
   </si>
   <si>
     <t xml:space="preserve">0.945623755455017</t>
@@ -3998,31 +3998,31 @@
     <t xml:space="preserve">0.932711243629456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939167499542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.920229196548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965422928333282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975322365760803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952510416507721</t>
+    <t xml:space="preserve">0.939167439937592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.920229136943817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965422868728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975322425365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952510356903076</t>
   </si>
   <si>
     <t xml:space="preserve">0.92625492811203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930128753185272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913342535495758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92195075750351</t>
+    <t xml:space="preserve">0.930128812789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913342595100403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921950876712799</t>
   </si>
   <si>
     <t xml:space="preserve">0.923242092132568</t>
@@ -4040,25 +4040,25 @@
     <t xml:space="preserve">0.852567851543427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.862984001636505</t>
+    <t xml:space="preserve">0.86298394203186</t>
   </si>
   <si>
     <t xml:space="preserve">0.85377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860659718513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879339635372162</t>
+    <t xml:space="preserve">0.860659658908844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879339694976807</t>
   </si>
   <si>
     <t xml:space="preserve">0.903442978858948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868579268455505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853256464004517</t>
+    <t xml:space="preserve">0.868579208850861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853256404399872</t>
   </si>
   <si>
     <t xml:space="preserve">0.8353511095047</t>
@@ -4073,10 +4073,10 @@
     <t xml:space="preserve">0.820200502872467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825882017612457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863844692707062</t>
+    <t xml:space="preserve">0.825881958007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863844633102417</t>
   </si>
   <si>
     <t xml:space="preserve">0.883643805980682</t>
@@ -4094,40 +4094,40 @@
     <t xml:space="preserve">0.949497520923615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948206305503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982209086418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971018254756927</t>
+    <t xml:space="preserve">0.948206186294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982209146022797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971018373966217</t>
   </si>
   <si>
     <t xml:space="preserve">0.965853273868561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966714143753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966283679008484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955092966556549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972309589385986</t>
+    <t xml:space="preserve">0.966714203357697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966283619403839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955092906951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972309470176697</t>
   </si>
   <si>
     <t xml:space="preserve">0.993830323219299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0045907497406</t>
+    <t xml:space="preserve">1.00459086894989</t>
   </si>
   <si>
     <t xml:space="preserve">1.01061654090881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11176431179047</t>
+    <t xml:space="preserve">1.11176419258118</t>
   </si>
   <si>
     <t xml:space="preserve">1.1160683631897</t>
@@ -4139,16 +4139,16 @@
     <t xml:space="preserve">1.10616886615753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.126828789711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12209439277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11822044849396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09669971466064</t>
+    <t xml:space="preserve">1.12682890892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1220942735672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11822056770325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09669959545135</t>
   </si>
   <si>
     <t xml:space="preserve">1.11391639709473</t>
@@ -4157,19 +4157,19 @@
     <t xml:space="preserve">1.13974130153656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11865091323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09928226470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11090338230133</t>
+    <t xml:space="preserve">1.11865103244781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09928214550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11090350151062</t>
   </si>
   <si>
     <t xml:space="preserve">1.12898087501526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13586759567261</t>
+    <t xml:space="preserve">1.13586747646332</t>
   </si>
   <si>
     <t xml:space="preserve">1.13027215003967</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">1.11951184272766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12166368961334</t>
+    <t xml:space="preserve">1.12166392803192</t>
   </si>
   <si>
     <t xml:space="preserve">1.12984180450439</t>
@@ -4193,10 +4193,10 @@
     <t xml:space="preserve">1.14490628242493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11692941188812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09282600879669</t>
+    <t xml:space="preserve">1.11692917346954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0928258895874</t>
   </si>
   <si>
     <t xml:space="preserve">1.07603967189789</t>
@@ -4208,10 +4208,10 @@
     <t xml:space="preserve">1.06958341598511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07173562049866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09971261024475</t>
+    <t xml:space="preserve">1.07173550128937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09971272945404</t>
   </si>
   <si>
     <t xml:space="preserve">1.12467670440674</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">1.12553763389587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13888037204742</t>
+    <t xml:space="preserve">1.13888049125671</t>
   </si>
   <si>
     <t xml:space="preserve">1.14705836772919</t>
@@ -4229,25 +4229,25 @@
     <t xml:space="preserve">1.18837833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19354343414307</t>
+    <t xml:space="preserve">1.19354331493378</t>
   </si>
   <si>
     <t xml:space="preserve">1.19827771186829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20043003559113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20516443252563</t>
+    <t xml:space="preserve">1.20042991638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20516455173492</t>
   </si>
   <si>
     <t xml:space="preserve">1.21032953262329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17245304584503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15093207359314</t>
+    <t xml:space="preserve">1.17245292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15093219280243</t>
   </si>
   <si>
     <t xml:space="preserve">1.18192207813263</t>
@@ -4262,16 +4262,16 @@
     <t xml:space="preserve">1.20430374145508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21119022369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1948344707489</t>
+    <t xml:space="preserve">1.21119034290314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19483458995819</t>
   </si>
   <si>
     <t xml:space="preserve">1.18665671348572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20989918708801</t>
+    <t xml:space="preserve">1.20989906787872</t>
   </si>
   <si>
     <t xml:space="preserve">1.18794786930084</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">1.17632663249969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17675697803497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19139111042023</t>
+    <t xml:space="preserve">1.17675709724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19139122962952</t>
   </si>
   <si>
     <t xml:space="preserve">1.18235242366791</t>
@@ -4301,16 +4301,16 @@
     <t xml:space="preserve">1.19225203990936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17976987361908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18579590320587</t>
+    <t xml:space="preserve">1.17976999282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18579578399658</t>
   </si>
   <si>
     <t xml:space="preserve">1.18966948986053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20215165615082</t>
+    <t xml:space="preserve">1.20215153694153</t>
   </si>
   <si>
     <t xml:space="preserve">1.20129072666168</t>
@@ -4322,10 +4322,10 @@
     <t xml:space="preserve">1.18364369869232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19784736633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18149161338806</t>
+    <t xml:space="preserve">1.1978474855423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18149149417877</t>
   </si>
   <si>
     <t xml:space="preserve">1.18493497371674</t>
@@ -4337,34 +4337,34 @@
     <t xml:space="preserve">1.16814875602722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15738832950592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18278300762177</t>
+    <t xml:space="preserve">1.15738821029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18278288841248</t>
   </si>
   <si>
     <t xml:space="preserve">1.18321335315704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25078856945038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26240992546082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2365847826004</t>
+    <t xml:space="preserve">1.25078845024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26240980625153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23658490180969</t>
   </si>
   <si>
     <t xml:space="preserve">1.25294065475464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2395977973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23787605762482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21678566932678</t>
+    <t xml:space="preserve">1.23959791660309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23787617683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21678578853607</t>
   </si>
   <si>
     <t xml:space="preserve">1.22496366500854</t>
@@ -4379,16 +4379,16 @@
     <t xml:space="preserve">1.25853610038757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26714432239532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29426074028015</t>
+    <t xml:space="preserve">1.26714444160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29426062107086</t>
   </si>
   <si>
     <t xml:space="preserve">1.32869386672974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33256769180298</t>
+    <t xml:space="preserve">1.33256757259369</t>
   </si>
   <si>
     <t xml:space="preserve">1.33730220794678</t>
@@ -4400,13 +4400,13 @@
     <t xml:space="preserve">1.32137680053711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31922471523285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35150587558746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33988475799561</t>
+    <t xml:space="preserve">1.31922483444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35150599479675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33988463878632</t>
   </si>
   <si>
     <t xml:space="preserve">1.35279715061188</t>
@@ -4415,19 +4415,19 @@
     <t xml:space="preserve">1.35968375205994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3523668050766</t>
+    <t xml:space="preserve">1.35236668586731</t>
   </si>
   <si>
     <t xml:space="preserve">1.36614012718201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37733089923859</t>
+    <t xml:space="preserve">1.3773307800293</t>
   </si>
   <si>
     <t xml:space="preserve">1.34332811832428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3678617477417</t>
+    <t xml:space="preserve">1.36786162853241</t>
   </si>
   <si>
     <t xml:space="preserve">1.36829209327698</t>
@@ -4436,16 +4436,16 @@
     <t xml:space="preserve">1.3880912065506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40057337284088</t>
+    <t xml:space="preserve">1.40057325363159</t>
   </si>
   <si>
     <t xml:space="preserve">1.39885175228119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4126250743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43113279342651</t>
+    <t xml:space="preserve">1.41262495517731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4311329126358</t>
   </si>
   <si>
     <t xml:space="preserve">1.45609700679779</t>
@@ -4454,22 +4454,22 @@
     <t xml:space="preserve">1.46728777885437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44877982139587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43758916854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37905251979828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41047286987305</t>
+    <t xml:space="preserve">1.44877994060516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43758904933929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37905263900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41047298908234</t>
   </si>
   <si>
     <t xml:space="preserve">1.42495942115784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42905950546265</t>
+    <t xml:space="preserve">1.42905938625336</t>
   </si>
   <si>
     <t xml:space="preserve">1.39261531829834</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">1.39079320430756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38532650470734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40719306468964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41038191318512</t>
+    <t xml:space="preserve">1.38532662391663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40719294548035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41038179397583</t>
   </si>
   <si>
     <t xml:space="preserve">1.4313371181488</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">1.45684790611267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4563924074173</t>
+    <t xml:space="preserve">1.45639228820801</t>
   </si>
   <si>
     <t xml:space="preserve">1.48235869407654</t>
@@ -4520,19 +4520,19 @@
     <t xml:space="preserve">1.50103628635406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50786936283112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51743614673615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50012505054474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50376951694489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4768922328949</t>
+    <t xml:space="preserve">1.50786948204041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51743602752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50012516975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50376963615417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47689211368561</t>
   </si>
   <si>
     <t xml:space="preserve">1.49784743785858</t>
@@ -4541,13 +4541,13 @@
     <t xml:space="preserve">1.49420297145844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50695836544037</t>
+    <t xml:space="preserve">1.50695848464966</t>
   </si>
   <si>
     <t xml:space="preserve">1.51652491092682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52563583850861</t>
+    <t xml:space="preserve">1.5256359577179</t>
   </si>
   <si>
     <t xml:space="preserve">1.5242692232132</t>
@@ -4571,7 +4571,7 @@
     <t xml:space="preserve">1.54112458229065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53975808620453</t>
+    <t xml:space="preserve">1.53975796699524</t>
   </si>
   <si>
     <t xml:space="preserve">1.52153599262238</t>
@@ -4583,7 +4583,7 @@
     <t xml:space="preserve">1.53064692020416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53383588790894</t>
+    <t xml:space="preserve">1.53383576869965</t>
   </si>
   <si>
     <t xml:space="preserve">1.53520238399506</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">1.54750227928162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55433559417725</t>
+    <t xml:space="preserve">1.55433547496796</t>
   </si>
   <si>
     <t xml:space="preserve">1.56435763835907</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">1.55160212516785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58121287822723</t>
+    <t xml:space="preserve">1.58121299743652</t>
   </si>
   <si>
     <t xml:space="preserve">1.57939076423645</t>
@@ -4613,10 +4613,10 @@
     <t xml:space="preserve">1.54249119758606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51470267772675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5110582113266</t>
+    <t xml:space="preserve">1.51470279693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51105833053589</t>
   </si>
   <si>
     <t xml:space="preserve">1.49921405315399</t>
@@ -4631,13 +4631,13 @@
     <t xml:space="preserve">1.54886901378632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56709098815918</t>
+    <t xml:space="preserve">1.56709086894989</t>
   </si>
   <si>
     <t xml:space="preserve">1.52335822582245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52836930751801</t>
+    <t xml:space="preserve">1.52836918830872</t>
   </si>
   <si>
     <t xml:space="preserve">1.54613566398621</t>
@@ -4649,37 +4649,37 @@
     <t xml:space="preserve">1.57210195064545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58349072933197</t>
+    <t xml:space="preserve">1.58349084854126</t>
   </si>
   <si>
     <t xml:space="preserve">1.58622407913208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60581278800964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59487950801849</t>
+    <t xml:space="preserve">1.60581266880035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5948793888092</t>
   </si>
   <si>
     <t xml:space="preserve">1.61219036579132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59214603900909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57984638214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56481313705444</t>
+    <t xml:space="preserve">1.59214615821838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57984626293182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56481325626373</t>
   </si>
   <si>
     <t xml:space="preserve">1.59123516082764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60034608840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61310148239136</t>
+    <t xml:space="preserve">1.60034596920013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61310136318207</t>
   </si>
   <si>
     <t xml:space="preserve">1.63041234016418</t>
@@ -4703,7 +4703,7 @@
     <t xml:space="preserve">1.70056700706482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6345123052597</t>
+    <t xml:space="preserve">1.63451242446899</t>
   </si>
   <si>
     <t xml:space="preserve">1.5994348526001</t>
@@ -4721,25 +4721,25 @@
     <t xml:space="preserve">1.51060271263123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53611361980438</t>
+    <t xml:space="preserve">1.53611350059509</t>
   </si>
   <si>
     <t xml:space="preserve">1.48828089237213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50285851955414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.521080493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55889093875885</t>
+    <t xml:space="preserve">1.50285840034485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52108037471771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55889105796814</t>
   </si>
   <si>
     <t xml:space="preserve">1.56800198554993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58440172672272</t>
+    <t xml:space="preserve">1.58440184593201</t>
   </si>
   <si>
     <t xml:space="preserve">1.57893526554108</t>
@@ -4754,10 +4754,10 @@
     <t xml:space="preserve">1.54659116268158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57756853103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57620203495026</t>
+    <t xml:space="preserve">1.57756865024567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57620191574097</t>
   </si>
   <si>
     <t xml:space="preserve">1.59761273860931</t>
@@ -4766,37 +4766,37 @@
     <t xml:space="preserve">1.60125720500946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61355710029602</t>
+    <t xml:space="preserve">1.61355698108673</t>
   </si>
   <si>
     <t xml:space="preserve">1.63724565505981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.633145570755</t>
+    <t xml:space="preserve">1.63314568996429</t>
   </si>
   <si>
     <t xml:space="preserve">1.63223457336426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62767899036407</t>
+    <t xml:space="preserve">1.62767910957336</t>
   </si>
   <si>
     <t xml:space="preserve">1.6167459487915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61765694618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63177907466888</t>
+    <t xml:space="preserve">1.61765706539154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63177895545959</t>
   </si>
   <si>
     <t xml:space="preserve">1.69601154327393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71742224693298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.761155128479</t>
+    <t xml:space="preserve">1.71742236614227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76115500926971</t>
   </si>
   <si>
     <t xml:space="preserve">1.7597883939743</t>
@@ -4826,7 +4826,7 @@
     <t xml:space="preserve">1.79031038284302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79759919643402</t>
+    <t xml:space="preserve">1.79759907722473</t>
   </si>
   <si>
     <t xml:space="preserve">1.79167699813843</t>
@@ -4835,7 +4835,7 @@
     <t xml:space="preserve">1.77709937095642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78256607055664</t>
+    <t xml:space="preserve">1.78256595134735</t>
   </si>
   <si>
     <t xml:space="preserve">1.77846598625183</t>
@@ -4844,16 +4844,16 @@
     <t xml:space="preserve">1.78211033344269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78712141513824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77618813514709</t>
+    <t xml:space="preserve">1.78712153434753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77618825435638</t>
   </si>
   <si>
     <t xml:space="preserve">1.74384427070618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77208840847015</t>
+    <t xml:space="preserve">1.77208828926086</t>
   </si>
   <si>
     <t xml:space="preserve">1.79805469512939</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">1.74019980430603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71377789974213</t>
+    <t xml:space="preserve">1.71377801895142</t>
   </si>
   <si>
     <t xml:space="preserve">1.6964670419693</t>
@@ -4886,10 +4886,10 @@
     <t xml:space="preserve">1.68280053138733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67778956890106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71651124954224</t>
+    <t xml:space="preserve">1.67778944969177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71651113033295</t>
   </si>
   <si>
     <t xml:space="preserve">1.72061121463776</t>
@@ -4898,10 +4898,10 @@
     <t xml:space="preserve">1.73792207241058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74247765541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74703299999237</t>
+    <t xml:space="preserve">1.74247753620148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74703311920166</t>
   </si>
   <si>
     <t xml:space="preserve">1.69692254066467</t>
@@ -4922,10 +4922,10 @@
     <t xml:space="preserve">1.64453434944153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66184520721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64225661754608</t>
+    <t xml:space="preserve">1.66184532642365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64225673675537</t>
   </si>
   <si>
     <t xml:space="preserve">1.59897947311401</t>
@@ -4934,7 +4934,7 @@
     <t xml:space="preserve">1.62995684146881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62859010696411</t>
+    <t xml:space="preserve">1.6285902261734</t>
   </si>
   <si>
     <t xml:space="preserve">1.66321194171906</t>
@@ -4943,10 +4943,10 @@
     <t xml:space="preserve">1.67687833309174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60307931900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56936872005463</t>
+    <t xml:space="preserve">1.60307943820953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56936860084534</t>
   </si>
   <si>
     <t xml:space="preserve">1.55296885967255</t>
@@ -4955,13 +4955,13 @@
     <t xml:space="preserve">1.5124249458313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51014733314514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49238073825836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48964750766754</t>
+    <t xml:space="preserve">1.51014721393585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49238085746765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48964738845825</t>
   </si>
   <si>
     <t xml:space="preserve">1.51698040962219</t>
@@ -4976,7 +4976,7 @@
     <t xml:space="preserve">1.55023562908173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55114662647247</t>
+    <t xml:space="preserve">1.55114674568176</t>
   </si>
   <si>
     <t xml:space="preserve">1.54066896438599</t>
@@ -4985,7 +4985,7 @@
     <t xml:space="preserve">1.53839135169983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52518045902252</t>
+    <t xml:space="preserve">1.52518033981323</t>
   </si>
   <si>
     <t xml:space="preserve">1.51288056373596</t>
@@ -5000,13 +5000,13 @@
     <t xml:space="preserve">1.58212411403656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59533500671387</t>
+    <t xml:space="preserve">1.59533512592316</t>
   </si>
   <si>
     <t xml:space="preserve">1.53748023509979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49602508544922</t>
+    <t xml:space="preserve">1.49602520465851</t>
   </si>
   <si>
     <t xml:space="preserve">1.50468063354492</t>
@@ -5015,13 +5015,13 @@
     <t xml:space="preserve">1.50149178504944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49556970596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47279214859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49283623695374</t>
+    <t xml:space="preserve">1.49556958675385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47279226779938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49283635616302</t>
   </si>
   <si>
     <t xml:space="preserve">1.52472484111786</t>
@@ -5033,7 +5033,7 @@
     <t xml:space="preserve">1.50422501564026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47370314598083</t>
+    <t xml:space="preserve">1.47370326519012</t>
   </si>
   <si>
     <t xml:space="preserve">1.50331389904022</t>
@@ -5042,7 +5042,7 @@
     <t xml:space="preserve">1.5051361322403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48418092727661</t>
+    <t xml:space="preserve">1.48418080806732</t>
   </si>
   <si>
     <t xml:space="preserve">1.49966955184937</t>
@@ -5051,7 +5051,7 @@
     <t xml:space="preserve">1.57574641704559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59624600410461</t>
+    <t xml:space="preserve">1.5962461233139</t>
   </si>
   <si>
     <t xml:space="preserve">1.65592312812805</t>
@@ -5066,19 +5066,19 @@
     <t xml:space="preserve">1.70694470405579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.690544962883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7142333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69464492797852</t>
+    <t xml:space="preserve">1.69054484367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71423351764679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69464480876923</t>
   </si>
   <si>
     <t xml:space="preserve">1.71241128444672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72380006313324</t>
+    <t xml:space="preserve">1.72379994392395</t>
   </si>
   <si>
     <t xml:space="preserve">1.74156641960144</t>
@@ -5087,7 +5087,7 @@
     <t xml:space="preserve">1.74794411659241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75341081619263</t>
+    <t xml:space="preserve">1.75341069698334</t>
   </si>
   <si>
     <t xml:space="preserve">1.7921324968338</t>
@@ -5102,7 +5102,7 @@
     <t xml:space="preserve">1.84497630596161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83586525917053</t>
+    <t xml:space="preserve">1.83586537837982</t>
   </si>
   <si>
     <t xml:space="preserve">1.84284818172455</t>
@@ -71015,13 +71015,13 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6513425926</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>10287961</v>
       </c>
       <c r="C2491" t="n">
-        <v>2.33200001716614</v>
+        <v>2.33500003814697</v>
       </c>
       <c r="D2491" t="n">
         <v>2.2720000743866</v>
@@ -71036,6 +71036,32 @@
         <v>1974</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.650162037</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>7709417</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>2.29699993133545</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>2.33599996566772</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>2.32100009918213</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1918</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="1975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="1976">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765547633171082</t>
+    <t xml:space="preserve">0.765547573566437</t>
   </si>
   <si>
     <t xml:space="preserve">A2A.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774304032325745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769300282001495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777431190013885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772427499294281</t>
+    <t xml:space="preserve">0.7743039727211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769300401210785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777431130409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772427618503571</t>
   </si>
   <si>
     <t xml:space="preserve">0.775554776191711</t>
@@ -65,34 +65,34 @@
     <t xml:space="preserve">0.728020906448364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.708631932735443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701126635074615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.678610563278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.686115860939026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.662974298000336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.66985422372818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.673606932163239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661723434925079</t>
+    <t xml:space="preserve">0.708632111549377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701126754283905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678610503673553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.686115801334381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.662974238395691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.669854164123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.673606991767883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661723375320435</t>
   </si>
   <si>
     <t xml:space="preserve">0.68986850976944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667352497577667</t>
+    <t xml:space="preserve">0.667352437973022</t>
   </si>
   <si>
     <t xml:space="preserve">0.688617646694183</t>
@@ -101,67 +101,67 @@
     <t xml:space="preserve">0.689243018627167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.676108717918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.671105027198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.666727006435394</t>
+    <t xml:space="preserve">0.676108658313751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.671105086803436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.666726887226105</t>
   </si>
   <si>
     <t xml:space="preserve">0.643585443496704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612313032150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597927749156952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605745851993561</t>
+    <t xml:space="preserve">0.612312972545624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597927689552307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605745792388916</t>
   </si>
   <si>
     <t xml:space="preserve">0.610749423503876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614189386367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627323925495148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617942094802856</t>
+    <t xml:space="preserve">0.614189445972443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627323806285858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617942154407501</t>
   </si>
   <si>
     <t xml:space="preserve">0.624822080135345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64671266078949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.636080086231232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.656719744205475</t>
+    <t xml:space="preserve">0.646712720394135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.636080026626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65671968460083</t>
   </si>
   <si>
     <t xml:space="preserve">0.645461678504944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641083717346191</t>
+    <t xml:space="preserve">0.641083598136902</t>
   </si>
   <si>
     <t xml:space="preserve">0.647963523864746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657345294952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661098003387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.67298150062561</t>
+    <t xml:space="preserve">0.657345235347748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661097943782806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.672981381416321</t>
   </si>
   <si>
     <t xml:space="preserve">0.666101574897766</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">0.664850652217865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658596217632294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651716291904449</t>
+    <t xml:space="preserve">0.658596277236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651716232299805</t>
   </si>
   <si>
     <t xml:space="preserve">0.654843509197235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669228911399841</t>
+    <t xml:space="preserve">0.669228792190552</t>
   </si>
   <si>
     <t xml:space="preserve">0.71301007270813</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">0.69299578666687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.691119492053986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.694246590137482</t>
+    <t xml:space="preserve">0.691119432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.694246649742126</t>
   </si>
   <si>
     <t xml:space="preserve">0.69799941778183</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">0.70300281047821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.692370295524597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.699250280857086</t>
+    <t xml:space="preserve">0.692370355129242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.699250161647797</t>
   </si>
   <si>
     <t xml:space="preserve">0.714260935783386</t>
@@ -218,64 +218,64 @@
     <t xml:space="preserve">0.702377438545227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.705504715442657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735526084899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.740529716014862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.744282484054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748660624027252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.738027930259705</t>
+    <t xml:space="preserve">0.705504834651947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735526263713837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.740529775619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74428254365921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748660564422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73802787065506</t>
   </si>
   <si>
     <t xml:space="preserve">0.750536918640137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.754289567470551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768049538135529</t>
+    <t xml:space="preserve">0.754289627075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768049478530884</t>
   </si>
   <si>
     <t xml:space="preserve">0.757416784763336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766798436641693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.752413094043732</t>
+    <t xml:space="preserve">0.766798555850983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.752413332462311</t>
   </si>
   <si>
     <t xml:space="preserve">0.781183838844299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778056621551514</t>
+    <t xml:space="preserve">0.778056561946869</t>
   </si>
   <si>
     <t xml:space="preserve">0.786187410354614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77930748462677</t>
+    <t xml:space="preserve">0.779307663440704</t>
   </si>
   <si>
     <t xml:space="preserve">0.768674969673157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.755540430545807</t>
+    <t xml:space="preserve">0.755540490150452</t>
   </si>
   <si>
     <t xml:space="preserve">0.760544061660767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.76429682970047</t>
+    <t xml:space="preserve">0.764296889305115</t>
   </si>
   <si>
     <t xml:space="preserve">0.770551264286041</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">0.769925832748413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.76116955280304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767423987388611</t>
+    <t xml:space="preserve">0.761169612407684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767423927783966</t>
   </si>
   <si>
     <t xml:space="preserve">0.747409701347351</t>
@@ -299,43 +299,43 @@
     <t xml:space="preserve">0.751787900924683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.754915058612823</t>
+    <t xml:space="preserve">0.754915177822113</t>
   </si>
   <si>
     <t xml:space="preserve">0.781809329986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801198124885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804950952529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79932177066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785562098026276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796820163726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791816532611847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801823556423187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733649790287018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725519061088562</t>
+    <t xml:space="preserve">0.801198244094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804950833320618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799321830272675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785561978816986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796820223331451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791816651821136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801823675632477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733649909496307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725519001483917</t>
   </si>
   <si>
     <t xml:space="preserve">0.766306400299072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.759828746318817</t>
+    <t xml:space="preserve">0.759828865528107</t>
   </si>
   <si>
     <t xml:space="preserve">0.750760078430176</t>
@@ -344,37 +344,37 @@
     <t xml:space="preserve">0.778614103794098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.703473269939423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692461252212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705416560173035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.730031549930573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763067543506622</t>
+    <t xml:space="preserve">0.703473150730133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69246119260788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705416440963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.730031609535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763067662715912</t>
   </si>
   <si>
     <t xml:space="preserve">0.762419879436493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769545257091522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75788539648056</t>
+    <t xml:space="preserve">0.769545316696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757885456085205</t>
   </si>
   <si>
     <t xml:space="preserve">0.742986857891083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.742339074611664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.758533298969269</t>
+    <t xml:space="preserve">0.742339134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758533239364624</t>
   </si>
   <si>
     <t xml:space="preserve">0.777318477630615</t>
@@ -383,10 +383,10 @@
     <t xml:space="preserve">0.774079620838165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776022911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783796191215515</t>
+    <t xml:space="preserve">0.776022970676422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783796072006226</t>
   </si>
   <si>
     <t xml:space="preserve">0.779909551143646</t>
@@ -398,22 +398,22 @@
     <t xml:space="preserve">0.789625942707062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79416024684906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805172383785248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807763457298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.822662055492401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81747978925705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820718705654144</t>
+    <t xml:space="preserve">0.794160306453705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805172264575958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807763397693634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.822662115097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817479968070984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820718765258789</t>
   </si>
   <si>
     <t xml:space="preserve">0.822014272212982</t>
@@ -422,61 +422,61 @@
     <t xml:space="preserve">0.809706747531891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814241051673889</t>
+    <t xml:space="preserve">0.814241111278534</t>
   </si>
   <si>
     <t xml:space="preserve">0.816184401512146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804524600505829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801285743713379</t>
+    <t xml:space="preserve">0.804524660110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801285922527313</t>
   </si>
   <si>
     <t xml:space="preserve">0.812945544719696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801933646202087</t>
+    <t xml:space="preserve">0.801933586597443</t>
   </si>
   <si>
     <t xml:space="preserve">0.786387205123901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.788330495357513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771488606929779</t>
+    <t xml:space="preserve">0.788330554962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771488547325134</t>
   </si>
   <si>
     <t xml:space="preserve">0.783148407936096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.782500505447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781852841377258</t>
+    <t xml:space="preserve">0.782500565052032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781852960586548</t>
   </si>
   <si>
     <t xml:space="preserve">0.770193040370941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785091698169708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795455992221832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811002254486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794808089733124</t>
+    <t xml:space="preserve">0.785091638565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795455873012543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811002314090729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794808030128479</t>
   </si>
   <si>
     <t xml:space="preserve">0.796103715896606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.798694670200348</t>
+    <t xml:space="preserve">0.798694789409637</t>
   </si>
   <si>
     <t xml:space="preserve">0.802581250667572</t>
@@ -485,13 +485,13 @@
     <t xml:space="preserve">0.7909215092659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.796751379966736</t>
+    <t xml:space="preserve">0.796751499176025</t>
   </si>
   <si>
     <t xml:space="preserve">0.799342513084412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81035453081131</t>
+    <t xml:space="preserve">0.810354471206665</t>
   </si>
   <si>
     <t xml:space="preserve">0.780557334423065</t>
@@ -500,40 +500,40 @@
     <t xml:space="preserve">0.784443795681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785739541053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827196419239044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813593447208405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80063807964325</t>
+    <t xml:space="preserve">0.785739421844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827196300029755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813593327999115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80063784122467</t>
   </si>
   <si>
     <t xml:space="preserve">0.7973992228508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803876936435699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80711567401886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.761124312877655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77084082365036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73132711648941</t>
+    <t xml:space="preserve">0.803876876831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807115793228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7611243724823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770840883255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.731327176094055</t>
   </si>
   <si>
     <t xml:space="preserve">0.735861480236053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720315039157867</t>
+    <t xml:space="preserve">0.720315158367157</t>
   </si>
   <si>
     <t xml:space="preserve">0.721610605716705</t>
@@ -542,10 +542,10 @@
     <t xml:space="preserve">0.719019532203674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696347832679749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696995615959167</t>
+    <t xml:space="preserve">0.696347951889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696995556354523</t>
   </si>
   <si>
     <t xml:space="preserve">0.709950923919678</t>
@@ -554,109 +554,109 @@
     <t xml:space="preserve">0.713837385177612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.711894154548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.707359850406647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728735983371735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715780794620514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722258329391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765010833740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7546466588974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755294382572174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787682712078094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776670634746552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772136330604553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787034928798676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81683224439621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819423198699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799990177154541</t>
+    <t xml:space="preserve">0.71189421415329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.707359910011292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728736102581024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715780735015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722258388996124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765010952949524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754646718502045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755294442176819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787682771682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776670575141907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772136390209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78703498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816832184791565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819423258304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799990236759186</t>
   </si>
   <si>
     <t xml:space="preserve">0.824605345726013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838856279850006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831730723381042</t>
+    <t xml:space="preserve">0.838856220245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831730782985687</t>
   </si>
   <si>
     <t xml:space="preserve">0.832378447055817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840151607990265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848572552204132</t>
+    <t xml:space="preserve">0.840151727199554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848572790622711</t>
   </si>
   <si>
     <t xml:space="preserve">0.841447293758392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.844685912132263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830435156822205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798046946525574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815536558628082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820071041584015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806467890739441</t>
+    <t xml:space="preserve">0.844686150550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830435276031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798047006130219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815536618232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820071160793304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80646800994873</t>
   </si>
   <si>
     <t xml:space="preserve">0.811649978160858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83626514673233</t>
+    <t xml:space="preserve">0.836265206336975</t>
   </si>
   <si>
     <t xml:space="preserve">0.844038307666779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837560713291168</t>
+    <t xml:space="preserve">0.837560594081879</t>
   </si>
   <si>
     <t xml:space="preserve">0.836912870407104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.821366608142853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828492045402527</t>
+    <t xml:space="preserve">0.821366429328918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828492105007172</t>
   </si>
   <si>
     <t xml:space="preserve">0.825900912284851</t>
@@ -665,220 +665,220 @@
     <t xml:space="preserve">0.829139649868011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.846629321575165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849220275878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864766836166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867357730865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868005573749542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870596647262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857641339302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.865414440631866</t>
+    <t xml:space="preserve">0.846629440784454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849220454692841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864766895771027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867357790470123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868005871772766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870596587657928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857641279697418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.865414619445801</t>
   </si>
   <si>
     <t xml:space="preserve">0.866710126399994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.853107035160065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855697929859161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858289122581482</t>
+    <t xml:space="preserve">0.85310697555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855697989463806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858289182186127</t>
   </si>
   <si>
     <t xml:space="preserve">0.860232353210449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872539937496185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874483168125153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887438535690308</t>
+    <t xml:space="preserve">0.872540056705475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874483346939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887438654899597</t>
   </si>
   <si>
     <t xml:space="preserve">0.893916189670563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892620742321014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912701427936554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909462571144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908167123794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919826865196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91853141784668</t>
+    <t xml:space="preserve">0.89262068271637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912701487541199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909462690353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908166944980621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919826745986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918531239032745</t>
   </si>
   <si>
     <t xml:space="preserve">0.87577885389328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877722024917603</t>
+    <t xml:space="preserve">0.877722203731537</t>
   </si>
   <si>
     <t xml:space="preserve">0.891972839832306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.884847462177277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895211637020111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884199738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876426517963409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862175643444061</t>
+    <t xml:space="preserve">0.884847700595856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895211815834045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884199857711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876426577568054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862175703048706</t>
   </si>
   <si>
     <t xml:space="preserve">0.856345891952515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.882256329059601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89909827709198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890677273273468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926952302455902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915292501449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917235851287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966466069221497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95804500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965170562267303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96128386259079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963227272033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941850900650024</t>
+    <t xml:space="preserve">0.882256507873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89909839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890677392482758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926952242851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91529256105423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917235791683197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966465890407562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958045065402985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96517026424408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961283802986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963227152824402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94185084104538</t>
   </si>
   <si>
     <t xml:space="preserve">0.941203117370605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958692908287048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982278108596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988308548927307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997019290924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00036942958832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992998898029327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96820741891861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981608331203461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986298501491547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988978505134583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989648759365082</t>
+    <t xml:space="preserve">0.958692789077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982278227806091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988308429718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997019171714783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00036931037903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992998659610748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968207180500031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981608152389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986298382282257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988978385925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989648520946503</t>
   </si>
   <si>
     <t xml:space="preserve">0.97490781545639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999699175357819</t>
+    <t xml:space="preserve">0.999699294567108</t>
   </si>
   <si>
     <t xml:space="preserve">1.00505948066711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998359084129333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997689068317413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00170946121216</t>
+    <t xml:space="preserve">0.998359203338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997689247131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00170934200287</t>
   </si>
   <si>
     <t xml:space="preserve">1.00706970691681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02047038078308</t>
+    <t xml:space="preserve">1.02047049999237</t>
   </si>
   <si>
     <t xml:space="preserve">1.02985095977783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01779043674469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995009064674377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999029219150543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976917862892151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.974237680435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970217525959015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965527355670929</t>
+    <t xml:space="preserve">1.0177903175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995008945465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999029338359833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976917803287506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.974237740039825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97021746635437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965527236461639</t>
   </si>
   <si>
     <t xml:space="preserve">0.960837006568909</t>
@@ -887,76 +887,76 @@
     <t xml:space="preserve">0.961506903171539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.964187145233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980268239974976</t>
+    <t xml:space="preserve">0.964187204837799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980268061161041</t>
   </si>
   <si>
     <t xml:space="preserve">0.978927969932556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984958350658417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972897708415985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960166871547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958826839923859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951456308364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955476701259613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949446320533752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963517010211945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950116336345673</t>
+    <t xml:space="preserve">0.984958291053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97289776802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960166931152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958826720714569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951456427574158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955476343631744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949446380138397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963517069816589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950116217136383</t>
   </si>
   <si>
     <t xml:space="preserve">0.953466475009918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.956816732883453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958156764507294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952796459197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962176978588104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944756031036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93135529756546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948106169700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954136610031128</t>
+    <t xml:space="preserve">0.956816554069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958156704902649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952796399593353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962177097797394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944755852222443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931355237960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948106288909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954136490821838</t>
   </si>
   <si>
     <t xml:space="preserve">0.957486748695374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939395666122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946766078472137</t>
+    <t xml:space="preserve">0.939395546913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946766197681427</t>
   </si>
   <si>
     <t xml:space="preserve">0.934705436229706</t>
@@ -971,46 +971,46 @@
     <t xml:space="preserve">0.932695209980011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945426166057587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959496974945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973567605018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978258073329926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993669033050537</t>
+    <t xml:space="preserve">0.945426106452942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959496915340424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973567724227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978258013725281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993668913841248</t>
   </si>
   <si>
     <t xml:space="preserve">0.984288394451141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983618378639221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994338929653168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977587938308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980938196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972227692604065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966197490692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969547510147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968877553939819</t>
+    <t xml:space="preserve">0.983618438243866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994338870048523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977587878704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980938136577606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972227513790131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96619725227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969547271728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968877375125885</t>
   </si>
   <si>
     <t xml:space="preserve">0.971557557582855</t>
@@ -1019,16 +1019,16 @@
     <t xml:space="preserve">0.995678961277008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992328703403473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96686726808548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02114057540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01041984558105</t>
+    <t xml:space="preserve">0.992328643798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966867208480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02114045619965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01041996479034</t>
   </si>
   <si>
     <t xml:space="preserve">1.01444017887115</t>
@@ -1037,34 +1037,34 @@
     <t xml:space="preserve">1.02181041240692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02382063865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0285108089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03320109844208</t>
+    <t xml:space="preserve">1.02382075786591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02851092815399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03320121765137</t>
   </si>
   <si>
     <t xml:space="preserve">1.03923153877258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0265007019043</t>
+    <t xml:space="preserve">1.02650082111359</t>
   </si>
   <si>
     <t xml:space="preserve">1.05531251430511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05866277217865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04459166526794</t>
+    <t xml:space="preserve">1.05866265296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04459190368652</t>
   </si>
   <si>
     <t xml:space="preserve">1.05330240726471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06804323196411</t>
+    <t xml:space="preserve">1.06804311275482</t>
   </si>
   <si>
     <t xml:space="preserve">1.07273352146149</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">1.0955148935318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08345425128937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08211421966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0539722442627</t>
+    <t xml:space="preserve">1.08345401287079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08211410045624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05397236347198</t>
   </si>
   <si>
     <t xml:space="preserve">1.06000280380249</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">1.04861223697662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04660201072693</t>
+    <t xml:space="preserve">1.04660189151764</t>
   </si>
   <si>
     <t xml:space="preserve">1.03990161418915</t>
@@ -1103,22 +1103,22 @@
     <t xml:space="preserve">1.04258179664612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01980018615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.015780210495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05196237564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06737327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06603300571442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02449083328247</t>
+    <t xml:space="preserve">1.01980042457581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01578032970428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05196225643158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06737315654755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06603312492371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02449059486389</t>
   </si>
   <si>
     <t xml:space="preserve">1.01846027374268</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">1.05665266513824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06134283542633</t>
+    <t xml:space="preserve">1.06134295463562</t>
   </si>
   <si>
     <t xml:space="preserve">1.07742381095886</t>
@@ -1139,61 +1139,61 @@
     <t xml:space="preserve">1.07943391799927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06938326358795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05933272838593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03856146335602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0268360376358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03588140010834</t>
+    <t xml:space="preserve">1.06938338279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05933260917664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03856158256531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02683579921722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03588151931763</t>
   </si>
   <si>
     <t xml:space="preserve">1.04191172122955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996349036693573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971222579479218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99534398317337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944421052932739</t>
+    <t xml:space="preserve">0.996349155902863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971222460269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995343923568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944420874118805</t>
   </si>
   <si>
     <t xml:space="preserve">0.953131496906281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941405713558197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959831953048706</t>
+    <t xml:space="preserve">0.941405773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959831833839417</t>
   </si>
   <si>
     <t xml:space="preserve">0.9464311003685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957821786403656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950451374053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936380445957184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967202425003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991323828697205</t>
+    <t xml:space="preserve">0.957821846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950451195240021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936380505561829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967202305793762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991323709487915</t>
   </si>
   <si>
     <t xml:space="preserve">0.975577831268311</t>
@@ -1202,22 +1202,22 @@
     <t xml:space="preserve">0.993333876132965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00003433227539</t>
+    <t xml:space="preserve">1.0000342130661</t>
   </si>
   <si>
     <t xml:space="preserve">1.00137436389923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991658866405487</t>
+    <t xml:space="preserve">0.991658687591553</t>
   </si>
   <si>
     <t xml:space="preserve">1.00673460960388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999364256858826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04023659229279</t>
+    <t xml:space="preserve">0.999364197254181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0402364730835</t>
   </si>
   <si>
     <t xml:space="preserve">1.04157662391663</t>
@@ -1229,64 +1229,64 @@
     <t xml:space="preserve">1.04961705207825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04995214939117</t>
+    <t xml:space="preserve">1.04995226860046</t>
   </si>
   <si>
     <t xml:space="preserve">1.06268298625946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07206344604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05832779407501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06335306167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07407367229462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08043897151947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08546423912048</t>
+    <t xml:space="preserve">1.07206356525421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05832755565643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06335318088531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07407379150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08043909072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08546435832977</t>
   </si>
   <si>
     <t xml:space="preserve">1.09048962593079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09484493732452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09819519519806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0985301733017</t>
+    <t xml:space="preserve">1.09484481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09819495677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09852993488312</t>
   </si>
   <si>
     <t xml:space="preserve">1.12198150157928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11762619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11729121208191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10724067687988</t>
+    <t xml:space="preserve">1.11762607097626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11729097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10724079608917</t>
   </si>
   <si>
     <t xml:space="preserve">1.10757565498352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12265145778656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13002192974091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10992097854614</t>
+    <t xml:space="preserve">1.12265169620514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13002181053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10992085933685</t>
   </si>
   <si>
     <t xml:space="preserve">1.11829626560211</t>
@@ -1295,16 +1295,16 @@
     <t xml:space="preserve">1.05732262134552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03387129306793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03895282745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05287516117096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04208552837372</t>
+    <t xml:space="preserve">1.03387105464935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0389529466629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05287528038025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04208528995514</t>
   </si>
   <si>
     <t xml:space="preserve">1.04730618000031</t>
@@ -1313,34 +1313,34 @@
     <t xml:space="preserve">1.02572667598724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00693142414093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980827152729034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998926162719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01076018810272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00484323501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02920734882355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00936806201935</t>
+    <t xml:space="preserve">1.00693154335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980827271938324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998926281929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01076030731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00484335422516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02920722961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00936794281006</t>
   </si>
   <si>
     <t xml:space="preserve">1.00658345222473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999622404575348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968993186950684</t>
+    <t xml:space="preserve">0.999622464179993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968993246555328</t>
   </si>
   <si>
     <t xml:space="preserve">1.01598107814789</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">1.02398645877838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03164374828339</t>
+    <t xml:space="preserve">1.0316436290741</t>
   </si>
   <si>
     <t xml:space="preserve">1.02851116657257</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">1.01980972290039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04382562637329</t>
+    <t xml:space="preserve">1.04382574558258</t>
   </si>
   <si>
     <t xml:space="preserve">1.04661011695862</t>
@@ -1367,25 +1367,25 @@
     <t xml:space="preserve">1.02363836765289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02537870407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00588750839233</t>
+    <t xml:space="preserve">1.02537858486176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00588738918304</t>
   </si>
   <si>
     <t xml:space="preserve">1.01250052452087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02120184898376</t>
+    <t xml:space="preserve">1.02120196819305</t>
   </si>
   <si>
     <t xml:space="preserve">1.02642273902893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03373217582703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01389288902283</t>
+    <t xml:space="preserve">1.03373205661774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01389265060425</t>
   </si>
   <si>
     <t xml:space="preserve">1.03860485553741</t>
@@ -1397,61 +1397,61 @@
     <t xml:space="preserve">1.06122851371765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07236647605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06018424034119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06262063980103</t>
+    <t xml:space="preserve">1.07236659526825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06018435955048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06262075901031</t>
   </si>
   <si>
     <t xml:space="preserve">1.05600762367249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07375860214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0671454668045</t>
+    <t xml:space="preserve">1.07375872135162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06714558601379</t>
   </si>
   <si>
     <t xml:space="preserve">1.0786315202713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09290194511414</t>
+    <t xml:space="preserve">1.09290182590485</t>
   </si>
   <si>
     <t xml:space="preserve">1.09429407119751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10160326957703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08420050144196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04835033416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06157672405243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07201826572418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07584702968597</t>
+    <t xml:space="preserve">1.10160338878632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08420038223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04835045337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06157660484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07201838493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07584714889526</t>
   </si>
   <si>
     <t xml:space="preserve">1.07132232189178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09394609928131</t>
+    <t xml:space="preserve">1.09394598007202</t>
   </si>
   <si>
     <t xml:space="preserve">1.08106791973114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09011745452881</t>
+    <t xml:space="preserve">1.09011733531952</t>
   </si>
   <si>
     <t xml:space="preserve">1.08246004581451</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">1.12387907505035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10473573207855</t>
+    <t xml:space="preserve">1.10473585128784</t>
   </si>
   <si>
     <t xml:space="preserve">1.10612809658051</t>
@@ -1496,52 +1496,52 @@
     <t xml:space="preserve">1.06540536880493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03338408470154</t>
+    <t xml:space="preserve">1.03338396549225</t>
   </si>
   <si>
     <t xml:space="preserve">1.04243338108063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02155005931854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03094732761383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04173731803894</t>
+    <t xml:space="preserve">1.02154994010925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03094744682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04173743724823</t>
   </si>
   <si>
     <t xml:space="preserve">1.05705189704895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0789794921875</t>
+    <t xml:space="preserve">1.07897937297821</t>
   </si>
   <si>
     <t xml:space="preserve">1.09220576286316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09116148948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08454835414886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08141601085663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0984708070755</t>
+    <t xml:space="preserve">1.09116160869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08454847335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08141589164734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09847068786621</t>
   </si>
   <si>
     <t xml:space="preserve">1.09603440761566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07619500160217</t>
+    <t xml:space="preserve">1.07619512081146</t>
   </si>
   <si>
     <t xml:space="preserve">1.07445478439331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05879211425781</t>
+    <t xml:space="preserve">1.0587922334671</t>
   </si>
   <si>
     <t xml:space="preserve">1.07758724689484</t>
@@ -1556,16 +1556,16 @@
     <t xml:space="preserve">1.03199172019958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04452192783356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04417371749878</t>
+    <t xml:space="preserve">1.04452168941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04417383670807</t>
   </si>
   <si>
     <t xml:space="preserve">1.05183112621307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03616845607758</t>
+    <t xml:space="preserve">1.03616833686829</t>
   </si>
   <si>
     <t xml:space="preserve">1.05844402313232</t>
@@ -1574,73 +1574,73 @@
     <t xml:space="preserve">1.03442811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00310289859772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9916170835495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00832378864288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01424098014832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01772129535675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01354467868805</t>
+    <t xml:space="preserve">1.00310301780701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991617023944855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00832390785217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01424062252045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01772117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01354455947876</t>
   </si>
   <si>
     <t xml:space="preserve">0.993705332279205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988136351108551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977346837520599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00553929805756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986047983169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989528715610504</t>
+    <t xml:space="preserve">0.98813658952713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97734659910202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00553941726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986047923564911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989528596401215</t>
   </si>
   <si>
     <t xml:space="preserve">0.992313206195831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98291540145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991964995861053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01319646835327</t>
+    <t xml:space="preserve">0.982915580272675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991965055465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01319658756256</t>
   </si>
   <si>
     <t xml:space="preserve">1.00414717197418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02050578594208</t>
+    <t xml:space="preserve">1.02050566673279</t>
   </si>
   <si>
     <t xml:space="preserve">1.0156329870224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03512418270111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0393009185791</t>
+    <t xml:space="preserve">1.0351243019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03930103778839</t>
   </si>
   <si>
     <t xml:space="preserve">1.05252707004547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05461537837982</t>
+    <t xml:space="preserve">1.05461549758911</t>
   </si>
   <si>
     <t xml:space="preserve">1.03721261024475</t>
@@ -1649,13 +1649,13 @@
     <t xml:space="preserve">1.02711892127991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03999698162079</t>
+    <t xml:space="preserve">1.03999710083008</t>
   </si>
   <si>
     <t xml:space="preserve">1.06610143184662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06088054180145</t>
+    <t xml:space="preserve">1.06088066101074</t>
   </si>
   <si>
     <t xml:space="preserve">1.04034519195557</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">1.03233981132507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04278171062469</t>
+    <t xml:space="preserve">1.04278147220612</t>
   </si>
   <si>
     <t xml:space="preserve">1.04347765445709</t>
@@ -1682,40 +1682,40 @@
     <t xml:space="preserve">1.12701141834259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1137855052948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1064760684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12318301200867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13118827342987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11448132991791</t>
+    <t xml:space="preserve">1.11378526687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10647594928741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12318289279938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13118815422058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1144814491272</t>
   </si>
   <si>
     <t xml:space="preserve">1.08872509002686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.094642162323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11622178554535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11831021308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13501679897308</t>
+    <t xml:space="preserve">1.09464204311371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11622166633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1183100938797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13501691818237</t>
   </si>
   <si>
     <t xml:space="preserve">1.13675713539124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13814949989319</t>
+    <t xml:space="preserve">1.1381493806839</t>
   </si>
   <si>
     <t xml:space="preserve">1.14302217960358</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">1.10403978824615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10891270637512</t>
+    <t xml:space="preserve">1.10891258716583</t>
   </si>
   <si>
     <t xml:space="preserve">1.09951496124268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10195124149323</t>
+    <t xml:space="preserve">1.10195136070251</t>
   </si>
   <si>
     <t xml:space="preserve">1.09916687011719</t>
@@ -1739,79 +1739,79 @@
     <t xml:space="preserve">1.0949901342392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10578012466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09185767173767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07793521881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08071970939636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08663690090179</t>
+    <t xml:space="preserve">1.10577988624573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09185779094696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07793533802032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08071994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08663666248322</t>
   </si>
   <si>
     <t xml:space="preserve">1.06227278709412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08280801773071</t>
+    <t xml:space="preserve">1.08280813694</t>
   </si>
   <si>
     <t xml:space="preserve">1.09742665290833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10021090507507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09777462482452</t>
+    <t xml:space="preserve">1.10021126270294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09777474403381</t>
   </si>
   <si>
     <t xml:space="preserve">1.10369169712067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11100089550018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10543191432953</t>
+    <t xml:space="preserve">1.11100077629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10543215274811</t>
   </si>
   <si>
     <t xml:space="preserve">1.08594059944153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09568619728088</t>
+    <t xml:space="preserve">1.09568631649017</t>
   </si>
   <si>
     <t xml:space="preserve">1.08907318115234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11726582050323</t>
+    <t xml:space="preserve">1.11726593971252</t>
   </si>
   <si>
     <t xml:space="preserve">1.12074661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10752022266388</t>
+    <t xml:space="preserve">1.10752046108246</t>
   </si>
   <si>
     <t xml:space="preserve">1.1103048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12179064750671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11935424804688</t>
+    <t xml:space="preserve">1.121790766716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11935436725616</t>
   </si>
   <si>
     <t xml:space="preserve">1.13571310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13536500930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13084006309509</t>
+    <t xml:space="preserve">1.13536477088928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13084018230438</t>
   </si>
   <si>
     <t xml:space="preserve">1.13223242759705</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">1.14754700660706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.063316822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05391943454742</t>
+    <t xml:space="preserve">1.06331706047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05391931533813</t>
   </si>
   <si>
     <t xml:space="preserve">1.04626214504242</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">1.05426740646362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04869854450226</t>
+    <t xml:space="preserve">1.04869842529297</t>
   </si>
   <si>
     <t xml:space="preserve">1.02433443069458</t>
@@ -1850,13 +1850,13 @@
     <t xml:space="preserve">0.997882068157196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.007279753685</t>
+    <t xml:space="preserve">1.00727963447571</t>
   </si>
   <si>
     <t xml:space="preserve">1.02015781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07654309272766</t>
+    <t xml:space="preserve">1.07654321193695</t>
   </si>
   <si>
     <t xml:space="preserve">1.08517646789551</t>
@@ -1868,10 +1868,10 @@
     <t xml:space="preserve">1.09647643566132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0662214756012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08116662502289</t>
+    <t xml:space="preserve">1.06622135639191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08116674423218</t>
   </si>
   <si>
     <t xml:space="preserve">1.07205379009247</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">1.06038916110992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05127596855164</t>
+    <t xml:space="preserve">1.05127608776093</t>
   </si>
   <si>
     <t xml:space="preserve">1.06403422355652</t>
@@ -1892,43 +1892,43 @@
     <t xml:space="preserve">1.08043766021729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0979346036911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09866344928741</t>
+    <t xml:space="preserve">1.09793448448181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0986635684967</t>
   </si>
   <si>
     <t xml:space="preserve">1.10449588298798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10048615932465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1023086309433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09574735164642</t>
+    <t xml:space="preserve">1.10048627853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10230875015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09574747085571</t>
   </si>
   <si>
     <t xml:space="preserve">1.09829914569855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13219940662384</t>
+    <t xml:space="preserve">1.13219952583313</t>
   </si>
   <si>
     <t xml:space="preserve">1.12563812732697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14021897315979</t>
+    <t xml:space="preserve">1.1402188539505</t>
   </si>
   <si>
     <t xml:space="preserve">1.14750933647156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1358448266983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11944139003754</t>
+    <t xml:space="preserve">1.13584458827972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11944127082825</t>
   </si>
   <si>
     <t xml:space="preserve">1.11543154716492</t>
@@ -1940,61 +1940,61 @@
     <t xml:space="preserve">1.11251533031464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11069285869598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13511562347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15006101131439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15188360214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14787375926971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15261256694794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16427731513977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17047417163849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17156767845154</t>
+    <t xml:space="preserve">1.11069273948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13511574268341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1500608921051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15188348293304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.147873878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15261244773865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16427719593048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1704740524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17156755924225</t>
   </si>
   <si>
     <t xml:space="preserve">1.17229676246643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17849349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17484831809998</t>
+    <t xml:space="preserve">1.17849361896515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17484843730927</t>
   </si>
   <si>
     <t xml:space="preserve">1.19161629676819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16318356990814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16609966754913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17995166778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18469047546387</t>
+    <t xml:space="preserve">1.16318368911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16609990596771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17995154857635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18469035625458</t>
   </si>
   <si>
     <t xml:space="preserve">1.18104517459869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17120313644409</t>
+    <t xml:space="preserve">1.17120325565338</t>
   </si>
   <si>
     <t xml:space="preserve">1.17375481128693</t>
@@ -2003,22 +2003,22 @@
     <t xml:space="preserve">1.14969646930695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15407073497772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17083847522736</t>
+    <t xml:space="preserve">1.15407061576843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17083859443665</t>
   </si>
   <si>
     <t xml:space="preserve">1.16209006309509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16682887077332</t>
+    <t xml:space="preserve">1.1668289899826</t>
   </si>
   <si>
     <t xml:space="preserve">1.16755795478821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17010951042175</t>
+    <t xml:space="preserve">1.17010962963104</t>
   </si>
   <si>
     <t xml:space="preserve">1.13183498382568</t>
@@ -2027,25 +2027,25 @@
     <t xml:space="preserve">1.12418007850647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12782537937164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14277052879333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16099667549133</t>
+    <t xml:space="preserve">1.12782526016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14277064800262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16099655628204</t>
   </si>
   <si>
     <t xml:space="preserve">1.14459323883057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15297722816467</t>
+    <t xml:space="preserve">1.15297710895538</t>
   </si>
   <si>
     <t xml:space="preserve">1.13985443115234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13475108146667</t>
+    <t xml:space="preserve">1.13475120067596</t>
   </si>
   <si>
     <t xml:space="preserve">1.16391277313232</t>
@@ -2054,13 +2054,13 @@
     <t xml:space="preserve">1.16938054561615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16573548316956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16500627994537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18833553791046</t>
+    <t xml:space="preserve">1.16573524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16500639915466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18833565711975</t>
   </si>
   <si>
     <t xml:space="preserve">1.20473897457123</t>
@@ -2090,13 +2090,13 @@
     <t xml:space="preserve">1.19599044322968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18979370594025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22551679611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21567463874817</t>
+    <t xml:space="preserve">1.18979358673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22551667690277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21567475795746</t>
   </si>
   <si>
     <t xml:space="preserve">1.22770380973816</t>
@@ -2105,46 +2105,46 @@
     <t xml:space="preserve">1.23207807540894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21421647071838</t>
+    <t xml:space="preserve">1.21421670913696</t>
   </si>
   <si>
     <t xml:space="preserve">1.21166479587555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23134899139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23025560379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2160392999649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21931993961334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23791027069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23462963104248</t>
+    <t xml:space="preserve">1.23134911060333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23025548458099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21603918075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21931982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2379105091095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23462986946106</t>
   </si>
   <si>
     <t xml:space="preserve">1.22806835174561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21640360355377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2218713760376</t>
+    <t xml:space="preserve">1.21640372276306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22187161445618</t>
   </si>
   <si>
     <t xml:space="preserve">1.22114229202271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22405862808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23061990737915</t>
+    <t xml:space="preserve">1.22405874729156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23062002658844</t>
   </si>
   <si>
     <t xml:space="preserve">1.22843277454376</t>
@@ -2159,16 +2159,16 @@
     <t xml:space="preserve">1.22624576091766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27363324165344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27691400051117</t>
+    <t xml:space="preserve">1.27363336086273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27691411972046</t>
   </si>
   <si>
     <t xml:space="preserve">1.31154346466064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3133659362793</t>
+    <t xml:space="preserve">1.31336605548859</t>
   </si>
   <si>
     <t xml:space="preserve">1.30972075462341</t>
@@ -2177,13 +2177,13 @@
     <t xml:space="preserve">1.30826270580292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31591761112213</t>
+    <t xml:space="preserve">1.31591749191284</t>
   </si>
   <si>
     <t xml:space="preserve">1.29331743717194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31518876552582</t>
+    <t xml:space="preserve">1.31518852710724</t>
   </si>
   <si>
     <t xml:space="preserve">1.31445956230164</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">1.30862724781036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29732704162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27873647212982</t>
+    <t xml:space="preserve">1.29732716083527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27873659133911</t>
   </si>
   <si>
     <t xml:space="preserve">1.288578748703</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">1.27509129047394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26452016830444</t>
+    <t xml:space="preserve">1.26452028751373</t>
   </si>
   <si>
     <t xml:space="preserve">1.24884593486786</t>
@@ -2219,28 +2219,28 @@
     <t xml:space="preserve">1.24665880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25249123573303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2452005147934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24483621120453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19052267074585</t>
+    <t xml:space="preserve">1.25249111652374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24520063400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24483609199524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19052278995514</t>
   </si>
   <si>
     <t xml:space="preserve">1.19635510444641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1985422372818</t>
+    <t xml:space="preserve">1.19854235649109</t>
   </si>
   <si>
     <t xml:space="preserve">1.19343888759613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18068063259125</t>
+    <t xml:space="preserve">1.18068075180054</t>
   </si>
   <si>
     <t xml:space="preserve">1.20218741893768</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">1.18906462192535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19270992279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20656156539917</t>
+    <t xml:space="preserve">1.19270980358124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20656168460846</t>
   </si>
   <si>
     <t xml:space="preserve">1.20729076862335</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">1.22515213489532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2415554523468</t>
+    <t xml:space="preserve">1.24155557155609</t>
   </si>
   <si>
     <t xml:space="preserve">1.23353612422943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21895527839661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21275854110718</t>
+    <t xml:space="preserve">1.2189553976059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2127583026886</t>
   </si>
   <si>
     <t xml:space="preserve">1.2083842754364</t>
@@ -2279,43 +2279,43 @@
     <t xml:space="preserve">1.25504267215729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25066864490509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25941705703735</t>
+    <t xml:space="preserve">1.25066840648651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25941693782806</t>
   </si>
   <si>
     <t xml:space="preserve">1.25650084018707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26852989196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2998788356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30315935611725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29368185997009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29222393035889</t>
+    <t xml:space="preserve">1.26853001117706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29987871646881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30315947532654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29368197917938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29222369194031</t>
   </si>
   <si>
     <t xml:space="preserve">1.30607557296753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3520051240921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34544372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33414375782013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31409502029419</t>
+    <t xml:space="preserve">1.35200524330139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34544384479523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33414363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31409513950348</t>
   </si>
   <si>
     <t xml:space="preserve">1.3224790096283</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">1.34580826759338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33159208297729</t>
+    <t xml:space="preserve">1.33159196376801</t>
   </si>
   <si>
     <t xml:space="preserve">1.33013391494751</t>
@@ -2336,13 +2336,13 @@
     <t xml:space="preserve">1.34981799125671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34398567676544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3414341211319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34945344924927</t>
+    <t xml:space="preserve">1.34398579597473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34143400192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34945356845856</t>
   </si>
   <si>
     <t xml:space="preserve">1.35893094539642</t>
@@ -2351,16 +2351,16 @@
     <t xml:space="preserve">1.36986649036407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38226044178009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36038911342621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34908902645111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26524937152863</t>
+    <t xml:space="preserve">1.3822603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3603892326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34908890724182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26524949073792</t>
   </si>
   <si>
     <t xml:space="preserve">1.25613629817963</t>
@@ -2372,19 +2372,19 @@
     <t xml:space="preserve">1.15589320659637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19708406925201</t>
+    <t xml:space="preserve">1.19708395004272</t>
   </si>
   <si>
     <t xml:space="preserve">1.11579608917236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996233522891998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924787640571594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905467987060547</t>
+    <t xml:space="preserve">0.996233582496643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924787521362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905468046665192</t>
   </si>
   <si>
     <t xml:space="preserve">0.733049929141998</t>
@@ -2393,16 +2393,16 @@
     <t xml:space="preserve">0.772782683372498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.750546991825104</t>
+    <t xml:space="preserve">0.750546932220459</t>
   </si>
   <si>
     <t xml:space="preserve">0.775334358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.751276016235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754556715488434</t>
+    <t xml:space="preserve">0.751276075839996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754556596279144</t>
   </si>
   <si>
     <t xml:space="preserve">0.741433918476105</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">0.729040205478668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786270022392273</t>
+    <t xml:space="preserve">0.786269962787628</t>
   </si>
   <si>
     <t xml:space="preserve">0.797205567359924</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">0.793195843696594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778250455856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824544548988342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826002538204193</t>
+    <t xml:space="preserve">0.778250515460968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824544429779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826002597808838</t>
   </si>
   <si>
     <t xml:space="preserve">0.816160500049591</t>
@@ -2438,91 +2438,91 @@
     <t xml:space="preserve">0.836209118366241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869016051292419</t>
+    <t xml:space="preserve">0.86901593208313</t>
   </si>
   <si>
     <t xml:space="preserve">0.869745016098022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855164110660553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876670956611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889429092407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885783970355988</t>
+    <t xml:space="preserve">0.855164170265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876670837402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889429152011871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885783910751343</t>
   </si>
   <si>
     <t xml:space="preserve">0.897448539733887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910935878753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91166490316391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.883961260318756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888335406780243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879587054252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890158176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906926035881042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901458323001862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899635672569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905832529067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872296631336212</t>
+    <t xml:space="preserve">0.910935819149017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91166478395462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883961200714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888335585594177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879587113857269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890158116817474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906926155090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901458263397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899635553359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905832409858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872296571731567</t>
   </si>
   <si>
     <t xml:space="preserve">0.879951596260071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878128886222839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882138669490814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877764403820038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914581120014191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93426513671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911300361156464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944332540035248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902750790119171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914020597934723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910522997379303</t>
+    <t xml:space="preserve">0.878128945827484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882138788700104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877764463424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914581000804901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93426501750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911300301551819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944332480430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902750670909882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914020538330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910522937774658</t>
   </si>
   <si>
     <t xml:space="preserve">0.912854731082916</t>
@@ -2531,28 +2531,28 @@
     <t xml:space="preserve">0.946275532245636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971146941184998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950550377368927</t>
+    <t xml:space="preserve">0.971146881580353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950550258159637</t>
   </si>
   <si>
     <t xml:space="preserve">0.971535444259644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969592392444611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981639444828033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00573348999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04265177249908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04342913627625</t>
+    <t xml:space="preserve">0.969592332839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981639504432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00573360919952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04265189170837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04342901706696</t>
   </si>
   <si>
     <t xml:space="preserve">1.03060472011566</t>
@@ -2561,22 +2561,22 @@
     <t xml:space="preserve">1.05236721038818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02710723876953</t>
+    <t xml:space="preserve">1.02710735797882</t>
   </si>
   <si>
     <t xml:space="preserve">1.01195132732391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960265755653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956379532814026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978141844272614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01156282424927</t>
+    <t xml:space="preserve">0.960265576839447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956379592418671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978141903877258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01156270503998</t>
   </si>
   <si>
     <t xml:space="preserve">1.01778054237366</t>
@@ -2585,52 +2585,52 @@
     <t xml:space="preserve">1.00961971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01933491230011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01467156410217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972312688827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963763236999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977364718914032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979696393013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984359741210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999904274940491</t>
+    <t xml:space="preserve">1.0193350315094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01467168331146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972312748432159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963763177394867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977364778518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979696333408356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984359860420227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99990439414978</t>
   </si>
   <si>
     <t xml:space="preserve">0.996795475482941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993686497211456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983193874359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982805371284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958322584629059</t>
+    <t xml:space="preserve">0.993686378002167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983194053173065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98280531167984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958322703838348</t>
   </si>
   <si>
     <t xml:space="preserve">0.961431443691254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960654258728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973867237567902</t>
+    <t xml:space="preserve">0.960654199123383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973867177963257</t>
   </si>
   <si>
     <t xml:space="preserve">0.973089993000031</t>
@@ -2642,16 +2642,16 @@
     <t xml:space="preserve">0.987857341766357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985525667667389</t>
+    <t xml:space="preserve">0.985525608062744</t>
   </si>
   <si>
     <t xml:space="preserve">0.949773132801056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954436480998993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970758140087128</t>
+    <t xml:space="preserve">0.954436421394348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970758199691772</t>
   </si>
   <si>
     <t xml:space="preserve">0.92878794670105</t>
@@ -2660,16 +2660,16 @@
     <t xml:space="preserve">0.943166613578796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95599091053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959877133369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953659236431122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965317666530609</t>
+    <t xml:space="preserve">0.955990970134735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959877014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953659296035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965317726135254</t>
   </si>
   <si>
     <t xml:space="preserve">0.982028067111969</t>
@@ -2678,10 +2678,10 @@
     <t xml:space="preserve">1.01739192008972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00612223148346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994852304458618</t>
+    <t xml:space="preserve">1.00612211227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994852244853973</t>
   </si>
   <si>
     <t xml:space="preserve">0.979307770729065</t>
@@ -2690,19 +2690,19 @@
     <t xml:space="preserve">0.989411771297455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987080097198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964929103851318</t>
+    <t xml:space="preserve">0.987079977989197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964929163455963</t>
   </si>
   <si>
     <t xml:space="preserve">0.96259731054306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958711206912994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96609491109848</t>
+    <t xml:space="preserve">0.958711266517639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966094970703125</t>
   </si>
   <si>
     <t xml:space="preserve">0.951327443122864</t>
@@ -2711,43 +2711,43 @@
     <t xml:space="preserve">0.954047858715057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975032985210419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968037962913513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937726140022278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946664154529572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938503265380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942000806331635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933451294898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971924066543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94899594783783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953270614147186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9458869099617</t>
+    <t xml:space="preserve">0.975033164024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968037903308868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937726080417633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946664273738861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938503324985504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942000687122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933451175689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971924185752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94899582862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953270554542542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945886969566345</t>
   </si>
   <si>
     <t xml:space="preserve">0.929565131664276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931119561195374</t>
+    <t xml:space="preserve">0.931119620800018</t>
   </si>
   <si>
     <t xml:space="preserve">0.900807678699493</t>
@@ -2756,88 +2756,88 @@
     <t xml:space="preserve">0.903528034687042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904693841934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898864567279816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878656625747681</t>
+    <t xml:space="preserve">0.904693961143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89886462688446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878656685352325</t>
   </si>
   <si>
     <t xml:space="preserve">0.886428952217102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.901584923267365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886040329933167</t>
+    <t xml:space="preserve">0.90158486366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886040270328522</t>
   </si>
   <si>
     <t xml:space="preserve">0.840961158275604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830079972743988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84834486246109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860780298709869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872050106525421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89847606420517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892646729946136</t>
+    <t xml:space="preserve">0.830079913139343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848344802856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860780358314514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872050225734711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898476004600525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892646670341492</t>
   </si>
   <si>
     <t xml:space="preserve">0.88137686252594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.942778170108795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93928050994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955213665962219</t>
+    <t xml:space="preserve">0.94277811050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939280569553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955213725566864</t>
   </si>
   <si>
     <t xml:space="preserve">0.95249330997467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947441458702087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952104806900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959488391876221</t>
+    <t xml:space="preserve">0.947441399097443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95210474729538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959488451480865</t>
   </si>
   <si>
     <t xml:space="preserve">0.97619891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01700329780579</t>
+    <t xml:space="preserve">1.01700341701508</t>
   </si>
   <si>
     <t xml:space="preserve">1.02205526828766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993297874927521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982416689395905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975421667098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976587533950806</t>
+    <t xml:space="preserve">0.993297934532166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982416749000549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975421726703644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976587474346161</t>
   </si>
   <si>
     <t xml:space="preserve">0.997183978557587</t>
@@ -2846,28 +2846,28 @@
     <t xml:space="preserve">0.990966200828552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988245844841003</t>
+    <t xml:space="preserve">0.988245904445648</t>
   </si>
   <si>
     <t xml:space="preserve">0.984748363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995629549026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954825222492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00651073455811</t>
+    <t xml:space="preserve">0.995629668235779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954825103282928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0065108537674</t>
   </si>
   <si>
     <t xml:space="preserve">1.01583755016327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0138943195343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03449082374573</t>
+    <t xml:space="preserve">1.01389443874359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03449094295502</t>
   </si>
   <si>
     <t xml:space="preserve">1.02399837970734</t>
@@ -2894,31 +2894,31 @@
     <t xml:space="preserve">1.02050077915192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03099358081818</t>
+    <t xml:space="preserve">1.03099346160889</t>
   </si>
   <si>
     <t xml:space="preserve">1.06596863269806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0729638338089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04653811454773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0589736700058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0535329580307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06169390678406</t>
+    <t xml:space="preserve">1.07296371459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04653799533844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05897355079651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05353307723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06169402599335</t>
   </si>
   <si>
     <t xml:space="preserve">1.0449835062027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10871636867523</t>
+    <t xml:space="preserve">1.10871624946594</t>
   </si>
   <si>
     <t xml:space="preserve">1.13630795478821</t>
@@ -2927,13 +2927,13 @@
     <t xml:space="preserve">1.15418422222137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12853574752808</t>
+    <t xml:space="preserve">1.12853562831879</t>
   </si>
   <si>
     <t xml:space="preserve">1.1382509469986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14252579212189</t>
+    <t xml:space="preserve">1.1425256729126</t>
   </si>
   <si>
     <t xml:space="preserve">1.17516922950745</t>
@@ -2942,16 +2942,16 @@
     <t xml:space="preserve">1.16195642948151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13863956928253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12154054641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13475346565247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12698113918304</t>
+    <t xml:space="preserve">1.13863968849182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12154066562653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13475358486176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12698125839233</t>
   </si>
   <si>
     <t xml:space="preserve">1.11415696144104</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">1.11221385002136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0931715965271</t>
+    <t xml:space="preserve">1.09317171573639</t>
   </si>
   <si>
     <t xml:space="preserve">1.08384501934052</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">1.11493408679962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10716187953949</t>
+    <t xml:space="preserve">1.1071617603302</t>
   </si>
   <si>
     <t xml:space="preserve">1.07918155193329</t>
@@ -2987,34 +2987,34 @@
     <t xml:space="preserve">1.1083277463913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13086748123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15262961387634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14874351024628</t>
+    <t xml:space="preserve">1.1308673620224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15262973308563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14874362945557</t>
   </si>
   <si>
     <t xml:space="preserve">1.15496134757996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1631224155426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14563465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15301835536957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14641189575195</t>
+    <t xml:space="preserve">1.16312229633331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14563453197479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15301847457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14641201496124</t>
   </si>
   <si>
     <t xml:space="preserve">1.17089450359344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18954813480377</t>
+    <t xml:space="preserve">1.18954801559448</t>
   </si>
   <si>
     <t xml:space="preserve">1.2047039270401</t>
@@ -3026,10 +3026,10 @@
     <t xml:space="preserve">1.21558511257172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2175281047821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20625853538513</t>
+    <t xml:space="preserve">1.21752822399139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20625841617584</t>
   </si>
   <si>
     <t xml:space="preserve">1.20392680168152</t>
@@ -3044,16 +3044,16 @@
     <t xml:space="preserve">1.20975589752197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19809746742249</t>
+    <t xml:space="preserve">1.19809758663177</t>
   </si>
   <si>
     <t xml:space="preserve">1.21286487579346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21597385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2132533788681</t>
+    <t xml:space="preserve">1.21597373485565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21325349807739</t>
   </si>
   <si>
     <t xml:space="preserve">1.20431530475616</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">1.22685503959656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21403074264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2357931137085</t>
+    <t xml:space="preserve">1.21403086185455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23579323291779</t>
   </si>
   <si>
     <t xml:space="preserve">1.23812484741211</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">1.24278819561005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26105296611786</t>
+    <t xml:space="preserve">1.26105308532715</t>
   </si>
   <si>
     <t xml:space="preserve">1.26455056667328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27582049369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26066434383392</t>
+    <t xml:space="preserve">1.27582037448883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26066446304321</t>
   </si>
   <si>
     <t xml:space="preserve">1.2649393081665</t>
@@ -3101,22 +3101,22 @@
     <t xml:space="preserve">1.3045779466629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31779086589813</t>
+    <t xml:space="preserve">1.31779074668884</t>
   </si>
   <si>
     <t xml:space="preserve">1.29291939735413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29874873161316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31740212440491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33061492443085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34693682193756</t>
+    <t xml:space="preserve">1.29874861240387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3174022436142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33061504364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34693670272827</t>
   </si>
   <si>
     <t xml:space="preserve">1.34382772445679</t>
@@ -3128,16 +3128,16 @@
     <t xml:space="preserve">1.35121142864227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37258529663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40067207813263</t>
+    <t xml:space="preserve">1.37258541584015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40067195892334</t>
   </si>
   <si>
     <t xml:space="preserve">1.37502765655518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38194763660431</t>
+    <t xml:space="preserve">1.38194751739502</t>
   </si>
   <si>
     <t xml:space="preserve">1.37787699699402</t>
@@ -3152,19 +3152,19 @@
     <t xml:space="preserve">1.38438987731934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39456617832184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38886749744415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41044116020203</t>
+    <t xml:space="preserve">1.39456629753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38886737823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41044127941132</t>
   </si>
   <si>
     <t xml:space="preserve">1.42306005954742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43323636054993</t>
+    <t xml:space="preserve">1.43323624134064</t>
   </si>
   <si>
     <t xml:space="preserve">1.45847368240356</t>
@@ -3179,10 +3179,10 @@
     <t xml:space="preserve">1.4491114616394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44951868057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45725250244141</t>
+    <t xml:space="preserve">1.44951856136322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4572526216507</t>
   </si>
   <si>
     <t xml:space="preserve">1.45765960216522</t>
@@ -3197,19 +3197,19 @@
     <t xml:space="preserve">1.4430056810379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44422674179077</t>
+    <t xml:space="preserve">1.44422686100006</t>
   </si>
   <si>
     <t xml:space="preserve">1.42713057994843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41858243942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40352141857147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41288363933563</t>
+    <t xml:space="preserve">1.41858232021332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40352153778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41288375854492</t>
   </si>
   <si>
     <t xml:space="preserve">1.41695427894592</t>
@@ -3224,10 +3224,10 @@
     <t xml:space="preserve">1.43527162075043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3795051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38072645664215</t>
+    <t xml:space="preserve">1.37950527667999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38072633743286</t>
   </si>
   <si>
     <t xml:space="preserve">1.39945089817047</t>
@@ -3239,46 +3239,46 @@
     <t xml:space="preserve">1.40392851829529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40148615837097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34734797477722</t>
+    <t xml:space="preserve">1.40148627758026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34734785556793</t>
   </si>
   <si>
     <t xml:space="preserve">1.3591525554657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38316881656647</t>
+    <t xml:space="preserve">1.38316869735718</t>
   </si>
   <si>
     <t xml:space="preserve">1.395787358284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45114684104919</t>
+    <t xml:space="preserve">1.4511467218399</t>
   </si>
   <si>
     <t xml:space="preserve">1.47719812393188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47801232337952</t>
+    <t xml:space="preserve">1.47801244258881</t>
   </si>
   <si>
     <t xml:space="preserve">1.47394180297852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47068524360657</t>
+    <t xml:space="preserve">1.47068536281586</t>
   </si>
   <si>
     <t xml:space="preserve">1.47923338413239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46824300289154</t>
+    <t xml:space="preserve">1.46824312210083</t>
   </si>
   <si>
     <t xml:space="preserve">1.47964036464691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49348020553589</t>
+    <t xml:space="preserve">1.49348032474518</t>
   </si>
   <si>
     <t xml:space="preserve">1.50691306591034</t>
@@ -3287,16 +3287,16 @@
     <t xml:space="preserve">1.52360236644745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53866338729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54069852828979</t>
+    <t xml:space="preserve">1.53866326808929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54069864749908</t>
   </si>
   <si>
     <t xml:space="preserve">1.55006086826324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58262515068054</t>
+    <t xml:space="preserve">1.58262503147125</t>
   </si>
   <si>
     <t xml:space="preserve">1.58669567108154</t>
@@ -3308,10 +3308,10 @@
     <t xml:space="preserve">1.5838463306427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55494546890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53215038776398</t>
+    <t xml:space="preserve">1.5549453496933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53215026855469</t>
   </si>
   <si>
     <t xml:space="preserve">1.52726578712463</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">1.50650596618652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49755084514618</t>
+    <t xml:space="preserve">1.49755072593689</t>
   </si>
   <si>
     <t xml:space="preserve">1.522381067276</t>
@@ -3347,16 +3347,16 @@
     <t xml:space="preserve">1.5162752866745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48615336418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48940968513489</t>
+    <t xml:space="preserve">1.48615348339081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48940980434418</t>
   </si>
   <si>
     <t xml:space="preserve">1.49063086509705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42794454097748</t>
+    <t xml:space="preserve">1.42794466018677</t>
   </si>
   <si>
     <t xml:space="preserve">1.45155382156372</t>
@@ -3371,10 +3371,10 @@
     <t xml:space="preserve">1.4837110042572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47882628440857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48411822319031</t>
+    <t xml:space="preserve">1.47882640361786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48411810398102</t>
   </si>
   <si>
     <t xml:space="preserve">1.45643842220306</t>
@@ -3383,31 +3383,31 @@
     <t xml:space="preserve">1.45562422275543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43812108039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44544792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44015634059906</t>
+    <t xml:space="preserve">1.43812096118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44544816017151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44015622138977</t>
   </si>
   <si>
     <t xml:space="preserve">1.45684540271759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48737442493439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48533916473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50406384468079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46417248249054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44504082202911</t>
+    <t xml:space="preserve">1.48737454414368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48533928394318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50406360626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46417236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4450409412384</t>
   </si>
   <si>
     <t xml:space="preserve">1.47475576400757</t>
@@ -3419,46 +3419,46 @@
     <t xml:space="preserve">1.50894844532013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50202858448029</t>
+    <t xml:space="preserve">1.502028465271</t>
   </si>
   <si>
     <t xml:space="preserve">1.48696756362915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50365674495697</t>
+    <t xml:space="preserve">1.50365662574768</t>
   </si>
   <si>
     <t xml:space="preserve">1.52970802783966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53662812709808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57407701015472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5569806098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55779480934143</t>
+    <t xml:space="preserve">1.53662800788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57407712936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55698072910309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55779469013214</t>
   </si>
   <si>
     <t xml:space="preserve">1.50732016563416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48004746437073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49022376537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49225902557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51016938686371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4776052236557</t>
+    <t xml:space="preserve">1.48004758358002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49022388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49225914478302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.510169506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47760534286499</t>
   </si>
   <si>
     <t xml:space="preserve">1.50040030479431</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">1.51953184604645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51546132564545</t>
+    <t xml:space="preserve">1.51546108722687</t>
   </si>
   <si>
     <t xml:space="preserve">1.3921240568161</t>
@@ -3482,28 +3482,28 @@
     <t xml:space="preserve">1.40596377849579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39538025856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40637063980103</t>
+    <t xml:space="preserve">1.39538037776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40637075901031</t>
   </si>
   <si>
     <t xml:space="preserve">1.45196080207825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4307941198349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45806670188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45440316200256</t>
+    <t xml:space="preserve">1.43079400062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45806658267975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45440304279327</t>
   </si>
   <si>
     <t xml:space="preserve">1.45399618148804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42835164070129</t>
+    <t xml:space="preserve">1.42835175991058</t>
   </si>
   <si>
     <t xml:space="preserve">1.39130973815918</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">1.32699537277222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34531271457672</t>
+    <t xml:space="preserve">1.34531283378601</t>
   </si>
   <si>
     <t xml:space="preserve">1.34775519371033</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">1.36810779571533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37177109718323</t>
+    <t xml:space="preserve">1.37177121639252</t>
   </si>
   <si>
     <t xml:space="preserve">1.39741563796997</t>
@@ -3536,22 +3536,22 @@
     <t xml:space="preserve">1.35548901557922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35955953598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35833847522736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37462055683136</t>
+    <t xml:space="preserve">1.35955965518951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35833835601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37462067604065</t>
   </si>
   <si>
     <t xml:space="preserve">1.36770057678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35589611530304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35263967514038</t>
+    <t xml:space="preserve">1.35589623451233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35263979434967</t>
   </si>
   <si>
     <t xml:space="preserve">1.33310115337372</t>
@@ -3560,28 +3560,28 @@
     <t xml:space="preserve">1.32414591312408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3530467748642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34164929389954</t>
+    <t xml:space="preserve">1.35304665565491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34164917469025</t>
   </si>
   <si>
     <t xml:space="preserve">1.30664253234863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3326940536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36525857448578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41532599925995</t>
+    <t xml:space="preserve">1.33269393444061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3652583360672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41532588005066</t>
   </si>
   <si>
     <t xml:space="preserve">1.37380647659302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36729371547699</t>
+    <t xml:space="preserve">1.3672935962677</t>
   </si>
   <si>
     <t xml:space="preserve">1.37909817695618</t>
@@ -3596,13 +3596,13 @@
     <t xml:space="preserve">1.33513641357422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30949199199677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28262639045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30094397068024</t>
+    <t xml:space="preserve">1.30949211120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28262650966644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30094385147095</t>
   </si>
   <si>
     <t xml:space="preserve">1.30542147159576</t>
@@ -3617,52 +3617,52 @@
     <t xml:space="preserve">1.28913938999176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28425478935242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28181231021881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27652072906494</t>
+    <t xml:space="preserve">1.28425455093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28181219100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27652060985565</t>
   </si>
   <si>
     <t xml:space="preserve">1.25413274765015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22889530658722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25046932697296</t>
+    <t xml:space="preserve">1.22889542579651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25046920776367</t>
   </si>
   <si>
     <t xml:space="preserve">1.22482478618622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28140544891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30012989044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2549467086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2284882068634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19918048381805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18249130249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20243680477142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25616788864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24639868736267</t>
+    <t xml:space="preserve">1.281405210495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3001297712326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25494682788849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22848832607269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19918036460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18249106407166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20243692398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25616800785065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24639880657196</t>
   </si>
   <si>
     <t xml:space="preserve">1.2447704076767</t>
@@ -3671,13 +3671,13 @@
     <t xml:space="preserve">1.23093068599701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22238254547119</t>
+    <t xml:space="preserve">1.22238266468048</t>
   </si>
   <si>
     <t xml:space="preserve">1.22116136550903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21464860439301</t>
+    <t xml:space="preserve">1.21464848518372</t>
   </si>
   <si>
     <t xml:space="preserve">1.23785054683685</t>
@@ -3692,52 +3692,52 @@
     <t xml:space="preserve">1.22808122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23540830612183</t>
+    <t xml:space="preserve">1.23540818691254</t>
   </si>
   <si>
     <t xml:space="preserve">1.25698208808899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27489233016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25779604911804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2655303478241</t>
+    <t xml:space="preserve">1.27489244937897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25779616832733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26553010940552</t>
   </si>
   <si>
     <t xml:space="preserve">1.25942444801331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28751111030579</t>
+    <t xml:space="preserve">1.28751122951508</t>
   </si>
   <si>
     <t xml:space="preserve">1.29768741130829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2980945110321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33554339408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36281597614288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35223269462585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35711741447449</t>
+    <t xml:space="preserve">1.29809439182281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33554327487946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36281609535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35223257541656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3571172952652</t>
   </si>
   <si>
     <t xml:space="preserve">1.34856915473938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34409153461456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36485135555267</t>
+    <t xml:space="preserve">1.34409165382385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36485123634338</t>
   </si>
   <si>
     <t xml:space="preserve">1.33961391448975</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">1.32455289363861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33432245254517</t>
+    <t xml:space="preserve">1.33432233333588</t>
   </si>
   <si>
     <t xml:space="preserve">1.33106589317322</t>
@@ -3758,19 +3758,19 @@
     <t xml:space="preserve">1.34002101421356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32862341403961</t>
+    <t xml:space="preserve">1.3286235332489</t>
   </si>
   <si>
     <t xml:space="preserve">1.31193435192108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3164119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35019743442535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34653389453888</t>
+    <t xml:space="preserve">1.31641185283661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35019731521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34653401374817</t>
   </si>
   <si>
     <t xml:space="preserve">1.34327745437622</t>
@@ -3779,10 +3779,10 @@
     <t xml:space="preserve">1.38561105728149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33147299289703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36037373542786</t>
+    <t xml:space="preserve">1.33147275447845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36037361621857</t>
   </si>
   <si>
     <t xml:space="preserve">1.34205627441406</t>
@@ -3794,10 +3794,10 @@
     <t xml:space="preserve">1.36872255802155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.378622174263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38507831096649</t>
+    <t xml:space="preserve">1.37862205505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38507843017578</t>
   </si>
   <si>
     <t xml:space="preserve">1.3631272315979</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">1.35796225070953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34504961967468</t>
+    <t xml:space="preserve">1.34504973888397</t>
   </si>
   <si>
     <t xml:space="preserve">1.32998502254486</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">1.270587682724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.187087059021</t>
+    <t xml:space="preserve">1.18708693981171</t>
   </si>
   <si>
     <t xml:space="preserve">1.14921045303345</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">1.15050172805786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11563801765442</t>
+    <t xml:space="preserve">1.11563789844513</t>
   </si>
   <si>
     <t xml:space="preserve">1.15437543392181</t>
@@ -3851,19 +3851,19 @@
     <t xml:space="preserve">1.091104388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06570982933044</t>
+    <t xml:space="preserve">1.06570971012115</t>
   </si>
   <si>
     <t xml:space="preserve">1.03945434093475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05581021308899</t>
+    <t xml:space="preserve">1.05581033229828</t>
   </si>
   <si>
     <t xml:space="preserve">1.10143435001373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08593940734863</t>
+    <t xml:space="preserve">1.08593928813934</t>
   </si>
   <si>
     <t xml:space="preserve">1.09540855884552</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">1.0510755777359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07130527496338</t>
+    <t xml:space="preserve">1.07130515575409</t>
   </si>
   <si>
     <t xml:space="preserve">1.06915318965912</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">1.03601109981537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04074573516846</t>
+    <t xml:space="preserve">1.04074561595917</t>
   </si>
   <si>
     <t xml:space="preserve">1.05451893806458</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">1.02955484390259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0588231086731</t>
+    <t xml:space="preserve">1.05882322788239</t>
   </si>
   <si>
     <t xml:space="preserve">1.08120477199554</t>
@@ -3932,13 +3932,13 @@
     <t xml:space="preserve">1.04978430271149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07474839687347</t>
+    <t xml:space="preserve">1.07474851608276</t>
   </si>
   <si>
     <t xml:space="preserve">1.09024357795715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06829226016998</t>
+    <t xml:space="preserve">1.06829237937927</t>
   </si>
   <si>
     <t xml:space="preserve">1.08636963367462</t>
@@ -3959,16 +3959,16 @@
     <t xml:space="preserve">1.10100388526917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10272562503815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08292639255524</t>
+    <t xml:space="preserve">1.10272550582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08292651176453</t>
   </si>
   <si>
     <t xml:space="preserve">1.06097519397736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06355762481689</t>
+    <t xml:space="preserve">1.06355774402618</t>
   </si>
   <si>
     <t xml:space="preserve">1.05839276313782</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">1.01707279682159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996843218803406</t>
+    <t xml:space="preserve">0.996843278408051</t>
   </si>
   <si>
     <t xml:space="preserve">0.999425709247589</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">0.963701248168945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946915030479431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968435764312744</t>
+    <t xml:space="preserve">0.946915090084076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968435704708099</t>
   </si>
   <si>
     <t xml:space="preserve">0.945623755455017</t>
@@ -4001,22 +4001,22 @@
     <t xml:space="preserve">0.939167439937592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920229136943817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965422868728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975322425365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952510356903076</t>
+    <t xml:space="preserve">0.920229196548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965422928333282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975322484970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952510416507721</t>
   </si>
   <si>
     <t xml:space="preserve">0.92625492811203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930128812789917</t>
+    <t xml:space="preserve">0.930128753185272</t>
   </si>
   <si>
     <t xml:space="preserve">0.913342595100403</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">0.921950876712799</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923242092132568</t>
+    <t xml:space="preserve">0.923242032527924</t>
   </si>
   <si>
     <t xml:space="preserve">0.912051260471344</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">0.888808846473694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852567851543427</t>
+    <t xml:space="preserve">0.852567791938782</t>
   </si>
   <si>
     <t xml:space="preserve">0.86298394203186</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">0.85377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860659658908844</t>
+    <t xml:space="preserve">0.860659718513489</t>
   </si>
   <si>
     <t xml:space="preserve">0.879339694976807</t>
@@ -4073,10 +4073,10 @@
     <t xml:space="preserve">0.820200502872467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825881958007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863844633102417</t>
+    <t xml:space="preserve">0.825882017612457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863844692707062</t>
   </si>
   <si>
     <t xml:space="preserve">0.883643805980682</t>
@@ -4097,7 +4097,7 @@
     <t xml:space="preserve">0.948206186294556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982209146022797</t>
+    <t xml:space="preserve">0.982209086418152</t>
   </si>
   <si>
     <t xml:space="preserve">0.971018373966217</t>
@@ -4106,13 +4106,13 @@
     <t xml:space="preserve">0.965853273868561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966714203357697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966283619403839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955092906951904</t>
+    <t xml:space="preserve">0.966714143753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966283679008484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955092966556549</t>
   </si>
   <si>
     <t xml:space="preserve">0.972309470176697</t>
@@ -4121,13 +4121,13 @@
     <t xml:space="preserve">0.993830323219299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00459086894989</t>
+    <t xml:space="preserve">1.0045907497406</t>
   </si>
   <si>
     <t xml:space="preserve">1.01061654090881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11176419258118</t>
+    <t xml:space="preserve">1.11176431179047</t>
   </si>
   <si>
     <t xml:space="preserve">1.1160683631897</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">1.10616886615753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12682890892029</t>
+    <t xml:space="preserve">1.126828789711</t>
   </si>
   <si>
     <t xml:space="preserve">1.1220942735672</t>
@@ -4148,16 +4148,16 @@
     <t xml:space="preserve">1.11822056770325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09669959545135</t>
+    <t xml:space="preserve">1.09669971466064</t>
   </si>
   <si>
     <t xml:space="preserve">1.11391639709473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13974130153656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11865103244781</t>
+    <t xml:space="preserve">1.13974118232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11865091323853</t>
   </si>
   <si>
     <t xml:space="preserve">1.09928214550018</t>
@@ -4169,7 +4169,7 @@
     <t xml:space="preserve">1.12898087501526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13586747646332</t>
+    <t xml:space="preserve">1.13586759567261</t>
   </si>
   <si>
     <t xml:space="preserve">1.13027215003967</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">1.11951184272766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12166392803192</t>
+    <t xml:space="preserve">1.12166380882263</t>
   </si>
   <si>
     <t xml:space="preserve">1.12984180450439</t>
@@ -4193,10 +4193,10 @@
     <t xml:space="preserve">1.14490628242493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11692917346954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0928258895874</t>
+    <t xml:space="preserve">1.11692929267883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09282600879669</t>
   </si>
   <si>
     <t xml:space="preserve">1.07603967189789</t>
@@ -4208,19 +4208,19 @@
     <t xml:space="preserve">1.06958341598511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07173550128937</t>
+    <t xml:space="preserve">1.07173562049866</t>
   </si>
   <si>
     <t xml:space="preserve">1.09971272945404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12467670440674</t>
+    <t xml:space="preserve">1.12467682361603</t>
   </si>
   <si>
     <t xml:space="preserve">1.12553763389587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13888049125671</t>
+    <t xml:space="preserve">1.13888037204742</t>
   </si>
   <si>
     <t xml:space="preserve">1.14705836772919</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">1.17245292663574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15093219280243</t>
+    <t xml:space="preserve">1.15093207359314</t>
   </si>
   <si>
     <t xml:space="preserve">1.18192207813263</t>
@@ -4259,10 +4259,10 @@
     <t xml:space="preserve">1.20387327671051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20430374145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21119034290314</t>
+    <t xml:space="preserve">1.20430386066437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21119022369385</t>
   </si>
   <si>
     <t xml:space="preserve">1.19483458995819</t>
@@ -4271,7 +4271,7 @@
     <t xml:space="preserve">1.18665671348572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20989906787872</t>
+    <t xml:space="preserve">1.20989918708801</t>
   </si>
   <si>
     <t xml:space="preserve">1.18794786930084</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">1.17632663249969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17675709724426</t>
+    <t xml:space="preserve">1.17675697803497</t>
   </si>
   <si>
     <t xml:space="preserve">1.19139122962952</t>
@@ -4301,19 +4301,19 @@
     <t xml:space="preserve">1.19225203990936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17976999282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18579578399658</t>
+    <t xml:space="preserve">1.17976987361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18579590320587</t>
   </si>
   <si>
     <t xml:space="preserve">1.18966948986053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20215153694153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20129072666168</t>
+    <t xml:space="preserve">1.20215165615082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20129084587097</t>
   </si>
   <si>
     <t xml:space="preserve">1.16944003105164</t>
@@ -4346,10 +4346,10 @@
     <t xml:space="preserve">1.18321335315704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25078845024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26240980625153</t>
+    <t xml:space="preserve">1.25078856945038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26240992546082</t>
   </si>
   <si>
     <t xml:space="preserve">1.23658490180969</t>
@@ -4361,13 +4361,13 @@
     <t xml:space="preserve">1.23959791660309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23787617683411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21678578853607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22496366500854</t>
+    <t xml:space="preserve">1.23787605762482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21678566932678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22496354579926</t>
   </si>
   <si>
     <t xml:space="preserve">1.25121903419495</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">1.26714444160461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29426062107086</t>
+    <t xml:space="preserve">1.29426074028015</t>
   </si>
   <si>
     <t xml:space="preserve">1.32869386672974</t>
@@ -4415,13 +4415,13 @@
     <t xml:space="preserve">1.35968375205994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35236668586731</t>
+    <t xml:space="preserve">1.3523668050766</t>
   </si>
   <si>
     <t xml:space="preserve">1.36614012718201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3773307800293</t>
+    <t xml:space="preserve">1.37733089923859</t>
   </si>
   <si>
     <t xml:space="preserve">1.34332811832428</t>
@@ -4430,13 +4430,13 @@
     <t xml:space="preserve">1.36786162853241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36829209327698</t>
+    <t xml:space="preserve">1.36829221248627</t>
   </si>
   <si>
     <t xml:space="preserve">1.3880912065506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40057325363159</t>
+    <t xml:space="preserve">1.40057337284088</t>
   </si>
   <si>
     <t xml:space="preserve">1.39885175228119</t>
@@ -4457,13 +4457,13 @@
     <t xml:space="preserve">1.44877994060516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43758904933929</t>
+    <t xml:space="preserve">1.43758916854858</t>
   </si>
   <si>
     <t xml:space="preserve">1.37905263900757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41047298908234</t>
+    <t xml:space="preserve">1.41047286987305</t>
   </si>
   <si>
     <t xml:space="preserve">1.42495942115784</t>
@@ -5937,6 +5937,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.33500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32999992370605</t>
   </si>
 </sst>
 </file>
@@ -71041,7 +71044,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.650162037</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>7709417</v>
@@ -71062,6 +71065,32 @@
         <v>1918</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6495601852</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>7382257</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>2.34899997711182</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>2.31200003623962</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>2.31699991226196</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>2.32999992370605</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1975</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="1976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1977" uniqueCount="1977">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,100 +38,100 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765547573566437</t>
+    <t xml:space="preserve">0.765547752380371</t>
   </si>
   <si>
     <t xml:space="preserve">A2A.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.7743039727211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769300401210785</t>
+    <t xml:space="preserve">0.774303913116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76930034160614</t>
   </si>
   <si>
     <t xml:space="preserve">0.777431130409241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.772427618503571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775554776191711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73615163564682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728020906448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.708632111549377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701126754283905</t>
+    <t xml:space="preserve">0.772427558898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775554895401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736151695251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728020846843719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.708631992340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701126575469971</t>
   </si>
   <si>
     <t xml:space="preserve">0.678610503673553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.686115801334381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.662974238395691</t>
+    <t xml:space="preserve">0.686115741729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.662974298000336</t>
   </si>
   <si>
     <t xml:space="preserve">0.669854164123535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.673606991767883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661723375320435</t>
+    <t xml:space="preserve">0.673606932163239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.66172331571579</t>
   </si>
   <si>
     <t xml:space="preserve">0.68986850976944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667352437973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.688617646694183</t>
+    <t xml:space="preserve">0.667352378368378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.688617587089539</t>
   </si>
   <si>
     <t xml:space="preserve">0.689243018627167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.676108658313751</t>
+    <t xml:space="preserve">0.676108717918396</t>
   </si>
   <si>
     <t xml:space="preserve">0.671105086803436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666726887226105</t>
+    <t xml:space="preserve">0.666727006435394</t>
   </si>
   <si>
     <t xml:space="preserve">0.643585443496704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612312972545624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597927689552307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605745792388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610749423503876</t>
+    <t xml:space="preserve">0.612313091754913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597927749156952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605745851993561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610749363899231</t>
   </si>
   <si>
     <t xml:space="preserve">0.614189445972443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627323806285858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617942154407501</t>
+    <t xml:space="preserve">0.627323865890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617942035198212</t>
   </si>
   <si>
     <t xml:space="preserve">0.624822080135345</t>
@@ -140,25 +140,25 @@
     <t xml:space="preserve">0.646712720394135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636080026626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65671968460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645461678504944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641083598136902</t>
+    <t xml:space="preserve">0.636079967021942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65671980381012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645461738109589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641083657741547</t>
   </si>
   <si>
     <t xml:space="preserve">0.647963523864746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657345235347748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661097943782806</t>
+    <t xml:space="preserve">0.657345354557037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661098003387451</t>
   </si>
   <si>
     <t xml:space="preserve">0.672981381416321</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">0.666101574897766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.664850652217865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658596277236938</t>
+    <t xml:space="preserve">0.66485059261322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658596098423004</t>
   </si>
   <si>
     <t xml:space="preserve">0.651716232299805</t>
@@ -179,49 +179,49 @@
     <t xml:space="preserve">0.654843509197235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669228792190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71301007270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69299578666687</t>
+    <t xml:space="preserve">0.669228851795197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713010013103485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692995727062225</t>
   </si>
   <si>
     <t xml:space="preserve">0.691119432449341</t>
   </si>
   <si>
-    <t xml:space="preserve">0.694246649742126</t>
+    <t xml:space="preserve">0.694246709346771</t>
   </si>
   <si>
     <t xml:space="preserve">0.69799941778183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696123003959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70300281047821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692370355129242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.699250161647797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714260935783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714886426925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.702377438545227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705504834651947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735526263713837</t>
+    <t xml:space="preserve">0.696123063564301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692370295524597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.699250221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714260995388031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714886367321014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.702377498149872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705504715442657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735526204109192</t>
   </si>
   <si>
     <t xml:space="preserve">0.740529775619507</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">0.748660564422607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73802787065506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750536918640137</t>
+    <t xml:space="preserve">0.738027930259705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750536978244781</t>
   </si>
   <si>
     <t xml:space="preserve">0.754289627075195</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">0.768049478530884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.757416784763336</t>
+    <t xml:space="preserve">0.757416963577271</t>
   </si>
   <si>
     <t xml:space="preserve">0.766798555850983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.752413332462311</t>
+    <t xml:space="preserve">0.752413272857666</t>
   </si>
   <si>
     <t xml:space="preserve">0.781183838844299</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">0.778056561946869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786187410354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779307663440704</t>
+    <t xml:space="preserve">0.786187291145325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77930748462677</t>
   </si>
   <si>
     <t xml:space="preserve">0.768674969673157</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">0.755540490150452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.760544061660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.764296889305115</t>
+    <t xml:space="preserve">0.760544002056122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76429671049118</t>
   </si>
   <si>
     <t xml:space="preserve">0.770551264286041</t>
@@ -284,61 +284,61 @@
     <t xml:space="preserve">0.75929319858551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769925832748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.761169612407684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767423927783966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747409701347351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751787900924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754915177822113</t>
+    <t xml:space="preserve">0.769925773143768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761169672012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767424046993256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747409760951996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751787960529327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754915058612823</t>
   </si>
   <si>
     <t xml:space="preserve">0.781809329986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801198244094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804950833320618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799321830272675</t>
+    <t xml:space="preserve">0.801198184490204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804950892925262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799321889877319</t>
   </si>
   <si>
     <t xml:space="preserve">0.785561978816986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.796820223331451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791816651821136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801823675632477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733649909496307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725519001483917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766306400299072</t>
+    <t xml:space="preserve">0.796820044517517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791816473007202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801823556423187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733649790287018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725519061088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766306459903717</t>
   </si>
   <si>
     <t xml:space="preserve">0.759828865528107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.750760078430176</t>
+    <t xml:space="preserve">0.750760197639465</t>
   </si>
   <si>
     <t xml:space="preserve">0.778614103794098</t>
@@ -350,88 +350,88 @@
     <t xml:space="preserve">0.69246119260788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.705416440963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.730031609535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763067662715912</t>
+    <t xml:space="preserve">0.705416560173035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.730031669139862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763067603111267</t>
   </si>
   <si>
     <t xml:space="preserve">0.762419879436493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769545316696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757885456085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742986857891083</t>
+    <t xml:space="preserve">0.769545257091522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757885575294495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742986917495728</t>
   </si>
   <si>
     <t xml:space="preserve">0.742339134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.758533239364624</t>
+    <t xml:space="preserve">0.758533298969269</t>
   </si>
   <si>
     <t xml:space="preserve">0.777318477630615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774079620838165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776022970676422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783796072006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779909551143646</t>
+    <t xml:space="preserve">0.77407968044281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776022851467133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783796191215515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779909491539001</t>
   </si>
   <si>
     <t xml:space="preserve">0.79027384519577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789625942707062</t>
+    <t xml:space="preserve">0.789626002311707</t>
   </si>
   <si>
     <t xml:space="preserve">0.794160306453705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805172264575958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807763397693634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.822662115097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817479968070984</t>
+    <t xml:space="preserve">0.805172383785248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807763457298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.822661936283112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817479908466339</t>
   </si>
   <si>
     <t xml:space="preserve">0.820718765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.822014272212982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809706747531891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814241111278534</t>
+    <t xml:space="preserve">0.822014212608337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809706807136536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814241051673889</t>
   </si>
   <si>
     <t xml:space="preserve">0.816184401512146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804524660110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801285922527313</t>
+    <t xml:space="preserve">0.804524719715118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801285803318024</t>
   </si>
   <si>
     <t xml:space="preserve">0.812945544719696</t>
@@ -440,64 +440,64 @@
     <t xml:space="preserve">0.801933586597443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786387205123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788330554962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771488547325134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783148407936096</t>
+    <t xml:space="preserve">0.786387145519257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788330495357513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771488606929779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783148288726807</t>
   </si>
   <si>
     <t xml:space="preserve">0.782500565052032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781852960586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770193040370941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785091638565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795455873012543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811002314090729</t>
+    <t xml:space="preserve">0.781852900981903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770193099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785091757774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795455992221832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811002254486084</t>
   </si>
   <si>
     <t xml:space="preserve">0.794808030128479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.796103715896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798694789409637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802581250667572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7909215092659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796751499176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799342513084412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810354471206665</t>
+    <t xml:space="preserve">0.796103656291962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798694729804993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802581369876862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790921568870544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796751439571381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799342572689056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810354590415955</t>
   </si>
   <si>
     <t xml:space="preserve">0.780557334423065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784443795681</t>
+    <t xml:space="preserve">0.784443855285645</t>
   </si>
   <si>
     <t xml:space="preserve">0.785739421844482</t>
@@ -509,58 +509,58 @@
     <t xml:space="preserve">0.813593327999115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.80063784122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7973992228508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803876876831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807115793228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7611243724823</t>
+    <t xml:space="preserve">0.80063796043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79739910364151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803876996040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80711567401886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76112425327301</t>
   </si>
   <si>
     <t xml:space="preserve">0.770840883255005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.731327176094055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735861480236053</t>
+    <t xml:space="preserve">0.731326997280121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735861599445343</t>
   </si>
   <si>
     <t xml:space="preserve">0.720315158367157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.721610605716705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.719019532203674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696347951889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696995556354523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.709950923919678</t>
+    <t xml:space="preserve">0.72161066532135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.719019591808319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696347773075104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696995496749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.709950804710388</t>
   </si>
   <si>
     <t xml:space="preserve">0.713837385177612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.71189421415329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.707359910011292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728736102581024</t>
+    <t xml:space="preserve">0.711894094944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.707359790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728736042976379</t>
   </si>
   <si>
     <t xml:space="preserve">0.715780735015869</t>
@@ -569,22 +569,22 @@
     <t xml:space="preserve">0.722258388996124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765010952949524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754646718502045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755294442176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787682771682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776670575141907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772136390209198</t>
+    <t xml:space="preserve">0.765011012554169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7546466588974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755294501781464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78768265247345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776670753955841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772136330604553</t>
   </si>
   <si>
     <t xml:space="preserve">0.78703498840332</t>
@@ -593,127 +593,127 @@
     <t xml:space="preserve">0.816832184791565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819423258304596</t>
+    <t xml:space="preserve">0.819423198699951</t>
   </si>
   <si>
     <t xml:space="preserve">0.799990236759186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824605345726013</t>
+    <t xml:space="preserve">0.824605405330658</t>
   </si>
   <si>
     <t xml:space="preserve">0.838856220245361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.831730782985687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832378447055817</t>
+    <t xml:space="preserve">0.831730842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832378506660461</t>
   </si>
   <si>
     <t xml:space="preserve">0.840151727199554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.848572790622711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841447293758392</t>
+    <t xml:space="preserve">0.848572611808777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841447234153748</t>
   </si>
   <si>
     <t xml:space="preserve">0.844686150550842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830435276031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798047006130219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815536618232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820071160793304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80646800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811649978160858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836265206336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844038307666779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837560594081879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836912870407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821366429328918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828492105007172</t>
+    <t xml:space="preserve">0.830435335636139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798046886920929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815536558628082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820071041584015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806467890739441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811650097370148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836264967918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844038248062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837560534477234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836913049221039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821366369724274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828491985797882</t>
   </si>
   <si>
     <t xml:space="preserve">0.825900912284851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.829139649868011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846629440784454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849220454692841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864766895771027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867357790470123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868005871772766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870596587657928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857641279697418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.865414619445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866710126399994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85310697555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855697989463806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858289182186127</t>
+    <t xml:space="preserve">0.829139709472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84662938117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84922057390213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864766776561737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867357850074768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868005692958832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870596766471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857641398906708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.865414500236511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866710007190704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853107154369354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85569816827774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858289062976837</t>
   </si>
   <si>
     <t xml:space="preserve">0.860232353210449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872540056705475</t>
+    <t xml:space="preserve">0.872539937496185</t>
   </si>
   <si>
     <t xml:space="preserve">0.874483346939087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.887438654899597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893916189670563</t>
+    <t xml:space="preserve">0.887438476085663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893916249275208</t>
   </si>
   <si>
     <t xml:space="preserve">0.89262068271637</t>
@@ -722,43 +722,43 @@
     <t xml:space="preserve">0.912701487541199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.909462690353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908166944980621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919826745986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918531239032745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87577885389328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877722203731537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891972839832306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884847700595856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895211815834045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884199857711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876426577568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862175703048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856345891952515</t>
+    <t xml:space="preserve">0.909462511539459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908167123794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919826805591583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918531358242035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87577897310257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877722144126892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89197301864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884847521781921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895211756229401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884199738502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876426637172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862175762653351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856345772743225</t>
   </si>
   <si>
     <t xml:space="preserve">0.882256507873535</t>
@@ -767,34 +767,34 @@
     <t xml:space="preserve">0.89909839630127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.890677392482758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926952242851257</t>
+    <t xml:space="preserve">0.890677452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926952183246613</t>
   </si>
   <si>
     <t xml:space="preserve">0.91529256105423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917235791683197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966465890407562</t>
+    <t xml:space="preserve">0.917235910892487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966465950012207</t>
   </si>
   <si>
     <t xml:space="preserve">0.958045065402985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96517026424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961283802986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963227152824402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94185084104538</t>
+    <t xml:space="preserve">0.965170562267303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96128386259079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963227093219757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941850900650024</t>
   </si>
   <si>
     <t xml:space="preserve">0.941203117370605</t>
@@ -803,34 +803,34 @@
     <t xml:space="preserve">0.958692789077759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982278227806091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988308429718018</t>
+    <t xml:space="preserve">0.982278108596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988308608531952</t>
   </si>
   <si>
     <t xml:space="preserve">0.997019171714783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00036931037903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992998659610748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968207180500031</t>
+    <t xml:space="preserve">1.00036919116974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992998719215393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968207478523254</t>
   </si>
   <si>
     <t xml:space="preserve">0.981608152389526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986298382282257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988978385925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989648520946503</t>
+    <t xml:space="preserve">0.986298203468323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988978564739227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989648640155792</t>
   </si>
   <si>
     <t xml:space="preserve">0.97490781545639</t>
@@ -842,16 +842,16 @@
     <t xml:space="preserve">1.00505948066711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998359203338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997689247131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00170934200287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00706970691681</t>
+    <t xml:space="preserve">0.998359143733978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997689008712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00170922279358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">1.02047049999237</t>
@@ -860,100 +860,100 @@
     <t xml:space="preserve">1.02985095977783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0177903175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995008945465088</t>
+    <t xml:space="preserve">1.01779043674469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995009005069733</t>
   </si>
   <si>
     <t xml:space="preserve">0.999029338359833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.976917803287506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.974237740039825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97021746635437</t>
+    <t xml:space="preserve">0.976917862892151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.974237620830536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970217525959015</t>
   </si>
   <si>
     <t xml:space="preserve">0.965527236461639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960837006568909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961506903171539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964187204837799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980268061161041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978927969932556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984958291053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97289776802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960166931152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958826720714569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951456427574158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955476343631744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949446380138397</t>
+    <t xml:space="preserve">0.960836946964264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961507022380829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96418708562851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980268180370331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978927850723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984958469867706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97289764881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960166752338409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958826780319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951456367969513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955476641654968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949446260929108</t>
   </si>
   <si>
     <t xml:space="preserve">0.963517069816589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950116217136383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953466475009918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956816554069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958156704902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952796399593353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962177097797394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944755852222443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931355237960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948106288909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954136490821838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957486748695374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939395546913147</t>
+    <t xml:space="preserve">0.950116157531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953466534614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956816673278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958156824111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952796459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962177038192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944755971431732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93135529756546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948106110095978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954136669635773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957486629486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939395785331726</t>
   </si>
   <si>
     <t xml:space="preserve">0.946766197681427</t>
@@ -965,400 +965,400 @@
     <t xml:space="preserve">0.928674936294556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92465478181839</t>
+    <t xml:space="preserve">0.9246546626091</t>
   </si>
   <si>
     <t xml:space="preserve">0.932695209980011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945426106452942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959496915340424</t>
+    <t xml:space="preserve">0.945426046848297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959496796131134</t>
   </si>
   <si>
     <t xml:space="preserve">0.973567724227905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978258013725281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993668913841248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984288394451141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983618438243866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994338870048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977587878704071</t>
+    <t xml:space="preserve">0.978257894515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993668735027313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984288275241852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983618319034576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994338810443878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977588057518005</t>
   </si>
   <si>
     <t xml:space="preserve">0.980938136577606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972227513790131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96619725227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969547271728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968877375125885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971557557582855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995678961277008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992328643798828</t>
+    <t xml:space="preserve">0.972227573394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966197311878204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96954756975174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96887731552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971557438373566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995678901672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992328882217407</t>
   </si>
   <si>
     <t xml:space="preserve">0.966867208480835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02114045619965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01041996479034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01444017887115</t>
+    <t xml:space="preserve">1.02114057540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01041984558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01443994045258</t>
   </si>
   <si>
     <t xml:space="preserve">1.02181041240692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02382075786591</t>
+    <t xml:space="preserve">1.02382063865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0285108089447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03320121765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03923153877258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02650082111359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05531251430511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05866265296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04459178447723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05330240726471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06804323196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0727334022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08613431453705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09551477432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08345413208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08211398124695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05397248268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0600026845932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04392170906067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04861211776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04660212993622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03990161418915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04258191585541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01980042457581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.015780210495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05196237564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06737315654755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06603312492371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02449059486389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01846039295197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02784097194672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05665278434753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06134295463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07742381095886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07943379878998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06938338279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05933272838593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03856134414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02683591842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03588128089905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04191184043884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996349096298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971222519874573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995344042778015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944420874118805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953131377696991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941405773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959831953048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946431040763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957821786403656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950451195240021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936380505561829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967202246189117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99132376909256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975577890872955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993333756923676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00003409385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00137424468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991658806800842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00673460960388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999364137649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04023671150208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04157662391663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04224681854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04961729049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04995214939117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06268286705017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07206344604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05832767486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06335294246674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07407355308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08043885231018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08546435832977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09048962593079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09484481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09819507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09853005409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12198150157928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11762619018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1172913312912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1072404384613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10757553577423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12265145778656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13002181053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10992074012756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11829626560211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05732250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03387129306793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03895270824432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05287528038025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04208540916443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04730629920959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02572679519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00693142414093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980827271938324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998926222324371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01076006889343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00484335422516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02920711040497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00936794281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00658357143402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999622404575348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968993127346039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01598119735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02398633956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03164374828339</t>
   </si>
   <si>
     <t xml:space="preserve">1.02851092815399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03320121765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03923153877258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02650082111359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05531251430511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05866265296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04459190368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05330240726471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06804311275482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07273352146149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08613443374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0955148935318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08345401287079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08211410045624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05397236347198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06000280380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04392170906067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04861223697662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04660189151764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03990161418915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04258179664612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01980042457581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01578032970428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05196225643158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06737315654755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06603312492371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02449059486389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01846027374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02784097194672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05665266513824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06134295463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07742381095886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07943391799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06938338279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05933260917664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03856158256531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02683579921722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03588151931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04191172122955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996349155902863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971222460269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995343923568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944420874118805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953131496906281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941405773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959831833839417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9464311003685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957821846008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950451195240021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936380505561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967202305793762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991323709487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975577831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993333876132965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0000342130661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00137436389923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991658687591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00673460960388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999364197254181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0402364730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04157662391663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04224681854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04961705207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04995226860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06268298625946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07206356525421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05832755565643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06335318088531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07407379150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08043909072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08546435832977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09048962593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09484481811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09819495677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09852993488312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12198150157928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11762607097626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11729097366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10724079608917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10757565498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12265169620514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13002181053162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10992085933685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11829626560211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05732262134552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03387105464935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0389529466629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05287528038025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04208528995514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04730618000031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02572667598724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00693154335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980827271938324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998926281929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01076030731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00484335422516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02920722961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00936794281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00658345222473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999622464179993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968993246555328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01598107814789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02398645877838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0316436290741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02851116657257</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.01980972290039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04382574558258</t>
+    <t xml:space="preserve">1.04382562637329</t>
   </si>
   <si>
     <t xml:space="preserve">1.04661011695862</t>
@@ -1367,70 +1367,70 @@
     <t xml:space="preserve">1.02363836765289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02537858486176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00588738918304</t>
+    <t xml:space="preserve">1.02537846565247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00588750839233</t>
   </si>
   <si>
     <t xml:space="preserve">1.01250052452087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02120196819305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02642273902893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03373205661774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01389265060425</t>
+    <t xml:space="preserve">1.02120208740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02642285823822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03373193740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01389276981354</t>
   </si>
   <si>
     <t xml:space="preserve">1.03860485553741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0511349439621</t>
+    <t xml:space="preserve">1.05113506317139</t>
   </si>
   <si>
     <t xml:space="preserve">1.06122851371765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07236659526825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06018435955048</t>
+    <t xml:space="preserve">1.07236647605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06018447875977</t>
   </si>
   <si>
     <t xml:space="preserve">1.06262075901031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05600762367249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07375872135162</t>
+    <t xml:space="preserve">1.05600774288177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07375884056091</t>
   </si>
   <si>
     <t xml:space="preserve">1.06714558601379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0786315202713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09290182590485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09429407119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10160338878632</t>
+    <t xml:space="preserve">1.07863140106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09290206432343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0942941904068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10160326957703</t>
   </si>
   <si>
     <t xml:space="preserve">1.08420038223267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04835045337677</t>
+    <t xml:space="preserve">1.04835033416748</t>
   </si>
   <si>
     <t xml:space="preserve">1.06157660484314</t>
@@ -1439,52 +1439,52 @@
     <t xml:space="preserve">1.07201838493347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07584714889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07132232189178</t>
+    <t xml:space="preserve">1.07584702968597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07132244110107</t>
   </si>
   <si>
     <t xml:space="preserve">1.09394598007202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08106791973114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09011733531952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08246004581451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10299551486969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12005043029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12387907505035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10473585128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10612809658051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11134886741638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10821640491486</t>
+    <t xml:space="preserve">1.08106780052185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09011745452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0824601650238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1029953956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12005031108856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12387895584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10473573207855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10612785816193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11134898662567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10821652412415</t>
   </si>
   <si>
     <t xml:space="preserve">1.10960865020752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08837723731995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08802890777588</t>
+    <t xml:space="preserve">1.08837711811066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08802902698517</t>
   </si>
   <si>
     <t xml:space="preserve">1.08942127227783</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">1.07549893856049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06540536880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03338396549225</t>
+    <t xml:space="preserve">1.06540524959564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03338408470154</t>
   </si>
   <si>
     <t xml:space="preserve">1.04243338108063</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">1.03094744682312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04173743724823</t>
+    <t xml:space="preserve">1.04173731803894</t>
   </si>
   <si>
     <t xml:space="preserve">1.05705189704895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07897937297821</t>
+    <t xml:space="preserve">1.0789794921875</t>
   </si>
   <si>
     <t xml:space="preserve">1.09220576286316</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">1.09116160869598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08454847335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08141589164734</t>
+    <t xml:space="preserve">1.08454823493958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08141601085663</t>
   </si>
   <si>
     <t xml:space="preserve">1.09847068786621</t>
@@ -1535,16 +1535,16 @@
     <t xml:space="preserve">1.09603440761566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07619512081146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07445478439331</t>
+    <t xml:space="preserve">1.07619500160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0744549036026</t>
   </si>
   <si>
     <t xml:space="preserve">1.0587922334671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07758724689484</t>
+    <t xml:space="preserve">1.07758736610413</t>
   </si>
   <si>
     <t xml:space="preserve">1.06923389434814</t>
@@ -1562,73 +1562,73 @@
     <t xml:space="preserve">1.04417383670807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05183112621307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03616833686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05844402313232</t>
+    <t xml:space="preserve">1.05183124542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03616845607758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05844414234161</t>
   </si>
   <si>
     <t xml:space="preserve">1.03442811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00310301780701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991617023944855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00832390785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01424062252045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01772117614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01354455947876</t>
+    <t xml:space="preserve">1.00310277938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99161684513092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00832378864288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01424086093903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01772129535675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01354467868805</t>
   </si>
   <si>
     <t xml:space="preserve">0.993705332279205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98813658952713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97734659910202</t>
+    <t xml:space="preserve">0.988136470317841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977346658706665</t>
   </si>
   <si>
     <t xml:space="preserve">1.00553941726685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986047923564911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989528596401215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992313206195831</t>
+    <t xml:space="preserve">0.9860480427742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989528656005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992313146591187</t>
   </si>
   <si>
     <t xml:space="preserve">0.982915580272675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991965055465698</t>
+    <t xml:space="preserve">0.991965115070343</t>
   </si>
   <si>
     <t xml:space="preserve">1.01319658756256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00414717197418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02050566673279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0156329870224</t>
+    <t xml:space="preserve">1.00414705276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02050578594208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01563310623169</t>
   </si>
   <si>
     <t xml:space="preserve">1.0351243019104</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">1.03930103778839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05252707004547</t>
+    <t xml:space="preserve">1.05252718925476</t>
   </si>
   <si>
     <t xml:space="preserve">1.05461549758911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03721261024475</t>
+    <t xml:space="preserve">1.03721272945404</t>
   </si>
   <si>
     <t xml:space="preserve">1.02711892127991</t>
@@ -1655,58 +1655,58 @@
     <t xml:space="preserve">1.06610143184662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06088066101074</t>
+    <t xml:space="preserve">1.06088054180145</t>
   </si>
   <si>
     <t xml:space="preserve">1.04034519195557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03233981132507</t>
+    <t xml:space="preserve">1.03233969211578</t>
   </si>
   <si>
     <t xml:space="preserve">1.04278147220612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04347765445709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07410669326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10090732574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11761391162872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12701141834259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11378526687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10647594928741</t>
+    <t xml:space="preserve">1.0434775352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07410657405853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10090708732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11761403083801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12701153755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11378538608551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1064760684967</t>
   </si>
   <si>
     <t xml:space="preserve">1.12318289279938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13118815422058</t>
+    <t xml:space="preserve">1.13118827342987</t>
   </si>
   <si>
     <t xml:space="preserve">1.1144814491272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08872509002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09464204311371</t>
+    <t xml:space="preserve">1.08872520923615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.094642162323</t>
   </si>
   <si>
     <t xml:space="preserve">1.11622166633606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1183100938797</t>
+    <t xml:space="preserve">1.11831021308899</t>
   </si>
   <si>
     <t xml:space="preserve">1.13501691818237</t>
@@ -1715,19 +1715,19 @@
     <t xml:space="preserve">1.13675713539124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1381493806839</t>
+    <t xml:space="preserve">1.13814926147461</t>
   </si>
   <si>
     <t xml:space="preserve">1.14302217960358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10403978824615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10891258716583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09951496124268</t>
+    <t xml:space="preserve">1.10403966903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10891270637512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09951484203339</t>
   </si>
   <si>
     <t xml:space="preserve">1.10195136070251</t>
@@ -1742,73 +1742,73 @@
     <t xml:space="preserve">1.10577988624573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09185779094696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07793533802032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08071994781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08663666248322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06227278709412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08280813694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09742665290833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10021126270294</t>
+    <t xml:space="preserve">1.09185767173767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07793521881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08071982860565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0866367816925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06227290630341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08280825614929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09742677211761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10021090507507</t>
   </si>
   <si>
     <t xml:space="preserve">1.09777474403381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10369169712067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11100077629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10543215274811</t>
+    <t xml:space="preserve">1.10369157791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11100089550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10543191432953</t>
   </si>
   <si>
     <t xml:space="preserve">1.08594059944153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09568631649017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08907318115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11726593971252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12074661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10752046108246</t>
+    <t xml:space="preserve">1.09568619728088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08907330036163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11726582050323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12074649333954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10752022266388</t>
   </si>
   <si>
     <t xml:space="preserve">1.1103048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.121790766716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11935436725616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13571310043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13536477088928</t>
+    <t xml:space="preserve">1.12179064750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11935424804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13571286201477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13536489009857</t>
   </si>
   <si>
     <t xml:space="preserve">1.13084018230438</t>
@@ -1817,16 +1817,16 @@
     <t xml:space="preserve">1.13223242759705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14754700660706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06331706047058</t>
+    <t xml:space="preserve">1.14754712581635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06331694126129</t>
   </si>
   <si>
     <t xml:space="preserve">1.05391931533813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04626214504242</t>
+    <t xml:space="preserve">1.04626202583313</t>
   </si>
   <si>
     <t xml:space="preserve">1.05426740646362</t>
@@ -1844,49 +1844,49 @@
     <t xml:space="preserve">1.01632916927338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00379908084869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997882068157196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00727963447571</t>
+    <t xml:space="preserve">1.0037989616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997882187366486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.007279753685</t>
   </si>
   <si>
     <t xml:space="preserve">1.02015781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07654321193695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08517646789551</t>
+    <t xml:space="preserve">1.07654309272766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08517634868622</t>
   </si>
   <si>
     <t xml:space="preserve">1.09720551967621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09647643566132</t>
+    <t xml:space="preserve">1.09647631645203</t>
   </si>
   <si>
     <t xml:space="preserve">1.06622135639191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08116674423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07205379009247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06038916110992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05127608776093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06403422355652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07168912887573</t>
+    <t xml:space="preserve">1.08116662502289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07205367088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06038904190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05127596855164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06403434276581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07168924808502</t>
   </si>
   <si>
     <t xml:space="preserve">1.08043766021729</t>
@@ -1898,31 +1898,31 @@
     <t xml:space="preserve">1.0986635684967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10449588298798</t>
+    <t xml:space="preserve">1.10449600219727</t>
   </si>
   <si>
     <t xml:space="preserve">1.10048627853394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10230875015259</t>
+    <t xml:space="preserve">1.10230886936188</t>
   </si>
   <si>
     <t xml:space="preserve">1.09574747085571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09829914569855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13219952583313</t>
+    <t xml:space="preserve">1.09829902648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13219940662384</t>
   </si>
   <si>
     <t xml:space="preserve">1.12563812732697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1402188539505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14750933647156</t>
+    <t xml:space="preserve">1.14021897315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14750921726227</t>
   </si>
   <si>
     <t xml:space="preserve">1.13584458827972</t>
@@ -1937,55 +1937,55 @@
     <t xml:space="preserve">1.10376691818237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11251533031464</t>
+    <t xml:space="preserve">1.11251544952393</t>
   </si>
   <si>
     <t xml:space="preserve">1.11069273948669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13511574268341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1500608921051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15188348293304</t>
+    <t xml:space="preserve">1.13511562347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15006101131439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15188360214233</t>
   </si>
   <si>
     <t xml:space="preserve">1.147873878479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15261244773865</t>
+    <t xml:space="preserve">1.15261256694794</t>
   </si>
   <si>
     <t xml:space="preserve">1.16427719593048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1704740524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17156755924225</t>
+    <t xml:space="preserve">1.17047417163849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17156767845154</t>
   </si>
   <si>
     <t xml:space="preserve">1.17229676246643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17849361896515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17484843730927</t>
+    <t xml:space="preserve">1.17849349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17484831809998</t>
   </si>
   <si>
     <t xml:space="preserve">1.19161629676819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16318368911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16609990596771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17995154857635</t>
+    <t xml:space="preserve">1.16318380832672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16609978675842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17995166778564</t>
   </si>
   <si>
     <t xml:space="preserve">1.18469035625458</t>
@@ -1997,31 +1997,31 @@
     <t xml:space="preserve">1.17120325565338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17375481128693</t>
+    <t xml:space="preserve">1.17375469207764</t>
   </si>
   <si>
     <t xml:space="preserve">1.14969646930695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15407061576843</t>
+    <t xml:space="preserve">1.15407073497772</t>
   </si>
   <si>
     <t xml:space="preserve">1.17083859443665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16209006309509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1668289899826</t>
+    <t xml:space="preserve">1.16209018230438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16682887077332</t>
   </si>
   <si>
     <t xml:space="preserve">1.16755795478821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17010962963104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13183498382568</t>
+    <t xml:space="preserve">1.17010951042175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13183510303497</t>
   </si>
   <si>
     <t xml:space="preserve">1.12418007850647</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">1.14277064800262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16099655628204</t>
+    <t xml:space="preserve">1.16099643707275</t>
   </si>
   <si>
     <t xml:space="preserve">1.14459323883057</t>
@@ -2045,16 +2045,16 @@
     <t xml:space="preserve">1.13985443115234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13475120067596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16391277313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16938054561615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16573524475098</t>
+    <t xml:space="preserve">1.13475108146667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16391289234161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16938042640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16573536396027</t>
   </si>
   <si>
     <t xml:space="preserve">1.16500639915466</t>
@@ -2075,19 +2075,19 @@
     <t xml:space="preserve">1.1795871257782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16464173793793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17922258377075</t>
+    <t xml:space="preserve">1.16464185714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17922246456146</t>
   </si>
   <si>
     <t xml:space="preserve">1.18213880062103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17630636692047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19599044322968</t>
+    <t xml:space="preserve">1.17630648612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19599032402039</t>
   </si>
   <si>
     <t xml:space="preserve">1.18979358673096</t>
@@ -2096,55 +2096,55 @@
     <t xml:space="preserve">1.22551667690277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21567475795746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22770380973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23207807540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21421670913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21166479587555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23134911060333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23025548458099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21603918075562</t>
+    <t xml:space="preserve">1.21567463874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22770392894745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23207795619965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21421647071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21166491508484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23134899139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2302553653717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21603894233704</t>
   </si>
   <si>
     <t xml:space="preserve">1.21931982040405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2379105091095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23462986946106</t>
+    <t xml:space="preserve">1.23791015148163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23462963104248</t>
   </si>
   <si>
     <t xml:space="preserve">1.22806835174561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21640372276306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22187161445618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22114229202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22405874729156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23062002658844</t>
+    <t xml:space="preserve">1.21640360355377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2218713760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22114241123199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22405862808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23061990737915</t>
   </si>
   <si>
     <t xml:space="preserve">1.22843277454376</t>
@@ -2153,19 +2153,19 @@
     <t xml:space="preserve">1.23645222187042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2287974357605</t>
+    <t xml:space="preserve">1.22879719734192</t>
   </si>
   <si>
     <t xml:space="preserve">1.22624576091766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27363336086273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27691411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31154346466064</t>
+    <t xml:space="preserve">1.27363324165344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27691400051117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31154334545135</t>
   </si>
   <si>
     <t xml:space="preserve">1.31336605548859</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">1.30972075462341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30826270580292</t>
+    <t xml:space="preserve">1.30826258659363</t>
   </si>
   <si>
     <t xml:space="preserve">1.31591749191284</t>
@@ -2189,10 +2189,10 @@
     <t xml:space="preserve">1.31445956230164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30862724781036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29732716083527</t>
+    <t xml:space="preserve">1.30862712860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29732704162598</t>
   </si>
   <si>
     <t xml:space="preserve">1.27873659133911</t>
@@ -2201,22 +2201,22 @@
     <t xml:space="preserve">1.288578748703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28420436382294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27727842330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27509129047394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26452028751373</t>
+    <t xml:space="preserve">1.28420448303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27727830410004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27509117126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26452040672302</t>
   </si>
   <si>
     <t xml:space="preserve">1.24884593486786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24665880203247</t>
+    <t xml:space="preserve">1.24665892124176</t>
   </si>
   <si>
     <t xml:space="preserve">1.25249111652374</t>
@@ -2225,37 +2225,37 @@
     <t xml:space="preserve">1.24520063400269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24483609199524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19052278995514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19635510444641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19854235649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19343888759613</t>
+    <t xml:space="preserve">1.24483621120453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19052267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1963552236557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19854211807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19343876838684</t>
   </si>
   <si>
     <t xml:space="preserve">1.18068075180054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20218741893768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18906462192535</t>
+    <t xml:space="preserve">1.20218753814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18906474113464</t>
   </si>
   <si>
     <t xml:space="preserve">1.19270980358124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20656168460846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20729076862335</t>
+    <t xml:space="preserve">1.20656156539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20729064941406</t>
   </si>
   <si>
     <t xml:space="preserve">1.22515213489532</t>
@@ -2279,10 +2279,10 @@
     <t xml:space="preserve">1.25504267215729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25066840648651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25941693782806</t>
+    <t xml:space="preserve">1.25066864490509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25941705703735</t>
   </si>
   <si>
     <t xml:space="preserve">1.25650084018707</t>
@@ -2294,28 +2294,28 @@
     <t xml:space="preserve">1.29987871646881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30315947532654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29368197917938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29222369194031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30607557296753</t>
+    <t xml:space="preserve">1.30315935611725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2936817407608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29222393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30607569217682</t>
   </si>
   <si>
     <t xml:space="preserve">1.35200524330139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34544384479523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33414363861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31409513950348</t>
+    <t xml:space="preserve">1.34544360637665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33414351940155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3140949010849</t>
   </si>
   <si>
     <t xml:space="preserve">1.3224790096283</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">1.33159196376801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33013391494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34981799125671</t>
+    <t xml:space="preserve">1.33013379573822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.349818110466</t>
   </si>
   <si>
     <t xml:space="preserve">1.34398579597473</t>
@@ -2342,25 +2342,25 @@
     <t xml:space="preserve">1.34143400192261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34945356845856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35893094539642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36986649036407</t>
+    <t xml:space="preserve">1.34945344924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35893106460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36986660957336</t>
   </si>
   <si>
     <t xml:space="preserve">1.3822603225708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3603892326355</t>
+    <t xml:space="preserve">1.36038911342621</t>
   </si>
   <si>
     <t xml:space="preserve">1.34908890724182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26524949073792</t>
+    <t xml:space="preserve">1.26524937152863</t>
   </si>
   <si>
     <t xml:space="preserve">1.25613629817963</t>
@@ -2369,19 +2369,19 @@
     <t xml:space="preserve">1.13766729831696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15589320659637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19708395004272</t>
+    <t xml:space="preserve">1.15589332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19708406925201</t>
   </si>
   <si>
     <t xml:space="preserve">1.11579608917236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996233582496643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924787521362305</t>
+    <t xml:space="preserve">0.996233463287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924787580966949</t>
   </si>
   <si>
     <t xml:space="preserve">0.905468046665192</t>
@@ -2390,13 +2390,13 @@
     <t xml:space="preserve">0.733049929141998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.772782683372498</t>
+    <t xml:space="preserve">0.772782623767853</t>
   </si>
   <si>
     <t xml:space="preserve">0.750546932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.775334358215332</t>
+    <t xml:space="preserve">0.775334298610687</t>
   </si>
   <si>
     <t xml:space="preserve">0.751276075839996</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">0.729040205478668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786269962787628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797205567359924</t>
+    <t xml:space="preserve">0.786269903182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79720550775528</t>
   </si>
   <si>
     <t xml:space="preserve">0.793195843696594</t>
@@ -2423,22 +2423,22 @@
     <t xml:space="preserve">0.778250515460968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824544429779053</t>
+    <t xml:space="preserve">0.824544489383698</t>
   </si>
   <si>
     <t xml:space="preserve">0.826002597808838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.816160500049591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841676950454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836209118366241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86901593208313</t>
+    <t xml:space="preserve">0.816160559654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841677069664001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836209177970886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869016110897064</t>
   </si>
   <si>
     <t xml:space="preserve">0.869745016098022</t>
@@ -2450,22 +2450,22 @@
     <t xml:space="preserve">0.876670837402344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.889429152011871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885783910751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.897448539733887</t>
+    <t xml:space="preserve">0.889429092407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885783791542053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.897448480129242</t>
   </si>
   <si>
     <t xml:space="preserve">0.910935819149017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91166478395462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.883961200714111</t>
+    <t xml:space="preserve">0.911664724349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883961319923401</t>
   </si>
   <si>
     <t xml:space="preserve">0.888335585594177</t>
@@ -2477,34 +2477,34 @@
     <t xml:space="preserve">0.890158116817474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906926155090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901458263397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899635553359985</t>
+    <t xml:space="preserve">0.906926095485687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901458203792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899635672569275</t>
   </si>
   <si>
     <t xml:space="preserve">0.905832409858704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872296571731567</t>
+    <t xml:space="preserve">0.872296631336212</t>
   </si>
   <si>
     <t xml:space="preserve">0.879951596260071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878128945827484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882138788700104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877764463424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914581000804901</t>
+    <t xml:space="preserve">0.878128886222839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882138669490814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877764523029327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914581060409546</t>
   </si>
   <si>
     <t xml:space="preserve">0.93426501750946</t>
@@ -2513,34 +2513,34 @@
     <t xml:space="preserve">0.911300301551819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944332480430603</t>
+    <t xml:space="preserve">0.944332420825958</t>
   </si>
   <si>
     <t xml:space="preserve">0.902750670909882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.914020538330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910522937774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912854731082916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946275532245636</t>
+    <t xml:space="preserve">0.914020478725433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910522997379303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912854611873627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946275591850281</t>
   </si>
   <si>
     <t xml:space="preserve">0.971146881580353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950550258159637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971535444259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969592332839966</t>
+    <t xml:space="preserve">0.950550377368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971535503864288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969592392444611</t>
   </si>
   <si>
     <t xml:space="preserve">0.981639504432678</t>
@@ -2552,10 +2552,10 @@
     <t xml:space="preserve">1.04265189170837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04342901706696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03060472011566</t>
+    <t xml:space="preserve">1.04342913627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03060483932495</t>
   </si>
   <si>
     <t xml:space="preserve">1.05236721038818</t>
@@ -2567,10 +2567,10 @@
     <t xml:space="preserve">1.01195132732391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960265576839447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956379592418671</t>
+    <t xml:space="preserve">0.960265636444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956379413604736</t>
   </si>
   <si>
     <t xml:space="preserve">0.978141903877258</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">1.00961971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0193350315094</t>
+    <t xml:space="preserve">1.01933491230011</t>
   </si>
   <si>
     <t xml:space="preserve">1.01467168331146</t>
@@ -2594,55 +2594,55 @@
     <t xml:space="preserve">0.972312748432159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.963763177394867</t>
+    <t xml:space="preserve">0.963763236999512</t>
   </si>
   <si>
     <t xml:space="preserve">0.977364778518677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979696333408356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984359860420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99990439414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996795475482941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993686378002167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983194053173065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98280531167984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958322703838348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961431443691254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960654199123383</t>
+    <t xml:space="preserve">0.979696273803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984359681606293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999904453754425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996795415878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993686437606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983193814754486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982805371284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958322763442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961431503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960654139518738</t>
   </si>
   <si>
     <t xml:space="preserve">0.973867177963257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973089993000031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985136926174164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987857341766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985525608062744</t>
+    <t xml:space="preserve">0.973089814186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985137045383453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987857282161713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985525548458099</t>
   </si>
   <si>
     <t xml:space="preserve">0.949773132801056</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">0.954436421394348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970758199691772</t>
+    <t xml:space="preserve">0.970758259296417</t>
   </si>
   <si>
     <t xml:space="preserve">0.92878794670105</t>
@@ -2660,55 +2660,55 @@
     <t xml:space="preserve">0.943166613578796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955990970134735</t>
+    <t xml:space="preserve">0.95599091053009</t>
   </si>
   <si>
     <t xml:space="preserve">0.959877014160156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953659296035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965317726135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982028067111969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01739192008972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00612211227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994852244853973</t>
+    <t xml:space="preserve">0.953659236431122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965317666530609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982028126716614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01739203929901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00612223148346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994852304458618</t>
   </si>
   <si>
     <t xml:space="preserve">0.979307770729065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989411771297455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987079977989197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964929163455963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96259731054306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958711266517639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966094970703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951327443122864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954047858715057</t>
+    <t xml:space="preserve">0.989411652088165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987080037593842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964929103851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962597250938416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95871114730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96609491109848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951327562332153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954047739505768</t>
   </si>
   <si>
     <t xml:space="preserve">0.975033164024353</t>
@@ -2717,130 +2717,130 @@
     <t xml:space="preserve">0.968037903308868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937726080417633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946664273738861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938503324985504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942000687122345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933451175689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971924185752869</t>
+    <t xml:space="preserve">0.937726020812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946664214134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938503265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942000865936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933451294898987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971924006938934</t>
   </si>
   <si>
     <t xml:space="preserve">0.94899582862854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953270554542542</t>
+    <t xml:space="preserve">0.953270733356476</t>
   </si>
   <si>
     <t xml:space="preserve">0.945886969566345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929565131664276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931119620800018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900807678699493</t>
+    <t xml:space="preserve">0.929565191268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931119501590729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900807797908783</t>
   </si>
   <si>
     <t xml:space="preserve">0.903528034687042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904693961143494</t>
+    <t xml:space="preserve">0.904693901538849</t>
   </si>
   <si>
     <t xml:space="preserve">0.89886462688446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878656685352325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886428952217102</t>
+    <t xml:space="preserve">0.878656625747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886428892612457</t>
   </si>
   <si>
     <t xml:space="preserve">0.90158486366272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.886040270328522</t>
+    <t xml:space="preserve">0.886040449142456</t>
   </si>
   <si>
     <t xml:space="preserve">0.840961158275604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830079913139343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848344802856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860780358314514</t>
+    <t xml:space="preserve">0.830079853534698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848344743251801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860780298709869</t>
   </si>
   <si>
     <t xml:space="preserve">0.872050225734711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.898476004600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892646670341492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88137686252594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94277811050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939280569553375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955213725566864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95249330997467</t>
+    <t xml:space="preserve">0.898476123809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892646729946136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.881376981735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942777991294861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939280450344086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95521354675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95249342918396</t>
   </si>
   <si>
     <t xml:space="preserve">0.947441399097443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95210474729538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959488451480865</t>
+    <t xml:space="preserve">0.952104926109314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95948851108551</t>
   </si>
   <si>
     <t xml:space="preserve">0.97619891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01700341701508</t>
+    <t xml:space="preserve">1.01700329780579</t>
   </si>
   <si>
     <t xml:space="preserve">1.02205526828766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993297934532166</t>
+    <t xml:space="preserve">0.993298053741455</t>
   </si>
   <si>
     <t xml:space="preserve">0.982416749000549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975421726703644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976587474346161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997183978557587</t>
+    <t xml:space="preserve">0.975421667098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976587414741516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997183918952942</t>
   </si>
   <si>
     <t xml:space="preserve">0.990966200828552</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">0.988245904445648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984748363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995629668235779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954825103282928</t>
+    <t xml:space="preserve">0.984748303890228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995629549026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954825043678284</t>
   </si>
   <si>
     <t xml:space="preserve">1.0065108537674</t>
@@ -2867,13 +2867,13 @@
     <t xml:space="preserve">1.01389443874359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03449094295502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02399837970734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04148602485657</t>
+    <t xml:space="preserve">1.03449082374573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02399849891663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04148614406586</t>
   </si>
   <si>
     <t xml:space="preserve">1.03954291343689</t>
@@ -2885,28 +2885,28 @@
     <t xml:space="preserve">1.01428294181824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03759980201721</t>
+    <t xml:space="preserve">1.03760004043579</t>
   </si>
   <si>
     <t xml:space="preserve">1.0321592092514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02050077915192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03099346160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06596863269806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07296371459961</t>
+    <t xml:space="preserve">1.02050089836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03099358081818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06596887111664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0729638338089</t>
   </si>
   <si>
     <t xml:space="preserve">1.04653799533844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05897355079651</t>
+    <t xml:space="preserve">1.0589736700058</t>
   </si>
   <si>
     <t xml:space="preserve">1.05353307723999</t>
@@ -2918,25 +2918,25 @@
     <t xml:space="preserve">1.0449835062027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10871624946594</t>
+    <t xml:space="preserve">1.10871636867523</t>
   </si>
   <si>
     <t xml:space="preserve">1.13630795478821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15418422222137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12853562831879</t>
+    <t xml:space="preserve">1.15418410301208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12853574752808</t>
   </si>
   <si>
     <t xml:space="preserve">1.1382509469986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1425256729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17516922950745</t>
+    <t xml:space="preserve">1.14252579212189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17516934871674</t>
   </si>
   <si>
     <t xml:space="preserve">1.16195642948151</t>
@@ -2945,13 +2945,13 @@
     <t xml:space="preserve">1.13863968849182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12154066562653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13475358486176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12698125839233</t>
+    <t xml:space="preserve">1.12154054641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13475346565247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12698113918304</t>
   </si>
   <si>
     <t xml:space="preserve">1.11415696144104</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">1.08384501934052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11493408679962</t>
+    <t xml:space="preserve">1.11493420600891</t>
   </si>
   <si>
     <t xml:space="preserve">1.1071617603302</t>
@@ -2981,19 +2981,19 @@
     <t xml:space="preserve">1.08656525611877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0772385597229</t>
+    <t xml:space="preserve">1.07723867893219</t>
   </si>
   <si>
     <t xml:space="preserve">1.1083277463913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1308673620224</t>
+    <t xml:space="preserve">1.13086724281311</t>
   </si>
   <si>
     <t xml:space="preserve">1.15262973308563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14874362945557</t>
+    <t xml:space="preserve">1.14874351024628</t>
   </si>
   <si>
     <t xml:space="preserve">1.15496134757996</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">1.16312229633331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14563453197479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15301847457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14641201496124</t>
+    <t xml:space="preserve">1.14563465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15301823616028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14641189575195</t>
   </si>
   <si>
     <t xml:space="preserve">1.17089450359344</t>
@@ -3029,16 +3029,16 @@
     <t xml:space="preserve">1.21752822399139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20625841617584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20392680168152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20859003067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22413468360901</t>
+    <t xml:space="preserve">1.20625853538513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20392668247223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20859014987946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2241348028183</t>
   </si>
   <si>
     <t xml:space="preserve">1.20975589752197</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">1.19809758663177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21286487579346</t>
+    <t xml:space="preserve">1.21286499500275</t>
   </si>
   <si>
     <t xml:space="preserve">1.21597373485565</t>
@@ -3059,28 +3059,28 @@
     <t xml:space="preserve">1.20431530475616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21247613430023</t>
+    <t xml:space="preserve">1.21247637271881</t>
   </si>
   <si>
     <t xml:space="preserve">1.22685503959656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21403086185455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23579323291779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23812484741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23851346969604</t>
+    <t xml:space="preserve">1.21403074264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2357931137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23812472820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23851335048676</t>
   </si>
   <si>
     <t xml:space="preserve">1.24278819561005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26105308532715</t>
+    <t xml:space="preserve">1.26105296611786</t>
   </si>
   <si>
     <t xml:space="preserve">1.26455056667328</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">1.26066446304321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2649393081665</t>
+    <t xml:space="preserve">1.26493942737579</t>
   </si>
   <si>
     <t xml:space="preserve">1.27892935276031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3045779466629</t>
+    <t xml:space="preserve">1.30457770824432</t>
   </si>
   <si>
     <t xml:space="preserve">1.31779074668884</t>
@@ -3110,28 +3110,28 @@
     <t xml:space="preserve">1.29874861240387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3174022436142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33061504364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34693670272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34382772445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3484913110733</t>
+    <t xml:space="preserve">1.31740212440491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33061492443085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34693682193756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34382796287537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34849119186401</t>
   </si>
   <si>
     <t xml:space="preserve">1.35121142864227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37258541584015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40067195892334</t>
+    <t xml:space="preserve">1.37258529663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40067207813263</t>
   </si>
   <si>
     <t xml:space="preserve">1.37502765655518</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">1.42306005954742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43323624134064</t>
+    <t xml:space="preserve">1.43323636054993</t>
   </si>
   <si>
     <t xml:space="preserve">1.45847368240356</t>
@@ -3176,7 +3176,7 @@
     <t xml:space="preserve">1.43771398067474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4491114616394</t>
+    <t xml:space="preserve">1.44911158084869</t>
   </si>
   <si>
     <t xml:space="preserve">1.44951856136322</t>
@@ -3185,19 +3185,19 @@
     <t xml:space="preserve">1.4572526216507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45765960216522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45521724224091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43120110034943</t>
+    <t xml:space="preserve">1.45765972137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4552173614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43120121955872</t>
   </si>
   <si>
     <t xml:space="preserve">1.4430056810379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44422686100006</t>
+    <t xml:space="preserve">1.44422698020935</t>
   </si>
   <si>
     <t xml:space="preserve">1.42713057994843</t>
@@ -3206,10 +3206,10 @@
     <t xml:space="preserve">1.41858232021332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40352153778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41288375854492</t>
+    <t xml:space="preserve">1.40352141857147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41288363933563</t>
   </si>
   <si>
     <t xml:space="preserve">1.41695427894592</t>
@@ -3218,37 +3218,37 @@
     <t xml:space="preserve">1.41898953914642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41329061985016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43527162075043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37950527667999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38072633743286</t>
+    <t xml:space="preserve">1.41329073905945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43527173995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3795051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38072621822357</t>
   </si>
   <si>
     <t xml:space="preserve">1.39945089817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41736125946045</t>
+    <t xml:space="preserve">1.41736137866974</t>
   </si>
   <si>
     <t xml:space="preserve">1.40392851829529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40148627758026</t>
+    <t xml:space="preserve">1.40148615837097</t>
   </si>
   <si>
     <t xml:space="preserve">1.34734785556793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3591525554657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38316869735718</t>
+    <t xml:space="preserve">1.35915243625641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38316857814789</t>
   </si>
   <si>
     <t xml:space="preserve">1.395787358284</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">1.47719812393188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47801244258881</t>
+    <t xml:space="preserve">1.47801232337952</t>
   </si>
   <si>
     <t xml:space="preserve">1.47394180297852</t>
@@ -3269,13 +3269,13 @@
     <t xml:space="preserve">1.47068536281586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47923338413239</t>
+    <t xml:space="preserve">1.47923350334167</t>
   </si>
   <si>
     <t xml:space="preserve">1.46824312210083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47964036464691</t>
+    <t xml:space="preserve">1.4796404838562</t>
   </si>
   <si>
     <t xml:space="preserve">1.49348032474518</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">1.50691306591034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52360236644745</t>
+    <t xml:space="preserve">1.52360224723816</t>
   </si>
   <si>
     <t xml:space="preserve">1.53866326808929</t>
@@ -3293,22 +3293,22 @@
     <t xml:space="preserve">1.54069864749908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55006086826324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58262503147125</t>
+    <t xml:space="preserve">1.55006074905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58262515068054</t>
   </si>
   <si>
     <t xml:space="preserve">1.58669567108154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56593596935272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5838463306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5549453496933</t>
+    <t xml:space="preserve">1.56593585014343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58384621143341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55494546890259</t>
   </si>
   <si>
     <t xml:space="preserve">1.53215026855469</t>
@@ -3317,10 +3317,10 @@
     <t xml:space="preserve">1.52726578712463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52889394760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52197408676147</t>
+    <t xml:space="preserve">1.52889406681061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52197420597076</t>
   </si>
   <si>
     <t xml:space="preserve">1.514240026474</t>
@@ -3329,13 +3329,13 @@
     <t xml:space="preserve">1.51912474632263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50650596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49755072593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.522381067276</t>
+    <t xml:space="preserve">1.50650608539581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49755084514618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52238118648529</t>
   </si>
   <si>
     <t xml:space="preserve">1.49307334423065</t>
@@ -3347,13 +3347,13 @@
     <t xml:space="preserve">1.5162752866745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48615348339081</t>
+    <t xml:space="preserve">1.48615336418152</t>
   </si>
   <si>
     <t xml:space="preserve">1.48940980434418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49063086509705</t>
+    <t xml:space="preserve">1.49063098430634</t>
   </si>
   <si>
     <t xml:space="preserve">1.42794466018677</t>
@@ -3380,34 +3380,34 @@
     <t xml:space="preserve">1.45643842220306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45562422275543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43812096118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44544816017151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44015622138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45684540271759</t>
+    <t xml:space="preserve">1.45562434196472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43812108039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44544804096222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44015634059906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45684552192688</t>
   </si>
   <si>
     <t xml:space="preserve">1.48737454414368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48533928394318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50406360626221</t>
+    <t xml:space="preserve">1.48533916473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5040637254715</t>
   </si>
   <si>
     <t xml:space="preserve">1.46417236328125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4450409412384</t>
+    <t xml:space="preserve">1.44504082202911</t>
   </si>
   <si>
     <t xml:space="preserve">1.47475576400757</t>
@@ -3434,13 +3434,13 @@
     <t xml:space="preserve">1.53662800788879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57407712936401</t>
+    <t xml:space="preserve">1.57407701015472</t>
   </si>
   <si>
     <t xml:space="preserve">1.55698072910309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55779469013214</t>
+    <t xml:space="preserve">1.55779480934143</t>
   </si>
   <si>
     <t xml:space="preserve">1.50732016563416</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">1.51953184604645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51546108722687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3921240568161</t>
+    <t xml:space="preserve">1.51546120643616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39212393760681</t>
   </si>
   <si>
     <t xml:space="preserve">1.40596377849579</t>
@@ -3485,22 +3485,22 @@
     <t xml:space="preserve">1.39538037776947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40637075901031</t>
+    <t xml:space="preserve">1.4063708782196</t>
   </si>
   <si>
     <t xml:space="preserve">1.45196080207825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43079400062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45806658267975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45440304279327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45399618148804</t>
+    <t xml:space="preserve">1.4307941198349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45806670188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45440316200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45399606227875</t>
   </si>
   <si>
     <t xml:space="preserve">1.42835175991058</t>
@@ -3509,28 +3509,28 @@
     <t xml:space="preserve">1.39130973815918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32699537277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34531283378601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34775519371033</t>
+    <t xml:space="preserve">1.32699525356293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34531271457672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34775507450104</t>
   </si>
   <si>
     <t xml:space="preserve">1.36810779571533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37177121639252</t>
+    <t xml:space="preserve">1.37177109718323</t>
   </si>
   <si>
     <t xml:space="preserve">1.39741563796997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4002650976181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40677785873413</t>
+    <t xml:space="preserve">1.40026497840881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40677797794342</t>
   </si>
   <si>
     <t xml:space="preserve">1.35548901557922</t>
@@ -3542,16 +3542,16 @@
     <t xml:space="preserve">1.35833835601807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37462067604065</t>
+    <t xml:space="preserve">1.37462055683136</t>
   </si>
   <si>
     <t xml:space="preserve">1.36770057678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35589623451233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35263979434967</t>
+    <t xml:space="preserve">1.35589611530304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35263967514038</t>
   </si>
   <si>
     <t xml:space="preserve">1.33310115337372</t>
@@ -3563,25 +3563,25 @@
     <t xml:space="preserve">1.35304665565491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34164917469025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30664253234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33269393444061</t>
+    <t xml:space="preserve">1.34164929389954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30664265155792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3326940536499</t>
   </si>
   <si>
     <t xml:space="preserve">1.3652583360672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41532588005066</t>
+    <t xml:space="preserve">1.41532599925995</t>
   </si>
   <si>
     <t xml:space="preserve">1.37380647659302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3672935962677</t>
+    <t xml:space="preserve">1.36729347705841</t>
   </si>
   <si>
     <t xml:space="preserve">1.37909817695618</t>
@@ -3590,16 +3590,16 @@
     <t xml:space="preserve">1.37624883651733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36973595619202</t>
+    <t xml:space="preserve">1.36973583698273</t>
   </si>
   <si>
     <t xml:space="preserve">1.33513641357422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30949211120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28262650966644</t>
+    <t xml:space="preserve">1.30949199199677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28262639045715</t>
   </si>
   <si>
     <t xml:space="preserve">1.30094385147095</t>
@@ -3617,10 +3617,10 @@
     <t xml:space="preserve">1.28913938999176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28425455093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28181219100952</t>
+    <t xml:space="preserve">1.28425467014313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28181231021881</t>
   </si>
   <si>
     <t xml:space="preserve">1.27652060985565</t>
@@ -3635,13 +3635,13 @@
     <t xml:space="preserve">1.25046920776367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22482478618622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.281405210495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3001297712326</t>
+    <t xml:space="preserve">1.22482490539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28140532970428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30012989044189</t>
   </si>
   <si>
     <t xml:space="preserve">1.25494682788849</t>
@@ -3650,16 +3650,16 @@
     <t xml:space="preserve">1.22848832607269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19918036460876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18249106407166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20243692398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25616800785065</t>
+    <t xml:space="preserve">1.19918048381805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18249118328094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20243680477142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25616788864136</t>
   </si>
   <si>
     <t xml:space="preserve">1.24639880657196</t>
@@ -3671,16 +3671,16 @@
     <t xml:space="preserve">1.23093068599701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22238266468048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22116136550903</t>
+    <t xml:space="preserve">1.22238254547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22116124629974</t>
   </si>
   <si>
     <t xml:space="preserve">1.21464848518372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23785054683685</t>
+    <t xml:space="preserve">1.23785066604614</t>
   </si>
   <si>
     <t xml:space="preserve">1.2508761882782</t>
@@ -3692,10 +3692,10 @@
     <t xml:space="preserve">1.22808122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23540818691254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25698208808899</t>
+    <t xml:space="preserve">1.23540830612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25698220729828</t>
   </si>
   <si>
     <t xml:space="preserve">1.27489244937897</t>
@@ -3704,31 +3704,31 @@
     <t xml:space="preserve">1.25779616832733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26553010940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25942444801331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28751122951508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29768741130829</t>
+    <t xml:space="preserve">1.26553022861481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2594245672226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28751111030579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29768753051758</t>
   </si>
   <si>
     <t xml:space="preserve">1.29809439182281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33554327487946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36281609535217</t>
+    <t xml:space="preserve">1.33554339408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36281597614288</t>
   </si>
   <si>
     <t xml:space="preserve">1.35223257541656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3571172952652</t>
+    <t xml:space="preserve">1.35711741447449</t>
   </si>
   <si>
     <t xml:space="preserve">1.34856915473938</t>
@@ -3743,13 +3743,13 @@
     <t xml:space="preserve">1.33961391448975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32129657268524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32455289363861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33432233333588</t>
+    <t xml:space="preserve">1.32129645347595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3245530128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33432221412659</t>
   </si>
   <si>
     <t xml:space="preserve">1.33106589317322</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">1.34327745437622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38561105728149</t>
+    <t xml:space="preserve">1.3856109380722</t>
   </si>
   <si>
     <t xml:space="preserve">1.33147275447845</t>
@@ -3794,22 +3794,22 @@
     <t xml:space="preserve">1.36872255802155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37862205505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38507843017578</t>
+    <t xml:space="preserve">1.378622174263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38507831096649</t>
   </si>
   <si>
     <t xml:space="preserve">1.3631272315979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35796225070953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34504973888397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32998502254486</t>
+    <t xml:space="preserve">1.35796213150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34504961967468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32998514175415</t>
   </si>
   <si>
     <t xml:space="preserve">1.31578135490417</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">1.33041560649872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31018590927124</t>
+    <t xml:space="preserve">1.31018602848053</t>
   </si>
   <si>
     <t xml:space="preserve">1.3123379945755</t>
@@ -3830,19 +3830,19 @@
     <t xml:space="preserve">1.270587682724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18708693981171</t>
+    <t xml:space="preserve">1.187087059021</t>
   </si>
   <si>
     <t xml:space="preserve">1.14921045303345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11047291755676</t>
+    <t xml:space="preserve">1.11047303676605</t>
   </si>
   <si>
     <t xml:space="preserve">1.15050172805786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11563789844513</t>
+    <t xml:space="preserve">1.11563801765442</t>
   </si>
   <si>
     <t xml:space="preserve">1.15437543392181</t>
@@ -3851,19 +3851,19 @@
     <t xml:space="preserve">1.091104388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06570971012115</t>
+    <t xml:space="preserve">1.06570982933044</t>
   </si>
   <si>
     <t xml:space="preserve">1.03945434093475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05581033229828</t>
+    <t xml:space="preserve">1.05581021308899</t>
   </si>
   <si>
     <t xml:space="preserve">1.10143435001373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08593928813934</t>
+    <t xml:space="preserve">1.08593940734863</t>
   </si>
   <si>
     <t xml:space="preserve">1.09540855884552</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">1.07517886161804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.043328166008</t>
+    <t xml:space="preserve">1.04332804679871</t>
   </si>
   <si>
     <t xml:space="preserve">1.06743133068085</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">1.02697229385376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00200819969177</t>
+    <t xml:space="preserve">1.00200831890106</t>
   </si>
   <si>
     <t xml:space="preserve">1.02352893352509</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">1.03601109981537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04074561595917</t>
+    <t xml:space="preserve">1.04074573516846</t>
   </si>
   <si>
     <t xml:space="preserve">1.05451893806458</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">1.02955484390259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05882322788239</t>
+    <t xml:space="preserve">1.0588231086731</t>
   </si>
   <si>
     <t xml:space="preserve">1.08120477199554</t>
@@ -3935,10 +3935,10 @@
     <t xml:space="preserve">1.07474851608276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09024357795715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06829237937927</t>
+    <t xml:space="preserve">1.09024345874786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06829226016998</t>
   </si>
   <si>
     <t xml:space="preserve">1.08636963367462</t>
@@ -3959,25 +3959,25 @@
     <t xml:space="preserve">1.10100388526917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10272550582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08292651176453</t>
+    <t xml:space="preserve">1.10272562503815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08292639255524</t>
   </si>
   <si>
     <t xml:space="preserve">1.06097519397736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06355774402618</t>
+    <t xml:space="preserve">1.06355762481689</t>
   </si>
   <si>
     <t xml:space="preserve">1.05839276313782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01707279682159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996843278408051</t>
+    <t xml:space="preserve">1.0170726776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996843218803406</t>
   </si>
   <si>
     <t xml:space="preserve">0.999425709247589</t>
@@ -3986,46 +3986,46 @@
     <t xml:space="preserve">0.963701248168945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946915090084076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968435704708099</t>
+    <t xml:space="preserve">0.946914970874786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968435883522034</t>
   </si>
   <si>
     <t xml:space="preserve">0.945623755455017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.932711243629456</t>
+    <t xml:space="preserve">0.9327113032341</t>
   </si>
   <si>
     <t xml:space="preserve">0.939167439937592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920229196548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965422928333282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975322484970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952510416507721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92625492811203</t>
+    <t xml:space="preserve">0.920229136943817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965422868728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975322425365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952510476112366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92625504732132</t>
   </si>
   <si>
     <t xml:space="preserve">0.930128753185272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913342595100403</t>
+    <t xml:space="preserve">0.913342535495758</t>
   </si>
   <si>
     <t xml:space="preserve">0.921950876712799</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923242032527924</t>
+    <t xml:space="preserve">0.923242151737213</t>
   </si>
   <si>
     <t xml:space="preserve">0.912051260471344</t>
@@ -4034,10 +4034,10 @@
     <t xml:space="preserve">0.882783055305481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888808846473694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852567791938782</t>
+    <t xml:space="preserve">0.888808906078339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852567851543427</t>
   </si>
   <si>
     <t xml:space="preserve">0.86298394203186</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">0.85377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860659718513489</t>
+    <t xml:space="preserve">0.860659658908844</t>
   </si>
   <si>
     <t xml:space="preserve">0.879339694976807</t>
@@ -4058,10 +4058,10 @@
     <t xml:space="preserve">0.868579208850861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.853256404399872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8353511095047</t>
+    <t xml:space="preserve">0.853256464004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835351169109344</t>
   </si>
   <si>
     <t xml:space="preserve">0.846542000770569</t>
@@ -4076,16 +4076,16 @@
     <t xml:space="preserve">0.825882017612457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863844692707062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.883643805980682</t>
+    <t xml:space="preserve">0.863844633102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883643865585327</t>
   </si>
   <si>
     <t xml:space="preserve">0.879770040512085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871161758899689</t>
+    <t xml:space="preserve">0.871161699295044</t>
   </si>
   <si>
     <t xml:space="preserve">0.896986782550812</t>
@@ -4094,28 +4094,28 @@
     <t xml:space="preserve">0.949497520923615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948206186294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982209086418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971018373966217</t>
+    <t xml:space="preserve">0.948206305503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982209146022797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971018254756927</t>
   </si>
   <si>
     <t xml:space="preserve">0.965853273868561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966714143753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966283679008484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955092966556549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972309470176697</t>
+    <t xml:space="preserve">0.966714084148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966283738613129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955092906951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972309589385986</t>
   </si>
   <si>
     <t xml:space="preserve">0.993830323219299</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">1.01061654090881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11176431179047</t>
+    <t xml:space="preserve">1.11176419258118</t>
   </si>
   <si>
     <t xml:space="preserve">1.1160683631897</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">1.10616886615753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.126828789711</t>
+    <t xml:space="preserve">1.12682890892029</t>
   </si>
   <si>
     <t xml:space="preserve">1.1220942735672</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">1.11391639709473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13974118232727</t>
+    <t xml:space="preserve">1.13974130153656</t>
   </si>
   <si>
     <t xml:space="preserve">1.11865091323853</t>
@@ -4169,7 +4169,7 @@
     <t xml:space="preserve">1.12898087501526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13586759567261</t>
+    <t xml:space="preserve">1.13586747646332</t>
   </si>
   <si>
     <t xml:space="preserve">1.13027215003967</t>
@@ -4178,13 +4178,13 @@
     <t xml:space="preserve">1.13543713092804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12381601333618</t>
+    <t xml:space="preserve">1.12381589412689</t>
   </si>
   <si>
     <t xml:space="preserve">1.11951184272766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12166380882263</t>
+    <t xml:space="preserve">1.12166392803192</t>
   </si>
   <si>
     <t xml:space="preserve">1.12984180450439</t>
@@ -4193,10 +4193,10 @@
     <t xml:space="preserve">1.14490628242493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11692929267883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09282600879669</t>
+    <t xml:space="preserve">1.11692917346954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0928258895874</t>
   </si>
   <si>
     <t xml:space="preserve">1.07603967189789</t>
@@ -4208,37 +4208,37 @@
     <t xml:space="preserve">1.06958341598511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07173562049866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09971272945404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12467682361603</t>
+    <t xml:space="preserve">1.07173550128937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09971261024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12467670440674</t>
   </si>
   <si>
     <t xml:space="preserve">1.12553763389587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13888037204742</t>
+    <t xml:space="preserve">1.13888049125671</t>
   </si>
   <si>
     <t xml:space="preserve">1.14705836772919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18837833404541</t>
+    <t xml:space="preserve">1.18837821483612</t>
   </si>
   <si>
     <t xml:space="preserve">1.19354331493378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19827771186829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20042991638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20516455173492</t>
+    <t xml:space="preserve">1.19827783107758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20043003559113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20516443252563</t>
   </si>
   <si>
     <t xml:space="preserve">1.21032953262329</t>
@@ -4247,22 +4247,22 @@
     <t xml:space="preserve">1.17245292663574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15093207359314</t>
+    <t xml:space="preserve">1.15093219280243</t>
   </si>
   <si>
     <t xml:space="preserve">1.18192207813263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19096076488495</t>
+    <t xml:space="preserve">1.19096088409424</t>
   </si>
   <si>
     <t xml:space="preserve">1.20387327671051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20430386066437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21119022369385</t>
+    <t xml:space="preserve">1.20430374145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21119034290314</t>
   </si>
   <si>
     <t xml:space="preserve">1.19483458995819</t>
@@ -4271,16 +4271,16 @@
     <t xml:space="preserve">1.18665671348572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20989918708801</t>
+    <t xml:space="preserve">1.20989906787872</t>
   </si>
   <si>
     <t xml:space="preserve">1.18794786930084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20344281196594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21506404876709</t>
+    <t xml:space="preserve">1.20344293117523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21506416797638</t>
   </si>
   <si>
     <t xml:space="preserve">1.20903825759888</t>
@@ -4301,31 +4301,31 @@
     <t xml:space="preserve">1.19225203990936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17976987361908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18579590320587</t>
+    <t xml:space="preserve">1.17976999282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18579578399658</t>
   </si>
   <si>
     <t xml:space="preserve">1.18966948986053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20215165615082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20129084587097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16944003105164</t>
+    <t xml:space="preserve">1.20215153694153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20129072666168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16943991184235</t>
   </si>
   <si>
     <t xml:space="preserve">1.18364369869232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1978474855423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18149149417877</t>
+    <t xml:space="preserve">1.19784736633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18149161338806</t>
   </si>
   <si>
     <t xml:space="preserve">1.18493497371674</t>
@@ -4337,7 +4337,7 @@
     <t xml:space="preserve">1.16814875602722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15738821029663</t>
+    <t xml:space="preserve">1.15738832950592</t>
   </si>
   <si>
     <t xml:space="preserve">1.18278288841248</t>
@@ -4349,7 +4349,7 @@
     <t xml:space="preserve">1.25078856945038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26240992546082</t>
+    <t xml:space="preserve">1.26240980625153</t>
   </si>
   <si>
     <t xml:space="preserve">1.23658490180969</t>
@@ -4367,7 +4367,7 @@
     <t xml:space="preserve">1.21678566932678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22496354579926</t>
+    <t xml:space="preserve">1.22496366500854</t>
   </si>
   <si>
     <t xml:space="preserve">1.25121903419495</t>
@@ -4379,19 +4379,19 @@
     <t xml:space="preserve">1.25853610038757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26714444160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29426074028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32869386672974</t>
+    <t xml:space="preserve">1.26714432239532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29426062107086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32869374752045</t>
   </si>
   <si>
     <t xml:space="preserve">1.33256757259369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33730220794678</t>
+    <t xml:space="preserve">1.33730232715607</t>
   </si>
   <si>
     <t xml:space="preserve">1.31664216518402</t>
@@ -4400,7 +4400,7 @@
     <t xml:space="preserve">1.32137680053711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31922483444214</t>
+    <t xml:space="preserve">1.31922471523285</t>
   </si>
   <si>
     <t xml:space="preserve">1.35150599479675</t>
@@ -4409,13 +4409,13 @@
     <t xml:space="preserve">1.33988463878632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35279715061188</t>
+    <t xml:space="preserve">1.35279703140259</t>
   </si>
   <si>
     <t xml:space="preserve">1.35968375205994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3523668050766</t>
+    <t xml:space="preserve">1.35236668586731</t>
   </si>
   <si>
     <t xml:space="preserve">1.36614012718201</t>
@@ -4424,13 +4424,13 @@
     <t xml:space="preserve">1.37733089923859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34332811832428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36786162853241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36829221248627</t>
+    <t xml:space="preserve">1.34332799911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3678617477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36829209327698</t>
   </si>
   <si>
     <t xml:space="preserve">1.3880912065506</t>
@@ -4457,10 +4457,10 @@
     <t xml:space="preserve">1.44877994060516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43758916854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37905263900757</t>
+    <t xml:space="preserve">1.43758904933929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37905251979828</t>
   </si>
   <si>
     <t xml:space="preserve">1.41047286987305</t>
@@ -5940,6 +5940,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.32999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36199998855591</t>
   </si>
 </sst>
 </file>
@@ -71070,7 +71073,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6495601852</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>7382257</v>
@@ -71091,6 +71094,32 @@
         <v>1975</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.649375</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>11812539</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>2.37899994850159</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>2.33400011062622</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>2.33899998664856</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>2.36199998855591</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1976</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="1979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="1980">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765547633171082</t>
+    <t xml:space="preserve">0.765547692775726</t>
   </si>
   <si>
     <t xml:space="preserve">A2A.MI</t>
@@ -47,43 +47,43 @@
     <t xml:space="preserve">0.774303913116455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.76930034160614</t>
+    <t xml:space="preserve">0.76930046081543</t>
   </si>
   <si>
     <t xml:space="preserve">0.77743124961853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.772427558898926</t>
+    <t xml:space="preserve">0.772427618503571</t>
   </si>
   <si>
     <t xml:space="preserve">0.775554835796356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.736151695251465</t>
+    <t xml:space="preserve">0.73615175485611</t>
   </si>
   <si>
     <t xml:space="preserve">0.728020846843719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.708631873130798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701126575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.678610444068909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.686115860939026</t>
+    <t xml:space="preserve">0.708632051944733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701126635074615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678610503673553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.686115741729736</t>
   </si>
   <si>
     <t xml:space="preserve">0.662974238395691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669854164123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.673606932163239</t>
+    <t xml:space="preserve">0.669854283332825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.673606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">0.661723375320435</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">0.68986850976944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667352378368378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.688617646694183</t>
+    <t xml:space="preserve">0.667352497577667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.688617527484894</t>
   </si>
   <si>
     <t xml:space="preserve">0.689243137836456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.676108717918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.671105086803436</t>
+    <t xml:space="preserve">0.676108658313751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.671105146408081</t>
   </si>
   <si>
     <t xml:space="preserve">0.666727006435394</t>
@@ -113,52 +113,52 @@
     <t xml:space="preserve">0.643585443496704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612312972545624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597927808761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605745911598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610749423503876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614189445972443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627323865890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617942035198212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624822020530701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64671266078949</t>
+    <t xml:space="preserve">0.612313032150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597927689552307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605745851993561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610749363899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614189326763153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627323746681213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617942094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624821960926056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.646712720394135</t>
   </si>
   <si>
     <t xml:space="preserve">0.636080086231232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656719863414764</t>
+    <t xml:space="preserve">0.656719744205475</t>
   </si>
   <si>
     <t xml:space="preserve">0.645461738109589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641083657741547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647963523864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.657345235347748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661098003387451</t>
+    <t xml:space="preserve">0.641083598136902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.647963583469391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.657345294952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661097943782806</t>
   </si>
   <si>
     <t xml:space="preserve">0.672981381416321</t>
@@ -167,34 +167,34 @@
     <t xml:space="preserve">0.666101574897766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.664850533008575</t>
+    <t xml:space="preserve">0.66485059261322</t>
   </si>
   <si>
     <t xml:space="preserve">0.658596158027649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.651716291904449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654843628406525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.669228792190552</t>
+    <t xml:space="preserve">0.651716232299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654843509197235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.669228911399841</t>
   </si>
   <si>
     <t xml:space="preserve">0.713010013103485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.692995727062225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.691119492053986</t>
+    <t xml:space="preserve">0.69299578666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.691119432449341</t>
   </si>
   <si>
     <t xml:space="preserve">0.694246649742126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.697999358177185</t>
+    <t xml:space="preserve">0.69799941778183</t>
   </si>
   <si>
     <t xml:space="preserve">0.696123003959656</t>
@@ -203,16 +203,16 @@
     <t xml:space="preserve">0.703002870082855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.692370355129242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.699250340461731</t>
+    <t xml:space="preserve">0.692370295524597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.699250221252441</t>
   </si>
   <si>
     <t xml:space="preserve">0.714260935783386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714886367321014</t>
+    <t xml:space="preserve">0.714886486530304</t>
   </si>
   <si>
     <t xml:space="preserve">0.702377498149872</t>
@@ -221,88 +221,88 @@
     <t xml:space="preserve">0.705504715442657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.735526263713837</t>
+    <t xml:space="preserve">0.735526144504547</t>
   </si>
   <si>
     <t xml:space="preserve">0.740529775619507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.744282484054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748660564422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.738028168678284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750536918640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754289567470551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768049538135529</t>
+    <t xml:space="preserve">0.744282603263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748660624027252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.738027989864349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750536978244781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75428968667984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768049478530884</t>
   </si>
   <si>
     <t xml:space="preserve">0.757416784763336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766798496246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.752413272857666</t>
+    <t xml:space="preserve">0.766798555850983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.752413332462311</t>
   </si>
   <si>
     <t xml:space="preserve">0.781183838844299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778056561946869</t>
+    <t xml:space="preserve">0.778056621551514</t>
   </si>
   <si>
     <t xml:space="preserve">0.786187469959259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779307544231415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768674850463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755540549755096</t>
+    <t xml:space="preserve">0.779307425022125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768674969673157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755540430545807</t>
   </si>
   <si>
     <t xml:space="preserve">0.760544002056122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.764296770095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770551323890686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759293138980865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769925832748413</t>
+    <t xml:space="preserve">0.764296889305115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770551204681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75929319858551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769925713539124</t>
   </si>
   <si>
     <t xml:space="preserve">0.76116955280304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.767424046993256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747409760951996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751787781715393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754915118217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781809210777283</t>
+    <t xml:space="preserve">0.767423987388611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747409701347351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751788020133972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754915058612823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781809270381927</t>
   </si>
   <si>
     <t xml:space="preserve">0.801198184490204</t>
@@ -311,10 +311,10 @@
     <t xml:space="preserve">0.804950892925262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799321711063385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785561919212341</t>
+    <t xml:space="preserve">0.799321889877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78556215763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.796820104122162</t>
@@ -323,34 +323,34 @@
     <t xml:space="preserve">0.791816413402557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801823675632477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733649790287018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725519001483917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766306459903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759828746318817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750760138034821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778613924980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703473269939423</t>
+    <t xml:space="preserve">0.801823616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733649849891663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725519061088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766306340694427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759828805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750760197639465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778614103794098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703473210334778</t>
   </si>
   <si>
     <t xml:space="preserve">0.69246119260788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.70541650056839</t>
+    <t xml:space="preserve">0.705416560173035</t>
   </si>
   <si>
     <t xml:space="preserve">0.730031549930573</t>
@@ -362,37 +362,37 @@
     <t xml:space="preserve">0.762419939041138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769545316696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757885456085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742986917495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742339134216309</t>
+    <t xml:space="preserve">0.769545257091522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75788551568985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742986857891083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742339253425598</t>
   </si>
   <si>
     <t xml:space="preserve">0.758533298969269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.777318477630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77407968044281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776022911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78379613161087</t>
+    <t xml:space="preserve">0.77731853723526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774079620838165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776022970676422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783796191215515</t>
   </si>
   <si>
     <t xml:space="preserve">0.779909551143646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.790273785591125</t>
+    <t xml:space="preserve">0.79027384519577</t>
   </si>
   <si>
     <t xml:space="preserve">0.789626061916351</t>
@@ -404,37 +404,37 @@
     <t xml:space="preserve">0.805172443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807763457298279</t>
+    <t xml:space="preserve">0.807763397693634</t>
   </si>
   <si>
     <t xml:space="preserve">0.822661995887756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817479908466339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820718824863434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.822014391422272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809706628322601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814241111278534</t>
+    <t xml:space="preserve">0.81747978925705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820718705654144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.822014331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809706807136536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814241051673889</t>
   </si>
   <si>
     <t xml:space="preserve">0.816184401512146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804524540901184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801285743713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812945663928986</t>
+    <t xml:space="preserve">0.804524660110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801285803318024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812945544719696</t>
   </si>
   <si>
     <t xml:space="preserve">0.801933526992798</t>
@@ -446,16 +446,16 @@
     <t xml:space="preserve">0.788330495357513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771488606929779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783148229122162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782500624656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781852900981903</t>
+    <t xml:space="preserve">0.771488547325134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783148407936096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782500505447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781852781772614</t>
   </si>
   <si>
     <t xml:space="preserve">0.770193099975586</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">0.785091698169708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.795455992221832</t>
+    <t xml:space="preserve">0.795455932617188</t>
   </si>
   <si>
     <t xml:space="preserve">0.811002194881439</t>
@@ -473,49 +473,49 @@
     <t xml:space="preserve">0.794808149337769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.796103596687317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798694729804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802581310272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7909215092659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796751439571381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799342453479767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810354471206665</t>
+    <t xml:space="preserve">0.796103656291962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798694789409637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802581250667572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790921568870544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796751379966736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799342513084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81035453081131</t>
   </si>
   <si>
     <t xml:space="preserve">0.78055727481842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784443795681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785739421844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827196419239044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81359326839447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800638020038605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7973992228508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803876936435699</t>
+    <t xml:space="preserve">0.784443855285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785739541053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827196478843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813593327999115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800637900829315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79739910364151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803876876831055</t>
   </si>
   <si>
     <t xml:space="preserve">0.807115733623505</t>
@@ -524,19 +524,19 @@
     <t xml:space="preserve">0.761124312877655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77084082365036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.731327056884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735861599445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.720315039157867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72161066532135</t>
+    <t xml:space="preserve">0.770840883255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73132711648941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735861539840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.720315098762512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721610546112061</t>
   </si>
   <si>
     <t xml:space="preserve">0.719019591808319</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">0.696347773075104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696995496749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.709950745105743</t>
+    <t xml:space="preserve">0.696995556354523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.709950923919678</t>
   </si>
   <si>
     <t xml:space="preserve">0.713837504386902</t>
@@ -557,16 +557,16 @@
     <t xml:space="preserve">0.711894094944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.707359790802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728735983371735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715780794620514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722258388996124</t>
+    <t xml:space="preserve">0.707359850406647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728736042976379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715780854225159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722258448600769</t>
   </si>
   <si>
     <t xml:space="preserve">0.765010893344879</t>
@@ -575,88 +575,88 @@
     <t xml:space="preserve">0.7546466588974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.755294501781464</t>
+    <t xml:space="preserve">0.755294442176819</t>
   </si>
   <si>
     <t xml:space="preserve">0.78768265247345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776670694351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772136390209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78703498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816832363605499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819423258304596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799990236759186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824605464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838856041431427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831730842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832378506660461</t>
+    <t xml:space="preserve">0.776670813560486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772136270999908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787034928798676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816832184791565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819423198699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799990296363831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824605345726013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838856339454651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831730782985687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832378566265106</t>
   </si>
   <si>
     <t xml:space="preserve">0.840151786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.848572671413422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841447234153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844686090946198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830435276031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798047006130219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815536618232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820070922374725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806467890739441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811650156974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836265087127686</t>
+    <t xml:space="preserve">0.848572731018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841447353363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844686031341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830435216426849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798046886920929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815536499023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820071041584015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80646800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811650097370148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83626514673233</t>
   </si>
   <si>
     <t xml:space="preserve">0.844038307666779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837560534477234</t>
+    <t xml:space="preserve">0.837560713291168</t>
   </si>
   <si>
     <t xml:space="preserve">0.836912930011749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.821366548538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828492045402527</t>
+    <t xml:space="preserve">0.821366488933563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828491866588593</t>
   </si>
   <si>
     <t xml:space="preserve">0.825900852680206</t>
@@ -668,175 +668,175 @@
     <t xml:space="preserve">0.84662938117981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849220275878906</t>
+    <t xml:space="preserve">0.849220395088196</t>
   </si>
   <si>
     <t xml:space="preserve">0.864766776561737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867357850074768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868005752563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870596766471863</t>
+    <t xml:space="preserve">0.867357909679413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868005633354187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870596647262573</t>
   </si>
   <si>
     <t xml:space="preserve">0.857641398906708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.865414619445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866710126399994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85310697555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855698108673096</t>
+    <t xml:space="preserve">0.865414559841156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866710186004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853107094764709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855698049068451</t>
   </si>
   <si>
     <t xml:space="preserve">0.858289182186127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860232412815094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872539877891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874483346939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887438714504242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893916249275208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89262068271637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912701487541199</t>
+    <t xml:space="preserve">0.860232472419739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87253999710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874483406543732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887438654899597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893916130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892620742321014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912701427936554</t>
   </si>
   <si>
     <t xml:space="preserve">0.909462571144104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908166944980621</t>
+    <t xml:space="preserve">0.908167123794556</t>
   </si>
   <si>
     <t xml:space="preserve">0.919826745986938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91853129863739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87577873468399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877722144126892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891972899436951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884847640991211</t>
+    <t xml:space="preserve">0.918531477451324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875778794288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877722024917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.891972839832306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884847581386566</t>
   </si>
   <si>
     <t xml:space="preserve">0.895211815834045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.884199738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876426756381989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862175703048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856345891952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88225644826889</t>
+    <t xml:space="preserve">0.884199678897858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876426458358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862175762653351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856345951557159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882256627082825</t>
   </si>
   <si>
     <t xml:space="preserve">0.89909827709198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.890677392482758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926952362060547</t>
+    <t xml:space="preserve">0.890677332878113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926952183246613</t>
   </si>
   <si>
     <t xml:space="preserve">0.915292501449585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917235732078552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966465890407562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958045065402985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965170562267303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9612837433815</t>
+    <t xml:space="preserve">0.917235970497131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966466069221497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95804488658905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965170443058014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961283802986145</t>
   </si>
   <si>
     <t xml:space="preserve">0.963227152824402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941850960254669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941203117370605</t>
+    <t xml:space="preserve">0.941850900650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941202998161316</t>
   </si>
   <si>
     <t xml:space="preserve">0.958692729473114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982278108596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988308489322662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997018992900848</t>
+    <t xml:space="preserve">0.982278227806091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988308548927307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997019052505493</t>
   </si>
   <si>
     <t xml:space="preserve">1.00036919116974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992998898029327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96820729970932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981608092784882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986298501491547</t>
+    <t xml:space="preserve">0.992998778820038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96820741891861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981608211994171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986298382282257</t>
   </si>
   <si>
     <t xml:space="preserve">0.988978505134583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989648580551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97490793466568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999699175357819</t>
+    <t xml:space="preserve">0.989648520946503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97490781545639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999699294567108</t>
   </si>
   <si>
     <t xml:space="preserve">1.00505948066711</t>
@@ -845,199 +845,199 @@
     <t xml:space="preserve">0.998359203338623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997689008712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00170934200287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00706970691681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02047049999237</t>
+    <t xml:space="preserve">0.997688949108124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00170922279358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00706958770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02047038078308</t>
   </si>
   <si>
     <t xml:space="preserve">1.02985095977783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0177903175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995008885860443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999029219150543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976917803287506</t>
+    <t xml:space="preserve">1.01779043674469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995008826255798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999029278755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976917862892151</t>
   </si>
   <si>
     <t xml:space="preserve">0.974237680435181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970217287540436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965527236461639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960836887359619</t>
+    <t xml:space="preserve">0.970217406749725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965527176856995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960837006568909</t>
   </si>
   <si>
     <t xml:space="preserve">0.961506903171539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96418708562851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980268239974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978927910327911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984958291053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972897469997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960166931152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958826839923859</t>
+    <t xml:space="preserve">0.964187145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980268120765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978927850723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984958469867706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972897589206696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960166752338409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958826720714569</t>
   </si>
   <si>
     <t xml:space="preserve">0.951456308364868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955476522445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949446260929108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963517010211945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950116157531738</t>
+    <t xml:space="preserve">0.955476582050323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949446201324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963517129421234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950116455554962</t>
   </si>
   <si>
     <t xml:space="preserve">0.953466594219208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.956816494464874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958156824111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952796518802643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962176918983459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944755971431732</t>
+    <t xml:space="preserve">0.956816613674164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958156764507294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952796459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962176978588104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944756031036377</t>
   </si>
   <si>
     <t xml:space="preserve">0.931355178356171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948106229305267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954136490821838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957486689090729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939395606517792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946766138076782</t>
+    <t xml:space="preserve">0.948106169700623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954136610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957486748695374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939395666122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946766078472137</t>
   </si>
   <si>
     <t xml:space="preserve">0.934705317020416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.928675055503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924654722213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932695090770721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945425987243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959496796131134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973567605018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978257894515991</t>
+    <t xml:space="preserve">0.928674936294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9246546626091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932695209980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945426046848297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959496855735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973567485809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978257954120636</t>
   </si>
   <si>
     <t xml:space="preserve">0.993668913841248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984288215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983618199825287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994338870048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977587878704071</t>
+    <t xml:space="preserve">0.984288275241852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983618259429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994338810443878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977587938308716</t>
   </si>
   <si>
     <t xml:space="preserve">0.980938076972961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97222775220871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966197311878204</t>
+    <t xml:space="preserve">0.972227573394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96619725227356</t>
   </si>
   <si>
     <t xml:space="preserve">0.969547510147095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96887743473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9715576171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995679020881653</t>
+    <t xml:space="preserve">0.968877553939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971557676792145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995678961277008</t>
   </si>
   <si>
     <t xml:space="preserve">0.992328703403473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966867327690125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02114069461823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01041984558105</t>
+    <t xml:space="preserve">0.96686726808548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02114057540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01041972637177</t>
   </si>
   <si>
     <t xml:space="preserve">1.01444017887115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02181053161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02382051944733</t>
+    <t xml:space="preserve">1.02181041240692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02382063865662</t>
   </si>
   <si>
     <t xml:space="preserve">1.0285108089447</t>
@@ -1046,10 +1046,10 @@
     <t xml:space="preserve">1.03320133686066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03923153877258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02650094032288</t>
+    <t xml:space="preserve">1.03923165798187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0265007019043</t>
   </si>
   <si>
     <t xml:space="preserve">1.0553126335144</t>
@@ -1064,67 +1064,67 @@
     <t xml:space="preserve">1.05330240726471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06804323196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07273352146149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08613443374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09551501274109</t>
+    <t xml:space="preserve">1.0680433511734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0727334022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08613431453705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09551477432251</t>
   </si>
   <si>
     <t xml:space="preserve">1.08345413208008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08211421966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05397248268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0600026845932</t>
+    <t xml:space="preserve">1.08211410045624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0539722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06000280380249</t>
   </si>
   <si>
     <t xml:space="preserve">1.04392182826996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04861211776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04660189151764</t>
+    <t xml:space="preserve">1.04861235618591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04660201072693</t>
   </si>
   <si>
     <t xml:space="preserve">1.03990161418915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04258167743683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01980042457581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01578032970428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05196225643158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06737339496613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06603300571442</t>
+    <t xml:space="preserve">1.04258179664612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01980030536652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01578009128571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05196237564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06737327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06603312492371</t>
   </si>
   <si>
     <t xml:space="preserve">1.02449071407318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01846039295197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02784085273743</t>
+    <t xml:space="preserve">1.01846027374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02784097194672</t>
   </si>
   <si>
     <t xml:space="preserve">1.05665254592896</t>
@@ -1136,34 +1136,34 @@
     <t xml:space="preserve">1.07742381095886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07943379878998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06938326358795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05933284759521</t>
+    <t xml:space="preserve">1.07943391799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06938314437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05933260917664</t>
   </si>
   <si>
     <t xml:space="preserve">1.03856146335602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02683579921722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03588151931763</t>
+    <t xml:space="preserve">1.02683591842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03588140010834</t>
   </si>
   <si>
     <t xml:space="preserve">1.04191172122955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996348857879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971222460269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995343923568726</t>
+    <t xml:space="preserve">0.996349036693573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971222400665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995343863964081</t>
   </si>
   <si>
     <t xml:space="preserve">0.944420874118805</t>
@@ -1172,28 +1172,28 @@
     <t xml:space="preserve">0.953131496906281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941405773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959831893444061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946431159973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957821786403656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950451254844666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936380505561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967202246189117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991323888301849</t>
+    <t xml:space="preserve">0.941405713558197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959831953048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9464311003685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957821547985077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950451135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936380445957184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967202365398407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991323828697205</t>
   </si>
   <si>
     <t xml:space="preserve">0.975577831268311</t>
@@ -1211,16 +1211,16 @@
     <t xml:space="preserve">0.991658687591553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00673472881317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999364256858826</t>
+    <t xml:space="preserve">1.00673460960388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999364376068115</t>
   </si>
   <si>
     <t xml:space="preserve">1.04023659229279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04157686233521</t>
+    <t xml:space="preserve">1.04157662391663</t>
   </si>
   <si>
     <t xml:space="preserve">1.04224681854248</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">1.04961717128754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04995226860046</t>
+    <t xml:space="preserve">1.04995214939117</t>
   </si>
   <si>
     <t xml:space="preserve">1.06268298625946</t>
@@ -1244,100 +1244,100 @@
     <t xml:space="preserve">1.06335306167603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07407367229462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08043885231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08546435832977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09048962593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09484469890594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09819507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09853005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12198150157928</t>
+    <t xml:space="preserve">1.07407355308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08043897151947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08546423912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0904895067215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09484481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09819519519806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0985301733017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12198138237</t>
   </si>
   <si>
     <t xml:space="preserve">1.11762619018555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1172913312912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1072404384613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10757553577423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12265157699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13002192974091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10992074012756</t>
+    <t xml:space="preserve">1.11729109287262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10724055767059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10757565498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12265145778656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13002181053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10992085933685</t>
   </si>
   <si>
     <t xml:space="preserve">1.11829614639282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05732250213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03387117385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03895270824432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05287528038025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04208528995514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04730618000031</t>
+    <t xml:space="preserve">1.05732262134552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03387141227722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0389529466629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05287516117096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04208540916443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04730606079102</t>
   </si>
   <si>
     <t xml:space="preserve">1.02572667598724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00693142414093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980827271938324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998926341533661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01076030731201</t>
+    <t xml:space="preserve">1.00693166255951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980827033519745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998926281929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01076006889343</t>
   </si>
   <si>
     <t xml:space="preserve">1.00484323501587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02920722961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00936794281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00658333301544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999622344970703</t>
+    <t xml:space="preserve">1.02920734882355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00936806201935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00658345222473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999622404575348</t>
   </si>
   <si>
     <t xml:space="preserve">0.968993186950684</t>
@@ -1346,22 +1346,22 @@
     <t xml:space="preserve">1.01598107814789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02398633956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03164374828339</t>
+    <t xml:space="preserve">1.02398645877838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0316436290741</t>
   </si>
   <si>
     <t xml:space="preserve">1.02851104736328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0198096036911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04382586479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0466103553772</t>
+    <t xml:space="preserve">1.01980972290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04382574558258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04661011695862</t>
   </si>
   <si>
     <t xml:space="preserve">1.02363836765289</t>
@@ -1370,52 +1370,52 @@
     <t xml:space="preserve">1.02537858486176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00588750839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01250040531158</t>
+    <t xml:space="preserve">1.00588738918304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01250052452087</t>
   </si>
   <si>
     <t xml:space="preserve">1.02120196819305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02642273902893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03373193740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01389253139496</t>
+    <t xml:space="preserve">1.02642285823822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03373217582703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01389265060425</t>
   </si>
   <si>
     <t xml:space="preserve">1.03860485553741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0511349439621</t>
+    <t xml:space="preserve">1.05113506317139</t>
   </si>
   <si>
     <t xml:space="preserve">1.06122851371765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07236635684967</t>
+    <t xml:space="preserve">1.07236647605896</t>
   </si>
   <si>
     <t xml:space="preserve">1.06018435955048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0626208782196</t>
+    <t xml:space="preserve">1.06262075901031</t>
   </si>
   <si>
     <t xml:space="preserve">1.05600762367249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07375860214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0671454668045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07863140106201</t>
+    <t xml:space="preserve">1.07375884056091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06714558601379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0786315202713</t>
   </si>
   <si>
     <t xml:space="preserve">1.09290182590485</t>
@@ -1427,34 +1427,34 @@
     <t xml:space="preserve">1.10160326957703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08420026302338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04835045337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06157648563385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07201838493347</t>
+    <t xml:space="preserve">1.08420050144196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04835057258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06157672405243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07201826572418</t>
   </si>
   <si>
     <t xml:space="preserve">1.07584702968597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0713222026825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09394609928131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08106780052185</t>
+    <t xml:space="preserve">1.07132232189178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0939462184906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08106791973114</t>
   </si>
   <si>
     <t xml:space="preserve">1.09011733531952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0824601650238</t>
+    <t xml:space="preserve">1.08246004581451</t>
   </si>
   <si>
     <t xml:space="preserve">1.10299551486969</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">1.12005043029785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12387907505035</t>
+    <t xml:space="preserve">1.12387895584106</t>
   </si>
   <si>
     <t xml:space="preserve">1.10473585128784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10612809658051</t>
+    <t xml:space="preserve">1.10612821578979</t>
   </si>
   <si>
     <t xml:space="preserve">1.11134910583496</t>
@@ -1484,49 +1484,49 @@
     <t xml:space="preserve">1.08837723731995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08802902698517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08942127227783</t>
+    <t xml:space="preserve">1.08802890777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08942115306854</t>
   </si>
   <si>
     <t xml:space="preserve">1.07549893856049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06540524959564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03338384628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04243338108063</t>
+    <t xml:space="preserve">1.06540536880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03338396549225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04243326187134</t>
   </si>
   <si>
     <t xml:space="preserve">1.02155005931854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03094732761383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04173731803894</t>
+    <t xml:space="preserve">1.03094756603241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04173743724823</t>
   </si>
   <si>
     <t xml:space="preserve">1.05705177783966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0789794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09220576286316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09116148948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08454847335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08141589164734</t>
+    <t xml:space="preserve">1.07897961139679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09220564365387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09116160869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08454835414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08141613006592</t>
   </si>
   <si>
     <t xml:space="preserve">1.09847068786621</t>
@@ -1547,76 +1547,76 @@
     <t xml:space="preserve">1.07758736610413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06923389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04069328308105</t>
+    <t xml:space="preserve">1.06923401355743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04069304466248</t>
   </si>
   <si>
     <t xml:space="preserve">1.03199172019958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04452180862427</t>
+    <t xml:space="preserve">1.04452192783356</t>
   </si>
   <si>
     <t xml:space="preserve">1.04417383670807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05183100700378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03616833686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05844402313232</t>
+    <t xml:space="preserve">1.05183124542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03616857528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05844414234161</t>
   </si>
   <si>
     <t xml:space="preserve">1.03442811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00310289859772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991616904735565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00832378864288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01424074172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01772141456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01354455947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993705451488495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988136410713196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977346658706665</t>
+    <t xml:space="preserve">1.00310277938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9916170835495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00832366943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01424098014832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01772117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01354467868805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993705332279205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988136351108551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977346837520599</t>
   </si>
   <si>
     <t xml:space="preserve">1.00553917884827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9860480427742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989528656005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992313086986542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98291540145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991964936256409</t>
+    <t xml:space="preserve">0.986047983169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989528775215149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992313206195831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982915341854095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991965174674988</t>
   </si>
   <si>
     <t xml:space="preserve">1.01319658756256</t>
@@ -1625,19 +1625,19 @@
     <t xml:space="preserve">1.00414705276489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02050578594208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01563310623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03512418270111</t>
+    <t xml:space="preserve">1.0205055475235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0156329870224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03512406349182</t>
   </si>
   <si>
     <t xml:space="preserve">1.0393009185791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05252707004547</t>
+    <t xml:space="preserve">1.05252718925476</t>
   </si>
   <si>
     <t xml:space="preserve">1.05461537837982</t>
@@ -1646,13 +1646,13 @@
     <t xml:space="preserve">1.03721261024475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0271190404892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03999710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06610143184662</t>
+    <t xml:space="preserve">1.02711892127991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0399968624115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06610131263733</t>
   </si>
   <si>
     <t xml:space="preserve">1.06088054180145</t>
@@ -1661,46 +1661,46 @@
     <t xml:space="preserve">1.04034519195557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03233981132507</t>
+    <t xml:space="preserve">1.03233969211578</t>
   </si>
   <si>
     <t xml:space="preserve">1.04278147220612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0434775352478</t>
+    <t xml:space="preserve">1.04347765445709</t>
   </si>
   <si>
     <t xml:space="preserve">1.07410669326782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10090708732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11761391162872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12701153755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11378526687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10647618770599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12318289279938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13118815422058</t>
+    <t xml:space="preserve">1.10090720653534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11761403083801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12701141834259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11378538608551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1064760684967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12318301200867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13118827342987</t>
   </si>
   <si>
     <t xml:space="preserve">1.11448132991791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08872509002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.094642162323</t>
+    <t xml:space="preserve">1.08872520923615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09464204311371</t>
   </si>
   <si>
     <t xml:space="preserve">1.11622178554535</t>
@@ -1709,52 +1709,52 @@
     <t xml:space="preserve">1.1183100938797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13501679897308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13675725460052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1381493806839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14302217960358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10403954982758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10891270637512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09951496124268</t>
+    <t xml:space="preserve">1.13501691818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13675713539124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13814949989319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14302206039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10403978824615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10891258716583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09951484203339</t>
   </si>
   <si>
     <t xml:space="preserve">1.10195136070251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09916698932648</t>
+    <t xml:space="preserve">1.09916687011719</t>
   </si>
   <si>
     <t xml:space="preserve">1.0949901342392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10578012466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09185779094696</t>
+    <t xml:space="preserve">1.10578000545502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09185755252838</t>
   </si>
   <si>
     <t xml:space="preserve">1.07793533802032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08071982860565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08663666248322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06227278709412</t>
+    <t xml:space="preserve">1.08071970939636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08663690090179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06227266788483</t>
   </si>
   <si>
     <t xml:space="preserve">1.08280825614929</t>
@@ -1763,34 +1763,34 @@
     <t xml:space="preserve">1.09742665290833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10021114349365</t>
+    <t xml:space="preserve">1.10021102428436</t>
   </si>
   <si>
     <t xml:space="preserve">1.09777462482452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10369157791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11100089550018</t>
+    <t xml:space="preserve">1.10369181632996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11100101470947</t>
   </si>
   <si>
     <t xml:space="preserve">1.10543191432953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08594059944153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09568619728088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08907318115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11726605892181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12074637413025</t>
+    <t xml:space="preserve">1.08594071865082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09568631649017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08907330036163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11726582050323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12074661254883</t>
   </si>
   <si>
     <t xml:space="preserve">1.10752022266388</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">1.1103048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.121790766716</t>
+    <t xml:space="preserve">1.12179064750671</t>
   </si>
   <si>
     <t xml:space="preserve">1.11935424804688</t>
@@ -1808,10 +1808,10 @@
     <t xml:space="preserve">1.13571298122406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13536512851715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13084018230438</t>
+    <t xml:space="preserve">1.13536500930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13084030151367</t>
   </si>
   <si>
     <t xml:space="preserve">1.13223242759705</t>
@@ -1820,16 +1820,16 @@
     <t xml:space="preserve">1.14754700660706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06331694126129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05391943454742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04626214504242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05426740646362</t>
+    <t xml:space="preserve">1.063316822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05391931533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04626202583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05426752567291</t>
   </si>
   <si>
     <t xml:space="preserve">1.04869854450226</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">1.02433454990387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01946151256561</t>
+    <t xml:space="preserve">1.0194616317749</t>
   </si>
   <si>
     <t xml:space="preserve">1.01632905006409</t>
@@ -1847,10 +1847,10 @@
     <t xml:space="preserve">1.00379908084869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997882127761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00727963447571</t>
+    <t xml:space="preserve">0.997881948947906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.007279753685</t>
   </si>
   <si>
     <t xml:space="preserve">1.02015769481659</t>
@@ -1859,19 +1859,19 @@
     <t xml:space="preserve">1.07654321193695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08517634868622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09720551967621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09647655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06622123718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08116674423218</t>
+    <t xml:space="preserve">1.08517646789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09720540046692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09647643566132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06622135639191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0811665058136</t>
   </si>
   <si>
     <t xml:space="preserve">1.07205379009247</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">1.06038904190063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05127608776093</t>
+    <t xml:space="preserve">1.05127596855164</t>
   </si>
   <si>
     <t xml:space="preserve">1.06403422355652</t>
@@ -1892,28 +1892,28 @@
     <t xml:space="preserve">1.08043766021729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09793448448181</t>
+    <t xml:space="preserve">1.0979346036911</t>
   </si>
   <si>
     <t xml:space="preserve">1.0986635684967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10449600219727</t>
+    <t xml:space="preserve">1.10449588298798</t>
   </si>
   <si>
     <t xml:space="preserve">1.10048627853394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10230886936188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09574747085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09829914569855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13219952583313</t>
+    <t xml:space="preserve">1.10230875015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09574735164642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09829902648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13219964504242</t>
   </si>
   <si>
     <t xml:space="preserve">1.12563824653625</t>
@@ -1928,37 +1928,37 @@
     <t xml:space="preserve">1.13584470748901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11944139003754</t>
+    <t xml:space="preserve">1.11944127082825</t>
   </si>
   <si>
     <t xml:space="preserve">1.11543154716492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10376703739166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11251544952393</t>
+    <t xml:space="preserve">1.10376679897308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11251533031464</t>
   </si>
   <si>
     <t xml:space="preserve">1.11069273948669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13511562347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1500608921051</t>
+    <t xml:space="preserve">1.13511574268341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15006113052368</t>
   </si>
   <si>
     <t xml:space="preserve">1.15188360214233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14787399768829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15261280536652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16427743434906</t>
+    <t xml:space="preserve">1.14787375926971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15261256694794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16427731513977</t>
   </si>
   <si>
     <t xml:space="preserve">1.1704740524292</t>
@@ -1970,64 +1970,64 @@
     <t xml:space="preserve">1.17229676246643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17849349975586</t>
+    <t xml:space="preserve">1.17849361896515</t>
   </si>
   <si>
     <t xml:space="preserve">1.17484831809998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19161629676819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16318380832672</t>
+    <t xml:space="preserve">1.1916161775589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16318368911743</t>
   </si>
   <si>
     <t xml:space="preserve">1.16609978675842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17995166778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18469035625458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1810450553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17120313644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17375469207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14969646930695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15407061576843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17083847522736</t>
+    <t xml:space="preserve">1.17995154857635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18469047546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18104517459869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17120325565338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17375481128693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14969658851624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15407073497772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17083859443665</t>
   </si>
   <si>
     <t xml:space="preserve">1.16209006309509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1668289899826</t>
+    <t xml:space="preserve">1.16682875156403</t>
   </si>
   <si>
     <t xml:space="preserve">1.16755795478821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17010974884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13183510303497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12418019771576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12782537937164</t>
+    <t xml:space="preserve">1.17010962963104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13183498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12418007850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12782526016235</t>
   </si>
   <si>
     <t xml:space="preserve">1.14277052879333</t>
@@ -2036,31 +2036,31 @@
     <t xml:space="preserve">1.16099655628204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14459311962128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15297710895538</t>
+    <t xml:space="preserve">1.14459323883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15297722816467</t>
   </si>
   <si>
     <t xml:space="preserve">1.13985443115234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13475120067596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1639130115509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16938042640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16573536396027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16500627994537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18833553791046</t>
+    <t xml:space="preserve">1.13475096225739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16391277313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16938054561615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16573548316956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16500639915466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18833565711975</t>
   </si>
   <si>
     <t xml:space="preserve">1.20473897457123</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">1.20036470890045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18869996070862</t>
+    <t xml:space="preserve">1.18870007991791</t>
   </si>
   <si>
     <t xml:space="preserve">1.1795871257782</t>
@@ -2084,16 +2084,16 @@
     <t xml:space="preserve">1.18213868141174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17630648612976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19599056243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18979358673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22551655769348</t>
+    <t xml:space="preserve">1.17630624771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19599044322968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18979370594025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22551667690277</t>
   </si>
   <si>
     <t xml:space="preserve">1.21567463874817</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.22770380973816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23207807540894</t>
+    <t xml:space="preserve">1.23207795619965</t>
   </si>
   <si>
     <t xml:space="preserve">1.21421658992767</t>
@@ -2111,31 +2111,31 @@
     <t xml:space="preserve">1.21166491508484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23134899139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2302553653717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21603918075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21931982040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23791038990021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23462963104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22806823253632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21640348434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22187149524689</t>
+    <t xml:space="preserve">1.23134887218475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23025548458099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21603906154633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21931993961334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23791015148163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23462975025177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22806835174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21640360355377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22187125682831</t>
   </si>
   <si>
     <t xml:space="preserve">1.22114229202271</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">1.23061990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22843277454376</t>
+    <t xml:space="preserve">1.22843265533447</t>
   </si>
   <si>
     <t xml:space="preserve">1.23645222187042</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">1.2287974357605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22624588012695</t>
+    <t xml:space="preserve">1.22624576091766</t>
   </si>
   <si>
     <t xml:space="preserve">1.27363324165344</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">1.3133659362793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30972063541412</t>
+    <t xml:space="preserve">1.30972075462341</t>
   </si>
   <si>
     <t xml:space="preserve">1.30826258659363</t>
@@ -2183,52 +2183,52 @@
     <t xml:space="preserve">1.29331743717194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31518852710724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31445968151093</t>
+    <t xml:space="preserve">1.31518864631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31445956230164</t>
   </si>
   <si>
     <t xml:space="preserve">1.30862712860107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29732704162598</t>
+    <t xml:space="preserve">1.29732716083527</t>
   </si>
   <si>
     <t xml:space="preserve">1.27873647212982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28857851028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28420436382294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27727830410004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27509129047394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26452040672302</t>
+    <t xml:space="preserve">1.288578748703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28420448303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27727842330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27509117126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26452028751373</t>
   </si>
   <si>
     <t xml:space="preserve">1.24884593486786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24665892124176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25249123573303</t>
+    <t xml:space="preserve">1.24665880203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25249111652374</t>
   </si>
   <si>
     <t xml:space="preserve">1.24520063400269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24483609199524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19052278995514</t>
+    <t xml:space="preserve">1.24483621120453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19052267074585</t>
   </si>
   <si>
     <t xml:space="preserve">1.19635510444641</t>
@@ -2237,13 +2237,13 @@
     <t xml:space="preserve">1.1985422372818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19343888759613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18068063259125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20218741893768</t>
+    <t xml:space="preserve">1.19343876838684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18068075180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20218753814697</t>
   </si>
   <si>
     <t xml:space="preserve">1.18906462192535</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">1.20729076862335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22515213489532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2415554523468</t>
+    <t xml:space="preserve">1.22515225410461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24155557155609</t>
   </si>
   <si>
     <t xml:space="preserve">1.23353612422943</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">1.21895527839661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21275842189789</t>
+    <t xml:space="preserve">1.21275854110718</t>
   </si>
   <si>
     <t xml:space="preserve">1.2083842754364</t>
@@ -2279,19 +2279,19 @@
     <t xml:space="preserve">1.25504279136658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2506685256958</t>
+    <t xml:space="preserve">1.25066864490509</t>
   </si>
   <si>
     <t xml:space="preserve">1.25941693782806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25650072097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26853001117706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29987871646881</t>
+    <t xml:space="preserve">1.25650084018707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26852989196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2998788356781</t>
   </si>
   <si>
     <t xml:space="preserve">1.30315947532654</t>
@@ -2303,40 +2303,40 @@
     <t xml:space="preserve">1.2922238111496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30607557296753</t>
+    <t xml:space="preserve">1.30607569217682</t>
   </si>
   <si>
     <t xml:space="preserve">1.3520051240921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34544384479523</t>
+    <t xml:space="preserve">1.34544372558594</t>
   </si>
   <si>
     <t xml:space="preserve">1.33414375782013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31409513950348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32247912883759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3294050693512</t>
+    <t xml:space="preserve">1.3140949010849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32247889041901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32940495014191</t>
   </si>
   <si>
     <t xml:space="preserve">1.34580826759338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33159208297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33013391494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34981822967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34398579597473</t>
+    <t xml:space="preserve">1.33159196376801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33013379573822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34981799125671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34398567676544</t>
   </si>
   <si>
     <t xml:space="preserve">1.3414341211319</t>
@@ -2354,49 +2354,49 @@
     <t xml:space="preserve">1.3822603225708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36038911342621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34908890724182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26524913311005</t>
+    <t xml:space="preserve">1.36038899421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34908878803253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26524949073792</t>
   </si>
   <si>
     <t xml:space="preserve">1.25613629817963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13766729831696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15589320659637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19708395004272</t>
+    <t xml:space="preserve">1.13766741752625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15589332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19708406925201</t>
   </si>
   <si>
     <t xml:space="preserve">1.11579608917236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996233344078064</t>
+    <t xml:space="preserve">0.996233522891998</t>
   </si>
   <si>
     <t xml:space="preserve">0.924787521362305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.905467927455902</t>
+    <t xml:space="preserve">0.905467987060547</t>
   </si>
   <si>
     <t xml:space="preserve">0.733049929141998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.772782564163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750546872615814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775334298610687</t>
+    <t xml:space="preserve">0.772782683372498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750546932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775334358215332</t>
   </si>
   <si>
     <t xml:space="preserve">0.751276016235352</t>
@@ -2408,25 +2408,25 @@
     <t xml:space="preserve">0.741433918476105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.729040205478668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786269962787628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797205567359924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793195784091949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778250396251678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824544548988342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826002478599548</t>
+    <t xml:space="preserve">0.729040265083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786269903182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79720550775528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.793195843696594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778250455856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824544489383698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826002597808838</t>
   </si>
   <si>
     <t xml:space="preserve">0.816160559654236</t>
@@ -2435,58 +2435,58 @@
     <t xml:space="preserve">0.841676950454712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.836209177970886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869015991687775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869744956493378</t>
+    <t xml:space="preserve">0.836209118366241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869016051292419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869745016098022</t>
   </si>
   <si>
     <t xml:space="preserve">0.855164110660553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.876670956611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889429092407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885783970355988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.897448539733887</t>
+    <t xml:space="preserve">0.876670897006989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889429032802582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885783910751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.897448420524597</t>
   </si>
   <si>
     <t xml:space="preserve">0.910935759544373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.911664724349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.883961379528046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888335585594177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879587113857269</t>
+    <t xml:space="preserve">0.91166478395462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883961260318756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888335466384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879587054252625</t>
   </si>
   <si>
     <t xml:space="preserve">0.890158116817474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906926035881042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901458263397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899635553359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905832350254059</t>
+    <t xml:space="preserve">0.906926095485687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901458203792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89963573217392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905832529067993</t>
   </si>
   <si>
     <t xml:space="preserve">0.872296571731567</t>
@@ -2495,64 +2495,64 @@
     <t xml:space="preserve">0.879951536655426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878128945827484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882138669490814</t>
+    <t xml:space="preserve">0.878128826618195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882138729095459</t>
   </si>
   <si>
     <t xml:space="preserve">0.877764403820038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.914581000804901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934264957904816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911300241947174</t>
+    <t xml:space="preserve">0.914581120014191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93426513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911300361156464</t>
   </si>
   <si>
     <t xml:space="preserve">0.944332540035248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.902750670909882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914020657539368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910523056983948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912854790687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946275472640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971146881580353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950550317764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971535444259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969592392444611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981639385223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00573360919952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04265189170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04342901706696</t>
+    <t xml:space="preserve">0.902750790119171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914020597934723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910522997379303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912854731082916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946275532245636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971146821975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950550377368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971535325050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969592273235321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981639444828033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00573348999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04265177249908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04342913627625</t>
   </si>
   <si>
     <t xml:space="preserve">1.03060483932495</t>
@@ -2564,142 +2564,142 @@
     <t xml:space="preserve">1.02710723876953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01195132732391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960265696048737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956379592418671</t>
+    <t xml:space="preserve">1.0119514465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960265636444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956379532814026</t>
   </si>
   <si>
     <t xml:space="preserve">0.978141844272614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01156282424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01778078079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0096195936203</t>
+    <t xml:space="preserve">1.01156270503998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01778054237366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00961971282959</t>
   </si>
   <si>
     <t xml:space="preserve">1.0193350315094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01467168331146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972312867641449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963763177394867</t>
+    <t xml:space="preserve">1.01467156410217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972312688827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963763117790222</t>
   </si>
   <si>
     <t xml:space="preserve">0.977364718914032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979696333408356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984359800815582</t>
+    <t xml:space="preserve">0.979696393013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984359741210938</t>
   </si>
   <si>
     <t xml:space="preserve">0.999904274940491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996795356273651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993686437606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983194053173065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982805371284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958322644233704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961431443691254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960654258728027</t>
+    <t xml:space="preserve">0.996795415878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993686497211456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983193874359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98280531167984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958322584629059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961431562900543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960654377937317</t>
   </si>
   <si>
     <t xml:space="preserve">0.973867237567902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973089933395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985137104988098</t>
+    <t xml:space="preserve">0.973089993000031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985137045383453</t>
   </si>
   <si>
     <t xml:space="preserve">0.987857341766357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985525608062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949773013591766</t>
+    <t xml:space="preserve">0.985525667667389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949773132801056</t>
   </si>
   <si>
     <t xml:space="preserve">0.954436480998993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970758318901062</t>
+    <t xml:space="preserve">0.970758140087128</t>
   </si>
   <si>
     <t xml:space="preserve">0.92878794670105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943166553974152</t>
+    <t xml:space="preserve">0.943166613578796</t>
   </si>
   <si>
     <t xml:space="preserve">0.95599091053009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959877073764801</t>
+    <t xml:space="preserve">0.959877133369446</t>
   </si>
   <si>
     <t xml:space="preserve">0.953659236431122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965317606925964</t>
+    <t xml:space="preserve">0.965317666530609</t>
   </si>
   <si>
     <t xml:space="preserve">0.982028067111969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01739192008972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00612211227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994852304458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979307651519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989411890506744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987080037593842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964928925037384</t>
+    <t xml:space="preserve">1.01739203929901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00612223148346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994852244853973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979307770729065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989411652088165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987080097198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964928984642029</t>
   </si>
   <si>
     <t xml:space="preserve">0.96259731054306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958711206912994</t>
+    <t xml:space="preserve">0.958711326122284</t>
   </si>
   <si>
     <t xml:space="preserve">0.96609491109848</t>
@@ -2708,16 +2708,16 @@
     <t xml:space="preserve">0.951327562332153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954047799110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975032985210419</t>
+    <t xml:space="preserve">0.954047858715057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975033044815063</t>
   </si>
   <si>
     <t xml:space="preserve">0.968037962913513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937726080417633</t>
+    <t xml:space="preserve">0.937726140022278</t>
   </si>
   <si>
     <t xml:space="preserve">0.946664154529572</t>
@@ -2726,73 +2726,73 @@
     <t xml:space="preserve">0.938503265380859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.942000806331635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933451175689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97192394733429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94899582862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953270733356476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945886969566345</t>
+    <t xml:space="preserve">0.942000687122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933451235294342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971924066543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94899594783783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953270614147186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945886790752411</t>
   </si>
   <si>
     <t xml:space="preserve">0.929565131664276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931119501590729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900807738304138</t>
+    <t xml:space="preserve">0.931119680404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900807797908783</t>
   </si>
   <si>
     <t xml:space="preserve">0.903528034687042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904693782329559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89886462688446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878656685352325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886428892612457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90158486366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886040329933167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840961098670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830079853534698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848344743251801</t>
+    <t xml:space="preserve">0.904693961143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898864686489105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878656625747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886428952217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901584923267365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886040270328522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840961158275604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830079913139343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848344802856445</t>
   </si>
   <si>
     <t xml:space="preserve">0.860780417919159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872050225734711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89847594499588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892646789550781</t>
+    <t xml:space="preserve">0.872050166130066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898476004600525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892646729946136</t>
   </si>
   <si>
     <t xml:space="preserve">0.881376922130585</t>
@@ -2801,28 +2801,28 @@
     <t xml:space="preserve">0.942778050899506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939280569553375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955213606357574</t>
+    <t xml:space="preserve">0.93928050994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955213665962219</t>
   </si>
   <si>
     <t xml:space="preserve">0.95249330997467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947441399097443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95210474729538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959488391876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976198852062225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01700341701508</t>
+    <t xml:space="preserve">0.947441339492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952104806900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95948851108551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97619891166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01700329780579</t>
   </si>
   <si>
     <t xml:space="preserve">1.02205526828766</t>
@@ -2837,25 +2837,25 @@
     <t xml:space="preserve">0.975421667098999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.976587414741516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997184038162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990966141223907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988245904445648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984748423099518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995629489421844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954825162887573</t>
+    <t xml:space="preserve">0.976587533950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997183859348297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990966200828552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988245844841003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984748244285583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995629549026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954825222492218</t>
   </si>
   <si>
     <t xml:space="preserve">1.00651061534882</t>
@@ -2882,55 +2882,55 @@
     <t xml:space="preserve">1.03487968444824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01428306102753</t>
+    <t xml:space="preserve">1.01428294181824</t>
   </si>
   <si>
     <t xml:space="preserve">1.0375999212265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03215932846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02050089836121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03099346160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06596875190735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0729638338089</t>
+    <t xml:space="preserve">1.0321592092514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02050077915192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03099358081818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06596863269806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07296371459961</t>
   </si>
   <si>
     <t xml:space="preserve">1.04653799533844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05897355079651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05353307723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06169402599335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0449835062027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10871624946594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13630783557892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15418410301208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12853562831879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13825082778931</t>
+    <t xml:space="preserve">1.0589736700058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0535329580307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06169390678406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04498362541199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10871636867523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13630795478821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15418422222137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12853574752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1382509469986</t>
   </si>
   <si>
     <t xml:space="preserve">1.14252579212189</t>
@@ -2942,28 +2942,28 @@
     <t xml:space="preserve">1.16195642948151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13863945007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12154054641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13475334644318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12698125839233</t>
+    <t xml:space="preserve">1.13863956928253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12154042720795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13475346565247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12698113918304</t>
   </si>
   <si>
     <t xml:space="preserve">1.11415696144104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10366427898407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11221396923065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09317171573639</t>
+    <t xml:space="preserve">1.10366439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11221385002136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0931715965271</t>
   </si>
   <si>
     <t xml:space="preserve">1.0838451385498</t>
@@ -2975,94 +2975,94 @@
     <t xml:space="preserve">1.1071617603302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07918167114258</t>
+    <t xml:space="preserve">1.07918155193329</t>
   </si>
   <si>
     <t xml:space="preserve">1.08656525611877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07723844051361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10832762718201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13086748123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15262973308563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14874362945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15496134757996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16312217712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14563465118408</t>
+    <t xml:space="preserve">1.0772385597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1083277463913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1308673620224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15262961387634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14874351024628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15496146678925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16312229633331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14563453197479</t>
   </si>
   <si>
     <t xml:space="preserve">1.15301835536957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14641189575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17089462280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18954801559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2047039270401</t>
+    <t xml:space="preserve">1.14641177654266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17089450359344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18954813480377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20470404624939</t>
   </si>
   <si>
     <t xml:space="preserve">1.20664715766907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21558511257172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21752822399139</t>
+    <t xml:space="preserve">1.21558523178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2175281047821</t>
   </si>
   <si>
     <t xml:space="preserve">1.20625853538513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20392668247223</t>
+    <t xml:space="preserve">1.20392680168152</t>
   </si>
   <si>
     <t xml:space="preserve">1.20859014987946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2241348028183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20975601673126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19809746742249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21286499500275</t>
+    <t xml:space="preserve">1.22413456439972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20975589752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19809758663177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21286487579346</t>
   </si>
   <si>
     <t xml:space="preserve">1.21597385406494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2132533788681</t>
+    <t xml:space="preserve">1.21325349807739</t>
   </si>
   <si>
     <t xml:space="preserve">1.20431530475616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21247625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22685503959656</t>
+    <t xml:space="preserve">1.21247613430023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22685515880585</t>
   </si>
   <si>
     <t xml:space="preserve">1.21403074264526</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">1.2357931137085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2381249666214</t>
+    <t xml:space="preserve">1.23812484741211</t>
   </si>
   <si>
     <t xml:space="preserve">1.23851346969604</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">1.24278819561005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26105284690857</t>
+    <t xml:space="preserve">1.26105296611786</t>
   </si>
   <si>
     <t xml:space="preserve">1.26455056667328</t>
@@ -3089,16 +3089,16 @@
     <t xml:space="preserve">1.27582037448883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26066434383392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2649393081665</t>
+    <t xml:space="preserve">1.26066446304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26493918895721</t>
   </si>
   <si>
     <t xml:space="preserve">1.27892935276031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30457782745361</t>
+    <t xml:space="preserve">1.3045779466629</t>
   </si>
   <si>
     <t xml:space="preserve">1.31779074668884</t>
@@ -3107,424 +3107,424 @@
     <t xml:space="preserve">1.29291939735413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29874849319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31740200519562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33061492443085</t>
+    <t xml:space="preserve">1.29874873161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31740212440491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33061504364014</t>
   </si>
   <si>
     <t xml:space="preserve">1.34693682193756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34382784366608</t>
+    <t xml:space="preserve">1.34382772445679</t>
   </si>
   <si>
     <t xml:space="preserve">1.34849119186401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35121166706085</t>
+    <t xml:space="preserve">1.35121130943298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37258541584015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40067207813263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37502765655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38194763660431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37787699699402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39497327804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.391716837883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38438999652863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39456617832184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38886749744415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41044116020203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42306005954742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43323624134064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45847368240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43852806091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43771398067474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44911134243011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44951868057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45725250244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45765972137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45521724224091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43120110034943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4430056810379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44422674179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42713057994843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41858243942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40352141857147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41288363933563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41695427894592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41898965835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41329061985016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43527162075043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3795051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38072645664215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39945089817047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41736125946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40392851829529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40148615837097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34734797477722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3591525554657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38316881656647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.395787358284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4511467218399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47719812393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47801220417023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47394168376923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47068536281586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47923338413239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46824300289154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4796404838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49348032474518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50691294670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52360224723816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53866326808929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54069852828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55006098747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58262515068054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58669567108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56593596935272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5838463306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55494546890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53215050697327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52726590633392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52889394760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52197408676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.514240026474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51912486553192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50650596618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49755084514618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52238118648529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49307322502136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51464712619781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51627540588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48615336418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48940980434418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49063086509705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42794466018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45155382156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46173024177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46213710308075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4837110042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47882616519928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48411810398102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45643842220306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45562434196472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43812096118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44544792175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44015622138977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45684540271759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48737454414368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48533928394318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5040637254715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46417236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44504082202911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47475576400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49673664569855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50894832611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.502028465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48696744441986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50365662574768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52970790863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53662800788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57407701015472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55698072910309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55779480934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50732028484344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48004746437073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49022388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49225914478302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.510169506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47760534286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5004004240036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50121438503265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51301884651184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51953172683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51546132564545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3921240568161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40596377849579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39538025856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40637063980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45196080207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4307941198349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45806658267975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45440316200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45399606227875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42835164070129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39130973815918</t>
   </si>
   <si>
     <t xml:space="preserve">1.37258529663086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40067207813263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37502765655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38194763660431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37787699699402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39497327804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.391716837883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38438999652863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39456629753113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38886749744415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41044127941132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42305994033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43323636054993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45847368240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43852806091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43771398067474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4491114616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44951868057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45725250244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45765960216522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45521724224091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43120110034943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4430056810379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44422686100006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42713057994843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41858243942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40352141857147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41288352012634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41695427894592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41898941993713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41329061985016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43527173995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3795051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38072645664215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39945089817047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41736137866974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.403928399086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40148615837097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34734797477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35915267467499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38316869735718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.395787358284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4511467218399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47719812393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47801232337952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47394168376923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47068524360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47923338413239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46824312210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4796404838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49348020553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50691306591034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52360236644745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53866326808929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54069864749908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55006098747253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58262515068054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58669567108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56593585014343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58384621143341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55494546890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53215050697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52726590633392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52889394760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52197420597076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.514240026474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51912474632263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50650596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49755084514618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52238118648529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49307322502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51464712619781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5162752866745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48615336418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48940980434418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49063098430634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42794454097748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45155382156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46173012256622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46213710308075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4837110042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47882616519928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48411810398102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45643842220306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45562422275543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43812108039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44544792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44015634059906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45684552192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48737466335297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48533916473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5040637254715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46417248249054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4450409412384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47475588321686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49673664569855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50894832611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.502028465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48696756362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50365662574768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52970802783966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53662800788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57407689094543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55698072910309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55779469013214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50732028484344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48004746437073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49022388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49225914478302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.510169506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47760534286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50040030479431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50121438503265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51301884651184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51953184604645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51546132564545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3921240568161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4059636592865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39538037776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40637063980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45196080207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43079400062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45806670188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45440316200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45399606227875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42835175991058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39130973815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37258541584015</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.32699525356293</t>
   </si>
   <si>
     <t xml:space="preserve">1.34531271457672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34775519371033</t>
+    <t xml:space="preserve">1.34775507450104</t>
   </si>
   <si>
     <t xml:space="preserve">1.36810779571533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37177121639252</t>
+    <t xml:space="preserve">1.37177109718323</t>
   </si>
   <si>
     <t xml:space="preserve">1.39741563796997</t>
@@ -3533,31 +3533,31 @@
     <t xml:space="preserve">1.4002650976181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40677797794342</t>
+    <t xml:space="preserve">1.40677785873413</t>
   </si>
   <si>
     <t xml:space="preserve">1.35548901557922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35955965518951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35833835601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37462067604065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36770069599152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35589623451233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35263979434967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33310127258301</t>
+    <t xml:space="preserve">1.35955953598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35833847522736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37462055683136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36770057678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35589611530304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35263967514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33310115337372</t>
   </si>
   <si>
     <t xml:space="preserve">1.32414591312408</t>
@@ -3569,16 +3569,16 @@
     <t xml:space="preserve">1.34164929389954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30664277076721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33269417285919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36525845527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41532611846924</t>
+    <t xml:space="preserve">1.30664265155792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3326940536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36525857448578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41532599925995</t>
   </si>
   <si>
     <t xml:space="preserve">1.37380647659302</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">1.37909817695618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37624871730804</t>
+    <t xml:space="preserve">1.37624883651733</t>
   </si>
   <si>
     <t xml:space="preserve">1.36973595619202</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">1.28262650966644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30094385147095</t>
+    <t xml:space="preserve">1.30094397068024</t>
   </si>
   <si>
     <t xml:space="preserve">1.30542147159576</t>
@@ -3632,10 +3632,10 @@
     <t xml:space="preserve">1.25413274765015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22889542579651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25046932697296</t>
+    <t xml:space="preserve">1.22889530658722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25046920776367</t>
   </si>
   <si>
     <t xml:space="preserve">1.22482478618622</t>
@@ -3644,13 +3644,13 @@
     <t xml:space="preserve">1.28140532970428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30012989044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2549467086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22848808765411</t>
+    <t xml:space="preserve">1.3001297712326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25494682788849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2284882068634</t>
   </si>
   <si>
     <t xml:space="preserve">1.19918048381805</t>
@@ -3680,58 +3680,58 @@
     <t xml:space="preserve">1.22116136550903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21464848518372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23785042762756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2508761882782</t>
+    <t xml:space="preserve">1.21464860439301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23785054683685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25087630748749</t>
   </si>
   <si>
     <t xml:space="preserve">1.22563886642456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22808110713959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23540818691254</t>
+    <t xml:space="preserve">1.22808122634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23540830612183</t>
   </si>
   <si>
     <t xml:space="preserve">1.25698220729828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27489233016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25779604911804</t>
+    <t xml:space="preserve">1.27489244937897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25779616832733</t>
   </si>
   <si>
     <t xml:space="preserve">1.26553022861481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25942444801331</t>
+    <t xml:space="preserve">1.25942432880402</t>
   </si>
   <si>
     <t xml:space="preserve">1.28751111030579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29768741130829</t>
+    <t xml:space="preserve">1.29768753051758</t>
   </si>
   <si>
     <t xml:space="preserve">1.2980945110321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33554339408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36281609535217</t>
+    <t xml:space="preserve">1.33554351329803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36281597614288</t>
   </si>
   <si>
     <t xml:space="preserve">1.35223269462585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3571172952652</t>
+    <t xml:space="preserve">1.35711741447449</t>
   </si>
   <si>
     <t xml:space="preserve">1.34856915473938</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">1.36485135555267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33961403369904</t>
+    <t xml:space="preserve">1.33961391448975</t>
   </si>
   <si>
     <t xml:space="preserve">1.32129657268524</t>
@@ -3770,37 +3770,37 @@
     <t xml:space="preserve">1.3164119720459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35019731521606</t>
+    <t xml:space="preserve">1.35019743442535</t>
   </si>
   <si>
     <t xml:space="preserve">1.34653389453888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34327733516693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38561117649078</t>
+    <t xml:space="preserve">1.34327745437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38561105728149</t>
   </si>
   <si>
     <t xml:space="preserve">1.33147299289703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36037361621857</t>
+    <t xml:space="preserve">1.36037373542786</t>
   </si>
   <si>
     <t xml:space="preserve">1.34205627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40272557735443</t>
+    <t xml:space="preserve">1.40272545814514</t>
   </si>
   <si>
     <t xml:space="preserve">1.36872255802155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37862205505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38507843017578</t>
+    <t xml:space="preserve">1.378622174263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38507831096649</t>
   </si>
   <si>
     <t xml:space="preserve">1.3631272315979</t>
@@ -3809,10 +3809,10 @@
     <t xml:space="preserve">1.35796213150024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34504973888397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32998502254486</t>
+    <t xml:space="preserve">1.34504961967468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32998514175415</t>
   </si>
   <si>
     <t xml:space="preserve">1.31578135490417</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">1.30416011810303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33041548728943</t>
+    <t xml:space="preserve">1.33041560649872</t>
   </si>
   <si>
     <t xml:space="preserve">1.31018602848053</t>
@@ -3833,13 +3833,13 @@
     <t xml:space="preserve">1.270587682724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18708693981171</t>
+    <t xml:space="preserve">1.187087059021</t>
   </si>
   <si>
     <t xml:space="preserve">1.14921045303345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11047291755676</t>
+    <t xml:space="preserve">1.11047303676605</t>
   </si>
   <si>
     <t xml:space="preserve">1.15050172805786</t>
@@ -3854,31 +3854,31 @@
     <t xml:space="preserve">1.091104388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06570971012115</t>
+    <t xml:space="preserve">1.06570982933044</t>
   </si>
   <si>
     <t xml:space="preserve">1.03945434093475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05581033229828</t>
+    <t xml:space="preserve">1.05581021308899</t>
   </si>
   <si>
     <t xml:space="preserve">1.10143435001373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08593928813934</t>
+    <t xml:space="preserve">1.08593940734863</t>
   </si>
   <si>
     <t xml:space="preserve">1.09540855884552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07517898082733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.043328166008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06743144989014</t>
+    <t xml:space="preserve">1.07517886161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04332804679871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06743133068085</t>
   </si>
   <si>
     <t xml:space="preserve">1.06614017486572</t>
@@ -3893,13 +3893,13 @@
     <t xml:space="preserve">1.07130515575409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06915307044983</t>
+    <t xml:space="preserve">1.06915318965912</t>
   </si>
   <si>
     <t xml:space="preserve">1.02697229385376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00200819969177</t>
+    <t xml:space="preserve">1.00200831890106</t>
   </si>
   <si>
     <t xml:space="preserve">1.02352893352509</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">1.03601109981537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04074561595917</t>
+    <t xml:space="preserve">1.04074573516846</t>
   </si>
   <si>
     <t xml:space="preserve">1.05451893806458</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">1.08636963367462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07690072059631</t>
+    <t xml:space="preserve">1.07690060138702</t>
   </si>
   <si>
     <t xml:space="preserve">1.06786179542542</t>
@@ -3959,19 +3959,19 @@
     <t xml:space="preserve">1.11305546760559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10100400447845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10272550582886</t>
+    <t xml:space="preserve">1.10100388526917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10272562503815</t>
   </si>
   <si>
     <t xml:space="preserve">1.08292639255524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06097531318665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06355774402618</t>
+    <t xml:space="preserve">1.06097519397736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06355762481689</t>
   </si>
   <si>
     <t xml:space="preserve">1.05839276313782</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">1.0170726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996843278408051</t>
+    <t xml:space="preserve">0.996843218803406</t>
   </si>
   <si>
     <t xml:space="preserve">0.999425709247589</t>
@@ -3992,31 +3992,31 @@
     <t xml:space="preserve">0.946914970874786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968435704708099</t>
+    <t xml:space="preserve">0.968435883522034</t>
   </si>
   <si>
     <t xml:space="preserve">0.945623755455017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.932711243629456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939167499542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.920229196548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965422928333282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975322365760803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952510416507721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92625492811203</t>
+    <t xml:space="preserve">0.9327113032341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939167439937592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.920229136943817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965422868728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975322425365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952510476112366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92625504732132</t>
   </si>
   <si>
     <t xml:space="preserve">0.930128753185272</t>
@@ -4025,10 +4025,10 @@
     <t xml:space="preserve">0.913342535495758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92195075750351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923242092132568</t>
+    <t xml:space="preserve">0.921950876712799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923242151737213</t>
   </si>
   <si>
     <t xml:space="preserve">0.912051260471344</t>
@@ -4037,34 +4037,34 @@
     <t xml:space="preserve">0.882783055305481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888808846473694</t>
+    <t xml:space="preserve">0.888808906078339</t>
   </si>
   <si>
     <t xml:space="preserve">0.852567851543427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.862984001636505</t>
+    <t xml:space="preserve">0.86298394203186</t>
   </si>
   <si>
     <t xml:space="preserve">0.85377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860659718513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879339635372162</t>
+    <t xml:space="preserve">0.860659658908844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879339694976807</t>
   </si>
   <si>
     <t xml:space="preserve">0.903442978858948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868579268455505</t>
+    <t xml:space="preserve">0.868579208850861</t>
   </si>
   <si>
     <t xml:space="preserve">0.853256464004517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8353511095047</t>
+    <t xml:space="preserve">0.835351169109344</t>
   </si>
   <si>
     <t xml:space="preserve">0.846542000770569</t>
@@ -4079,16 +4079,16 @@
     <t xml:space="preserve">0.825882017612457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863844692707062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.883643805980682</t>
+    <t xml:space="preserve">0.863844633102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883643865585327</t>
   </si>
   <si>
     <t xml:space="preserve">0.879770040512085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871161758899689</t>
+    <t xml:space="preserve">0.871161699295044</t>
   </si>
   <si>
     <t xml:space="preserve">0.896986782550812</t>
@@ -4100,7 +4100,7 @@
     <t xml:space="preserve">0.948206305503845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982209086418152</t>
+    <t xml:space="preserve">0.982209146022797</t>
   </si>
   <si>
     <t xml:space="preserve">0.971018254756927</t>
@@ -4109,13 +4109,13 @@
     <t xml:space="preserve">0.965853273868561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966714143753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966283679008484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955092966556549</t>
+    <t xml:space="preserve">0.966714084148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966283738613129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955092906951904</t>
   </si>
   <si>
     <t xml:space="preserve">0.972309589385986</t>
@@ -4130,7 +4130,7 @@
     <t xml:space="preserve">1.01061654090881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11176431179047</t>
+    <t xml:space="preserve">1.11176419258118</t>
   </si>
   <si>
     <t xml:space="preserve">1.1160683631897</t>
@@ -4142,13 +4142,13 @@
     <t xml:space="preserve">1.10616886615753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.126828789711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12209439277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11822044849396</t>
+    <t xml:space="preserve">1.12682890892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1220942735672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11822056770325</t>
   </si>
   <si>
     <t xml:space="preserve">1.09669971466064</t>
@@ -4163,16 +4163,16 @@
     <t xml:space="preserve">1.11865091323853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09928226470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11090338230133</t>
+    <t xml:space="preserve">1.09928214550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11090350151062</t>
   </si>
   <si>
     <t xml:space="preserve">1.12898087501526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13586759567261</t>
+    <t xml:space="preserve">1.13586747646332</t>
   </si>
   <si>
     <t xml:space="preserve">1.13027215003967</t>
@@ -4181,13 +4181,13 @@
     <t xml:space="preserve">1.13543713092804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12381601333618</t>
+    <t xml:space="preserve">1.12381589412689</t>
   </si>
   <si>
     <t xml:space="preserve">1.11951184272766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12166368961334</t>
+    <t xml:space="preserve">1.12166392803192</t>
   </si>
   <si>
     <t xml:space="preserve">1.12984180450439</t>
@@ -4196,10 +4196,10 @@
     <t xml:space="preserve">1.14490628242493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11692941188812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09282600879669</t>
+    <t xml:space="preserve">1.11692917346954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0928258895874</t>
   </si>
   <si>
     <t xml:space="preserve">1.07603967189789</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">1.06958341598511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07173562049866</t>
+    <t xml:space="preserve">1.07173550128937</t>
   </si>
   <si>
     <t xml:space="preserve">1.09971261024475</t>
@@ -4223,19 +4223,19 @@
     <t xml:space="preserve">1.12553763389587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13888037204742</t>
+    <t xml:space="preserve">1.13888049125671</t>
   </si>
   <si>
     <t xml:space="preserve">1.14705836772919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18837833404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19354343414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19827771186829</t>
+    <t xml:space="preserve">1.18837821483612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19354331493378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19827783107758</t>
   </si>
   <si>
     <t xml:space="preserve">1.20043003559113</t>
@@ -4247,16 +4247,16 @@
     <t xml:space="preserve">1.21032953262329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17245304584503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15093207359314</t>
+    <t xml:space="preserve">1.17245292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15093219280243</t>
   </si>
   <si>
     <t xml:space="preserve">1.18192207813263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19096076488495</t>
+    <t xml:space="preserve">1.19096088409424</t>
   </si>
   <si>
     <t xml:space="preserve">1.20387327671051</t>
@@ -4265,25 +4265,25 @@
     <t xml:space="preserve">1.20430374145508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21119022369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1948344707489</t>
+    <t xml:space="preserve">1.21119034290314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19483458995819</t>
   </si>
   <si>
     <t xml:space="preserve">1.18665671348572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20989918708801</t>
+    <t xml:space="preserve">1.20989906787872</t>
   </si>
   <si>
     <t xml:space="preserve">1.18794786930084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20344281196594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21506404876709</t>
+    <t xml:space="preserve">1.20344293117523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21506416797638</t>
   </si>
   <si>
     <t xml:space="preserve">1.20903825759888</t>
@@ -4295,7 +4295,7 @@
     <t xml:space="preserve">1.17675697803497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19139111042023</t>
+    <t xml:space="preserve">1.19139122962952</t>
   </si>
   <si>
     <t xml:space="preserve">1.18235242366791</t>
@@ -4304,22 +4304,22 @@
     <t xml:space="preserve">1.19225203990936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17976987361908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18579590320587</t>
+    <t xml:space="preserve">1.17976999282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18579578399658</t>
   </si>
   <si>
     <t xml:space="preserve">1.18966948986053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20215165615082</t>
+    <t xml:space="preserve">1.20215153694153</t>
   </si>
   <si>
     <t xml:space="preserve">1.20129072666168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16944003105164</t>
+    <t xml:space="preserve">1.16943991184235</t>
   </si>
   <si>
     <t xml:space="preserve">1.18364369869232</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">1.15738832950592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18278300762177</t>
+    <t xml:space="preserve">1.18278288841248</t>
   </si>
   <si>
     <t xml:space="preserve">1.18321335315704</t>
@@ -4352,16 +4352,16 @@
     <t xml:space="preserve">1.25078856945038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26240992546082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2365847826004</t>
+    <t xml:space="preserve">1.26240980625153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23658490180969</t>
   </si>
   <si>
     <t xml:space="preserve">1.25294065475464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2395977973938</t>
+    <t xml:space="preserve">1.23959791660309</t>
   </si>
   <si>
     <t xml:space="preserve">1.23787605762482</t>
@@ -4385,16 +4385,16 @@
     <t xml:space="preserve">1.26714432239532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29426074028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32869386672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33256769180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33730220794678</t>
+    <t xml:space="preserve">1.29426062107086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32869374752045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33256757259369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33730232715607</t>
   </si>
   <si>
     <t xml:space="preserve">1.31664216518402</t>
@@ -4406,19 +4406,19 @@
     <t xml:space="preserve">1.31922471523285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35150587558746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33988475799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35279715061188</t>
+    <t xml:space="preserve">1.35150599479675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33988463878632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35279703140259</t>
   </si>
   <si>
     <t xml:space="preserve">1.35968375205994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3523668050766</t>
+    <t xml:space="preserve">1.35236668586731</t>
   </si>
   <si>
     <t xml:space="preserve">1.36614012718201</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">1.37733089923859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34332811832428</t>
+    <t xml:space="preserve">1.34332799911499</t>
   </si>
   <si>
     <t xml:space="preserve">1.3678617477417</t>
@@ -4445,10 +4445,10 @@
     <t xml:space="preserve">1.39885175228119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4126250743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43113279342651</t>
+    <t xml:space="preserve">1.41262495517731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4311329126358</t>
   </si>
   <si>
     <t xml:space="preserve">1.45609700679779</t>
@@ -4457,10 +4457,10 @@
     <t xml:space="preserve">1.46728777885437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44877982139587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43758916854858</t>
+    <t xml:space="preserve">1.44877994060516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43758904933929</t>
   </si>
   <si>
     <t xml:space="preserve">1.37905251979828</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">1.42495942115784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42905950546265</t>
+    <t xml:space="preserve">1.42905938625336</t>
   </si>
   <si>
     <t xml:space="preserve">1.39261531829834</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">1.39079320430756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38532650470734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40719306468964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41038191318512</t>
+    <t xml:space="preserve">1.38532662391663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40719294548035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41038179397583</t>
   </si>
   <si>
     <t xml:space="preserve">1.4313371181488</t>
@@ -4499,7 +4499,7 @@
     <t xml:space="preserve">1.45684790611267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4563924074173</t>
+    <t xml:space="preserve">1.45639228820801</t>
   </si>
   <si>
     <t xml:space="preserve">1.48235869407654</t>
@@ -4523,19 +4523,19 @@
     <t xml:space="preserve">1.50103628635406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50786936283112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51743614673615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50012505054474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50376951694489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4768922328949</t>
+    <t xml:space="preserve">1.50786948204041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51743602752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50012516975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50376963615417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47689211368561</t>
   </si>
   <si>
     <t xml:space="preserve">1.49784743785858</t>
@@ -4544,13 +4544,13 @@
     <t xml:space="preserve">1.49420297145844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50695836544037</t>
+    <t xml:space="preserve">1.50695848464966</t>
   </si>
   <si>
     <t xml:space="preserve">1.51652491092682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52563583850861</t>
+    <t xml:space="preserve">1.5256359577179</t>
   </si>
   <si>
     <t xml:space="preserve">1.5242692232132</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">1.54112458229065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53975808620453</t>
+    <t xml:space="preserve">1.53975796699524</t>
   </si>
   <si>
     <t xml:space="preserve">1.52153599262238</t>
@@ -4586,7 +4586,7 @@
     <t xml:space="preserve">1.53064692020416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53383588790894</t>
+    <t xml:space="preserve">1.53383576869965</t>
   </si>
   <si>
     <t xml:space="preserve">1.53520238399506</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">1.54750227928162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55433559417725</t>
+    <t xml:space="preserve">1.55433547496796</t>
   </si>
   <si>
     <t xml:space="preserve">1.56435763835907</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">1.55160212516785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58121287822723</t>
+    <t xml:space="preserve">1.58121299743652</t>
   </si>
   <si>
     <t xml:space="preserve">1.57939076423645</t>
@@ -4616,10 +4616,10 @@
     <t xml:space="preserve">1.54249119758606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51470267772675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5110582113266</t>
+    <t xml:space="preserve">1.51470279693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51105833053589</t>
   </si>
   <si>
     <t xml:space="preserve">1.49921405315399</t>
@@ -4634,13 +4634,13 @@
     <t xml:space="preserve">1.54886901378632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56709098815918</t>
+    <t xml:space="preserve">1.56709086894989</t>
   </si>
   <si>
     <t xml:space="preserve">1.52335822582245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52836930751801</t>
+    <t xml:space="preserve">1.52836918830872</t>
   </si>
   <si>
     <t xml:space="preserve">1.54613566398621</t>
@@ -4652,37 +4652,37 @@
     <t xml:space="preserve">1.57210195064545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58349072933197</t>
+    <t xml:space="preserve">1.58349084854126</t>
   </si>
   <si>
     <t xml:space="preserve">1.58622407913208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60581278800964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59487950801849</t>
+    <t xml:space="preserve">1.60581266880035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5948793888092</t>
   </si>
   <si>
     <t xml:space="preserve">1.61219036579132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59214603900909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57984638214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56481313705444</t>
+    <t xml:space="preserve">1.59214615821838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57984626293182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56481325626373</t>
   </si>
   <si>
     <t xml:space="preserve">1.59123516082764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60034608840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61310148239136</t>
+    <t xml:space="preserve">1.60034596920013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61310136318207</t>
   </si>
   <si>
     <t xml:space="preserve">1.63041234016418</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">1.70056700706482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6345123052597</t>
+    <t xml:space="preserve">1.63451242446899</t>
   </si>
   <si>
     <t xml:space="preserve">1.5994348526001</t>
@@ -4724,25 +4724,25 @@
     <t xml:space="preserve">1.51060271263123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53611361980438</t>
+    <t xml:space="preserve">1.53611350059509</t>
   </si>
   <si>
     <t xml:space="preserve">1.48828089237213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50285851955414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.521080493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55889093875885</t>
+    <t xml:space="preserve">1.50285840034485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52108037471771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55889105796814</t>
   </si>
   <si>
     <t xml:space="preserve">1.56800198554993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58440172672272</t>
+    <t xml:space="preserve">1.58440184593201</t>
   </si>
   <si>
     <t xml:space="preserve">1.57893526554108</t>
@@ -4757,10 +4757,10 @@
     <t xml:space="preserve">1.54659116268158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57756853103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57620203495026</t>
+    <t xml:space="preserve">1.57756865024567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57620191574097</t>
   </si>
   <si>
     <t xml:space="preserve">1.59761273860931</t>
@@ -4769,37 +4769,37 @@
     <t xml:space="preserve">1.60125720500946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61355710029602</t>
+    <t xml:space="preserve">1.61355698108673</t>
   </si>
   <si>
     <t xml:space="preserve">1.63724565505981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.633145570755</t>
+    <t xml:space="preserve">1.63314568996429</t>
   </si>
   <si>
     <t xml:space="preserve">1.63223457336426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62767899036407</t>
+    <t xml:space="preserve">1.62767910957336</t>
   </si>
   <si>
     <t xml:space="preserve">1.6167459487915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61765694618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63177907466888</t>
+    <t xml:space="preserve">1.61765706539154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63177895545959</t>
   </si>
   <si>
     <t xml:space="preserve">1.69601154327393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71742224693298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.761155128479</t>
+    <t xml:space="preserve">1.71742236614227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76115500926971</t>
   </si>
   <si>
     <t xml:space="preserve">1.7597883939743</t>
@@ -4829,7 +4829,7 @@
     <t xml:space="preserve">1.79031038284302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79759919643402</t>
+    <t xml:space="preserve">1.79759907722473</t>
   </si>
   <si>
     <t xml:space="preserve">1.79167699813843</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">1.77709937095642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78256607055664</t>
+    <t xml:space="preserve">1.78256595134735</t>
   </si>
   <si>
     <t xml:space="preserve">1.77846598625183</t>
@@ -4847,16 +4847,16 @@
     <t xml:space="preserve">1.78211033344269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78712141513824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77618813514709</t>
+    <t xml:space="preserve">1.78712153434753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77618825435638</t>
   </si>
   <si>
     <t xml:space="preserve">1.74384427070618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77208840847015</t>
+    <t xml:space="preserve">1.77208828926086</t>
   </si>
   <si>
     <t xml:space="preserve">1.79805469512939</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">1.74019980430603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71377789974213</t>
+    <t xml:space="preserve">1.71377801895142</t>
   </si>
   <si>
     <t xml:space="preserve">1.6964670419693</t>
@@ -4889,10 +4889,10 @@
     <t xml:space="preserve">1.68280053138733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67778956890106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71651124954224</t>
+    <t xml:space="preserve">1.67778944969177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71651113033295</t>
   </si>
   <si>
     <t xml:space="preserve">1.72061121463776</t>
@@ -4901,10 +4901,10 @@
     <t xml:space="preserve">1.73792207241058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74247765541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74703299999237</t>
+    <t xml:space="preserve">1.74247753620148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74703311920166</t>
   </si>
   <si>
     <t xml:space="preserve">1.69692254066467</t>
@@ -4925,10 +4925,10 @@
     <t xml:space="preserve">1.64453434944153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66184520721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64225661754608</t>
+    <t xml:space="preserve">1.66184532642365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64225673675537</t>
   </si>
   <si>
     <t xml:space="preserve">1.59897947311401</t>
@@ -4937,7 +4937,7 @@
     <t xml:space="preserve">1.62995684146881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62859010696411</t>
+    <t xml:space="preserve">1.6285902261734</t>
   </si>
   <si>
     <t xml:space="preserve">1.66321194171906</t>
@@ -4946,10 +4946,10 @@
     <t xml:space="preserve">1.67687833309174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60307931900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56936872005463</t>
+    <t xml:space="preserve">1.60307943820953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56936860084534</t>
   </si>
   <si>
     <t xml:space="preserve">1.55296885967255</t>
@@ -4958,13 +4958,13 @@
     <t xml:space="preserve">1.5124249458313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51014733314514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49238073825836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48964750766754</t>
+    <t xml:space="preserve">1.51014721393585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49238085746765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48964738845825</t>
   </si>
   <si>
     <t xml:space="preserve">1.51698040962219</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">1.55023562908173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55114662647247</t>
+    <t xml:space="preserve">1.55114674568176</t>
   </si>
   <si>
     <t xml:space="preserve">1.54066896438599</t>
@@ -4988,7 +4988,7 @@
     <t xml:space="preserve">1.53839135169983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52518045902252</t>
+    <t xml:space="preserve">1.52518033981323</t>
   </si>
   <si>
     <t xml:space="preserve">1.51288056373596</t>
@@ -5003,13 +5003,13 @@
     <t xml:space="preserve">1.58212411403656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59533500671387</t>
+    <t xml:space="preserve">1.59533512592316</t>
   </si>
   <si>
     <t xml:space="preserve">1.53748023509979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49602508544922</t>
+    <t xml:space="preserve">1.49602520465851</t>
   </si>
   <si>
     <t xml:space="preserve">1.50468063354492</t>
@@ -5018,13 +5018,13 @@
     <t xml:space="preserve">1.50149178504944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49556970596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47279214859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49283623695374</t>
+    <t xml:space="preserve">1.49556958675385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47279226779938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49283635616302</t>
   </si>
   <si>
     <t xml:space="preserve">1.52472484111786</t>
@@ -5036,7 +5036,7 @@
     <t xml:space="preserve">1.50422501564026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47370314598083</t>
+    <t xml:space="preserve">1.47370326519012</t>
   </si>
   <si>
     <t xml:space="preserve">1.50331389904022</t>
@@ -5045,7 +5045,7 @@
     <t xml:space="preserve">1.5051361322403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48418092727661</t>
+    <t xml:space="preserve">1.48418080806732</t>
   </si>
   <si>
     <t xml:space="preserve">1.49966955184937</t>
@@ -5054,7 +5054,7 @@
     <t xml:space="preserve">1.57574641704559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59624600410461</t>
+    <t xml:space="preserve">1.5962461233139</t>
   </si>
   <si>
     <t xml:space="preserve">1.65592312812805</t>
@@ -5069,19 +5069,19 @@
     <t xml:space="preserve">1.70694470405579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.690544962883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7142333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69464492797852</t>
+    <t xml:space="preserve">1.69054484367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71423351764679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69464480876923</t>
   </si>
   <si>
     <t xml:space="preserve">1.71241128444672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72380006313324</t>
+    <t xml:space="preserve">1.72379994392395</t>
   </si>
   <si>
     <t xml:space="preserve">1.74156641960144</t>
@@ -5090,7 +5090,7 @@
     <t xml:space="preserve">1.74794411659241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75341081619263</t>
+    <t xml:space="preserve">1.75341069698334</t>
   </si>
   <si>
     <t xml:space="preserve">1.7921324968338</t>
@@ -5105,7 +5105,7 @@
     <t xml:space="preserve">1.84497630596161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83586525917053</t>
+    <t xml:space="preserve">1.83586537837982</t>
   </si>
   <si>
     <t xml:space="preserve">1.84284818172455</t>
@@ -5949,6 +5949,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.36500000953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43700003623962</t>
   </si>
 </sst>
 </file>
@@ -71131,7 +71134,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6506134259</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>11298852</v>
@@ -71152,6 +71155,32 @@
         <v>1978</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6493055556</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>16117302</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>2.44300007820129</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>2.37199997901917</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>2.37599992752075</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>2.43700003623962</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1979</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="1980">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="1981">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,64 +44,64 @@
     <t xml:space="preserve">A2A.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774303913116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76930046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77743124961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772427618503571</t>
+    <t xml:space="preserve">0.774303793907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76930034160614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777431309223175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772427558898926</t>
   </si>
   <si>
     <t xml:space="preserve">0.775554835796356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73615175485611</t>
+    <t xml:space="preserve">0.736151695251465</t>
   </si>
   <si>
     <t xml:space="preserve">0.728020846843719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.708632051944733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701126635074615</t>
+    <t xml:space="preserve">0.708631932735443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701126575469971</t>
   </si>
   <si>
     <t xml:space="preserve">0.678610503673553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.686115741729736</t>
+    <t xml:space="preserve">0.686115801334381</t>
   </si>
   <si>
     <t xml:space="preserve">0.662974238395691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669854283332825</t>
+    <t xml:space="preserve">0.669854164123535</t>
   </si>
   <si>
     <t xml:space="preserve">0.673606872558594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.661723375320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.68986850976944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.667352497577667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.688617527484894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689243137836456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.676108658313751</t>
+    <t xml:space="preserve">0.661723434925079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689868569374084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.667352437973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.688617646694183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689243078231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.676108717918396</t>
   </si>
   <si>
     <t xml:space="preserve">0.671105146408081</t>
@@ -122,97 +122,97 @@
     <t xml:space="preserve">0.605745851993561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610749363899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614189326763153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627323746681213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617942094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624821960926056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.646712720394135</t>
+    <t xml:space="preserve">0.610749423503876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614189386367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627323865890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617942035198212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624822020530701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64671266078949</t>
   </si>
   <si>
     <t xml:space="preserve">0.636080086231232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656719744205475</t>
+    <t xml:space="preserve">0.656719863414764</t>
   </si>
   <si>
     <t xml:space="preserve">0.645461738109589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641083598136902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647963583469391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.657345294952393</t>
+    <t xml:space="preserve">0.641083657741547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.647963464260101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.657345235347748</t>
   </si>
   <si>
     <t xml:space="preserve">0.661097943782806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672981381416321</t>
+    <t xml:space="preserve">0.672981441020966</t>
   </si>
   <si>
     <t xml:space="preserve">0.666101574897766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66485059261322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658596158027649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651716232299805</t>
+    <t xml:space="preserve">0.664850533008575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658596217632294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651716291904449</t>
   </si>
   <si>
     <t xml:space="preserve">0.654843509197235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669228911399841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713010013103485</t>
+    <t xml:space="preserve">0.669228851795197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71301007270813</t>
   </si>
   <si>
     <t xml:space="preserve">0.69299578666687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.691119432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.694246649742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69799941778183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696123003959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703002870082855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692370295524597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.699250221252441</t>
+    <t xml:space="preserve">0.691119372844696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.694246709346771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697999358177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696122944355011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692370355129242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.699250280857086</t>
   </si>
   <si>
     <t xml:space="preserve">0.714260935783386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714886486530304</t>
+    <t xml:space="preserve">0.714886367321014</t>
   </si>
   <si>
     <t xml:space="preserve">0.702377498149872</t>
@@ -221,37 +221,37 @@
     <t xml:space="preserve">0.705504715442657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.735526144504547</t>
+    <t xml:space="preserve">0.735526263713837</t>
   </si>
   <si>
     <t xml:space="preserve">0.740529775619507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.744282603263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748660624027252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.738027989864349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750536978244781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75428968667984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768049478530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757416784763336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766798555850983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.752413332462311</t>
+    <t xml:space="preserve">0.744282424449921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748660564422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.738028049468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750536918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754289567470551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768049538135529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757416844367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766798496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.752413272857666</t>
   </si>
   <si>
     <t xml:space="preserve">0.781183838844299</t>
@@ -263,43 +263,43 @@
     <t xml:space="preserve">0.786187469959259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779307425022125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768674969673157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755540430545807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.760544002056122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.764296889305115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770551204681396</t>
+    <t xml:space="preserve">0.779307544231415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768674910068512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755540549755096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.760544121265411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.764296650886536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770551323890686</t>
   </si>
   <si>
     <t xml:space="preserve">0.75929319858551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769925713539124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76116955280304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767423987388611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747409701347351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751788020133972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754915058612823</t>
+    <t xml:space="preserve">0.769925832748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761169493198395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767424046993256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747409760951996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751787781715393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754915177822113</t>
   </si>
   <si>
     <t xml:space="preserve">0.781809270381927</t>
@@ -311,43 +311,43 @@
     <t xml:space="preserve">0.804950892925262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799321889877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78556215763092</t>
+    <t xml:space="preserve">0.79932177066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785562098026276</t>
   </si>
   <si>
     <t xml:space="preserve">0.796820104122162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791816413402557</t>
+    <t xml:space="preserve">0.791816353797913</t>
   </si>
   <si>
     <t xml:space="preserve">0.801823616027832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.733649849891663</t>
+    <t xml:space="preserve">0.733649790287018</t>
   </si>
   <si>
     <t xml:space="preserve">0.725519061088562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766306340694427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759828805923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750760197639465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778614103794098</t>
+    <t xml:space="preserve">0.766306400299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759828686714172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750760078430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778613924980164</t>
   </si>
   <si>
     <t xml:space="preserve">0.703473210334778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69246119260788</t>
+    <t xml:space="preserve">0.692461133003235</t>
   </si>
   <si>
     <t xml:space="preserve">0.705416560173035</t>
@@ -359,13 +359,13 @@
     <t xml:space="preserve">0.763067662715912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.762419939041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769545257091522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75788551568985</t>
+    <t xml:space="preserve">0.762419879436493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769545316696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75788539648056</t>
   </si>
   <si>
     <t xml:space="preserve">0.742986857891083</t>
@@ -374,19 +374,19 @@
     <t xml:space="preserve">0.742339253425598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.758533298969269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77731853723526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774079620838165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776022970676422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783796191215515</t>
+    <t xml:space="preserve">0.758533358573914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777318477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77407968044281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776022911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78379613161087</t>
   </si>
   <si>
     <t xml:space="preserve">0.779909551143646</t>
@@ -401,28 +401,28 @@
     <t xml:space="preserve">0.794160306453705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805172443389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807763397693634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.822661995887756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81747978925705</t>
+    <t xml:space="preserve">0.805172502994537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807763457298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.822661936283112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817479908466339</t>
   </si>
   <si>
     <t xml:space="preserve">0.820718705654144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.822014331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809706807136536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814241051673889</t>
+    <t xml:space="preserve">0.822014391422272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809706628322601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814241170883179</t>
   </si>
   <si>
     <t xml:space="preserve">0.816184401512146</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">0.804524660110474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801285803318024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812945544719696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801933526992798</t>
+    <t xml:space="preserve">0.801285684108734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812945604324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801933467388153</t>
   </si>
   <si>
     <t xml:space="preserve">0.786387145519257</t>
@@ -446,28 +446,28 @@
     <t xml:space="preserve">0.788330495357513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771488547325134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783148407936096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782500505447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781852781772614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770193099975586</t>
+    <t xml:space="preserve">0.771488606929779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783148229122162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782500684261322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781852900981903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770193040370941</t>
   </si>
   <si>
     <t xml:space="preserve">0.785091698169708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.795455932617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811002194881439</t>
+    <t xml:space="preserve">0.795455992221832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811002254486084</t>
   </si>
   <si>
     <t xml:space="preserve">0.794808149337769</t>
@@ -479,67 +479,67 @@
     <t xml:space="preserve">0.798694789409637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.802581250667572</t>
+    <t xml:space="preserve">0.802581369876862</t>
   </si>
   <si>
     <t xml:space="preserve">0.790921568870544</t>
   </si>
   <si>
-    <t xml:space="preserve">0.796751379966736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799342513084412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81035453081131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78055727481842</t>
+    <t xml:space="preserve">0.796751439571381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799342453479767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810354471206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780557334423065</t>
   </si>
   <si>
     <t xml:space="preserve">0.784443855285645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785739541053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827196478843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813593327999115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800637900829315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79739910364151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803876876831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807115733623505</t>
+    <t xml:space="preserve">0.785739481449127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827196419239044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81359338760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800638020038605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7973992228508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803876757621765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807115793228149</t>
   </si>
   <si>
     <t xml:space="preserve">0.761124312877655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.770840883255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73132711648941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735861539840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.720315098762512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721610546112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.719019591808319</t>
+    <t xml:space="preserve">0.77084082365036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.731327056884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735861480236053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.720315158367157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.72161066532135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.719019651412964</t>
   </si>
   <si>
     <t xml:space="preserve">0.696347773075104</t>
@@ -548,190 +548,190 @@
     <t xml:space="preserve">0.696995556354523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.709950923919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713837504386902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.711894094944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.707359850406647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728736042976379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715780854225159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722258448600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765010893344879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7546466588974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755294442176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78768265247345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776670813560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772136270999908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787034928798676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816832184791565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819423198699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799990296363831</t>
+    <t xml:space="preserve">0.709950864315033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713837444782257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.711894154548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.707359790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728735983371735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715780794620514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722258508205414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76501077413559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754646599292755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755294501781464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787682771682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776670694351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772136390209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78703498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816832304000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819423258304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799990236759186</t>
   </si>
   <si>
     <t xml:space="preserve">0.824605345726013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838856339454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831730782985687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832378566265106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840151786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848572731018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841447353363037</t>
+    <t xml:space="preserve">0.838856041431427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831730842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832378506660461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840151727199554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848572671413422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841447234153748</t>
   </si>
   <si>
     <t xml:space="preserve">0.844686031341553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830435216426849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798046886920929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815536499023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820071041584015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80646800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811650097370148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83626514673233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844038307666779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837560713291168</t>
+    <t xml:space="preserve">0.830435156822205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798047006130219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815536618232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820070862770081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806467890739441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811650156974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836265027523041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844038367271423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837560653686523</t>
   </si>
   <si>
     <t xml:space="preserve">0.836912930011749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.821366488933563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828491866588593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825900852680206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829139649868011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84662938117981</t>
+    <t xml:space="preserve">0.821366608142853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828492045402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825900971889496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829139769077301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84662926197052</t>
   </si>
   <si>
     <t xml:space="preserve">0.849220395088196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.864766776561737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867357909679413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868005633354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870596647262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857641398906708</t>
+    <t xml:space="preserve">0.864766836166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867357790470123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868005692958832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870596766471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857641458511353</t>
   </si>
   <si>
     <t xml:space="preserve">0.865414559841156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866710186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853107094764709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855698049068451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858289182186127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860232472419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87253999710083</t>
+    <t xml:space="preserve">0.866710126399994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853107035160065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855698108673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858289241790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860232532024384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872539877891541</t>
   </si>
   <si>
     <t xml:space="preserve">0.874483406543732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.887438654899597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893916130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892620742321014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912701427936554</t>
+    <t xml:space="preserve">0.887438774108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893916189670563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89262068271637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912701547145844</t>
   </si>
   <si>
     <t xml:space="preserve">0.909462571144104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908167123794556</t>
+    <t xml:space="preserve">0.908167064189911</t>
   </si>
   <si>
     <t xml:space="preserve">0.919826745986938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918531477451324</t>
+    <t xml:space="preserve">0.91853141784668</t>
   </si>
   <si>
     <t xml:space="preserve">0.875778794288635</t>
@@ -740,46 +740,46 @@
     <t xml:space="preserve">0.877722024917603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.891972839832306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884847581386566</t>
+    <t xml:space="preserve">0.891972959041595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884847640991211</t>
   </si>
   <si>
     <t xml:space="preserve">0.895211815834045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.884199678897858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876426458358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862175762653351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856345951557159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882256627082825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89909827709198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890677332878113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926952183246613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915292501449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917235970497131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966466069221497</t>
+    <t xml:space="preserve">0.884199738502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876426577568054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862175643444061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85634583234787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882256507873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899098336696625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890677392482758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926952421665192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91529244184494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917235612869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966465950012207</t>
   </si>
   <si>
     <t xml:space="preserve">0.95804488658905</t>
@@ -791,16 +791,16 @@
     <t xml:space="preserve">0.961283802986145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.963227152824402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941850900650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941202998161316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958692729473114</t>
+    <t xml:space="preserve">0.963227033615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94185084104538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941203117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958692789077759</t>
   </si>
   <si>
     <t xml:space="preserve">0.982278227806091</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">0.96820741891861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.981608211994171</t>
+    <t xml:space="preserve">0.981608092784882</t>
   </si>
   <si>
     <t xml:space="preserve">0.986298382282257</t>
@@ -833,13 +833,13 @@
     <t xml:space="preserve">0.989648520946503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97490781545639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999699294567108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00505948066711</t>
+    <t xml:space="preserve">0.97490793466568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999699115753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0050595998764</t>
   </si>
   <si>
     <t xml:space="preserve">0.998359203338623</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">0.997688949108124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00170922279358</t>
+    <t xml:space="preserve">1.00170934200287</t>
   </si>
   <si>
     <t xml:space="preserve">1.00706958770752</t>
@@ -857,16 +857,16 @@
     <t xml:space="preserve">1.02047038078308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02985095977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01779043674469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995008826255798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999029278755188</t>
+    <t xml:space="preserve">1.02985084056854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0177903175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995008945465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999029219150543</t>
   </si>
   <si>
     <t xml:space="preserve">0.976917862892151</t>
@@ -875,37 +875,37 @@
     <t xml:space="preserve">0.974237680435181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970217406749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965527176856995</t>
+    <t xml:space="preserve">0.970217287540436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965527296066284</t>
   </si>
   <si>
     <t xml:space="preserve">0.960837006568909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961506903171539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964187145233154</t>
+    <t xml:space="preserve">0.961507022380829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964187264442444</t>
   </si>
   <si>
     <t xml:space="preserve">0.980268120765686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978927850723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984958469867706</t>
+    <t xml:space="preserve">0.978927969932556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984958350658417</t>
   </si>
   <si>
     <t xml:space="preserve">0.972897589206696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960166752338409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958826720714569</t>
+    <t xml:space="preserve">0.960166871547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958826839923859</t>
   </si>
   <si>
     <t xml:space="preserve">0.951456308364868</t>
@@ -914,31 +914,31 @@
     <t xml:space="preserve">0.955476582050323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949446201324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963517129421234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950116455554962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953466594219208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956816613674164</t>
+    <t xml:space="preserve">0.949446439743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963517010211945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950116217136383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953466475009918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956816732883453</t>
   </si>
   <si>
     <t xml:space="preserve">0.958156764507294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952796459197998</t>
+    <t xml:space="preserve">0.952796578407288</t>
   </si>
   <si>
     <t xml:space="preserve">0.962176978588104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944756031036377</t>
+    <t xml:space="preserve">0.944755971431732</t>
   </si>
   <si>
     <t xml:space="preserve">0.931355178356171</t>
@@ -947,13 +947,13 @@
     <t xml:space="preserve">0.948106169700623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954136610031128</t>
+    <t xml:space="preserve">0.954136490821838</t>
   </si>
   <si>
     <t xml:space="preserve">0.957486748695374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939395666122437</t>
+    <t xml:space="preserve">0.939395725727081</t>
   </si>
   <si>
     <t xml:space="preserve">0.946766078472137</t>
@@ -962,13 +962,13 @@
     <t xml:space="preserve">0.934705317020416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.928674936294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9246546626091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932695209980011</t>
+    <t xml:space="preserve">0.9286749958992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924654603004456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932695150375366</t>
   </si>
   <si>
     <t xml:space="preserve">0.945426046848297</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">0.959496855735779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973567485809326</t>
+    <t xml:space="preserve">0.97356766462326</t>
   </si>
   <si>
     <t xml:space="preserve">0.978257954120636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993668913841248</t>
+    <t xml:space="preserve">0.993668794631958</t>
   </si>
   <si>
     <t xml:space="preserve">0.984288275241852</t>
@@ -992,28 +992,28 @@
     <t xml:space="preserve">0.983618259429932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994338810443878</t>
+    <t xml:space="preserve">0.994338929653168</t>
   </si>
   <si>
     <t xml:space="preserve">0.977587938308716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980938076972961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972227573394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96619725227356</t>
+    <t xml:space="preserve">0.980938017368317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972227692604065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96619713306427</t>
   </si>
   <si>
     <t xml:space="preserve">0.969547510147095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968877553939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971557676792145</t>
+    <t xml:space="preserve">0.96887743473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971557557582855</t>
   </si>
   <si>
     <t xml:space="preserve">0.995678961277008</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">1.02114057540894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01041972637177</t>
+    <t xml:space="preserve">1.01041984558105</t>
   </si>
   <si>
     <t xml:space="preserve">1.01444017887115</t>
@@ -1043,16 +1043,16 @@
     <t xml:space="preserve">1.0285108089447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03320133686066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03923165798187</t>
+    <t xml:space="preserve">1.03320121765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03923153877258</t>
   </si>
   <si>
     <t xml:space="preserve">1.0265007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0553126335144</t>
+    <t xml:space="preserve">1.05531251430511</t>
   </si>
   <si>
     <t xml:space="preserve">1.05866277217865</t>
@@ -1067,34 +1067,34 @@
     <t xml:space="preserve">1.0680433511734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0727334022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08613431453705</t>
+    <t xml:space="preserve">1.07273352146149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08613443374634</t>
   </si>
   <si>
     <t xml:space="preserve">1.09551477432251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08345413208008</t>
+    <t xml:space="preserve">1.08345425128937</t>
   </si>
   <si>
     <t xml:space="preserve">1.08211410045624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0539722442627</t>
+    <t xml:space="preserve">1.05397236347198</t>
   </si>
   <si>
     <t xml:space="preserve">1.06000280380249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04392182826996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04861235618591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04660201072693</t>
+    <t xml:space="preserve">1.04392194747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04861223697662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04660189151764</t>
   </si>
   <si>
     <t xml:space="preserve">1.03990161418915</t>
@@ -1106,28 +1106,28 @@
     <t xml:space="preserve">1.01980030536652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01578009128571</t>
+    <t xml:space="preserve">1.015780210495</t>
   </si>
   <si>
     <t xml:space="preserve">1.05196237564087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06737327575684</t>
+    <t xml:space="preserve">1.06737339496613</t>
   </si>
   <si>
     <t xml:space="preserve">1.06603312492371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02449071407318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01846027374268</t>
+    <t xml:space="preserve">1.02449059486389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01846039295197</t>
   </si>
   <si>
     <t xml:space="preserve">1.02784097194672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05665254592896</t>
+    <t xml:space="preserve">1.05665266513824</t>
   </si>
   <si>
     <t xml:space="preserve">1.06134283542633</t>
@@ -1139,52 +1139,52 @@
     <t xml:space="preserve">1.07943391799927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06938314437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05933260917664</t>
+    <t xml:space="preserve">1.06938326358795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05933272838593</t>
   </si>
   <si>
     <t xml:space="preserve">1.03856146335602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02683591842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03588140010834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04191172122955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996349036693573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971222400665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995343863964081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944420874118805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953131496906281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941405713558197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959831953048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9464311003685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957821547985077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950451135635376</t>
+    <t xml:space="preserve">1.02683579921722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03588128089905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04191184043884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996348917484283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971222579479218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99534398317337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944420993328094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953131377696991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941405773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959831714630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946431219577789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957821786403656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950451374053955</t>
   </si>
   <si>
     <t xml:space="preserve">0.936380445957184</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">0.991323828697205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975577831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993333876132965</t>
+    <t xml:space="preserve">0.975577712059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993333756923676</t>
   </si>
   <si>
     <t xml:space="preserve">1.00003409385681</t>
@@ -1214,16 +1214,16 @@
     <t xml:space="preserve">1.00673460960388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999364376068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04023659229279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04157662391663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04224681854248</t>
+    <t xml:space="preserve">0.999364256858826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04023671150208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04157674312592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04224669933319</t>
   </si>
   <si>
     <t xml:space="preserve">1.04961717128754</t>
@@ -1232,19 +1232,19 @@
     <t xml:space="preserve">1.04995214939117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06268298625946</t>
+    <t xml:space="preserve">1.06268286705017</t>
   </si>
   <si>
     <t xml:space="preserve">1.07206344604492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05832755565643</t>
+    <t xml:space="preserve">1.05832767486572</t>
   </si>
   <si>
     <t xml:space="preserve">1.06335306167603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07407355308533</t>
+    <t xml:space="preserve">1.07407367229462</t>
   </si>
   <si>
     <t xml:space="preserve">1.08043897151947</t>
@@ -1253,19 +1253,19 @@
     <t xml:space="preserve">1.08546423912048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0904895067215</t>
+    <t xml:space="preserve">1.09048974514008</t>
   </si>
   <si>
     <t xml:space="preserve">1.09484481811523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09819519519806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0985301733017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12198138237</t>
+    <t xml:space="preserve">1.09819507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09853005409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12198126316071</t>
   </si>
   <si>
     <t xml:space="preserve">1.11762619018555</t>
@@ -1283,22 +1283,22 @@
     <t xml:space="preserve">1.12265145778656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13002181053162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10992085933685</t>
+    <t xml:space="preserve">1.13002192974091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10992074012756</t>
   </si>
   <si>
     <t xml:space="preserve">1.11829614639282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05732262134552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03387141227722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0389529466629</t>
+    <t xml:space="preserve">1.05732250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03387117385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03895282745361</t>
   </si>
   <si>
     <t xml:space="preserve">1.05287516117096</t>
@@ -1307,19 +1307,19 @@
     <t xml:space="preserve">1.04208540916443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04730606079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02572667598724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00693166255951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980827033519745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998926281929016</t>
+    <t xml:space="preserve">1.04730629920959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02572679519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00693154335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980827271938324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998926162719727</t>
   </si>
   <si>
     <t xml:space="preserve">1.01076006889343</t>
@@ -1328,16 +1328,16 @@
     <t xml:space="preserve">1.00484323501587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02920734882355</t>
+    <t xml:space="preserve">1.02920722961426</t>
   </si>
   <si>
     <t xml:space="preserve">1.00936806201935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00658345222473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999622404575348</t>
+    <t xml:space="preserve">1.00658357143402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999622285366058</t>
   </si>
   <si>
     <t xml:space="preserve">0.968993186950684</t>
@@ -1346,43 +1346,43 @@
     <t xml:space="preserve">1.01598107814789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02398645877838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0316436290741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02851104736328</t>
+    <t xml:space="preserve">1.02398633956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03164374828339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02851116657257</t>
   </si>
   <si>
     <t xml:space="preserve">1.01980972290039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04382574558258</t>
+    <t xml:space="preserve">1.04382598400116</t>
   </si>
   <si>
     <t xml:space="preserve">1.04661011695862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02363836765289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02537858486176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00588738918304</t>
+    <t xml:space="preserve">1.0236382484436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02537846565247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00588750839233</t>
   </si>
   <si>
     <t xml:space="preserve">1.01250052452087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02120196819305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02642285823822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03373217582703</t>
+    <t xml:space="preserve">1.02120184898376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02642273902893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03373193740845</t>
   </si>
   <si>
     <t xml:space="preserve">1.01389265060425</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">1.03860485553741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05113506317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06122851371765</t>
+    <t xml:space="preserve">1.05113482475281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06122863292694</t>
   </si>
   <si>
     <t xml:space="preserve">1.07236647605896</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">1.05600762367249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07375884056091</t>
+    <t xml:space="preserve">1.07375872135162</t>
   </si>
   <si>
     <t xml:space="preserve">1.06714558601379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0786315202713</t>
+    <t xml:space="preserve">1.07863140106201</t>
   </si>
   <si>
     <t xml:space="preserve">1.09290182590485</t>
@@ -1427,16 +1427,16 @@
     <t xml:space="preserve">1.10160326957703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08420050144196</t>
+    <t xml:space="preserve">1.08420038223267</t>
   </si>
   <si>
     <t xml:space="preserve">1.04835057258606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06157672405243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07201826572418</t>
+    <t xml:space="preserve">1.06157660484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07201850414276</t>
   </si>
   <si>
     <t xml:space="preserve">1.07584702968597</t>
@@ -1445,19 +1445,19 @@
     <t xml:space="preserve">1.07132232189178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0939462184906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08106791973114</t>
+    <t xml:space="preserve">1.09394598007202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08106780052185</t>
   </si>
   <si>
     <t xml:space="preserve">1.09011733531952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08246004581451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10299551486969</t>
+    <t xml:space="preserve">1.0824601650238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10299563407898</t>
   </si>
   <si>
     <t xml:space="preserve">1.12005043029785</t>
@@ -1469,22 +1469,22 @@
     <t xml:space="preserve">1.10473585128784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10612821578979</t>
+    <t xml:space="preserve">1.10612809658051</t>
   </si>
   <si>
     <t xml:space="preserve">1.11134910583496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10821640491486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10960853099823</t>
+    <t xml:space="preserve">1.10821628570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10960865020752</t>
   </si>
   <si>
     <t xml:space="preserve">1.08837723731995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08802890777588</t>
+    <t xml:space="preserve">1.08802902698517</t>
   </si>
   <si>
     <t xml:space="preserve">1.08942115306854</t>
@@ -1499,55 +1499,55 @@
     <t xml:space="preserve">1.03338396549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04243326187134</t>
+    <t xml:space="preserve">1.04243338108063</t>
   </si>
   <si>
     <t xml:space="preserve">1.02155005931854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03094756603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04173743724823</t>
+    <t xml:space="preserve">1.03094732761383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04173731803894</t>
   </si>
   <si>
     <t xml:space="preserve">1.05705177783966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07897961139679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09220564365387</t>
+    <t xml:space="preserve">1.0789794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09220576286316</t>
   </si>
   <si>
     <t xml:space="preserve">1.09116160869598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08454835414886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08141613006592</t>
+    <t xml:space="preserve">1.08454847335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08141589164734</t>
   </si>
   <si>
     <t xml:space="preserve">1.09847068786621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09603440761566</t>
+    <t xml:space="preserve">1.09603428840637</t>
   </si>
   <si>
     <t xml:space="preserve">1.07619512081146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07445478439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0587922334671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07758736610413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06923401355743</t>
+    <t xml:space="preserve">1.07445466518402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05879211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07758748531342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06923389434814</t>
   </si>
   <si>
     <t xml:space="preserve">1.04069304466248</t>
@@ -1556,40 +1556,40 @@
     <t xml:space="preserve">1.03199172019958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04452192783356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04417383670807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05183124542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03616857528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05844414234161</t>
+    <t xml:space="preserve">1.04452168941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04417371749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05183100700378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03616833686829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05844390392303</t>
   </si>
   <si>
     <t xml:space="preserve">1.03442811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00310277938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9916170835495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00832366943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01424098014832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01772117614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01354467868805</t>
+    <t xml:space="preserve">1.00310289859772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99161696434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00832378864288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01424074172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01772141456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01354455947876</t>
   </si>
   <si>
     <t xml:space="preserve">0.993705332279205</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">0.988136351108551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977346837520599</t>
+    <t xml:space="preserve">0.97734659910202</t>
   </si>
   <si>
     <t xml:space="preserve">1.00553917884827</t>
@@ -1607,31 +1607,31 @@
     <t xml:space="preserve">0.986047983169556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989528775215149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992313206195831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982915341854095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991965174674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01319658756256</t>
+    <t xml:space="preserve">0.989528596401215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992313086986542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98291540145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991964995861053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01319646835327</t>
   </si>
   <si>
     <t xml:space="preserve">1.00414705276489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0205055475235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0156329870224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03512406349182</t>
+    <t xml:space="preserve">1.02050566673279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01563310623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03512418270111</t>
   </si>
   <si>
     <t xml:space="preserve">1.0393009185791</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">1.05252718925476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05461537837982</t>
+    <t xml:space="preserve">1.05461549758911</t>
   </si>
   <si>
     <t xml:space="preserve">1.03721261024475</t>
@@ -1649,19 +1649,19 @@
     <t xml:space="preserve">1.02711892127991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0399968624115</t>
+    <t xml:space="preserve">1.03999698162079</t>
   </si>
   <si>
     <t xml:space="preserve">1.06610131263733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06088054180145</t>
+    <t xml:space="preserve">1.06088066101074</t>
   </si>
   <si>
     <t xml:space="preserve">1.04034519195557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03233969211578</t>
+    <t xml:space="preserve">1.03233981132507</t>
   </si>
   <si>
     <t xml:space="preserve">1.04278147220612</t>
@@ -1673,34 +1673,34 @@
     <t xml:space="preserve">1.07410669326782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10090720653534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11761403083801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12701141834259</t>
+    <t xml:space="preserve">1.10090708732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11761379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12701153755188</t>
   </si>
   <si>
     <t xml:space="preserve">1.11378538608551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1064760684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12318301200867</t>
+    <t xml:space="preserve">1.10647594928741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12318289279938</t>
   </si>
   <si>
     <t xml:space="preserve">1.13118827342987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11448132991791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08872520923615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09464204311371</t>
+    <t xml:space="preserve">1.11448156833649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08872509002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.094642162323</t>
   </si>
   <si>
     <t xml:space="preserve">1.11622178554535</t>
@@ -1709,25 +1709,25 @@
     <t xml:space="preserve">1.1183100938797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13501691818237</t>
+    <t xml:space="preserve">1.13501667976379</t>
   </si>
   <si>
     <t xml:space="preserve">1.13675713539124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13814949989319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14302206039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10403978824615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10891258716583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09951484203339</t>
+    <t xml:space="preserve">1.1381493806839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14302217960358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10403966903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10891270637512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09951496124268</t>
   </si>
   <si>
     <t xml:space="preserve">1.10195136070251</t>
@@ -1742,22 +1742,22 @@
     <t xml:space="preserve">1.10578000545502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09185755252838</t>
+    <t xml:space="preserve">1.09185779094696</t>
   </si>
   <si>
     <t xml:space="preserve">1.07793533802032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08071970939636</t>
+    <t xml:space="preserve">1.08071982860565</t>
   </si>
   <si>
     <t xml:space="preserve">1.08663690090179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06227266788483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08280825614929</t>
+    <t xml:space="preserve">1.06227278709412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08280837535858</t>
   </si>
   <si>
     <t xml:space="preserve">1.09742665290833</t>
@@ -1769,28 +1769,28 @@
     <t xml:space="preserve">1.09777462482452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10369181632996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11100101470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10543191432953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08594071865082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09568631649017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08907330036163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11726582050323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12074661254883</t>
+    <t xml:space="preserve">1.10369169712067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11100089550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10543203353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08594059944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09568619728088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08907318115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11726593971252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12074649333954</t>
   </si>
   <si>
     <t xml:space="preserve">1.10752022266388</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">1.12179064750671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11935424804688</t>
+    <t xml:space="preserve">1.11935436725616</t>
   </si>
   <si>
     <t xml:space="preserve">1.13571298122406</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">1.13536500930786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13084030151367</t>
+    <t xml:space="preserve">1.13084018230438</t>
   </si>
   <si>
     <t xml:space="preserve">1.13223242759705</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">1.14754700660706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.063316822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05391931533813</t>
+    <t xml:space="preserve">1.06331694126129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05391943454742</t>
   </si>
   <si>
     <t xml:space="preserve">1.04626202583313</t>
@@ -1838,55 +1838,55 @@
     <t xml:space="preserve">1.02433454990387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0194616317749</t>
+    <t xml:space="preserve">1.01946139335632</t>
   </si>
   <si>
     <t xml:space="preserve">1.01632905006409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00379908084869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997881948947906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.007279753685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02015769481659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07654321193695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08517646789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09720540046692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09647643566132</t>
+    <t xml:space="preserve">1.0037989616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997882068157196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00727963447571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02015781402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07654309272766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08517634868622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09720551967621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09647655487061</t>
   </si>
   <si>
     <t xml:space="preserve">1.06622135639191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0811665058136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07205379009247</t>
+    <t xml:space="preserve">1.08116662502289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07205367088318</t>
   </si>
   <si>
     <t xml:space="preserve">1.06038904190063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05127596855164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06403422355652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07168912887573</t>
+    <t xml:space="preserve">1.05127608776093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0640344619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07168924808502</t>
   </si>
   <si>
     <t xml:space="preserve">1.08043766021729</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">1.10230875015259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09574735164642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09829902648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13219964504242</t>
+    <t xml:space="preserve">1.09574747085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09829914569855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13219952583313</t>
   </si>
   <si>
     <t xml:space="preserve">1.12563824653625</t>
@@ -1925,16 +1925,16 @@
     <t xml:space="preserve">1.14750933647156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13584470748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11944127082825</t>
+    <t xml:space="preserve">1.1358448266983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11944139003754</t>
   </si>
   <si>
     <t xml:space="preserve">1.11543154716492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10376679897308</t>
+    <t xml:space="preserve">1.10376691818237</t>
   </si>
   <si>
     <t xml:space="preserve">1.11251533031464</t>
@@ -1946,19 +1946,19 @@
     <t xml:space="preserve">1.13511574268341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15006113052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15188360214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14787375926971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15261256694794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16427731513977</t>
+    <t xml:space="preserve">1.1500608921051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15188372135162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.147873878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15261268615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16427743434906</t>
   </si>
   <si>
     <t xml:space="preserve">1.1704740524292</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">1.17156767845154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17229676246643</t>
+    <t xml:space="preserve">1.17229664325714</t>
   </si>
   <si>
     <t xml:space="preserve">1.17849361896515</t>
@@ -1982,25 +1982,25 @@
     <t xml:space="preserve">1.16318368911743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16609978675842</t>
+    <t xml:space="preserve">1.16609966754913</t>
   </si>
   <si>
     <t xml:space="preserve">1.17995154857635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18469047546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18104517459869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17120325565338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17375481128693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14969658851624</t>
+    <t xml:space="preserve">1.18469059467316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18104529380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1712030172348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17375469207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14969635009766</t>
   </si>
   <si>
     <t xml:space="preserve">1.15407073497772</t>
@@ -2009,13 +2009,13 @@
     <t xml:space="preserve">1.17083859443665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16209006309509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16682875156403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16755795478821</t>
+    <t xml:space="preserve">1.16209018230438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1668289899826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16755783557892</t>
   </si>
   <si>
     <t xml:space="preserve">1.17010962963104</t>
@@ -2030,22 +2030,22 @@
     <t xml:space="preserve">1.12782526016235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14277052879333</t>
+    <t xml:space="preserve">1.14277064800262</t>
   </si>
   <si>
     <t xml:space="preserve">1.16099655628204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14459323883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15297722816467</t>
+    <t xml:space="preserve">1.14459311962128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15297710895538</t>
   </si>
   <si>
     <t xml:space="preserve">1.13985443115234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13475096225739</t>
+    <t xml:space="preserve">1.13475120067596</t>
   </si>
   <si>
     <t xml:space="preserve">1.16391277313232</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">1.16573548316956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16500639915466</t>
+    <t xml:space="preserve">1.16500627994537</t>
   </si>
   <si>
     <t xml:space="preserve">1.18833565711975</t>
@@ -2078,10 +2078,10 @@
     <t xml:space="preserve">1.16464173793793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17922258377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18213868141174</t>
+    <t xml:space="preserve">1.17922246456146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18213880062103</t>
   </si>
   <si>
     <t xml:space="preserve">1.17630624771118</t>
@@ -2102,16 +2102,16 @@
     <t xml:space="preserve">1.22770380973816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23207795619965</t>
+    <t xml:space="preserve">1.23207807540894</t>
   </si>
   <si>
     <t xml:space="preserve">1.21421658992767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21166491508484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23134887218475</t>
+    <t xml:space="preserve">1.21166503429413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23134899139404</t>
   </si>
   <si>
     <t xml:space="preserve">1.23025548458099</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">1.21931993961334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23791015148163</t>
+    <t xml:space="preserve">1.23791027069092</t>
   </si>
   <si>
     <t xml:space="preserve">1.23462975025177</t>
@@ -2135,13 +2135,13 @@
     <t xml:space="preserve">1.21640360355377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22187125682831</t>
+    <t xml:space="preserve">1.22187149524689</t>
   </si>
   <si>
     <t xml:space="preserve">1.22114229202271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22405862808228</t>
+    <t xml:space="preserve">1.22405850887299</t>
   </si>
   <si>
     <t xml:space="preserve">1.23061990737915</t>
@@ -2162,64 +2162,64 @@
     <t xml:space="preserve">1.27363324165344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27691388130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31154346466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3133659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30972075462341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30826258659363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31591761112213</t>
+    <t xml:space="preserve">1.27691400051117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31154358386993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31336605548859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30972063541412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30826270580292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31591773033142</t>
   </si>
   <si>
     <t xml:space="preserve">1.29331743717194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31518864631653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31445956230164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30862712860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29732716083527</t>
+    <t xml:space="preserve">1.31518852710724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31445968151093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30862724781036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29732704162598</t>
   </si>
   <si>
     <t xml:space="preserve">1.27873647212982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.288578748703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28420448303223</t>
+    <t xml:space="preserve">1.28857862949371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28420436382294</t>
   </si>
   <si>
     <t xml:space="preserve">1.27727842330933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27509117126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26452028751373</t>
+    <t xml:space="preserve">1.27509129047394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26452040672302</t>
   </si>
   <si>
     <t xml:space="preserve">1.24884593486786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24665880203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25249111652374</t>
+    <t xml:space="preserve">1.24665892124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25249123573303</t>
   </si>
   <si>
     <t xml:space="preserve">1.24520063400269</t>
@@ -2228,40 +2228,40 @@
     <t xml:space="preserve">1.24483621120453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19052267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19635510444641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1985422372818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19343876838684</t>
+    <t xml:space="preserve">1.19052278995514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1963552236557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19854211807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19343888759613</t>
   </si>
   <si>
     <t xml:space="preserve">1.18068075180054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20218753814697</t>
+    <t xml:space="preserve">1.20218729972839</t>
   </si>
   <si>
     <t xml:space="preserve">1.18906462192535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19270992279053</t>
+    <t xml:space="preserve">1.19270980358124</t>
   </si>
   <si>
     <t xml:space="preserve">1.20656156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20729076862335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22515225410461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24155557155609</t>
+    <t xml:space="preserve">1.20729064941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22515213489532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24155533313751</t>
   </si>
   <si>
     <t xml:space="preserve">1.23353612422943</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">1.25504279136658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25066864490509</t>
+    <t xml:space="preserve">1.2506685256958</t>
   </si>
   <si>
     <t xml:space="preserve">1.25941693782806</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">1.25650084018707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26852989196777</t>
+    <t xml:space="preserve">1.26853001117706</t>
   </si>
   <si>
     <t xml:space="preserve">1.2998788356781</t>
@@ -2300,10 +2300,10 @@
     <t xml:space="preserve">1.29368197917938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2922238111496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30607569217682</t>
+    <t xml:space="preserve">1.29222393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30607557296753</t>
   </si>
   <si>
     <t xml:space="preserve">1.3520051240921</t>
@@ -2312,13 +2312,13 @@
     <t xml:space="preserve">1.34544372558594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33414375782013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3140949010849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32247889041901</t>
+    <t xml:space="preserve">1.33414363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31409502029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3224790096283</t>
   </si>
   <si>
     <t xml:space="preserve">1.32940495014191</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">1.33159196376801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33013379573822</t>
+    <t xml:space="preserve">1.33013367652893</t>
   </si>
   <si>
     <t xml:space="preserve">1.34981799125671</t>
@@ -2345,22 +2345,22 @@
     <t xml:space="preserve">1.34945344924927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35893106460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36986660957336</t>
+    <t xml:space="preserve">1.358931183815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36986649036407</t>
   </si>
   <si>
     <t xml:space="preserve">1.3822603225708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36038899421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34908878803253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26524949073792</t>
+    <t xml:space="preserve">1.3603892326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34908890724182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26524925231934</t>
   </si>
   <si>
     <t xml:space="preserve">1.25613629817963</t>
@@ -2369,13 +2369,13 @@
     <t xml:space="preserve">1.13766741752625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15589332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19708406925201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11579608917236</t>
+    <t xml:space="preserve">1.15589320659637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19708395004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11579620838165</t>
   </si>
   <si>
     <t xml:space="preserve">0.996233522891998</t>
@@ -2384,151 +2384,151 @@
     <t xml:space="preserve">0.924787521362305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.905467987060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733049929141998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772782683372498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750546932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775334358215332</t>
+    <t xml:space="preserve">0.905467927455902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733049988746643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772782564163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750546872615814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775334298610687</t>
   </si>
   <si>
     <t xml:space="preserve">0.751276016235352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.754556655883789</t>
+    <t xml:space="preserve">0.754556715488434</t>
   </si>
   <si>
     <t xml:space="preserve">0.741433918476105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.729040265083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786269903182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79720550775528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793195843696594</t>
+    <t xml:space="preserve">0.729040205478668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786269962787628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797205567359924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.793195784091949</t>
   </si>
   <si>
     <t xml:space="preserve">0.778250455856323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824544489383698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826002597808838</t>
+    <t xml:space="preserve">0.824544608592987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826002538204193</t>
   </si>
   <si>
     <t xml:space="preserve">0.816160559654236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841676950454712</t>
+    <t xml:space="preserve">0.841677010059357</t>
   </si>
   <si>
     <t xml:space="preserve">0.836209118366241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869016051292419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869745016098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855164110660553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876670897006989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889429032802582</t>
+    <t xml:space="preserve">0.869015991687775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869744956493378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855164170265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876670956611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889429152011871</t>
   </si>
   <si>
     <t xml:space="preserve">0.885783910751343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.897448420524597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910935759544373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91166478395462</t>
+    <t xml:space="preserve">0.897448480129242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910935819149017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911664724349976</t>
   </si>
   <si>
     <t xml:space="preserve">0.883961260318756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888335466384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879587054252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890158116817474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906926095485687</t>
+    <t xml:space="preserve">0.888335585594177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879587173461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89015805721283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906925976276398</t>
   </si>
   <si>
     <t xml:space="preserve">0.901458203792572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89963573217392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905832529067993</t>
+    <t xml:space="preserve">0.89963561296463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905832469463348</t>
   </si>
   <si>
     <t xml:space="preserve">0.872296571731567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.879951536655426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878128826618195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882138729095459</t>
+    <t xml:space="preserve">0.879951596260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878128945827484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882138669490814</t>
   </si>
   <si>
     <t xml:space="preserve">0.877764403820038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.914581120014191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93426513671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911300361156464</t>
+    <t xml:space="preserve">0.914580941200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934265077114105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911300301551819</t>
   </si>
   <si>
     <t xml:space="preserve">0.944332540035248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.902750790119171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914020597934723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910522997379303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912854731082916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946275532245636</t>
+    <t xml:space="preserve">0.902750730514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914020717144012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910523056983948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912854790687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946275413036346</t>
   </si>
   <si>
     <t xml:space="preserve">0.971146821975708</t>
@@ -2537,10 +2537,10 @@
     <t xml:space="preserve">0.950550377368927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971535325050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969592273235321</t>
+    <t xml:space="preserve">0.971535444259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969592392444611</t>
   </si>
   <si>
     <t xml:space="preserve">0.981639444828033</t>
@@ -2549,19 +2549,19 @@
     <t xml:space="preserve">1.00573348999023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04265177249908</t>
+    <t xml:space="preserve">1.04265189170837</t>
   </si>
   <si>
     <t xml:space="preserve">1.04342913627625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03060483932495</t>
+    <t xml:space="preserve">1.03060472011566</t>
   </si>
   <si>
     <t xml:space="preserve">1.05236732959747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02710723876953</t>
+    <t xml:space="preserve">1.02710735797882</t>
   </si>
   <si>
     <t xml:space="preserve">1.0119514465332</t>
@@ -2576,34 +2576,34 @@
     <t xml:space="preserve">0.978141844272614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01156270503998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01778054237366</t>
+    <t xml:space="preserve">1.01156282424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01778066158295</t>
   </si>
   <si>
     <t xml:space="preserve">1.00961971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0193350315094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01467156410217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972312688827515</t>
+    <t xml:space="preserve">1.01933491230011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01467180252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972312808036804</t>
   </si>
   <si>
     <t xml:space="preserve">0.963763117790222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977364718914032</t>
+    <t xml:space="preserve">0.977364599704742</t>
   </si>
   <si>
     <t xml:space="preserve">0.979696393013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984359741210938</t>
+    <t xml:space="preserve">0.984359622001648</t>
   </si>
   <si>
     <t xml:space="preserve">0.999904274940491</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">0.996795415878296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993686497211456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983193874359131</t>
+    <t xml:space="preserve">0.993686378002167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98319399356842</t>
   </si>
   <si>
     <t xml:space="preserve">0.98280531167984</t>
@@ -2624,16 +2624,16 @@
     <t xml:space="preserve">0.958322584629059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961431562900543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960654377937317</t>
+    <t xml:space="preserve">0.961431443691254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960654258728027</t>
   </si>
   <si>
     <t xml:space="preserve">0.973867237567902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973089993000031</t>
+    <t xml:space="preserve">0.973089873790741</t>
   </si>
   <si>
     <t xml:space="preserve">0.985137045383453</t>
@@ -2642,16 +2642,16 @@
     <t xml:space="preserve">0.987857341766357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985525667667389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949773132801056</t>
+    <t xml:space="preserve">0.985525548458099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949773013591766</t>
   </si>
   <si>
     <t xml:space="preserve">0.954436480998993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970758140087128</t>
+    <t xml:space="preserve">0.970758259296417</t>
   </si>
   <si>
     <t xml:space="preserve">0.92878794670105</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">0.95599091053009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959877133369446</t>
+    <t xml:space="preserve">0.959877014160156</t>
   </si>
   <si>
     <t xml:space="preserve">0.953659236431122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965317666530609</t>
+    <t xml:space="preserve">0.96531754732132</t>
   </si>
   <si>
     <t xml:space="preserve">0.982028067111969</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">1.01739203929901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00612223148346</t>
+    <t xml:space="preserve">1.00612199306488</t>
   </si>
   <si>
     <t xml:space="preserve">0.994852244853973</t>
@@ -2687,22 +2687,22 @@
     <t xml:space="preserve">0.979307770729065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989411652088165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987080097198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964928984642029</t>
+    <t xml:space="preserve">0.989411771297455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987079977989197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964929103851318</t>
   </si>
   <si>
     <t xml:space="preserve">0.96259731054306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958711326122284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96609491109848</t>
+    <t xml:space="preserve">0.958711206912994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96609503030777</t>
   </si>
   <si>
     <t xml:space="preserve">0.951327562332153</t>
@@ -2711,10 +2711,10 @@
     <t xml:space="preserve">0.954047858715057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975033044815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968037962913513</t>
+    <t xml:space="preserve">0.975032985210419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968037843704224</t>
   </si>
   <si>
     <t xml:space="preserve">0.937726140022278</t>
@@ -2723,49 +2723,49 @@
     <t xml:space="preserve">0.946664154529572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938503265380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942000687122345</t>
+    <t xml:space="preserve">0.938503324985504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942000865936279</t>
   </si>
   <si>
     <t xml:space="preserve">0.933451235294342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971924066543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94899594783783</t>
+    <t xml:space="preserve">0.97192394733429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94899582862854</t>
   </si>
   <si>
     <t xml:space="preserve">0.953270614147186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945886790752411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929565131664276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931119680404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900807797908783</t>
+    <t xml:space="preserve">0.9458869099617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929565072059631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931119561195374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900807738304138</t>
   </si>
   <si>
     <t xml:space="preserve">0.903528034687042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904693961143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898864686489105</t>
+    <t xml:space="preserve">0.904693841934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898864567279816</t>
   </si>
   <si>
     <t xml:space="preserve">0.878656625747681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.886428952217102</t>
+    <t xml:space="preserve">0.886428892612457</t>
   </si>
   <si>
     <t xml:space="preserve">0.901584923267365</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">0.840961158275604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830079913139343</t>
+    <t xml:space="preserve">0.830079853534698</t>
   </si>
   <si>
     <t xml:space="preserve">0.848344802856445</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">0.860780417919159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872050166130066</t>
+    <t xml:space="preserve">0.872050225734711</t>
   </si>
   <si>
     <t xml:space="preserve">0.898476004600525</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">0.892646729946136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.881376922130585</t>
+    <t xml:space="preserve">0.881376981735229</t>
   </si>
   <si>
     <t xml:space="preserve">0.942778050899506</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">0.955213665962219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95249330997467</t>
+    <t xml:space="preserve">0.95249342918396</t>
   </si>
   <si>
     <t xml:space="preserve">0.947441339492798</t>
@@ -2822,16 +2822,16 @@
     <t xml:space="preserve">0.97619891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01700329780579</t>
+    <t xml:space="preserve">1.01700341701508</t>
   </si>
   <si>
     <t xml:space="preserve">1.02205526828766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993297755718231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982416689395905</t>
+    <t xml:space="preserve">0.993297874927521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982416808605194</t>
   </si>
   <si>
     <t xml:space="preserve">0.975421667098999</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">0.976587533950806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997183859348297</t>
+    <t xml:space="preserve">0.997184097766876</t>
   </si>
   <si>
     <t xml:space="preserve">0.990966200828552</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">0.988245844841003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984748244285583</t>
+    <t xml:space="preserve">0.984748363494873</t>
   </si>
   <si>
     <t xml:space="preserve">0.995629549026489</t>
@@ -2861,13 +2861,13 @@
     <t xml:space="preserve">1.00651061534882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01583755016327</t>
+    <t xml:space="preserve">1.01583743095398</t>
   </si>
   <si>
     <t xml:space="preserve">1.0138943195343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03449094295502</t>
+    <t xml:space="preserve">1.03449082374573</t>
   </si>
   <si>
     <t xml:space="preserve">1.02399849891663</t>
@@ -2879,40 +2879,40 @@
     <t xml:space="preserve">1.03954291343689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03487968444824</t>
+    <t xml:space="preserve">1.03487956523895</t>
   </si>
   <si>
     <t xml:space="preserve">1.01428294181824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0375999212265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0321592092514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02050077915192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03099358081818</t>
+    <t xml:space="preserve">1.03759980201721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03215932846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02050089836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03099346160889</t>
   </si>
   <si>
     <t xml:space="preserve">1.06596863269806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07296371459961</t>
+    <t xml:space="preserve">1.0729638338089</t>
   </si>
   <si>
     <t xml:space="preserve">1.04653799533844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0589736700058</t>
+    <t xml:space="preserve">1.05897355079651</t>
   </si>
   <si>
     <t xml:space="preserve">1.0535329580307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06169390678406</t>
+    <t xml:space="preserve">1.06169402599335</t>
   </si>
   <si>
     <t xml:space="preserve">1.04498362541199</t>
@@ -2924,13 +2924,13 @@
     <t xml:space="preserve">1.13630795478821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15418422222137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12853574752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1382509469986</t>
+    <t xml:space="preserve">1.15418410301208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12853562831879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13825082778931</t>
   </si>
   <si>
     <t xml:space="preserve">1.14252579212189</t>
@@ -2942,28 +2942,28 @@
     <t xml:space="preserve">1.16195642948151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13863956928253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12154042720795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13475346565247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12698113918304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11415696144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10366439819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11221385002136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0931715965271</t>
+    <t xml:space="preserve">1.13863945007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12154054641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13475334644318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12698125839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11415684223175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10366415977478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11221396923065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09317171573639</t>
   </si>
   <si>
     <t xml:space="preserve">1.0838451385498</t>
@@ -2996,10 +2996,10 @@
     <t xml:space="preserve">1.14874351024628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15496146678925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16312229633331</t>
+    <t xml:space="preserve">1.15496134757996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16312217712402</t>
   </si>
   <si>
     <t xml:space="preserve">1.14563453197479</t>
@@ -3008,16 +3008,16 @@
     <t xml:space="preserve">1.15301835536957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14641177654266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17089450359344</t>
+    <t xml:space="preserve">1.14641189575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17089462280273</t>
   </si>
   <si>
     <t xml:space="preserve">1.18954813480377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20470404624939</t>
+    <t xml:space="preserve">1.2047039270401</t>
   </si>
   <si>
     <t xml:space="preserve">1.20664715766907</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">1.21558523178101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2175281047821</t>
+    <t xml:space="preserve">1.21752822399139</t>
   </si>
   <si>
     <t xml:space="preserve">1.20625853538513</t>
@@ -3035,25 +3035,25 @@
     <t xml:space="preserve">1.20392680168152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20859014987946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22413456439972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20975589752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19809758663177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21286487579346</t>
+    <t xml:space="preserve">1.20859003067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22413468360901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20975601673126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19809746742249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21286499500275</t>
   </si>
   <si>
     <t xml:space="preserve">1.21597385406494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21325349807739</t>
+    <t xml:space="preserve">1.2132533788681</t>
   </si>
   <si>
     <t xml:space="preserve">1.20431530475616</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">1.21247613430023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22685515880585</t>
+    <t xml:space="preserve">1.22685503959656</t>
   </si>
   <si>
     <t xml:space="preserve">1.21403074264526</t>
@@ -3071,16 +3071,16 @@
     <t xml:space="preserve">1.2357931137085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23812484741211</t>
+    <t xml:space="preserve">1.2381249666214</t>
   </si>
   <si>
     <t xml:space="preserve">1.23851346969604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24278819561005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26105296611786</t>
+    <t xml:space="preserve">1.24278831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26105284690857</t>
   </si>
   <si>
     <t xml:space="preserve">1.26455056667328</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">1.27582037448883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26066446304321</t>
+    <t xml:space="preserve">1.26066434383392</t>
   </si>
   <si>
     <t xml:space="preserve">1.26493918895721</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">1.27892935276031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3045779466629</t>
+    <t xml:space="preserve">1.30457782745361</t>
   </si>
   <si>
     <t xml:space="preserve">1.31779074668884</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">1.29291939735413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29874873161316</t>
+    <t xml:space="preserve">1.29874861240387</t>
   </si>
   <si>
     <t xml:space="preserve">1.31740212440491</t>
@@ -3119,412 +3119,412 @@
     <t xml:space="preserve">1.34693682193756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34382772445679</t>
+    <t xml:space="preserve">1.34382784366608</t>
   </si>
   <si>
     <t xml:space="preserve">1.34849119186401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35121130943298</t>
+    <t xml:space="preserve">1.35121154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37258529663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40067207813263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37502765655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38194763660431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37787699699402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39497327804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.391716837883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38438999652863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39456629753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38886749744415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41044127941132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42305994033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43323636054993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45847368240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43852806091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43771398067474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4491114616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44951868057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45725250244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45765960216522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45521724224091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43120110034943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4430056810379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44422686100006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42713057994843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41858243942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40352141857147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41288352012634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41695427894592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41898941993713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41329061985016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43527173995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3795051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38072645664215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39945089817047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41736137866974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.403928399086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40148615837097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34734797477722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35915267467499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38316869735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.395787358284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4511467218399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47719812393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47801232337952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47394168376923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47068524360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47923338413239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46824312210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4796404838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49348020553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50691306591034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52360236644745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53866326808929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54069864749908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55006098747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58262515068054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58669567108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56593585014343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58384621143341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55494546890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53215050697327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52726590633392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52889394760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52197420597076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.514240026474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51912474632263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50650596618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49755084514618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52238118648529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49307322502136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51464712619781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5162752866745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48615336418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48940980434418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49063098430634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42794454097748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45155382156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46173012256622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46213710308075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4837110042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47882616519928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48411810398102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45643842220306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45562422275543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43812108039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44544792175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44015634059906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45684552192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48737466335297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48533916473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5040637254715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46417248249054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4450409412384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47475588321686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49673664569855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50894832611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.502028465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48696756362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50365662574768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52970802783966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53662800788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57407689094543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55698072910309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55779469013214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50732028484344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48004746437073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49022388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49225914478302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.510169506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47760534286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50040030479431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50121438503265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51301884651184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51953184604645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51546132564545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3921240568161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4059636592865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39538037776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40637063980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45196080207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43079400062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45806670188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45440316200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45399606227875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42835175991058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39130973815918</t>
   </si>
   <si>
     <t xml:space="preserve">1.37258541584015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40067207813263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37502765655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38194763660431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37787699699402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39497327804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.391716837883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38438999652863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39456617832184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38886749744415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41044116020203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42306005954742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43323624134064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45847368240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43852806091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43771398067474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44911134243011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44951868057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45725250244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45765972137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45521724224091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43120110034943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4430056810379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44422674179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42713057994843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41858243942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40352141857147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41288363933563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41695427894592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41898965835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41329061985016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43527162075043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3795051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38072645664215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39945089817047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41736125946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40392851829529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40148615837097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34734797477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3591525554657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38316881656647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.395787358284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4511467218399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47719812393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47801220417023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47394168376923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47068536281586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47923338413239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46824300289154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4796404838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49348032474518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50691294670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52360224723816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53866326808929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54069852828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55006098747253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58262515068054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58669567108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56593596935272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5838463306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55494546890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53215050697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52726590633392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52889394760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52197408676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.514240026474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51912486553192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50650596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49755084514618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52238118648529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49307322502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51464712619781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51627540588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48615336418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48940980434418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49063086509705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42794466018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45155382156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46173024177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46213710308075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4837110042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47882616519928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48411810398102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45643842220306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45562434196472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43812096118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44544792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44015622138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45684540271759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48737454414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48533928394318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5040637254715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46417236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44504082202911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47475576400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49673664569855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50894832611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.502028465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48696744441986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50365662574768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52970790863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53662800788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57407701015472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55698072910309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55779480934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50732028484344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48004746437073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49022388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49225914478302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.510169506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47760534286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5004004240036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50121438503265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51301884651184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51953172683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51546132564545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3921240568161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40596377849579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39538025856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40637063980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45196080207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4307941198349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45806658267975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45440316200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45399606227875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42835164070129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39130973815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37258529663086</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.32699525356293</t>
   </si>
   <si>
     <t xml:space="preserve">1.34531271457672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34775507450104</t>
+    <t xml:space="preserve">1.34775519371033</t>
   </si>
   <si>
     <t xml:space="preserve">1.36810779571533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37177109718323</t>
+    <t xml:space="preserve">1.37177121639252</t>
   </si>
   <si>
     <t xml:space="preserve">1.39741563796997</t>
@@ -3533,31 +3533,31 @@
     <t xml:space="preserve">1.4002650976181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40677785873413</t>
+    <t xml:space="preserve">1.40677797794342</t>
   </si>
   <si>
     <t xml:space="preserve">1.35548901557922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35955953598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35833847522736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37462055683136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36770057678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35589611530304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35263967514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33310115337372</t>
+    <t xml:space="preserve">1.35955965518951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35833835601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37462067604065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36770069599152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35589623451233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35263979434967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33310127258301</t>
   </si>
   <si>
     <t xml:space="preserve">1.32414591312408</t>
@@ -3569,16 +3569,16 @@
     <t xml:space="preserve">1.34164929389954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30664265155792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3326940536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36525857448578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41532599925995</t>
+    <t xml:space="preserve">1.30664277076721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33269417285919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36525845527649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41532611846924</t>
   </si>
   <si>
     <t xml:space="preserve">1.37380647659302</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">1.37909817695618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37624883651733</t>
+    <t xml:space="preserve">1.37624871730804</t>
   </si>
   <si>
     <t xml:space="preserve">1.36973595619202</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">1.28262650966644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30094397068024</t>
+    <t xml:space="preserve">1.30094385147095</t>
   </si>
   <si>
     <t xml:space="preserve">1.30542147159576</t>
@@ -3632,10 +3632,10 @@
     <t xml:space="preserve">1.25413274765015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22889530658722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25046920776367</t>
+    <t xml:space="preserve">1.22889542579651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25046932697296</t>
   </si>
   <si>
     <t xml:space="preserve">1.22482478618622</t>
@@ -3644,13 +3644,13 @@
     <t xml:space="preserve">1.28140532970428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3001297712326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25494682788849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2284882068634</t>
+    <t xml:space="preserve">1.30012989044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2549467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22848808765411</t>
   </si>
   <si>
     <t xml:space="preserve">1.19918048381805</t>
@@ -3680,58 +3680,58 @@
     <t xml:space="preserve">1.22116136550903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21464860439301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23785054683685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25087630748749</t>
+    <t xml:space="preserve">1.21464848518372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23785042762756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2508761882782</t>
   </si>
   <si>
     <t xml:space="preserve">1.22563886642456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22808122634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23540830612183</t>
+    <t xml:space="preserve">1.22808110713959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23540818691254</t>
   </si>
   <si>
     <t xml:space="preserve">1.25698220729828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27489244937897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25779616832733</t>
+    <t xml:space="preserve">1.27489233016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25779604911804</t>
   </si>
   <si>
     <t xml:space="preserve">1.26553022861481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25942432880402</t>
+    <t xml:space="preserve">1.25942444801331</t>
   </si>
   <si>
     <t xml:space="preserve">1.28751111030579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29768753051758</t>
+    <t xml:space="preserve">1.29768741130829</t>
   </si>
   <si>
     <t xml:space="preserve">1.2980945110321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33554351329803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36281597614288</t>
+    <t xml:space="preserve">1.33554339408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36281609535217</t>
   </si>
   <si>
     <t xml:space="preserve">1.35223269462585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35711741447449</t>
+    <t xml:space="preserve">1.3571172952652</t>
   </si>
   <si>
     <t xml:space="preserve">1.34856915473938</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">1.36485135555267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33961391448975</t>
+    <t xml:space="preserve">1.33961403369904</t>
   </si>
   <si>
     <t xml:space="preserve">1.32129657268524</t>
@@ -3770,37 +3770,37 @@
     <t xml:space="preserve">1.3164119720459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35019743442535</t>
+    <t xml:space="preserve">1.35019731521606</t>
   </si>
   <si>
     <t xml:space="preserve">1.34653389453888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34327745437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38561105728149</t>
+    <t xml:space="preserve">1.34327733516693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38561117649078</t>
   </si>
   <si>
     <t xml:space="preserve">1.33147299289703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36037373542786</t>
+    <t xml:space="preserve">1.36037361621857</t>
   </si>
   <si>
     <t xml:space="preserve">1.34205627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40272545814514</t>
+    <t xml:space="preserve">1.40272557735443</t>
   </si>
   <si>
     <t xml:space="preserve">1.36872255802155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.378622174263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38507831096649</t>
+    <t xml:space="preserve">1.37862205505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38507843017578</t>
   </si>
   <si>
     <t xml:space="preserve">1.3631272315979</t>
@@ -3809,10 +3809,10 @@
     <t xml:space="preserve">1.35796213150024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34504961967468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32998514175415</t>
+    <t xml:space="preserve">1.34504973888397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32998502254486</t>
   </si>
   <si>
     <t xml:space="preserve">1.31578135490417</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">1.30416011810303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33041560649872</t>
+    <t xml:space="preserve">1.33041548728943</t>
   </si>
   <si>
     <t xml:space="preserve">1.31018602848053</t>
@@ -3833,13 +3833,13 @@
     <t xml:space="preserve">1.270587682724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.187087059021</t>
+    <t xml:space="preserve">1.18708693981171</t>
   </si>
   <si>
     <t xml:space="preserve">1.14921045303345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11047303676605</t>
+    <t xml:space="preserve">1.11047291755676</t>
   </si>
   <si>
     <t xml:space="preserve">1.15050172805786</t>
@@ -3854,31 +3854,31 @@
     <t xml:space="preserve">1.091104388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06570982933044</t>
+    <t xml:space="preserve">1.06570971012115</t>
   </si>
   <si>
     <t xml:space="preserve">1.03945434093475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05581021308899</t>
+    <t xml:space="preserve">1.05581033229828</t>
   </si>
   <si>
     <t xml:space="preserve">1.10143435001373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08593940734863</t>
+    <t xml:space="preserve">1.08593928813934</t>
   </si>
   <si>
     <t xml:space="preserve">1.09540855884552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07517886161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04332804679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06743133068085</t>
+    <t xml:space="preserve">1.07517898082733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.043328166008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06743144989014</t>
   </si>
   <si>
     <t xml:space="preserve">1.06614017486572</t>
@@ -3893,13 +3893,13 @@
     <t xml:space="preserve">1.07130515575409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06915318965912</t>
+    <t xml:space="preserve">1.06915307044983</t>
   </si>
   <si>
     <t xml:space="preserve">1.02697229385376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00200831890106</t>
+    <t xml:space="preserve">1.00200819969177</t>
   </si>
   <si>
     <t xml:space="preserve">1.02352893352509</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">1.03601109981537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04074573516846</t>
+    <t xml:space="preserve">1.04074561595917</t>
   </si>
   <si>
     <t xml:space="preserve">1.05451893806458</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">1.08636963367462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07690060138702</t>
+    <t xml:space="preserve">1.07690072059631</t>
   </si>
   <si>
     <t xml:space="preserve">1.06786179542542</t>
@@ -3959,19 +3959,19 @@
     <t xml:space="preserve">1.11305546760559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10100388526917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10272562503815</t>
+    <t xml:space="preserve">1.10100400447845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10272550582886</t>
   </si>
   <si>
     <t xml:space="preserve">1.08292639255524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06097519397736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06355762481689</t>
+    <t xml:space="preserve">1.06097531318665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06355774402618</t>
   </si>
   <si>
     <t xml:space="preserve">1.05839276313782</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">1.0170726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996843218803406</t>
+    <t xml:space="preserve">0.996843278408051</t>
   </si>
   <si>
     <t xml:space="preserve">0.999425709247589</t>
@@ -3992,31 +3992,31 @@
     <t xml:space="preserve">0.946914970874786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968435883522034</t>
+    <t xml:space="preserve">0.968435704708099</t>
   </si>
   <si>
     <t xml:space="preserve">0.945623755455017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9327113032341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939167439937592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.920229136943817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965422868728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975322425365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952510476112366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92625504732132</t>
+    <t xml:space="preserve">0.932711243629456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939167499542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.920229196548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965422928333282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975322365760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952510416507721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92625492811203</t>
   </si>
   <si>
     <t xml:space="preserve">0.930128753185272</t>
@@ -4025,10 +4025,10 @@
     <t xml:space="preserve">0.913342535495758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.921950876712799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923242151737213</t>
+    <t xml:space="preserve">0.92195075750351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923242092132568</t>
   </si>
   <si>
     <t xml:space="preserve">0.912051260471344</t>
@@ -4037,34 +4037,34 @@
     <t xml:space="preserve">0.882783055305481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888808906078339</t>
+    <t xml:space="preserve">0.888808846473694</t>
   </si>
   <si>
     <t xml:space="preserve">0.852567851543427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86298394203186</t>
+    <t xml:space="preserve">0.862984001636505</t>
   </si>
   <si>
     <t xml:space="preserve">0.85377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860659658908844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879339694976807</t>
+    <t xml:space="preserve">0.860659718513489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879339635372162</t>
   </si>
   <si>
     <t xml:space="preserve">0.903442978858948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868579208850861</t>
+    <t xml:space="preserve">0.868579268455505</t>
   </si>
   <si>
     <t xml:space="preserve">0.853256464004517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.835351169109344</t>
+    <t xml:space="preserve">0.8353511095047</t>
   </si>
   <si>
     <t xml:space="preserve">0.846542000770569</t>
@@ -4079,16 +4079,16 @@
     <t xml:space="preserve">0.825882017612457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863844633102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.883643865585327</t>
+    <t xml:space="preserve">0.863844692707062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883643805980682</t>
   </si>
   <si>
     <t xml:space="preserve">0.879770040512085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871161699295044</t>
+    <t xml:space="preserve">0.871161758899689</t>
   </si>
   <si>
     <t xml:space="preserve">0.896986782550812</t>
@@ -4100,7 +4100,7 @@
     <t xml:space="preserve">0.948206305503845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982209146022797</t>
+    <t xml:space="preserve">0.982209086418152</t>
   </si>
   <si>
     <t xml:space="preserve">0.971018254756927</t>
@@ -4109,13 +4109,13 @@
     <t xml:space="preserve">0.965853273868561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966714084148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966283738613129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955092906951904</t>
+    <t xml:space="preserve">0.966714143753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966283679008484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955092966556549</t>
   </si>
   <si>
     <t xml:space="preserve">0.972309589385986</t>
@@ -4130,7 +4130,7 @@
     <t xml:space="preserve">1.01061654090881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11176419258118</t>
+    <t xml:space="preserve">1.11176431179047</t>
   </si>
   <si>
     <t xml:space="preserve">1.1160683631897</t>
@@ -4142,13 +4142,13 @@
     <t xml:space="preserve">1.10616886615753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12682890892029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1220942735672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11822056770325</t>
+    <t xml:space="preserve">1.126828789711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12209439277649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11822044849396</t>
   </si>
   <si>
     <t xml:space="preserve">1.09669971466064</t>
@@ -4163,16 +4163,16 @@
     <t xml:space="preserve">1.11865091323853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09928214550018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11090350151062</t>
+    <t xml:space="preserve">1.09928226470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11090338230133</t>
   </si>
   <si>
     <t xml:space="preserve">1.12898087501526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13586747646332</t>
+    <t xml:space="preserve">1.13586759567261</t>
   </si>
   <si>
     <t xml:space="preserve">1.13027215003967</t>
@@ -4181,13 +4181,13 @@
     <t xml:space="preserve">1.13543713092804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12381589412689</t>
+    <t xml:space="preserve">1.12381601333618</t>
   </si>
   <si>
     <t xml:space="preserve">1.11951184272766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12166392803192</t>
+    <t xml:space="preserve">1.12166368961334</t>
   </si>
   <si>
     <t xml:space="preserve">1.12984180450439</t>
@@ -4196,10 +4196,10 @@
     <t xml:space="preserve">1.14490628242493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11692917346954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0928258895874</t>
+    <t xml:space="preserve">1.11692941188812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09282600879669</t>
   </si>
   <si>
     <t xml:space="preserve">1.07603967189789</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">1.06958341598511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07173550128937</t>
+    <t xml:space="preserve">1.07173562049866</t>
   </si>
   <si>
     <t xml:space="preserve">1.09971261024475</t>
@@ -4223,19 +4223,19 @@
     <t xml:space="preserve">1.12553763389587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13888049125671</t>
+    <t xml:space="preserve">1.13888037204742</t>
   </si>
   <si>
     <t xml:space="preserve">1.14705836772919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18837821483612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19354331493378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19827783107758</t>
+    <t xml:space="preserve">1.18837833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19354343414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19827771186829</t>
   </si>
   <si>
     <t xml:space="preserve">1.20043003559113</t>
@@ -4247,16 +4247,16 @@
     <t xml:space="preserve">1.21032953262329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17245292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15093219280243</t>
+    <t xml:space="preserve">1.17245304584503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15093207359314</t>
   </si>
   <si>
     <t xml:space="preserve">1.18192207813263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19096088409424</t>
+    <t xml:space="preserve">1.19096076488495</t>
   </si>
   <si>
     <t xml:space="preserve">1.20387327671051</t>
@@ -4265,25 +4265,25 @@
     <t xml:space="preserve">1.20430374145508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21119034290314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19483458995819</t>
+    <t xml:space="preserve">1.21119022369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1948344707489</t>
   </si>
   <si>
     <t xml:space="preserve">1.18665671348572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20989906787872</t>
+    <t xml:space="preserve">1.20989918708801</t>
   </si>
   <si>
     <t xml:space="preserve">1.18794786930084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20344293117523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21506416797638</t>
+    <t xml:space="preserve">1.20344281196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21506404876709</t>
   </si>
   <si>
     <t xml:space="preserve">1.20903825759888</t>
@@ -4295,7 +4295,7 @@
     <t xml:space="preserve">1.17675697803497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19139122962952</t>
+    <t xml:space="preserve">1.19139111042023</t>
   </si>
   <si>
     <t xml:space="preserve">1.18235242366791</t>
@@ -4304,22 +4304,22 @@
     <t xml:space="preserve">1.19225203990936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17976999282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18579578399658</t>
+    <t xml:space="preserve">1.17976987361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18579590320587</t>
   </si>
   <si>
     <t xml:space="preserve">1.18966948986053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20215153694153</t>
+    <t xml:space="preserve">1.20215165615082</t>
   </si>
   <si>
     <t xml:space="preserve">1.20129072666168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16943991184235</t>
+    <t xml:space="preserve">1.16944003105164</t>
   </si>
   <si>
     <t xml:space="preserve">1.18364369869232</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">1.15738832950592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18278288841248</t>
+    <t xml:space="preserve">1.18278300762177</t>
   </si>
   <si>
     <t xml:space="preserve">1.18321335315704</t>
@@ -4352,16 +4352,16 @@
     <t xml:space="preserve">1.25078856945038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26240980625153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23658490180969</t>
+    <t xml:space="preserve">1.26240992546082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2365847826004</t>
   </si>
   <si>
     <t xml:space="preserve">1.25294065475464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23959791660309</t>
+    <t xml:space="preserve">1.2395977973938</t>
   </si>
   <si>
     <t xml:space="preserve">1.23787605762482</t>
@@ -4385,16 +4385,16 @@
     <t xml:space="preserve">1.26714432239532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29426062107086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32869374752045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33256757259369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33730232715607</t>
+    <t xml:space="preserve">1.29426074028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32869386672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33256769180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33730220794678</t>
   </si>
   <si>
     <t xml:space="preserve">1.31664216518402</t>
@@ -4406,19 +4406,19 @@
     <t xml:space="preserve">1.31922471523285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35150599479675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33988463878632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35279703140259</t>
+    <t xml:space="preserve">1.35150587558746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33988475799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35279715061188</t>
   </si>
   <si>
     <t xml:space="preserve">1.35968375205994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35236668586731</t>
+    <t xml:space="preserve">1.3523668050766</t>
   </si>
   <si>
     <t xml:space="preserve">1.36614012718201</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">1.37733089923859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34332799911499</t>
+    <t xml:space="preserve">1.34332811832428</t>
   </si>
   <si>
     <t xml:space="preserve">1.3678617477417</t>
@@ -4445,10 +4445,10 @@
     <t xml:space="preserve">1.39885175228119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41262495517731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4311329126358</t>
+    <t xml:space="preserve">1.4126250743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43113279342651</t>
   </si>
   <si>
     <t xml:space="preserve">1.45609700679779</t>
@@ -4457,10 +4457,10 @@
     <t xml:space="preserve">1.46728777885437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44877994060516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43758904933929</t>
+    <t xml:space="preserve">1.44877982139587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43758916854858</t>
   </si>
   <si>
     <t xml:space="preserve">1.37905251979828</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">1.42495942115784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42905938625336</t>
+    <t xml:space="preserve">1.42905950546265</t>
   </si>
   <si>
     <t xml:space="preserve">1.39261531829834</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">1.39079320430756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38532662391663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40719294548035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41038179397583</t>
+    <t xml:space="preserve">1.38532650470734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40719306468964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41038191318512</t>
   </si>
   <si>
     <t xml:space="preserve">1.4313371181488</t>
@@ -4499,7 +4499,7 @@
     <t xml:space="preserve">1.45684790611267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45639228820801</t>
+    <t xml:space="preserve">1.4563924074173</t>
   </si>
   <si>
     <t xml:space="preserve">1.48235869407654</t>
@@ -4523,19 +4523,19 @@
     <t xml:space="preserve">1.50103628635406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50786948204041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51743602752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50012516975403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50376963615417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47689211368561</t>
+    <t xml:space="preserve">1.50786936283112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51743614673615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50012505054474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50376951694489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4768922328949</t>
   </si>
   <si>
     <t xml:space="preserve">1.49784743785858</t>
@@ -4544,13 +4544,13 @@
     <t xml:space="preserve">1.49420297145844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50695848464966</t>
+    <t xml:space="preserve">1.50695836544037</t>
   </si>
   <si>
     <t xml:space="preserve">1.51652491092682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5256359577179</t>
+    <t xml:space="preserve">1.52563583850861</t>
   </si>
   <si>
     <t xml:space="preserve">1.5242692232132</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">1.54112458229065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53975796699524</t>
+    <t xml:space="preserve">1.53975808620453</t>
   </si>
   <si>
     <t xml:space="preserve">1.52153599262238</t>
@@ -4586,7 +4586,7 @@
     <t xml:space="preserve">1.53064692020416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53383576869965</t>
+    <t xml:space="preserve">1.53383588790894</t>
   </si>
   <si>
     <t xml:space="preserve">1.53520238399506</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">1.54750227928162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55433547496796</t>
+    <t xml:space="preserve">1.55433559417725</t>
   </si>
   <si>
     <t xml:space="preserve">1.56435763835907</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">1.55160212516785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58121299743652</t>
+    <t xml:space="preserve">1.58121287822723</t>
   </si>
   <si>
     <t xml:space="preserve">1.57939076423645</t>
@@ -4616,10 +4616,10 @@
     <t xml:space="preserve">1.54249119758606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51470279693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51105833053589</t>
+    <t xml:space="preserve">1.51470267772675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5110582113266</t>
   </si>
   <si>
     <t xml:space="preserve">1.49921405315399</t>
@@ -4634,13 +4634,13 @@
     <t xml:space="preserve">1.54886901378632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56709086894989</t>
+    <t xml:space="preserve">1.56709098815918</t>
   </si>
   <si>
     <t xml:space="preserve">1.52335822582245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52836918830872</t>
+    <t xml:space="preserve">1.52836930751801</t>
   </si>
   <si>
     <t xml:space="preserve">1.54613566398621</t>
@@ -4652,37 +4652,37 @@
     <t xml:space="preserve">1.57210195064545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58349084854126</t>
+    <t xml:space="preserve">1.58349072933197</t>
   </si>
   <si>
     <t xml:space="preserve">1.58622407913208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60581266880035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5948793888092</t>
+    <t xml:space="preserve">1.60581278800964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59487950801849</t>
   </si>
   <si>
     <t xml:space="preserve">1.61219036579132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59214615821838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57984626293182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56481325626373</t>
+    <t xml:space="preserve">1.59214603900909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57984638214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56481313705444</t>
   </si>
   <si>
     <t xml:space="preserve">1.59123516082764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60034596920013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61310136318207</t>
+    <t xml:space="preserve">1.60034608840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61310148239136</t>
   </si>
   <si>
     <t xml:space="preserve">1.63041234016418</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">1.70056700706482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63451242446899</t>
+    <t xml:space="preserve">1.6345123052597</t>
   </si>
   <si>
     <t xml:space="preserve">1.5994348526001</t>
@@ -4724,25 +4724,25 @@
     <t xml:space="preserve">1.51060271263123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53611350059509</t>
+    <t xml:space="preserve">1.53611361980438</t>
   </si>
   <si>
     <t xml:space="preserve">1.48828089237213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50285840034485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52108037471771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55889105796814</t>
+    <t xml:space="preserve">1.50285851955414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.521080493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55889093875885</t>
   </si>
   <si>
     <t xml:space="preserve">1.56800198554993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58440184593201</t>
+    <t xml:space="preserve">1.58440172672272</t>
   </si>
   <si>
     <t xml:space="preserve">1.57893526554108</t>
@@ -4757,10 +4757,10 @@
     <t xml:space="preserve">1.54659116268158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57756865024567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57620191574097</t>
+    <t xml:space="preserve">1.57756853103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57620203495026</t>
   </si>
   <si>
     <t xml:space="preserve">1.59761273860931</t>
@@ -4769,37 +4769,37 @@
     <t xml:space="preserve">1.60125720500946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61355698108673</t>
+    <t xml:space="preserve">1.61355710029602</t>
   </si>
   <si>
     <t xml:space="preserve">1.63724565505981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63314568996429</t>
+    <t xml:space="preserve">1.633145570755</t>
   </si>
   <si>
     <t xml:space="preserve">1.63223457336426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62767910957336</t>
+    <t xml:space="preserve">1.62767899036407</t>
   </si>
   <si>
     <t xml:space="preserve">1.6167459487915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61765706539154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63177895545959</t>
+    <t xml:space="preserve">1.61765694618225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63177907466888</t>
   </si>
   <si>
     <t xml:space="preserve">1.69601154327393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71742236614227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76115500926971</t>
+    <t xml:space="preserve">1.71742224693298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.761155128479</t>
   </si>
   <si>
     <t xml:space="preserve">1.7597883939743</t>
@@ -4829,7 +4829,7 @@
     <t xml:space="preserve">1.79031038284302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79759907722473</t>
+    <t xml:space="preserve">1.79759919643402</t>
   </si>
   <si>
     <t xml:space="preserve">1.79167699813843</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">1.77709937095642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78256595134735</t>
+    <t xml:space="preserve">1.78256607055664</t>
   </si>
   <si>
     <t xml:space="preserve">1.77846598625183</t>
@@ -4847,16 +4847,16 @@
     <t xml:space="preserve">1.78211033344269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78712153434753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77618825435638</t>
+    <t xml:space="preserve">1.78712141513824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77618813514709</t>
   </si>
   <si>
     <t xml:space="preserve">1.74384427070618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77208828926086</t>
+    <t xml:space="preserve">1.77208840847015</t>
   </si>
   <si>
     <t xml:space="preserve">1.79805469512939</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">1.74019980430603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71377801895142</t>
+    <t xml:space="preserve">1.71377789974213</t>
   </si>
   <si>
     <t xml:space="preserve">1.6964670419693</t>
@@ -4889,10 +4889,10 @@
     <t xml:space="preserve">1.68280053138733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67778944969177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71651113033295</t>
+    <t xml:space="preserve">1.67778956890106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71651124954224</t>
   </si>
   <si>
     <t xml:space="preserve">1.72061121463776</t>
@@ -4901,10 +4901,10 @@
     <t xml:space="preserve">1.73792207241058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74247753620148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74703311920166</t>
+    <t xml:space="preserve">1.74247765541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74703299999237</t>
   </si>
   <si>
     <t xml:space="preserve">1.69692254066467</t>
@@ -4925,10 +4925,10 @@
     <t xml:space="preserve">1.64453434944153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66184532642365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64225673675537</t>
+    <t xml:space="preserve">1.66184520721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64225661754608</t>
   </si>
   <si>
     <t xml:space="preserve">1.59897947311401</t>
@@ -4937,7 +4937,7 @@
     <t xml:space="preserve">1.62995684146881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6285902261734</t>
+    <t xml:space="preserve">1.62859010696411</t>
   </si>
   <si>
     <t xml:space="preserve">1.66321194171906</t>
@@ -4946,10 +4946,10 @@
     <t xml:space="preserve">1.67687833309174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60307943820953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56936860084534</t>
+    <t xml:space="preserve">1.60307931900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56936872005463</t>
   </si>
   <si>
     <t xml:space="preserve">1.55296885967255</t>
@@ -4958,13 +4958,13 @@
     <t xml:space="preserve">1.5124249458313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51014721393585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49238085746765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48964738845825</t>
+    <t xml:space="preserve">1.51014733314514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49238073825836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48964750766754</t>
   </si>
   <si>
     <t xml:space="preserve">1.51698040962219</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">1.55023562908173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55114674568176</t>
+    <t xml:space="preserve">1.55114662647247</t>
   </si>
   <si>
     <t xml:space="preserve">1.54066896438599</t>
@@ -4988,7 +4988,7 @@
     <t xml:space="preserve">1.53839135169983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52518033981323</t>
+    <t xml:space="preserve">1.52518045902252</t>
   </si>
   <si>
     <t xml:space="preserve">1.51288056373596</t>
@@ -5003,13 +5003,13 @@
     <t xml:space="preserve">1.58212411403656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59533512592316</t>
+    <t xml:space="preserve">1.59533500671387</t>
   </si>
   <si>
     <t xml:space="preserve">1.53748023509979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49602520465851</t>
+    <t xml:space="preserve">1.49602508544922</t>
   </si>
   <si>
     <t xml:space="preserve">1.50468063354492</t>
@@ -5018,13 +5018,13 @@
     <t xml:space="preserve">1.50149178504944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49556958675385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47279226779938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49283635616302</t>
+    <t xml:space="preserve">1.49556970596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47279214859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49283623695374</t>
   </si>
   <si>
     <t xml:space="preserve">1.52472484111786</t>
@@ -5036,7 +5036,7 @@
     <t xml:space="preserve">1.50422501564026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47370326519012</t>
+    <t xml:space="preserve">1.47370314598083</t>
   </si>
   <si>
     <t xml:space="preserve">1.50331389904022</t>
@@ -5045,7 +5045,7 @@
     <t xml:space="preserve">1.5051361322403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48418080806732</t>
+    <t xml:space="preserve">1.48418092727661</t>
   </si>
   <si>
     <t xml:space="preserve">1.49966955184937</t>
@@ -5054,7 +5054,7 @@
     <t xml:space="preserve">1.57574641704559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5962461233139</t>
+    <t xml:space="preserve">1.59624600410461</t>
   </si>
   <si>
     <t xml:space="preserve">1.65592312812805</t>
@@ -5069,19 +5069,19 @@
     <t xml:space="preserve">1.70694470405579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69054484367371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71423351764679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69464480876923</t>
+    <t xml:space="preserve">1.690544962883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7142333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69464492797852</t>
   </si>
   <si>
     <t xml:space="preserve">1.71241128444672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72379994392395</t>
+    <t xml:space="preserve">1.72380006313324</t>
   </si>
   <si>
     <t xml:space="preserve">1.74156641960144</t>
@@ -5090,7 +5090,7 @@
     <t xml:space="preserve">1.74794411659241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75341069698334</t>
+    <t xml:space="preserve">1.75341081619263</t>
   </si>
   <si>
     <t xml:space="preserve">1.7921324968338</t>
@@ -5105,7 +5105,7 @@
     <t xml:space="preserve">1.84497630596161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83586537837982</t>
+    <t xml:space="preserve">1.83586525917053</t>
   </si>
   <si>
     <t xml:space="preserve">1.84284818172455</t>
@@ -5952,6 +5952,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.43700003623962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45300006866455</t>
   </si>
 </sst>
 </file>
@@ -71160,7 +71163,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6493055556</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>16117302</v>
@@ -71181,6 +71184,32 @@
         <v>1979</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6497685185</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>9135328</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>2.45300006866455</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>2.40799999237061</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>2.45300006866455</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1980</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="1981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="1982">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,22 +44,22 @@
     <t xml:space="preserve">A2A.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774303793907166</t>
+    <t xml:space="preserve">0.774303913116455</t>
   </si>
   <si>
     <t xml:space="preserve">0.76930034160614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.777431309223175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772427558898926</t>
+    <t xml:space="preserve">0.777431190013885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772427618503571</t>
   </si>
   <si>
     <t xml:space="preserve">0.775554835796356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.736151695251465</t>
+    <t xml:space="preserve">0.736151576042175</t>
   </si>
   <si>
     <t xml:space="preserve">0.728020846843719</t>
@@ -71,10 +71,10 @@
     <t xml:space="preserve">0.701126575469971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.678610503673553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.686115801334381</t>
+    <t xml:space="preserve">0.678610563278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.686115860939026</t>
   </si>
   <si>
     <t xml:space="preserve">0.662974238395691</t>
@@ -86,40 +86,40 @@
     <t xml:space="preserve">0.673606872558594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.661723434925079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689868569374084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.667352437973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.688617646694183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689243078231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.676108717918396</t>
+    <t xml:space="preserve">0.661723375320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689868628978729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.667352378368378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.688617587089539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689243018627167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.676108658313751</t>
   </si>
   <si>
     <t xml:space="preserve">0.671105146408081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666727006435394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643585443496704</t>
+    <t xml:space="preserve">0.66672694683075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643585503101349</t>
   </si>
   <si>
     <t xml:space="preserve">0.612313032150269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597927689552307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605745851993561</t>
+    <t xml:space="preserve">0.597927749156952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605745911598206</t>
   </si>
   <si>
     <t xml:space="preserve">0.610749423503876</t>
@@ -128,19 +128,19 @@
     <t xml:space="preserve">0.614189386367798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627323865890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617942035198212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624822020530701</t>
+    <t xml:space="preserve">0.627323806285858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617942094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624821901321411</t>
   </si>
   <si>
     <t xml:space="preserve">0.64671266078949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636080086231232</t>
+    <t xml:space="preserve">0.636080026626587</t>
   </si>
   <si>
     <t xml:space="preserve">0.656719863414764</t>
@@ -152,67 +152,67 @@
     <t xml:space="preserve">0.641083657741547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647963464260101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.657345235347748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661097943782806</t>
+    <t xml:space="preserve">0.647963583469391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.657345294952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661098003387451</t>
   </si>
   <si>
     <t xml:space="preserve">0.672981441020966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666101574897766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.664850533008575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658596217632294</t>
+    <t xml:space="preserve">0.666101515293121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.664850652217865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658596158027649</t>
   </si>
   <si>
     <t xml:space="preserve">0.651716291904449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654843509197235</t>
+    <t xml:space="preserve">0.65484344959259</t>
   </si>
   <si>
     <t xml:space="preserve">0.669228851795197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.71301007270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69299578666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.691119372844696</t>
+    <t xml:space="preserve">0.713010013103485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692995727062225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.691119492053986</t>
   </si>
   <si>
     <t xml:space="preserve">0.694246709346771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.697999358177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696122944355011</t>
+    <t xml:space="preserve">0.69799929857254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696123063564301</t>
   </si>
   <si>
     <t xml:space="preserve">0.7030029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.692370355129242</t>
+    <t xml:space="preserve">0.692370414733887</t>
   </si>
   <si>
     <t xml:space="preserve">0.699250280857086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714260935783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714886367321014</t>
+    <t xml:space="preserve">0.714260995388031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714886486530304</t>
   </si>
   <si>
     <t xml:space="preserve">0.702377498149872</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">0.705504715442657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.735526263713837</t>
+    <t xml:space="preserve">0.735526204109192</t>
   </si>
   <si>
     <t xml:space="preserve">0.740529775619507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.744282424449921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748660564422607</t>
+    <t xml:space="preserve">0.74428254365921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748660683631897</t>
   </si>
   <si>
     <t xml:space="preserve">0.738028049468994</t>
@@ -239,52 +239,52 @@
     <t xml:space="preserve">0.750536918640137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.754289567470551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768049538135529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757416844367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766798496246338</t>
+    <t xml:space="preserve">0.754289627075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768049418926239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757416725158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766798615455627</t>
   </si>
   <si>
     <t xml:space="preserve">0.752413272857666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781183838844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778056621551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786187469959259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779307544231415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768674910068512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755540549755096</t>
+    <t xml:space="preserve">0.781183898448944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778056681156158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786187410354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77930748462677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768674850463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755540609359741</t>
   </si>
   <si>
     <t xml:space="preserve">0.760544121265411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.764296650886536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770551323890686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75929319858551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769925832748413</t>
+    <t xml:space="preserve">0.76429682970047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770551383495331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7592933177948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769925773143768</t>
   </si>
   <si>
     <t xml:space="preserve">0.761169493198395</t>
@@ -302,61 +302,61 @@
     <t xml:space="preserve">0.754915177822113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781809270381927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801198184490204</t>
+    <t xml:space="preserve">0.781809210777283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801198124885559</t>
   </si>
   <si>
     <t xml:space="preserve">0.804950892925262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79932177066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785562098026276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796820104122162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791816353797913</t>
+    <t xml:space="preserve">0.799321830272675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785562038421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796820044517517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791816473007202</t>
   </si>
   <si>
     <t xml:space="preserve">0.801823616027832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.733649790287018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725519061088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766306400299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759828686714172</t>
+    <t xml:space="preserve">0.733649909496307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725519001483917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766306519508362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759828746318817</t>
   </si>
   <si>
     <t xml:space="preserve">0.750760078430176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778613924980164</t>
+    <t xml:space="preserve">0.778613984584808</t>
   </si>
   <si>
     <t xml:space="preserve">0.703473210334778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.692461133003235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705416560173035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.730031549930573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763067662715912</t>
+    <t xml:space="preserve">0.69246119260788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705416440963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.730031609535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763067722320557</t>
   </si>
   <si>
     <t xml:space="preserve">0.762419879436493</t>
@@ -365,73 +365,73 @@
     <t xml:space="preserve">0.769545316696167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.75788539648056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742986857891083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742339253425598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.758533358573914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777318477630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77407968044281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776022911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78379613161087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779909551143646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79027384519577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789626061916351</t>
+    <t xml:space="preserve">0.757885456085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742986977100372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742339193820953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758533298969269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77731865644455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774079740047455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776022970676422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783796191215515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779909491539001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790273904800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789626002311707</t>
   </si>
   <si>
     <t xml:space="preserve">0.794160306453705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805172502994537</t>
+    <t xml:space="preserve">0.805172443389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.807763457298279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.822661936283112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817479908466339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820718705654144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.822014391422272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809706628322601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814241170883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816184401512146</t>
+    <t xml:space="preserve">0.822662115097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817479848861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8207186460495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.822014331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809706747531891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814241111278534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816184341907501</t>
   </si>
   <si>
     <t xml:space="preserve">0.804524660110474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801285684108734</t>
+    <t xml:space="preserve">0.801285862922668</t>
   </si>
   <si>
     <t xml:space="preserve">0.812945604324341</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">0.801933467388153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786387145519257</t>
+    <t xml:space="preserve">0.786387205123901</t>
   </si>
   <si>
     <t xml:space="preserve">0.788330495357513</t>
@@ -449,16 +449,16 @@
     <t xml:space="preserve">0.771488606929779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783148229122162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782500684261322</t>
+    <t xml:space="preserve">0.783148288726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782500624656677</t>
   </si>
   <si>
     <t xml:space="preserve">0.781852900981903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.770193040370941</t>
+    <t xml:space="preserve">0.770192980766296</t>
   </si>
   <si>
     <t xml:space="preserve">0.785091698169708</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.795455992221832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.811002254486084</t>
+    <t xml:space="preserve">0.811002314090729</t>
   </si>
   <si>
     <t xml:space="preserve">0.794808149337769</t>
@@ -476,76 +476,76 @@
     <t xml:space="preserve">0.796103656291962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.798694789409637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802581369876862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790921568870544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796751439571381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799342453479767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810354471206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780557334423065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784443855285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785739481449127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827196419239044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81359338760376</t>
+    <t xml:space="preserve">0.798694610595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802581191062927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79092139005661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796751499176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799342513084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810354590415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78055739402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784443795681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785739421844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827196359634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813593327999115</t>
   </si>
   <si>
     <t xml:space="preserve">0.800638020038605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.7973992228508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803876757621765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807115793228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.761124312877655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77084082365036</t>
+    <t xml:space="preserve">0.797399163246155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803876876831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80711567401886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7611243724823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77084094285965</t>
   </si>
   <si>
     <t xml:space="preserve">0.731327056884766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.735861480236053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.720315158367157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72161066532135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.719019651412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696347773075104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696995556354523</t>
+    <t xml:space="preserve">0.735861420631409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.720315039157867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721610605716705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.719019591808319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696347832679749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696995496749878</t>
   </si>
   <si>
     <t xml:space="preserve">0.709950864315033</t>
@@ -560,172 +560,172 @@
     <t xml:space="preserve">0.707359790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.728735983371735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715780794620514</t>
+    <t xml:space="preserve">0.728736042976379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715780854225159</t>
   </si>
   <si>
     <t xml:space="preserve">0.722258508205414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.76501077413559</t>
+    <t xml:space="preserve">0.765010833740234</t>
   </si>
   <si>
     <t xml:space="preserve">0.754646599292755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.755294501781464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787682771682739</t>
+    <t xml:space="preserve">0.755294382572174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787682712078094</t>
   </si>
   <si>
     <t xml:space="preserve">0.776670694351196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.772136390209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78703498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816832304000854</t>
+    <t xml:space="preserve">0.772136330604553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787035048007965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81683224439621</t>
   </si>
   <si>
     <t xml:space="preserve">0.819423258304596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799990236759186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824605345726013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838856041431427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831730842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832378506660461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840151727199554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848572671413422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841447234153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844686031341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830435156822205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798047006130219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815536618232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820070862770081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806467890739441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811650156974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836265027523041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844038367271423</t>
+    <t xml:space="preserve">0.799990296363831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824605464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838856101036072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831730782985687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832378625869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840151846408844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848572492599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841447412967682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844686210155487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830435216426849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798047065734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815536558628082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820070922374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806467831134796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811650097370148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836265087127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844038248062134</t>
   </si>
   <si>
     <t xml:space="preserve">0.837560653686523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.836912930011749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821366608142853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828492045402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825900971889496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829139769077301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84662926197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849220395088196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864766836166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867357790470123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868005692958832</t>
+    <t xml:space="preserve">0.836913049221039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821366429328918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828491926193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825900852680206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829139709472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846629500389099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849220216274261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864766776561737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867357850074768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868005573749542</t>
   </si>
   <si>
     <t xml:space="preserve">0.870596766471863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.857641458511353</t>
+    <t xml:space="preserve">0.857641398906708</t>
   </si>
   <si>
     <t xml:space="preserve">0.865414559841156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866710126399994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853107035160065</t>
+    <t xml:space="preserve">0.866710066795349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853107094764709</t>
   </si>
   <si>
     <t xml:space="preserve">0.855698108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858289241790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860232532024384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872539877891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874483406543732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887438774108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893916189670563</t>
+    <t xml:space="preserve">0.858289122581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860232412815094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872539937496185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874483346939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887438654899597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893916249275208</t>
   </si>
   <si>
     <t xml:space="preserve">0.89262068271637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912701547145844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909462571144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908167064189911</t>
+    <t xml:space="preserve">0.912701606750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909462690353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908167004585266</t>
   </si>
   <si>
     <t xml:space="preserve">0.919826745986938</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">0.875778794288635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877722024917603</t>
+    <t xml:space="preserve">0.877722084522247</t>
   </si>
   <si>
     <t xml:space="preserve">0.891972959041595</t>
@@ -749,67 +749,67 @@
     <t xml:space="preserve">0.895211815834045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.884199738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876426577568054</t>
+    <t xml:space="preserve">0.884199798107147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876426517963409</t>
   </si>
   <si>
     <t xml:space="preserve">0.862175643444061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85634583234787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882256507873535</t>
+    <t xml:space="preserve">0.856345891952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882256388664246</t>
   </si>
   <si>
     <t xml:space="preserve">0.899098336696625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.890677392482758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926952421665192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91529244184494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917235612869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966465950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95804488658905</t>
+    <t xml:space="preserve">0.890677332878113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926952302455902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915292501449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917235851287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966465890407562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958045184612274</t>
   </si>
   <si>
     <t xml:space="preserve">0.965170443058014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961283802986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963227033615112</t>
+    <t xml:space="preserve">0.9612837433815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963227152824402</t>
   </si>
   <si>
     <t xml:space="preserve">0.94185084104538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941203117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958692789077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982278227806091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988308548927307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997019052505493</t>
+    <t xml:space="preserve">0.941203057765961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958692729473114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982278108596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988308489322662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997018992900848</t>
   </si>
   <si>
     <t xml:space="preserve">1.00036919116974</t>
@@ -818,10 +818,10 @@
     <t xml:space="preserve">0.992998778820038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96820741891861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981608092784882</t>
+    <t xml:space="preserve">0.968207538127899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981608211994171</t>
   </si>
   <si>
     <t xml:space="preserve">0.986298382282257</t>
@@ -830,118 +830,118 @@
     <t xml:space="preserve">0.988978505134583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989648520946503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97490793466568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999699115753174</t>
+    <t xml:space="preserve">0.989648580551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97490781545639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999699056148529</t>
   </si>
   <si>
     <t xml:space="preserve">1.0050595998764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998359203338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997688949108124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00170934200287</t>
+    <t xml:space="preserve">0.998359084129333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997689068317413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00170946121216</t>
   </si>
   <si>
     <t xml:space="preserve">1.00706958770752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02047038078308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02985084056854</t>
+    <t xml:space="preserve">1.02047049999237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02985107898712</t>
   </si>
   <si>
     <t xml:space="preserve">1.0177903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995008945465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999029219150543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976917862892151</t>
+    <t xml:space="preserve">0.995009005069733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999029338359833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976917922496796</t>
   </si>
   <si>
     <t xml:space="preserve">0.974237680435181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970217287540436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965527296066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960837006568909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961507022380829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964187264442444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980268120765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978927969932556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984958350658417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972897589206696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960166871547699</t>
+    <t xml:space="preserve">0.970217406749725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965527236461639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960836887359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961506903171539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96418708562851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980268239974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978927910327911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984958291053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972897708415985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960166811943054</t>
   </si>
   <si>
     <t xml:space="preserve">0.958826839923859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.951456308364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955476582050323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949446439743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963517010211945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950116217136383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953466475009918</t>
+    <t xml:space="preserve">0.951456248760223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955476641654968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949446141719818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963517129421234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950116336345673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953466653823853</t>
   </si>
   <si>
     <t xml:space="preserve">0.956816732883453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958156764507294</t>
+    <t xml:space="preserve">0.958156704902649</t>
   </si>
   <si>
     <t xml:space="preserve">0.952796578407288</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962176978588104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944755971431732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931355178356171</t>
+    <t xml:space="preserve">0.962177038192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944755911827087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931355237960815</t>
   </si>
   <si>
     <t xml:space="preserve">0.948106169700623</t>
@@ -950,37 +950,37 @@
     <t xml:space="preserve">0.954136490821838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957486748695374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939395725727081</t>
+    <t xml:space="preserve">0.957486689090729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939395546913147</t>
   </si>
   <si>
     <t xml:space="preserve">0.946766078472137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.934705317020416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9286749958992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924654603004456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932695150375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945426046848297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959496855735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97356766462326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978257954120636</t>
+    <t xml:space="preserve">0.934705436229706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928675174713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92465478181839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932695090770721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945425868034363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959496796131134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973567485809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978257894515991</t>
   </si>
   <si>
     <t xml:space="preserve">0.993668794631958</t>
@@ -989,64 +989,64 @@
     <t xml:space="preserve">0.984288275241852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983618259429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994338929653168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977587938308716</t>
+    <t xml:space="preserve">0.983618199825287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994338810443878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977587878704071</t>
   </si>
   <si>
     <t xml:space="preserve">0.980938017368317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972227692604065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96619713306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969547510147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96887743473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971557557582855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995678961277008</t>
+    <t xml:space="preserve">0.97222763299942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966197192668915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969547390937805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96887731552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9715576171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995679020881653</t>
   </si>
   <si>
     <t xml:space="preserve">0.992328703403473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96686726808548</t>
+    <t xml:space="preserve">0.966867327690125</t>
   </si>
   <si>
     <t xml:space="preserve">1.02114057540894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01041984558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01444017887115</t>
+    <t xml:space="preserve">1.01041996479034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01444005966187</t>
   </si>
   <si>
     <t xml:space="preserve">1.02181041240692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02382063865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0285108089447</t>
+    <t xml:space="preserve">1.02382075786591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02851104736328</t>
   </si>
   <si>
     <t xml:space="preserve">1.03320121765137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03923153877258</t>
+    <t xml:space="preserve">1.03923141956329</t>
   </si>
   <si>
     <t xml:space="preserve">1.0265007019043</t>
@@ -1058,76 +1058,76 @@
     <t xml:space="preserve">1.05866277217865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04459190368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05330240726471</t>
+    <t xml:space="preserve">1.04459202289581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.053302526474</t>
   </si>
   <si>
     <t xml:space="preserve">1.0680433511734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07273352146149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08613443374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09551477432251</t>
+    <t xml:space="preserve">1.0727334022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08613431453705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09551501274109</t>
   </si>
   <si>
     <t xml:space="preserve">1.08345425128937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08211410045624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05397236347198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06000280380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04392194747925</t>
+    <t xml:space="preserve">1.08211421966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0539722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0600026845932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04392182826996</t>
   </si>
   <si>
     <t xml:space="preserve">1.04861223697662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04660189151764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03990161418915</t>
+    <t xml:space="preserve">1.04660201072693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03990173339844</t>
   </si>
   <si>
     <t xml:space="preserve">1.04258179664612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01980030536652</t>
+    <t xml:space="preserve">1.01980042457581</t>
   </si>
   <si>
     <t xml:space="preserve">1.015780210495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05196237564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06737339496613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06603312492371</t>
+    <t xml:space="preserve">1.05196225643158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06737327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06603300571442</t>
   </si>
   <si>
     <t xml:space="preserve">1.02449059486389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01846039295197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02784097194672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05665266513824</t>
+    <t xml:space="preserve">1.01846027374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02784073352814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05665254592896</t>
   </si>
   <si>
     <t xml:space="preserve">1.06134283542633</t>
@@ -1136,70 +1136,70 @@
     <t xml:space="preserve">1.07742381095886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07943391799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06938326358795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05933272838593</t>
+    <t xml:space="preserve">1.07943379878998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06938350200653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05933284759521</t>
   </si>
   <si>
     <t xml:space="preserve">1.03856146335602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02683579921722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03588128089905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04191184043884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996348917484283</t>
+    <t xml:space="preserve">1.02683568000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03588151931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04191172122955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996349096298218</t>
   </si>
   <si>
     <t xml:space="preserve">0.971222579479218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99534398317337</t>
+    <t xml:space="preserve">0.995343923568726</t>
   </si>
   <si>
     <t xml:space="preserve">0.944420993328094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953131377696991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941405773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959831714630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946431219577789</t>
+    <t xml:space="preserve">0.953131556510925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941405713558197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959831893444061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9464311003685</t>
   </si>
   <si>
     <t xml:space="preserve">0.957821786403656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950451374053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936380445957184</t>
+    <t xml:space="preserve">0.950451254844666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936380565166473</t>
   </si>
   <si>
     <t xml:space="preserve">0.967202365398407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991323828697205</t>
+    <t xml:space="preserve">0.99132376909256</t>
   </si>
   <si>
     <t xml:space="preserve">0.975577712059021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993333756923676</t>
+    <t xml:space="preserve">0.993333876132965</t>
   </si>
   <si>
     <t xml:space="preserve">1.00003409385681</t>
@@ -1217,34 +1217,34 @@
     <t xml:space="preserve">0.999364256858826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04023671150208</t>
+    <t xml:space="preserve">1.04023659229279</t>
   </si>
   <si>
     <t xml:space="preserve">1.04157674312592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04224669933319</t>
+    <t xml:space="preserve">1.04224681854248</t>
   </si>
   <si>
     <t xml:space="preserve">1.04961717128754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04995214939117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06268286705017</t>
+    <t xml:space="preserve">1.04995238780975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06268298625946</t>
   </si>
   <si>
     <t xml:space="preserve">1.07206344604492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05832767486572</t>
+    <t xml:space="preserve">1.05832743644714</t>
   </si>
   <si>
     <t xml:space="preserve">1.06335306167603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07407367229462</t>
+    <t xml:space="preserve">1.07407379150391</t>
   </si>
   <si>
     <t xml:space="preserve">1.08043897151947</t>
@@ -1253,31 +1253,31 @@
     <t xml:space="preserve">1.08546423912048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09048974514008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09484481811523</t>
+    <t xml:space="preserve">1.09048962593079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09484469890594</t>
   </si>
   <si>
     <t xml:space="preserve">1.09819507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09853005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12198126316071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11762619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11729109287262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10724055767059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10757565498352</t>
+    <t xml:space="preserve">1.09852993488312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12198150157928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11762607097626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11729121208191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10724067687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10757577419281</t>
   </si>
   <si>
     <t xml:space="preserve">1.12265145778656</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">1.10992074012756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11829614639282</t>
+    <t xml:space="preserve">1.11829626560211</t>
   </si>
   <si>
     <t xml:space="preserve">1.05732250213623</t>
@@ -1298,13 +1298,13 @@
     <t xml:space="preserve">1.03387117385864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03895282745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05287516117096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04208540916443</t>
+    <t xml:space="preserve">1.03895270824432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05287528038025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04208528995514</t>
   </si>
   <si>
     <t xml:space="preserve">1.04730629920959</t>
@@ -1319,22 +1319,22 @@
     <t xml:space="preserve">0.980827271938324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998926162719727</t>
+    <t xml:space="preserve">0.998926341533661</t>
   </si>
   <si>
     <t xml:space="preserve">1.01076006889343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00484323501587</t>
+    <t xml:space="preserve">1.00484311580658</t>
   </si>
   <si>
     <t xml:space="preserve">1.02920722961426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00936806201935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00658357143402</t>
+    <t xml:space="preserve">1.00936794281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00658345222473</t>
   </si>
   <si>
     <t xml:space="preserve">0.999622285366058</t>
@@ -1346,10 +1346,10 @@
     <t xml:space="preserve">1.01598107814789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02398633956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03164374828339</t>
+    <t xml:space="preserve">1.02398645877838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03164386749268</t>
   </si>
   <si>
     <t xml:space="preserve">1.02851116657257</t>
@@ -1358,49 +1358,49 @@
     <t xml:space="preserve">1.01980972290039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04382598400116</t>
+    <t xml:space="preserve">1.04382574558258</t>
   </si>
   <si>
     <t xml:space="preserve">1.04661011695862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0236382484436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02537846565247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00588750839233</t>
+    <t xml:space="preserve">1.02363836765289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02537858486176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00588738918304</t>
   </si>
   <si>
     <t xml:space="preserve">1.01250052452087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02120184898376</t>
+    <t xml:space="preserve">1.02120196819305</t>
   </si>
   <si>
     <t xml:space="preserve">1.02642273902893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03373193740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01389265060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03860485553741</t>
+    <t xml:space="preserve">1.03373181819916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01389276981354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03860473632812</t>
   </si>
   <si>
     <t xml:space="preserve">1.05113482475281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06122863292694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07236647605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06018435955048</t>
+    <t xml:space="preserve">1.06122875213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07236635684967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06018447875977</t>
   </si>
   <si>
     <t xml:space="preserve">1.06262075901031</t>
@@ -1409,22 +1409,22 @@
     <t xml:space="preserve">1.05600762367249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07375872135162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06714558601379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07863140106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09290182590485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09429407119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10160326957703</t>
+    <t xml:space="preserve">1.07375860214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06714570522308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0786315202713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09290194511414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09429395198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10160338878632</t>
   </si>
   <si>
     <t xml:space="preserve">1.08420038223267</t>
@@ -1451,19 +1451,19 @@
     <t xml:space="preserve">1.08106780052185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09011733531952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0824601650238</t>
+    <t xml:space="preserve">1.09011745452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08246004581451</t>
   </si>
   <si>
     <t xml:space="preserve">1.10299563407898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12005043029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12387895584106</t>
+    <t xml:space="preserve">1.12005031108856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12387907505035</t>
   </si>
   <si>
     <t xml:space="preserve">1.10473585128784</t>
@@ -1472,40 +1472,40 @@
     <t xml:space="preserve">1.10612809658051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11134910583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10821628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10960865020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08837723731995</t>
+    <t xml:space="preserve">1.11134886741638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10821640491486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10960876941681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08837711811066</t>
   </si>
   <si>
     <t xml:space="preserve">1.08802902698517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08942115306854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07549893856049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06540536880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03338396549225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04243338108063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02155005931854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03094732761383</t>
+    <t xml:space="preserve">1.08942127227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0754988193512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06540513038635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03338384628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04243326187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02154994010925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03094744682312</t>
   </si>
   <si>
     <t xml:space="preserve">1.04173731803894</t>
@@ -1520,55 +1520,55 @@
     <t xml:space="preserve">1.09220576286316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09116160869598</t>
+    <t xml:space="preserve">1.09116148948669</t>
   </si>
   <si>
     <t xml:space="preserve">1.08454847335815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08141589164734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09847068786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09603428840637</t>
+    <t xml:space="preserve">1.08141601085663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09847056865692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09603440761566</t>
   </si>
   <si>
     <t xml:space="preserve">1.07619512081146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07445466518402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05879211425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07758748531342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06923389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04069304466248</t>
+    <t xml:space="preserve">1.07445478439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0587922334671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07758736610413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06923401355743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04069328308105</t>
   </si>
   <si>
     <t xml:space="preserve">1.03199172019958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04452168941498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04417371749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05183100700378</t>
+    <t xml:space="preserve">1.04452180862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04417383670807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05183112621307</t>
   </si>
   <si>
     <t xml:space="preserve">1.03616833686829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05844390392303</t>
+    <t xml:space="preserve">1.05844414234161</t>
   </si>
   <si>
     <t xml:space="preserve">1.03442811965942</t>
@@ -1577,46 +1577,46 @@
     <t xml:space="preserve">1.00310289859772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99161696434021</t>
+    <t xml:space="preserve">0.991616904735565</t>
   </si>
   <si>
     <t xml:space="preserve">1.00832378864288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01424074172974</t>
+    <t xml:space="preserve">1.01424086093903</t>
   </si>
   <si>
     <t xml:space="preserve">1.01772141456604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01354455947876</t>
+    <t xml:space="preserve">1.01354444026947</t>
   </si>
   <si>
     <t xml:space="preserve">0.993705332279205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988136351108551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97734659910202</t>
+    <t xml:space="preserve">0.988136410713196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97734671831131</t>
   </si>
   <si>
     <t xml:space="preserve">1.00553917884827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986047983169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989528596401215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992313086986542</t>
+    <t xml:space="preserve">0.98604816198349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989528656005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992313206195831</t>
   </si>
   <si>
     <t xml:space="preserve">0.98291540145874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991964995861053</t>
+    <t xml:space="preserve">0.991965055465698</t>
   </si>
   <si>
     <t xml:space="preserve">1.01319646835327</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">1.00414705276489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02050566673279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01563310623169</t>
+    <t xml:space="preserve">1.02050578594208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01563286781311</t>
   </si>
   <si>
     <t xml:space="preserve">1.03512418270111</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">1.0393009185791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05252718925476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05461549758911</t>
+    <t xml:space="preserve">1.05252707004547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0546156167984</t>
   </si>
   <si>
     <t xml:space="preserve">1.03721261024475</t>
@@ -1649,13 +1649,13 @@
     <t xml:space="preserve">1.02711892127991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03999698162079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06610131263733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06088066101074</t>
+    <t xml:space="preserve">1.03999710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06610155105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06088054180145</t>
   </si>
   <si>
     <t xml:space="preserve">1.04034519195557</t>
@@ -1673,43 +1673,43 @@
     <t xml:space="preserve">1.07410669326782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10090708732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11761379241943</t>
+    <t xml:space="preserve">1.10090720653534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11761391162872</t>
   </si>
   <si>
     <t xml:space="preserve">1.12701153755188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11378538608551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10647594928741</t>
+    <t xml:space="preserve">1.11378526687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1064760684967</t>
   </si>
   <si>
     <t xml:space="preserve">1.12318289279938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13118827342987</t>
+    <t xml:space="preserve">1.13118815422058</t>
   </si>
   <si>
     <t xml:space="preserve">1.11448156833649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08872509002686</t>
+    <t xml:space="preserve">1.08872520923615</t>
   </si>
   <si>
     <t xml:space="preserve">1.094642162323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11622178554535</t>
+    <t xml:space="preserve">1.11622166633606</t>
   </si>
   <si>
     <t xml:space="preserve">1.1183100938797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13501667976379</t>
+    <t xml:space="preserve">1.13501679897308</t>
   </si>
   <si>
     <t xml:space="preserve">1.13675713539124</t>
@@ -1721,16 +1721,16 @@
     <t xml:space="preserve">1.14302217960358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10403966903687</t>
+    <t xml:space="preserve">1.10403954982758</t>
   </si>
   <si>
     <t xml:space="preserve">1.10891270637512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09951496124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10195136070251</t>
+    <t xml:space="preserve">1.0995147228241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1019514799118</t>
   </si>
   <si>
     <t xml:space="preserve">1.09916687011719</t>
@@ -1739,52 +1739,52 @@
     <t xml:space="preserve">1.0949901342392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10578000545502</t>
+    <t xml:space="preserve">1.10578012466431</t>
   </si>
   <si>
     <t xml:space="preserve">1.09185779094696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07793533802032</t>
+    <t xml:space="preserve">1.07793545722961</t>
   </si>
   <si>
     <t xml:space="preserve">1.08071982860565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08663690090179</t>
+    <t xml:space="preserve">1.08663666248322</t>
   </si>
   <si>
     <t xml:space="preserve">1.06227278709412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08280837535858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09742665290833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10021102428436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09777462482452</t>
+    <t xml:space="preserve">1.08280813694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09742677211761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10021114349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09777474403381</t>
   </si>
   <si>
     <t xml:space="preserve">1.10369169712067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11100089550018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10543203353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08594059944153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09568619728088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08907318115234</t>
+    <t xml:space="preserve">1.11100077629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10543191432953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08594071865082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09568631649017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08907341957092</t>
   </si>
   <si>
     <t xml:space="preserve">1.11726593971252</t>
@@ -1793,19 +1793,19 @@
     <t xml:space="preserve">1.12074649333954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10752022266388</t>
+    <t xml:space="preserve">1.10752034187317</t>
   </si>
   <si>
     <t xml:space="preserve">1.1103048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12179064750671</t>
+    <t xml:space="preserve">1.121790766716</t>
   </si>
   <si>
     <t xml:space="preserve">1.11935436725616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13571298122406</t>
+    <t xml:space="preserve">1.13571286201477</t>
   </si>
   <si>
     <t xml:space="preserve">1.13536500930786</t>
@@ -1814,19 +1814,19 @@
     <t xml:space="preserve">1.13084018230438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13223242759705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14754700660706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06331694126129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05391943454742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04626202583313</t>
+    <t xml:space="preserve">1.13223254680634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14754688739777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06331706047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05391919612885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04626214504242</t>
   </si>
   <si>
     <t xml:space="preserve">1.05426752567291</t>
@@ -1838,16 +1838,16 @@
     <t xml:space="preserve">1.02433454990387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01946139335632</t>
+    <t xml:space="preserve">1.01946151256561</t>
   </si>
   <si>
     <t xml:space="preserve">1.01632905006409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0037989616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997882068157196</t>
+    <t xml:space="preserve">1.00379920005798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997882127761841</t>
   </si>
   <si>
     <t xml:space="preserve">1.00727963447571</t>
@@ -1865,40 +1865,40 @@
     <t xml:space="preserve">1.09720551967621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09647655487061</t>
+    <t xml:space="preserve">1.0964766740799</t>
   </si>
   <si>
     <t xml:space="preserve">1.06622135639191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08116662502289</t>
+    <t xml:space="preserve">1.08116674423218</t>
   </si>
   <si>
     <t xml:space="preserve">1.07205367088318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06038904190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05127608776093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0640344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07168924808502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08043766021729</t>
+    <t xml:space="preserve">1.06038916110992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05127620697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06403422355652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07168912887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08043777942657</t>
   </si>
   <si>
     <t xml:space="preserve">1.0979346036911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0986635684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10449588298798</t>
+    <t xml:space="preserve">1.09866368770599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10449612140656</t>
   </si>
   <si>
     <t xml:space="preserve">1.10048627853394</t>
@@ -1913,19 +1913,19 @@
     <t xml:space="preserve">1.09829914569855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13219952583313</t>
+    <t xml:space="preserve">1.13219940662384</t>
   </si>
   <si>
     <t xml:space="preserve">1.12563824653625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14021897315979</t>
+    <t xml:space="preserve">1.14021909236908</t>
   </si>
   <si>
     <t xml:space="preserve">1.14750933647156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1358448266983</t>
+    <t xml:space="preserve">1.13584470748901</t>
   </si>
   <si>
     <t xml:space="preserve">1.11944139003754</t>
@@ -1934,28 +1934,28 @@
     <t xml:space="preserve">1.11543154716492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10376691818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11251533031464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11069273948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13511574268341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1500608921051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15188372135162</t>
+    <t xml:space="preserve">1.10376679897308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11251544952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11069285869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13511562347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15006101131439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15188360214233</t>
   </si>
   <si>
     <t xml:space="preserve">1.147873878479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15261268615723</t>
+    <t xml:space="preserve">1.15261280536652</t>
   </si>
   <si>
     <t xml:space="preserve">1.16427743434906</t>
@@ -1964,43 +1964,43 @@
     <t xml:space="preserve">1.1704740524292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17156767845154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17229664325714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17849361896515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17484831809998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1916161775589</t>
+    <t xml:space="preserve">1.17156755924225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17229676246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17849349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17484843730927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19161629676819</t>
   </si>
   <si>
     <t xml:space="preserve">1.16318368911743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16609966754913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17995154857635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18469059467316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18104529380798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1712030172348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17375469207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14969635009766</t>
+    <t xml:space="preserve">1.16609990596771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17995166778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18469035625458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18104517459869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17120325565338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17375481128693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14969646930695</t>
   </si>
   <si>
     <t xml:space="preserve">1.15407073497772</t>
@@ -2012,16 +2012,16 @@
     <t xml:space="preserve">1.16209018230438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1668289899826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16755783557892</t>
+    <t xml:space="preserve">1.16682887077332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16755795478821</t>
   </si>
   <si>
     <t xml:space="preserve">1.17010962963104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13183498382568</t>
+    <t xml:space="preserve">1.13183510303497</t>
   </si>
   <si>
     <t xml:space="preserve">1.12418007850647</t>
@@ -2030,13 +2030,13 @@
     <t xml:space="preserve">1.12782526016235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14277064800262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16099655628204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14459311962128</t>
+    <t xml:space="preserve">1.14277052879333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16099643707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14459323883057</t>
   </si>
   <si>
     <t xml:space="preserve">1.15297710895538</t>
@@ -2051,22 +2051,22 @@
     <t xml:space="preserve">1.16391277313232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16938054561615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16573548316956</t>
+    <t xml:space="preserve">1.16938042640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16573536396027</t>
   </si>
   <si>
     <t xml:space="preserve">1.16500627994537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18833565711975</t>
+    <t xml:space="preserve">1.18833577632904</t>
   </si>
   <si>
     <t xml:space="preserve">1.20473897457123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20036470890045</t>
+    <t xml:space="preserve">1.20036482810974</t>
   </si>
   <si>
     <t xml:space="preserve">1.18870007991791</t>
@@ -2075,19 +2075,19 @@
     <t xml:space="preserve">1.1795871257782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16464173793793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17922246456146</t>
+    <t xml:space="preserve">1.16464185714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17922270298004</t>
   </si>
   <si>
     <t xml:space="preserve">1.18213880062103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17630624771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19599044322968</t>
+    <t xml:space="preserve">1.17630648612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19599056243896</t>
   </si>
   <si>
     <t xml:space="preserve">1.18979370594025</t>
@@ -2108,16 +2108,16 @@
     <t xml:space="preserve">1.21421658992767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21166503429413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23134899139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23025548458099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21603906154633</t>
+    <t xml:space="preserve">1.21166479587555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23134911060333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2302553653717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21603918075562</t>
   </si>
   <si>
     <t xml:space="preserve">1.21931993961334</t>
@@ -2141,19 +2141,19 @@
     <t xml:space="preserve">1.22114229202271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22405850887299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23061990737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22843265533447</t>
+    <t xml:space="preserve">1.22405862808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23062002658844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22843277454376</t>
   </si>
   <si>
     <t xml:space="preserve">1.23645222187042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2287974357605</t>
+    <t xml:space="preserve">1.22879719734192</t>
   </si>
   <si>
     <t xml:space="preserve">1.22624576091766</t>
@@ -2162,31 +2162,31 @@
     <t xml:space="preserve">1.27363324165344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27691400051117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31154358386993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31336605548859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30972063541412</t>
+    <t xml:space="preserve">1.27691388130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31154334545135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3133659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30972075462341</t>
   </si>
   <si>
     <t xml:space="preserve">1.30826270580292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31591773033142</t>
+    <t xml:space="preserve">1.31591749191284</t>
   </si>
   <si>
     <t xml:space="preserve">1.29331743717194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31518852710724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31445968151093</t>
+    <t xml:space="preserve">1.31518864631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31445956230164</t>
   </si>
   <si>
     <t xml:space="preserve">1.30862724781036</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">1.29732704162598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27873647212982</t>
+    <t xml:space="preserve">1.2787367105484</t>
   </si>
   <si>
     <t xml:space="preserve">1.28857862949371</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">1.27727842330933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27509129047394</t>
+    <t xml:space="preserve">1.27509140968323</t>
   </si>
   <si>
     <t xml:space="preserve">1.26452040672302</t>
@@ -2225,25 +2225,25 @@
     <t xml:space="preserve">1.24520063400269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24483621120453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19052278995514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1963552236557</t>
+    <t xml:space="preserve">1.24483609199524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19052267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19635510444641</t>
   </si>
   <si>
     <t xml:space="preserve">1.19854211807251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19343888759613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18068075180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20218729972839</t>
+    <t xml:space="preserve">1.19343876838684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18068063259125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20218741893768</t>
   </si>
   <si>
     <t xml:space="preserve">1.18906462192535</t>
@@ -2255,28 +2255,28 @@
     <t xml:space="preserve">1.20656156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20729064941406</t>
+    <t xml:space="preserve">1.20729076862335</t>
   </si>
   <si>
     <t xml:space="preserve">1.22515213489532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24155533313751</t>
+    <t xml:space="preserve">1.2415554523468</t>
   </si>
   <si>
     <t xml:space="preserve">1.23353612422943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21895527839661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21275854110718</t>
+    <t xml:space="preserve">1.2189553976059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21275842189789</t>
   </si>
   <si>
     <t xml:space="preserve">1.2083842754364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25504279136658</t>
+    <t xml:space="preserve">1.25504291057587</t>
   </si>
   <si>
     <t xml:space="preserve">1.2506685256958</t>
@@ -2300,22 +2300,22 @@
     <t xml:space="preserve">1.29368197917938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29222393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30607557296753</t>
+    <t xml:space="preserve">1.29222369194031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30607569217682</t>
   </si>
   <si>
     <t xml:space="preserve">1.3520051240921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34544372558594</t>
+    <t xml:space="preserve">1.34544384479523</t>
   </si>
   <si>
     <t xml:space="preserve">1.33414363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31409502029419</t>
+    <t xml:space="preserve">1.31409513950348</t>
   </si>
   <si>
     <t xml:space="preserve">1.3224790096283</t>
@@ -2330,25 +2330,25 @@
     <t xml:space="preserve">1.33159196376801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33013367652893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34981799125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34398567676544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3414341211319</t>
+    <t xml:space="preserve">1.33013391494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.349818110466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34398579597473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34143424034119</t>
   </si>
   <si>
     <t xml:space="preserve">1.34945344924927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.358931183815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36986649036407</t>
+    <t xml:space="preserve">1.35893106460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36986660957336</t>
   </si>
   <si>
     <t xml:space="preserve">1.3822603225708</t>
@@ -2369,28 +2369,28 @@
     <t xml:space="preserve">1.13766741752625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15589320659637</t>
+    <t xml:space="preserve">1.15589332580566</t>
   </si>
   <si>
     <t xml:space="preserve">1.19708395004272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11579620838165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996233522891998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924787521362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905467927455902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733049988746643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772782564163208</t>
+    <t xml:space="preserve">1.11579596996307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996233463287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924787580966949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905467867851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733049869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772782623767853</t>
   </si>
   <si>
     <t xml:space="preserve">0.750546872615814</t>
@@ -2402,25 +2402,25 @@
     <t xml:space="preserve">0.751276016235352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.754556715488434</t>
+    <t xml:space="preserve">0.754556596279144</t>
   </si>
   <si>
     <t xml:space="preserve">0.741433918476105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.729040205478668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786269962787628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797205567359924</t>
+    <t xml:space="preserve">0.729040265083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786269903182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79720550775528</t>
   </si>
   <si>
     <t xml:space="preserve">0.793195784091949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778250455856323</t>
+    <t xml:space="preserve">0.778250396251678</t>
   </si>
   <si>
     <t xml:space="preserve">0.824544608592987</t>
@@ -2438,49 +2438,49 @@
     <t xml:space="preserve">0.836209118366241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869015991687775</t>
+    <t xml:space="preserve">0.869016051292419</t>
   </si>
   <si>
     <t xml:space="preserve">0.869744956493378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855164170265198</t>
+    <t xml:space="preserve">0.855164110660553</t>
   </si>
   <si>
     <t xml:space="preserve">0.876670956611633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.889429152011871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885783910751343</t>
+    <t xml:space="preserve">0.889429092407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885783970355988</t>
   </si>
   <si>
     <t xml:space="preserve">0.897448480129242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910935819149017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911664724349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.883961260318756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888335585594177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879587173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89015805721283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906925976276398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901458203792572</t>
+    <t xml:space="preserve">0.910935699939728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911664843559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88396143913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888335466384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879587113857269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890158116817474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906926035881042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901458263397217</t>
   </si>
   <si>
     <t xml:space="preserve">0.89963561296463</t>
@@ -2489,10 +2489,10 @@
     <t xml:space="preserve">0.905832469463348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872296571731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879951596260071</t>
+    <t xml:space="preserve">0.872296512126923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879951655864716</t>
   </si>
   <si>
     <t xml:space="preserve">0.878128945827484</t>
@@ -2501,52 +2501,52 @@
     <t xml:space="preserve">0.882138669490814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877764403820038</t>
+    <t xml:space="preserve">0.877764463424683</t>
   </si>
   <si>
     <t xml:space="preserve">0.914580941200256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.934265077114105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911300301551819</t>
+    <t xml:space="preserve">0.93426513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911300361156464</t>
   </si>
   <si>
     <t xml:space="preserve">0.944332540035248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.902750730514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914020717144012</t>
+    <t xml:space="preserve">0.902750790119171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914020657539368</t>
   </si>
   <si>
     <t xml:space="preserve">0.910523056983948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912854790687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946275413036346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971146821975708</t>
+    <t xml:space="preserve">0.912854731082916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946275472640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971146762371063</t>
   </si>
   <si>
     <t xml:space="preserve">0.950550377368927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971535444259644</t>
+    <t xml:space="preserve">0.971535563468933</t>
   </si>
   <si>
     <t xml:space="preserve">0.969592392444611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.981639444828033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00573348999023</t>
+    <t xml:space="preserve">0.981639385223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00573360919952</t>
   </si>
   <si>
     <t xml:space="preserve">1.04265189170837</t>
@@ -2558,19 +2558,19 @@
     <t xml:space="preserve">1.03060472011566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05236732959747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02710735797882</t>
+    <t xml:space="preserve">1.05236721038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02710723876953</t>
   </si>
   <si>
     <t xml:space="preserve">1.0119514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960265636444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956379532814026</t>
+    <t xml:space="preserve">0.960265696048737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956379473209381</t>
   </si>
   <si>
     <t xml:space="preserve">0.978141844272614</t>
@@ -2579,49 +2579,49 @@
     <t xml:space="preserve">1.01156282424927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01778066158295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00961971282959</t>
+    <t xml:space="preserve">1.01778054237366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0096195936203</t>
   </si>
   <si>
     <t xml:space="preserve">1.01933491230011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01467180252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972312808036804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963763117790222</t>
+    <t xml:space="preserve">1.01467168331146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972312748432159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963763296604156</t>
   </si>
   <si>
     <t xml:space="preserve">0.977364599704742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979696393013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984359622001648</t>
+    <t xml:space="preserve">0.979696452617645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984359800815582</t>
   </si>
   <si>
     <t xml:space="preserve">0.999904274940491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996795415878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993686378002167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98319399356842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98280531167984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958322584629059</t>
+    <t xml:space="preserve">0.996795356273651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993686556816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983194053173065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982805371284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958322525024414</t>
   </si>
   <si>
     <t xml:space="preserve">0.961431443691254</t>
@@ -2630,28 +2630,28 @@
     <t xml:space="preserve">0.960654258728027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973867237567902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973089873790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985137045383453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987857341766357</t>
+    <t xml:space="preserve">0.973867118358612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973089933395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985136985778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987857222557068</t>
   </si>
   <si>
     <t xml:space="preserve">0.985525548458099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949773013591766</t>
+    <t xml:space="preserve">0.949773073196411</t>
   </si>
   <si>
     <t xml:space="preserve">0.954436480998993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970758259296417</t>
+    <t xml:space="preserve">0.970758199691772</t>
   </si>
   <si>
     <t xml:space="preserve">0.92878794670105</t>
@@ -2663,25 +2663,25 @@
     <t xml:space="preserve">0.95599091053009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959877014160156</t>
+    <t xml:space="preserve">0.959876954555511</t>
   </si>
   <si>
     <t xml:space="preserve">0.953659236431122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96531754732132</t>
+    <t xml:space="preserve">0.965317606925964</t>
   </si>
   <si>
     <t xml:space="preserve">0.982028067111969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01739203929901</t>
+    <t xml:space="preserve">1.01739192008972</t>
   </si>
   <si>
     <t xml:space="preserve">1.00612199306488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994852244853973</t>
+    <t xml:space="preserve">0.994852304458618</t>
   </si>
   <si>
     <t xml:space="preserve">0.979307770729065</t>
@@ -2690,10 +2690,10 @@
     <t xml:space="preserve">0.989411771297455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987079977989197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964929103851318</t>
+    <t xml:space="preserve">0.987079918384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964929163455963</t>
   </si>
   <si>
     <t xml:space="preserve">0.96259731054306</t>
@@ -2702,10 +2702,10 @@
     <t xml:space="preserve">0.958711206912994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96609503030777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951327562332153</t>
+    <t xml:space="preserve">0.96609491109848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951327502727509</t>
   </si>
   <si>
     <t xml:space="preserve">0.954047858715057</t>
@@ -2714,61 +2714,61 @@
     <t xml:space="preserve">0.975032985210419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968037843704224</t>
+    <t xml:space="preserve">0.968037962913513</t>
   </si>
   <si>
     <t xml:space="preserve">0.937726140022278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946664154529572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938503324985504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942000865936279</t>
+    <t xml:space="preserve">0.946664214134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938503265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942000806331635</t>
   </si>
   <si>
     <t xml:space="preserve">0.933451235294342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97192394733429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94899582862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953270614147186</t>
+    <t xml:space="preserve">0.971924066543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948995888233185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953270554542542</t>
   </si>
   <si>
     <t xml:space="preserve">0.9458869099617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929565072059631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931119561195374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900807738304138</t>
+    <t xml:space="preserve">0.929565250873566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931119620800018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900807678699493</t>
   </si>
   <si>
     <t xml:space="preserve">0.903528034687042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904693841934204</t>
+    <t xml:space="preserve">0.904693782329559</t>
   </si>
   <si>
     <t xml:space="preserve">0.898864567279816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878656625747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886428892612457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901584923267365</t>
+    <t xml:space="preserve">0.878656685352325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886428952217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90158486366272</t>
   </si>
   <si>
     <t xml:space="preserve">0.886040270328522</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">0.830079853534698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.848344802856445</t>
+    <t xml:space="preserve">0.848344743251801</t>
   </si>
   <si>
     <t xml:space="preserve">0.860780417919159</t>
@@ -2795,31 +2795,31 @@
     <t xml:space="preserve">0.892646729946136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.881376981735229</t>
+    <t xml:space="preserve">0.88137686252594</t>
   </si>
   <si>
     <t xml:space="preserve">0.942778050899506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93928050994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955213665962219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95249342918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947441339492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952104806900024</t>
+    <t xml:space="preserve">0.939280569553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955213725566864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952493369579315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947441399097443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952104866504669</t>
   </si>
   <si>
     <t xml:space="preserve">0.95948851108551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97619891166687</t>
+    <t xml:space="preserve">0.976198971271515</t>
   </si>
   <si>
     <t xml:space="preserve">1.01700341701508</t>
@@ -2828,10 +2828,10 @@
     <t xml:space="preserve">1.02205526828766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993297874927521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982416808605194</t>
+    <t xml:space="preserve">0.993297755718231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982416689395905</t>
   </si>
   <si>
     <t xml:space="preserve">0.975421667098999</t>
@@ -2843,19 +2843,19 @@
     <t xml:space="preserve">0.997184097766876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990966200828552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988245844841003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984748363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995629549026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954825222492218</t>
+    <t xml:space="preserve">0.990966141223907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988245904445648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984748303890228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995629608631134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954825043678284</t>
   </si>
   <si>
     <t xml:space="preserve">1.00651061534882</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">1.0138943195343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03449082374573</t>
+    <t xml:space="preserve">1.03449094295502</t>
   </si>
   <si>
     <t xml:space="preserve">1.02399849891663</t>
@@ -2879,16 +2879,16 @@
     <t xml:space="preserve">1.03954291343689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03487956523895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01428294181824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03759980201721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03215932846069</t>
+    <t xml:space="preserve">1.03487968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01428306102753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0375999212265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03215909004211</t>
   </si>
   <si>
     <t xml:space="preserve">1.02050089836121</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">1.03099346160889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06596863269806</t>
+    <t xml:space="preserve">1.06596875190735</t>
   </si>
   <si>
     <t xml:space="preserve">1.0729638338089</t>
@@ -2909,46 +2909,46 @@
     <t xml:space="preserve">1.05897355079651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0535329580307</t>
+    <t xml:space="preserve">1.05353307723999</t>
   </si>
   <si>
     <t xml:space="preserve">1.06169402599335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04498362541199</t>
+    <t xml:space="preserve">1.0449835062027</t>
   </si>
   <si>
     <t xml:space="preserve">1.10871636867523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13630795478821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15418410301208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12853562831879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13825082778931</t>
+    <t xml:space="preserve">1.13630783557892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1541839838028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1285355091095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1382509469986</t>
   </si>
   <si>
     <t xml:space="preserve">1.14252579212189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17516934871674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16195642948151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13863945007324</t>
+    <t xml:space="preserve">1.17516922950745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16195631027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13863956928253</t>
   </si>
   <si>
     <t xml:space="preserve">1.12154054641724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13475334644318</t>
+    <t xml:space="preserve">1.13475346565247</t>
   </si>
   <si>
     <t xml:space="preserve">1.12698125839233</t>
@@ -2957,13 +2957,13 @@
     <t xml:space="preserve">1.11415684223175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10366415977478</t>
+    <t xml:space="preserve">1.10366427898407</t>
   </si>
   <si>
     <t xml:space="preserve">1.11221396923065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09317171573639</t>
+    <t xml:space="preserve">1.0931715965271</t>
   </si>
   <si>
     <t xml:space="preserve">1.0838451385498</t>
@@ -2990,13 +2990,13 @@
     <t xml:space="preserve">1.1308673620224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15262961387634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14874351024628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15496134757996</t>
+    <t xml:space="preserve">1.15262973308563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14874362945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15496146678925</t>
   </si>
   <si>
     <t xml:space="preserve">1.16312217712402</t>
@@ -3005,19 +3005,19 @@
     <t xml:space="preserve">1.14563453197479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15301835536957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14641189575195</t>
+    <t xml:space="preserve">1.15301847457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14641201496124</t>
   </si>
   <si>
     <t xml:space="preserve">1.17089462280273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18954813480377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2047039270401</t>
+    <t xml:space="preserve">1.18954801559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20470380783081</t>
   </si>
   <si>
     <t xml:space="preserve">1.20664715766907</t>
@@ -3026,16 +3026,16 @@
     <t xml:space="preserve">1.21558523178101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21752822399139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20625853538513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20392680168152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20859003067017</t>
+    <t xml:space="preserve">1.21752834320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20625865459442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20392668247223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20859014987946</t>
   </si>
   <si>
     <t xml:space="preserve">1.22413468360901</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">1.20975601673126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19809746742249</t>
+    <t xml:space="preserve">1.19809758663177</t>
   </si>
   <si>
     <t xml:space="preserve">1.21286499500275</t>
@@ -3056,16 +3056,16 @@
     <t xml:space="preserve">1.2132533788681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20431530475616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21247613430023</t>
+    <t xml:space="preserve">1.20431542396545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21247637271881</t>
   </si>
   <si>
     <t xml:space="preserve">1.22685503959656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21403074264526</t>
+    <t xml:space="preserve">1.21403086185455</t>
   </si>
   <si>
     <t xml:space="preserve">1.2357931137085</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">1.23851346969604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24278831481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26105284690857</t>
+    <t xml:space="preserve">1.24278819561005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26105296611786</t>
   </si>
   <si>
     <t xml:space="preserve">1.26455056667328</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">1.26493918895721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27892935276031</t>
+    <t xml:space="preserve">1.27892923355103</t>
   </si>
   <si>
     <t xml:space="preserve">1.30457782745361</t>
@@ -3104,16 +3104,16 @@
     <t xml:space="preserve">1.31779074668884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29291939735413</t>
+    <t xml:space="preserve">1.29291927814484</t>
   </si>
   <si>
     <t xml:space="preserve">1.29874861240387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31740212440491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33061504364014</t>
+    <t xml:space="preserve">1.31740200519562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33061492443085</t>
   </si>
   <si>
     <t xml:space="preserve">1.34693682193756</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">1.37258529663086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40067207813263</t>
+    <t xml:space="preserve">1.40067195892334</t>
   </si>
   <si>
     <t xml:space="preserve">1.37502765655518</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">1.37787699699402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39497327804565</t>
+    <t xml:space="preserve">1.39497339725494</t>
   </si>
   <si>
     <t xml:space="preserve">1.391716837883</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">1.41044127941132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42305994033813</t>
+    <t xml:space="preserve">1.42306005954742</t>
   </si>
   <si>
     <t xml:space="preserve">1.43323636054993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45847368240356</t>
+    <t xml:space="preserve">1.45847380161285</t>
   </si>
   <si>
     <t xml:space="preserve">1.43852806091309</t>
@@ -3176,10 +3176,10 @@
     <t xml:space="preserve">1.43771398067474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4491114616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44951868057251</t>
+    <t xml:space="preserve">1.44911134243011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44951856136322</t>
   </si>
   <si>
     <t xml:space="preserve">1.45725250244141</t>
@@ -3188,13 +3188,13 @@
     <t xml:space="preserve">1.45765960216522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45521724224091</t>
+    <t xml:space="preserve">1.4552173614502</t>
   </si>
   <si>
     <t xml:space="preserve">1.43120110034943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4430056810379</t>
+    <t xml:space="preserve">1.44300556182861</t>
   </si>
   <si>
     <t xml:space="preserve">1.44422686100006</t>
@@ -3209,31 +3209,31 @@
     <t xml:space="preserve">1.40352141857147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41288352012634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41695427894592</t>
+    <t xml:space="preserve">1.41288363933563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41695415973663</t>
   </si>
   <si>
     <t xml:space="preserve">1.41898941993713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41329061985016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43527173995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3795051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38072645664215</t>
+    <t xml:space="preserve">1.41329073905945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43527162075043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37950527667999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38072633743286</t>
   </si>
   <si>
     <t xml:space="preserve">1.39945089817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41736137866974</t>
+    <t xml:space="preserve">1.41736125946045</t>
   </si>
   <si>
     <t xml:space="preserve">1.403928399086</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">1.35915267467499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38316869735718</t>
+    <t xml:space="preserve">1.38316881656647</t>
   </si>
   <si>
     <t xml:space="preserve">1.395787358284</t>
@@ -3263,22 +3263,22 @@
     <t xml:space="preserve">1.47801232337952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47394168376923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47068524360657</t>
+    <t xml:space="preserve">1.47394180297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47068536281586</t>
   </si>
   <si>
     <t xml:space="preserve">1.47923338413239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46824312210083</t>
+    <t xml:space="preserve">1.46824300289154</t>
   </si>
   <si>
     <t xml:space="preserve">1.4796404838562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49348020553589</t>
+    <t xml:space="preserve">1.49348032474518</t>
   </si>
   <si>
     <t xml:space="preserve">1.50691306591034</t>
@@ -3287,16 +3287,16 @@
     <t xml:space="preserve">1.52360236644745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53866326808929</t>
+    <t xml:space="preserve">1.53866314888</t>
   </si>
   <si>
     <t xml:space="preserve">1.54069864749908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55006098747253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58262515068054</t>
+    <t xml:space="preserve">1.55006086826324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58262503147125</t>
   </si>
   <si>
     <t xml:space="preserve">1.58669567108154</t>
@@ -3308,25 +3308,25 @@
     <t xml:space="preserve">1.58384621143341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55494546890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53215050697327</t>
+    <t xml:space="preserve">1.5549453496933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53215026855469</t>
   </si>
   <si>
     <t xml:space="preserve">1.52726590633392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52889394760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52197420597076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.514240026474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51912474632263</t>
+    <t xml:space="preserve">1.52889406681061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52197396755219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51424014568329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51912486553192</t>
   </si>
   <si>
     <t xml:space="preserve">1.50650596618652</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">1.49307322502136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51464712619781</t>
+    <t xml:space="preserve">1.51464700698853</t>
   </si>
   <si>
     <t xml:space="preserve">1.5162752866745</t>
@@ -3350,16 +3350,16 @@
     <t xml:space="preserve">1.48615336418152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48940980434418</t>
+    <t xml:space="preserve">1.48940968513489</t>
   </si>
   <si>
     <t xml:space="preserve">1.49063098430634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42794454097748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45155382156372</t>
+    <t xml:space="preserve">1.42794466018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45155394077301</t>
   </si>
   <si>
     <t xml:space="preserve">1.46173012256622</t>
@@ -3371,13 +3371,13 @@
     <t xml:space="preserve">1.4837110042572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47882616519928</t>
+    <t xml:space="preserve">1.47882640361786</t>
   </si>
   <si>
     <t xml:space="preserve">1.48411810398102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45643842220306</t>
+    <t xml:space="preserve">1.45643830299377</t>
   </si>
   <si>
     <t xml:space="preserve">1.45562422275543</t>
@@ -3395,10 +3395,10 @@
     <t xml:space="preserve">1.45684552192688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48737466335297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48533916473389</t>
+    <t xml:space="preserve">1.48737454414368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48533928394318</t>
   </si>
   <si>
     <t xml:space="preserve">1.5040637254715</t>
@@ -3407,16 +3407,16 @@
     <t xml:space="preserve">1.46417248249054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4450409412384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47475588321686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49673664569855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50894832611084</t>
+    <t xml:space="preserve">1.44504106044769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47475576400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49673676490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50894844532013</t>
   </si>
   <si>
     <t xml:space="preserve">1.502028465271</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">1.55779469013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50732028484344</t>
+    <t xml:space="preserve">1.50732016563416</t>
   </si>
   <si>
     <t xml:space="preserve">1.48004746437073</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">1.51301884651184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51953184604645</t>
+    <t xml:space="preserve">1.51953172683716</t>
   </si>
   <si>
     <t xml:space="preserve">1.51546132564545</t>
@@ -3479,13 +3479,13 @@
     <t xml:space="preserve">1.3921240568161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4059636592865</t>
+    <t xml:space="preserve">1.40596377849579</t>
   </si>
   <si>
     <t xml:space="preserve">1.39538037776947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40637063980103</t>
+    <t xml:space="preserve">1.40637075901031</t>
   </si>
   <si>
     <t xml:space="preserve">1.45196080207825</t>
@@ -3494,31 +3494,31 @@
     <t xml:space="preserve">1.43079400062561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45806670188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45440316200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45399606227875</t>
+    <t xml:space="preserve">1.45806658267975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45440304279327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45399618148804</t>
   </si>
   <si>
     <t xml:space="preserve">1.42835175991058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39130973815918</t>
+    <t xml:space="preserve">1.39130985736847</t>
   </si>
   <si>
     <t xml:space="preserve">1.37258541584015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32699525356293</t>
+    <t xml:space="preserve">1.32699537277222</t>
   </si>
   <si>
     <t xml:space="preserve">1.34531271457672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34775519371033</t>
+    <t xml:space="preserve">1.34775507450104</t>
   </si>
   <si>
     <t xml:space="preserve">1.36810779571533</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">1.39741563796997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4002650976181</t>
+    <t xml:space="preserve">1.40026497840881</t>
   </si>
   <si>
     <t xml:space="preserve">1.40677797794342</t>
@@ -3542,13 +3542,13 @@
     <t xml:space="preserve">1.35955965518951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35833835601807</t>
+    <t xml:space="preserve">1.35833847522736</t>
   </si>
   <si>
     <t xml:space="preserve">1.37462067604065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36770069599152</t>
+    <t xml:space="preserve">1.36770057678223</t>
   </si>
   <si>
     <t xml:space="preserve">1.35589623451233</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">1.35263979434967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33310127258301</t>
+    <t xml:space="preserve">1.33310115337372</t>
   </si>
   <si>
     <t xml:space="preserve">1.32414591312408</t>
@@ -3566,37 +3566,37 @@
     <t xml:space="preserve">1.3530467748642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34164929389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30664277076721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33269417285919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36525845527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41532611846924</t>
+    <t xml:space="preserve">1.34164917469025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30664265155792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3326940536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3652583360672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41532599925995</t>
   </si>
   <si>
     <t xml:space="preserve">1.37380647659302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36729371547699</t>
+    <t xml:space="preserve">1.3672935962677</t>
   </si>
   <si>
     <t xml:space="preserve">1.37909817695618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37624871730804</t>
+    <t xml:space="preserve">1.37624883651733</t>
   </si>
   <si>
     <t xml:space="preserve">1.36973595619202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33513641357422</t>
+    <t xml:space="preserve">1.33513629436493</t>
   </si>
   <si>
     <t xml:space="preserve">1.30949199199677</t>
@@ -3605,16 +3605,16 @@
     <t xml:space="preserve">1.28262650966644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30094385147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30542147159576</t>
+    <t xml:space="preserve">1.30094397068024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30542159080505</t>
   </si>
   <si>
     <t xml:space="preserve">1.29036045074463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26430904865265</t>
+    <t xml:space="preserve">1.26430892944336</t>
   </si>
   <si>
     <t xml:space="preserve">1.28913938999176</t>
@@ -3629,7 +3629,7 @@
     <t xml:space="preserve">1.27652060985565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25413274765015</t>
+    <t xml:space="preserve">1.25413262844086</t>
   </si>
   <si>
     <t xml:space="preserve">1.22889542579651</t>
@@ -3641,16 +3641,16 @@
     <t xml:space="preserve">1.22482478618622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28140532970428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30012989044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2549467086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22848808765411</t>
+    <t xml:space="preserve">1.281405210495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3001297712326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25494682788849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2284882068634</t>
   </si>
   <si>
     <t xml:space="preserve">1.19918048381805</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">1.18249118328094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20243680477142</t>
+    <t xml:space="preserve">1.20243692398071</t>
   </si>
   <si>
     <t xml:space="preserve">1.25616788864136</t>
@@ -3668,22 +3668,22 @@
     <t xml:space="preserve">1.24639868736267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2447704076767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23093068599701</t>
+    <t xml:space="preserve">1.24477052688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23093056678772</t>
   </si>
   <si>
     <t xml:space="preserve">1.22238254547119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22116136550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21464848518372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23785042762756</t>
+    <t xml:space="preserve">1.22116148471832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21464836597443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23785054683685</t>
   </si>
   <si>
     <t xml:space="preserve">1.2508761882782</t>
@@ -3701,13 +3701,13 @@
     <t xml:space="preserve">1.25698220729828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27489233016968</t>
+    <t xml:space="preserve">1.27489244937897</t>
   </si>
   <si>
     <t xml:space="preserve">1.25779604911804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26553022861481</t>
+    <t xml:space="preserve">1.26553010940552</t>
   </si>
   <si>
     <t xml:space="preserve">1.25942444801331</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">1.29768741130829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2980945110321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33554339408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36281609535217</t>
+    <t xml:space="preserve">1.29809439182281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33554351329803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36281621456146</t>
   </si>
   <si>
     <t xml:space="preserve">1.35223269462585</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">1.3571172952652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34856915473938</t>
+    <t xml:space="preserve">1.34856903553009</t>
   </si>
   <si>
     <t xml:space="preserve">1.34409153461456</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">1.36485135555267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33961403369904</t>
+    <t xml:space="preserve">1.33961391448975</t>
   </si>
   <si>
     <t xml:space="preserve">1.32129657268524</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">1.3245530128479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33432245254517</t>
+    <t xml:space="preserve">1.33432233333588</t>
   </si>
   <si>
     <t xml:space="preserve">1.33106589317322</t>
@@ -3761,10 +3761,10 @@
     <t xml:space="preserve">1.34002101421356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32862341403961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31193435192108</t>
+    <t xml:space="preserve">1.3286235332489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31193447113037</t>
   </si>
   <si>
     <t xml:space="preserve">1.3164119720459</t>
@@ -3779,19 +3779,19 @@
     <t xml:space="preserve">1.34327733516693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38561117649078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33147299289703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36037361621857</t>
+    <t xml:space="preserve">1.38561105728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33147287368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36037373542786</t>
   </si>
   <si>
     <t xml:space="preserve">1.34205627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40272557735443</t>
+    <t xml:space="preserve">1.40272545814514</t>
   </si>
   <si>
     <t xml:space="preserve">1.36872255802155</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">1.35796213150024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34504973888397</t>
+    <t xml:space="preserve">1.34504961967468</t>
   </si>
   <si>
     <t xml:space="preserve">1.32998502254486</t>
@@ -3818,16 +3818,16 @@
     <t xml:space="preserve">1.31578135490417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30416011810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33041548728943</t>
+    <t xml:space="preserve">1.30416023731232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33041560649872</t>
   </si>
   <si>
     <t xml:space="preserve">1.31018602848053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3123379945755</t>
+    <t xml:space="preserve">1.31233811378479</t>
   </si>
   <si>
     <t xml:space="preserve">1.270587682724</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">1.14921045303345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11047291755676</t>
+    <t xml:space="preserve">1.11047303676605</t>
   </si>
   <si>
     <t xml:space="preserve">1.15050172805786</t>
@@ -3860,10 +3860,10 @@
     <t xml:space="preserve">1.03945434093475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05581033229828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10143435001373</t>
+    <t xml:space="preserve">1.05581021308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10143423080444</t>
   </si>
   <si>
     <t xml:space="preserve">1.08593928813934</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">1.09540855884552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07517898082733</t>
+    <t xml:space="preserve">1.07517886161804</t>
   </si>
   <si>
     <t xml:space="preserve">1.043328166008</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">1.00200819969177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02352893352509</t>
+    <t xml:space="preserve">1.02352905273438</t>
   </si>
   <si>
     <t xml:space="preserve">1.05365812778473</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">1.03816306591034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02955484390259</t>
+    <t xml:space="preserve">1.02955496311188</t>
   </si>
   <si>
     <t xml:space="preserve">1.0588231086731</t>
@@ -3932,10 +3932,10 @@
     <t xml:space="preserve">1.04203689098358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04978430271149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07474851608276</t>
+    <t xml:space="preserve">1.04978442192078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07474863529205</t>
   </si>
   <si>
     <t xml:space="preserve">1.09024345874786</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">1.08636963367462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07690072059631</t>
+    <t xml:space="preserve">1.07690060138702</t>
   </si>
   <si>
     <t xml:space="preserve">1.06786179542542</t>
@@ -3959,40 +3959,40 @@
     <t xml:space="preserve">1.11305546760559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10100400447845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10272550582886</t>
+    <t xml:space="preserve">1.10100388526917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10272562503815</t>
   </si>
   <si>
     <t xml:space="preserve">1.08292639255524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06097531318665</t>
+    <t xml:space="preserve">1.06097519397736</t>
   </si>
   <si>
     <t xml:space="preserve">1.06355774402618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05839276313782</t>
+    <t xml:space="preserve">1.05839264392853</t>
   </si>
   <si>
     <t xml:space="preserve">1.0170726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996843278408051</t>
+    <t xml:space="preserve">0.996843218803406</t>
   </si>
   <si>
     <t xml:space="preserve">0.999425709247589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.963701248168945</t>
+    <t xml:space="preserve">0.963701188564301</t>
   </si>
   <si>
     <t xml:space="preserve">0.946914970874786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968435704708099</t>
+    <t xml:space="preserve">0.968435764312744</t>
   </si>
   <si>
     <t xml:space="preserve">0.945623755455017</t>
@@ -4007,22 +4007,22 @@
     <t xml:space="preserve">0.920229196548462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965422928333282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975322365760803</t>
+    <t xml:space="preserve">0.965422809123993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975322425365448</t>
   </si>
   <si>
     <t xml:space="preserve">0.952510416507721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92625492811203</t>
+    <t xml:space="preserve">0.926254987716675</t>
   </si>
   <si>
     <t xml:space="preserve">0.930128753185272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913342535495758</t>
+    <t xml:space="preserve">0.913342595100403</t>
   </si>
   <si>
     <t xml:space="preserve">0.92195075750351</t>
@@ -4037,22 +4037,22 @@
     <t xml:space="preserve">0.882783055305481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888808846473694</t>
+    <t xml:space="preserve">0.888808906078339</t>
   </si>
   <si>
     <t xml:space="preserve">0.852567851543427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.862984001636505</t>
+    <t xml:space="preserve">0.86298394203186</t>
   </si>
   <si>
     <t xml:space="preserve">0.85377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860659718513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879339635372162</t>
+    <t xml:space="preserve">0.860659658908844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879339694976807</t>
   </si>
   <si>
     <t xml:space="preserve">0.903442978858948</t>
@@ -4067,10 +4067,10 @@
     <t xml:space="preserve">0.8353511095047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.846542000770569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837245047092438</t>
+    <t xml:space="preserve">0.846541941165924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837244987487793</t>
   </si>
   <si>
     <t xml:space="preserve">0.820200502872467</t>
@@ -4088,19 +4088,19 @@
     <t xml:space="preserve">0.879770040512085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871161758899689</t>
+    <t xml:space="preserve">0.871161699295044</t>
   </si>
   <si>
     <t xml:space="preserve">0.896986782550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949497520923615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948206305503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982209086418152</t>
+    <t xml:space="preserve">0.949497580528259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9482062458992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982209026813507</t>
   </si>
   <si>
     <t xml:space="preserve">0.971018254756927</t>
@@ -4115,25 +4115,25 @@
     <t xml:space="preserve">0.966283679008484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955092966556549</t>
+    <t xml:space="preserve">0.955092906951904</t>
   </si>
   <si>
     <t xml:space="preserve">0.972309589385986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993830323219299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0045907497406</t>
+    <t xml:space="preserve">0.993830382823944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00459086894989</t>
   </si>
   <si>
     <t xml:space="preserve">1.01061654090881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11176431179047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1160683631897</t>
+    <t xml:space="preserve">1.11176419258118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11606848239899</t>
   </si>
   <si>
     <t xml:space="preserve">1.12295508384705</t>
@@ -4142,13 +4142,13 @@
     <t xml:space="preserve">1.10616886615753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.126828789711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12209439277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11822044849396</t>
+    <t xml:space="preserve">1.12682890892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1220942735672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11822056770325</t>
   </si>
   <si>
     <t xml:space="preserve">1.09669971466064</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">1.12898087501526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13586759567261</t>
+    <t xml:space="preserve">1.13586747646332</t>
   </si>
   <si>
     <t xml:space="preserve">1.13027215003967</t>
@@ -4187,22 +4187,22 @@
     <t xml:space="preserve">1.11951184272766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12166368961334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12984180450439</t>
+    <t xml:space="preserve">1.12166380882263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1298416852951</t>
   </si>
   <si>
     <t xml:space="preserve">1.14490628242493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11692941188812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09282600879669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07603967189789</t>
+    <t xml:space="preserve">1.11692929267883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0928258895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07603979110718</t>
   </si>
   <si>
     <t xml:space="preserve">1.08378720283508</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">1.06958341598511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07173562049866</t>
+    <t xml:space="preserve">1.07173550128937</t>
   </si>
   <si>
     <t xml:space="preserve">1.09971261024475</t>
@@ -4223,19 +4223,19 @@
     <t xml:space="preserve">1.12553763389587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13888037204742</t>
+    <t xml:space="preserve">1.13888049125671</t>
   </si>
   <si>
     <t xml:space="preserve">1.14705836772919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18837833404541</t>
+    <t xml:space="preserve">1.18837821483612</t>
   </si>
   <si>
     <t xml:space="preserve">1.19354343414307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19827771186829</t>
+    <t xml:space="preserve">1.19827783107758</t>
   </si>
   <si>
     <t xml:space="preserve">1.20043003559113</t>
@@ -4244,13 +4244,13 @@
     <t xml:space="preserve">1.20516443252563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21032953262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17245304584503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15093207359314</t>
+    <t xml:space="preserve">1.21032965183258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17245292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15093219280243</t>
   </si>
   <si>
     <t xml:space="preserve">1.18192207813263</t>
@@ -4268,10 +4268,10 @@
     <t xml:space="preserve">1.21119022369385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1948344707489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18665671348572</t>
+    <t xml:space="preserve">1.19483458995819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18665659427643</t>
   </si>
   <si>
     <t xml:space="preserve">1.20989918708801</t>
@@ -4295,7 +4295,7 @@
     <t xml:space="preserve">1.17675697803497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19139111042023</t>
+    <t xml:space="preserve">1.19139122962952</t>
   </si>
   <si>
     <t xml:space="preserve">1.18235242366791</t>
@@ -4310,16 +4310,16 @@
     <t xml:space="preserve">1.18579590320587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18966948986053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20215165615082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20129072666168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16944003105164</t>
+    <t xml:space="preserve">1.18966960906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20215153694153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20129060745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16943991184235</t>
   </si>
   <si>
     <t xml:space="preserve">1.18364369869232</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">1.18493497371674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17503547668457</t>
+    <t xml:space="preserve">1.17503535747528</t>
   </si>
   <si>
     <t xml:space="preserve">1.16814875602722</t>
@@ -4343,10 +4343,10 @@
     <t xml:space="preserve">1.15738832950592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18278300762177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18321335315704</t>
+    <t xml:space="preserve">1.18278288841248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18321323394775</t>
   </si>
   <si>
     <t xml:space="preserve">1.25078856945038</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">1.26240992546082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2365847826004</t>
+    <t xml:space="preserve">1.23658490180969</t>
   </si>
   <si>
     <t xml:space="preserve">1.25294065475464</t>
@@ -4376,16 +4376,16 @@
     <t xml:space="preserve">1.25121903419495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26542282104492</t>
+    <t xml:space="preserve">1.26542270183563</t>
   </si>
   <si>
     <t xml:space="preserve">1.25853610038757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26714432239532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29426074028015</t>
+    <t xml:space="preserve">1.26714444160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29426062107086</t>
   </si>
   <si>
     <t xml:space="preserve">1.32869386672974</t>
@@ -4406,7 +4406,7 @@
     <t xml:space="preserve">1.31922471523285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35150587558746</t>
+    <t xml:space="preserve">1.35150599479675</t>
   </si>
   <si>
     <t xml:space="preserve">1.33988475799561</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">1.35968375205994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3523668050766</t>
+    <t xml:space="preserve">1.35236668586731</t>
   </si>
   <si>
     <t xml:space="preserve">1.36614012718201</t>
@@ -4451,7 +4451,7 @@
     <t xml:space="preserve">1.43113279342651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45609700679779</t>
+    <t xml:space="preserve">1.4560968875885</t>
   </si>
   <si>
     <t xml:space="preserve">1.46728777885437</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">1.37905251979828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41047286987305</t>
+    <t xml:space="preserve">1.41047275066376</t>
   </si>
   <si>
     <t xml:space="preserve">1.42495942115784</t>
@@ -5955,6 +5955,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.45300006866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46399998664856</t>
   </si>
 </sst>
 </file>
@@ -71189,7 +71192,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6497685185</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>9135328</v>
@@ -71210,6 +71213,32 @@
         <v>1980</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6910763889</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>19470094</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>2.48300004005432</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>2.44300007820129</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>2.45799994468689</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>2.46399998664856</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1981</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1987" uniqueCount="1987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="1988">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765547573566437</t>
+    <t xml:space="preserve">0.765547692775726</t>
   </si>
   <si>
     <t xml:space="preserve">A2A.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.7743039727211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76930034160614</t>
+    <t xml:space="preserve">0.774303913116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769300401210785</t>
   </si>
   <si>
     <t xml:space="preserve">0.777431190013885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.772427618503571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775554656982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736151695251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728020787239075</t>
+    <t xml:space="preserve">0.772427558898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775554776191711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736151576042175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728020906448364</t>
   </si>
   <si>
     <t xml:space="preserve">0.708631992340088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.701126635074615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.678610444068909</t>
+    <t xml:space="preserve">0.701126575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678610503673553</t>
   </si>
   <si>
     <t xml:space="preserve">0.686115801334381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66297435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.669854283332825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.673606991767883</t>
+    <t xml:space="preserve">0.662974238395691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.66985422372818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.673606872558594</t>
   </si>
   <si>
     <t xml:space="preserve">0.661723375320435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689868569374084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.667352497577667</t>
+    <t xml:space="preserve">0.68986850976944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.667352437973022</t>
   </si>
   <si>
     <t xml:space="preserve">0.688617587089539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689243137836456</t>
+    <t xml:space="preserve">0.689243018627167</t>
   </si>
   <si>
     <t xml:space="preserve">0.676108658313751</t>
@@ -107,19 +107,19 @@
     <t xml:space="preserve">0.671105086803436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66672694683075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643585443496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612313091754913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597927808761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605745851993561</t>
+    <t xml:space="preserve">0.666727006435394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643585562705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612313032150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597927749156952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605745911598206</t>
   </si>
   <si>
     <t xml:space="preserve">0.610749423503876</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">0.614189386367798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627323806285858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617942035198212</t>
+    <t xml:space="preserve">0.627323746681213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617942094802856</t>
   </si>
   <si>
     <t xml:space="preserve">0.624822020530701</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">0.646712720394135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636080026626587</t>
+    <t xml:space="preserve">0.636079967021942</t>
   </si>
   <si>
     <t xml:space="preserve">0.656719744205475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645461797714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641083657741547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647963464260101</t>
+    <t xml:space="preserve">0.645461678504944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641083538532257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.647963523864746</t>
   </si>
   <si>
     <t xml:space="preserve">0.657345235347748</t>
@@ -164,55 +164,55 @@
     <t xml:space="preserve">0.67298150062561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666101574897766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.66485071182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658596098423004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651716232299805</t>
+    <t xml:space="preserve">0.666101634502411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.66485059261322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658596158027649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651716291904449</t>
   </si>
   <si>
     <t xml:space="preserve">0.654843509197235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669228911399841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71301007270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692995727062225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.691119372844696</t>
+    <t xml:space="preserve">0.669228851795197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713010132312775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69299578666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.691119492053986</t>
   </si>
   <si>
     <t xml:space="preserve">0.694246709346771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69799941778183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696123063564301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703002989292145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692370235919952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.699250280857086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714260995388031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71488630771637</t>
+    <t xml:space="preserve">0.697999358177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696123003959656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692370295524597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.699250340461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714261054992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714886426925659</t>
   </si>
   <si>
     <t xml:space="preserve">0.702377557754517</t>
@@ -221,13 +221,13 @@
     <t xml:space="preserve">0.705504775047302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.735526263713837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.740529716014862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.744282424449921</t>
+    <t xml:space="preserve">0.735526204109192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.740529775619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.744282603263855</t>
   </si>
   <si>
     <t xml:space="preserve">0.748660624027252</t>
@@ -236,58 +236,58 @@
     <t xml:space="preserve">0.738027989864349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.750536918640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754289627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768049538135529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757416903972626</t>
+    <t xml:space="preserve">0.750536978244781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754289507865906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768049418926239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757416784763336</t>
   </si>
   <si>
     <t xml:space="preserve">0.766798555850983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.752413272857666</t>
+    <t xml:space="preserve">0.752413332462311</t>
   </si>
   <si>
     <t xml:space="preserve">0.781183779239655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778056621551514</t>
+    <t xml:space="preserve">0.778056561946869</t>
   </si>
   <si>
     <t xml:space="preserve">0.786187350749969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779307544231415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768674910068512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755540490150452</t>
+    <t xml:space="preserve">0.77930760383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768674850463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755540430545807</t>
   </si>
   <si>
     <t xml:space="preserve">0.760544061660767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.764296889305115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770551383495331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75929319858551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769925773143768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.761169493198395</t>
+    <t xml:space="preserve">0.76429682970047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770551323890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759293258190155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769925892353058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76116955280304</t>
   </si>
   <si>
     <t xml:space="preserve">0.767424046993256</t>
@@ -299,22 +299,22 @@
     <t xml:space="preserve">0.751787841320038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.754914999008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781809270381927</t>
+    <t xml:space="preserve">0.754915058612823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781809329986572</t>
   </si>
   <si>
     <t xml:space="preserve">0.801198244094849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804951012134552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799321949481964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785561978816986</t>
+    <t xml:space="preserve">0.804950892925262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799321830272675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785562038421631</t>
   </si>
   <si>
     <t xml:space="preserve">0.796820104122162</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">0.791816473007202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801823675632477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733649849891663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725519001483917</t>
+    <t xml:space="preserve">0.801823556423187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733649790287018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725519061088562</t>
   </si>
   <si>
     <t xml:space="preserve">0.766306459903717</t>
@@ -341,28 +341,28 @@
     <t xml:space="preserve">0.750760138034821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778614103794098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703473269939423</t>
+    <t xml:space="preserve">0.778614044189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703473150730133</t>
   </si>
   <si>
     <t xml:space="preserve">0.69246119260788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.70541650056839</t>
+    <t xml:space="preserve">0.705416560173035</t>
   </si>
   <si>
     <t xml:space="preserve">0.730031549930573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.763067603111267</t>
+    <t xml:space="preserve">0.763067483901978</t>
   </si>
   <si>
     <t xml:space="preserve">0.762419879436493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769545257091522</t>
+    <t xml:space="preserve">0.769545197486877</t>
   </si>
   <si>
     <t xml:space="preserve">0.75788551568985</t>
@@ -374,40 +374,40 @@
     <t xml:space="preserve">0.742339134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.758533298969269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77731853723526</t>
+    <t xml:space="preserve">0.758533239364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777318477630615</t>
   </si>
   <si>
     <t xml:space="preserve">0.774079740047455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776022970676422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783796191215515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779909491539001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790273904800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789626181125641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79416024684906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805172502994537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807763516902924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.822661995887756</t>
+    <t xml:space="preserve">0.776022851467133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78379625082016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779909610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79027384519577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789625883102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794160306453705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805172443389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807763457298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.822662115097046</t>
   </si>
   <si>
     <t xml:space="preserve">0.817479908466339</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">0.820718705654144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.822014451026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809706687927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814241111278534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816184461116791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804524540901184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801285743713379</t>
+    <t xml:space="preserve">0.822014212608337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809706747531891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814240992069244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816184520721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804524660110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801285922527313</t>
   </si>
   <si>
     <t xml:space="preserve">0.812945604324341</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">0.801933526992798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786387085914612</t>
+    <t xml:space="preserve">0.786387264728546</t>
   </si>
   <si>
     <t xml:space="preserve">0.788330495357513</t>
@@ -449,79 +449,79 @@
     <t xml:space="preserve">0.771488547325134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783148288726807</t>
+    <t xml:space="preserve">0.783148407936096</t>
   </si>
   <si>
     <t xml:space="preserve">0.782500565052032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781852900981903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770192980766296</t>
+    <t xml:space="preserve">0.781852841377258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770193099975586</t>
   </si>
   <si>
     <t xml:space="preserve">0.785091638565063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.795455992221832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811002314090729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794808208942413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796103596687317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798694610595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802581250667572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79092139005661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796751320362091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799342453479767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81035453081131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78055727481842</t>
+    <t xml:space="preserve">0.795455873012543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811002254486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794808149337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796103656291962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798694670200348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802581310272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790921449661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796751499176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799342393875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810354471206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780557334423065</t>
   </si>
   <si>
     <t xml:space="preserve">0.784443855285645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785739302635193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827196419239044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813593327999115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80063796043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79739910364151</t>
+    <t xml:space="preserve">0.785739421844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827196359634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81359338760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800638020038605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797399282455444</t>
   </si>
   <si>
     <t xml:space="preserve">0.80387681722641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.80711567401886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.761124312877655</t>
+    <t xml:space="preserve">0.807115733623505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761124432086945</t>
   </si>
   <si>
     <t xml:space="preserve">0.770840883255005</t>
@@ -530,70 +530,70 @@
     <t xml:space="preserve">0.73132711648941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.735861480236053</t>
+    <t xml:space="preserve">0.735861420631409</t>
   </si>
   <si>
     <t xml:space="preserve">0.720315158367157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.72161066532135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.719019591808319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696347832679749</t>
+    <t xml:space="preserve">0.721610724925995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.719019651412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696347773075104</t>
   </si>
   <si>
     <t xml:space="preserve">0.696995556354523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.709950923919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713837504386902</t>
+    <t xml:space="preserve">0.709950804710388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713837385177612</t>
   </si>
   <si>
     <t xml:space="preserve">0.711894154548645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.707359850406647</t>
+    <t xml:space="preserve">0.707359790802002</t>
   </si>
   <si>
     <t xml:space="preserve">0.728736102581024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715780854225159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722258508205414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76501077413559</t>
+    <t xml:space="preserve">0.715780794620514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722258448600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765011012554169</t>
   </si>
   <si>
     <t xml:space="preserve">0.754646718502045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.755294442176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787682712078094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776670694351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772136449813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787034928798676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816832184791565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819423317909241</t>
+    <t xml:space="preserve">0.755294501781464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78768265247345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776670753955841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772136390209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78703498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81683212518692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819423198699951</t>
   </si>
   <si>
     <t xml:space="preserve">0.799990236759186</t>
@@ -602,139 +602,139 @@
     <t xml:space="preserve">0.824605345726013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838856101036072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831730842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832378625869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840151846408844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848572611808777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841447174549103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844686031341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830435276031494</t>
+    <t xml:space="preserve">0.838856220245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831730663776398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832378447055817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840151607990265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848572671413422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841447234153748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844686150550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830435156822205</t>
   </si>
   <si>
     <t xml:space="preserve">0.798047006130219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.815536677837372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820071041584015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806467831134796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811650037765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836265206336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844038188457489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837560653686523</t>
+    <t xml:space="preserve">0.815536618232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82007098197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80646800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811650097370148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836265087127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844038307666779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837560713291168</t>
   </si>
   <si>
     <t xml:space="preserve">0.836912989616394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.821366608142853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828492045402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825900793075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829139649868011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846629440784454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849220514297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864766716957092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867357850074768</t>
+    <t xml:space="preserve">0.821366310119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828491985797882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825900912284851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829139709472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84662938117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849220335483551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864766895771027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867357790470123</t>
   </si>
   <si>
     <t xml:space="preserve">0.868005573749542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.870596587657928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857641398906708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.865414500236511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866710066795349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853107094764709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855698108673096</t>
+    <t xml:space="preserve">0.870596706867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857641339302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.865414559841156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866710245609283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85310697555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855698049068451</t>
   </si>
   <si>
     <t xml:space="preserve">0.858289182186127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860232353210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872539877891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874483287334442</t>
+    <t xml:space="preserve">0.860232532024384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87253999710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874483346939087</t>
   </si>
   <si>
     <t xml:space="preserve">0.887438714504242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.893916308879852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892620801925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912701427936554</t>
+    <t xml:space="preserve">0.893916249275208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892620742321014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912701487541199</t>
   </si>
   <si>
     <t xml:space="preserve">0.909462690353394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.908167004585266</t>
+    <t xml:space="preserve">0.908167064189911</t>
   </si>
   <si>
     <t xml:space="preserve">0.919826984405518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91853141784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875778913497925</t>
+    <t xml:space="preserve">0.918531358242035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875778794288635</t>
   </si>
   <si>
     <t xml:space="preserve">0.877722144126892</t>
@@ -743,67 +743,67 @@
     <t xml:space="preserve">0.891972899436951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.884847640991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895211815834045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884199857711792</t>
+    <t xml:space="preserve">0.884847342967987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895211696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884199798107147</t>
   </si>
   <si>
     <t xml:space="preserve">0.876426637172699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.862175643444061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856345772743225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88225656747818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899098455905914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890677571296692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926952302455902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91529244184494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917235851287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966465890407562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958045065402985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965170562267303</t>
+    <t xml:space="preserve">0.862175583839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85634583234787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882256507873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899098336696625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890677452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926952183246613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915292501449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917235732078552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966466069221497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95804500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965170443058014</t>
   </si>
   <si>
     <t xml:space="preserve">0.96128386259079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.963227272033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941850781440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941202998161316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958692848682404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982278108596802</t>
+    <t xml:space="preserve">0.963227152824402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941850900650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941203117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958692729473114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982278227806091</t>
   </si>
   <si>
     <t xml:space="preserve">0.988308608531952</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">1.00036931037903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992998778820038</t>
+    <t xml:space="preserve">0.992998898029327</t>
   </si>
   <si>
     <t xml:space="preserve">0.96820741891861</t>
@@ -830,28 +830,28 @@
     <t xml:space="preserve">0.988978505134583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989648818969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97490781545639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999699056148529</t>
+    <t xml:space="preserve">0.989648520946503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.974907755851746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999699115753174</t>
   </si>
   <si>
     <t xml:space="preserve">1.00505948066711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998358964920044</t>
+    <t xml:space="preserve">0.998359084129333</t>
   </si>
   <si>
     <t xml:space="preserve">0.997689008712769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00170946121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00706970691681</t>
+    <t xml:space="preserve">1.00170934200287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0070698261261</t>
   </si>
   <si>
     <t xml:space="preserve">1.02047049999237</t>
@@ -860,10 +860,10 @@
     <t xml:space="preserve">1.02985095977783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01779043674469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995009005069733</t>
+    <t xml:space="preserve">1.0177903175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995008945465088</t>
   </si>
   <si>
     <t xml:space="preserve">0.999029219150543</t>
@@ -872,112 +872,112 @@
     <t xml:space="preserve">0.976917803287506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974237680435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970217406749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965527236461639</t>
+    <t xml:space="preserve">0.974237620830536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970217347145081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965527176856995</t>
   </si>
   <si>
     <t xml:space="preserve">0.960836887359619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961507022380829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964187204837799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980268120765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978928029537201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984958410263062</t>
+    <t xml:space="preserve">0.961506903171539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964187145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980268180370331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97892814874649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984958350658417</t>
   </si>
   <si>
     <t xml:space="preserve">0.972897589206696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960166811943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958826839923859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951456248760223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955476522445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949446260929108</t>
+    <t xml:space="preserve">0.960166752338409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958826720714569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951456308364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955476582050323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949446439743042</t>
   </si>
   <si>
     <t xml:space="preserve">0.963517129421234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950116395950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953466653823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956816613674164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958156704902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952796518802643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962176918983459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944755852222443</t>
+    <t xml:space="preserve">0.950116217136383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953466415405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956816732883453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958156585693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952796399593353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962177038192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944755911827087</t>
   </si>
   <si>
     <t xml:space="preserve">0.931355118751526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948106110095978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954136490821838</t>
+    <t xml:space="preserve">0.948106229305267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954136431217194</t>
   </si>
   <si>
     <t xml:space="preserve">0.957486689090729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939395666122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946766018867493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934705257415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9286749958992</t>
+    <t xml:space="preserve">0.939395606517792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946766138076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934705317020416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928674876689911</t>
   </si>
   <si>
     <t xml:space="preserve">0.924654722213745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.932695150375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945425868034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959496676921844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973567605018616</t>
+    <t xml:space="preserve">0.932695209980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945426046848297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959496855735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973567724227905</t>
   </si>
   <si>
     <t xml:space="preserve">0.978258013725281</t>
@@ -986,43 +986,43 @@
     <t xml:space="preserve">0.993668913841248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984288394451141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983618199825287</t>
+    <t xml:space="preserve">0.984288215637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983618319034576</t>
   </si>
   <si>
     <t xml:space="preserve">0.994338810443878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977587819099426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980938017368317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972227513790131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966197073459625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969547390937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968877553939819</t>
+    <t xml:space="preserve">0.977587997913361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980938076972961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972227692604065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966197192668915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96954745054245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96887731552124</t>
   </si>
   <si>
     <t xml:space="preserve">0.9715576171875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995679020881653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992328703403473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966867208480835</t>
+    <t xml:space="preserve">0.995678961277008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992328822612762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966867327690125</t>
   </si>
   <si>
     <t xml:space="preserve">1.02114045619965</t>
@@ -1034,13 +1034,13 @@
     <t xml:space="preserve">1.01444005966187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0218106508255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02382063865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02851104736328</t>
+    <t xml:space="preserve">1.02181053161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02382051944733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0285108089447</t>
   </si>
   <si>
     <t xml:space="preserve">1.03320121765137</t>
@@ -1049,19 +1049,19 @@
     <t xml:space="preserve">1.03923153877258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02650058269501</t>
+    <t xml:space="preserve">1.0265007019043</t>
   </si>
   <si>
     <t xml:space="preserve">1.05531251430511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05866277217865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04459190368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05330240726471</t>
+    <t xml:space="preserve">1.05866265296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04459178447723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05330228805542</t>
   </si>
   <si>
     <t xml:space="preserve">1.06804323196411</t>
@@ -1073,37 +1073,37 @@
     <t xml:space="preserve">1.08613443374634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0955148935318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08345425128937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08211410045624</t>
+    <t xml:space="preserve">1.09551477432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08345413208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08211398124695</t>
   </si>
   <si>
     <t xml:space="preserve">1.05397236347198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06000280380249</t>
+    <t xml:space="preserve">1.0600026845932</t>
   </si>
   <si>
     <t xml:space="preserve">1.04392170906067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04861211776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04660212993622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03990173339844</t>
+    <t xml:space="preserve">1.04861223697662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04660201072693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03990149497986</t>
   </si>
   <si>
     <t xml:space="preserve">1.04258179664612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01980030536652</t>
+    <t xml:space="preserve">1.01980042457581</t>
   </si>
   <si>
     <t xml:space="preserve">1.015780210495</t>
@@ -1115,43 +1115,43 @@
     <t xml:space="preserve">1.06737327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06603300571442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02449071407318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01846039295197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02784085273743</t>
+    <t xml:space="preserve">1.06603312492371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02449059486389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01846027374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02784073352814</t>
   </si>
   <si>
     <t xml:space="preserve">1.05665266513824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06134283542633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07742381095886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07943379878998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06938338279724</t>
+    <t xml:space="preserve">1.06134271621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07742369174957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07943403720856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06938326358795</t>
   </si>
   <si>
     <t xml:space="preserve">1.05933284759521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03856146335602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02683579921722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03588140010834</t>
+    <t xml:space="preserve">1.03856134414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02683591842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03588128089905</t>
   </si>
   <si>
     <t xml:space="preserve">1.04191172122955</t>
@@ -1160,49 +1160,49 @@
     <t xml:space="preserve">0.996349096298218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971222460269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995344042778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944421052932739</t>
+    <t xml:space="preserve">0.971222519874573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99534398317337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944420993328094</t>
   </si>
   <si>
     <t xml:space="preserve">0.953131377696991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941405594348907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959831893444061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9464311003685</t>
+    <t xml:space="preserve">0.941405832767487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959831714630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946431040763855</t>
   </si>
   <si>
     <t xml:space="preserve">0.957821786403656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950451195240021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936380505561829</t>
+    <t xml:space="preserve">0.950451135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936380445957184</t>
   </si>
   <si>
     <t xml:space="preserve">0.967202365398407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99132376909256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975577831268311</t>
+    <t xml:space="preserve">0.991323709487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975577652454376</t>
   </si>
   <si>
     <t xml:space="preserve">0.993333876132965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00003409385681</t>
+    <t xml:space="preserve">1.00003433227539</t>
   </si>
   <si>
     <t xml:space="preserve">1.00137436389923</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">0.991658687591553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00673460960388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999364137649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04023671150208</t>
+    <t xml:space="preserve">1.00673449039459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99936431646347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04023659229279</t>
   </si>
   <si>
     <t xml:space="preserve">1.04157674312592</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">1.04961705207825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04995214939117</t>
+    <t xml:space="preserve">1.04995226860046</t>
   </si>
   <si>
     <t xml:space="preserve">1.06268286705017</t>
@@ -1238,31 +1238,31 @@
     <t xml:space="preserve">1.07206344604492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05832755565643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06335294246674</t>
+    <t xml:space="preserve">1.05832779407501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06335306167603</t>
   </si>
   <si>
     <t xml:space="preserve">1.07407367229462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08043897151947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08546447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09048974514008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09484457969666</t>
+    <t xml:space="preserve">1.08043909072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08546423912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09048962593079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09484493732452</t>
   </si>
   <si>
     <t xml:space="preserve">1.09819507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09852993488312</t>
+    <t xml:space="preserve">1.0985301733017</t>
   </si>
   <si>
     <t xml:space="preserve">1.12198138237</t>
@@ -1271,22 +1271,22 @@
     <t xml:space="preserve">1.11762619018555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11729121208191</t>
+    <t xml:space="preserve">1.1172913312912</t>
   </si>
   <si>
     <t xml:space="preserve">1.10724055767059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10757553577423</t>
+    <t xml:space="preserve">1.10757565498352</t>
   </si>
   <si>
     <t xml:space="preserve">1.12265157699585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13002192974091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10992074012756</t>
+    <t xml:space="preserve">1.13002181053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10992085933685</t>
   </si>
   <si>
     <t xml:space="preserve">1.1182963848114</t>
@@ -1298,52 +1298,52 @@
     <t xml:space="preserve">1.03387129306793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03895270824432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05287516117096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04208528995514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04730618000031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02572667598724</t>
+    <t xml:space="preserve">1.0389529466629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05287528038025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04208540916443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04730629920959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02572679519653</t>
   </si>
   <si>
     <t xml:space="preserve">1.00693154335022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980827271938324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998926222324371</t>
+    <t xml:space="preserve">0.980827391147614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998926162719727</t>
   </si>
   <si>
     <t xml:space="preserve">1.01076018810272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00484311580658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02920722961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00936794281006</t>
+    <t xml:space="preserve">1.00484323501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02920734882355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00936782360077</t>
   </si>
   <si>
     <t xml:space="preserve">1.00658345222473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999622285366058</t>
+    <t xml:space="preserve">0.999622344970703</t>
   </si>
   <si>
     <t xml:space="preserve">0.968993246555328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0159809589386</t>
+    <t xml:space="preserve">1.01598107814789</t>
   </si>
   <si>
     <t xml:space="preserve">1.02398633956909</t>
@@ -1355,28 +1355,28 @@
     <t xml:space="preserve">1.02851116657257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01980984210968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04382574558258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04660999774933</t>
+    <t xml:space="preserve">1.01980972290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04382586479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04661011695862</t>
   </si>
   <si>
     <t xml:space="preserve">1.0236382484436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02537846565247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00588738918304</t>
+    <t xml:space="preserve">1.02537858486176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00588750839233</t>
   </si>
   <si>
     <t xml:space="preserve">1.01250040531158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02120208740234</t>
+    <t xml:space="preserve">1.02120184898376</t>
   </si>
   <si>
     <t xml:space="preserve">1.02642273902893</t>
@@ -1385,13 +1385,13 @@
     <t xml:space="preserve">1.03373193740845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01389265060425</t>
+    <t xml:space="preserve">1.01389276981354</t>
   </si>
   <si>
     <t xml:space="preserve">1.03860473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0511349439621</t>
+    <t xml:space="preserve">1.05113482475281</t>
   </si>
   <si>
     <t xml:space="preserve">1.06122863292694</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">1.06262075901031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05600774288177</t>
+    <t xml:space="preserve">1.05600762367249</t>
   </si>
   <si>
     <t xml:space="preserve">1.07375872135162</t>
@@ -1415,40 +1415,40 @@
     <t xml:space="preserve">1.06714558601379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0786315202713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09290194511414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09429407119751</t>
+    <t xml:space="preserve">1.07863163948059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09290170669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09429395198822</t>
   </si>
   <si>
     <t xml:space="preserve">1.10160326957703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08420038223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04835057258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06157648563385</t>
+    <t xml:space="preserve">1.08420050144196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04835045337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06157672405243</t>
   </si>
   <si>
     <t xml:space="preserve">1.07201826572418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07584702968597</t>
+    <t xml:space="preserve">1.07584714889526</t>
   </si>
   <si>
     <t xml:space="preserve">1.07132232189178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09394609928131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08106780052185</t>
+    <t xml:space="preserve">1.09394598007202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08106791973114</t>
   </si>
   <si>
     <t xml:space="preserve">1.09011745452881</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">1.0824601650238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10299563407898</t>
+    <t xml:space="preserve">1.10299551486969</t>
   </si>
   <si>
     <t xml:space="preserve">1.12005043029785</t>
@@ -1466,13 +1466,13 @@
     <t xml:space="preserve">1.12387907505035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10473573207855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10612797737122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11134910583496</t>
+    <t xml:space="preserve">1.10473585128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10612809658051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11134898662567</t>
   </si>
   <si>
     <t xml:space="preserve">1.10821640491486</t>
@@ -1487,28 +1487,28 @@
     <t xml:space="preserve">1.08802902698517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08942127227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07549905776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06540536880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03338384628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04243338108063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02155005931854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03094744682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04173731803894</t>
+    <t xml:space="preserve">1.08942139148712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07549893856049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06540524959564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03338408470154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04243350028992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02154994010925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03094756603241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04173719882965</t>
   </si>
   <si>
     <t xml:space="preserve">1.05705189704895</t>
@@ -1517,25 +1517,25 @@
     <t xml:space="preserve">1.07897937297821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09220576286316</t>
+    <t xml:space="preserve">1.09220588207245</t>
   </si>
   <si>
     <t xml:space="preserve">1.09116160869598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08454847335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08141589164734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09847068786621</t>
+    <t xml:space="preserve">1.08454835414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08141601085663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09847056865692</t>
   </si>
   <si>
     <t xml:space="preserve">1.09603440761566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07619500160217</t>
+    <t xml:space="preserve">1.07619512081146</t>
   </si>
   <si>
     <t xml:space="preserve">1.07445478439331</t>
@@ -1550,19 +1550,19 @@
     <t xml:space="preserve">1.06923389434814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04069316387177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0319916009903</t>
+    <t xml:space="preserve">1.04069328308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03199172019958</t>
   </si>
   <si>
     <t xml:space="preserve">1.04452168941498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04417383670807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05183100700378</t>
+    <t xml:space="preserve">1.04417359828949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05183112621307</t>
   </si>
   <si>
     <t xml:space="preserve">1.03616833686829</t>
@@ -1571,19 +1571,19 @@
     <t xml:space="preserve">1.05844402313232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03442800045013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00310301780701</t>
+    <t xml:space="preserve">1.03442811965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00310289859772</t>
   </si>
   <si>
     <t xml:space="preserve">0.991617023944855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00832366943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01424086093903</t>
+    <t xml:space="preserve">1.00832390785217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01424074172974</t>
   </si>
   <si>
     <t xml:space="preserve">1.01772129535675</t>
@@ -1592,34 +1592,34 @@
     <t xml:space="preserve">1.01354467868805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993705213069916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988136291503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97734671831131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00553929805756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9860480427742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98952853679657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992313206195831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982915639877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991965174674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01319646835327</t>
+    <t xml:space="preserve">0.99370539188385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988136470317841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977346658706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00553941726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986047923564911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989528715610504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992313265800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98291540145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991965115070343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01319658756256</t>
   </si>
   <si>
     <t xml:space="preserve">1.00414717197418</t>
@@ -1628,52 +1628,52 @@
     <t xml:space="preserve">1.02050590515137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0156329870224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03512418270111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0393009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05252718925476</t>
+    <t xml:space="preserve">1.01563310623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0351243019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03930103778839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05252707004547</t>
   </si>
   <si>
     <t xml:space="preserve">1.05461549758911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03721272945404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02711892127991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03999710083008</t>
+    <t xml:space="preserve">1.03721249103546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0271190404892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0399968624115</t>
   </si>
   <si>
     <t xml:space="preserve">1.06610131263733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06088042259216</t>
+    <t xml:space="preserve">1.06088054180145</t>
   </si>
   <si>
     <t xml:space="preserve">1.04034507274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03233981132507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04278159141541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0434775352478</t>
+    <t xml:space="preserve">1.03233969211578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04278147220612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04347765445709</t>
   </si>
   <si>
     <t xml:space="preserve">1.07410681247711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10090732574463</t>
+    <t xml:space="preserve">1.10090720653534</t>
   </si>
   <si>
     <t xml:space="preserve">1.11761391162872</t>
@@ -1682,25 +1682,25 @@
     <t xml:space="preserve">1.12701153755188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11378526687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1064760684967</t>
+    <t xml:space="preserve">1.11378538608551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10647618770599</t>
   </si>
   <si>
     <t xml:space="preserve">1.12318289279938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13118815422058</t>
+    <t xml:space="preserve">1.13118827342987</t>
   </si>
   <si>
     <t xml:space="preserve">1.11448132991791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08872520923615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.094642162323</t>
+    <t xml:space="preserve">1.08872509002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09464228153229</t>
   </si>
   <si>
     <t xml:space="preserve">1.11622166633606</t>
@@ -1709,13 +1709,13 @@
     <t xml:space="preserve">1.11831021308899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13501691818237</t>
+    <t xml:space="preserve">1.13501667976379</t>
   </si>
   <si>
     <t xml:space="preserve">1.13675725460052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1381493806839</t>
+    <t xml:space="preserve">1.13814926147461</t>
   </si>
   <si>
     <t xml:space="preserve">1.14302206039429</t>
@@ -1727,34 +1727,34 @@
     <t xml:space="preserve">1.10891258716583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09951496124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10195136070251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09916687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0949901342392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10578012466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09185779094696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07793533802032</t>
+    <t xml:space="preserve">1.09951508045197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1019514799118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09916698932648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09499025344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10577988624573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09185767173767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07793521881104</t>
   </si>
   <si>
     <t xml:space="preserve">1.08071982860565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0866367816925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06227266788483</t>
+    <t xml:space="preserve">1.08663690090179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06227290630341</t>
   </si>
   <si>
     <t xml:space="preserve">1.08280825614929</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">1.09742677211761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10021114349365</t>
+    <t xml:space="preserve">1.10021090507507</t>
   </si>
   <si>
     <t xml:space="preserve">1.09777462482452</t>
@@ -1772,19 +1772,19 @@
     <t xml:space="preserve">1.10369169712067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11100101470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10543203353882</t>
+    <t xml:space="preserve">1.11100089550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10543191432953</t>
   </si>
   <si>
     <t xml:space="preserve">1.08594059944153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09568631649017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08907330036163</t>
+    <t xml:space="preserve">1.09568619728088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08907318115234</t>
   </si>
   <si>
     <t xml:space="preserve">1.11726593971252</t>
@@ -1793,28 +1793,28 @@
     <t xml:space="preserve">1.12074649333954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10752010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1103048324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12179064750671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11935448646545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13571310043335</t>
+    <t xml:space="preserve">1.10752022266388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11030471324921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.121790766716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11935424804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13571298122406</t>
   </si>
   <si>
     <t xml:space="preserve">1.13536500930786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13084030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13223242759705</t>
+    <t xml:space="preserve">1.13084006309509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13223230838776</t>
   </si>
   <si>
     <t xml:space="preserve">1.14754688739777</t>
@@ -1823,40 +1823,40 @@
     <t xml:space="preserve">1.06331694126129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05391931533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04626214504242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05426740646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04869842529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02433443069458</t>
+    <t xml:space="preserve">1.05391919612885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04626226425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05426752567291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04869854450226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02433454990387</t>
   </si>
   <si>
     <t xml:space="preserve">1.0194616317749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01632905006409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00379908084869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997882008552551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.007279753685</t>
+    <t xml:space="preserve">1.01632916927338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0037989616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997882127761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00727963447571</t>
   </si>
   <si>
     <t xml:space="preserve">1.02015769481659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07654321193695</t>
+    <t xml:space="preserve">1.07654309272766</t>
   </si>
   <si>
     <t xml:space="preserve">1.08517634868622</t>
@@ -1865,55 +1865,55 @@
     <t xml:space="preserve">1.0972056388855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09647655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06622135639191</t>
+    <t xml:space="preserve">1.09647631645203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06622123718262</t>
   </si>
   <si>
     <t xml:space="preserve">1.08116674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07205367088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06038904190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05127608776093</t>
+    <t xml:space="preserve">1.07205355167389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06038892269135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05127596855164</t>
   </si>
   <si>
     <t xml:space="preserve">1.06403422355652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07168912887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08043777942657</t>
+    <t xml:space="preserve">1.07168924808502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08043766021729</t>
   </si>
   <si>
     <t xml:space="preserve">1.0979346036911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0986635684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10449600219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10048615932465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10230886936188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.095747590065</t>
+    <t xml:space="preserve">1.09866368770599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10449588298798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10048627853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10230875015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09574770927429</t>
   </si>
   <si>
     <t xml:space="preserve">1.09829914569855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13219940662384</t>
+    <t xml:space="preserve">1.13219952583313</t>
   </si>
   <si>
     <t xml:space="preserve">1.12563812732697</t>
@@ -1922,34 +1922,34 @@
     <t xml:space="preserve">1.14021897315979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14750933647156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13584470748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11944139003754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11543142795563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10376703739166</t>
+    <t xml:space="preserve">1.14750921726227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13584458827972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11944127082825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11543130874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10376691818237</t>
   </si>
   <si>
     <t xml:space="preserve">1.11251533031464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11069273948669</t>
+    <t xml:space="preserve">1.11069285869598</t>
   </si>
   <si>
     <t xml:space="preserve">1.13511562347412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1500608921051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15188372135162</t>
+    <t xml:space="preserve">1.15006101131439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15188348293304</t>
   </si>
   <si>
     <t xml:space="preserve">1.147873878479</t>
@@ -1958,40 +1958,40 @@
     <t xml:space="preserve">1.15261268615723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16427743434906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1704740524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17156767845154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17229688167572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17849361896515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17484831809998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19161641597748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16318356990814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16609966754913</t>
+    <t xml:space="preserve">1.16427707672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17047393321991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17156755924225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17229664325714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17849349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17484843730927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19161629676819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16318380832672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16609990596771</t>
   </si>
   <si>
     <t xml:space="preserve">1.17995166778564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18469035625458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1810450553894</t>
+    <t xml:space="preserve">1.18469047546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18104517459869</t>
   </si>
   <si>
     <t xml:space="preserve">1.17120313644409</t>
@@ -2000,16 +2000,16 @@
     <t xml:space="preserve">1.17375481128693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14969635009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15407049655914</t>
+    <t xml:space="preserve">1.14969658851624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15407073497772</t>
   </si>
   <si>
     <t xml:space="preserve">1.17083859443665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16209006309509</t>
+    <t xml:space="preserve">1.16209018230438</t>
   </si>
   <si>
     <t xml:space="preserve">1.16682887077332</t>
@@ -2021,28 +2021,28 @@
     <t xml:space="preserve">1.17010962963104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13183510303497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12417995929718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12782537937164</t>
+    <t xml:space="preserve">1.13183498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12418007850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12782526016235</t>
   </si>
   <si>
     <t xml:space="preserve">1.14277064800262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16099643707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14459323883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15297710895538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13985455036163</t>
+    <t xml:space="preserve">1.16099655628204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14459311962128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15297722816467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13985443115234</t>
   </si>
   <si>
     <t xml:space="preserve">1.13475120067596</t>
@@ -2057,22 +2057,22 @@
     <t xml:space="preserve">1.16573536396027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16500627994537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18833565711975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20473885536194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20036482810974</t>
+    <t xml:space="preserve">1.16500639915466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18833553791046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20473909378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20036470890045</t>
   </si>
   <si>
     <t xml:space="preserve">1.18869996070862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17958724498749</t>
+    <t xml:space="preserve">1.17958700656891</t>
   </si>
   <si>
     <t xml:space="preserve">1.16464185714722</t>
@@ -2081,19 +2081,19 @@
     <t xml:space="preserve">1.17922258377075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18213868141174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17630648612976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19599056243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18979358673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22551655769348</t>
+    <t xml:space="preserve">1.18213880062103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17630636692047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19599044322968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18979370594025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22551667690277</t>
   </si>
   <si>
     <t xml:space="preserve">1.21567463874817</t>
@@ -2114,28 +2114,28 @@
     <t xml:space="preserve">1.23134899139404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23025548458099</t>
+    <t xml:space="preserve">1.2302553653717</t>
   </si>
   <si>
     <t xml:space="preserve">1.21603918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21931993961334</t>
+    <t xml:space="preserve">1.21931982040405</t>
   </si>
   <si>
     <t xml:space="preserve">1.23791038990021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23462963104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22806835174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21640360355377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22187149524689</t>
+    <t xml:space="preserve">1.23462951183319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22806823253632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21640348434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22187161445618</t>
   </si>
   <si>
     <t xml:space="preserve">1.22114229202271</t>
@@ -2162,16 +2162,16 @@
     <t xml:space="preserve">1.27363324165344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27691400051117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31154346466064</t>
+    <t xml:space="preserve">1.27691411972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31154334545135</t>
   </si>
   <si>
     <t xml:space="preserve">1.3133659362793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30972075462341</t>
+    <t xml:space="preserve">1.30972063541412</t>
   </si>
   <si>
     <t xml:space="preserve">1.30826270580292</t>
@@ -2183,13 +2183,13 @@
     <t xml:space="preserve">1.29331755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31518852710724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31445968151093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30862724781036</t>
+    <t xml:space="preserve">1.31518876552582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31445944309235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30862712860107</t>
   </si>
   <si>
     <t xml:space="preserve">1.29732716083527</t>
@@ -2201,67 +2201,67 @@
     <t xml:space="preserve">1.28857862949371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28420436382294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27727842330933</t>
+    <t xml:space="preserve">1.28420448303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27727854251862</t>
   </si>
   <si>
     <t xml:space="preserve">1.27509140968323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26452040672302</t>
+    <t xml:space="preserve">1.26452028751373</t>
   </si>
   <si>
     <t xml:space="preserve">1.24884605407715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24665892124176</t>
+    <t xml:space="preserve">1.24665880203247</t>
   </si>
   <si>
     <t xml:space="preserve">1.25249111652374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24520075321198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24483609199524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19052278995514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19635510444641</t>
+    <t xml:space="preserve">1.24520063400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24483633041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19052267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19635498523712</t>
   </si>
   <si>
     <t xml:space="preserve">1.1985422372818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19343888759613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18068063259125</t>
+    <t xml:space="preserve">1.19343876838684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18068075180054</t>
   </si>
   <si>
     <t xml:space="preserve">1.20218741893768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18906462192535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19270968437195</t>
+    <t xml:space="preserve">1.18906474113464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19270980358124</t>
   </si>
   <si>
     <t xml:space="preserve">1.20656156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20729076862335</t>
+    <t xml:space="preserve">1.20729064941406</t>
   </si>
   <si>
     <t xml:space="preserve">1.22515213489532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24155533313751</t>
+    <t xml:space="preserve">1.2415554523468</t>
   </si>
   <si>
     <t xml:space="preserve">1.23353612422943</t>
@@ -2276,31 +2276,31 @@
     <t xml:space="preserve">1.2083842754364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25504291057587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25066840648651</t>
+    <t xml:space="preserve">1.25504279136658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2506685256958</t>
   </si>
   <si>
     <t xml:space="preserve">1.25941693782806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25650072097778</t>
+    <t xml:space="preserve">1.25650084018707</t>
   </si>
   <si>
     <t xml:space="preserve">1.26852989196777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29987871646881</t>
+    <t xml:space="preserve">1.2998788356781</t>
   </si>
   <si>
     <t xml:space="preserve">1.30315947532654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29368197917938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29222369194031</t>
+    <t xml:space="preserve">1.29368185997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29222393035889</t>
   </si>
   <si>
     <t xml:space="preserve">1.30607557296753</t>
@@ -2315,13 +2315,13 @@
     <t xml:space="preserve">1.33414363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31409513950348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3224790096283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3294050693512</t>
+    <t xml:space="preserve">1.31409502029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32247912883759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32940483093262</t>
   </si>
   <si>
     <t xml:space="preserve">1.34580826759338</t>
@@ -2339,10 +2339,10 @@
     <t xml:space="preserve">1.34398579597473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34143424034119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34945344924927</t>
+    <t xml:space="preserve">1.34143400192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34945333003998</t>
   </si>
   <si>
     <t xml:space="preserve">1.35893106460571</t>
@@ -2357,10 +2357,10 @@
     <t xml:space="preserve">1.36038911342621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34908890724182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26524913311005</t>
+    <t xml:space="preserve">1.34908902645111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26524937152863</t>
   </si>
   <si>
     <t xml:space="preserve">1.25613629817963</t>
@@ -2369,43 +2369,43 @@
     <t xml:space="preserve">1.13766729831696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15589344501495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19708395004272</t>
+    <t xml:space="preserve">1.15589332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19708406925201</t>
   </si>
   <si>
     <t xml:space="preserve">1.11579620838165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996233463287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92478746175766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905467867851257</t>
+    <t xml:space="preserve">0.996233522891998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924787580966949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905467987060547</t>
   </si>
   <si>
     <t xml:space="preserve">0.733049869537354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.772782564163208</t>
+    <t xml:space="preserve">0.772782623767853</t>
   </si>
   <si>
     <t xml:space="preserve">0.750546932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.775334298610687</t>
+    <t xml:space="preserve">0.775334358215332</t>
   </si>
   <si>
     <t xml:space="preserve">0.751275956630707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.754556655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.741433918476105</t>
+    <t xml:space="preserve">0.754556715488434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74143385887146</t>
   </si>
   <si>
     <t xml:space="preserve">0.729040265083313</t>
@@ -2417,22 +2417,22 @@
     <t xml:space="preserve">0.79720550775528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.793195784091949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778250396251678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824544608592987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826002597808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816160500049591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841676890850067</t>
+    <t xml:space="preserve">0.793195843696594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778250455856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824544548988342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826002538204193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816160619258881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841676950454712</t>
   </si>
   <si>
     <t xml:space="preserve">0.836209118366241</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">0.869744956493378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855164229869843</t>
+    <t xml:space="preserve">0.855164170265198</t>
   </si>
   <si>
     <t xml:space="preserve">0.876670956611633</t>
@@ -2453,19 +2453,19 @@
     <t xml:space="preserve">0.889429211616516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.885783910751343</t>
+    <t xml:space="preserve">0.885783970355988</t>
   </si>
   <si>
     <t xml:space="preserve">0.897448480129242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910935699939728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91166490316391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.883961319923401</t>
+    <t xml:space="preserve">0.910935759544373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911664843559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883961260318756</t>
   </si>
   <si>
     <t xml:space="preserve">0.888335585594177</t>
@@ -2483,109 +2483,109 @@
     <t xml:space="preserve">0.901458382606506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89963561296463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905832529067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872296571731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879951536655426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878129065036774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882138788700104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877764523029327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914580941200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93426513671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911300241947174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944332420825958</t>
+    <t xml:space="preserve">0.899635672569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905832469463348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872296750545502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879951596260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878128945827484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882138729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877764463424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914580881595612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93426501750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911300301551819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944332599639893</t>
   </si>
   <si>
     <t xml:space="preserve">0.902750730514526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.914020657539368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910523056983948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912854850292206</t>
+    <t xml:space="preserve">0.914020597934723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910522937774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912854731082916</t>
   </si>
   <si>
     <t xml:space="preserve">0.946275472640991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971146881580353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950550377368927</t>
+    <t xml:space="preserve">0.971146941184998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950550317764282</t>
   </si>
   <si>
     <t xml:space="preserve">0.971535444259644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969592392444611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981639385223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00573360919952</t>
+    <t xml:space="preserve">0.969592273235321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981639444828033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00573348999023</t>
   </si>
   <si>
     <t xml:space="preserve">1.04265189170837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04342913627625</t>
+    <t xml:space="preserve">1.04342901706696</t>
   </si>
   <si>
     <t xml:space="preserve">1.03060483932495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05236721038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02710723876953</t>
+    <t xml:space="preserve">1.05236732959747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02710711956024</t>
   </si>
   <si>
     <t xml:space="preserve">1.0119514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960265576839447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956379473209381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978141844272614</t>
+    <t xml:space="preserve">0.960265636444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956379592418671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978141903877258</t>
   </si>
   <si>
     <t xml:space="preserve">1.01156270503998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01778066158295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0096195936203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0193350315094</t>
+    <t xml:space="preserve">1.01778054237366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00961971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01933515071869</t>
   </si>
   <si>
     <t xml:space="preserve">1.01467168331146</t>
@@ -2597,37 +2597,37 @@
     <t xml:space="preserve">0.963763177394867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977364599704742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979696452617645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984359800815582</t>
+    <t xml:space="preserve">0.977364659309387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979696393013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984359622001648</t>
   </si>
   <si>
     <t xml:space="preserve">0.999904274940491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996795475482941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993686437606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983194053173065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982805371284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958322525024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961431443691254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960654258728027</t>
+    <t xml:space="preserve">0.996795415878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993686556816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983193933963776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982805252075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958322584629059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961431503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960654318332672</t>
   </si>
   <si>
     <t xml:space="preserve">0.973867118358612</t>
@@ -2636,40 +2636,40 @@
     <t xml:space="preserve">0.973089933395386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985136985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987857341766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985525608062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949773073196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954436480998993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970758318901062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92878794670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943166613578796</t>
+    <t xml:space="preserve">0.985137045383453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987857282161713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985525488853455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949772953987122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954436421394348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970758140087128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928788006305695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943166732788086</t>
   </si>
   <si>
     <t xml:space="preserve">0.95599091053009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959877073764801</t>
+    <t xml:space="preserve">0.959877014160156</t>
   </si>
   <si>
     <t xml:space="preserve">0.953659236431122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965317606925964</t>
+    <t xml:space="preserve">0.96531754732132</t>
   </si>
   <si>
     <t xml:space="preserve">0.982028067111969</t>
@@ -2678,64 +2678,64 @@
     <t xml:space="preserve">1.01739192008972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00612199306488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994852304458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979307770729065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989411771297455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987079918384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964929044246674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96259731054306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958711326122284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96609491109848</t>
+    <t xml:space="preserve">1.00612223148346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994852244853973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97930771112442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98941171169281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987080097198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964929163455963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962597370147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958711266517639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966094851493835</t>
   </si>
   <si>
     <t xml:space="preserve">0.951327502727509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954047858715057</t>
+    <t xml:space="preserve">0.954047739505768</t>
   </si>
   <si>
     <t xml:space="preserve">0.975032985210419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968037843704224</t>
+    <t xml:space="preserve">0.968038022518158</t>
   </si>
   <si>
     <t xml:space="preserve">0.937726020812988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946664094924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938503384590149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942000925540924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933451235294342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971924066543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948995769023895</t>
+    <t xml:space="preserve">0.946664214134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938503205776215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94200074672699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933451294898987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971924126148224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948995888233185</t>
   </si>
   <si>
     <t xml:space="preserve">0.953270554542542</t>
@@ -2744,10 +2744,10 @@
     <t xml:space="preserve">0.9458869099617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929565131664276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931119501590729</t>
+    <t xml:space="preserve">0.929565191268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931119620800018</t>
   </si>
   <si>
     <t xml:space="preserve">0.900807797908783</t>
@@ -2756,49 +2756,49 @@
     <t xml:space="preserve">0.903528034687042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904693782329559</t>
+    <t xml:space="preserve">0.904693961143494</t>
   </si>
   <si>
     <t xml:space="preserve">0.89886462688446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878656685352325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886428833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901584804058075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886040270328522</t>
+    <t xml:space="preserve">0.878656625747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886428952217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901584982872009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886040389537811</t>
   </si>
   <si>
     <t xml:space="preserve">0.840961158275604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830079913139343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848344743251801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860780298709869</t>
+    <t xml:space="preserve">0.830079853534698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84834486246109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860780417919159</t>
   </si>
   <si>
     <t xml:space="preserve">0.872050225734711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89847594499588</t>
+    <t xml:space="preserve">0.898476004600525</t>
   </si>
   <si>
     <t xml:space="preserve">0.892646729946136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.88137686252594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942778050899506</t>
+    <t xml:space="preserve">0.881376922130585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942777991294861</t>
   </si>
   <si>
     <t xml:space="preserve">0.939280450344086</t>
@@ -2810,58 +2810,58 @@
     <t xml:space="preserve">0.952493369579315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947441399097443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952104866504669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95948851108551</t>
+    <t xml:space="preserve">0.947441339492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952104806900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959488570690155</t>
   </si>
   <si>
     <t xml:space="preserve">0.976198971271515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01700353622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02205526828766</t>
+    <t xml:space="preserve">1.01700329780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02205538749695</t>
   </si>
   <si>
     <t xml:space="preserve">0.993297874927521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982416689395905</t>
+    <t xml:space="preserve">0.98241662979126</t>
   </si>
   <si>
     <t xml:space="preserve">0.975421667098999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.976587533950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997184038162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990966141223907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988245904445648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984748303890228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995629608631134</t>
+    <t xml:space="preserve">0.97658759355545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997183978557587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990966200828552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988245964050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984748423099518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995629668235779</t>
   </si>
   <si>
     <t xml:space="preserve">0.954825043678284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00651061534882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01583755016327</t>
+    <t xml:space="preserve">1.00651073455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01583743095398</t>
   </si>
   <si>
     <t xml:space="preserve">1.0138943195343</t>
@@ -2870,25 +2870,25 @@
     <t xml:space="preserve">1.03449094295502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02399849891663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04148614406586</t>
+    <t xml:space="preserve">1.02399837970734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04148602485657</t>
   </si>
   <si>
     <t xml:space="preserve">1.03954291343689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03487968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01428306102753</t>
+    <t xml:space="preserve">1.03487956523895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01428294181824</t>
   </si>
   <si>
     <t xml:space="preserve">1.0375999212265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03215909004211</t>
+    <t xml:space="preserve">1.03215932846069</t>
   </si>
   <si>
     <t xml:space="preserve">1.02050089836121</t>
@@ -2897,28 +2897,28 @@
     <t xml:space="preserve">1.03099346160889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06596875190735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0729638338089</t>
+    <t xml:space="preserve">1.06596863269806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07296371459961</t>
   </si>
   <si>
     <t xml:space="preserve">1.04653799533844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05897355079651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05353307723999</t>
+    <t xml:space="preserve">1.0589736700058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0535329580307</t>
   </si>
   <si>
     <t xml:space="preserve">1.06169402599335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04498362541199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10871636867523</t>
+    <t xml:space="preserve">1.0449835062027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10871613025665</t>
   </si>
   <si>
     <t xml:space="preserve">1.13630783557892</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">1.12853562831879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1382509469986</t>
+    <t xml:space="preserve">1.13825082778931</t>
   </si>
   <si>
     <t xml:space="preserve">1.14252579212189</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">1.17516922950745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16195631027222</t>
+    <t xml:space="preserve">1.16195642948151</t>
   </si>
   <si>
     <t xml:space="preserve">1.13863956928253</t>
@@ -2948,19 +2948,19 @@
     <t xml:space="preserve">1.12154054641724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13475346565247</t>
+    <t xml:space="preserve">1.13475358486176</t>
   </si>
   <si>
     <t xml:space="preserve">1.12698125839233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11415684223175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10366415977478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11221396923065</t>
+    <t xml:space="preserve">1.11415696144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10366439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11221385002136</t>
   </si>
   <si>
     <t xml:space="preserve">1.09317171573639</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">1.0838451385498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11493408679962</t>
+    <t xml:space="preserve">1.11493420600891</t>
   </si>
   <si>
     <t xml:space="preserve">1.1071617603302</t>
@@ -2981,16 +2981,16 @@
     <t xml:space="preserve">1.08656537532806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07723867893219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1083277463913</t>
+    <t xml:space="preserve">1.0772385597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10832762718201</t>
   </si>
   <si>
     <t xml:space="preserve">1.1308673620224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15262985229492</t>
+    <t xml:space="preserve">1.15262961387634</t>
   </si>
   <si>
     <t xml:space="preserve">1.14874362945557</t>
@@ -2999,37 +2999,37 @@
     <t xml:space="preserve">1.15496146678925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16312217712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14563465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15301835536957</t>
+    <t xml:space="preserve">1.1631224155426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14563453197479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15301847457886</t>
   </si>
   <si>
     <t xml:space="preserve">1.14641189575195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17089450359344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18954813480377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20470380783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20664703845978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21558511257172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21752834320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20625865459442</t>
+    <t xml:space="preserve">1.17089462280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18954801559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2047039270401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20664715766907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21558523178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2175281047821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20625841617584</t>
   </si>
   <si>
     <t xml:space="preserve">1.20392680168152</t>
@@ -3044,25 +3044,25 @@
     <t xml:space="preserve">1.20975601673126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19809746742249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21286499500275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21597385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21325349807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20431542396545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21247637271881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22685492038727</t>
+    <t xml:space="preserve">1.19809758663177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21286487579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21597373485565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2132533788681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20431530475616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21247625350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22685515880585</t>
   </si>
   <si>
     <t xml:space="preserve">1.21403086185455</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">1.23851346969604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24278807640076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26105296611786</t>
+    <t xml:space="preserve">1.24278831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26105308532715</t>
   </si>
   <si>
     <t xml:space="preserve">1.26455056667328</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">1.27582049369812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26066434383392</t>
+    <t xml:space="preserve">1.26066446304321</t>
   </si>
   <si>
     <t xml:space="preserve">1.26493918895721</t>
@@ -3098,22 +3098,22 @@
     <t xml:space="preserve">1.27892923355103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30457782745361</t>
+    <t xml:space="preserve">1.3045779466629</t>
   </si>
   <si>
     <t xml:space="preserve">1.31779074668884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29291927814484</t>
+    <t xml:space="preserve">1.29291939735413</t>
   </si>
   <si>
     <t xml:space="preserve">1.29874861240387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31740212440491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33061504364014</t>
+    <t xml:space="preserve">1.3174022436142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33061492443085</t>
   </si>
   <si>
     <t xml:space="preserve">1.34693682193756</t>
@@ -3122,22 +3122,22 @@
     <t xml:space="preserve">1.34382784366608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34849119186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35121154785156</t>
+    <t xml:space="preserve">1.3484913110733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35121142864227</t>
   </si>
   <si>
     <t xml:space="preserve">1.37258529663086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40067195892334</t>
+    <t xml:space="preserve">1.40067207813263</t>
   </si>
   <si>
     <t xml:space="preserve">1.37502765655518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38194763660431</t>
+    <t xml:space="preserve">1.38194751739502</t>
   </si>
   <si>
     <t xml:space="preserve">1.37787699699402</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">1.391716837883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38438987731934</t>
+    <t xml:space="preserve">1.38438999652863</t>
   </si>
   <si>
     <t xml:space="preserve">1.39456629753113</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">1.38886749744415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41044139862061</t>
+    <t xml:space="preserve">1.41044127941132</t>
   </si>
   <si>
     <t xml:space="preserve">1.42306005954742</t>
@@ -3167,13 +3167,13 @@
     <t xml:space="preserve">1.43323636054993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45847380161285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43852818012238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43771398067474</t>
+    <t xml:space="preserve">1.45847368240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43852806091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43771409988403</t>
   </si>
   <si>
     <t xml:space="preserve">1.44911134243011</t>
@@ -3182,31 +3182,31 @@
     <t xml:space="preserve">1.44951856136322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45725250244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45765960216522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45521724224091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43120110034943</t>
+    <t xml:space="preserve">1.45725238323212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45765972137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4552173614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43120098114014</t>
   </si>
   <si>
     <t xml:space="preserve">1.4430056810379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44422698020935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42713046073914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41858243942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40352141857147</t>
+    <t xml:space="preserve">1.44422686100006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42713057994843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41858232021332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40352129936218</t>
   </si>
   <si>
     <t xml:space="preserve">1.41288363933563</t>
@@ -3218,43 +3218,43 @@
     <t xml:space="preserve">1.41898941993713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41329061985016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43527162075043</t>
+    <t xml:space="preserve">1.41329073905945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43527150154114</t>
   </si>
   <si>
     <t xml:space="preserve">1.37950527667999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38072633743286</t>
+    <t xml:space="preserve">1.38072645664215</t>
   </si>
   <si>
     <t xml:space="preserve">1.39945089817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41736137866974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.403928399086</t>
+    <t xml:space="preserve">1.41736125946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40392851829529</t>
   </si>
   <si>
     <t xml:space="preserve">1.40148615837097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34734797477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3591525554657</t>
+    <t xml:space="preserve">1.34734809398651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35915267467499</t>
   </si>
   <si>
     <t xml:space="preserve">1.38316881656647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39578747749329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45114684104919</t>
+    <t xml:space="preserve">1.395787358284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4511467218399</t>
   </si>
   <si>
     <t xml:space="preserve">1.47719812393188</t>
@@ -3263,19 +3263,19 @@
     <t xml:space="preserve">1.47801232337952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47394180297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47068524360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47923338413239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46824300289154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4796404838562</t>
+    <t xml:space="preserve">1.47394168376923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47068536281586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47923350334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46824288368225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47964060306549</t>
   </si>
   <si>
     <t xml:space="preserve">1.49348032474518</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">1.50691306591034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52360236644745</t>
+    <t xml:space="preserve">1.52360224723816</t>
   </si>
   <si>
     <t xml:space="preserve">1.53866314888</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">1.56593585014343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5838463306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5549453496933</t>
+    <t xml:space="preserve">1.58384644985199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55494546890259</t>
   </si>
   <si>
     <t xml:space="preserve">1.53215038776398</t>
@@ -3320,10 +3320,10 @@
     <t xml:space="preserve">1.52889406681061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52197408676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51424014568329</t>
+    <t xml:space="preserve">1.52197396755219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.514240026474</t>
   </si>
   <si>
     <t xml:space="preserve">1.51912474632263</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">1.49755072593689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.522381067276</t>
+    <t xml:space="preserve">1.52238118648529</t>
   </si>
   <si>
     <t xml:space="preserve">1.49307322502136</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">1.51464700698853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5162752866745</t>
+    <t xml:space="preserve">1.51627540588379</t>
   </si>
   <si>
     <t xml:space="preserve">1.48615336418152</t>
@@ -3356,16 +3356,16 @@
     <t xml:space="preserve">1.49063098430634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42794466018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45155394077301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46173000335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46213722229004</t>
+    <t xml:space="preserve">1.42794454097748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45155382156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46173012256622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46213710308075</t>
   </si>
   <si>
     <t xml:space="preserve">1.4837110042572</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">1.48411810398102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45643830299377</t>
+    <t xml:space="preserve">1.45643842220306</t>
   </si>
   <si>
     <t xml:space="preserve">1.45562422275543</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">1.43812096118927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44544792175293</t>
+    <t xml:space="preserve">1.44544804096222</t>
   </si>
   <si>
     <t xml:space="preserve">1.44015622138977</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">1.5040637254715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46417248249054</t>
+    <t xml:space="preserve">1.46417236328125</t>
   </si>
   <si>
     <t xml:space="preserve">1.4450409412384</t>
@@ -3419,10 +3419,10 @@
     <t xml:space="preserve">1.50894844532013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.502028465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48696744441986</t>
+    <t xml:space="preserve">1.50202834606171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48696756362915</t>
   </si>
   <si>
     <t xml:space="preserve">1.50365662574768</t>
@@ -3434,13 +3434,13 @@
     <t xml:space="preserve">1.53662800788879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57407689094543</t>
+    <t xml:space="preserve">1.57407701015472</t>
   </si>
   <si>
     <t xml:space="preserve">1.55698072910309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55779469013214</t>
+    <t xml:space="preserve">1.55779480934143</t>
   </si>
   <si>
     <t xml:space="preserve">1.50732016563416</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">1.49022388458252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49225902557373</t>
+    <t xml:space="preserve">1.49225914478302</t>
   </si>
   <si>
     <t xml:space="preserve">1.510169506073</t>
@@ -3467,28 +3467,28 @@
     <t xml:space="preserve">1.50121426582336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51301884651184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51953184604645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51546120643616</t>
+    <t xml:space="preserve">1.51301896572113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51953172683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51546132564545</t>
   </si>
   <si>
     <t xml:space="preserve">1.3921240568161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4059636592865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39538025856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40637075901031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45196068286896</t>
+    <t xml:space="preserve">1.40596377849579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39538037776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40637063980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45196080207825</t>
   </si>
   <si>
     <t xml:space="preserve">1.43079400062561</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">1.45440304279327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45399618148804</t>
+    <t xml:space="preserve">1.45399606227875</t>
   </si>
   <si>
     <t xml:space="preserve">1.42835175991058</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">1.39130985736847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37258541584015</t>
+    <t xml:space="preserve">1.37258517742157</t>
   </si>
   <si>
     <t xml:space="preserve">1.32699525356293</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">1.34531283378601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34775507450104</t>
+    <t xml:space="preserve">1.34775495529175</t>
   </si>
   <si>
     <t xml:space="preserve">1.36810779571533</t>
@@ -3527,16 +3527,16 @@
     <t xml:space="preserve">1.37177121639252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39741575717926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40026497840881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40677797794342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35548901557922</t>
+    <t xml:space="preserve">1.39741551876068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4002650976181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40677785873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35548913478851</t>
   </si>
   <si>
     <t xml:space="preserve">1.35955965518951</t>
@@ -3551,10 +3551,10 @@
     <t xml:space="preserve">1.36770057678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35589611530304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35263979434967</t>
+    <t xml:space="preserve">1.35589599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35263967514038</t>
   </si>
   <si>
     <t xml:space="preserve">1.33310115337372</t>
@@ -3569,52 +3569,52 @@
     <t xml:space="preserve">1.34164929389954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30664265155792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33269417285919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36525845527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41532599925995</t>
+    <t xml:space="preserve">1.30664253234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3326940536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3652583360672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41532588005066</t>
   </si>
   <si>
     <t xml:space="preserve">1.37380647659302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3672935962677</t>
+    <t xml:space="preserve">1.36729371547699</t>
   </si>
   <si>
     <t xml:space="preserve">1.37909817695618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37624883651733</t>
+    <t xml:space="preserve">1.37624895572662</t>
   </si>
   <si>
     <t xml:space="preserve">1.36973583698273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33513641357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30949211120605</t>
+    <t xml:space="preserve">1.33513629436493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30949199199677</t>
   </si>
   <si>
     <t xml:space="preserve">1.28262650966644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30094397068024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30542147159576</t>
+    <t xml:space="preserve">1.30094408988953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30542159080505</t>
   </si>
   <si>
     <t xml:space="preserve">1.29036045074463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26430892944336</t>
+    <t xml:space="preserve">1.26430916786194</t>
   </si>
   <si>
     <t xml:space="preserve">1.28913938999176</t>
@@ -3635,19 +3635,19 @@
     <t xml:space="preserve">1.22889542579651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25046932697296</t>
+    <t xml:space="preserve">1.25046920776367</t>
   </si>
   <si>
     <t xml:space="preserve">1.22482478618622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28140532970428</t>
+    <t xml:space="preserve">1.281405210495</t>
   </si>
   <si>
     <t xml:space="preserve">1.3001297712326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2549467086792</t>
+    <t xml:space="preserve">1.25494682788849</t>
   </si>
   <si>
     <t xml:space="preserve">1.22848832607269</t>
@@ -3665,22 +3665,22 @@
     <t xml:space="preserve">1.25616800785065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24639856815338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24477052688599</t>
+    <t xml:space="preserve">1.24639868736267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2447704076767</t>
   </si>
   <si>
     <t xml:space="preserve">1.23093056678772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22238254547119</t>
+    <t xml:space="preserve">1.22238266468048</t>
   </si>
   <si>
     <t xml:space="preserve">1.22116136550903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21464836597443</t>
+    <t xml:space="preserve">1.21464848518372</t>
   </si>
   <si>
     <t xml:space="preserve">1.23785054683685</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">1.2508761882782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22563886642456</t>
+    <t xml:space="preserve">1.22563898563385</t>
   </si>
   <si>
     <t xml:space="preserve">1.22808110713959</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">1.25698208808899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27489233016968</t>
+    <t xml:space="preserve">1.27489244937897</t>
   </si>
   <si>
     <t xml:space="preserve">1.25779616832733</t>
@@ -3713,13 +3713,13 @@
     <t xml:space="preserve">1.25942444801331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2875109910965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29768741130829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29809439182281</t>
+    <t xml:space="preserve">1.28751111030579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29768753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2980945110321</t>
   </si>
   <si>
     <t xml:space="preserve">1.33554339408875</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">1.3571172952652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34856903553009</t>
+    <t xml:space="preserve">1.34856915473938</t>
   </si>
   <si>
     <t xml:space="preserve">1.34409153461456</t>
@@ -3752,16 +3752,16 @@
     <t xml:space="preserve">1.3245530128479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33432221412659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33106589317322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34002113342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32862341403961</t>
+    <t xml:space="preserve">1.33432233333588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33106577396393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34002101421356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3286235332489</t>
   </si>
   <si>
     <t xml:space="preserve">1.31193447113037</t>
@@ -3770,16 +3770,16 @@
     <t xml:space="preserve">1.3164119720459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35019731521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34653389453888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34327733516693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38561117649078</t>
+    <t xml:space="preserve">1.35019743442535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34653401374817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34327745437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38561105728149</t>
   </si>
   <si>
     <t xml:space="preserve">1.33147287368774</t>
@@ -3788,16 +3788,16 @@
     <t xml:space="preserve">1.36037373542786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34205639362335</t>
+    <t xml:space="preserve">1.34205627441406</t>
   </si>
   <si>
     <t xml:space="preserve">1.40272545814514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36872255802155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37862205505371</t>
+    <t xml:space="preserve">1.36872267723083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.378622174263</t>
   </si>
   <si>
     <t xml:space="preserve">1.38507843017578</t>
@@ -3806,16 +3806,16 @@
     <t xml:space="preserve">1.3631272315979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35796213150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34504961967468</t>
+    <t xml:space="preserve">1.35796201229095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34504973888397</t>
   </si>
   <si>
     <t xml:space="preserve">1.32998502254486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31578135490417</t>
+    <t xml:space="preserve">1.31578147411346</t>
   </si>
   <si>
     <t xml:space="preserve">1.30416023731232</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">1.31233811378479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.270587682724</t>
+    <t xml:space="preserve">1.27058780193329</t>
   </si>
   <si>
     <t xml:space="preserve">1.18708693981171</t>
@@ -3848,13 +3848,13 @@
     <t xml:space="preserve">1.11563801765442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15437543392181</t>
+    <t xml:space="preserve">1.15437531471252</t>
   </si>
   <si>
     <t xml:space="preserve">1.091104388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06570971012115</t>
+    <t xml:space="preserve">1.06570982933044</t>
   </si>
   <si>
     <t xml:space="preserve">1.03945434093475</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">1.10143423080444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08593928813934</t>
+    <t xml:space="preserve">1.08593940734863</t>
   </si>
   <si>
     <t xml:space="preserve">1.09540855884552</t>
@@ -3875,13 +3875,13 @@
     <t xml:space="preserve">1.07517886161804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.043328166008</t>
+    <t xml:space="preserve">1.04332804679871</t>
   </si>
   <si>
     <t xml:space="preserve">1.06743144989014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06614017486572</t>
+    <t xml:space="preserve">1.06614005565643</t>
   </si>
   <si>
     <t xml:space="preserve">1.04677140712738</t>
@@ -3893,13 +3893,13 @@
     <t xml:space="preserve">1.07130515575409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06915307044983</t>
+    <t xml:space="preserve">1.06915318965912</t>
   </si>
   <si>
     <t xml:space="preserve">1.02697229385376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00200819969177</t>
+    <t xml:space="preserve">1.00200831890106</t>
   </si>
   <si>
     <t xml:space="preserve">1.02352905273438</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">1.03601109981537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04074561595917</t>
+    <t xml:space="preserve">1.04074573516846</t>
   </si>
   <si>
     <t xml:space="preserve">1.05451893806458</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">1.03816306591034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02955496311188</t>
+    <t xml:space="preserve">1.02955484390259</t>
   </si>
   <si>
     <t xml:space="preserve">1.0588231086731</t>
@@ -3932,13 +3932,13 @@
     <t xml:space="preserve">1.04203689098358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04978442192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07474863529205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09024345874786</t>
+    <t xml:space="preserve">1.04978430271149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07474851608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09024333953857</t>
   </si>
   <si>
     <t xml:space="preserve">1.06829226016998</t>
@@ -3968,13 +3968,13 @@
     <t xml:space="preserve">1.08292639255524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06097519397736</t>
+    <t xml:space="preserve">1.06097507476807</t>
   </si>
   <si>
     <t xml:space="preserve">1.06355774402618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05839264392853</t>
+    <t xml:space="preserve">1.05839276313782</t>
   </si>
   <si>
     <t xml:space="preserve">1.0170726776123</t>
@@ -3989,22 +3989,22 @@
     <t xml:space="preserve">0.963701188564301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946914970874786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968435764312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945623755455017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932711243629456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939167499542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.920229196548462</t>
+    <t xml:space="preserve">0.946915030479431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968435883522034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945623695850372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932711362838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939167380332947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.920229136943817</t>
   </si>
   <si>
     <t xml:space="preserve">0.965422809123993</t>
@@ -4016,19 +4016,19 @@
     <t xml:space="preserve">0.952510416507721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.926254987716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930128753185272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913342595100403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92195075750351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923242092132568</t>
+    <t xml:space="preserve">0.92625504732132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930128812789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913342535495758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921950817108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923242151737213</t>
   </si>
   <si>
     <t xml:space="preserve">0.912051260471344</t>
@@ -4040,7 +4040,7 @@
     <t xml:space="preserve">0.888808906078339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852567851543427</t>
+    <t xml:space="preserve">0.852567791938782</t>
   </si>
   <si>
     <t xml:space="preserve">0.86298394203186</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">0.85377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860659658908844</t>
+    <t xml:space="preserve">0.860659599304199</t>
   </si>
   <si>
     <t xml:space="preserve">0.879339694976807</t>
@@ -4058,16 +4058,16 @@
     <t xml:space="preserve">0.903442978858948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868579268455505</t>
+    <t xml:space="preserve">0.868579208850861</t>
   </si>
   <si>
     <t xml:space="preserve">0.853256464004517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8353511095047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846541941165924</t>
+    <t xml:space="preserve">0.835351169109344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846542000770569</t>
   </si>
   <si>
     <t xml:space="preserve">0.837244987487793</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">0.863844692707062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.883643805980682</t>
+    <t xml:space="preserve">0.883643865585327</t>
   </si>
   <si>
     <t xml:space="preserve">0.879770040512085</t>
@@ -4121,16 +4121,16 @@
     <t xml:space="preserve">0.972309589385986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993830382823944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00459086894989</t>
+    <t xml:space="preserve">0.993830263614655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0045907497406</t>
   </si>
   <si>
     <t xml:space="preserve">1.01061654090881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11176419258118</t>
+    <t xml:space="preserve">1.11176431179047</t>
   </si>
   <si>
     <t xml:space="preserve">1.11606848239899</t>
@@ -4160,13 +4160,13 @@
     <t xml:space="preserve">1.13974130153656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11865091323853</t>
+    <t xml:space="preserve">1.11865079402924</t>
   </si>
   <si>
     <t xml:space="preserve">1.09928226470947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11090338230133</t>
+    <t xml:space="preserve">1.11090350151062</t>
   </si>
   <si>
     <t xml:space="preserve">1.12898087501526</t>
@@ -4175,19 +4175,19 @@
     <t xml:space="preserve">1.13586747646332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13027215003967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13543713092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12381601333618</t>
+    <t xml:space="preserve">1.13027203083038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13543701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12381589412689</t>
   </si>
   <si>
     <t xml:space="preserve">1.11951184272766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12166380882263</t>
+    <t xml:space="preserve">1.12166392803192</t>
   </si>
   <si>
     <t xml:space="preserve">1.1298416852951</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">1.11692929267883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0928258895874</t>
+    <t xml:space="preserve">1.09282600879669</t>
   </si>
   <si>
     <t xml:space="preserve">1.07603979110718</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">1.06958341598511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07173550128937</t>
+    <t xml:space="preserve">1.07173562049866</t>
   </si>
   <si>
     <t xml:space="preserve">1.09971261024475</t>
@@ -4226,13 +4226,13 @@
     <t xml:space="preserve">1.13888049125671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14705836772919</t>
+    <t xml:space="preserve">1.1470582485199</t>
   </si>
   <si>
     <t xml:space="preserve">1.18837821483612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19354343414307</t>
+    <t xml:space="preserve">1.19354331493378</t>
   </si>
   <si>
     <t xml:space="preserve">1.19827783107758</t>
@@ -4244,7 +4244,7 @@
     <t xml:space="preserve">1.20516443252563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21032965183258</t>
+    <t xml:space="preserve">1.21032953262329</t>
   </si>
   <si>
     <t xml:space="preserve">1.17245292663574</t>
@@ -4256,10 +4256,10 @@
     <t xml:space="preserve">1.18192207813263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19096076488495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20387327671051</t>
+    <t xml:space="preserve">1.19096088409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20387315750122</t>
   </si>
   <si>
     <t xml:space="preserve">1.20430374145508</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">1.18665659427643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20989918708801</t>
+    <t xml:space="preserve">1.20989906787872</t>
   </si>
   <si>
     <t xml:space="preserve">1.18794786930084</t>
@@ -4286,7 +4286,7 @@
     <t xml:space="preserve">1.21506404876709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20903825759888</t>
+    <t xml:space="preserve">1.20903813838959</t>
   </si>
   <si>
     <t xml:space="preserve">1.17632663249969</t>
@@ -4301,10 +4301,10 @@
     <t xml:space="preserve">1.18235242366791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19225203990936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17976987361908</t>
+    <t xml:space="preserve">1.19225192070007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17976999282837</t>
   </si>
   <si>
     <t xml:space="preserve">1.18579590320587</t>
@@ -4313,10 +4313,10 @@
     <t xml:space="preserve">1.18966960906982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20215153694153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20129060745239</t>
+    <t xml:space="preserve">1.20215165615082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20129072666168</t>
   </si>
   <si>
     <t xml:space="preserve">1.16943991184235</t>
@@ -4340,19 +4340,19 @@
     <t xml:space="preserve">1.16814875602722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15738832950592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18278288841248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18321323394775</t>
+    <t xml:space="preserve">1.15738844871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18278276920319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18321335315704</t>
   </si>
   <si>
     <t xml:space="preserve">1.25078856945038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26240992546082</t>
+    <t xml:space="preserve">1.26240980625153</t>
   </si>
   <si>
     <t xml:space="preserve">1.23658490180969</t>
@@ -4376,7 +4376,7 @@
     <t xml:space="preserve">1.25121903419495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26542270183563</t>
+    <t xml:space="preserve">1.26542282104492</t>
   </si>
   <si>
     <t xml:space="preserve">1.25853610038757</t>
@@ -4397,7 +4397,7 @@
     <t xml:space="preserve">1.33730220794678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31664216518402</t>
+    <t xml:space="preserve">1.31664228439331</t>
   </si>
   <si>
     <t xml:space="preserve">1.32137680053711</t>
@@ -4406,13 +4406,13 @@
     <t xml:space="preserve">1.31922471523285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35150599479675</t>
+    <t xml:space="preserve">1.35150611400604</t>
   </si>
   <si>
     <t xml:space="preserve">1.33988475799561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35279715061188</t>
+    <t xml:space="preserve">1.35279703140259</t>
   </si>
   <si>
     <t xml:space="preserve">1.35968375205994</t>
@@ -4427,13 +4427,13 @@
     <t xml:space="preserve">1.37733089923859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34332811832428</t>
+    <t xml:space="preserve">1.34332799911499</t>
   </si>
   <si>
     <t xml:space="preserve">1.3678617477417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36829209327698</t>
+    <t xml:space="preserve">1.36829221248627</t>
   </si>
   <si>
     <t xml:space="preserve">1.3880912065506</t>
@@ -4445,22 +4445,22 @@
     <t xml:space="preserve">1.39885175228119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4126250743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43113279342651</t>
+    <t xml:space="preserve">1.41262495517731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4311329126358</t>
   </si>
   <si>
     <t xml:space="preserve">1.4560968875885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46728777885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44877982139587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43758916854858</t>
+    <t xml:space="preserve">1.46728765964508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44877994060516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43758904933929</t>
   </si>
   <si>
     <t xml:space="preserve">1.37905251979828</t>
@@ -5973,6 +5973,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.70799994468689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71199989318848</t>
   </si>
 </sst>
 </file>
@@ -71363,7 +71366,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.691099537</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>27546302</v>
@@ -71384,6 +71387,32 @@
         <v>1986</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6912847222</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>10615422</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>2.72900009155273</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>2.69199991226196</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>2.71199989318848</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1987</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="1988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="1989">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,52 +44,52 @@
     <t xml:space="preserve">A2A.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774303913116455</t>
+    <t xml:space="preserve">0.7743039727211</t>
   </si>
   <si>
     <t xml:space="preserve">0.769300401210785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.777431190013885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772427558898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775554776191711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736151576042175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728020906448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.708631992340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701126575469971</t>
+    <t xml:space="preserve">0.777431130409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772427618503571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775554895401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736151695251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728020846843719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.708631932735443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701126635074615</t>
   </si>
   <si>
     <t xml:space="preserve">0.678610503673553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.686115801334381</t>
+    <t xml:space="preserve">0.686115860939026</t>
   </si>
   <si>
     <t xml:space="preserve">0.662974238395691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66985422372818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.673606872558594</t>
+    <t xml:space="preserve">0.669854164123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.673606932163239</t>
   </si>
   <si>
     <t xml:space="preserve">0.661723375320435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68986850976944</t>
+    <t xml:space="preserve">0.689868569374084</t>
   </si>
   <si>
     <t xml:space="preserve">0.667352437973022</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">0.688617587089539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689243018627167</t>
+    <t xml:space="preserve">0.689243137836456</t>
   </si>
   <si>
     <t xml:space="preserve">0.676108658313751</t>
@@ -107,19 +107,19 @@
     <t xml:space="preserve">0.671105086803436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666727006435394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643585562705994</t>
+    <t xml:space="preserve">0.66672694683075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643585443496704</t>
   </si>
   <si>
     <t xml:space="preserve">0.612313032150269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597927749156952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605745911598206</t>
+    <t xml:space="preserve">0.597927689552307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605745851993561</t>
   </si>
   <si>
     <t xml:space="preserve">0.610749423503876</t>
@@ -128,55 +128,55 @@
     <t xml:space="preserve">0.614189386367798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627323746681213</t>
+    <t xml:space="preserve">0.627323865890503</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942094802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624822020530701</t>
+    <t xml:space="preserve">0.624821960926056</t>
   </si>
   <si>
     <t xml:space="preserve">0.646712720394135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636079967021942</t>
+    <t xml:space="preserve">0.636080026626587</t>
   </si>
   <si>
     <t xml:space="preserve">0.656719744205475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645461678504944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641083538532257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647963523864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.657345235347748</t>
+    <t xml:space="preserve">0.645461797714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641083598136902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.647963464260101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.657345294952393</t>
   </si>
   <si>
     <t xml:space="preserve">0.661097943782806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.67298150062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.666101634502411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.66485059261322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658596158027649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651716291904449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654843509197235</t>
+    <t xml:space="preserve">0.672981441020966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.666101574897766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.664850652217865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658596098423004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651716351509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65484356880188</t>
   </si>
   <si>
     <t xml:space="preserve">0.669228851795197</t>
@@ -185,49 +185,49 @@
     <t xml:space="preserve">0.713010132312775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69299578666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.691119492053986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.694246709346771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697999358177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696123003959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7030029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692370295524597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.699250340461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714261054992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714886426925659</t>
+    <t xml:space="preserve">0.692995846271515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.691119432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.694246649742126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69799941778183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69612318277359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703002870082855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692370355129242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.699250221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714260935783386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714886367321014</t>
   </si>
   <si>
     <t xml:space="preserve">0.702377557754517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.705504775047302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735526204109192</t>
+    <t xml:space="preserve">0.705504655838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735526323318481</t>
   </si>
   <si>
     <t xml:space="preserve">0.740529775619507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.744282603263855</t>
+    <t xml:space="preserve">0.74428254365921</t>
   </si>
   <si>
     <t xml:space="preserve">0.748660624027252</t>
@@ -236,40 +236,40 @@
     <t xml:space="preserve">0.738027989864349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.750536978244781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754289507865906</t>
+    <t xml:space="preserve">0.750536918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754289627075195</t>
   </si>
   <si>
     <t xml:space="preserve">0.768049418926239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.757416784763336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766798555850983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.752413332462311</t>
+    <t xml:space="preserve">0.757416844367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766798496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.752413272857666</t>
   </si>
   <si>
     <t xml:space="preserve">0.781183779239655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778056561946869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786187350749969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77930760383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768674850463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755540430545807</t>
+    <t xml:space="preserve">0.778056442737579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786187469959259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779307544231415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768674910068512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755540549755096</t>
   </si>
   <si>
     <t xml:space="preserve">0.760544061660767</t>
@@ -284,13 +284,13 @@
     <t xml:space="preserve">0.759293258190155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769925892353058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76116955280304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767424046993256</t>
+    <t xml:space="preserve">0.769925773143768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761169493198395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767423987388611</t>
   </si>
   <si>
     <t xml:space="preserve">0.747409760951996</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.754915058612823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781809329986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801198244094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804950892925262</t>
+    <t xml:space="preserve">0.781809270381927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801198065280914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804950714111328</t>
   </si>
   <si>
     <t xml:space="preserve">0.799321830272675</t>
@@ -317,37 +317,37 @@
     <t xml:space="preserve">0.785562038421631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.796820104122162</t>
+    <t xml:space="preserve">0.796820044517517</t>
   </si>
   <si>
     <t xml:space="preserve">0.791816473007202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801823556423187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733649790287018</t>
+    <t xml:space="preserve">0.801823496818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733649849891663</t>
   </si>
   <si>
     <t xml:space="preserve">0.725519061088562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766306459903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759828746318817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750760138034821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778614044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703473150730133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69246119260788</t>
+    <t xml:space="preserve">0.766306579113007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759828805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750760078430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778613984584808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703473210334778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692461252212524</t>
   </si>
   <si>
     <t xml:space="preserve">0.705416560173035</t>
@@ -356,55 +356,55 @@
     <t xml:space="preserve">0.730031549930573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.763067483901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762419879436493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769545197486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75788551568985</t>
+    <t xml:space="preserve">0.763067603111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762419939041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769545316696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757885575294495</t>
   </si>
   <si>
     <t xml:space="preserve">0.742986917495728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.742339134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.758533239364624</t>
+    <t xml:space="preserve">0.742339193820953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758533298969269</t>
   </si>
   <si>
     <t xml:space="preserve">0.777318477630615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774079740047455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776022851467133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78379625082016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779909610748291</t>
+    <t xml:space="preserve">0.77407968044281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776022970676422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78379613161087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779909551143646</t>
   </si>
   <si>
     <t xml:space="preserve">0.79027384519577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789625883102417</t>
+    <t xml:space="preserve">0.789625942707062</t>
   </si>
   <si>
     <t xml:space="preserve">0.794160306453705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805172443389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807763457298279</t>
+    <t xml:space="preserve">0.805172324180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807763516902924</t>
   </si>
   <si>
     <t xml:space="preserve">0.822662115097046</t>
@@ -416,34 +416,34 @@
     <t xml:space="preserve">0.820718705654144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.822014212608337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809706747531891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814240992069244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816184520721436</t>
+    <t xml:space="preserve">0.822014272212982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809706687927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814241111278534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816184341907501</t>
   </si>
   <si>
     <t xml:space="preserve">0.804524660110474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801285922527313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812945604324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801933526992798</t>
+    <t xml:space="preserve">0.801285743713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812945485115051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801933586597443</t>
   </si>
   <si>
     <t xml:space="preserve">0.786387264728546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.788330495357513</t>
+    <t xml:space="preserve">0.788330435752869</t>
   </si>
   <si>
     <t xml:space="preserve">0.771488547325134</t>
@@ -452,46 +452,46 @@
     <t xml:space="preserve">0.783148407936096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.782500565052032</t>
+    <t xml:space="preserve">0.782500624656677</t>
   </si>
   <si>
     <t xml:space="preserve">0.781852841377258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.770193099975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785091638565063</t>
+    <t xml:space="preserve">0.770193159580231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785091578960419</t>
   </si>
   <si>
     <t xml:space="preserve">0.795455873012543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.811002254486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794808149337769</t>
+    <t xml:space="preserve">0.811002314090729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794808089733124</t>
   </si>
   <si>
     <t xml:space="preserve">0.796103656291962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.798694670200348</t>
+    <t xml:space="preserve">0.798694789409637</t>
   </si>
   <si>
     <t xml:space="preserve">0.802581310272217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.790921449661255</t>
+    <t xml:space="preserve">0.790921568870544</t>
   </si>
   <si>
     <t xml:space="preserve">0.796751499176025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799342393875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810354471206665</t>
+    <t xml:space="preserve">0.799342453479767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810354590415955</t>
   </si>
   <si>
     <t xml:space="preserve">0.780557334423065</t>
@@ -503,25 +503,25 @@
     <t xml:space="preserve">0.785739421844482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.827196359634399</t>
+    <t xml:space="preserve">0.827196419239044</t>
   </si>
   <si>
     <t xml:space="preserve">0.81359338760376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800638020038605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797399282455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80387681722641</t>
+    <t xml:space="preserve">0.800637900829315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797399163246155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803876936435699</t>
   </si>
   <si>
     <t xml:space="preserve">0.807115733623505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.761124432086945</t>
+    <t xml:space="preserve">0.76112425327301</t>
   </si>
   <si>
     <t xml:space="preserve">0.770840883255005</t>
@@ -530,28 +530,28 @@
     <t xml:space="preserve">0.73132711648941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.735861420631409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.720315158367157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721610724925995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.719019651412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696347773075104</t>
+    <t xml:space="preserve">0.735861480236053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.720315039157867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.72161066532135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.719019591808319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696347832679749</t>
   </si>
   <si>
     <t xml:space="preserve">0.696995556354523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.709950804710388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713837385177612</t>
+    <t xml:space="preserve">0.709950923919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713837504386902</t>
   </si>
   <si>
     <t xml:space="preserve">0.711894154548645</t>
@@ -560,28 +560,28 @@
     <t xml:space="preserve">0.707359790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.728736102581024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715780794620514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722258448600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765011012554169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754646718502045</t>
+    <t xml:space="preserve">0.728736042976379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715780735015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722258388996124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765010893344879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7546466588974</t>
   </si>
   <si>
     <t xml:space="preserve">0.755294501781464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.78768265247345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776670753955841</t>
+    <t xml:space="preserve">0.787682712078094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776670694351196</t>
   </si>
   <si>
     <t xml:space="preserve">0.772136390209198</t>
@@ -590,40 +590,40 @@
     <t xml:space="preserve">0.78703498840332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81683212518692</t>
+    <t xml:space="preserve">0.816832184791565</t>
   </si>
   <si>
     <t xml:space="preserve">0.819423198699951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799990236759186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824605345726013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838856220245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831730663776398</t>
+    <t xml:space="preserve">0.799990296363831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824605286121368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838856160640717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831730842590332</t>
   </si>
   <si>
     <t xml:space="preserve">0.832378447055817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840151607990265</t>
+    <t xml:space="preserve">0.840151727199554</t>
   </si>
   <si>
     <t xml:space="preserve">0.848572671413422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841447234153748</t>
+    <t xml:space="preserve">0.841447174549103</t>
   </si>
   <si>
     <t xml:space="preserve">0.844686150550842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830435156822205</t>
+    <t xml:space="preserve">0.83043509721756</t>
   </si>
   <si>
     <t xml:space="preserve">0.798047006130219</t>
@@ -635,61 +635,61 @@
     <t xml:space="preserve">0.82007098197937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.80646800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811650097370148</t>
+    <t xml:space="preserve">0.806467890739441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811650037765503</t>
   </si>
   <si>
     <t xml:space="preserve">0.836265087127686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.844038307666779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837560713291168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836912989616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821366310119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828491985797882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825900912284851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829139709472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84662938117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849220335483551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864766895771027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867357790470123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868005573749542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870596706867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857641339302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.865414559841156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866710245609283</t>
+    <t xml:space="preserve">0.844038248062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837560653686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836912870407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821366488933563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828491926193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825900852680206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829139649868011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84662926197052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849220454692841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864766776561737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867357850074768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868005692958832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870596587657928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857641398906708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.865414619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866710186004639</t>
   </si>
   <si>
     <t xml:space="preserve">0.85310697555542</t>
@@ -698,166 +698,166 @@
     <t xml:space="preserve">0.855698049068451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858289182186127</t>
+    <t xml:space="preserve">0.858289122581482</t>
   </si>
   <si>
     <t xml:space="preserve">0.860232532024384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.87253999710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874483346939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887438714504242</t>
+    <t xml:space="preserve">0.872540056705475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874483287334442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887438595294952</t>
   </si>
   <si>
     <t xml:space="preserve">0.893916249275208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892620742321014</t>
+    <t xml:space="preserve">0.892620861530304</t>
   </si>
   <si>
     <t xml:space="preserve">0.912701487541199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.909462690353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908167064189911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919826984405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918531358242035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875778794288635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877722144126892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891972899436951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884847342967987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895211696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884199798107147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876426637172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862175583839417</t>
+    <t xml:space="preserve">0.909462571144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908166944980621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919826865196228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918531239032745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875778913497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877722203731537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.891972959041595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884847581386566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895211637020111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884199857711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876426577568054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862175822257996</t>
   </si>
   <si>
     <t xml:space="preserve">0.85634583234787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.882256507873535</t>
+    <t xml:space="preserve">0.882256388664246</t>
   </si>
   <si>
     <t xml:space="preserve">0.899098336696625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.890677452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926952183246613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915292501449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917235732078552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966466069221497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95804500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965170443058014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96128386259079</t>
+    <t xml:space="preserve">0.890677392482758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926952362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91529244184494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917235910892487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966465890407562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958045065402985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965170383453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961283922195435</t>
   </si>
   <si>
     <t xml:space="preserve">0.963227152824402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941850900650024</t>
+    <t xml:space="preserve">0.94185084104538</t>
   </si>
   <si>
     <t xml:space="preserve">0.941203117370605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958692729473114</t>
+    <t xml:space="preserve">0.958692908287048</t>
   </si>
   <si>
     <t xml:space="preserve">0.982278227806091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988308608531952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997018992900848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00036931037903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992998898029327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96820741891861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981608092784882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986298382282257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988978505134583</t>
+    <t xml:space="preserve">0.988308429718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997019052505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00036919116974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992998659610748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968207180500031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981608271598816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986298263072968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988978385925293</t>
   </si>
   <si>
     <t xml:space="preserve">0.989648520946503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974907755851746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999699115753174</t>
+    <t xml:space="preserve">0.97490781545639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999699175357819</t>
   </si>
   <si>
     <t xml:space="preserve">1.00505948066711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998359084129333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997689008712769</t>
+    <t xml:space="preserve">0.998359262943268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997689127922058</t>
   </si>
   <si>
     <t xml:space="preserve">1.00170934200287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0070698261261</t>
+    <t xml:space="preserve">1.00706970691681</t>
   </si>
   <si>
     <t xml:space="preserve">1.02047049999237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02985095977783</t>
+    <t xml:space="preserve">1.02985107898712</t>
   </si>
   <si>
     <t xml:space="preserve">1.0177903175354</t>
@@ -866,202 +866,202 @@
     <t xml:space="preserve">0.995008945465088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999029219150543</t>
+    <t xml:space="preserve">0.999029338359833</t>
   </si>
   <si>
     <t xml:space="preserve">0.976917803287506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974237620830536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970217347145081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965527176856995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960836887359619</t>
+    <t xml:space="preserve">0.974237740039825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97021746635437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96552711725235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960837006568909</t>
   </si>
   <si>
     <t xml:space="preserve">0.961506903171539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.964187145233154</t>
+    <t xml:space="preserve">0.964187204837799</t>
   </si>
   <si>
     <t xml:space="preserve">0.980268180370331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97892814874649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984958350658417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972897589206696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960166752338409</t>
+    <t xml:space="preserve">0.978927969932556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984958291053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97289764881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960166811943054</t>
   </si>
   <si>
     <t xml:space="preserve">0.958826720714569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.951456308364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955476582050323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949446439743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963517129421234</t>
+    <t xml:space="preserve">0.951456427574158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955476462841034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949446260929108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963517069816589</t>
   </si>
   <si>
     <t xml:space="preserve">0.950116217136383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953466415405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956816732883453</t>
+    <t xml:space="preserve">0.953466475009918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956816554069519</t>
   </si>
   <si>
     <t xml:space="preserve">0.958156585693359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952796399593353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962177038192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944755911827087</t>
+    <t xml:space="preserve">0.952796518802643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962177097797394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944755971431732</t>
   </si>
   <si>
     <t xml:space="preserve">0.931355118751526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948106229305267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954136431217194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957486689090729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939395606517792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946766138076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934705317020416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928674876689911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924654722213745</t>
+    <t xml:space="preserve">0.948106288909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954136490821838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957486629486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939395666122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946766078472137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934705436229706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928675055503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92465478181839</t>
   </si>
   <si>
     <t xml:space="preserve">0.932695209980011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945426046848297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959496855735779</t>
+    <t xml:space="preserve">0.945426106452942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959496796131134</t>
   </si>
   <si>
     <t xml:space="preserve">0.973567724227905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978258013725281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993668913841248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984288215637207</t>
+    <t xml:space="preserve">0.978257954120636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993668854236603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984288275241852</t>
   </si>
   <si>
     <t xml:space="preserve">0.983618319034576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994338810443878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977587997913361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980938076972961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972227692604065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966197192668915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96954745054245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96887731552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9715576171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995678961277008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992328822612762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966867327690125</t>
+    <t xml:space="preserve">0.994338870048523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977587878704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980938255786896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972227513790131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96619725227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969547510147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968877255916595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971557557582855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995678842067719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992328643798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966867208480835</t>
   </si>
   <si>
     <t xml:space="preserve">1.02114045619965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01041984558105</t>
+    <t xml:space="preserve">1.01041996479034</t>
   </si>
   <si>
     <t xml:space="preserve">1.01444005966187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02181053161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02382051944733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0285108089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03320121765137</t>
+    <t xml:space="preserve">1.02181041240692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02382063865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02851092815399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03320133686066</t>
   </si>
   <si>
     <t xml:space="preserve">1.03923153877258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0265007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05531251430511</t>
+    <t xml:space="preserve">1.02650082111359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0553126335144</t>
   </si>
   <si>
     <t xml:space="preserve">1.05866265296936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04459178447723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05330228805542</t>
+    <t xml:space="preserve">1.04459202289581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.053302526474</t>
   </si>
   <si>
     <t xml:space="preserve">1.06804323196411</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">1.07273352146149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08613443374634</t>
+    <t xml:space="preserve">1.08613431453705</t>
   </si>
   <si>
     <t xml:space="preserve">1.09551477432251</t>
@@ -1079,25 +1079,25 @@
     <t xml:space="preserve">1.08345413208008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08211398124695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05397236347198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0600026845932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04392170906067</t>
+    <t xml:space="preserve">1.08211410045624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05397248268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06000280380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04392182826996</t>
   </si>
   <si>
     <t xml:space="preserve">1.04861223697662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04660201072693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03990149497986</t>
+    <t xml:space="preserve">1.04660189151764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03990161418915</t>
   </si>
   <si>
     <t xml:space="preserve">1.04258179664612</t>
@@ -1109,13 +1109,13 @@
     <t xml:space="preserve">1.015780210495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05196225643158</t>
+    <t xml:space="preserve">1.05196237564087</t>
   </si>
   <si>
     <t xml:space="preserve">1.06737327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06603312492371</t>
+    <t xml:space="preserve">1.066033244133</t>
   </si>
   <si>
     <t xml:space="preserve">1.02449059486389</t>
@@ -1124,121 +1124,121 @@
     <t xml:space="preserve">1.01846027374268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02784073352814</t>
+    <t xml:space="preserve">1.02784085273743</t>
   </si>
   <si>
     <t xml:space="preserve">1.05665266513824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06134271621704</t>
+    <t xml:space="preserve">1.06134283542633</t>
   </si>
   <si>
     <t xml:space="preserve">1.07742369174957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07943403720856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06938326358795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05933284759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03856134414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02683591842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03588128089905</t>
+    <t xml:space="preserve">1.07943391799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06938350200653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05933272838593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03856158256531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02683579921722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03588151931763</t>
   </si>
   <si>
     <t xml:space="preserve">1.04191172122955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996349096298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971222519874573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99534398317337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944420993328094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953131377696991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941405832767487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959831714630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946431040763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957821786403656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950451135635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936380445957184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967202365398407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991323709487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975577652454376</t>
+    <t xml:space="preserve">0.996349036693573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971222579479218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995343923568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94442081451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953131496906281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941405773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959831833839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9464311003685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957821726799011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950451254844666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936380386352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967202305793762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991323590278625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975577712059021</t>
   </si>
   <si>
     <t xml:space="preserve">0.993333876132965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00003433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00137436389923</t>
+    <t xml:space="preserve">1.0000342130661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00137448310852</t>
   </si>
   <si>
     <t xml:space="preserve">0.991658687591553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00673449039459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99936431646347</t>
+    <t xml:space="preserve">1.00673472881317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999364197254181</t>
   </si>
   <si>
     <t xml:space="preserve">1.04023659229279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04157674312592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04224681854248</t>
+    <t xml:space="preserve">1.04157662391663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04224669933319</t>
   </si>
   <si>
     <t xml:space="preserve">1.04961705207825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04995226860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06268286705017</t>
+    <t xml:space="preserve">1.04995214939117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06268298625946</t>
   </si>
   <si>
     <t xml:space="preserve">1.07206344604492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05832779407501</t>
+    <t xml:space="preserve">1.05832755565643</t>
   </si>
   <si>
     <t xml:space="preserve">1.06335306167603</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">1.07407367229462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08043909072876</t>
+    <t xml:space="preserve">1.08043873310089</t>
   </si>
   <si>
     <t xml:space="preserve">1.08546423912048</t>
@@ -1256,43 +1256,43 @@
     <t xml:space="preserve">1.09048962593079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09484493732452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09819507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0985301733017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12198138237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11762619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1172913312912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10724055767059</t>
+    <t xml:space="preserve">1.09484481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09819519519806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09853005409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12198162078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11762607097626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11729109287262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10724067687988</t>
   </si>
   <si>
     <t xml:space="preserve">1.10757565498352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12265157699585</t>
+    <t xml:space="preserve">1.12265169620514</t>
   </si>
   <si>
     <t xml:space="preserve">1.13002181053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10992085933685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1182963848114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05732250213623</t>
+    <t xml:space="preserve">1.10992097854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11829614639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05732262134552</t>
   </si>
   <si>
     <t xml:space="preserve">1.03387129306793</t>
@@ -1301,22 +1301,22 @@
     <t xml:space="preserve">1.0389529466629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05287528038025</t>
+    <t xml:space="preserve">1.05287516117096</t>
   </si>
   <si>
     <t xml:space="preserve">1.04208540916443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04730629920959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02572679519653</t>
+    <t xml:space="preserve">1.04730618000031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02572667598724</t>
   </si>
   <si>
     <t xml:space="preserve">1.00693154335022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980827391147614</t>
+    <t xml:space="preserve">0.980827152729034</t>
   </si>
   <si>
     <t xml:space="preserve">0.998926162719727</t>
@@ -1325,10 +1325,10 @@
     <t xml:space="preserve">1.01076018810272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00484323501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02920734882355</t>
+    <t xml:space="preserve">1.00484335422516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02920722961426</t>
   </si>
   <si>
     <t xml:space="preserve">1.00936782360077</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">1.00658345222473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999622344970703</t>
+    <t xml:space="preserve">0.999622464179993</t>
   </si>
   <si>
     <t xml:space="preserve">0.968993246555328</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">1.02398633956909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03164374828339</t>
+    <t xml:space="preserve">1.0316436290741</t>
   </si>
   <si>
     <t xml:space="preserve">1.02851116657257</t>
@@ -1358,31 +1358,31 @@
     <t xml:space="preserve">1.01980972290039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04382586479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04661011695862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0236382484436</t>
+    <t xml:space="preserve">1.04382574558258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04661023616791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02363848686218</t>
   </si>
   <si>
     <t xml:space="preserve">1.02537858486176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00588750839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01250040531158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02120184898376</t>
+    <t xml:space="preserve">1.00588738918304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01250064373016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02120196819305</t>
   </si>
   <si>
     <t xml:space="preserve">1.02642273902893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03373193740845</t>
+    <t xml:space="preserve">1.03373205661774</t>
   </si>
   <si>
     <t xml:space="preserve">1.01389276981354</t>
@@ -1391,16 +1391,16 @@
     <t xml:space="preserve">1.03860473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05113482475281</t>
+    <t xml:space="preserve">1.05113470554352</t>
   </si>
   <si>
     <t xml:space="preserve">1.06122863292694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07236635684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06018447875977</t>
+    <t xml:space="preserve">1.07236659526825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06018435955048</t>
   </si>
   <si>
     <t xml:space="preserve">1.06262075901031</t>
@@ -1412,16 +1412,16 @@
     <t xml:space="preserve">1.07375872135162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06714558601379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07863163948059</t>
+    <t xml:space="preserve">1.06714570522308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0786315202713</t>
   </si>
   <si>
     <t xml:space="preserve">1.09290170669556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09429395198822</t>
+    <t xml:space="preserve">1.09429407119751</t>
   </si>
   <si>
     <t xml:space="preserve">1.10160326957703</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">1.04835045337677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06157672405243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07201826572418</t>
+    <t xml:space="preserve">1.06157660484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07201838493347</t>
   </si>
   <si>
     <t xml:space="preserve">1.07584714889526</t>
@@ -1463,16 +1463,16 @@
     <t xml:space="preserve">1.12005043029785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12387907505035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10473585128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10612809658051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11134898662567</t>
+    <t xml:space="preserve">1.12387895584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10473597049713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10612797737122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11134886741638</t>
   </si>
   <si>
     <t xml:space="preserve">1.10821640491486</t>
@@ -1481,22 +1481,22 @@
     <t xml:space="preserve">1.10960865020752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08837711811066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08802902698517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08942139148712</t>
+    <t xml:space="preserve">1.08837723731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08802890777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08942127227783</t>
   </si>
   <si>
     <t xml:space="preserve">1.07549893856049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06540524959564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03338408470154</t>
+    <t xml:space="preserve">1.06540536880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03338396549225</t>
   </si>
   <si>
     <t xml:space="preserve">1.04243350028992</t>
@@ -1505,19 +1505,19 @@
     <t xml:space="preserve">1.02154994010925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03094756603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04173719882965</t>
+    <t xml:space="preserve">1.03094744682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04173731803894</t>
   </si>
   <si>
     <t xml:space="preserve">1.05705189704895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07897937297821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09220588207245</t>
+    <t xml:space="preserve">1.0789794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09220576286316</t>
   </si>
   <si>
     <t xml:space="preserve">1.09116160869598</t>
@@ -1526,10 +1526,10 @@
     <t xml:space="preserve">1.08454835414886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08141601085663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09847056865692</t>
+    <t xml:space="preserve">1.08141589164734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09847068786621</t>
   </si>
   <si>
     <t xml:space="preserve">1.09603440761566</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">1.07445478439331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0587922334671</t>
+    <t xml:space="preserve">1.05879211425781</t>
   </si>
   <si>
     <t xml:space="preserve">1.07758724689484</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">1.06923389434814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04069328308105</t>
+    <t xml:space="preserve">1.04069316387177</t>
   </si>
   <si>
     <t xml:space="preserve">1.03199172019958</t>
@@ -1559,19 +1559,19 @@
     <t xml:space="preserve">1.04452168941498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04417359828949</t>
+    <t xml:space="preserve">1.04417383670807</t>
   </si>
   <si>
     <t xml:space="preserve">1.05183112621307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03616833686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05844402313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03442811965942</t>
+    <t xml:space="preserve">1.03616845607758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05844414234161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03442800045013</t>
   </si>
   <si>
     <t xml:space="preserve">1.00310289859772</t>
@@ -1580,61 +1580,61 @@
     <t xml:space="preserve">0.991617023944855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00832390785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01424074172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01772129535675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01354467868805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99370539188385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988136470317841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977346658706665</t>
+    <t xml:space="preserve">1.00832402706146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01424062252045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01772117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01354455947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993705332279205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988136351108551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97734659910202</t>
   </si>
   <si>
     <t xml:space="preserve">1.00553941726685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986047923564911</t>
+    <t xml:space="preserve">0.9860480427742</t>
   </si>
   <si>
     <t xml:space="preserve">0.989528715610504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992313265800476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98291540145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991965115070343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01319658756256</t>
+    <t xml:space="preserve">0.992312967777252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98291552066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991965055465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01319670677185</t>
   </si>
   <si>
     <t xml:space="preserve">1.00414717197418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02050590515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01563310623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0351243019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03930103778839</t>
+    <t xml:space="preserve">1.02050566673279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0156329870224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03512418270111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0393009185791</t>
   </si>
   <si>
     <t xml:space="preserve">1.05252707004547</t>
@@ -1643,34 +1643,34 @@
     <t xml:space="preserve">1.05461549758911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03721249103546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0271190404892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0399968624115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06610131263733</t>
+    <t xml:space="preserve">1.03721272945404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02711892127991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03999698162079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06610143184662</t>
   </si>
   <si>
     <t xml:space="preserve">1.06088054180145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04034507274628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03233969211578</t>
+    <t xml:space="preserve">1.04034519195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03233981132507</t>
   </si>
   <si>
     <t xml:space="preserve">1.04278147220612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04347765445709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07410681247711</t>
+    <t xml:space="preserve">1.04347741603851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07410669326782</t>
   </si>
   <si>
     <t xml:space="preserve">1.10090720653534</t>
@@ -1685,100 +1685,100 @@
     <t xml:space="preserve">1.11378538608551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10647618770599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12318289279938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13118827342987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11448132991791</t>
+    <t xml:space="preserve">1.1064760684967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12318277359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13118815422058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1144814491272</t>
   </si>
   <si>
     <t xml:space="preserve">1.08872509002686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09464228153229</t>
+    <t xml:space="preserve">1.09464204311371</t>
   </si>
   <si>
     <t xml:space="preserve">1.11622166633606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11831021308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13501667976379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13675725460052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13814926147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14302206039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10403966903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10891258716583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09951508045197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1019514799118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09916698932648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09499025344849</t>
+    <t xml:space="preserve">1.1183100938797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13501679897308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13675713539124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1381493806839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14302217960358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10403978824615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10891270637512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09951484203339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10195136070251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09916687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0949901342392</t>
   </si>
   <si>
     <t xml:space="preserve">1.10577988624573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09185767173767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07793521881104</t>
+    <t xml:space="preserve">1.09185779094696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07793533802032</t>
   </si>
   <si>
     <t xml:space="preserve">1.08071982860565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08663690090179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06227290630341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08280825614929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09742677211761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10021090507507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09777462482452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10369169712067</t>
+    <t xml:space="preserve">1.0866367816925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06227278709412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08280813694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09742653369904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10021114349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09777474403381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10369157791138</t>
   </si>
   <si>
     <t xml:space="preserve">1.11100089550018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10543191432953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08594059944153</t>
+    <t xml:space="preserve">1.10543203353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08594071865082</t>
   </si>
   <si>
     <t xml:space="preserve">1.09568619728088</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">1.11726593971252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12074649333954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10752022266388</t>
+    <t xml:space="preserve">1.12074661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10752034187317</t>
   </si>
   <si>
     <t xml:space="preserve">1.11030471324921</t>
@@ -1808,13 +1808,13 @@
     <t xml:space="preserve">1.13571298122406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13536500930786</t>
+    <t xml:space="preserve">1.13536489009857</t>
   </si>
   <si>
     <t xml:space="preserve">1.13084006309509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13223230838776</t>
+    <t xml:space="preserve">1.13223242759705</t>
   </si>
   <si>
     <t xml:space="preserve">1.14754688739777</t>
@@ -1823,16 +1823,16 @@
     <t xml:space="preserve">1.06331694126129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05391919612885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04626226425171</t>
+    <t xml:space="preserve">1.05391931533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04626214504242</t>
   </si>
   <si>
     <t xml:space="preserve">1.05426752567291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04869854450226</t>
+    <t xml:space="preserve">1.04869842529297</t>
   </si>
   <si>
     <t xml:space="preserve">1.02433454990387</t>
@@ -1844,49 +1844,49 @@
     <t xml:space="preserve">1.01632916927338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0037989616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997882127761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00727963447571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02015769481659</t>
+    <t xml:space="preserve">1.00379908084869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997882068157196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.007279753685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02015793323517</t>
   </si>
   <si>
     <t xml:space="preserve">1.07654309272766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08517634868622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0972056388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09647631645203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06622123718262</t>
+    <t xml:space="preserve">1.08517646789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09720540046692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09647643566132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06622135639191</t>
   </si>
   <si>
     <t xml:space="preserve">1.08116674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07205355167389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06038892269135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05127596855164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06403422355652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07168924808502</t>
+    <t xml:space="preserve">1.07205379009247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06038904190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05127608776093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06403434276581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07168912887573</t>
   </si>
   <si>
     <t xml:space="preserve">1.08043766021729</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">1.0979346036911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09866368770599</t>
+    <t xml:space="preserve">1.0986635684967</t>
   </si>
   <si>
     <t xml:space="preserve">1.10449588298798</t>
@@ -1907,10 +1907,10 @@
     <t xml:space="preserve">1.10230875015259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09574770927429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09829914569855</t>
+    <t xml:space="preserve">1.09574747085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09829902648926</t>
   </si>
   <si>
     <t xml:space="preserve">1.13219952583313</t>
@@ -1922,55 +1922,55 @@
     <t xml:space="preserve">1.14021897315979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14750921726227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13584458827972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11944127082825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11543130874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10376691818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11251533031464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11069285869598</t>
+    <t xml:space="preserve">1.14750933647156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13584470748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11944139003754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11543154716492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10376703739166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11251544952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11069273948669</t>
   </si>
   <si>
     <t xml:space="preserve">1.13511562347412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15006101131439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15188348293304</t>
+    <t xml:space="preserve">1.1500608921051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15188360214233</t>
   </si>
   <si>
     <t xml:space="preserve">1.147873878479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15261268615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16427707672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17047393321991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17156755924225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17229664325714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17849349975586</t>
+    <t xml:space="preserve">1.15261256694794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16427719593048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17047417163849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17156767845154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17229676246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17849361896515</t>
   </si>
   <si>
     <t xml:space="preserve">1.17484843730927</t>
@@ -1982,40 +1982,40 @@
     <t xml:space="preserve">1.16318380832672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16609990596771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17995166778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18469047546387</t>
+    <t xml:space="preserve">1.16609978675842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17995154857635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18469035625458</t>
   </si>
   <si>
     <t xml:space="preserve">1.18104517459869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17120313644409</t>
+    <t xml:space="preserve">1.17120325565338</t>
   </si>
   <si>
     <t xml:space="preserve">1.17375481128693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14969658851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15407073497772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17083859443665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16209018230438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16682887077332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16755795478821</t>
+    <t xml:space="preserve">1.14969635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15407061576843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17083847522736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16209006309509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1668289899826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1675580739975</t>
   </si>
   <si>
     <t xml:space="preserve">1.17010962963104</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">1.13183498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12418007850647</t>
+    <t xml:space="preserve">1.12418019771576</t>
   </si>
   <si>
     <t xml:space="preserve">1.12782526016235</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">1.16099655628204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14459311962128</t>
+    <t xml:space="preserve">1.14459335803986</t>
   </si>
   <si>
     <t xml:space="preserve">1.15297722816467</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">1.13475120067596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16391277313232</t>
+    <t xml:space="preserve">1.16391265392303</t>
   </si>
   <si>
     <t xml:space="preserve">1.16938054561615</t>
@@ -2057,13 +2057,13 @@
     <t xml:space="preserve">1.16573536396027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16500639915466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18833553791046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20473909378052</t>
+    <t xml:space="preserve">1.16500627994537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18833565711975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20473897457123</t>
   </si>
   <si>
     <t xml:space="preserve">1.20036470890045</t>
@@ -2072,13 +2072,13 @@
     <t xml:space="preserve">1.18869996070862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17958700656891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16464185714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17922258377075</t>
+    <t xml:space="preserve">1.1795871257782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16464173793793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17922270298004</t>
   </si>
   <si>
     <t xml:space="preserve">1.18213880062103</t>
@@ -2090,16 +2090,16 @@
     <t xml:space="preserve">1.19599044322968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18979370594025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22551667690277</t>
+    <t xml:space="preserve">1.18979358673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22551679611206</t>
   </si>
   <si>
     <t xml:space="preserve">1.21567463874817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22770380973816</t>
+    <t xml:space="preserve">1.22770369052887</t>
   </si>
   <si>
     <t xml:space="preserve">1.23207807540894</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">1.21166479587555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23134899139404</t>
+    <t xml:space="preserve">1.23134911060333</t>
   </si>
   <si>
     <t xml:space="preserve">1.2302553653717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21603918075562</t>
+    <t xml:space="preserve">1.21603906154633</t>
   </si>
   <si>
     <t xml:space="preserve">1.21931982040405</t>
@@ -2126,16 +2126,16 @@
     <t xml:space="preserve">1.23791038990021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23462951183319</t>
+    <t xml:space="preserve">1.23462975025177</t>
   </si>
   <si>
     <t xml:space="preserve">1.22806823253632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21640348434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22187161445618</t>
+    <t xml:space="preserve">1.21640360355377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22187149524689</t>
   </si>
   <si>
     <t xml:space="preserve">1.22114229202271</t>
@@ -2147,10 +2147,10 @@
     <t xml:space="preserve">1.23061990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22843265533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23645222187042</t>
+    <t xml:space="preserve">1.22843277454376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23645210266113</t>
   </si>
   <si>
     <t xml:space="preserve">1.2287974357605</t>
@@ -2159,19 +2159,19 @@
     <t xml:space="preserve">1.22624576091766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27363324165344</t>
+    <t xml:space="preserve">1.27363336086273</t>
   </si>
   <si>
     <t xml:space="preserve">1.27691411972046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31154334545135</t>
+    <t xml:space="preserve">1.31154346466064</t>
   </si>
   <si>
     <t xml:space="preserve">1.3133659362793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30972063541412</t>
+    <t xml:space="preserve">1.30972075462341</t>
   </si>
   <si>
     <t xml:space="preserve">1.30826270580292</t>
@@ -2180,31 +2180,31 @@
     <t xml:space="preserve">1.31591749191284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29331755638123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31518876552582</t>
+    <t xml:space="preserve">1.29331743717194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31518852710724</t>
   </si>
   <si>
     <t xml:space="preserve">1.31445944309235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30862712860107</t>
+    <t xml:space="preserve">1.30862724781036</t>
   </si>
   <si>
     <t xml:space="preserve">1.29732716083527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27873659133911</t>
+    <t xml:space="preserve">1.27873647212982</t>
   </si>
   <si>
     <t xml:space="preserve">1.28857862949371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28420448303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27727854251862</t>
+    <t xml:space="preserve">1.28420436382294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27727842330933</t>
   </si>
   <si>
     <t xml:space="preserve">1.27509140968323</t>
@@ -2213,46 +2213,46 @@
     <t xml:space="preserve">1.26452028751373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24884605407715</t>
+    <t xml:space="preserve">1.24884593486786</t>
   </si>
   <si>
     <t xml:space="preserve">1.24665880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25249111652374</t>
+    <t xml:space="preserve">1.25249099731445</t>
   </si>
   <si>
     <t xml:space="preserve">1.24520063400269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24483633041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19052267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19635498523712</t>
+    <t xml:space="preserve">1.24483621120453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19052278995514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19635510444641</t>
   </si>
   <si>
     <t xml:space="preserve">1.1985422372818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19343876838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18068075180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20218741893768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18906474113464</t>
+    <t xml:space="preserve">1.19343888759613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18068063259125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20218753814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18906462192535</t>
   </si>
   <si>
     <t xml:space="preserve">1.19270980358124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20656156539917</t>
+    <t xml:space="preserve">1.20656168460846</t>
   </si>
   <si>
     <t xml:space="preserve">1.20729064941406</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">1.22515213489532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2415554523468</t>
+    <t xml:space="preserve">1.24155557155609</t>
   </si>
   <si>
     <t xml:space="preserve">1.23353612422943</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">1.25650084018707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26852989196777</t>
+    <t xml:space="preserve">1.26853001117706</t>
   </si>
   <si>
     <t xml:space="preserve">1.2998788356781</t>
@@ -2297,28 +2297,28 @@
     <t xml:space="preserve">1.30315947532654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29368185997009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29222393035889</t>
+    <t xml:space="preserve">1.29368197917938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2922238111496</t>
   </si>
   <si>
     <t xml:space="preserve">1.30607557296753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3520051240921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34544384479523</t>
+    <t xml:space="preserve">1.35200536251068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34544372558594</t>
   </si>
   <si>
     <t xml:space="preserve">1.33414363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31409502029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32247912883759</t>
+    <t xml:space="preserve">1.31409513950348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32247889041901</t>
   </si>
   <si>
     <t xml:space="preserve">1.32940483093262</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">1.34580826759338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33159196376801</t>
+    <t xml:space="preserve">1.33159208297729</t>
   </si>
   <si>
     <t xml:space="preserve">1.33013391494751</t>
@@ -2339,79 +2339,79 @@
     <t xml:space="preserve">1.34398579597473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34143400192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34945333003998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35893106460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36986660957336</t>
+    <t xml:space="preserve">1.3414341211319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34945356845856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35893094539642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36986649036407</t>
   </si>
   <si>
     <t xml:space="preserve">1.3822603225708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36038911342621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34908902645111</t>
+    <t xml:space="preserve">1.3603892326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34908890724182</t>
   </si>
   <si>
     <t xml:space="preserve">1.26524937152863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25613629817963</t>
+    <t xml:space="preserve">1.25613641738892</t>
   </si>
   <si>
     <t xml:space="preserve">1.13766729831696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15589332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19708406925201</t>
+    <t xml:space="preserve">1.15589320659637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19708395004272</t>
   </si>
   <si>
     <t xml:space="preserve">1.11579620838165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996233522891998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924787580966949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905467987060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733049869537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772782623767853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750546932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775334358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751275956630707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754556715488434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74143385887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.729040265083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786269962787628</t>
+    <t xml:space="preserve">0.996233463287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924787640571594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905467927455902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733049929141998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772782683372498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750546813011169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775334298610687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751276075839996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7545565366745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.741433918476105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.729040205478668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786269903182983</t>
   </si>
   <si>
     <t xml:space="preserve">0.79720550775528</t>
@@ -2420,49 +2420,49 @@
     <t xml:space="preserve">0.793195843696594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778250455856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824544548988342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826002538204193</t>
+    <t xml:space="preserve">0.778250396251678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824544429779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826002717018127</t>
   </si>
   <si>
     <t xml:space="preserve">0.816160619258881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841676950454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836209118366241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869016051292419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869744956493378</t>
+    <t xml:space="preserve">0.841677010059357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836209177970886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86901593208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869745016098022</t>
   </si>
   <si>
     <t xml:space="preserve">0.855164170265198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.876670956611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889429211616516</t>
+    <t xml:space="preserve">0.876670897006989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889429092407227</t>
   </si>
   <si>
     <t xml:space="preserve">0.885783970355988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.897448480129242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910935759544373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911664843559265</t>
+    <t xml:space="preserve">0.897448539733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910935938358307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91166478395462</t>
   </si>
   <si>
     <t xml:space="preserve">0.883961260318756</t>
@@ -2471,55 +2471,55 @@
     <t xml:space="preserve">0.888335585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.879587054252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89015805721283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906925976276398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901458382606506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899635672569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905832469463348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872296750545502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879951596260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878128945827484</t>
+    <t xml:space="preserve">0.879587173461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890158116817474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906926035881042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901458263397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899635553359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905832409858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872296631336212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879951655864716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878129005432129</t>
   </si>
   <si>
     <t xml:space="preserve">0.882138729095459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877764463424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914580881595612</t>
+    <t xml:space="preserve">0.877764403820038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914581120014191</t>
   </si>
   <si>
     <t xml:space="preserve">0.93426501750946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.911300301551819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944332599639893</t>
+    <t xml:space="preserve">0.911300182342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944332480430603</t>
   </si>
   <si>
     <t xml:space="preserve">0.902750730514526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.914020597934723</t>
+    <t xml:space="preserve">0.914020538330078</t>
   </si>
   <si>
     <t xml:space="preserve">0.910522937774658</t>
@@ -2531,19 +2531,19 @@
     <t xml:space="preserve">0.946275472640991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971146941184998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950550317764282</t>
+    <t xml:space="preserve">0.971147000789642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950550258159637</t>
   </si>
   <si>
     <t xml:space="preserve">0.971535444259644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969592273235321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981639444828033</t>
+    <t xml:space="preserve">0.969592332839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981639504432678</t>
   </si>
   <si>
     <t xml:space="preserve">1.00573348999023</t>
@@ -2561,16 +2561,16 @@
     <t xml:space="preserve">1.05236732959747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02710711956024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0119514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960265636444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956379592418671</t>
+    <t xml:space="preserve">1.02710735797882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01195132732391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960265576839447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956379473209381</t>
   </si>
   <si>
     <t xml:space="preserve">0.978141903877258</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">1.00961971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01933515071869</t>
+    <t xml:space="preserve">1.0193350315094</t>
   </si>
   <si>
     <t xml:space="preserve">1.01467168331146</t>
@@ -2597,13 +2597,13 @@
     <t xml:space="preserve">0.963763177394867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977364659309387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979696393013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984359622001648</t>
+    <t xml:space="preserve">0.977364778518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979696333408356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984359800815582</t>
   </si>
   <si>
     <t xml:space="preserve">0.999904274940491</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">0.996795415878296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993686556816101</t>
+    <t xml:space="preserve">0.993686497211456</t>
   </si>
   <si>
     <t xml:space="preserve">0.983193933963776</t>
@@ -2624,124 +2624,124 @@
     <t xml:space="preserve">0.958322584629059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961431503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960654318332672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973867118358612</t>
+    <t xml:space="preserve">0.961431443691254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960654199123383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973867058753967</t>
   </si>
   <si>
     <t xml:space="preserve">0.973089933395386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985137045383453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987857282161713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985525488853455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949772953987122</t>
+    <t xml:space="preserve">0.985136926174164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987857222557068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985525548458099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949773013591766</t>
   </si>
   <si>
     <t xml:space="preserve">0.954436421394348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970758140087128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928788006305695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943166732788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95599091053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959877014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953659236431122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96531754732132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982028067111969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01739192008972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00612223148346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994852244853973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97930771112442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98941171169281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987080097198486</t>
+    <t xml:space="preserve">0.970758199691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92878794670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943166613578796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955990970134735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959877133369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953659296035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965317726135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982027947902679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01739203929901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00612211227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994852364063263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979307770729065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989411771297455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987079977989197</t>
   </si>
   <si>
     <t xml:space="preserve">0.964929163455963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962597370147705</t>
+    <t xml:space="preserve">0.96259731054306</t>
   </si>
   <si>
     <t xml:space="preserve">0.958711266517639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966094851493835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951327502727509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954047739505768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975032985210419</t>
+    <t xml:space="preserve">0.966094970703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951327562332153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954047858715057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975033044815063</t>
   </si>
   <si>
     <t xml:space="preserve">0.968038022518158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937726020812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946664214134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938503205776215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94200074672699</t>
+    <t xml:space="preserve">0.937726080417633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946664273738861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938503324985504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942000806331635</t>
   </si>
   <si>
     <t xml:space="preserve">0.933451294898987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971924126148224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948995888233185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953270554542542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9458869099617</t>
+    <t xml:space="preserve">0.971924185752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94899570941925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953270673751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945886850357056</t>
   </si>
   <si>
     <t xml:space="preserve">0.929565191268921</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">0.931119620800018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.900807797908783</t>
+    <t xml:space="preserve">0.900807738304138</t>
   </si>
   <si>
     <t xml:space="preserve">0.903528034687042</t>
@@ -2759,19 +2759,19 @@
     <t xml:space="preserve">0.904693961143494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89886462688446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878656625747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886428952217102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901584982872009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886040389537811</t>
+    <t xml:space="preserve">0.898864567279816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87865674495697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886428892612457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90158486366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886040270328522</t>
   </si>
   <si>
     <t xml:space="preserve">0.840961158275604</t>
@@ -2789,55 +2789,55 @@
     <t xml:space="preserve">0.872050225734711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.898476004600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892646729946136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.881376922130585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942777991294861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939280450344086</t>
+    <t xml:space="preserve">0.89847606420517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892646789550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.881376981735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94277811050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939280569553375</t>
   </si>
   <si>
     <t xml:space="preserve">0.955213725566864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952493369579315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947441339492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952104806900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959488570690155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976198971271515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01700329780579</t>
+    <t xml:space="preserve">0.95249330997467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947441279888153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952104866504669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959488451480865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97619891166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01700341701508</t>
   </si>
   <si>
     <t xml:space="preserve">1.02205538749695</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993297874927521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98241662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975421667098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97658759355545</t>
+    <t xml:space="preserve">0.993297934532166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982416749000549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975421488285065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976587474346161</t>
   </si>
   <si>
     <t xml:space="preserve">0.997183978557587</t>
@@ -2846,28 +2846,28 @@
     <t xml:space="preserve">0.990966200828552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988245964050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984748423099518</t>
+    <t xml:space="preserve">0.988245904445648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984748244285583</t>
   </si>
   <si>
     <t xml:space="preserve">0.995629668235779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954825043678284</t>
+    <t xml:space="preserve">0.954825103282928</t>
   </si>
   <si>
     <t xml:space="preserve">1.00651073455811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01583743095398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0138943195343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03449094295502</t>
+    <t xml:space="preserve">1.01583755016327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01389443874359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03449106216431</t>
   </si>
   <si>
     <t xml:space="preserve">1.02399837970734</t>
@@ -2882,49 +2882,49 @@
     <t xml:space="preserve">1.03487956523895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01428294181824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0375999212265</t>
+    <t xml:space="preserve">1.01428306102753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03759980201721</t>
   </si>
   <si>
     <t xml:space="preserve">1.03215932846069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02050089836121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03099346160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06596863269806</t>
+    <t xml:space="preserve">1.02050077915192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03099358081818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06596875190735</t>
   </si>
   <si>
     <t xml:space="preserve">1.07296371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04653799533844</t>
+    <t xml:space="preserve">1.04653811454773</t>
   </si>
   <si>
     <t xml:space="preserve">1.0589736700058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0535329580307</t>
+    <t xml:space="preserve">1.05353307723999</t>
   </si>
   <si>
     <t xml:space="preserve">1.06169402599335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0449835062027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10871613025665</t>
+    <t xml:space="preserve">1.04498338699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10871624946594</t>
   </si>
   <si>
     <t xml:space="preserve">1.13630783557892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15418410301208</t>
+    <t xml:space="preserve">1.15418422222137</t>
   </si>
   <si>
     <t xml:space="preserve">1.12853562831879</t>
@@ -2933,7 +2933,7 @@
     <t xml:space="preserve">1.13825082778931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14252579212189</t>
+    <t xml:space="preserve">1.1425256729126</t>
   </si>
   <si>
     <t xml:space="preserve">1.17516922950745</t>
@@ -2942,34 +2942,34 @@
     <t xml:space="preserve">1.16195642948151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13863956928253</t>
+    <t xml:space="preserve">1.13863945007324</t>
   </si>
   <si>
     <t xml:space="preserve">1.12154054641724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13475358486176</t>
+    <t xml:space="preserve">1.13475346565247</t>
   </si>
   <si>
     <t xml:space="preserve">1.12698125839233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11415696144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10366439819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11221385002136</t>
+    <t xml:space="preserve">1.11415684223175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10366415977478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11221373081207</t>
   </si>
   <si>
     <t xml:space="preserve">1.09317171573639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0838451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11493420600891</t>
+    <t xml:space="preserve">1.08384501934052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11493408679962</t>
   </si>
   <si>
     <t xml:space="preserve">1.1071617603302</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">1.07918155193329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08656537532806</t>
+    <t xml:space="preserve">1.08656513690948</t>
   </si>
   <si>
     <t xml:space="preserve">1.0772385597229</t>
@@ -2990,16 +2990,16 @@
     <t xml:space="preserve">1.1308673620224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15262961387634</t>
+    <t xml:space="preserve">1.15262973308563</t>
   </si>
   <si>
     <t xml:space="preserve">1.14874362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15496146678925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1631224155426</t>
+    <t xml:space="preserve">1.15496134757996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16312217712402</t>
   </si>
   <si>
     <t xml:space="preserve">1.14563453197479</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">1.14641189575195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17089462280273</t>
+    <t xml:space="preserve">1.17089450359344</t>
   </si>
   <si>
     <t xml:space="preserve">1.18954801559448</t>
@@ -3020,31 +3020,31 @@
     <t xml:space="preserve">1.2047039270401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20664715766907</t>
+    <t xml:space="preserve">1.20664703845978</t>
   </si>
   <si>
     <t xml:space="preserve">1.21558523178101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2175281047821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20625841617584</t>
+    <t xml:space="preserve">1.21752834320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20625853538513</t>
   </si>
   <si>
     <t xml:space="preserve">1.20392680168152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20859014987946</t>
+    <t xml:space="preserve">1.20859003067017</t>
   </si>
   <si>
     <t xml:space="preserve">1.22413468360901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20975601673126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19809758663177</t>
+    <t xml:space="preserve">1.20975589752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19809746742249</t>
   </si>
   <si>
     <t xml:space="preserve">1.21286487579346</t>
@@ -3053,49 +3053,49 @@
     <t xml:space="preserve">1.21597373485565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2132533788681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20431530475616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21247625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22685515880585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21403086185455</t>
+    <t xml:space="preserve">1.21325349807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20431542396545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21247613430023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22685503959656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21403074264526</t>
   </si>
   <si>
     <t xml:space="preserve">1.2357931137085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2381249666214</t>
+    <t xml:space="preserve">1.23812484741211</t>
   </si>
   <si>
     <t xml:space="preserve">1.23851346969604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24278831481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26105308532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26455056667328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27582049369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26066446304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26493918895721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27892923355103</t>
+    <t xml:space="preserve">1.24278819561005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26105296611786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26455044746399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27582037448883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26066434383392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2649393081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27892935276031</t>
   </si>
   <si>
     <t xml:space="preserve">1.3045779466629</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">1.3174022436142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33061492443085</t>
+    <t xml:space="preserve">1.33061504364014</t>
   </si>
   <si>
     <t xml:space="preserve">1.34693682193756</t>
@@ -3128,397 +3128,397 @@
     <t xml:space="preserve">1.35121142864227</t>
   </si>
   <si>
+    <t xml:space="preserve">1.37258541584015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40067195892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37502765655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38194763660431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37787699699402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39497339725494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.391716837883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38438987731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39456629753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38886749744415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41044127941132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42305994033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43323636054993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45847368240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43852806091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43771398067474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4491114616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44951856136322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45725250244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45765948295593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45521724224091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43120110034943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44300556182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44422686100006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42713057994843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41858243942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40352141857147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41288375854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41695427894592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41898953914642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41329061985016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43527162075043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37950527667999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38072633743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39945089817047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41736125946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40392851829529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40148627758026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34734797477722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3591525554657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38316869735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.395787358284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45114684104919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47719812393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47801244258881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47394180297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47068536281586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47923338413239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46824312210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47964036464691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49348032474518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50691306591034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52360236644745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53866326808929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54069852828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55006086826324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58262503147125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58669567108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56593585014343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5838463306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5549453496933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53215038776398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52726590633392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52889382839203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52197408676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.514240026474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51912474632263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50650596618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49755084514618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52238118648529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49307334423065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51464712619781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5162752866745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48615348339081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48940968513489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49063086509705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42794454097748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45155382156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46173012256622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46213722229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4837110042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47882640361786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48411810398102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45643842220306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45562422275543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43812096118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44544804096222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44015622138977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45684540271759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48737454414368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48533928394318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50406360626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46417236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4450409412384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47475576400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49673676490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50894844532013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.502028465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48696756362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50365662574768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52970814704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53662800788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57407712936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55698072910309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55779469013214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50732016563416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48004758358002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49022388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49225914478302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.510169506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47760534286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50040030479431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50121426582336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51301884651184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51953184604645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51546120643616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3921240568161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4059636592865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39538037776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40637075901031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45196080207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43079400062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45806670188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45440304279327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45399618148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42835187911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39130973815918</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.37258529663086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40067207813263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37502765655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38194751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37787699699402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39497339725494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.391716837883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38438999652863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39456629753113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38886749744415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41044127941132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42306005954742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43323636054993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45847368240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43852806091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43771409988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44911134243011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44951856136322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45725238323212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45765972137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4552173614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43120098114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4430056810379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44422686100006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42713057994843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41858232021332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40352129936218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41288363933563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41695415973663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41898941993713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41329073905945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43527150154114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37950527667999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38072645664215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39945089817047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41736125946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40392851829529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40148615837097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34734809398651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35915267467499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38316881656647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.395787358284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4511467218399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47719812393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47801232337952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47394168376923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47068536281586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47923350334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46824288368225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47964060306549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49348032474518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50691306591034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52360224723816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53866314888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54069864749908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55006098747253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58262515068054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58669567108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56593585014343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58384644985199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55494546890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53215038776398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52726590633392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52889406681061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52197396755219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.514240026474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51912474632263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50650596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49755072593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52238118648529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49307322502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51464700698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51627540588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48615336418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48940968513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49063098430634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42794454097748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45155382156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46173012256622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46213710308075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4837110042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47882628440857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48411810398102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45643842220306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45562422275543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43812096118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44544804096222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44015622138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45684552192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48737454414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48533928394318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5040637254715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46417236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4450409412384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47475588321686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49673676490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50894844532013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50202834606171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48696756362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50365662574768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52970802783966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53662800788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57407701015472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55698072910309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55779480934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50732016563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48004746437073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49022388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49225914478302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.510169506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4776052236557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50040030479431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50121426582336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51301896572113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51953172683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51546132564545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3921240568161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40596377849579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39538037776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40637063980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45196080207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43079400062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45806658267975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45440304279327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45399606227875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42835175991058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39130985736847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37258517742157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32699525356293</t>
+    <t xml:space="preserve">1.32699537277222</t>
   </si>
   <si>
     <t xml:space="preserve">1.34531283378601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34775495529175</t>
+    <t xml:space="preserve">1.34775519371033</t>
   </si>
   <si>
     <t xml:space="preserve">1.36810779571533</t>
@@ -3527,22 +3527,22 @@
     <t xml:space="preserve">1.37177121639252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39741551876068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4002650976181</t>
+    <t xml:space="preserve">1.39741563796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40026497840881</t>
   </si>
   <si>
     <t xml:space="preserve">1.40677785873413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35548913478851</t>
+    <t xml:space="preserve">1.35548901557922</t>
   </si>
   <si>
     <t xml:space="preserve">1.35955965518951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35833847522736</t>
+    <t xml:space="preserve">1.35833835601807</t>
   </si>
   <si>
     <t xml:space="preserve">1.37462067604065</t>
@@ -3551,22 +3551,22 @@
     <t xml:space="preserve">1.36770057678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35589599609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35263967514038</t>
+    <t xml:space="preserve">1.35589611530304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35263979434967</t>
   </si>
   <si>
     <t xml:space="preserve">1.33310115337372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32414591312408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3530467748642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34164929389954</t>
+    <t xml:space="preserve">1.32414579391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35304665565491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34164917469025</t>
   </si>
   <si>
     <t xml:space="preserve">1.30664253234863</t>
@@ -3575,46 +3575,46 @@
     <t xml:space="preserve">1.3326940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3652583360672</t>
+    <t xml:space="preserve">1.36525845527649</t>
   </si>
   <si>
     <t xml:space="preserve">1.41532588005066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37380647659302</t>
+    <t xml:space="preserve">1.37380635738373</t>
   </si>
   <si>
     <t xml:space="preserve">1.36729371547699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37909817695618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37624895572662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36973583698273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33513629436493</t>
+    <t xml:space="preserve">1.37909829616547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37624883651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36973595619202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33513641357422</t>
   </si>
   <si>
     <t xml:space="preserve">1.30949199199677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28262650966644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30094408988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30542159080505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29036045074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26430916786194</t>
+    <t xml:space="preserve">1.28262639045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30094397068024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30542147159576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29036056995392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26430904865265</t>
   </si>
   <si>
     <t xml:space="preserve">1.28913938999176</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">1.28425467014313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28181231021881</t>
+    <t xml:space="preserve">1.28181219100952</t>
   </si>
   <si>
     <t xml:space="preserve">1.27652060985565</t>
@@ -3641,16 +3641,16 @@
     <t xml:space="preserve">1.22482478618622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.281405210495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3001297712326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25494682788849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22848832607269</t>
+    <t xml:space="preserve">1.28140532970428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30012989044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2549467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2284882068634</t>
   </si>
   <si>
     <t xml:space="preserve">1.19918048381805</t>
@@ -3659,22 +3659,22 @@
     <t xml:space="preserve">1.18249118328094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20243692398071</t>
+    <t xml:space="preserve">1.20243680477142</t>
   </si>
   <si>
     <t xml:space="preserve">1.25616800785065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24639868736267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2447704076767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23093056678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22238266468048</t>
+    <t xml:space="preserve">1.24639880657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24477052688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23093068599701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22238254547119</t>
   </si>
   <si>
     <t xml:space="preserve">1.22116136550903</t>
@@ -3689,22 +3689,22 @@
     <t xml:space="preserve">1.2508761882782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22563898563385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22808110713959</t>
+    <t xml:space="preserve">1.22563886642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22808122634888</t>
   </si>
   <si>
     <t xml:space="preserve">1.23540818691254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25698208808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27489244937897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25779616832733</t>
+    <t xml:space="preserve">1.2569819688797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27489233016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25779604911804</t>
   </si>
   <si>
     <t xml:space="preserve">1.26553010940552</t>
@@ -3716,7 +3716,7 @@
     <t xml:space="preserve">1.28751111030579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29768753051758</t>
+    <t xml:space="preserve">1.29768741130829</t>
   </si>
   <si>
     <t xml:space="preserve">1.2980945110321</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">1.36281609535217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35223257541656</t>
+    <t xml:space="preserve">1.35223269462585</t>
   </si>
   <si>
     <t xml:space="preserve">1.3571172952652</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">1.32129657268524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3245530128479</t>
+    <t xml:space="preserve">1.32455289363861</t>
   </si>
   <si>
     <t xml:space="preserve">1.33432233333588</t>
@@ -3764,13 +3764,13 @@
     <t xml:space="preserve">1.3286235332489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31193447113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3164119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35019743442535</t>
+    <t xml:space="preserve">1.31193435192108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31641185283661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35019731521606</t>
   </si>
   <si>
     <t xml:space="preserve">1.34653401374817</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">1.38561105728149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33147287368774</t>
+    <t xml:space="preserve">1.33147275447845</t>
   </si>
   <si>
     <t xml:space="preserve">1.36037373542786</t>
@@ -3794,10 +3794,10 @@
     <t xml:space="preserve">1.40272545814514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36872267723083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.378622174263</t>
+    <t xml:space="preserve">1.36872255802155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37862205505371</t>
   </si>
   <si>
     <t xml:space="preserve">1.38507843017578</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">1.3631272315979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35796201229095</t>
+    <t xml:space="preserve">1.35796225070953</t>
   </si>
   <si>
     <t xml:space="preserve">1.34504973888397</t>
@@ -3815,22 +3815,22 @@
     <t xml:space="preserve">1.32998502254486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31578147411346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30416023731232</t>
+    <t xml:space="preserve">1.31578135490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30416011810303</t>
   </si>
   <si>
     <t xml:space="preserve">1.33041560649872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31018602848053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31233811378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27058780193329</t>
+    <t xml:space="preserve">1.31018590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3123379945755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.270587682724</t>
   </si>
   <si>
     <t xml:space="preserve">1.18708693981171</t>
@@ -3839,34 +3839,34 @@
     <t xml:space="preserve">1.14921045303345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11047303676605</t>
+    <t xml:space="preserve">1.11047291755676</t>
   </si>
   <si>
     <t xml:space="preserve">1.15050172805786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11563801765442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15437531471252</t>
+    <t xml:space="preserve">1.11563789844513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15437543392181</t>
   </si>
   <si>
     <t xml:space="preserve">1.091104388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06570982933044</t>
+    <t xml:space="preserve">1.06570971012115</t>
   </si>
   <si>
     <t xml:space="preserve">1.03945434093475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05581021308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10143423080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08593940734863</t>
+    <t xml:space="preserve">1.05581033229828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10143435001373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08593928813934</t>
   </si>
   <si>
     <t xml:space="preserve">1.09540855884552</t>
@@ -3875,13 +3875,13 @@
     <t xml:space="preserve">1.07517886161804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04332804679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06743144989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06614005565643</t>
+    <t xml:space="preserve">1.043328166008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06743133068085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06614017486572</t>
   </si>
   <si>
     <t xml:space="preserve">1.04677140712738</t>
@@ -3899,10 +3899,10 @@
     <t xml:space="preserve">1.02697229385376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00200831890106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02352905273438</t>
+    <t xml:space="preserve">1.00200819969177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02352893352509</t>
   </si>
   <si>
     <t xml:space="preserve">1.05365812778473</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">1.03601109981537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04074573516846</t>
+    <t xml:space="preserve">1.04074561595917</t>
   </si>
   <si>
     <t xml:space="preserve">1.05451893806458</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">1.02955484390259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0588231086731</t>
+    <t xml:space="preserve">1.05882322788239</t>
   </si>
   <si>
     <t xml:space="preserve">1.08120477199554</t>
@@ -3938,10 +3938,10 @@
     <t xml:space="preserve">1.07474851608276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09024333953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06829226016998</t>
+    <t xml:space="preserve">1.09024357795715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06829237937927</t>
   </si>
   <si>
     <t xml:space="preserve">1.08636963367462</t>
@@ -3962,13 +3962,13 @@
     <t xml:space="preserve">1.10100388526917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10272562503815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08292639255524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06097507476807</t>
+    <t xml:space="preserve">1.10272550582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08292651176453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06097519397736</t>
   </si>
   <si>
     <t xml:space="preserve">1.06355774402618</t>
@@ -3977,58 +3977,58 @@
     <t xml:space="preserve">1.05839276313782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0170726776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996843218803406</t>
+    <t xml:space="preserve">1.01707279682159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996843278408051</t>
   </si>
   <si>
     <t xml:space="preserve">0.999425709247589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.963701188564301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946915030479431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968435883522034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945623695850372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932711362838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939167380332947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.920229136943817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965422809123993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975322425365448</t>
+    <t xml:space="preserve">0.963701248168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946915090084076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968435704708099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945623755455017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932711243629456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939167439937592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.920229196548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965422928333282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975322484970093</t>
   </si>
   <si>
     <t xml:space="preserve">0.952510416507721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92625504732132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930128812789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913342535495758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921950817108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923242151737213</t>
+    <t xml:space="preserve">0.92625492811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930128753185272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913342595100403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921950876712799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923242032527924</t>
   </si>
   <si>
     <t xml:space="preserve">0.912051260471344</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">0.882783055305481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888808906078339</t>
+    <t xml:space="preserve">0.888808846473694</t>
   </si>
   <si>
     <t xml:space="preserve">0.852567791938782</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">0.85377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860659599304199</t>
+    <t xml:space="preserve">0.860659718513489</t>
   </si>
   <si>
     <t xml:space="preserve">0.879339694976807</t>
@@ -4061,16 +4061,16 @@
     <t xml:space="preserve">0.868579208850861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.853256464004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835351169109344</t>
+    <t xml:space="preserve">0.853256404399872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8353511095047</t>
   </si>
   <si>
     <t xml:space="preserve">0.846542000770569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837244987487793</t>
+    <t xml:space="preserve">0.837245047092438</t>
   </si>
   <si>
     <t xml:space="preserve">0.820200502872467</t>
@@ -4082,28 +4082,28 @@
     <t xml:space="preserve">0.863844692707062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.883643865585327</t>
+    <t xml:space="preserve">0.883643805980682</t>
   </si>
   <si>
     <t xml:space="preserve">0.879770040512085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871161699295044</t>
+    <t xml:space="preserve">0.871161758899689</t>
   </si>
   <si>
     <t xml:space="preserve">0.896986782550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949497580528259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9482062458992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982209026813507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971018254756927</t>
+    <t xml:space="preserve">0.949497520923615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948206186294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982209086418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971018373966217</t>
   </si>
   <si>
     <t xml:space="preserve">0.965853273868561</t>
@@ -4115,13 +4115,13 @@
     <t xml:space="preserve">0.966283679008484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955092906951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972309589385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993830263614655</t>
+    <t xml:space="preserve">0.955092966556549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972309470176697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993830323219299</t>
   </si>
   <si>
     <t xml:space="preserve">1.0045907497406</t>
@@ -4133,7 +4133,7 @@
     <t xml:space="preserve">1.11176431179047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11606848239899</t>
+    <t xml:space="preserve">1.1160683631897</t>
   </si>
   <si>
     <t xml:space="preserve">1.12295508384705</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">1.10616886615753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12682890892029</t>
+    <t xml:space="preserve">1.126828789711</t>
   </si>
   <si>
     <t xml:space="preserve">1.1220942735672</t>
@@ -4157,13 +4157,13 @@
     <t xml:space="preserve">1.11391639709473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13974130153656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11865079402924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09928226470947</t>
+    <t xml:space="preserve">1.13974118232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11865091323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09928214550018</t>
   </si>
   <si>
     <t xml:space="preserve">1.11090350151062</t>
@@ -4172,25 +4172,25 @@
     <t xml:space="preserve">1.12898087501526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13586747646332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13027203083038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13543701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12381589412689</t>
+    <t xml:space="preserve">1.13586759567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13027215003967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13543713092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12381601333618</t>
   </si>
   <si>
     <t xml:space="preserve">1.11951184272766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12166392803192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1298416852951</t>
+    <t xml:space="preserve">1.12166380882263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12984180450439</t>
   </si>
   <si>
     <t xml:space="preserve">1.14490628242493</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">1.09282600879669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07603979110718</t>
+    <t xml:space="preserve">1.07603967189789</t>
   </si>
   <si>
     <t xml:space="preserve">1.08378720283508</t>
@@ -4214,34 +4214,34 @@
     <t xml:space="preserve">1.07173562049866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09971261024475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12467670440674</t>
+    <t xml:space="preserve">1.09971272945404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12467682361603</t>
   </si>
   <si>
     <t xml:space="preserve">1.12553763389587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13888049125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1470582485199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18837821483612</t>
+    <t xml:space="preserve">1.13888037204742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14705836772919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18837833404541</t>
   </si>
   <si>
     <t xml:space="preserve">1.19354331493378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19827783107758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20043003559113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20516443252563</t>
+    <t xml:space="preserve">1.19827771186829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20042991638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20516455173492</t>
   </si>
   <si>
     <t xml:space="preserve">1.21032953262329</t>
@@ -4250,19 +4250,19 @@
     <t xml:space="preserve">1.17245292663574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15093219280243</t>
+    <t xml:space="preserve">1.15093207359314</t>
   </si>
   <si>
     <t xml:space="preserve">1.18192207813263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19096088409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20387315750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20430374145508</t>
+    <t xml:space="preserve">1.19096076488495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20387327671051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20430386066437</t>
   </si>
   <si>
     <t xml:space="preserve">1.21119022369385</t>
@@ -4271,10 +4271,10 @@
     <t xml:space="preserve">1.19483458995819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18665659427643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20989906787872</t>
+    <t xml:space="preserve">1.18665671348572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20989918708801</t>
   </si>
   <si>
     <t xml:space="preserve">1.18794786930084</t>
@@ -4286,7 +4286,7 @@
     <t xml:space="preserve">1.21506404876709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20903813838959</t>
+    <t xml:space="preserve">1.20903825759888</t>
   </si>
   <si>
     <t xml:space="preserve">1.17632663249969</t>
@@ -4301,49 +4301,49 @@
     <t xml:space="preserve">1.18235242366791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19225192070007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17976999282837</t>
+    <t xml:space="preserve">1.19225203990936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17976987361908</t>
   </si>
   <si>
     <t xml:space="preserve">1.18579590320587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18966960906982</t>
+    <t xml:space="preserve">1.18966948986053</t>
   </si>
   <si>
     <t xml:space="preserve">1.20215165615082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20129072666168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16943991184235</t>
+    <t xml:space="preserve">1.20129084587097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16944003105164</t>
   </si>
   <si>
     <t xml:space="preserve">1.18364369869232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19784736633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18149161338806</t>
+    <t xml:space="preserve">1.1978474855423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18149149417877</t>
   </si>
   <si>
     <t xml:space="preserve">1.18493497371674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17503535747528</t>
+    <t xml:space="preserve">1.17503547668457</t>
   </si>
   <si>
     <t xml:space="preserve">1.16814875602722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15738844871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18278276920319</t>
+    <t xml:space="preserve">1.15738821029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18278288841248</t>
   </si>
   <si>
     <t xml:space="preserve">1.18321335315704</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">1.25078856945038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26240980625153</t>
+    <t xml:space="preserve">1.26240992546082</t>
   </si>
   <si>
     <t xml:space="preserve">1.23658490180969</t>
@@ -4361,7 +4361,7 @@
     <t xml:space="preserve">1.25294065475464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2395977973938</t>
+    <t xml:space="preserve">1.23959791660309</t>
   </si>
   <si>
     <t xml:space="preserve">1.23787605762482</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">1.21678566932678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22496366500854</t>
+    <t xml:space="preserve">1.22496354579926</t>
   </si>
   <si>
     <t xml:space="preserve">1.25121903419495</t>
@@ -4385,40 +4385,40 @@
     <t xml:space="preserve">1.26714444160461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29426062107086</t>
+    <t xml:space="preserve">1.29426074028015</t>
   </si>
   <si>
     <t xml:space="preserve">1.32869386672974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33256769180298</t>
+    <t xml:space="preserve">1.33256757259369</t>
   </si>
   <si>
     <t xml:space="preserve">1.33730220794678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31664228439331</t>
+    <t xml:space="preserve">1.31664216518402</t>
   </si>
   <si>
     <t xml:space="preserve">1.32137680053711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31922471523285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35150611400604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33988475799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35279703140259</t>
+    <t xml:space="preserve">1.31922483444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35150599479675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33988463878632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35279715061188</t>
   </si>
   <si>
     <t xml:space="preserve">1.35968375205994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35236668586731</t>
+    <t xml:space="preserve">1.3523668050766</t>
   </si>
   <si>
     <t xml:space="preserve">1.36614012718201</t>
@@ -4427,10 +4427,10 @@
     <t xml:space="preserve">1.37733089923859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34332799911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3678617477417</t>
+    <t xml:space="preserve">1.34332811832428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36786162853241</t>
   </si>
   <si>
     <t xml:space="preserve">1.36829221248627</t>
@@ -4451,28 +4451,28 @@
     <t xml:space="preserve">1.4311329126358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4560968875885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46728765964508</t>
+    <t xml:space="preserve">1.45609700679779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46728777885437</t>
   </si>
   <si>
     <t xml:space="preserve">1.44877994060516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43758904933929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37905251979828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41047275066376</t>
+    <t xml:space="preserve">1.43758916854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37905263900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41047286987305</t>
   </si>
   <si>
     <t xml:space="preserve">1.42495942115784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42905950546265</t>
+    <t xml:space="preserve">1.42905938625336</t>
   </si>
   <si>
     <t xml:space="preserve">1.39261531829834</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">1.39079320430756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38532650470734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40719306468964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41038191318512</t>
+    <t xml:space="preserve">1.38532662391663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40719294548035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41038179397583</t>
   </si>
   <si>
     <t xml:space="preserve">1.4313371181488</t>
@@ -4499,7 +4499,7 @@
     <t xml:space="preserve">1.45684790611267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4563924074173</t>
+    <t xml:space="preserve">1.45639228820801</t>
   </si>
   <si>
     <t xml:space="preserve">1.48235869407654</t>
@@ -4523,19 +4523,19 @@
     <t xml:space="preserve">1.50103628635406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50786936283112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51743614673615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50012505054474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50376951694489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4768922328949</t>
+    <t xml:space="preserve">1.50786948204041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51743602752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50012516975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50376963615417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47689211368561</t>
   </si>
   <si>
     <t xml:space="preserve">1.49784743785858</t>
@@ -4544,13 +4544,13 @@
     <t xml:space="preserve">1.49420297145844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50695836544037</t>
+    <t xml:space="preserve">1.50695848464966</t>
   </si>
   <si>
     <t xml:space="preserve">1.51652491092682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52563583850861</t>
+    <t xml:space="preserve">1.5256359577179</t>
   </si>
   <si>
     <t xml:space="preserve">1.5242692232132</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">1.54112458229065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53975808620453</t>
+    <t xml:space="preserve">1.53975796699524</t>
   </si>
   <si>
     <t xml:space="preserve">1.52153599262238</t>
@@ -4586,7 +4586,7 @@
     <t xml:space="preserve">1.53064692020416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53383588790894</t>
+    <t xml:space="preserve">1.53383576869965</t>
   </si>
   <si>
     <t xml:space="preserve">1.53520238399506</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">1.54750227928162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55433559417725</t>
+    <t xml:space="preserve">1.55433547496796</t>
   </si>
   <si>
     <t xml:space="preserve">1.56435763835907</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">1.55160212516785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58121287822723</t>
+    <t xml:space="preserve">1.58121299743652</t>
   </si>
   <si>
     <t xml:space="preserve">1.57939076423645</t>
@@ -4616,10 +4616,10 @@
     <t xml:space="preserve">1.54249119758606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51470267772675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5110582113266</t>
+    <t xml:space="preserve">1.51470279693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51105833053589</t>
   </si>
   <si>
     <t xml:space="preserve">1.49921405315399</t>
@@ -4634,13 +4634,13 @@
     <t xml:space="preserve">1.54886901378632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56709098815918</t>
+    <t xml:space="preserve">1.56709086894989</t>
   </si>
   <si>
     <t xml:space="preserve">1.52335822582245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52836930751801</t>
+    <t xml:space="preserve">1.52836918830872</t>
   </si>
   <si>
     <t xml:space="preserve">1.54613566398621</t>
@@ -4652,37 +4652,37 @@
     <t xml:space="preserve">1.57210195064545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58349072933197</t>
+    <t xml:space="preserve">1.58349084854126</t>
   </si>
   <si>
     <t xml:space="preserve">1.58622407913208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60581278800964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59487950801849</t>
+    <t xml:space="preserve">1.60581266880035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5948793888092</t>
   </si>
   <si>
     <t xml:space="preserve">1.61219036579132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59214603900909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57984638214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56481313705444</t>
+    <t xml:space="preserve">1.59214615821838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57984626293182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56481325626373</t>
   </si>
   <si>
     <t xml:space="preserve">1.59123516082764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60034608840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61310148239136</t>
+    <t xml:space="preserve">1.60034596920013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61310136318207</t>
   </si>
   <si>
     <t xml:space="preserve">1.63041234016418</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">1.70056700706482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6345123052597</t>
+    <t xml:space="preserve">1.63451242446899</t>
   </si>
   <si>
     <t xml:space="preserve">1.5994348526001</t>
@@ -4724,25 +4724,25 @@
     <t xml:space="preserve">1.51060271263123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53611361980438</t>
+    <t xml:space="preserve">1.53611350059509</t>
   </si>
   <si>
     <t xml:space="preserve">1.48828089237213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50285851955414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.521080493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55889093875885</t>
+    <t xml:space="preserve">1.50285840034485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52108037471771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55889105796814</t>
   </si>
   <si>
     <t xml:space="preserve">1.56800198554993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58440172672272</t>
+    <t xml:space="preserve">1.58440184593201</t>
   </si>
   <si>
     <t xml:space="preserve">1.57893526554108</t>
@@ -4757,10 +4757,10 @@
     <t xml:space="preserve">1.54659116268158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57756853103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57620203495026</t>
+    <t xml:space="preserve">1.57756865024567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57620191574097</t>
   </si>
   <si>
     <t xml:space="preserve">1.59761273860931</t>
@@ -4769,37 +4769,37 @@
     <t xml:space="preserve">1.60125720500946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61355710029602</t>
+    <t xml:space="preserve">1.61355698108673</t>
   </si>
   <si>
     <t xml:space="preserve">1.63724565505981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.633145570755</t>
+    <t xml:space="preserve">1.63314568996429</t>
   </si>
   <si>
     <t xml:space="preserve">1.63223457336426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62767899036407</t>
+    <t xml:space="preserve">1.62767910957336</t>
   </si>
   <si>
     <t xml:space="preserve">1.6167459487915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61765694618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63177907466888</t>
+    <t xml:space="preserve">1.61765706539154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63177895545959</t>
   </si>
   <si>
     <t xml:space="preserve">1.69601154327393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71742224693298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.761155128479</t>
+    <t xml:space="preserve">1.71742236614227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76115500926971</t>
   </si>
   <si>
     <t xml:space="preserve">1.7597883939743</t>
@@ -4829,7 +4829,7 @@
     <t xml:space="preserve">1.79031038284302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79759919643402</t>
+    <t xml:space="preserve">1.79759907722473</t>
   </si>
   <si>
     <t xml:space="preserve">1.79167699813843</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">1.77709937095642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78256607055664</t>
+    <t xml:space="preserve">1.78256595134735</t>
   </si>
   <si>
     <t xml:space="preserve">1.77846598625183</t>
@@ -4847,16 +4847,16 @@
     <t xml:space="preserve">1.78211033344269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78712141513824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77618813514709</t>
+    <t xml:space="preserve">1.78712153434753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77618825435638</t>
   </si>
   <si>
     <t xml:space="preserve">1.74384427070618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77208840847015</t>
+    <t xml:space="preserve">1.77208828926086</t>
   </si>
   <si>
     <t xml:space="preserve">1.79805469512939</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">1.74019980430603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71377789974213</t>
+    <t xml:space="preserve">1.71377801895142</t>
   </si>
   <si>
     <t xml:space="preserve">1.6964670419693</t>
@@ -4889,10 +4889,10 @@
     <t xml:space="preserve">1.68280053138733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67778956890106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71651124954224</t>
+    <t xml:space="preserve">1.67778944969177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71651113033295</t>
   </si>
   <si>
     <t xml:space="preserve">1.72061121463776</t>
@@ -4901,10 +4901,10 @@
     <t xml:space="preserve">1.73792207241058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74247765541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74703299999237</t>
+    <t xml:space="preserve">1.74247753620148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74703311920166</t>
   </si>
   <si>
     <t xml:space="preserve">1.69692254066467</t>
@@ -4925,10 +4925,10 @@
     <t xml:space="preserve">1.64453434944153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66184520721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64225661754608</t>
+    <t xml:space="preserve">1.66184532642365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64225673675537</t>
   </si>
   <si>
     <t xml:space="preserve">1.59897947311401</t>
@@ -4937,7 +4937,7 @@
     <t xml:space="preserve">1.62995684146881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62859010696411</t>
+    <t xml:space="preserve">1.6285902261734</t>
   </si>
   <si>
     <t xml:space="preserve">1.66321194171906</t>
@@ -4946,10 +4946,10 @@
     <t xml:space="preserve">1.67687833309174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60307931900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56936872005463</t>
+    <t xml:space="preserve">1.60307943820953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56936860084534</t>
   </si>
   <si>
     <t xml:space="preserve">1.55296885967255</t>
@@ -4958,13 +4958,13 @@
     <t xml:space="preserve">1.5124249458313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51014733314514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49238073825836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48964750766754</t>
+    <t xml:space="preserve">1.51014721393585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49238085746765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48964738845825</t>
   </si>
   <si>
     <t xml:space="preserve">1.51698040962219</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">1.55023562908173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55114662647247</t>
+    <t xml:space="preserve">1.55114674568176</t>
   </si>
   <si>
     <t xml:space="preserve">1.54066896438599</t>
@@ -4988,7 +4988,7 @@
     <t xml:space="preserve">1.53839135169983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52518045902252</t>
+    <t xml:space="preserve">1.52518033981323</t>
   </si>
   <si>
     <t xml:space="preserve">1.51288056373596</t>
@@ -5003,13 +5003,13 @@
     <t xml:space="preserve">1.58212411403656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59533500671387</t>
+    <t xml:space="preserve">1.59533512592316</t>
   </si>
   <si>
     <t xml:space="preserve">1.53748023509979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49602508544922</t>
+    <t xml:space="preserve">1.49602520465851</t>
   </si>
   <si>
     <t xml:space="preserve">1.50468063354492</t>
@@ -5018,13 +5018,13 @@
     <t xml:space="preserve">1.50149178504944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49556970596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47279214859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49283623695374</t>
+    <t xml:space="preserve">1.49556958675385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47279226779938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49283635616302</t>
   </si>
   <si>
     <t xml:space="preserve">1.52472484111786</t>
@@ -5036,7 +5036,7 @@
     <t xml:space="preserve">1.50422501564026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47370314598083</t>
+    <t xml:space="preserve">1.47370326519012</t>
   </si>
   <si>
     <t xml:space="preserve">1.50331389904022</t>
@@ -5045,7 +5045,7 @@
     <t xml:space="preserve">1.5051361322403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48418092727661</t>
+    <t xml:space="preserve">1.48418080806732</t>
   </si>
   <si>
     <t xml:space="preserve">1.49966955184937</t>
@@ -5054,7 +5054,7 @@
     <t xml:space="preserve">1.57574641704559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59624600410461</t>
+    <t xml:space="preserve">1.5962461233139</t>
   </si>
   <si>
     <t xml:space="preserve">1.65592312812805</t>
@@ -5069,19 +5069,19 @@
     <t xml:space="preserve">1.70694470405579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.690544962883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7142333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69464492797852</t>
+    <t xml:space="preserve">1.69054484367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71423351764679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69464480876923</t>
   </si>
   <si>
     <t xml:space="preserve">1.71241128444672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72380006313324</t>
+    <t xml:space="preserve">1.72379994392395</t>
   </si>
   <si>
     <t xml:space="preserve">1.74156641960144</t>
@@ -5090,7 +5090,7 @@
     <t xml:space="preserve">1.74794411659241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75341081619263</t>
+    <t xml:space="preserve">1.75341069698334</t>
   </si>
   <si>
     <t xml:space="preserve">1.7921324968338</t>
@@ -5105,7 +5105,7 @@
     <t xml:space="preserve">1.84497630596161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83586525917053</t>
+    <t xml:space="preserve">1.83586537837982</t>
   </si>
   <si>
     <t xml:space="preserve">1.84284818172455</t>
@@ -5976,6 +5976,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.71199989318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70900011062622</t>
   </si>
 </sst>
 </file>
@@ -71392,7 +71395,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6912847222</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>10615422</v>
@@ -71413,6 +71416,32 @@
         <v>1987</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6943287037</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>6207128</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>2.73399996757507</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>2.69799995422363</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>2.70900011062622</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1988</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -38,94 +38,94 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765547692775726</t>
+    <t xml:space="preserve">0.765547633171082</t>
   </si>
   <si>
     <t xml:space="preserve">A2A.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.7743039727211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769300401210785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777431130409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772427618503571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775554895401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736151695251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728020846843719</t>
+    <t xml:space="preserve">0.774304032325745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76930034160614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77743124961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772427558898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775554835796356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73615163564682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728020906448364</t>
   </si>
   <si>
     <t xml:space="preserve">0.708631932735443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.701126635074615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.678610503673553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.686115860939026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.662974238395691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.669854164123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.673606932163239</t>
+    <t xml:space="preserve">0.70112669467926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678610444068909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.686115920543671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.662974298000336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.66985422372818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.673606991767883</t>
   </si>
   <si>
     <t xml:space="preserve">0.661723375320435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689868569374084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.667352437973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.688617587089539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689243137836456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.676108658313751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.671105086803436</t>
+    <t xml:space="preserve">0.68986850976944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.667352497577667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.688617706298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689243018627167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.676108717918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.671105027198792</t>
   </si>
   <si>
     <t xml:space="preserve">0.66672694683075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643585443496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612313032150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597927689552307</t>
+    <t xml:space="preserve">0.643585503101349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612312972545624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597927808761597</t>
   </si>
   <si>
     <t xml:space="preserve">0.605745851993561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610749423503876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614189386367798</t>
+    <t xml:space="preserve">0.610749363899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614189445972443</t>
   </si>
   <si>
     <t xml:space="preserve">0.627323865890503</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">0.636080026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656719744205475</t>
+    <t xml:space="preserve">0.656719863414764</t>
   </si>
   <si>
     <t xml:space="preserve">0.645461797714233</t>
@@ -152,40 +152,40 @@
     <t xml:space="preserve">0.641083598136902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647963464260101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.657345294952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661097943782806</t>
+    <t xml:space="preserve">0.647963583469391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.657345235347748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661098122596741</t>
   </si>
   <si>
     <t xml:space="preserve">0.672981441020966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666101574897766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.664850652217865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658596098423004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651716351509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65484356880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.669228851795197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713010132312775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692995846271515</t>
+    <t xml:space="preserve">0.666101515293121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.664850533008575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658596158027649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651716232299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654843509197235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.669228792190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713010013103485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69299578666687</t>
   </si>
   <si>
     <t xml:space="preserve">0.691119432449341</t>
@@ -194,37 +194,37 @@
     <t xml:space="preserve">0.694246649742126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69799941778183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69612318277359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703002870082855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692370355129242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.699250221252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714260935783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714886367321014</t>
+    <t xml:space="preserve">0.697999358177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696123003959656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692370295524597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.699250161647797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714261054992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714886486530304</t>
   </si>
   <si>
     <t xml:space="preserve">0.702377557754517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.705504655838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735526323318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.740529775619507</t>
+    <t xml:space="preserve">0.705504715442657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735526204109192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.740529656410217</t>
   </si>
   <si>
     <t xml:space="preserve">0.74428254365921</t>
@@ -236,13 +236,13 @@
     <t xml:space="preserve">0.738027989864349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.750536918640137</t>
+    <t xml:space="preserve">0.750537097454071</t>
   </si>
   <si>
     <t xml:space="preserve">0.754289627075195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.768049418926239</t>
+    <t xml:space="preserve">0.768049538135529</t>
   </si>
   <si>
     <t xml:space="preserve">0.757416844367981</t>
@@ -251,103 +251,103 @@
     <t xml:space="preserve">0.766798496246338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.752413272857666</t>
+    <t xml:space="preserve">0.752413213253021</t>
   </si>
   <si>
     <t xml:space="preserve">0.781183779239655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778056442737579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786187469959259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779307544231415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768674910068512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755540549755096</t>
+    <t xml:space="preserve">0.778056621551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786187350749969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779307663440704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768675029277802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755540430545807</t>
   </si>
   <si>
     <t xml:space="preserve">0.760544061660767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.76429682970047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770551323890686</t>
+    <t xml:space="preserve">0.764296770095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770551264286041</t>
   </si>
   <si>
     <t xml:space="preserve">0.759293258190155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769925773143768</t>
+    <t xml:space="preserve">0.769925832748413</t>
   </si>
   <si>
     <t xml:space="preserve">0.761169493198395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.767423987388611</t>
+    <t xml:space="preserve">0.767424046993256</t>
   </si>
   <si>
     <t xml:space="preserve">0.747409760951996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.751787841320038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754915058612823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781809270381927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801198065280914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804950714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799321830272675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785562038421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796820044517517</t>
+    <t xml:space="preserve">0.751787781715393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754915177822113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781809210777283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801198244094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804950833320618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79932177066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78556215763092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796820104122162</t>
   </si>
   <si>
     <t xml:space="preserve">0.791816473007202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801823496818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733649849891663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725519061088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766306579113007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759828805923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750760078430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778613984584808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703473210334778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692461252212524</t>
+    <t xml:space="preserve">0.801823556423187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733649909496307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725519001483917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766306459903717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759828746318817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750760018825531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778613924980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703473091125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692461311817169</t>
   </si>
   <si>
     <t xml:space="preserve">0.705416560173035</t>
@@ -362,55 +362,55 @@
     <t xml:space="preserve">0.762419939041138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769545316696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757885575294495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742986917495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742339193820953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.758533298969269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777318477630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77407968044281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776022970676422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78379613161087</t>
+    <t xml:space="preserve">0.769545257091522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75788551568985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742986738681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742339134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758533358573914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777318596839905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774079740047455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776022911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783796191215515</t>
   </si>
   <si>
     <t xml:space="preserve">0.779909551143646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79027384519577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789625942707062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794160306453705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805172324180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807763516902924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.822662115097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817479908466339</t>
+    <t xml:space="preserve">0.790273725986481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789626002311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79416024684906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805172502994537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807763457298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.822662055492401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817480027675629</t>
   </si>
   <si>
     <t xml:space="preserve">0.820718705654144</t>
@@ -422,19 +422,19 @@
     <t xml:space="preserve">0.809706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814241111278534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816184341907501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804524660110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801285743713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812945485115051</t>
+    <t xml:space="preserve">0.814241051673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816184461116791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804524600505829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801285862922668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812945544719696</t>
   </si>
   <si>
     <t xml:space="preserve">0.801933586597443</t>
@@ -446,31 +446,31 @@
     <t xml:space="preserve">0.788330435752869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771488547325134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783148407936096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782500624656677</t>
+    <t xml:space="preserve">0.771488606929779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783148348331451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782500565052032</t>
   </si>
   <si>
     <t xml:space="preserve">0.781852841377258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.770193159580231</t>
+    <t xml:space="preserve">0.770192980766296</t>
   </si>
   <si>
     <t xml:space="preserve">0.785091578960419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.795455873012543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811002314090729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794808089733124</t>
+    <t xml:space="preserve">0.795455932617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811002373695374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794808149337769</t>
   </si>
   <si>
     <t xml:space="preserve">0.796103656291962</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">0.798694789409637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.802581310272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790921568870544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796751499176025</t>
+    <t xml:space="preserve">0.802581250667572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790921449661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796751439571381</t>
   </si>
   <si>
     <t xml:space="preserve">0.799342453479767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.810354590415955</t>
+    <t xml:space="preserve">0.81035453081131</t>
   </si>
   <si>
     <t xml:space="preserve">0.780557334423065</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">0.784443855285645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785739421844482</t>
+    <t xml:space="preserve">0.785739481449127</t>
   </si>
   <si>
     <t xml:space="preserve">0.827196419239044</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">0.81359338760376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800637900829315</t>
+    <t xml:space="preserve">0.80063784122467</t>
   </si>
   <si>
     <t xml:space="preserve">0.797399163246155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803876936435699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807115733623505</t>
+    <t xml:space="preserve">0.803876876831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807115912437439</t>
   </si>
   <si>
     <t xml:space="preserve">0.76112425327301</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">0.770840883255005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73132711648941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735861480236053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.720315039157867</t>
+    <t xml:space="preserve">0.731327176094055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735861539840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.720315158367157</t>
   </si>
   <si>
     <t xml:space="preserve">0.72161066532135</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">0.709950923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.713837504386902</t>
+    <t xml:space="preserve">0.713837444782257</t>
   </si>
   <si>
     <t xml:space="preserve">0.711894154548645</t>
@@ -560,49 +560,49 @@
     <t xml:space="preserve">0.707359790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.728736042976379</t>
+    <t xml:space="preserve">0.728735983371735</t>
   </si>
   <si>
     <t xml:space="preserve">0.715780735015869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722258388996124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765010893344879</t>
+    <t xml:space="preserve">0.722258448600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765010952949524</t>
   </si>
   <si>
     <t xml:space="preserve">0.7546466588974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.755294501781464</t>
+    <t xml:space="preserve">0.755294382572174</t>
   </si>
   <si>
     <t xml:space="preserve">0.787682712078094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776670694351196</t>
+    <t xml:space="preserve">0.776670634746552</t>
   </si>
   <si>
     <t xml:space="preserve">0.772136390209198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.78703498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816832184791565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819423198699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799990296363831</t>
+    <t xml:space="preserve">0.787034928798676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81683224439621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819423258304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799990236759186</t>
   </si>
   <si>
     <t xml:space="preserve">0.824605286121368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838856160640717</t>
+    <t xml:space="preserve">0.838856101036072</t>
   </si>
   <si>
     <t xml:space="preserve">0.831730842590332</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">0.840151727199554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.848572671413422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841447174549103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844686150550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83043509721756</t>
+    <t xml:space="preserve">0.848572492599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841447293758392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844686090946198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830435156822205</t>
   </si>
   <si>
     <t xml:space="preserve">0.798047006130219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.815536618232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82007098197937</t>
+    <t xml:space="preserve">0.815536677837372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820071041584015</t>
   </si>
   <si>
     <t xml:space="preserve">0.806467890739441</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">0.836265087127686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.844038248062134</t>
+    <t xml:space="preserve">0.844038307666779</t>
   </si>
   <si>
     <t xml:space="preserve">0.837560653686523</t>
@@ -653,58 +653,58 @@
     <t xml:space="preserve">0.836912870407104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.821366488933563</t>
+    <t xml:space="preserve">0.821366548538208</t>
   </si>
   <si>
     <t xml:space="preserve">0.828491926193237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825900852680206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829139649868011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84662926197052</t>
+    <t xml:space="preserve">0.825900912284851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829139709472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84662938117981</t>
   </si>
   <si>
     <t xml:space="preserve">0.849220454692841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.864766776561737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867357850074768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868005692958832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870596587657928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857641398906708</t>
+    <t xml:space="preserve">0.864766836166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867357730865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868005812168121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870596647262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857641339302063</t>
   </si>
   <si>
     <t xml:space="preserve">0.865414619445801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866710186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85310697555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855698049068451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858289122581482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860232532024384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872540056705475</t>
+    <t xml:space="preserve">0.866710245609283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.853107035160065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855698108673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858289241790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860232353210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87254011631012</t>
   </si>
   <si>
     <t xml:space="preserve">0.874483287334442</t>
@@ -713,208 +713,208 @@
     <t xml:space="preserve">0.887438595294952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.893916249275208</t>
+    <t xml:space="preserve">0.893916130065918</t>
   </si>
   <si>
     <t xml:space="preserve">0.892620861530304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.912701487541199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909462571144104</t>
+    <t xml:space="preserve">0.912701547145844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909462630748749</t>
   </si>
   <si>
     <t xml:space="preserve">0.908166944980621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919826865196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918531239032745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875778913497925</t>
+    <t xml:space="preserve">0.919826745986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918531179428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875778794288635</t>
   </si>
   <si>
     <t xml:space="preserve">0.877722203731537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.891972959041595</t>
+    <t xml:space="preserve">0.891972839832306</t>
   </si>
   <si>
     <t xml:space="preserve">0.884847581386566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895211637020111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884199857711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876426577568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862175822257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85634583234787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882256388664246</t>
+    <t xml:space="preserve">0.895211756229401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884199738502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876426696777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862175703048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856345891952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88225644826889</t>
   </si>
   <si>
     <t xml:space="preserve">0.899098336696625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.890677392482758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926952362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91529244184494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917235910892487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966465890407562</t>
+    <t xml:space="preserve">0.890677452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926952183246613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915292382240295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917235791683197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966466069221497</t>
   </si>
   <si>
     <t xml:space="preserve">0.958045065402985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965170383453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961283922195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963227152824402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94185084104538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941203117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958692908287048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982278227806091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988308429718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997019052505493</t>
+    <t xml:space="preserve">0.965170621871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9612837433815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963227093219757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941850781440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941202998161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958692789077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982278108596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988308548927307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997018933296204</t>
   </si>
   <si>
     <t xml:space="preserve">1.00036919116974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.992998659610748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968207180500031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981608271598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986298263072968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988978385925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989648520946503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97490781545639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999699175357819</t>
+    <t xml:space="preserve">0.992998838424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968207359313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981608152389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986298441886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988978564739227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989648640155792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.974907696247101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999699056148529</t>
   </si>
   <si>
     <t xml:space="preserve">1.00505948066711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998359262943268</t>
+    <t xml:space="preserve">0.998359143733978</t>
   </si>
   <si>
     <t xml:space="preserve">0.997689127922058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00170934200287</t>
+    <t xml:space="preserve">1.00170946121216</t>
   </si>
   <si>
     <t xml:space="preserve">1.00706970691681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02047049999237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02985107898712</t>
+    <t xml:space="preserve">1.02047026157379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02985095977783</t>
   </si>
   <si>
     <t xml:space="preserve">1.0177903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995008945465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999029338359833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976917803287506</t>
+    <t xml:space="preserve">0.995009124279022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999029219150543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976917862892151</t>
   </si>
   <si>
     <t xml:space="preserve">0.974237740039825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97021746635437</t>
+    <t xml:space="preserve">0.970217525959015</t>
   </si>
   <si>
     <t xml:space="preserve">0.96552711725235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960837006568909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961506903171539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964187204837799</t>
+    <t xml:space="preserve">0.960836946964264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961507022380829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96418708562851</t>
   </si>
   <si>
     <t xml:space="preserve">0.980268180370331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978927969932556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984958291053772</t>
+    <t xml:space="preserve">0.978927850723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984958350658417</t>
   </si>
   <si>
     <t xml:space="preserve">0.97289764881134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960166811943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958826720714569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951456427574158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955476462841034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949446260929108</t>
+    <t xml:space="preserve">0.960166871547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958826899528503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951456248760223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955476522445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949446320533752</t>
   </si>
   <si>
     <t xml:space="preserve">0.963517069816589</t>
@@ -923,28 +923,28 @@
     <t xml:space="preserve">0.950116217136383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953466475009918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956816554069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958156585693359</t>
+    <t xml:space="preserve">0.953466415405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956816613674164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958156704902649</t>
   </si>
   <si>
     <t xml:space="preserve">0.952796518802643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962177097797394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944755971431732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931355118751526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948106288909912</t>
+    <t xml:space="preserve">0.962176918983459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944755852222443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931355237960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948106110095978</t>
   </si>
   <si>
     <t xml:space="preserve">0.954136490821838</t>
@@ -953,37 +953,37 @@
     <t xml:space="preserve">0.957486629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939395666122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946766078472137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934705436229706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928675055503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92465478181839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932695209980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945426106452942</t>
+    <t xml:space="preserve">0.939395546913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946766197681427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934705317020416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9286749958992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9246546626091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932695269584656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945425987243652</t>
   </si>
   <si>
     <t xml:space="preserve">0.959496796131134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973567724227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978257954120636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993668854236603</t>
+    <t xml:space="preserve">0.973567605018616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978258013725281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993668735027313</t>
   </si>
   <si>
     <t xml:space="preserve">0.984288275241852</t>
@@ -992,37 +992,37 @@
     <t xml:space="preserve">0.983618319034576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994338870048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977587878704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980938255786896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972227513790131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96619725227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969547510147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968877255916595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971557557582855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995678842067719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992328643798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966867208480835</t>
+    <t xml:space="preserve">0.994338929653168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977587938308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980938017368317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972227454185486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966197192668915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96954745054245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96887743473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97155749797821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995678901672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992328882217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966867327690125</t>
   </si>
   <si>
     <t xml:space="preserve">1.02114045619965</t>
@@ -1031,58 +1031,58 @@
     <t xml:space="preserve">1.01041996479034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01444005966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02181041240692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02382063865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02851092815399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03320133686066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03923153877258</t>
+    <t xml:space="preserve">1.01443994045258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02181053161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02382051944733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0285108089447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03320109844208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03923165798187</t>
   </si>
   <si>
     <t xml:space="preserve">1.02650082111359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0553126335144</t>
+    <t xml:space="preserve">1.05531251430511</t>
   </si>
   <si>
     <t xml:space="preserve">1.05866265296936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04459202289581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.053302526474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06804323196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07273352146149</t>
+    <t xml:space="preserve">1.04459190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05330240726471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0680433511734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0727334022522</t>
   </si>
   <si>
     <t xml:space="preserve">1.08613431453705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09551477432251</t>
+    <t xml:space="preserve">1.0955148935318</t>
   </si>
   <si>
     <t xml:space="preserve">1.08345413208008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08211410045624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05397248268127</t>
+    <t xml:space="preserve">1.08211398124695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05397236347198</t>
   </si>
   <si>
     <t xml:space="preserve">1.06000280380249</t>
@@ -1091,13 +1091,13 @@
     <t xml:space="preserve">1.04392182826996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04861223697662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04660189151764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03990161418915</t>
+    <t xml:space="preserve">1.04861199855804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04660212993622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03990149497986</t>
   </si>
   <si>
     <t xml:space="preserve">1.04258179664612</t>
@@ -1106,10 +1106,10 @@
     <t xml:space="preserve">1.01980042457581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.015780210495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05196237564087</t>
+    <t xml:space="preserve">1.01578032970428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05196249485016</t>
   </si>
   <si>
     <t xml:space="preserve">1.06737327575684</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">1.066033244133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02449059486389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01846027374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02784085273743</t>
+    <t xml:space="preserve">1.02449071407318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01846039295197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02784097194672</t>
   </si>
   <si>
     <t xml:space="preserve">1.05665266513824</t>
@@ -1133,40 +1133,40 @@
     <t xml:space="preserve">1.06134283542633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07742369174957</t>
+    <t xml:space="preserve">1.07742381095886</t>
   </si>
   <si>
     <t xml:space="preserve">1.07943391799927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06938350200653</t>
+    <t xml:space="preserve">1.06938314437866</t>
   </si>
   <si>
     <t xml:space="preserve">1.05933272838593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03856158256531</t>
+    <t xml:space="preserve">1.03856134414673</t>
   </si>
   <si>
     <t xml:space="preserve">1.02683579921722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03588151931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04191172122955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996349036693573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971222579479218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995343923568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94442081451416</t>
+    <t xml:space="preserve">1.03588140010834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04191160202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996348977088928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971222400665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995343804359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944421052932739</t>
   </si>
   <si>
     <t xml:space="preserve">0.953131496906281</t>
@@ -1175,34 +1175,34 @@
     <t xml:space="preserve">0.941405773162842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959831833839417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9464311003685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957821726799011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950451254844666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936380386352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967202305793762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991323590278625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975577712059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993333876132965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0000342130661</t>
+    <t xml:space="preserve">0.959831953048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94643098115921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957821786403656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95045131444931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936380565166473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967202246189117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99132364988327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975577771663666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99333381652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00003433227539</t>
   </si>
   <si>
     <t xml:space="preserve">1.00137448310852</t>
@@ -1214,43 +1214,43 @@
     <t xml:space="preserve">1.00673472881317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999364197254181</t>
+    <t xml:space="preserve">0.999364256858826</t>
   </si>
   <si>
     <t xml:space="preserve">1.04023659229279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04157662391663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04224669933319</t>
+    <t xml:space="preserve">1.04157674312592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04224681854248</t>
   </si>
   <si>
     <t xml:space="preserve">1.04961705207825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04995214939117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06268298625946</t>
+    <t xml:space="preserve">1.04995238780975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06268286705017</t>
   </si>
   <si>
     <t xml:space="preserve">1.07206344604492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05832755565643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06335306167603</t>
+    <t xml:space="preserve">1.05832779407501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06335282325745</t>
   </si>
   <si>
     <t xml:space="preserve">1.07407367229462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08043873310089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08546423912048</t>
+    <t xml:space="preserve">1.08043897151947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08546447753906</t>
   </si>
   <si>
     <t xml:space="preserve">1.09048962593079</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">1.09484481811523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09819519519806</t>
+    <t xml:space="preserve">1.09819507598877</t>
   </si>
   <si>
     <t xml:space="preserve">1.09853005409241</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">1.11762607097626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11729109287262</t>
+    <t xml:space="preserve">1.11729121208191</t>
   </si>
   <si>
     <t xml:space="preserve">1.10724067687988</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">1.10757565498352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12265169620514</t>
+    <t xml:space="preserve">1.12265145778656</t>
   </si>
   <si>
     <t xml:space="preserve">1.13002181053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10992097854614</t>
+    <t xml:space="preserve">1.10992085933685</t>
   </si>
   <si>
     <t xml:space="preserve">1.11829614639282</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">1.05732262134552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03387129306793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0389529466629</t>
+    <t xml:space="preserve">1.03387117385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03895282745361</t>
   </si>
   <si>
     <t xml:space="preserve">1.05287516117096</t>
@@ -1307,37 +1307,37 @@
     <t xml:space="preserve">1.04208540916443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04730618000031</t>
+    <t xml:space="preserve">1.04730629920959</t>
   </si>
   <si>
     <t xml:space="preserve">1.02572667598724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00693154335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980827152729034</t>
+    <t xml:space="preserve">1.00693142414093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980827271938324</t>
   </si>
   <si>
     <t xml:space="preserve">0.998926162719727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01076018810272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00484335422516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02920722961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00936782360077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00658345222473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999622464179993</t>
+    <t xml:space="preserve">1.01076030731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00484323501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02920734882355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00936806201935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00658357143402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999622285366058</t>
   </si>
   <si>
     <t xml:space="preserve">0.968993246555328</t>
@@ -1352,28 +1352,28 @@
     <t xml:space="preserve">1.0316436290741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02851116657257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01980972290039</t>
+    <t xml:space="preserve">1.02851104736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01980984210968</t>
   </si>
   <si>
     <t xml:space="preserve">1.04382574558258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04661023616791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02363848686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02537858486176</t>
+    <t xml:space="preserve">1.04661011695862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02363836765289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02537870407104</t>
   </si>
   <si>
     <t xml:space="preserve">1.00588738918304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01250064373016</t>
+    <t xml:space="preserve">1.01250052452087</t>
   </si>
   <si>
     <t xml:space="preserve">1.02120196819305</t>
@@ -1382,19 +1382,19 @@
     <t xml:space="preserve">1.02642273902893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03373205661774</t>
+    <t xml:space="preserve">1.03373193740845</t>
   </si>
   <si>
     <t xml:space="preserve">1.01389276981354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03860473632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05113470554352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06122863292694</t>
+    <t xml:space="preserve">1.03860485553741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0511349439621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06122851371765</t>
   </si>
   <si>
     <t xml:space="preserve">1.07236659526825</t>
@@ -1412,19 +1412,19 @@
     <t xml:space="preserve">1.07375872135162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06714570522308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0786315202713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09290170669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09429407119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10160326957703</t>
+    <t xml:space="preserve">1.0671454668045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07863140106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09290194511414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0942941904068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10160315036774</t>
   </si>
   <si>
     <t xml:space="preserve">1.08420050144196</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">1.04835045337677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06157660484314</t>
+    <t xml:space="preserve">1.06157672405243</t>
   </si>
   <si>
     <t xml:space="preserve">1.07201838493347</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">1.09394598007202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08106791973114</t>
+    <t xml:space="preserve">1.08106803894043</t>
   </si>
   <si>
     <t xml:space="preserve">1.09011745452881</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">1.12387895584106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10473597049713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10612797737122</t>
+    <t xml:space="preserve">1.10473585128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10612809658051</t>
   </si>
   <si>
     <t xml:space="preserve">1.11134886741638</t>
@@ -1499,16 +1499,16 @@
     <t xml:space="preserve">1.03338396549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04243350028992</t>
+    <t xml:space="preserve">1.04243326187134</t>
   </si>
   <si>
     <t xml:space="preserve">1.02154994010925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03094744682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04173731803894</t>
+    <t xml:space="preserve">1.0309476852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04173743724823</t>
   </si>
   <si>
     <t xml:space="preserve">1.05705189704895</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">1.0789794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09220576286316</t>
+    <t xml:space="preserve">1.09220564365387</t>
   </si>
   <si>
     <t xml:space="preserve">1.09116160869598</t>
@@ -1529,22 +1529,22 @@
     <t xml:space="preserve">1.08141589164734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09847068786621</t>
+    <t xml:space="preserve">1.09847092628479</t>
   </si>
   <si>
     <t xml:space="preserve">1.09603440761566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07619512081146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07445478439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05879211425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07758724689484</t>
+    <t xml:space="preserve">1.07619500160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07445466518402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0587922334671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07758736610413</t>
   </si>
   <si>
     <t xml:space="preserve">1.06923389434814</t>
@@ -1553,13 +1553,13 @@
     <t xml:space="preserve">1.04069316387177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03199172019958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04452168941498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04417383670807</t>
+    <t xml:space="preserve">1.0319916009903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04452192783356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04417359828949</t>
   </si>
   <si>
     <t xml:space="preserve">1.05183112621307</t>
@@ -1568,70 +1568,70 @@
     <t xml:space="preserve">1.03616845607758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05844414234161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03442800045013</t>
+    <t xml:space="preserve">1.05844402313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03442811965942</t>
   </si>
   <si>
     <t xml:space="preserve">1.00310289859772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991617023944855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00832402706146</t>
+    <t xml:space="preserve">0.99161696434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00832378864288</t>
   </si>
   <si>
     <t xml:space="preserve">1.01424062252045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01772117614746</t>
+    <t xml:space="preserve">1.01772129535675</t>
   </si>
   <si>
     <t xml:space="preserve">1.01354455947876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993705332279205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988136351108551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97734659910202</t>
+    <t xml:space="preserve">0.993705272674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988136470317841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977346777915955</t>
   </si>
   <si>
     <t xml:space="preserve">1.00553941726685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9860480427742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989528715610504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992312967777252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98291552066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991965055465698</t>
+    <t xml:space="preserve">0.986047923564911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98952853679657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992313265800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982915461063385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991965115070343</t>
   </si>
   <si>
     <t xml:space="preserve">1.01319670677185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00414717197418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02050566673279</t>
+    <t xml:space="preserve">1.00414705276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02050578594208</t>
   </si>
   <si>
     <t xml:space="preserve">1.0156329870224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03512418270111</t>
+    <t xml:space="preserve">1.0351243019104</t>
   </si>
   <si>
     <t xml:space="preserve">1.0393009185791</t>
@@ -1643,43 +1643,43 @@
     <t xml:space="preserve">1.05461549758911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03721272945404</t>
+    <t xml:space="preserve">1.03721261024475</t>
   </si>
   <si>
     <t xml:space="preserve">1.02711892127991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03999698162079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06610143184662</t>
+    <t xml:space="preserve">1.03999710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06610131263733</t>
   </si>
   <si>
     <t xml:space="preserve">1.06088054180145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04034519195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03233981132507</t>
+    <t xml:space="preserve">1.04034507274628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03233969211578</t>
   </si>
   <si>
     <t xml:space="preserve">1.04278147220612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04347741603851</t>
+    <t xml:space="preserve">1.0434775352478</t>
   </si>
   <si>
     <t xml:space="preserve">1.07410669326782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10090720653534</t>
+    <t xml:space="preserve">1.10090708732605</t>
   </si>
   <si>
     <t xml:space="preserve">1.11761391162872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12701153755188</t>
+    <t xml:space="preserve">1.12701141834259</t>
   </si>
   <si>
     <t xml:space="preserve">1.11378538608551</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">1.1064760684967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12318277359009</t>
+    <t xml:space="preserve">1.12318289279938</t>
   </si>
   <si>
     <t xml:space="preserve">1.13118815422058</t>
@@ -1697,22 +1697,22 @@
     <t xml:space="preserve">1.1144814491272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08872509002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09464204311371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11622166633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1183100938797</t>
+    <t xml:space="preserve">1.08872520923615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.094642162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11622190475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11831021308899</t>
   </si>
   <si>
     <t xml:space="preserve">1.13501679897308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13675713539124</t>
+    <t xml:space="preserve">1.13675725460052</t>
   </si>
   <si>
     <t xml:space="preserve">1.1381493806839</t>
@@ -1721,7 +1721,7 @@
     <t xml:space="preserve">1.14302217960358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10403978824615</t>
+    <t xml:space="preserve">1.10403966903687</t>
   </si>
   <si>
     <t xml:space="preserve">1.10891270637512</t>
@@ -1730,19 +1730,19 @@
     <t xml:space="preserve">1.09951484203339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10195136070251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09916687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0949901342392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10577988624573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09185779094696</t>
+    <t xml:space="preserve">1.1019514799118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0991667509079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09499001502991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10578012466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09185767173767</t>
   </si>
   <si>
     <t xml:space="preserve">1.07793533802032</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">1.0866367816925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06227278709412</t>
+    <t xml:space="preserve">1.06227290630341</t>
   </si>
   <si>
     <t xml:space="preserve">1.08280813694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09742653369904</t>
+    <t xml:space="preserve">1.09742665290833</t>
   </si>
   <si>
     <t xml:space="preserve">1.10021114349365</t>
@@ -1772,10 +1772,10 @@
     <t xml:space="preserve">1.10369157791138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11100089550018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10543203353882</t>
+    <t xml:space="preserve">1.11100077629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10543191432953</t>
   </si>
   <si>
     <t xml:space="preserve">1.08594071865082</t>
@@ -1784,22 +1784,22 @@
     <t xml:space="preserve">1.09568619728088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08907318115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11726593971252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12074661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10752034187317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11030471324921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.121790766716</t>
+    <t xml:space="preserve">1.08907306194305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11726582050323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12074649333954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10752010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1103048324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12179064750671</t>
   </si>
   <si>
     <t xml:space="preserve">1.11935424804688</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">1.13536489009857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13084006309509</t>
+    <t xml:space="preserve">1.13084018230438</t>
   </si>
   <si>
     <t xml:space="preserve">1.13223242759705</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">1.14754688739777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06331694126129</t>
+    <t xml:space="preserve">1.06331706047058</t>
   </si>
   <si>
     <t xml:space="preserve">1.05391931533813</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">1.04626214504242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05426752567291</t>
+    <t xml:space="preserve">1.05426740646362</t>
   </si>
   <si>
     <t xml:space="preserve">1.04869842529297</t>
@@ -1838,55 +1838,55 @@
     <t xml:space="preserve">1.02433454990387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0194616317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01632916927338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00379908084869</t>
+    <t xml:space="preserve">1.01946151256561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01632905006409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0037989616394</t>
   </si>
   <si>
     <t xml:space="preserve">0.997882068157196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.007279753685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02015793323517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07654309272766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08517646789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09720540046692</t>
+    <t xml:space="preserve">1.00727963447571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02015769481659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07654321193695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08517634868622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0972056388855</t>
   </si>
   <si>
     <t xml:space="preserve">1.09647643566132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06622135639191</t>
+    <t xml:space="preserve">1.06622123718262</t>
   </si>
   <si>
     <t xml:space="preserve">1.08116674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07205379009247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06038904190063</t>
+    <t xml:space="preserve">1.07205367088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06038892269135</t>
   </si>
   <si>
     <t xml:space="preserve">1.05127608776093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06403434276581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07168912887573</t>
+    <t xml:space="preserve">1.06403422355652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07168924808502</t>
   </si>
   <si>
     <t xml:space="preserve">1.08043766021729</t>
@@ -1895,16 +1895,16 @@
     <t xml:space="preserve">1.0979346036911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0986635684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10449588298798</t>
+    <t xml:space="preserve">1.09866368770599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10449600219727</t>
   </si>
   <si>
     <t xml:space="preserve">1.10048627853394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10230875015259</t>
+    <t xml:space="preserve">1.10230886936188</t>
   </si>
   <si>
     <t xml:space="preserve">1.09574747085571</t>
@@ -1913,28 +1913,28 @@
     <t xml:space="preserve">1.09829902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13219952583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12563812732697</t>
+    <t xml:space="preserve">1.13219964504242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12563800811768</t>
   </si>
   <si>
     <t xml:space="preserve">1.14021897315979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14750933647156</t>
+    <t xml:space="preserve">1.14750921726227</t>
   </si>
   <si>
     <t xml:space="preserve">1.13584470748901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11944139003754</t>
+    <t xml:space="preserve">1.11944127082825</t>
   </si>
   <si>
     <t xml:space="preserve">1.11543154716492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10376703739166</t>
+    <t xml:space="preserve">1.10376679897308</t>
   </si>
   <si>
     <t xml:space="preserve">1.11251544952393</t>
@@ -1943,49 +1943,49 @@
     <t xml:space="preserve">1.11069273948669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13511562347412</t>
+    <t xml:space="preserve">1.13511574268341</t>
   </si>
   <si>
     <t xml:space="preserve">1.1500608921051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15188360214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.147873878479</t>
+    <t xml:space="preserve">1.15188348293304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14787375926971</t>
   </si>
   <si>
     <t xml:space="preserve">1.15261256694794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16427719593048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17047417163849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17156767845154</t>
+    <t xml:space="preserve">1.16427731513977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1704740524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17156755924225</t>
   </si>
   <si>
     <t xml:space="preserve">1.17229676246643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17849361896515</t>
+    <t xml:space="preserve">1.17849349975586</t>
   </si>
   <si>
     <t xml:space="preserve">1.17484843730927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19161629676819</t>
+    <t xml:space="preserve">1.19161641597748</t>
   </si>
   <si>
     <t xml:space="preserve">1.16318380832672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16609978675842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17995154857635</t>
+    <t xml:space="preserve">1.16609966754913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17995166778564</t>
   </si>
   <si>
     <t xml:space="preserve">1.18469035625458</t>
@@ -1997,37 +1997,37 @@
     <t xml:space="preserve">1.17120325565338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17375481128693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14969635009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15407061576843</t>
+    <t xml:space="preserve">1.17375469207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14969646930695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15407085418701</t>
   </si>
   <si>
     <t xml:space="preserve">1.17083847522736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16209006309509</t>
+    <t xml:space="preserve">1.16209030151367</t>
   </si>
   <si>
     <t xml:space="preserve">1.1668289899826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1675580739975</t>
+    <t xml:space="preserve">1.16755795478821</t>
   </si>
   <si>
     <t xml:space="preserve">1.17010962963104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13183498382568</t>
+    <t xml:space="preserve">1.13183510303497</t>
   </si>
   <si>
     <t xml:space="preserve">1.12418019771576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12782526016235</t>
+    <t xml:space="preserve">1.12782514095306</t>
   </si>
   <si>
     <t xml:space="preserve">1.14277064800262</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">1.16099655628204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14459335803986</t>
+    <t xml:space="preserve">1.14459323883057</t>
   </si>
   <si>
     <t xml:space="preserve">1.15297722816467</t>
@@ -2048,19 +2048,19 @@
     <t xml:space="preserve">1.13475120067596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16391265392303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16938054561615</t>
+    <t xml:space="preserve">1.16391277313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16938066482544</t>
   </si>
   <si>
     <t xml:space="preserve">1.16573536396027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16500627994537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18833565711975</t>
+    <t xml:space="preserve">1.16500639915466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18833553791046</t>
   </si>
   <si>
     <t xml:space="preserve">1.20473897457123</t>
@@ -2072,19 +2072,19 @@
     <t xml:space="preserve">1.18869996070862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1795871257782</t>
+    <t xml:space="preserve">1.17958700656891</t>
   </si>
   <si>
     <t xml:space="preserve">1.16464173793793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17922270298004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18213880062103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17630636692047</t>
+    <t xml:space="preserve">1.17922258377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18213868141174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17630648612976</t>
   </si>
   <si>
     <t xml:space="preserve">1.19599044322968</t>
@@ -2093,19 +2093,19 @@
     <t xml:space="preserve">1.18979358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22551679611206</t>
+    <t xml:space="preserve">1.22551667690277</t>
   </si>
   <si>
     <t xml:space="preserve">1.21567463874817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22770369052887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23207807540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21421658992767</t>
+    <t xml:space="preserve">1.22770392894745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23207795619965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21421647071838</t>
   </si>
   <si>
     <t xml:space="preserve">1.21166479587555</t>
@@ -2123,22 +2123,22 @@
     <t xml:space="preserve">1.21931982040405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23791038990021</t>
+    <t xml:space="preserve">1.23791027069092</t>
   </si>
   <si>
     <t xml:space="preserve">1.23462975025177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22806823253632</t>
+    <t xml:space="preserve">1.22806835174561</t>
   </si>
   <si>
     <t xml:space="preserve">1.21640360355377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22187149524689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22114229202271</t>
+    <t xml:space="preserve">1.22187125682831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22114253044128</t>
   </si>
   <si>
     <t xml:space="preserve">1.22405862808228</t>
@@ -2150,19 +2150,19 @@
     <t xml:space="preserve">1.22843277454376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23645210266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2287974357605</t>
+    <t xml:space="preserve">1.23645222187042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22879731655121</t>
   </si>
   <si>
     <t xml:space="preserve">1.22624576091766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27363336086273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27691411972046</t>
+    <t xml:space="preserve">1.27363324165344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27691400051117</t>
   </si>
   <si>
     <t xml:space="preserve">1.31154346466064</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">1.3133659362793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30972075462341</t>
+    <t xml:space="preserve">1.3097208738327</t>
   </si>
   <si>
     <t xml:space="preserve">1.30826270580292</t>
@@ -2180,22 +2180,22 @@
     <t xml:space="preserve">1.31591749191284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29331743717194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31518852710724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31445944309235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30862724781036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29732716083527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27873647212982</t>
+    <t xml:space="preserve">1.29331731796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31518864631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31445968151093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30862712860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29732704162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27873659133911</t>
   </si>
   <si>
     <t xml:space="preserve">1.28857862949371</t>
@@ -2207,19 +2207,19 @@
     <t xml:space="preserve">1.27727842330933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27509140968323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26452028751373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24884593486786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24665880203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25249099731445</t>
+    <t xml:space="preserve">1.27509129047394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26452040672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24884581565857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24665892124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25249111652374</t>
   </si>
   <si>
     <t xml:space="preserve">1.24520063400269</t>
@@ -2234,7 +2234,7 @@
     <t xml:space="preserve">1.19635510444641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1985422372818</t>
+    <t xml:space="preserve">1.19854235649109</t>
   </si>
   <si>
     <t xml:space="preserve">1.19343888759613</t>
@@ -2264,22 +2264,22 @@
     <t xml:space="preserve">1.24155557155609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23353612422943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2189553976059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21275842189789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2083842754364</t>
+    <t xml:space="preserve">1.23353624343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21895527839661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2127583026886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20838415622711</t>
   </si>
   <si>
     <t xml:space="preserve">1.25504279136658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2506685256958</t>
+    <t xml:space="preserve">1.25066864490509</t>
   </si>
   <si>
     <t xml:space="preserve">1.25941693782806</t>
@@ -2288,37 +2288,37 @@
     <t xml:space="preserve">1.25650084018707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26853001117706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2998788356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30315947532654</t>
+    <t xml:space="preserve">1.26853013038635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29987871646881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30315935611725</t>
   </si>
   <si>
     <t xml:space="preserve">1.29368197917938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2922238111496</t>
+    <t xml:space="preserve">1.29222393035889</t>
   </si>
   <si>
     <t xml:space="preserve">1.30607557296753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35200536251068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34544372558594</t>
+    <t xml:space="preserve">1.3520051240921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34544360637665</t>
   </si>
   <si>
     <t xml:space="preserve">1.33414363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31409513950348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32247889041901</t>
+    <t xml:space="preserve">1.31409502029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3224790096283</t>
   </si>
   <si>
     <t xml:space="preserve">1.32940483093262</t>
@@ -2327,37 +2327,37 @@
     <t xml:space="preserve">1.34580826759338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33159208297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33013391494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34981799125671</t>
+    <t xml:space="preserve">1.33159196376801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33013379573822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.349818110466</t>
   </si>
   <si>
     <t xml:space="preserve">1.34398579597473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3414341211319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34945356845856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35893094539642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36986649036407</t>
+    <t xml:space="preserve">1.34143400192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34945344924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35893106460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36986660957336</t>
   </si>
   <si>
     <t xml:space="preserve">1.3822603225708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3603892326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34908890724182</t>
+    <t xml:space="preserve">1.36038911342621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34908902645111</t>
   </si>
   <si>
     <t xml:space="preserve">1.26524937152863</t>
@@ -2369,160 +2369,160 @@
     <t xml:space="preserve">1.13766729831696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15589320659637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19708395004272</t>
+    <t xml:space="preserve">1.15589332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1970841884613</t>
   </si>
   <si>
     <t xml:space="preserve">1.11579620838165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996233463287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924787640571594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905467927455902</t>
+    <t xml:space="preserve">0.996233344078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92478746175766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905467987060547</t>
   </si>
   <si>
     <t xml:space="preserve">0.733049929141998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.772782683372498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750546813011169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775334298610687</t>
+    <t xml:space="preserve">0.772782623767853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750546932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775334417819977</t>
   </si>
   <si>
     <t xml:space="preserve">0.751276075839996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.7545565366745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.741433918476105</t>
+    <t xml:space="preserve">0.754556596279144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74143385887146</t>
   </si>
   <si>
     <t xml:space="preserve">0.729040205478668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786269903182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79720550775528</t>
+    <t xml:space="preserve">0.786269962787628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797205448150635</t>
   </si>
   <si>
     <t xml:space="preserve">0.793195843696594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778250396251678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824544429779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826002717018127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816160619258881</t>
+    <t xml:space="preserve">0.778250515460968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824544548988342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826002657413483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816160678863525</t>
   </si>
   <si>
     <t xml:space="preserve">0.841677010059357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.836209177970886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86901593208313</t>
+    <t xml:space="preserve">0.836209058761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869015991687775</t>
   </si>
   <si>
     <t xml:space="preserve">0.869745016098022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855164170265198</t>
+    <t xml:space="preserve">0.855164229869843</t>
   </si>
   <si>
     <t xml:space="preserve">0.876670897006989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.889429092407227</t>
+    <t xml:space="preserve">0.889429211616516</t>
   </si>
   <si>
     <t xml:space="preserve">0.885783970355988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.897448539733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910935938358307</t>
+    <t xml:space="preserve">0.897448599338531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910935759544373</t>
   </si>
   <si>
     <t xml:space="preserve">0.91166478395462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.883961260318756</t>
+    <t xml:space="preserve">0.883961200714111</t>
   </si>
   <si>
     <t xml:space="preserve">0.888335585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.879587173461914</t>
+    <t xml:space="preserve">0.879587054252625</t>
   </si>
   <si>
     <t xml:space="preserve">0.890158116817474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906926035881042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901458263397217</t>
+    <t xml:space="preserve">0.906925976276398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901458323001862</t>
   </si>
   <si>
     <t xml:space="preserve">0.899635553359985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.905832409858704</t>
+    <t xml:space="preserve">0.905832350254059</t>
   </si>
   <si>
     <t xml:space="preserve">0.872296631336212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.879951655864716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878129005432129</t>
+    <t xml:space="preserve">0.879951477050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878128886222839</t>
   </si>
   <si>
     <t xml:space="preserve">0.882138729095459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877764403820038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914581120014191</t>
+    <t xml:space="preserve">0.877764463424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914581060409546</t>
   </si>
   <si>
     <t xml:space="preserve">0.93426501750946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.911300182342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944332480430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902750730514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914020538330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910522937774658</t>
+    <t xml:space="preserve">0.911300361156464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944332540035248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902750790119171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914020597934723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910522997379303</t>
   </si>
   <si>
     <t xml:space="preserve">0.912854731082916</t>
@@ -2531,19 +2531,19 @@
     <t xml:space="preserve">0.946275472640991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971147000789642</t>
+    <t xml:space="preserve">0.971146881580353</t>
   </si>
   <si>
     <t xml:space="preserve">0.950550258159637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971535444259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969592332839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981639504432678</t>
+    <t xml:space="preserve">0.971535503864288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969592273235321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981639385223389</t>
   </si>
   <si>
     <t xml:space="preserve">1.00573348999023</t>
@@ -2552,34 +2552,34 @@
     <t xml:space="preserve">1.04265189170837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04342901706696</t>
+    <t xml:space="preserve">1.04342913627625</t>
   </si>
   <si>
     <t xml:space="preserve">1.03060483932495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05236732959747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02710735797882</t>
+    <t xml:space="preserve">1.05236721038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02710723876953</t>
   </si>
   <si>
     <t xml:space="preserve">1.01195132732391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960265576839447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956379473209381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978141903877258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01156270503998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01778054237366</t>
+    <t xml:space="preserve">0.960265755653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956379532814026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978141784667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01156282424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01778042316437</t>
   </si>
   <si>
     <t xml:space="preserve">1.00961971282959</t>
@@ -2588,127 +2588,127 @@
     <t xml:space="preserve">1.0193350315094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01467168331146</t>
+    <t xml:space="preserve">1.01467156410217</t>
   </si>
   <si>
     <t xml:space="preserve">0.972312748432159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.963763177394867</t>
+    <t xml:space="preserve">0.963763117790222</t>
   </si>
   <si>
     <t xml:space="preserve">0.977364778518677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979696333408356</t>
+    <t xml:space="preserve">0.979696273803711</t>
   </si>
   <si>
     <t xml:space="preserve">0.984359800815582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999904274940491</t>
+    <t xml:space="preserve">0.999904334545135</t>
   </si>
   <si>
     <t xml:space="preserve">0.996795415878296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993686497211456</t>
+    <t xml:space="preserve">0.993686437606812</t>
   </si>
   <si>
     <t xml:space="preserve">0.983193933963776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982805252075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958322584629059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961431443691254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960654199123383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973867058753967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973089933395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985136926174164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987857222557068</t>
+    <t xml:space="preserve">0.98280531167984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958322644233704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961431503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960654377937317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973867177963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973089873790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985137045383453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987857401371002</t>
   </si>
   <si>
     <t xml:space="preserve">0.985525548458099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949773013591766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954436421394348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970758199691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92878794670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943166613578796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955990970134735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959877133369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953659296035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965317726135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982027947902679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01739203929901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00612211227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994852364063263</t>
+    <t xml:space="preserve">0.949773073196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954436480998993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970758259296417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928788006305695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943166673183441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95599091053009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959877014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953659176826477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96531754732132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982028007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01739192008972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00612223148346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994852304458618</t>
   </si>
   <si>
     <t xml:space="preserve">0.979307770729065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989411771297455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987079977989197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964929163455963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96259731054306</t>
+    <t xml:space="preserve">0.989411652088165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987080037593842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964929103851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962597250938416</t>
   </si>
   <si>
     <t xml:space="preserve">0.958711266517639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966094970703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951327562332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954047858715057</t>
+    <t xml:space="preserve">0.96609491109848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951327502727509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954047739505768</t>
   </si>
   <si>
     <t xml:space="preserve">0.975033044815063</t>
@@ -2717,61 +2717,61 @@
     <t xml:space="preserve">0.968038022518158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937726080417633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946664273738861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938503324985504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942000806331635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933451294898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971924185752869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94899570941925</t>
+    <t xml:space="preserve">0.937726020812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946664154529572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938503205776215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942000687122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933451235294342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971924126148224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948995888233185</t>
   </si>
   <si>
     <t xml:space="preserve">0.953270673751831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945886850357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929565191268921</t>
+    <t xml:space="preserve">0.9458869099617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929565072059631</t>
   </si>
   <si>
     <t xml:space="preserve">0.931119620800018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.900807738304138</t>
+    <t xml:space="preserve">0.900807857513428</t>
   </si>
   <si>
     <t xml:space="preserve">0.903528034687042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904693961143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898864567279816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87865674495697</t>
+    <t xml:space="preserve">0.904693901538849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898864686489105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878656625747681</t>
   </si>
   <si>
     <t xml:space="preserve">0.886428892612457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.90158486366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886040270328522</t>
+    <t xml:space="preserve">0.901584982872009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886040389537811</t>
   </si>
   <si>
     <t xml:space="preserve">0.840961158275604</t>
@@ -2789,58 +2789,58 @@
     <t xml:space="preserve">0.872050225734711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89847606420517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892646789550781</t>
+    <t xml:space="preserve">0.898476004600525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892646729946136</t>
   </si>
   <si>
     <t xml:space="preserve">0.881376981735229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94277811050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939280569553375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955213725566864</t>
+    <t xml:space="preserve">0.942778050899506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93928050994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955213606357574</t>
   </si>
   <si>
     <t xml:space="preserve">0.95249330997467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947441279888153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952104866504669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959488451480865</t>
+    <t xml:space="preserve">0.947441339492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952104806900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95948851108551</t>
   </si>
   <si>
     <t xml:space="preserve">0.97619891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01700341701508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02205538749695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993297934532166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982416749000549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975421488285065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976587474346161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997183978557587</t>
+    <t xml:space="preserve">1.01700329780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02205550670624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993297815322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982416689395905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975421667098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976587533950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997183918952942</t>
   </si>
   <si>
     <t xml:space="preserve">0.990966200828552</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">0.988245904445648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984748244285583</t>
+    <t xml:space="preserve">0.984748303890228</t>
   </si>
   <si>
     <t xml:space="preserve">0.995629668235779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954825103282928</t>
+    <t xml:space="preserve">0.954825043678284</t>
   </si>
   <si>
     <t xml:space="preserve">1.00651073455811</t>
@@ -2864,46 +2864,46 @@
     <t xml:space="preserve">1.01583755016327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01389443874359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03449106216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02399837970734</t>
+    <t xml:space="preserve">1.0138943195343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03449094295502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02399849891663</t>
   </si>
   <si>
     <t xml:space="preserve">1.04148602485657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03954291343689</t>
+    <t xml:space="preserve">1.03954303264618</t>
   </si>
   <si>
     <t xml:space="preserve">1.03487956523895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01428306102753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03759980201721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03215932846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02050077915192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03099358081818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06596875190735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07296371459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04653811454773</t>
+    <t xml:space="preserve">1.01428294181824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0375999212265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0321592092514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02050089836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03099346160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06596863269806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0729638338089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04653799533844</t>
   </si>
   <si>
     <t xml:space="preserve">1.0589736700058</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">1.06169402599335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04498338699341</t>
+    <t xml:space="preserve">1.0449835062027</t>
   </si>
   <si>
     <t xml:space="preserve">1.10871624946594</t>
@@ -2924,40 +2924,40 @@
     <t xml:space="preserve">1.13630783557892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15418422222137</t>
+    <t xml:space="preserve">1.15418410301208</t>
   </si>
   <si>
     <t xml:space="preserve">1.12853562831879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13825082778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1425256729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17516922950745</t>
+    <t xml:space="preserve">1.1382509469986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14252579212189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17516934871674</t>
   </si>
   <si>
     <t xml:space="preserve">1.16195642948151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13863945007324</t>
+    <t xml:space="preserve">1.13863968849182</t>
   </si>
   <si>
     <t xml:space="preserve">1.12154054641724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13475346565247</t>
+    <t xml:space="preserve">1.13475358486176</t>
   </si>
   <si>
     <t xml:space="preserve">1.12698125839233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11415684223175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10366415977478</t>
+    <t xml:space="preserve">1.11415696144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10366427898407</t>
   </si>
   <si>
     <t xml:space="preserve">1.11221373081207</t>
@@ -2966,19 +2966,19 @@
     <t xml:space="preserve">1.09317171573639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08384501934052</t>
+    <t xml:space="preserve">1.0838451385498</t>
   </si>
   <si>
     <t xml:space="preserve">1.11493408679962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1071617603302</t>
+    <t xml:space="preserve">1.10716199874878</t>
   </si>
   <si>
     <t xml:space="preserve">1.07918155193329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08656513690948</t>
+    <t xml:space="preserve">1.08656525611877</t>
   </si>
   <si>
     <t xml:space="preserve">1.0772385597229</t>
@@ -2990,79 +2990,79 @@
     <t xml:space="preserve">1.1308673620224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15262973308563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14874362945557</t>
+    <t xml:space="preserve">1.15262961387634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14874351024628</t>
   </si>
   <si>
     <t xml:space="preserve">1.15496134757996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16312217712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14563453197479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15301847457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14641189575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17089450359344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18954801559448</t>
+    <t xml:space="preserve">1.16312229633331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14563465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15301823616028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14641177654266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17089462280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18954813480377</t>
   </si>
   <si>
     <t xml:space="preserve">1.2047039270401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20664703845978</t>
+    <t xml:space="preserve">1.20664715766907</t>
   </si>
   <si>
     <t xml:space="preserve">1.21558523178101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21752834320068</t>
+    <t xml:space="preserve">1.21752822399139</t>
   </si>
   <si>
     <t xml:space="preserve">1.20625853538513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20392680168152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20859003067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22413468360901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20975589752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19809746742249</t>
+    <t xml:space="preserve">1.20392668247223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20859014987946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2241348028183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20975601673126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19809758663177</t>
   </si>
   <si>
     <t xml:space="preserve">1.21286487579346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21597373485565</t>
+    <t xml:space="preserve">1.21597361564636</t>
   </si>
   <si>
     <t xml:space="preserve">1.21325349807739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20431542396545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21247613430023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22685503959656</t>
+    <t xml:space="preserve">1.20431530475616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21247625350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22685515880585</t>
   </si>
   <si>
     <t xml:space="preserve">1.21403074264526</t>
@@ -3077,25 +3077,25 @@
     <t xml:space="preserve">1.23851346969604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24278819561005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26105296611786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26455044746399</t>
+    <t xml:space="preserve">1.24278831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26105308532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26455056667328</t>
   </si>
   <si>
     <t xml:space="preserve">1.27582037448883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26066434383392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2649393081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27892935276031</t>
+    <t xml:space="preserve">1.26066446304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26493918895721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27892923355103</t>
   </si>
   <si>
     <t xml:space="preserve">1.3045779466629</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">1.3174022436142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33061504364014</t>
+    <t xml:space="preserve">1.33061492443085</t>
   </si>
   <si>
     <t xml:space="preserve">1.34693682193756</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">1.34382784366608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3484913110733</t>
+    <t xml:space="preserve">1.34849119186401</t>
   </si>
   <si>
     <t xml:space="preserve">1.35121142864227</t>
@@ -3131,28 +3131,28 @@
     <t xml:space="preserve">1.37258541584015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40067195892334</t>
+    <t xml:space="preserve">1.40067207813263</t>
   </si>
   <si>
     <t xml:space="preserve">1.37502765655518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38194763660431</t>
+    <t xml:space="preserve">1.38194751739502</t>
   </si>
   <si>
     <t xml:space="preserve">1.37787699699402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39497339725494</t>
+    <t xml:space="preserve">1.39497327804565</t>
   </si>
   <si>
     <t xml:space="preserve">1.391716837883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38438987731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39456629753113</t>
+    <t xml:space="preserve">1.38438999652863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39456617832184</t>
   </si>
   <si>
     <t xml:space="preserve">1.38886749744415</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">1.41044127941132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42305994033813</t>
+    <t xml:space="preserve">1.42306005954742</t>
   </si>
   <si>
     <t xml:space="preserve">1.43323636054993</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">1.43852806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43771398067474</t>
+    <t xml:space="preserve">1.43771409988403</t>
   </si>
   <si>
     <t xml:space="preserve">1.4491114616394</t>
@@ -3185,16 +3185,16 @@
     <t xml:space="preserve">1.45725250244141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45765948295593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45521724224091</t>
+    <t xml:space="preserve">1.45765972137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4552173614502</t>
   </si>
   <si>
     <t xml:space="preserve">1.43120110034943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44300556182861</t>
+    <t xml:space="preserve">1.4430056810379</t>
   </si>
   <si>
     <t xml:space="preserve">1.44422686100006</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">1.42713057994843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41858243942261</t>
+    <t xml:space="preserve">1.41858232021332</t>
   </si>
   <si>
     <t xml:space="preserve">1.40352141857147</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">1.41898953914642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41329061985016</t>
+    <t xml:space="preserve">1.41329085826874</t>
   </si>
   <si>
     <t xml:space="preserve">1.43527162075043</t>
@@ -3233,13 +3233,13 @@
     <t xml:space="preserve">1.39945089817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41736125946045</t>
+    <t xml:space="preserve">1.41736137866974</t>
   </si>
   <si>
     <t xml:space="preserve">1.40392851829529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40148627758026</t>
+    <t xml:space="preserve">1.40148615837097</t>
   </si>
   <si>
     <t xml:space="preserve">1.34734797477722</t>
@@ -3260,22 +3260,22 @@
     <t xml:space="preserve">1.47719812393188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47801244258881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47394180297852</t>
+    <t xml:space="preserve">1.47801232337952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47394168376923</t>
   </si>
   <si>
     <t xml:space="preserve">1.47068536281586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47923338413239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46824312210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47964036464691</t>
+    <t xml:space="preserve">1.47923350334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46824300289154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47964060306549</t>
   </si>
   <si>
     <t xml:space="preserve">1.49348032474518</t>
@@ -3284,10 +3284,10 @@
     <t xml:space="preserve">1.50691306591034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52360236644745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53866326808929</t>
+    <t xml:space="preserve">1.52360224723816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53866314888</t>
   </si>
   <si>
     <t xml:space="preserve">1.54069852828979</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">1.55006086826324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58262503147125</t>
+    <t xml:space="preserve">1.58262515068054</t>
   </si>
   <si>
     <t xml:space="preserve">1.58669567108154</t>
@@ -3308,16 +3308,16 @@
     <t xml:space="preserve">1.5838463306427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5549453496933</t>
+    <t xml:space="preserve">1.55494546890259</t>
   </si>
   <si>
     <t xml:space="preserve">1.53215038776398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52726590633392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52889382839203</t>
+    <t xml:space="preserve">1.52726578712463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52889406681061</t>
   </si>
   <si>
     <t xml:space="preserve">1.52197408676147</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">1.51912474632263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50650596618652</t>
+    <t xml:space="preserve">1.50650608539581</t>
   </si>
   <si>
     <t xml:space="preserve">1.49755084514618</t>
@@ -3338,40 +3338,40 @@
     <t xml:space="preserve">1.52238118648529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49307334423065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51464712619781</t>
+    <t xml:space="preserve">1.49307322502136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51464700698853</t>
   </si>
   <si>
     <t xml:space="preserve">1.5162752866745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48615348339081</t>
+    <t xml:space="preserve">1.48615336418152</t>
   </si>
   <si>
     <t xml:space="preserve">1.48940968513489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49063086509705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42794454097748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45155382156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46173012256622</t>
+    <t xml:space="preserve">1.49063098430634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42794466018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45155370235443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46173024177551</t>
   </si>
   <si>
     <t xml:space="preserve">1.46213722229004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4837110042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47882640361786</t>
+    <t xml:space="preserve">1.48371112346649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47882628440857</t>
   </si>
   <si>
     <t xml:space="preserve">1.48411810398102</t>
@@ -3380,28 +3380,28 @@
     <t xml:space="preserve">1.45643842220306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45562422275543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43812096118927</t>
+    <t xml:space="preserve">1.45562434196472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43812108039856</t>
   </si>
   <si>
     <t xml:space="preserve">1.44544804096222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44015622138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45684540271759</t>
+    <t xml:space="preserve">1.44015634059906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45684552192688</t>
   </si>
   <si>
     <t xml:space="preserve">1.48737454414368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48533928394318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50406360626221</t>
+    <t xml:space="preserve">1.48533916473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5040637254715</t>
   </si>
   <si>
     <t xml:space="preserve">1.46417236328125</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">1.4450409412384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47475576400757</t>
+    <t xml:space="preserve">1.47475588321686</t>
   </si>
   <si>
     <t xml:space="preserve">1.49673676490784</t>
@@ -3428,19 +3428,19 @@
     <t xml:space="preserve">1.50365662574768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52970814704895</t>
+    <t xml:space="preserve">1.52970802783966</t>
   </si>
   <si>
     <t xml:space="preserve">1.53662800788879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57407712936401</t>
+    <t xml:space="preserve">1.57407701015472</t>
   </si>
   <si>
     <t xml:space="preserve">1.55698072910309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55779469013214</t>
+    <t xml:space="preserve">1.55779480934143</t>
   </si>
   <si>
     <t xml:space="preserve">1.50732016563416</t>
@@ -3467,19 +3467,19 @@
     <t xml:space="preserve">1.50121426582336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51301884651184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51953184604645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51546120643616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3921240568161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4059636592865</t>
+    <t xml:space="preserve">1.51301896572113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51953172683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51546132564545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39212393760681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40596377849579</t>
   </si>
   <si>
     <t xml:space="preserve">1.39538037776947</t>
@@ -3491,40 +3491,40 @@
     <t xml:space="preserve">1.45196080207825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43079400062561</t>
+    <t xml:space="preserve">1.4307941198349</t>
   </si>
   <si>
     <t xml:space="preserve">1.45806670188904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45440304279327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45399618148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42835187911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39130973815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37258529663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32699537277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34531283378601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34775519371033</t>
+    <t xml:space="preserve">1.45440316200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45399606227875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42835175991058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39130985736847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37258517742157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32699525356293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34531271457672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34775495529175</t>
   </si>
   <si>
     <t xml:space="preserve">1.36810779571533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37177121639252</t>
+    <t xml:space="preserve">1.37177109718323</t>
   </si>
   <si>
     <t xml:space="preserve">1.39741563796997</t>
@@ -3533,10 +3533,10 @@
     <t xml:space="preserve">1.40026497840881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40677785873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35548901557922</t>
+    <t xml:space="preserve">1.40677797794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35548913478851</t>
   </si>
   <si>
     <t xml:space="preserve">1.35955965518951</t>
@@ -3545,58 +3545,58 @@
     <t xml:space="preserve">1.35833835601807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37462067604065</t>
+    <t xml:space="preserve">1.37462055683136</t>
   </si>
   <si>
     <t xml:space="preserve">1.36770057678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35589611530304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35263979434967</t>
+    <t xml:space="preserve">1.35589599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35263967514038</t>
   </si>
   <si>
     <t xml:space="preserve">1.33310115337372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32414579391479</t>
+    <t xml:space="preserve">1.32414591312408</t>
   </si>
   <si>
     <t xml:space="preserve">1.35304665565491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34164917469025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30664253234863</t>
+    <t xml:space="preserve">1.34164929389954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30664265155792</t>
   </si>
   <si>
     <t xml:space="preserve">1.3326940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36525845527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41532588005066</t>
+    <t xml:space="preserve">1.3652583360672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41532599925995</t>
   </si>
   <si>
     <t xml:space="preserve">1.37380635738373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36729371547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37909829616547</t>
+    <t xml:space="preserve">1.3672935962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37909817695618</t>
   </si>
   <si>
     <t xml:space="preserve">1.37624883651733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36973595619202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33513641357422</t>
+    <t xml:space="preserve">1.36973583698273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33513629436493</t>
   </si>
   <si>
     <t xml:space="preserve">1.30949199199677</t>
@@ -3611,10 +3611,10 @@
     <t xml:space="preserve">1.30542147159576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29036056995392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26430904865265</t>
+    <t xml:space="preserve">1.29036045074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26430916786194</t>
   </si>
   <si>
     <t xml:space="preserve">1.28913938999176</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">1.28425467014313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28181219100952</t>
+    <t xml:space="preserve">1.28181231021881</t>
   </si>
   <si>
     <t xml:space="preserve">1.27652060985565</t>
@@ -3641,16 +3641,16 @@
     <t xml:space="preserve">1.22482478618622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28140532970428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30012989044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2549467086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2284882068634</t>
+    <t xml:space="preserve">1.281405210495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3001297712326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25494682788849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22848832607269</t>
   </si>
   <si>
     <t xml:space="preserve">1.19918048381805</t>
@@ -3662,13 +3662,13 @@
     <t xml:space="preserve">1.20243680477142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25616800785065</t>
+    <t xml:space="preserve">1.25616788864136</t>
   </si>
   <si>
     <t xml:space="preserve">1.24639880657196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24477052688599</t>
+    <t xml:space="preserve">1.2447704076767</t>
   </si>
   <si>
     <t xml:space="preserve">1.23093068599701</t>
@@ -3686,25 +3686,25 @@
     <t xml:space="preserve">1.23785054683685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2508761882782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22563886642456</t>
+    <t xml:space="preserve">1.25087630748749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22563898563385</t>
   </si>
   <si>
     <t xml:space="preserve">1.22808122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23540818691254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2569819688797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27489233016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25779604911804</t>
+    <t xml:space="preserve">1.23540830612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25698208808899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27489244937897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25779616832733</t>
   </si>
   <si>
     <t xml:space="preserve">1.26553010940552</t>
@@ -3716,19 +3716,19 @@
     <t xml:space="preserve">1.28751111030579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29768741130829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2980945110321</t>
+    <t xml:space="preserve">1.29768753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29809439182281</t>
   </si>
   <si>
     <t xml:space="preserve">1.33554339408875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36281609535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35223269462585</t>
+    <t xml:space="preserve">1.36281597614288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35223257541656</t>
   </si>
   <si>
     <t xml:space="preserve">1.3571172952652</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">1.34409153461456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36485123634338</t>
+    <t xml:space="preserve">1.36485111713409</t>
   </si>
   <si>
     <t xml:space="preserve">1.33961391448975</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">1.32129657268524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32455289363861</t>
+    <t xml:space="preserve">1.3245530128479</t>
   </si>
   <si>
     <t xml:space="preserve">1.33432233333588</t>
@@ -3779,13 +3779,13 @@
     <t xml:space="preserve">1.34327745437622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38561105728149</t>
+    <t xml:space="preserve">1.3856109380722</t>
   </si>
   <si>
     <t xml:space="preserve">1.33147275447845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36037373542786</t>
+    <t xml:space="preserve">1.36037361621857</t>
   </si>
   <si>
     <t xml:space="preserve">1.34205627441406</t>
@@ -3797,22 +3797,22 @@
     <t xml:space="preserve">1.36872255802155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37862205505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38507843017578</t>
+    <t xml:space="preserve">1.378622174263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38507831096649</t>
   </si>
   <si>
     <t xml:space="preserve">1.3631272315979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35796225070953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34504973888397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32998502254486</t>
+    <t xml:space="preserve">1.35796213150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34504961967468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32998514175415</t>
   </si>
   <si>
     <t xml:space="preserve">1.31578135490417</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">1.33041560649872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31018590927124</t>
+    <t xml:space="preserve">1.31018602848053</t>
   </si>
   <si>
     <t xml:space="preserve">1.3123379945755</t>
@@ -3833,19 +3833,19 @@
     <t xml:space="preserve">1.270587682724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18708693981171</t>
+    <t xml:space="preserve">1.187087059021</t>
   </si>
   <si>
     <t xml:space="preserve">1.14921045303345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11047291755676</t>
+    <t xml:space="preserve">1.11047303676605</t>
   </si>
   <si>
     <t xml:space="preserve">1.15050172805786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11563789844513</t>
+    <t xml:space="preserve">1.11563801765442</t>
   </si>
   <si>
     <t xml:space="preserve">1.15437543392181</t>
@@ -3854,19 +3854,19 @@
     <t xml:space="preserve">1.091104388237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06570971012115</t>
+    <t xml:space="preserve">1.06570982933044</t>
   </si>
   <si>
     <t xml:space="preserve">1.03945434093475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05581033229828</t>
+    <t xml:space="preserve">1.05581021308899</t>
   </si>
   <si>
     <t xml:space="preserve">1.10143435001373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08593928813934</t>
+    <t xml:space="preserve">1.08593940734863</t>
   </si>
   <si>
     <t xml:space="preserve">1.09540855884552</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">1.07517886161804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.043328166008</t>
+    <t xml:space="preserve">1.04332804679871</t>
   </si>
   <si>
     <t xml:space="preserve">1.06743133068085</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">1.02697229385376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00200819969177</t>
+    <t xml:space="preserve">1.00200831890106</t>
   </si>
   <si>
     <t xml:space="preserve">1.02352893352509</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">1.03601109981537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04074561595917</t>
+    <t xml:space="preserve">1.04074573516846</t>
   </si>
   <si>
     <t xml:space="preserve">1.05451893806458</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">1.02955484390259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05882322788239</t>
+    <t xml:space="preserve">1.0588231086731</t>
   </si>
   <si>
     <t xml:space="preserve">1.08120477199554</t>
@@ -3938,10 +3938,10 @@
     <t xml:space="preserve">1.07474851608276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09024357795715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06829237937927</t>
+    <t xml:space="preserve">1.09024345874786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06829226016998</t>
   </si>
   <si>
     <t xml:space="preserve">1.08636963367462</t>
@@ -3962,25 +3962,25 @@
     <t xml:space="preserve">1.10100388526917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10272550582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08292651176453</t>
+    <t xml:space="preserve">1.10272562503815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08292639255524</t>
   </si>
   <si>
     <t xml:space="preserve">1.06097519397736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06355774402618</t>
+    <t xml:space="preserve">1.06355762481689</t>
   </si>
   <si>
     <t xml:space="preserve">1.05839276313782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01707279682159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996843278408051</t>
+    <t xml:space="preserve">1.0170726776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996843218803406</t>
   </si>
   <si>
     <t xml:space="preserve">0.999425709247589</t>
@@ -3989,46 +3989,46 @@
     <t xml:space="preserve">0.963701248168945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946915090084076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968435704708099</t>
+    <t xml:space="preserve">0.946914970874786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968435883522034</t>
   </si>
   <si>
     <t xml:space="preserve">0.945623755455017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.932711243629456</t>
+    <t xml:space="preserve">0.9327113032341</t>
   </si>
   <si>
     <t xml:space="preserve">0.939167439937592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920229196548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965422928333282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975322484970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952510416507721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92625492811203</t>
+    <t xml:space="preserve">0.920229136943817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965422868728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975322425365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952510476112366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92625504732132</t>
   </si>
   <si>
     <t xml:space="preserve">0.930128753185272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913342595100403</t>
+    <t xml:space="preserve">0.913342535495758</t>
   </si>
   <si>
     <t xml:space="preserve">0.921950876712799</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923242032527924</t>
+    <t xml:space="preserve">0.923242151737213</t>
   </si>
   <si>
     <t xml:space="preserve">0.912051260471344</t>
@@ -4037,10 +4037,10 @@
     <t xml:space="preserve">0.882783055305481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888808846473694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852567791938782</t>
+    <t xml:space="preserve">0.888808906078339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852567851543427</t>
   </si>
   <si>
     <t xml:space="preserve">0.86298394203186</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">0.85377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860659718513489</t>
+    <t xml:space="preserve">0.860659658908844</t>
   </si>
   <si>
     <t xml:space="preserve">0.879339694976807</t>
@@ -4061,10 +4061,10 @@
     <t xml:space="preserve">0.868579208850861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.853256404399872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8353511095047</t>
+    <t xml:space="preserve">0.853256464004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835351169109344</t>
   </si>
   <si>
     <t xml:space="preserve">0.846542000770569</t>
@@ -4079,16 +4079,16 @@
     <t xml:space="preserve">0.825882017612457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863844692707062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.883643805980682</t>
+    <t xml:space="preserve">0.863844633102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883643865585327</t>
   </si>
   <si>
     <t xml:space="preserve">0.879770040512085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871161758899689</t>
+    <t xml:space="preserve">0.871161699295044</t>
   </si>
   <si>
     <t xml:space="preserve">0.896986782550812</t>
@@ -4097,28 +4097,28 @@
     <t xml:space="preserve">0.949497520923615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948206186294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982209086418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971018373966217</t>
+    <t xml:space="preserve">0.948206305503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982209146022797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971018254756927</t>
   </si>
   <si>
     <t xml:space="preserve">0.965853273868561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966714143753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966283679008484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955092966556549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972309470176697</t>
+    <t xml:space="preserve">0.966714084148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966283738613129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955092906951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972309589385986</t>
   </si>
   <si>
     <t xml:space="preserve">0.993830323219299</t>
@@ -4130,7 +4130,7 @@
     <t xml:space="preserve">1.01061654090881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11176431179047</t>
+    <t xml:space="preserve">1.11176419258118</t>
   </si>
   <si>
     <t xml:space="preserve">1.1160683631897</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">1.10616886615753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.126828789711</t>
+    <t xml:space="preserve">1.12682890892029</t>
   </si>
   <si>
     <t xml:space="preserve">1.1220942735672</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">1.11391639709473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13974118232727</t>
+    <t xml:space="preserve">1.13974130153656</t>
   </si>
   <si>
     <t xml:space="preserve">1.11865091323853</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">1.12898087501526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13586759567261</t>
+    <t xml:space="preserve">1.13586747646332</t>
   </si>
   <si>
     <t xml:space="preserve">1.13027215003967</t>
@@ -4181,13 +4181,13 @@
     <t xml:space="preserve">1.13543713092804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12381601333618</t>
+    <t xml:space="preserve">1.12381589412689</t>
   </si>
   <si>
     <t xml:space="preserve">1.11951184272766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12166380882263</t>
+    <t xml:space="preserve">1.12166392803192</t>
   </si>
   <si>
     <t xml:space="preserve">1.12984180450439</t>
@@ -4196,10 +4196,10 @@
     <t xml:space="preserve">1.14490628242493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11692929267883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09282600879669</t>
+    <t xml:space="preserve">1.11692917346954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0928258895874</t>
   </si>
   <si>
     <t xml:space="preserve">1.07603967189789</t>
@@ -4211,37 +4211,37 @@
     <t xml:space="preserve">1.06958341598511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07173562049866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09971272945404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12467682361603</t>
+    <t xml:space="preserve">1.07173550128937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09971261024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12467670440674</t>
   </si>
   <si>
     <t xml:space="preserve">1.12553763389587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13888037204742</t>
+    <t xml:space="preserve">1.13888049125671</t>
   </si>
   <si>
     <t xml:space="preserve">1.14705836772919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18837833404541</t>
+    <t xml:space="preserve">1.18837821483612</t>
   </si>
   <si>
     <t xml:space="preserve">1.19354331493378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19827771186829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20042991638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20516455173492</t>
+    <t xml:space="preserve">1.19827783107758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20043003559113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20516443252563</t>
   </si>
   <si>
     <t xml:space="preserve">1.21032953262329</t>
@@ -4250,22 +4250,22 @@
     <t xml:space="preserve">1.17245292663574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15093207359314</t>
+    <t xml:space="preserve">1.15093219280243</t>
   </si>
   <si>
     <t xml:space="preserve">1.18192207813263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19096076488495</t>
+    <t xml:space="preserve">1.19096088409424</t>
   </si>
   <si>
     <t xml:space="preserve">1.20387327671051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20430386066437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21119022369385</t>
+    <t xml:space="preserve">1.20430374145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21119034290314</t>
   </si>
   <si>
     <t xml:space="preserve">1.19483458995819</t>
@@ -4274,16 +4274,16 @@
     <t xml:space="preserve">1.18665671348572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20989918708801</t>
+    <t xml:space="preserve">1.20989906787872</t>
   </si>
   <si>
     <t xml:space="preserve">1.18794786930084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20344281196594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21506404876709</t>
+    <t xml:space="preserve">1.20344293117523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21506416797638</t>
   </si>
   <si>
     <t xml:space="preserve">1.20903825759888</t>
@@ -4304,31 +4304,31 @@
     <t xml:space="preserve">1.19225203990936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17976987361908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18579590320587</t>
+    <t xml:space="preserve">1.17976999282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18579578399658</t>
   </si>
   <si>
     <t xml:space="preserve">1.18966948986053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20215165615082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20129084587097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16944003105164</t>
+    <t xml:space="preserve">1.20215153694153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20129072666168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16943991184235</t>
   </si>
   <si>
     <t xml:space="preserve">1.18364369869232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1978474855423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18149149417877</t>
+    <t xml:space="preserve">1.19784736633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18149161338806</t>
   </si>
   <si>
     <t xml:space="preserve">1.18493497371674</t>
@@ -4340,7 +4340,7 @@
     <t xml:space="preserve">1.16814875602722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15738821029663</t>
+    <t xml:space="preserve">1.15738832950592</t>
   </si>
   <si>
     <t xml:space="preserve">1.18278288841248</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">1.25078856945038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26240992546082</t>
+    <t xml:space="preserve">1.26240980625153</t>
   </si>
   <si>
     <t xml:space="preserve">1.23658490180969</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">1.21678566932678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22496354579926</t>
+    <t xml:space="preserve">1.22496366500854</t>
   </si>
   <si>
     <t xml:space="preserve">1.25121903419495</t>
@@ -4382,19 +4382,19 @@
     <t xml:space="preserve">1.25853610038757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26714444160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29426074028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32869386672974</t>
+    <t xml:space="preserve">1.26714432239532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29426062107086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32869374752045</t>
   </si>
   <si>
     <t xml:space="preserve">1.33256757259369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33730220794678</t>
+    <t xml:space="preserve">1.33730232715607</t>
   </si>
   <si>
     <t xml:space="preserve">1.31664216518402</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">1.32137680053711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31922483444214</t>
+    <t xml:space="preserve">1.31922471523285</t>
   </si>
   <si>
     <t xml:space="preserve">1.35150599479675</t>
@@ -4412,13 +4412,13 @@
     <t xml:space="preserve">1.33988463878632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35279715061188</t>
+    <t xml:space="preserve">1.35279703140259</t>
   </si>
   <si>
     <t xml:space="preserve">1.35968375205994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3523668050766</t>
+    <t xml:space="preserve">1.35236668586731</t>
   </si>
   <si>
     <t xml:space="preserve">1.36614012718201</t>
@@ -4427,13 +4427,13 @@
     <t xml:space="preserve">1.37733089923859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34332811832428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36786162853241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36829221248627</t>
+    <t xml:space="preserve">1.34332799911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3678617477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36829209327698</t>
   </si>
   <si>
     <t xml:space="preserve">1.3880912065506</t>
@@ -4460,10 +4460,10 @@
     <t xml:space="preserve">1.44877994060516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43758916854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37905263900757</t>
+    <t xml:space="preserve">1.43758904933929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37905251979828</t>
   </si>
   <si>
     <t xml:space="preserve">1.41047286987305</t>
@@ -5978,7 +5978,7 @@
     <t xml:space="preserve">2.71199989318848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70900011062622</t>
+    <t xml:space="preserve">2.72399997711182</t>
   </si>
 </sst>
 </file>
@@ -71421,22 +71421,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6943287037</v>
+        <v>45967.6932060185</v>
       </c>
       <c r="B2505" t="n">
-        <v>6207128</v>
+        <v>8906889</v>
       </c>
       <c r="C2505" t="n">
-        <v>2.73399996757507</v>
+        <v>2.74399995803833</v>
       </c>
       <c r="D2505" t="n">
-        <v>2.69799995422363</v>
+        <v>2.70099997520447</v>
       </c>
       <c r="E2505" t="n">
-        <v>2.72000002861023</v>
+        <v>2.72900009155273</v>
       </c>
       <c r="F2505" t="n">
-        <v>2.70900011062622</v>
+        <v>2.72399997711182</v>
       </c>
       <c r="G2505" t="s">
         <v>1988</v>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765547633171082</t>
+    <t xml:space="preserve">0.765547692775726</t>
   </si>
   <si>
     <t xml:space="preserve">A2A.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774304032325745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76930034160614</t>
+    <t xml:space="preserve">0.774303913116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769300401210785</t>
   </si>
   <si>
     <t xml:space="preserve">0.77743124961853</t>
@@ -56,49 +56,49 @@
     <t xml:space="preserve">0.772427558898926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.775554835796356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73615163564682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728020906448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.708631932735443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70112669467926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.678610444068909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.686115920543671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.662974298000336</t>
+    <t xml:space="preserve">0.775554776191711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73615175485611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728020846843719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.708631992340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701126575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678610503673553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.686115860939026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.662974238395691</t>
   </si>
   <si>
     <t xml:space="preserve">0.66985422372818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.673606991767883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661723375320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.68986850976944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.667352497577667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.688617706298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689243018627167</t>
+    <t xml:space="preserve">0.673606932163239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661723434925079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689868569374084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.667352437973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.688617527484894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689243078231812</t>
   </si>
   <si>
     <t xml:space="preserve">0.676108717918396</t>
@@ -107,28 +107,28 @@
     <t xml:space="preserve">0.671105027198792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66672694683075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643585503101349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612312972545624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597927808761597</t>
+    <t xml:space="preserve">0.666727006435394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643585383892059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612313032150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597927689552307</t>
   </si>
   <si>
     <t xml:space="preserve">0.605745851993561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610749363899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614189445972443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627323865890503</t>
+    <t xml:space="preserve">0.610749423503876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614189326763153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627323806285858</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942094802856</t>
@@ -140,34 +140,34 @@
     <t xml:space="preserve">0.646712720394135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636080026626587</t>
+    <t xml:space="preserve">0.636080086231232</t>
   </si>
   <si>
     <t xml:space="preserve">0.656719863414764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645461797714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641083598136902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647963583469391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.657345235347748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661098122596741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.672981441020966</t>
+    <t xml:space="preserve">0.645461678504944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641083717346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.647963643074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.657345294952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661097884178162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.672981381416321</t>
   </si>
   <si>
     <t xml:space="preserve">0.666101515293121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.664850533008575</t>
+    <t xml:space="preserve">0.66485059261322</t>
   </si>
   <si>
     <t xml:space="preserve">0.658596158027649</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">0.651716232299805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654843509197235</t>
+    <t xml:space="preserve">0.65484344959259</t>
   </si>
   <si>
     <t xml:space="preserve">0.669228792190552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.713010013103485</t>
+    <t xml:space="preserve">0.71301007270813</t>
   </si>
   <si>
     <t xml:space="preserve">0.69299578666687</t>
@@ -191,97 +191,97 @@
     <t xml:space="preserve">0.691119432449341</t>
   </si>
   <si>
-    <t xml:space="preserve">0.694246649742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697999358177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696123003959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7030029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692370295524597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.699250161647797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714261054992676</t>
+    <t xml:space="preserve">0.694246768951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697999477386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696123063564301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703002870082855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692370355129242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.699250340461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714260995388031</t>
   </si>
   <si>
     <t xml:space="preserve">0.714886486530304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.702377557754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705504715442657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735526204109192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.740529656410217</t>
+    <t xml:space="preserve">0.702377498149872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705504834651947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735526144504547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.740529775619507</t>
   </si>
   <si>
     <t xml:space="preserve">0.74428254365921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.748660624027252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.738027989864349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750537097454071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754289627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768049538135529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757416844367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766798496246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.752413213253021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781183779239655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778056621551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786187350749969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779307663440704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768675029277802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755540430545807</t>
+    <t xml:space="preserve">0.748660683631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.738027930259705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750536918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754289507865906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768049418926239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757416784763336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766798555850983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.752413272857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781183838844299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778056740760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786187469959259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779307544231415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768674910068512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755540549755096</t>
   </si>
   <si>
     <t xml:space="preserve">0.760544061660767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.764296770095825</t>
+    <t xml:space="preserve">0.764296650886536</t>
   </si>
   <si>
     <t xml:space="preserve">0.770551264286041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.759293258190155</t>
+    <t xml:space="preserve">0.75929319858551</t>
   </si>
   <si>
     <t xml:space="preserve">0.769925832748413</t>
@@ -290,118 +290,118 @@
     <t xml:space="preserve">0.761169493198395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.767424046993256</t>
+    <t xml:space="preserve">0.7674241065979</t>
   </si>
   <si>
     <t xml:space="preserve">0.747409760951996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.751787781715393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754915177822113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781809210777283</t>
+    <t xml:space="preserve">0.751787841320038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754914999008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781809270381927</t>
   </si>
   <si>
     <t xml:space="preserve">0.801198244094849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804950833320618</t>
+    <t xml:space="preserve">0.804950952529907</t>
   </si>
   <si>
     <t xml:space="preserve">0.79932177066803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.78556215763092</t>
+    <t xml:space="preserve">0.785562038421631</t>
   </si>
   <si>
     <t xml:space="preserve">0.796820104122162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791816473007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801823556423187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733649909496307</t>
+    <t xml:space="preserve">0.791816413402557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801823616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733649849891663</t>
   </si>
   <si>
     <t xml:space="preserve">0.725519001483917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766306459903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759828746318817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750760018825531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778613924980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703473091125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692461311817169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705416560173035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.730031549930573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763067603111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762419939041138</t>
+    <t xml:space="preserve">0.766306400299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759828805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750760197639465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778614044189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703473210334778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692461133003235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.70541650056839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.730031609535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763067662715912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762419879436493</t>
   </si>
   <si>
     <t xml:space="preserve">0.769545257091522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.75788551568985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742986738681793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742339134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.758533358573914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777318596839905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774079740047455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776022911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783796191215515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779909551143646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790273725986481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789626002311707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79416024684906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805172502994537</t>
+    <t xml:space="preserve">0.75788539648056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742986917495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742339253425598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758533298969269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777318477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77407968044281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776022970676422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78379613161087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779909491539001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790273785591125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789626061916351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79416036605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805172443389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.807763457298279</t>
@@ -410,151 +410,151 @@
     <t xml:space="preserve">0.822662055492401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817480027675629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820718705654144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.822014272212982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809706687927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814241051673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816184461116791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804524600505829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801285862922668</t>
+    <t xml:space="preserve">0.817479908466339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8207186460495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.822014331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809706747531891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814241111278534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816184401512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804524719715118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801285743713379</t>
   </si>
   <si>
     <t xml:space="preserve">0.812945544719696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801933586597443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786387264728546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788330435752869</t>
+    <t xml:space="preserve">0.801933467388153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786387205123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788330495357513</t>
   </si>
   <si>
     <t xml:space="preserve">0.771488606929779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783148348331451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782500565052032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781852841377258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770192980766296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785091578960419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795455932617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811002373695374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794808149337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796103656291962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798694789409637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802581250667572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790921449661255</t>
+    <t xml:space="preserve">0.783148407936096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782500684261322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781852781772614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770193040370941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785091698169708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795455873012543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811002314090729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794808208942413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796103715896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798694729804993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802581369876862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7909215092659</t>
   </si>
   <si>
     <t xml:space="preserve">0.796751439571381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799342453479767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81035453081131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780557334423065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784443855285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785739481449127</t>
+    <t xml:space="preserve">0.799342393875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810354471206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780557215213776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784443795681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785739421844482</t>
   </si>
   <si>
     <t xml:space="preserve">0.827196419239044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81359338760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80063784122467</t>
+    <t xml:space="preserve">0.813593447208405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80063796043396</t>
   </si>
   <si>
     <t xml:space="preserve">0.797399163246155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803876876831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807115912437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76112425327301</t>
+    <t xml:space="preserve">0.803876936435699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807115733623505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761124432086945</t>
   </si>
   <si>
     <t xml:space="preserve">0.770840883255005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.731327176094055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735861539840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.720315158367157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72161066532135</t>
+    <t xml:space="preserve">0.731327056884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735861420631409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.720315217971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721610605716705</t>
   </si>
   <si>
     <t xml:space="preserve">0.719019591808319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696347832679749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696995556354523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.709950923919678</t>
+    <t xml:space="preserve">0.696347773075104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696995496749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.709950804710388</t>
   </si>
   <si>
     <t xml:space="preserve">0.713837444782257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.711894154548645</t>
+    <t xml:space="preserve">0.71189421415329</t>
   </si>
   <si>
     <t xml:space="preserve">0.707359790802002</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">0.728735983371735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715780735015869</t>
+    <t xml:space="preserve">0.715780794620514</t>
   </si>
   <si>
     <t xml:space="preserve">0.722258448600769</t>
@@ -572,10 +572,10 @@
     <t xml:space="preserve">0.765010952949524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.7546466588974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755294382572174</t>
+    <t xml:space="preserve">0.754646718502045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755294322967529</t>
   </si>
   <si>
     <t xml:space="preserve">0.787682712078094</t>
@@ -584,55 +584,55 @@
     <t xml:space="preserve">0.776670634746552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.772136390209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787034928798676</t>
+    <t xml:space="preserve">0.772136449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78703498840332</t>
   </si>
   <si>
     <t xml:space="preserve">0.81683224439621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819423258304596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799990236759186</t>
+    <t xml:space="preserve">0.819423198699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799990296363831</t>
   </si>
   <si>
     <t xml:space="preserve">0.824605286121368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838856101036072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831730842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832378447055817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840151727199554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848572492599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841447293758392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844686090946198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830435156822205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798047006130219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815536677837372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820071041584015</t>
+    <t xml:space="preserve">0.838856160640717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831730663776398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832378387451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84015166759491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848572671413422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841447353363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844685971736908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830435216426849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798046886920929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815536558628082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820070922374725</t>
   </si>
   <si>
     <t xml:space="preserve">0.806467890739441</t>
@@ -641,13 +641,13 @@
     <t xml:space="preserve">0.811650037765503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.836265087127686</t>
+    <t xml:space="preserve">0.83626514673233</t>
   </si>
   <si>
     <t xml:space="preserve">0.844038307666779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837560653686523</t>
+    <t xml:space="preserve">0.837560772895813</t>
   </si>
   <si>
     <t xml:space="preserve">0.836912870407104</t>
@@ -662,10 +662,10 @@
     <t xml:space="preserve">0.825900912284851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.829139709472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84662938117981</t>
+    <t xml:space="preserve">0.829139769077301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846629321575165</t>
   </si>
   <si>
     <t xml:space="preserve">0.849220454692841</t>
@@ -674,85 +674,85 @@
     <t xml:space="preserve">0.864766836166382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867357730865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868005812168121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870596647262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857641339302063</t>
+    <t xml:space="preserve">0.867357969284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868005692958832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870596766471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857641458511353</t>
   </si>
   <si>
     <t xml:space="preserve">0.865414619445801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866710245609283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.853107035160065</t>
+    <t xml:space="preserve">0.866710126399994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85310697555542</t>
   </si>
   <si>
     <t xml:space="preserve">0.855698108673096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.858289241790771</t>
+    <t xml:space="preserve">0.858289301395416</t>
   </si>
   <si>
     <t xml:space="preserve">0.860232353210449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.87254011631012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874483287334442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887438595294952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893916130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892620861530304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912701547145844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909462630748749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908166944980621</t>
+    <t xml:space="preserve">0.872539937496185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.874483346939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887438714504242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893916189670563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892620742321014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912701368331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909462571144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908167123794556</t>
   </si>
   <si>
     <t xml:space="preserve">0.919826745986938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918531179428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875778794288635</t>
+    <t xml:space="preserve">0.918531358242035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875778675079346</t>
   </si>
   <si>
     <t xml:space="preserve">0.877722203731537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.891972839832306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884847581386566</t>
+    <t xml:space="preserve">0.891972959041595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884847521781921</t>
   </si>
   <si>
     <t xml:space="preserve">0.895211756229401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.884199738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876426696777344</t>
+    <t xml:space="preserve">0.884199798107147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876426517963409</t>
   </si>
   <si>
     <t xml:space="preserve">0.862175703048706</t>
@@ -764,97 +764,97 @@
     <t xml:space="preserve">0.88225644826889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899098336696625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890677452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926952183246613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915292382240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917235791683197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966466069221497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958045065402985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965170621871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9612837433815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963227093219757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941850781440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941202998161316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958692789077759</t>
+    <t xml:space="preserve">0.899098515510559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890677392482758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926952242851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.915292501449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917235672473907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966465950012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958045125007629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965170443058014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961283981800079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963227152824402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94185084104538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941203117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958692729473114</t>
   </si>
   <si>
     <t xml:space="preserve">0.982278108596802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988308548927307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997018933296204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00036919116974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992998838424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968207359313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981608152389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986298441886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988978564739227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989648640155792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.974907696247101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999699056148529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00505948066711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998359143733978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997689127922058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00170946121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00706970691681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02047026157379</t>
+    <t xml:space="preserve">0.988308608531952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997019052505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00036907196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992998778820038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96820729970932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981608092784882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986298501491547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988978385925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989648520946503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97490781545639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999699175357819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00505971908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998359203338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997689187526703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00170934200287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00706958770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02047049999237</t>
   </si>
   <si>
     <t xml:space="preserve">1.02985095977783</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">1.0177903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995009124279022</t>
+    <t xml:space="preserve">0.995009064674377</t>
   </si>
   <si>
     <t xml:space="preserve">0.999029219150543</t>
@@ -872,127 +872,127 @@
     <t xml:space="preserve">0.976917862892151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974237740039825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970217525959015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96552711725235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960836946964264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961507022380829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96418708562851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980268180370331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978927850723267</t>
+    <t xml:space="preserve">0.974237680435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970217406749725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965527176856995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960837006568909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961506903171539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964187145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980268120765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978927969932556</t>
   </si>
   <si>
     <t xml:space="preserve">0.984958350658417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97289764881134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960166871547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958826899528503</t>
+    <t xml:space="preserve">0.972897589206696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960166752338409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958826720714569</t>
   </si>
   <si>
     <t xml:space="preserve">0.951456248760223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955476522445679</t>
+    <t xml:space="preserve">0.955476582050323</t>
   </si>
   <si>
     <t xml:space="preserve">0.949446320533752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.963517069816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950116217136383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953466415405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956816613674164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958156704902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952796518802643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962176918983459</t>
+    <t xml:space="preserve">0.963517129421234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950116336345673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953466475009918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956816732883453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958156645298004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952796578407288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962176978588104</t>
   </si>
   <si>
     <t xml:space="preserve">0.944755852222443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931355237960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948106110095978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954136490821838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957486629486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939395546913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946766197681427</t>
+    <t xml:space="preserve">0.931355178356171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948106050491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954136610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957486748695374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939395725727081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946766078472137</t>
   </si>
   <si>
     <t xml:space="preserve">0.934705317020416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9286749958992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9246546626091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932695269584656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945425987243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959496796131134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973567605018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978258013725281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993668735027313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984288275241852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983618319034576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994338929653168</t>
+    <t xml:space="preserve">0.928675055503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924654722213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932695150375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945425927639008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959496855735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97356766462326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978257954120636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993668794631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984288394451141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983618259429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994339048862457</t>
   </si>
   <si>
     <t xml:space="preserve">0.977587938308716</t>
@@ -1001,52 +1001,52 @@
     <t xml:space="preserve">0.980938017368317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972227454185486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966197192668915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96954745054245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96887743473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97155749797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995678901672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992328882217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966867327690125</t>
+    <t xml:space="preserve">0.972227573394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96619713306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96954733133316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96887731552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971557557582855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995678842067719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992328703403473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96686726808548</t>
   </si>
   <si>
     <t xml:space="preserve">1.02114045619965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01041996479034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01443994045258</t>
+    <t xml:space="preserve">1.01041984558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01444005966187</t>
   </si>
   <si>
     <t xml:space="preserve">1.02181053161621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02382051944733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0285108089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03320109844208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03923165798187</t>
+    <t xml:space="preserve">1.02382063865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02851092815399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03320121765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03923153877258</t>
   </si>
   <si>
     <t xml:space="preserve">1.02650082111359</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">1.05531251430511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05866265296936</t>
+    <t xml:space="preserve">1.05866277217865</t>
   </si>
   <si>
     <t xml:space="preserve">1.04459190368652</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">1.05330240726471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0680433511734</t>
+    <t xml:space="preserve">1.06804323196411</t>
   </si>
   <si>
     <t xml:space="preserve">1.0727334022522</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">1.08613431453705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0955148935318</t>
+    <t xml:space="preserve">1.09551477432251</t>
   </si>
   <si>
     <t xml:space="preserve">1.08345413208008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08211398124695</t>
+    <t xml:space="preserve">1.08211410045624</t>
   </si>
   <si>
     <t xml:space="preserve">1.05397236347198</t>
@@ -1091,31 +1091,31 @@
     <t xml:space="preserve">1.04392182826996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04861199855804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04660212993622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03990149497986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04258179664612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01980042457581</t>
+    <t xml:space="preserve">1.04861223697662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04660189151764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03990173339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04258167743683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01980030536652</t>
   </si>
   <si>
     <t xml:space="preserve">1.01578032970428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05196249485016</t>
+    <t xml:space="preserve">1.05196237564087</t>
   </si>
   <si>
     <t xml:space="preserve">1.06737327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.066033244133</t>
+    <t xml:space="preserve">1.06603312492371</t>
   </si>
   <si>
     <t xml:space="preserve">1.02449071407318</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">1.02784097194672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05665266513824</t>
+    <t xml:space="preserve">1.05665254592896</t>
   </si>
   <si>
     <t xml:space="preserve">1.06134283542633</t>
@@ -1136,100 +1136,100 @@
     <t xml:space="preserve">1.07742381095886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07943391799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06938314437866</t>
+    <t xml:space="preserve">1.07943379878998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06938326358795</t>
   </si>
   <si>
     <t xml:space="preserve">1.05933272838593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03856134414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02683579921722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03588140010834</t>
+    <t xml:space="preserve">1.03856146335602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02683591842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03588128089905</t>
   </si>
   <si>
     <t xml:space="preserve">1.04191160202026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996348977088928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971222400665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995343804359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944421052932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953131496906281</t>
+    <t xml:space="preserve">0.996349036693573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971222519874573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995343863964081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944420874118805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953131377696991</t>
   </si>
   <si>
     <t xml:space="preserve">0.941405773162842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959831953048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94643098115921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957821786403656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95045131444931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936380565166473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967202246189117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99132364988327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975577771663666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99333381652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00003433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00137448310852</t>
+    <t xml:space="preserve">0.959831833839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9464311003685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957821667194366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950451374053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936380386352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967202365398407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991323590278625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975577831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993333876132965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00003409385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00137424468994</t>
   </si>
   <si>
     <t xml:space="preserve">0.991658687591553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00673472881317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999364256858826</t>
+    <t xml:space="preserve">1.00673460960388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999364137649536</t>
   </si>
   <si>
     <t xml:space="preserve">1.04023659229279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04157674312592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04224681854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04961705207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04995238780975</t>
+    <t xml:space="preserve">1.04157662391663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04224669933319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04961717128754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04995214939117</t>
   </si>
   <si>
     <t xml:space="preserve">1.06268286705017</t>
@@ -1238,58 +1238,58 @@
     <t xml:space="preserve">1.07206344604492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05832779407501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06335282325745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07407367229462</t>
+    <t xml:space="preserve">1.05832767486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06335294246674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07407379150391</t>
   </si>
   <si>
     <t xml:space="preserve">1.08043897151947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08546447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09048962593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09484481811523</t>
+    <t xml:space="preserve">1.08546435832977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09048974514008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09484493732452</t>
   </si>
   <si>
     <t xml:space="preserve">1.09819507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09853005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12198162078857</t>
+    <t xml:space="preserve">1.0985301733017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12198138237</t>
   </si>
   <si>
     <t xml:space="preserve">1.11762607097626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11729121208191</t>
+    <t xml:space="preserve">1.11729109287262</t>
   </si>
   <si>
     <t xml:space="preserve">1.10724067687988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10757565498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12265145778656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13002181053162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10992085933685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11829614639282</t>
+    <t xml:space="preserve">1.10757577419281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12265157699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13002192974091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10992074012756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11829602718353</t>
   </si>
   <si>
     <t xml:space="preserve">1.05732262134552</t>
@@ -1301,10 +1301,10 @@
     <t xml:space="preserve">1.03895282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05287516117096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04208540916443</t>
+    <t xml:space="preserve">1.05287528038025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04208528995514</t>
   </si>
   <si>
     <t xml:space="preserve">1.04730629920959</t>
@@ -1313,37 +1313,37 @@
     <t xml:space="preserve">1.02572667598724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00693142414093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980827271938324</t>
+    <t xml:space="preserve">1.00693166255951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980827152729034</t>
   </si>
   <si>
     <t xml:space="preserve">0.998926162719727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01076030731201</t>
+    <t xml:space="preserve">1.01076018810272</t>
   </si>
   <si>
     <t xml:space="preserve">1.00484323501587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02920734882355</t>
+    <t xml:space="preserve">1.02920711040497</t>
   </si>
   <si>
     <t xml:space="preserve">1.00936806201935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00658357143402</t>
+    <t xml:space="preserve">1.00658345222473</t>
   </si>
   <si>
     <t xml:space="preserve">0.999622285366058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968993246555328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01598107814789</t>
+    <t xml:space="preserve">0.968993186950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0159809589386</t>
   </si>
   <si>
     <t xml:space="preserve">1.02398633956909</t>
@@ -1352,10 +1352,10 @@
     <t xml:space="preserve">1.0316436290741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02851104736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01980984210968</t>
+    <t xml:space="preserve">1.02851116657257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01980972290039</t>
   </si>
   <si>
     <t xml:space="preserve">1.04382574558258</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">1.04661011695862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02363836765289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02537870407104</t>
+    <t xml:space="preserve">1.0236382484436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02537858486176</t>
   </si>
   <si>
     <t xml:space="preserve">1.00588738918304</t>
@@ -1379,10 +1379,10 @@
     <t xml:space="preserve">1.02120196819305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02642273902893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03373193740845</t>
+    <t xml:space="preserve">1.02642285823822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03373217582703</t>
   </si>
   <si>
     <t xml:space="preserve">1.01389276981354</t>
@@ -1391,70 +1391,70 @@
     <t xml:space="preserve">1.03860485553741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0511349439621</t>
+    <t xml:space="preserve">1.05113482475281</t>
   </si>
   <si>
     <t xml:space="preserve">1.06122851371765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07236659526825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06018435955048</t>
+    <t xml:space="preserve">1.07236647605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06018447875977</t>
   </si>
   <si>
     <t xml:space="preserve">1.06262075901031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05600762367249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07375872135162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0671454668045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07863140106201</t>
+    <t xml:space="preserve">1.05600774288177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07375860214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06714558601379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0786315202713</t>
   </si>
   <si>
     <t xml:space="preserve">1.09290194511414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0942941904068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10160315036774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08420050144196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04835045337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06157672405243</t>
+    <t xml:space="preserve">1.09429407119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10160338878632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08420038223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04835057258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06157660484314</t>
   </si>
   <si>
     <t xml:space="preserve">1.07201838493347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07584714889526</t>
+    <t xml:space="preserve">1.07584702968597</t>
   </si>
   <si>
     <t xml:space="preserve">1.07132232189178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09394598007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08106803894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09011745452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0824601650238</t>
+    <t xml:space="preserve">1.09394609928131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08106791973114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09011733531952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08246004581451</t>
   </si>
   <si>
     <t xml:space="preserve">1.10299551486969</t>
@@ -1472,10 +1472,10 @@
     <t xml:space="preserve">1.10612809658051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11134886741638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10821640491486</t>
+    <t xml:space="preserve">1.11134898662567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10821628570557</t>
   </si>
   <si>
     <t xml:space="preserve">1.10960865020752</t>
@@ -1484,31 +1484,31 @@
     <t xml:space="preserve">1.08837723731995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08802890777588</t>
+    <t xml:space="preserve">1.08802902698517</t>
   </si>
   <si>
     <t xml:space="preserve">1.08942127227783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07549893856049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06540536880493</t>
+    <t xml:space="preserve">1.0754988193512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06540524959564</t>
   </si>
   <si>
     <t xml:space="preserve">1.03338396549225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04243326187134</t>
+    <t xml:space="preserve">1.04243338108063</t>
   </si>
   <si>
     <t xml:space="preserve">1.02154994010925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0309476852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04173743724823</t>
+    <t xml:space="preserve">1.03094744682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04173731803894</t>
   </si>
   <si>
     <t xml:space="preserve">1.05705189704895</t>
@@ -1517,28 +1517,28 @@
     <t xml:space="preserve">1.0789794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09220564365387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09116160869598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08454835414886</t>
+    <t xml:space="preserve">1.09220576286316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09116148948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08454847335815</t>
   </si>
   <si>
     <t xml:space="preserve">1.08141589164734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09847092628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09603440761566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07619500160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07445466518402</t>
+    <t xml:space="preserve">1.09847068786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09603428840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07619512081146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0744549036026</t>
   </si>
   <si>
     <t xml:space="preserve">1.0587922334671</t>
@@ -1553,106 +1553,106 @@
     <t xml:space="preserve">1.04069316387177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0319916009903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04452192783356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04417359828949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05183112621307</t>
+    <t xml:space="preserve">1.03199172019958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04452180862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04417395591736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05183088779449</t>
   </si>
   <si>
     <t xml:space="preserve">1.03616845607758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05844402313232</t>
+    <t xml:space="preserve">1.05844414234161</t>
   </si>
   <si>
     <t xml:space="preserve">1.03442811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00310289859772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99161696434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00832378864288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01424062252045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01772129535675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01354455947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993705272674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988136470317841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977346777915955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00553941726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986047923564911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98952853679657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992313265800476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982915461063385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991965115070343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01319670677185</t>
+    <t xml:space="preserve">1.00310277938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9916170835495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00832366943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01424074172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01772141456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01354467868805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993705332279205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98813658952713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97734659910202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00553929805756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986047863960266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989528715610504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992313206195831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98291552066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991964995861053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01319658756256</t>
   </si>
   <si>
     <t xml:space="preserve">1.00414705276489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02050578594208</t>
+    <t xml:space="preserve">1.02050566673279</t>
   </si>
   <si>
     <t xml:space="preserve">1.0156329870224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0351243019104</t>
+    <t xml:space="preserve">1.03512418270111</t>
   </si>
   <si>
     <t xml:space="preserve">1.0393009185791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05252707004547</t>
+    <t xml:space="preserve">1.05252718925476</t>
   </si>
   <si>
     <t xml:space="preserve">1.05461549758911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03721261024475</t>
+    <t xml:space="preserve">1.03721272945404</t>
   </si>
   <si>
     <t xml:space="preserve">1.02711892127991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03999710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06610131263733</t>
+    <t xml:space="preserve">1.03999698162079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06610143184662</t>
   </si>
   <si>
     <t xml:space="preserve">1.06088054180145</t>
@@ -1661,34 +1661,34 @@
     <t xml:space="preserve">1.04034507274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03233969211578</t>
+    <t xml:space="preserve">1.03233981132507</t>
   </si>
   <si>
     <t xml:space="preserve">1.04278147220612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0434775352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07410669326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10090708732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11761391162872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12701141834259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11378538608551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1064760684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12318289279938</t>
+    <t xml:space="preserve">1.04347765445709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07410657405853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10090720653534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11761403083801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12701153755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11378526687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10647594928741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12318301200867</t>
   </si>
   <si>
     <t xml:space="preserve">1.13118815422058</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">1.094642162323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11622190475464</t>
+    <t xml:space="preserve">1.11622166633606</t>
   </si>
   <si>
     <t xml:space="preserve">1.11831021308899</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">1.13501679897308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13675725460052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1381493806839</t>
+    <t xml:space="preserve">1.13675713539124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13814926147461</t>
   </si>
   <si>
     <t xml:space="preserve">1.14302217960358</t>
@@ -1724,22 +1724,22 @@
     <t xml:space="preserve">1.10403966903687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10891270637512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09951484203339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1019514799118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0991667509079</t>
+    <t xml:space="preserve">1.10891258716583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09951496124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10195136070251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09916687011719</t>
   </si>
   <si>
     <t xml:space="preserve">1.09499001502991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10578012466431</t>
+    <t xml:space="preserve">1.10578000545502</t>
   </si>
   <si>
     <t xml:space="preserve">1.09185767173767</t>
@@ -1748,52 +1748,52 @@
     <t xml:space="preserve">1.07793533802032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08071982860565</t>
+    <t xml:space="preserve">1.08071970939636</t>
   </si>
   <si>
     <t xml:space="preserve">1.0866367816925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06227290630341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08280813694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09742665290833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10021114349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09777474403381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10369157791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11100077629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10543191432953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08594071865082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09568619728088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08907306194305</t>
+    <t xml:space="preserve">1.06227278709412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08280825614929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09742677211761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10021102428436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09777462482452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10369169712067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11100089550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10543203353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08594059944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09568631649017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08907330036163</t>
   </si>
   <si>
     <t xml:space="preserve">1.11726582050323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12074649333954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10752010345459</t>
+    <t xml:space="preserve">1.12074661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10752022266388</t>
   </si>
   <si>
     <t xml:space="preserve">1.1103048324585</t>
@@ -1802,13 +1802,13 @@
     <t xml:space="preserve">1.12179064750671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11935424804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13571298122406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13536489009857</t>
+    <t xml:space="preserve">1.11935436725616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13571310043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13536500930786</t>
   </si>
   <si>
     <t xml:space="preserve">1.13084018230438</t>
@@ -1817,25 +1817,25 @@
     <t xml:space="preserve">1.13223242759705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14754688739777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06331706047058</t>
+    <t xml:space="preserve">1.14754700660706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.063316822052</t>
   </si>
   <si>
     <t xml:space="preserve">1.05391931533813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04626214504242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05426740646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04869842529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02433454990387</t>
+    <t xml:space="preserve">1.04626202583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05426752567291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04869854450226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02433443069458</t>
   </si>
   <si>
     <t xml:space="preserve">1.01946151256561</t>
@@ -1847,22 +1847,22 @@
     <t xml:space="preserve">1.0037989616394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997882068157196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00727963447571</t>
+    <t xml:space="preserve">0.997881948947906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00727951526642</t>
   </si>
   <si>
     <t xml:space="preserve">1.02015769481659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07654321193695</t>
+    <t xml:space="preserve">1.07654297351837</t>
   </si>
   <si>
     <t xml:space="preserve">1.08517634868622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0972056388855</t>
+    <t xml:space="preserve">1.09720551967621</t>
   </si>
   <si>
     <t xml:space="preserve">1.09647643566132</t>
@@ -1871,25 +1871,25 @@
     <t xml:space="preserve">1.06622123718262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08116674423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07205367088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06038892269135</t>
+    <t xml:space="preserve">1.08116662502289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07205379009247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06038904190063</t>
   </si>
   <si>
     <t xml:space="preserve">1.05127608776093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06403422355652</t>
+    <t xml:space="preserve">1.06403434276581</t>
   </si>
   <si>
     <t xml:space="preserve">1.07168924808502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08043766021729</t>
+    <t xml:space="preserve">1.080437541008</t>
   </si>
   <si>
     <t xml:space="preserve">1.0979346036911</t>
@@ -1898,13 +1898,13 @@
     <t xml:space="preserve">1.09866368770599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10449600219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10048627853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10230886936188</t>
+    <t xml:space="preserve">1.10449588298798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10048639774323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10230875015259</t>
   </si>
   <si>
     <t xml:space="preserve">1.09574747085571</t>
@@ -1916,28 +1916,28 @@
     <t xml:space="preserve">1.13219964504242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12563800811768</t>
+    <t xml:space="preserve">1.12563812732697</t>
   </si>
   <si>
     <t xml:space="preserve">1.14021897315979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14750921726227</t>
+    <t xml:space="preserve">1.14750945568085</t>
   </si>
   <si>
     <t xml:space="preserve">1.13584470748901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11944127082825</t>
+    <t xml:space="preserve">1.11944139003754</t>
   </si>
   <si>
     <t xml:space="preserve">1.11543154716492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10376679897308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11251544952393</t>
+    <t xml:space="preserve">1.10376691818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11251533031464</t>
   </si>
   <si>
     <t xml:space="preserve">1.11069273948669</t>
@@ -1946,16 +1946,16 @@
     <t xml:space="preserve">1.13511574268341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1500608921051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15188348293304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14787375926971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15261256694794</t>
+    <t xml:space="preserve">1.15006101131439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15188372135162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.147873878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15261268615723</t>
   </si>
   <si>
     <t xml:space="preserve">1.16427731513977</t>
@@ -1964,55 +1964,55 @@
     <t xml:space="preserve">1.1704740524292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17156755924225</t>
+    <t xml:space="preserve">1.17156767845154</t>
   </si>
   <si>
     <t xml:space="preserve">1.17229676246643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17849349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17484843730927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19161641597748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16318380832672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16609966754913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17995166778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18469035625458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18104517459869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17120325565338</t>
+    <t xml:space="preserve">1.17849361896515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17484831809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19161629676819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16318368911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16609978675842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17995154857635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18469047546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18104529380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1712030172348</t>
   </si>
   <si>
     <t xml:space="preserve">1.17375469207764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14969646930695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15407085418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17083847522736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16209030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1668289899826</t>
+    <t xml:space="preserve">1.14969635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15407073497772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17083859443665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16209006309509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16682887077332</t>
   </si>
   <si>
     <t xml:space="preserve">1.16755795478821</t>
@@ -2021,19 +2021,19 @@
     <t xml:space="preserve">1.17010962963104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13183510303497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12418019771576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12782514095306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14277064800262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16099655628204</t>
+    <t xml:space="preserve">1.13183498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12418007850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12782526016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14277052879333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16099643707275</t>
   </si>
   <si>
     <t xml:space="preserve">1.14459323883057</t>
@@ -2042,10 +2042,10 @@
     <t xml:space="preserve">1.15297722816467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13985443115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13475120067596</t>
+    <t xml:space="preserve">1.13985455036163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13475108146667</t>
   </si>
   <si>
     <t xml:space="preserve">1.16391277313232</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">1.16500639915466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18833553791046</t>
+    <t xml:space="preserve">1.18833565711975</t>
   </si>
   <si>
     <t xml:space="preserve">1.20473897457123</t>
@@ -2069,49 +2069,49 @@
     <t xml:space="preserve">1.20036470890045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18869996070862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17958700656891</t>
+    <t xml:space="preserve">1.18870007991791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17958724498749</t>
   </si>
   <si>
     <t xml:space="preserve">1.16464173793793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17922258377075</t>
+    <t xml:space="preserve">1.17922246456146</t>
   </si>
   <si>
     <t xml:space="preserve">1.18213868141174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17630648612976</t>
+    <t xml:space="preserve">1.17630636692047</t>
   </si>
   <si>
     <t xml:space="preserve">1.19599044322968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18979358673096</t>
+    <t xml:space="preserve">1.18979370594025</t>
   </si>
   <si>
     <t xml:space="preserve">1.22551667690277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21567463874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22770392894745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23207795619965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21421647071838</t>
+    <t xml:space="preserve">1.21567475795746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22770380973816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23207807540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21421658992767</t>
   </si>
   <si>
     <t xml:space="preserve">1.21166479587555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23134911060333</t>
+    <t xml:space="preserve">1.23134899139404</t>
   </si>
   <si>
     <t xml:space="preserve">1.2302553653717</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">1.23791027069092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23462975025177</t>
+    <t xml:space="preserve">1.23462986946106</t>
   </si>
   <si>
     <t xml:space="preserve">1.22806835174561</t>
@@ -2135,13 +2135,13 @@
     <t xml:space="preserve">1.21640360355377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22187125682831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22114253044128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22405862808228</t>
+    <t xml:space="preserve">1.22187149524689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22114217281342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22405850887299</t>
   </si>
   <si>
     <t xml:space="preserve">1.23061990737915</t>
@@ -2156,46 +2156,46 @@
     <t xml:space="preserve">1.22879731655121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22624576091766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27363324165344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27691400051117</t>
+    <t xml:space="preserve">1.22624564170837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27363312244415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27691411972046</t>
   </si>
   <si>
     <t xml:space="preserve">1.31154346466064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3133659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3097208738327</t>
+    <t xml:space="preserve">1.31336581707001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30972075462341</t>
   </si>
   <si>
     <t xml:space="preserve">1.30826270580292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31591749191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29331731796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31518864631653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31445968151093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30862712860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29732704162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27873659133911</t>
+    <t xml:space="preserve">1.31591761112213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29331743717194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31518852710724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31445956230164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30862724781036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29732716083527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27873647212982</t>
   </si>
   <si>
     <t xml:space="preserve">1.28857862949371</t>
@@ -2207,34 +2207,34 @@
     <t xml:space="preserve">1.27727842330933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27509129047394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26452040672302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24884581565857</t>
+    <t xml:space="preserve">1.27509140968323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26452028751373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24884593486786</t>
   </si>
   <si>
     <t xml:space="preserve">1.24665892124176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25249111652374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24520063400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24483621120453</t>
+    <t xml:space="preserve">1.25249123573303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2452005147934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24483633041382</t>
   </si>
   <si>
     <t xml:space="preserve">1.19052278995514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19635510444641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19854235649109</t>
+    <t xml:space="preserve">1.19635498523712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19854211807251</t>
   </si>
   <si>
     <t xml:space="preserve">1.19343888759613</t>
@@ -2243,73 +2243,73 @@
     <t xml:space="preserve">1.18068063259125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20218753814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18906462192535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19270980358124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20656168460846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20729064941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22515213489532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24155557155609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23353624343872</t>
+    <t xml:space="preserve">1.20218741893768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18906474113464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19270992279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20656156539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20729053020477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22515225410461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2415554523468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23353600502014</t>
   </si>
   <si>
     <t xml:space="preserve">1.21895527839661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2127583026886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20838415622711</t>
+    <t xml:space="preserve">1.21275854110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2083842754364</t>
   </si>
   <si>
     <t xml:space="preserve">1.25504279136658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25066864490509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25941693782806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25650084018707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26853013038635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29987871646881</t>
+    <t xml:space="preserve">1.2506685256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25941705703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25650095939636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26852989196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2998788356781</t>
   </si>
   <si>
     <t xml:space="preserve">1.30315935611725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29368197917938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29222393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30607557296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3520051240921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34544360637665</t>
+    <t xml:space="preserve">1.29368209838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2922238111496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30607569217682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35200500488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34544372558594</t>
   </si>
   <si>
     <t xml:space="preserve">1.33414363861084</t>
@@ -2321,25 +2321,25 @@
     <t xml:space="preserve">1.3224790096283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32940483093262</t>
+    <t xml:space="preserve">1.32940495014191</t>
   </si>
   <si>
     <t xml:space="preserve">1.34580826759338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33159196376801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33013379573822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.349818110466</t>
+    <t xml:space="preserve">1.33159208297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33013391494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34981787204742</t>
   </si>
   <si>
     <t xml:space="preserve">1.34398579597473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34143400192261</t>
+    <t xml:space="preserve">1.34143424034119</t>
   </si>
   <si>
     <t xml:space="preserve">1.34945344924927</t>
@@ -2354,34 +2354,34 @@
     <t xml:space="preserve">1.3822603225708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36038911342621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34908902645111</t>
+    <t xml:space="preserve">1.3603892326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34908890724182</t>
   </si>
   <si>
     <t xml:space="preserve">1.26524937152863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25613641738892</t>
+    <t xml:space="preserve">1.25613629817963</t>
   </si>
   <si>
     <t xml:space="preserve">1.13766729831696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15589332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1970841884613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11579620838165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996233344078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92478746175766</t>
+    <t xml:space="preserve">1.15589320659637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19708395004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11579608917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996233522891998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924787521362305</t>
   </si>
   <si>
     <t xml:space="preserve">0.905467987060547</t>
@@ -2393,34 +2393,34 @@
     <t xml:space="preserve">0.772782623767853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.750546932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775334417819977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751276075839996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754556596279144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74143385887146</t>
+    <t xml:space="preserve">0.750546872615814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775334298610687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751276016235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754556655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.741433918476105</t>
   </si>
   <si>
     <t xml:space="preserve">0.729040205478668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786269962787628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797205448150635</t>
+    <t xml:space="preserve">0.786269843578339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79720550775528</t>
   </si>
   <si>
     <t xml:space="preserve">0.793195843696594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778250515460968</t>
+    <t xml:space="preserve">0.778250455856323</t>
   </si>
   <si>
     <t xml:space="preserve">0.824544548988342</t>
@@ -2429,13 +2429,13 @@
     <t xml:space="preserve">0.826002657413483</t>
   </si>
   <si>
-    <t xml:space="preserve">0.816160678863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841677010059357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836209058761597</t>
+    <t xml:space="preserve">0.816160619258881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841676950454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836209118366241</t>
   </si>
   <si>
     <t xml:space="preserve">0.869015991687775</t>
@@ -2447,52 +2447,52 @@
     <t xml:space="preserve">0.855164229869843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.876670897006989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889429211616516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885783970355988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.897448599338531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910935759544373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91166478395462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.883961200714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888335585594177</t>
+    <t xml:space="preserve">0.876670837402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889429152011871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885783910751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.897448420524597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910935878753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911664843559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883961260318756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888335466384888</t>
   </si>
   <si>
     <t xml:space="preserve">0.879587054252625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.890158116817474</t>
+    <t xml:space="preserve">0.89015805721283</t>
   </si>
   <si>
     <t xml:space="preserve">0.906925976276398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.901458323001862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899635553359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905832350254059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872296631336212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879951477050781</t>
+    <t xml:space="preserve">0.901458203792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89963561296463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905832469463348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872296571731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879951596260071</t>
   </si>
   <si>
     <t xml:space="preserve">0.878128886222839</t>
@@ -2501,16 +2501,16 @@
     <t xml:space="preserve">0.882138729095459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877764463424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914581060409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93426501750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911300361156464</t>
+    <t xml:space="preserve">0.877764344215393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914580941200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934265077114105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911300182342529</t>
   </si>
   <si>
     <t xml:space="preserve">0.944332540035248</t>
@@ -2528,22 +2528,22 @@
     <t xml:space="preserve">0.912854731082916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946275472640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971146881580353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950550258159637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971535503864288</t>
+    <t xml:space="preserve">0.946275532245636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971146941184998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950550377368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971535325050354</t>
   </si>
   <si>
     <t xml:space="preserve">0.969592273235321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.981639385223389</t>
+    <t xml:space="preserve">0.981639444828033</t>
   </si>
   <si>
     <t xml:space="preserve">1.00573348999023</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">1.03060483932495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05236721038818</t>
+    <t xml:space="preserve">1.05236732959747</t>
   </si>
   <si>
     <t xml:space="preserve">1.02710723876953</t>
@@ -2567,19 +2567,19 @@
     <t xml:space="preserve">1.01195132732391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960265755653381</t>
+    <t xml:space="preserve">0.960265636444092</t>
   </si>
   <si>
     <t xml:space="preserve">0.956379532814026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.978141784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01156282424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01778042316437</t>
+    <t xml:space="preserve">0.978141844272614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01156270503998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01778054237366</t>
   </si>
   <si>
     <t xml:space="preserve">1.00961971282959</t>
@@ -2588,94 +2588,94 @@
     <t xml:space="preserve">1.0193350315094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01467156410217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972312748432159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963763117790222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977364778518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979696273803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984359800815582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999904334545135</t>
+    <t xml:space="preserve">1.01467168331146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972312688827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963763236999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977364718914032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979696393013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984359741210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999904155731201</t>
   </si>
   <si>
     <t xml:space="preserve">0.996795415878296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993686437606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983193933963776</t>
+    <t xml:space="preserve">0.993686497211456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983193874359131</t>
   </si>
   <si>
     <t xml:space="preserve">0.98280531167984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958322644233704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961431503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960654377937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973867177963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973089873790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985137045383453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987857401371002</t>
+    <t xml:space="preserve">0.958322584629059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961431443691254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960654258728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973867237567902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973089993000031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985136926174164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987857341766357</t>
   </si>
   <si>
     <t xml:space="preserve">0.985525548458099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949773073196411</t>
+    <t xml:space="preserve">0.949773013591766</t>
   </si>
   <si>
     <t xml:space="preserve">0.954436480998993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970758259296417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928788006305695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943166673183441</t>
+    <t xml:space="preserve">0.970758140087128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92878794670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943166613578796</t>
   </si>
   <si>
     <t xml:space="preserve">0.95599091053009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959877014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953659176826477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96531754732132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982028007507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01739192008972</t>
+    <t xml:space="preserve">0.959877133369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953659236431122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965317666530609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982028067111969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01739203929901</t>
   </si>
   <si>
     <t xml:space="preserve">1.00612223148346</t>
@@ -2687,34 +2687,34 @@
     <t xml:space="preserve">0.979307770729065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989411652088165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987080037593842</t>
+    <t xml:space="preserve">0.989411771297455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987079977989197</t>
   </si>
   <si>
     <t xml:space="preserve">0.964929103851318</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962597250938416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958711266517639</t>
+    <t xml:space="preserve">0.96259731054306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958711206912994</t>
   </si>
   <si>
     <t xml:space="preserve">0.96609491109848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.951327502727509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954047739505768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975033044815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968038022518158</t>
+    <t xml:space="preserve">0.951327562332153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954047858715057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975032985210419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968037962913513</t>
   </si>
   <si>
     <t xml:space="preserve">0.937726020812988</t>
@@ -2723,61 +2723,61 @@
     <t xml:space="preserve">0.946664154529572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938503205776215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942000687122345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933451235294342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971924126148224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948995888233185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953270673751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9458869099617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929565072059631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931119620800018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900807857513428</t>
+    <t xml:space="preserve">0.938503265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942000806331635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933451294898987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971924066543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94899582862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953270614147186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945886790752411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929565131664276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931119561195374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900807797908783</t>
   </si>
   <si>
     <t xml:space="preserve">0.903528034687042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904693901538849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898864686489105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878656625747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886428892612457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901584982872009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886040389537811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840961158275604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830079853534698</t>
+    <t xml:space="preserve">0.904693841934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898864567279816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878656685352325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886428833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901584923267365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886040329933167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840961217880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830079913139343</t>
   </si>
   <si>
     <t xml:space="preserve">0.84834486246109</t>
@@ -2786,79 +2786,79 @@
     <t xml:space="preserve">0.860780417919159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872050225734711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898476004600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892646729946136</t>
+    <t xml:space="preserve">0.872050166130066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89847606420517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892646849155426</t>
   </si>
   <si>
     <t xml:space="preserve">0.881376981735229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.942778050899506</t>
+    <t xml:space="preserve">0.942778170108795</t>
   </si>
   <si>
     <t xml:space="preserve">0.93928050994873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955213606357574</t>
+    <t xml:space="preserve">0.955213665962219</t>
   </si>
   <si>
     <t xml:space="preserve">0.95249330997467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947441339492798</t>
+    <t xml:space="preserve">0.947441458702087</t>
   </si>
   <si>
     <t xml:space="preserve">0.952104806900024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95948851108551</t>
+    <t xml:space="preserve">0.959488391876221</t>
   </si>
   <si>
     <t xml:space="preserve">0.97619891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01700329780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02205550670624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993297815322876</t>
+    <t xml:space="preserve">1.01700341701508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02205526828766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993297874927521</t>
   </si>
   <si>
     <t xml:space="preserve">0.982416689395905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975421667098999</t>
+    <t xml:space="preserve">0.975421547889709</t>
   </si>
   <si>
     <t xml:space="preserve">0.976587533950806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997183918952942</t>
+    <t xml:space="preserve">0.997183859348297</t>
   </si>
   <si>
     <t xml:space="preserve">0.990966200828552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988245904445648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984748303890228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995629668235779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954825043678284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00651073455811</t>
+    <t xml:space="preserve">0.988245844841003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984748244285583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995629549026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954825222492218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00651061534882</t>
   </si>
   <si>
     <t xml:space="preserve">1.01583755016327</t>
@@ -2870,31 +2870,31 @@
     <t xml:space="preserve">1.03449094295502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02399849891663</t>
+    <t xml:space="preserve">1.02399837970734</t>
   </si>
   <si>
     <t xml:space="preserve">1.04148602485657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03954303264618</t>
+    <t xml:space="preserve">1.03954291343689</t>
   </si>
   <si>
     <t xml:space="preserve">1.03487956523895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01428294181824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0375999212265</t>
+    <t xml:space="preserve">1.01428306102753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03759980201721</t>
   </si>
   <si>
     <t xml:space="preserve">1.0321592092514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02050089836121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03099346160889</t>
+    <t xml:space="preserve">1.02050077915192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03099358081818</t>
   </si>
   <si>
     <t xml:space="preserve">1.06596863269806</t>
@@ -2903,31 +2903,31 @@
     <t xml:space="preserve">1.0729638338089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04653799533844</t>
+    <t xml:space="preserve">1.04653811454773</t>
   </si>
   <si>
     <t xml:space="preserve">1.0589736700058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05353307723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06169402599335</t>
+    <t xml:space="preserve">1.0535329580307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06169390678406</t>
   </si>
   <si>
     <t xml:space="preserve">1.0449835062027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10871624946594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13630783557892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15418410301208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12853562831879</t>
+    <t xml:space="preserve">1.10871636867523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13630795478821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15418422222137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12853574752808</t>
   </si>
   <si>
     <t xml:space="preserve">1.1382509469986</t>
@@ -2936,25 +2936,25 @@
     <t xml:space="preserve">1.14252579212189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17516934871674</t>
+    <t xml:space="preserve">1.17516922950745</t>
   </si>
   <si>
     <t xml:space="preserve">1.16195642948151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13863968849182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12154054641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13475358486176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12698125839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11415696144104</t>
+    <t xml:space="preserve">1.13863945007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12154042720795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13475334644318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12698113918304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11415684223175</t>
   </si>
   <si>
     <t xml:space="preserve">1.10366427898407</t>
@@ -2963,22 +2963,22 @@
     <t xml:space="preserve">1.11221373081207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09317171573639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0838451385498</t>
+    <t xml:space="preserve">1.0931715965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08384501934052</t>
   </si>
   <si>
     <t xml:space="preserve">1.11493408679962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10716199874878</t>
+    <t xml:space="preserve">1.10716187953949</t>
   </si>
   <si>
     <t xml:space="preserve">1.07918155193329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08656525611877</t>
+    <t xml:space="preserve">1.08656513690948</t>
   </si>
   <si>
     <t xml:space="preserve">1.0772385597229</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">1.10832762718201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1308673620224</t>
+    <t xml:space="preserve">1.13086748123169</t>
   </si>
   <si>
     <t xml:space="preserve">1.15262961387634</t>
@@ -3005,22 +3005,22 @@
     <t xml:space="preserve">1.14563465118408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15301823616028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14641177654266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17089462280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18954813480377</t>
+    <t xml:space="preserve">1.15301835536957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14641189575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17089450359344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18954801559448</t>
   </si>
   <si>
     <t xml:space="preserve">1.2047039270401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20664715766907</t>
+    <t xml:space="preserve">1.20664703845978</t>
   </si>
   <si>
     <t xml:space="preserve">1.21558523178101</t>
@@ -3032,40 +3032,40 @@
     <t xml:space="preserve">1.20625853538513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20392668247223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20859014987946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2241348028183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20975601673126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19809758663177</t>
+    <t xml:space="preserve">1.20392680168152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20859003067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22413468360901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20975589752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19809746742249</t>
   </si>
   <si>
     <t xml:space="preserve">1.21286487579346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21597361564636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21325349807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20431530475616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21247625350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22685515880585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21403074264526</t>
+    <t xml:space="preserve">1.21597385406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2132533788681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20431542396545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21247613430023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22685503959656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21403062343597</t>
   </si>
   <si>
     <t xml:space="preserve">1.2357931137085</t>
@@ -3077,43 +3077,43 @@
     <t xml:space="preserve">1.23851346969604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24278831481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26105308532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26455056667328</t>
+    <t xml:space="preserve">1.24278819561005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26105296611786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26455044746399</t>
   </si>
   <si>
     <t xml:space="preserve">1.27582037448883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26066446304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26493918895721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27892923355103</t>
+    <t xml:space="preserve">1.26066434383392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2649393081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27892935276031</t>
   </si>
   <si>
     <t xml:space="preserve">1.3045779466629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31779074668884</t>
+    <t xml:space="preserve">1.31779086589813</t>
   </si>
   <si>
     <t xml:space="preserve">1.29291939735413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29874861240387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3174022436142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33061492443085</t>
+    <t xml:space="preserve">1.29874873161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31740212440491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33061504364014</t>
   </si>
   <si>
     <t xml:space="preserve">1.34693682193756</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">1.34382784366608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34849119186401</t>
+    <t xml:space="preserve">1.3484913110733</t>
   </si>
   <si>
     <t xml:space="preserve">1.35121142864227</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">1.37502765655518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38194751739502</t>
+    <t xml:space="preserve">1.38194763660431</t>
   </si>
   <si>
     <t xml:space="preserve">1.37787699699402</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">1.391716837883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38438999652863</t>
+    <t xml:space="preserve">1.38438987731934</t>
   </si>
   <si>
     <t xml:space="preserve">1.39456617832184</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">1.38886749744415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41044127941132</t>
+    <t xml:space="preserve">1.41044116020203</t>
   </si>
   <si>
     <t xml:space="preserve">1.42306005954742</t>
@@ -3173,22 +3173,22 @@
     <t xml:space="preserve">1.43852806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43771409988403</t>
+    <t xml:space="preserve">1.43771398067474</t>
   </si>
   <si>
     <t xml:space="preserve">1.4491114616394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44951856136322</t>
+    <t xml:space="preserve">1.44951868057251</t>
   </si>
   <si>
     <t xml:space="preserve">1.45725250244141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45765972137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4552173614502</t>
+    <t xml:space="preserve">1.45765960216522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45521724224091</t>
   </si>
   <si>
     <t xml:space="preserve">1.43120110034943</t>
@@ -3197,19 +3197,19 @@
     <t xml:space="preserve">1.4430056810379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44422686100006</t>
+    <t xml:space="preserve">1.44422674179077</t>
   </si>
   <si>
     <t xml:space="preserve">1.42713057994843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41858232021332</t>
+    <t xml:space="preserve">1.41858243942261</t>
   </si>
   <si>
     <t xml:space="preserve">1.40352141857147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41288375854492</t>
+    <t xml:space="preserve">1.41288363933563</t>
   </si>
   <si>
     <t xml:space="preserve">1.41695427894592</t>
@@ -3218,22 +3218,22 @@
     <t xml:space="preserve">1.41898953914642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41329085826874</t>
+    <t xml:space="preserve">1.41329061985016</t>
   </si>
   <si>
     <t xml:space="preserve">1.43527162075043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37950527667999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38072633743286</t>
+    <t xml:space="preserve">1.3795051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38072645664215</t>
   </si>
   <si>
     <t xml:space="preserve">1.39945089817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41736137866974</t>
+    <t xml:space="preserve">1.41736125946045</t>
   </si>
   <si>
     <t xml:space="preserve">1.40392851829529</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">1.3591525554657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38316869735718</t>
+    <t xml:space="preserve">1.38316881656647</t>
   </si>
   <si>
     <t xml:space="preserve">1.395787358284</t>
@@ -3263,31 +3263,31 @@
     <t xml:space="preserve">1.47801232337952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47394168376923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47068536281586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47923350334167</t>
+    <t xml:space="preserve">1.47394180297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47068524360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47923338413239</t>
   </si>
   <si>
     <t xml:space="preserve">1.46824300289154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47964060306549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49348032474518</t>
+    <t xml:space="preserve">1.47964036464691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49348020553589</t>
   </si>
   <si>
     <t xml:space="preserve">1.50691306591034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52360224723816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53866314888</t>
+    <t xml:space="preserve">1.52360236644745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53866338729858</t>
   </si>
   <si>
     <t xml:space="preserve">1.54069852828979</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">1.58669567108154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56593585014343</t>
+    <t xml:space="preserve">1.56593596935272</t>
   </si>
   <si>
     <t xml:space="preserve">1.5838463306427</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">1.52726578712463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52889406681061</t>
+    <t xml:space="preserve">1.52889394760132</t>
   </si>
   <si>
     <t xml:space="preserve">1.52197408676147</t>
@@ -3329,19 +3329,19 @@
     <t xml:space="preserve">1.51912474632263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50650608539581</t>
+    <t xml:space="preserve">1.50650596618652</t>
   </si>
   <si>
     <t xml:space="preserve">1.49755084514618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52238118648529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49307322502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51464700698853</t>
+    <t xml:space="preserve">1.522381067276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49307334423065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51464712619781</t>
   </si>
   <si>
     <t xml:space="preserve">1.5162752866745</t>
@@ -3353,64 +3353,64 @@
     <t xml:space="preserve">1.48940968513489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49063098430634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42794466018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45155370235443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46173024177551</t>
+    <t xml:space="preserve">1.49063086509705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42794454097748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45155382156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46173012256622</t>
   </si>
   <si>
     <t xml:space="preserve">1.46213722229004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48371112346649</t>
+    <t xml:space="preserve">1.4837110042572</t>
   </si>
   <si>
     <t xml:space="preserve">1.47882628440857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48411810398102</t>
+    <t xml:space="preserve">1.48411822319031</t>
   </si>
   <si>
     <t xml:space="preserve">1.45643842220306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45562434196472</t>
+    <t xml:space="preserve">1.45562422275543</t>
   </si>
   <si>
     <t xml:space="preserve">1.43812108039856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44544804096222</t>
+    <t xml:space="preserve">1.44544792175293</t>
   </si>
   <si>
     <t xml:space="preserve">1.44015634059906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45684552192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48737454414368</t>
+    <t xml:space="preserve">1.45684540271759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48737442493439</t>
   </si>
   <si>
     <t xml:space="preserve">1.48533916473389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5040637254715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46417236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4450409412384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47475588321686</t>
+    <t xml:space="preserve">1.50406384468079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46417248249054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44504082202911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47475576400757</t>
   </si>
   <si>
     <t xml:space="preserve">1.49673676490784</t>
@@ -3419,25 +3419,25 @@
     <t xml:space="preserve">1.50894844532013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.502028465271</t>
+    <t xml:space="preserve">1.50202858448029</t>
   </si>
   <si>
     <t xml:space="preserve">1.48696756362915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50365662574768</t>
+    <t xml:space="preserve">1.50365674495697</t>
   </si>
   <si>
     <t xml:space="preserve">1.52970802783966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53662800788879</t>
+    <t xml:space="preserve">1.53662812709808</t>
   </si>
   <si>
     <t xml:space="preserve">1.57407701015472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55698072910309</t>
+    <t xml:space="preserve">1.5569806098938</t>
   </si>
   <si>
     <t xml:space="preserve">1.55779480934143</t>
@@ -3446,19 +3446,19 @@
     <t xml:space="preserve">1.50732016563416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48004758358002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49022388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49225914478302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.510169506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47760534286499</t>
+    <t xml:space="preserve">1.48004746437073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49022376537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49225902557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51016938686371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4776052236557</t>
   </si>
   <si>
     <t xml:space="preserve">1.50040030479431</t>
@@ -3467,25 +3467,25 @@
     <t xml:space="preserve">1.50121426582336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51301896572113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51953172683716</t>
+    <t xml:space="preserve">1.51301884651184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51953184604645</t>
   </si>
   <si>
     <t xml:space="preserve">1.51546132564545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39212393760681</t>
+    <t xml:space="preserve">1.3921240568161</t>
   </si>
   <si>
     <t xml:space="preserve">1.40596377849579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39538037776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40637075901031</t>
+    <t xml:space="preserve">1.39538025856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40637063980103</t>
   </si>
   <si>
     <t xml:space="preserve">1.45196080207825</t>
@@ -3500,25 +3500,25 @@
     <t xml:space="preserve">1.45440316200256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45399606227875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42835175991058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39130985736847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37258517742157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32699525356293</t>
+    <t xml:space="preserve">1.45399618148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42835164070129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39130973815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37258529663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32699537277222</t>
   </si>
   <si>
     <t xml:space="preserve">1.34531271457672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34775495529175</t>
+    <t xml:space="preserve">1.34775519371033</t>
   </si>
   <si>
     <t xml:space="preserve">1.36810779571533</t>
@@ -3530,19 +3530,19 @@
     <t xml:space="preserve">1.39741563796997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40026497840881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40677797794342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35548913478851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35955965518951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35833835601807</t>
+    <t xml:space="preserve">1.4002650976181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40677785873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35548901557922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35955953598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35833847522736</t>
   </si>
   <si>
     <t xml:space="preserve">1.37462055683136</t>
@@ -3551,7 +3551,7 @@
     <t xml:space="preserve">1.36770057678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35589599609375</t>
+    <t xml:space="preserve">1.35589611530304</t>
   </si>
   <si>
     <t xml:space="preserve">1.35263967514038</t>
@@ -3563,28 +3563,28 @@
     <t xml:space="preserve">1.32414591312408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35304665565491</t>
+    <t xml:space="preserve">1.3530467748642</t>
   </si>
   <si>
     <t xml:space="preserve">1.34164929389954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30664265155792</t>
+    <t xml:space="preserve">1.30664253234863</t>
   </si>
   <si>
     <t xml:space="preserve">1.3326940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3652583360672</t>
+    <t xml:space="preserve">1.36525857448578</t>
   </si>
   <si>
     <t xml:space="preserve">1.41532599925995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37380635738373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3672935962677</t>
+    <t xml:space="preserve">1.37380647659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36729371547699</t>
   </si>
   <si>
     <t xml:space="preserve">1.37909817695618</t>
@@ -3593,10 +3593,10 @@
     <t xml:space="preserve">1.37624883651733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36973583698273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33513629436493</t>
+    <t xml:space="preserve">1.36973595619202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33513641357422</t>
   </si>
   <si>
     <t xml:space="preserve">1.30949199199677</t>
@@ -3611,52 +3611,52 @@
     <t xml:space="preserve">1.30542147159576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29036045074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26430916786194</t>
+    <t xml:space="preserve">1.29036056995392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26430904865265</t>
   </si>
   <si>
     <t xml:space="preserve">1.28913938999176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28425467014313</t>
+    <t xml:space="preserve">1.28425478935242</t>
   </si>
   <si>
     <t xml:space="preserve">1.28181231021881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27652060985565</t>
+    <t xml:space="preserve">1.27652072906494</t>
   </si>
   <si>
     <t xml:space="preserve">1.25413274765015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22889542579651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25046920776367</t>
+    <t xml:space="preserve">1.22889530658722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25046932697296</t>
   </si>
   <si>
     <t xml:space="preserve">1.22482478618622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.281405210495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3001297712326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25494682788849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22848832607269</t>
+    <t xml:space="preserve">1.28140544891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30012989044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2549467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2284882068634</t>
   </si>
   <si>
     <t xml:space="preserve">1.19918048381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18249118328094</t>
+    <t xml:space="preserve">1.18249130249023</t>
   </si>
   <si>
     <t xml:space="preserve">1.20243680477142</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">1.25616788864136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24639880657196</t>
+    <t xml:space="preserve">1.24639868736267</t>
   </si>
   <si>
     <t xml:space="preserve">1.2447704076767</t>
@@ -3680,16 +3680,16 @@
     <t xml:space="preserve">1.22116136550903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21464848518372</t>
+    <t xml:space="preserve">1.21464860439301</t>
   </si>
   <si>
     <t xml:space="preserve">1.23785054683685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25087630748749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22563898563385</t>
+    <t xml:space="preserve">1.2508761882782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22563886642456</t>
   </si>
   <si>
     <t xml:space="preserve">1.22808122634888</t>
@@ -3701,13 +3701,13 @@
     <t xml:space="preserve">1.25698208808899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27489244937897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25779616832733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26553010940552</t>
+    <t xml:space="preserve">1.27489233016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25779604911804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2655303478241</t>
   </si>
   <si>
     <t xml:space="preserve">1.25942444801331</t>
@@ -3716,10 +3716,10 @@
     <t xml:space="preserve">1.28751111030579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29768753051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29809439182281</t>
+    <t xml:space="preserve">1.29768741130829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2980945110321</t>
   </si>
   <si>
     <t xml:space="preserve">1.33554339408875</t>
@@ -3728,10 +3728,10 @@
     <t xml:space="preserve">1.36281597614288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35223257541656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3571172952652</t>
+    <t xml:space="preserve">1.35223269462585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35711741447449</t>
   </si>
   <si>
     <t xml:space="preserve">1.34856915473938</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">1.34409153461456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36485111713409</t>
+    <t xml:space="preserve">1.36485135555267</t>
   </si>
   <si>
     <t xml:space="preserve">1.33961391448975</t>
@@ -3749,43 +3749,43 @@
     <t xml:space="preserve">1.32129657268524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3245530128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33432233333588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33106577396393</t>
+    <t xml:space="preserve">1.32455289363861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33432245254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33106589317322</t>
   </si>
   <si>
     <t xml:space="preserve">1.34002101421356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3286235332489</t>
+    <t xml:space="preserve">1.32862341403961</t>
   </si>
   <si>
     <t xml:space="preserve">1.31193435192108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31641185283661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35019731521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34653401374817</t>
+    <t xml:space="preserve">1.3164119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35019743442535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34653389453888</t>
   </si>
   <si>
     <t xml:space="preserve">1.34327745437622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3856109380722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33147275447845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36037361621857</t>
+    <t xml:space="preserve">1.38561105728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33147299289703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36037373542786</t>
   </si>
   <si>
     <t xml:space="preserve">1.34205627441406</t>
@@ -3806,13 +3806,13 @@
     <t xml:space="preserve">1.3631272315979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35796213150024</t>
+    <t xml:space="preserve">1.35796225070953</t>
   </si>
   <si>
     <t xml:space="preserve">1.34504961967468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32998514175415</t>
+    <t xml:space="preserve">1.32998502254486</t>
   </si>
   <si>
     <t xml:space="preserve">1.31578135490417</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">1.33041560649872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31018602848053</t>
+    <t xml:space="preserve">1.31018590927124</t>
   </si>
   <si>
     <t xml:space="preserve">1.3123379945755</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">1.14921045303345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11047303676605</t>
+    <t xml:space="preserve">1.11047291755676</t>
   </si>
   <si>
     <t xml:space="preserve">1.15050172805786</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">1.07517886161804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04332804679871</t>
+    <t xml:space="preserve">1.043328166008</t>
   </si>
   <si>
     <t xml:space="preserve">1.06743133068085</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">1.0510755777359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07130515575409</t>
+    <t xml:space="preserve">1.07130527496338</t>
   </si>
   <si>
     <t xml:space="preserve">1.06915318965912</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">1.02697229385376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00200831890106</t>
+    <t xml:space="preserve">1.00200819969177</t>
   </si>
   <si>
     <t xml:space="preserve">1.02352893352509</t>
@@ -3935,10 +3935,10 @@
     <t xml:space="preserve">1.04978430271149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07474851608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09024345874786</t>
+    <t xml:space="preserve">1.07474839687347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09024357795715</t>
   </si>
   <si>
     <t xml:space="preserve">1.06829226016998</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">1.05839276313782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0170726776123</t>
+    <t xml:space="preserve">1.01707279682159</t>
   </si>
   <si>
     <t xml:space="preserve">0.996843218803406</t>
@@ -3989,16 +3989,16 @@
     <t xml:space="preserve">0.963701248168945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946914970874786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968435883522034</t>
+    <t xml:space="preserve">0.946915030479431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968435764312744</t>
   </si>
   <si>
     <t xml:space="preserve">0.945623755455017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9327113032341</t>
+    <t xml:space="preserve">0.932711243629456</t>
   </si>
   <si>
     <t xml:space="preserve">0.939167439937592</t>
@@ -4013,22 +4013,22 @@
     <t xml:space="preserve">0.975322425365448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952510476112366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92625504732132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930128753185272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913342535495758</t>
+    <t xml:space="preserve">0.952510356903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92625492811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930128812789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913342595100403</t>
   </si>
   <si>
     <t xml:space="preserve">0.921950876712799</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923242151737213</t>
+    <t xml:space="preserve">0.923242092132568</t>
   </si>
   <si>
     <t xml:space="preserve">0.912051260471344</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">0.882783055305481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888808906078339</t>
+    <t xml:space="preserve">0.888808846473694</t>
   </si>
   <si>
     <t xml:space="preserve">0.852567851543427</t>
@@ -4061,10 +4061,10 @@
     <t xml:space="preserve">0.868579208850861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.853256464004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835351169109344</t>
+    <t xml:space="preserve">0.853256404399872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8353511095047</t>
   </si>
   <si>
     <t xml:space="preserve">0.846542000770569</t>
@@ -4076,19 +4076,19 @@
     <t xml:space="preserve">0.820200502872467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.825882017612457</t>
+    <t xml:space="preserve">0.825881958007812</t>
   </si>
   <si>
     <t xml:space="preserve">0.863844633102417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.883643865585327</t>
+    <t xml:space="preserve">0.883643805980682</t>
   </si>
   <si>
     <t xml:space="preserve">0.879770040512085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871161699295044</t>
+    <t xml:space="preserve">0.871161758899689</t>
   </si>
   <si>
     <t xml:space="preserve">0.896986782550812</t>
@@ -4097,34 +4097,34 @@
     <t xml:space="preserve">0.949497520923615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948206305503845</t>
+    <t xml:space="preserve">0.948206186294556</t>
   </si>
   <si>
     <t xml:space="preserve">0.982209146022797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971018254756927</t>
+    <t xml:space="preserve">0.971018373966217</t>
   </si>
   <si>
     <t xml:space="preserve">0.965853273868561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966714084148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966283738613129</t>
+    <t xml:space="preserve">0.966714203357697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966283619403839</t>
   </si>
   <si>
     <t xml:space="preserve">0.955092906951904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972309589385986</t>
+    <t xml:space="preserve">0.972309470176697</t>
   </si>
   <si>
     <t xml:space="preserve">0.993830323219299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0045907497406</t>
+    <t xml:space="preserve">1.00459086894989</t>
   </si>
   <si>
     <t xml:space="preserve">1.01061654090881</t>
@@ -4151,7 +4151,7 @@
     <t xml:space="preserve">1.11822056770325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09669971466064</t>
+    <t xml:space="preserve">1.09669959545135</t>
   </si>
   <si>
     <t xml:space="preserve">1.11391639709473</t>
@@ -4160,7 +4160,7 @@
     <t xml:space="preserve">1.13974130153656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11865091323853</t>
+    <t xml:space="preserve">1.11865103244781</t>
   </si>
   <si>
     <t xml:space="preserve">1.09928214550018</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">1.13543713092804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12381589412689</t>
+    <t xml:space="preserve">1.12381601333618</t>
   </si>
   <si>
     <t xml:space="preserve">1.11951184272766</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">1.07173550128937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09971261024475</t>
+    <t xml:space="preserve">1.09971272945404</t>
   </si>
   <si>
     <t xml:space="preserve">1.12467670440674</t>
@@ -4229,19 +4229,19 @@
     <t xml:space="preserve">1.14705836772919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18837821483612</t>
+    <t xml:space="preserve">1.18837833404541</t>
   </si>
   <si>
     <t xml:space="preserve">1.19354331493378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19827783107758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20043003559113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20516443252563</t>
+    <t xml:space="preserve">1.19827771186829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20042991638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20516455173492</t>
   </si>
   <si>
     <t xml:space="preserve">1.21032953262329</t>
@@ -4256,7 +4256,7 @@
     <t xml:space="preserve">1.18192207813263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19096088409424</t>
+    <t xml:space="preserve">1.19096076488495</t>
   </si>
   <si>
     <t xml:space="preserve">1.20387327671051</t>
@@ -4280,10 +4280,10 @@
     <t xml:space="preserve">1.18794786930084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20344293117523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21506416797638</t>
+    <t xml:space="preserve">1.20344281196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21506404876709</t>
   </si>
   <si>
     <t xml:space="preserve">1.20903825759888</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">1.17632663249969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17675697803497</t>
+    <t xml:space="preserve">1.17675709724426</t>
   </si>
   <si>
     <t xml:space="preserve">1.19139122962952</t>
@@ -4319,16 +4319,16 @@
     <t xml:space="preserve">1.20129072666168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16943991184235</t>
+    <t xml:space="preserve">1.16944003105164</t>
   </si>
   <si>
     <t xml:space="preserve">1.18364369869232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19784736633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18149161338806</t>
+    <t xml:space="preserve">1.1978474855423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18149149417877</t>
   </si>
   <si>
     <t xml:space="preserve">1.18493497371674</t>
@@ -4340,7 +4340,7 @@
     <t xml:space="preserve">1.16814875602722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15738832950592</t>
+    <t xml:space="preserve">1.15738821029663</t>
   </si>
   <si>
     <t xml:space="preserve">1.18278288841248</t>
@@ -4349,7 +4349,7 @@
     <t xml:space="preserve">1.18321335315704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25078856945038</t>
+    <t xml:space="preserve">1.25078845024109</t>
   </si>
   <si>
     <t xml:space="preserve">1.26240980625153</t>
@@ -4364,10 +4364,10 @@
     <t xml:space="preserve">1.23959791660309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23787605762482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21678566932678</t>
+    <t xml:space="preserve">1.23787617683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21678578853607</t>
   </si>
   <si>
     <t xml:space="preserve">1.22496366500854</t>
@@ -4382,19 +4382,19 @@
     <t xml:space="preserve">1.25853610038757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26714432239532</t>
+    <t xml:space="preserve">1.26714444160461</t>
   </si>
   <si>
     <t xml:space="preserve">1.29426062107086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32869374752045</t>
+    <t xml:space="preserve">1.32869386672974</t>
   </si>
   <si>
     <t xml:space="preserve">1.33256757259369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33730232715607</t>
+    <t xml:space="preserve">1.33730220794678</t>
   </si>
   <si>
     <t xml:space="preserve">1.31664216518402</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">1.32137680053711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31922471523285</t>
+    <t xml:space="preserve">1.31922483444214</t>
   </si>
   <si>
     <t xml:space="preserve">1.35150599479675</t>
@@ -4412,7 +4412,7 @@
     <t xml:space="preserve">1.33988463878632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35279703140259</t>
+    <t xml:space="preserve">1.35279715061188</t>
   </si>
   <si>
     <t xml:space="preserve">1.35968375205994</t>
@@ -4424,13 +4424,13 @@
     <t xml:space="preserve">1.36614012718201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37733089923859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34332799911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3678617477417</t>
+    <t xml:space="preserve">1.3773307800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34332811832428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36786162853241</t>
   </si>
   <si>
     <t xml:space="preserve">1.36829209327698</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">1.3880912065506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40057337284088</t>
+    <t xml:space="preserve">1.40057325363159</t>
   </si>
   <si>
     <t xml:space="preserve">1.39885175228119</t>
@@ -4463,10 +4463,10 @@
     <t xml:space="preserve">1.43758904933929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37905251979828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41047286987305</t>
+    <t xml:space="preserve">1.37905263900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41047298908234</t>
   </si>
   <si>
     <t xml:space="preserve">1.42495942115784</t>
@@ -5978,7 +5978,7 @@
     <t xml:space="preserve">2.71199989318848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72399997711182</t>
+    <t xml:space="preserve">2.66499996185303</t>
   </si>
 </sst>
 </file>
@@ -71421,22 +71421,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6932060185</v>
+        <v>45968.6941898148</v>
       </c>
       <c r="B2505" t="n">
-        <v>8906889</v>
+        <v>9228938</v>
       </c>
       <c r="C2505" t="n">
-        <v>2.74399995803833</v>
+        <v>2.72900009155273</v>
       </c>
       <c r="D2505" t="n">
-        <v>2.70099997520447</v>
+        <v>2.65599989891052</v>
       </c>
       <c r="E2505" t="n">
-        <v>2.72900009155273</v>
+        <v>2.72199988365173</v>
       </c>
       <c r="F2505" t="n">
-        <v>2.72399997711182</v>
+        <v>2.66499996185303</v>
       </c>
       <c r="G2505" t="s">
         <v>1988</v>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="1995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="1996">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765547633171082</t>
+    <t xml:space="preserve">0.765547692775726</t>
   </si>
   <si>
     <t xml:space="preserve">A2A.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774303913116455</t>
+    <t xml:space="preserve">0.774304032325745</t>
   </si>
   <si>
     <t xml:space="preserve">0.76930046081543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.777431190013885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772427618503571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775554835796356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736151516437531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728020846843719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.708631992340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701126575469971</t>
+    <t xml:space="preserve">0.77743124961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77242773771286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775554776191711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736151695251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728020906448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.708631932735443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701126635074615</t>
   </si>
   <si>
     <t xml:space="preserve">0.678610563278198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.686115920543671</t>
+    <t xml:space="preserve">0.686115860939026</t>
   </si>
   <si>
     <t xml:space="preserve">0.662974238395691</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">0.673606932163239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.661723375320435</t>
+    <t xml:space="preserve">0.661723434925079</t>
   </si>
   <si>
     <t xml:space="preserve">0.68986850976944</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">0.688617646694183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689243078231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.676108717918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.671105146408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.66672694683075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643585562705994</t>
+    <t xml:space="preserve">0.689243018627167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.676108658313751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.671105086803436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.666727006435394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643585443496704</t>
   </si>
   <si>
     <t xml:space="preserve">0.612312972545624</t>
@@ -119,49 +119,49 @@
     <t xml:space="preserve">0.597927749156952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.605745911598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610749483108521</t>
+    <t xml:space="preserve">0.605745851993561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610749423503876</t>
   </si>
   <si>
     <t xml:space="preserve">0.614189386367798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627323806285858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617942035198212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624821960926056</t>
+    <t xml:space="preserve">0.627323865890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617942094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624822020530701</t>
   </si>
   <si>
     <t xml:space="preserve">0.646712720394135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636080026626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.656719744205475</t>
+    <t xml:space="preserve">0.636080086231232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65671980381012</t>
   </si>
   <si>
     <t xml:space="preserve">0.645461797714233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641083657741547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647963583469391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.657345235347748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661098122596741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.67298150062561</t>
+    <t xml:space="preserve">0.641083598136902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.647963523864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.657345354557037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661098003387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.672981560230255</t>
   </si>
   <si>
     <t xml:space="preserve">0.666101574897766</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">0.658596158027649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.651716291904449</t>
+    <t xml:space="preserve">0.651716232299805</t>
   </si>
   <si>
     <t xml:space="preserve">0.65484344959259</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">0.669228792190552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.713010013103485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69299578666687</t>
+    <t xml:space="preserve">0.713010132312775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692995667457581</t>
   </si>
   <si>
     <t xml:space="preserve">0.691119492053986</t>
@@ -194,16 +194,16 @@
     <t xml:space="preserve">0.694246649742126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.697999358177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696123063564301</t>
+    <t xml:space="preserve">0.69799941778183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696123003959656</t>
   </si>
   <si>
     <t xml:space="preserve">0.70300281047821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.692370295524597</t>
+    <t xml:space="preserve">0.692370235919952</t>
   </si>
   <si>
     <t xml:space="preserve">0.699250221252441</t>
@@ -212,25 +212,25 @@
     <t xml:space="preserve">0.714260935783386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714886486530304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.702377498149872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705504655838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735526144504547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.740529775619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74428254365921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748660564422607</t>
+    <t xml:space="preserve">0.714886426925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.702377557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705504596233368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735526204109192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.740529835224152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.744282424449921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748660624027252</t>
   </si>
   <si>
     <t xml:space="preserve">0.738027930259705</t>
@@ -239,49 +239,49 @@
     <t xml:space="preserve">0.750536978244781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.75428968667984</t>
+    <t xml:space="preserve">0.754289627075195</t>
   </si>
   <si>
     <t xml:space="preserve">0.768049478530884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.757416844367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766798555850983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.752413332462311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781183898448944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778056561946869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786187529563904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77930760383606</t>
+    <t xml:space="preserve">0.757416784763336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766798615455627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.752413272857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781183838844299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778056740760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786187350749969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77930748462677</t>
   </si>
   <si>
     <t xml:space="preserve">0.768674850463867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.755540549755096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.760543942451477</t>
+    <t xml:space="preserve">0.755540430545807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.760544002056122</t>
   </si>
   <si>
     <t xml:space="preserve">0.76429682970047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.770551204681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7592933177948</t>
+    <t xml:space="preserve">0.770551264286041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759293079376221</t>
   </si>
   <si>
     <t xml:space="preserve">0.769925773143768</t>
@@ -290,31 +290,31 @@
     <t xml:space="preserve">0.761169612407684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.7674241065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747409760951996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751787900924683</t>
+    <t xml:space="preserve">0.767423987388611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747409701347351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751787841320038</t>
   </si>
   <si>
     <t xml:space="preserve">0.754915058612823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781809270381927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801198363304138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804950892925262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799321889877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785562098026276</t>
+    <t xml:space="preserve">0.781809210777283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801198244094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804950833320618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799322009086609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785562038421631</t>
   </si>
   <si>
     <t xml:space="preserve">0.796820104122162</t>
@@ -323,163 +323,163 @@
     <t xml:space="preserve">0.791816532611847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801823616027832</t>
+    <t xml:space="preserve">0.801823675632477</t>
   </si>
   <si>
     <t xml:space="preserve">0.733649730682373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.725519061088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766306459903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759828686714172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750760197639465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778614103794098</t>
+    <t xml:space="preserve">0.725519120693207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766306519508362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759828746318817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750760138034821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778613984584808</t>
   </si>
   <si>
     <t xml:space="preserve">0.703473210334778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.692461252212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705416560173035</t>
+    <t xml:space="preserve">0.69246119260788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.70541650056839</t>
   </si>
   <si>
     <t xml:space="preserve">0.730031549930573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.763067722320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762419819831848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769545197486877</t>
+    <t xml:space="preserve">0.763067543506622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762419879436493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769545316696167</t>
   </si>
   <si>
     <t xml:space="preserve">0.757885456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.742986977100372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742339015007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.758533239364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777318477630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77407968044281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776022911071777</t>
+    <t xml:space="preserve">0.742986798286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742339074611664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758533179759979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77731853723526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774079620838165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776022970676422</t>
   </si>
   <si>
     <t xml:space="preserve">0.78379613161087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779909551143646</t>
+    <t xml:space="preserve">0.779909610748291</t>
   </si>
   <si>
     <t xml:space="preserve">0.79027384519577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789626002311707</t>
+    <t xml:space="preserve">0.789625942707062</t>
   </si>
   <si>
     <t xml:space="preserve">0.79416036605835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805172443389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807763397693634</t>
+    <t xml:space="preserve">0.805172502994537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807763516902924</t>
   </si>
   <si>
     <t xml:space="preserve">0.822662055492401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817479908466339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820718765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.822014451026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809706687927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814241170883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816184461116791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804524600505829</t>
+    <t xml:space="preserve">0.817479968070984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820718824863434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.822014331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809706807136536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814241051673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816184401512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804524660110474</t>
   </si>
   <si>
     <t xml:space="preserve">0.801285743713379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812945544719696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801933586597443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786387264728546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788330495357513</t>
+    <t xml:space="preserve">0.812945604324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801933705806732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786387085914612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788330435752869</t>
   </si>
   <si>
     <t xml:space="preserve">0.771488606929779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783148348331451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782500565052032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781852781772614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770192921161652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785091698169708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795455932617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811002254486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794808208942413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796103596687317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798694789409637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802581369876862</t>
+    <t xml:space="preserve">0.783148288726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782500505447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781852722167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770193040370941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785091638565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795455992221832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811002373695374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794808030128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796103656291962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798694729804993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802581310272217</t>
   </si>
   <si>
     <t xml:space="preserve">0.790921449661255</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">0.799342453479767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.810354650020599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780557334423065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784443914890289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785739362239838</t>
+    <t xml:space="preserve">0.810354590415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78055727481842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784443855285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785739541053772</t>
   </si>
   <si>
     <t xml:space="preserve">0.827196538448334</t>
@@ -515,49 +515,49 @@
     <t xml:space="preserve">0.797399163246155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803876876831055</t>
+    <t xml:space="preserve">0.803876936435699</t>
   </si>
   <si>
     <t xml:space="preserve">0.807115733623505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.761124312877655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77084094285965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.731327056884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735861480236053</t>
+    <t xml:space="preserve">0.7611243724823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770840883255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.731326997280121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735861539840698</t>
   </si>
   <si>
     <t xml:space="preserve">0.720315098762512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.721610546112061</t>
+    <t xml:space="preserve">0.721610605716705</t>
   </si>
   <si>
     <t xml:space="preserve">0.719019591808319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696347832679749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696995556354523</t>
+    <t xml:space="preserve">0.696347892284393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696995615959167</t>
   </si>
   <si>
     <t xml:space="preserve">0.709950923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.713837444782257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.711894273757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.707359850406647</t>
+    <t xml:space="preserve">0.713837385177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.711894154548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.707359910011292</t>
   </si>
   <si>
     <t xml:space="preserve">0.728736042976379</t>
@@ -569,133 +569,133 @@
     <t xml:space="preserve">0.722258388996124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.765011012554169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754646718502045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755294561386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787682592868805</t>
+    <t xml:space="preserve">0.765010952949524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7546466588974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755294442176819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78768265247345</t>
   </si>
   <si>
     <t xml:space="preserve">0.776670813560486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.772136270999908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78703498840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816832304000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819423198699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799990296363831</t>
+    <t xml:space="preserve">0.772136390209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787034928798676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816832184791565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819423377513885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799990355968475</t>
   </si>
   <si>
     <t xml:space="preserve">0.824605405330658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838856279850006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.831730782985687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832378625869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840151786804199</t>
+    <t xml:space="preserve">0.838856220245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.831730902194977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832378447055817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84015166759491</t>
   </si>
   <si>
     <t xml:space="preserve">0.848572552204132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.841447174549103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844685971736908</t>
+    <t xml:space="preserve">0.841447234153748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844686090946198</t>
   </si>
   <si>
     <t xml:space="preserve">0.830435335636139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.798046946525574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815536558628082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820071041584015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80646800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811649978160858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836265206336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844038307666779</t>
+    <t xml:space="preserve">0.798046886920929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815536499023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82007098197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806467950344086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811650037765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836265087127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844038188457489</t>
   </si>
   <si>
     <t xml:space="preserve">0.837560653686523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.836912870407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821366429328918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828492045402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825900971889496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829139649868011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84662926197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849220335483551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864766836166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867357730865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868005633354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870596647262573</t>
+    <t xml:space="preserve">0.836912989616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821366608142853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828492105007172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825900793075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829139828681946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846629440784454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849220395088196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864766657352448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867357790470123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868005573749542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870596587657928</t>
   </si>
   <si>
     <t xml:space="preserve">0.857641458511353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.865414500236511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866710007190704</t>
+    <t xml:space="preserve">0.865414440631866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866710245609283</t>
   </si>
   <si>
     <t xml:space="preserve">0.85310697555542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855698108673096</t>
+    <t xml:space="preserve">0.855698049068451</t>
   </si>
   <si>
     <t xml:space="preserve">0.858289182186127</t>
@@ -707,37 +707,37 @@
     <t xml:space="preserve">0.872539937496185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874483346939087</t>
+    <t xml:space="preserve">0.874483227729797</t>
   </si>
   <si>
     <t xml:space="preserve">0.887438595294952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.893916130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89262056350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912701547145844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909462690353394</t>
+    <t xml:space="preserve">0.893916249275208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89262068271637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912701487541199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909462511539459</t>
   </si>
   <si>
     <t xml:space="preserve">0.908167123794556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919826745986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918531358242035</t>
+    <t xml:space="preserve">0.919826924800873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91853129863739</t>
   </si>
   <si>
     <t xml:space="preserve">0.87577885389328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877722144126892</t>
+    <t xml:space="preserve">0.877722263336182</t>
   </si>
   <si>
     <t xml:space="preserve">0.891972899436951</t>
@@ -746,34 +746,34 @@
     <t xml:space="preserve">0.884847462177277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.895211756229401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884199678897858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876426637172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862175643444061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856345891952515</t>
+    <t xml:space="preserve">0.895211815834045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884199619293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876426696777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862175703048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85634583234787</t>
   </si>
   <si>
     <t xml:space="preserve">0.882256388664246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89909839630127</t>
+    <t xml:space="preserve">0.899098455905914</t>
   </si>
   <si>
     <t xml:space="preserve">0.890677332878113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.926952362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915292501449585</t>
+    <t xml:space="preserve">0.926952302455902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91529256105423</t>
   </si>
   <si>
     <t xml:space="preserve">0.917235851287842</t>
@@ -782,76 +782,76 @@
     <t xml:space="preserve">0.966466069221497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95804500579834</t>
+    <t xml:space="preserve">0.958045125007629</t>
   </si>
   <si>
     <t xml:space="preserve">0.965170443058014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961283802986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963227033615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941850781440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941202998161316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958692729473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982278227806091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988308489322662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997019231319427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00036919116974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992998898029327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96820729970932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981608211994171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986298382282257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988978624343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989648520946503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.974907875061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999699234962463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0050595998764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998359084129333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997689008712769</t>
+    <t xml:space="preserve">0.961283922195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963227152824402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941850960254669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941203057765961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958692908287048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982278048992157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988308668136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997019052505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00036942958832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992998957633972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96820741891861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981608271598816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986298620700836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988978683948517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989648699760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.974907755851746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999699354171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00505936145782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998359203338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997689187526703</t>
   </si>
   <si>
     <t xml:space="preserve">1.00170934200287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00706958770752</t>
+    <t xml:space="preserve">1.00706970691681</t>
   </si>
   <si>
     <t xml:space="preserve">1.02047049999237</t>
@@ -863,40 +863,40 @@
     <t xml:space="preserve">1.0177903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995008945465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999029338359833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976917922496796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.974237501621246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970217347145081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965527176856995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960836887359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961507022380829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964187145233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980268061161041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978928029537201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984958589076996</t>
+    <t xml:space="preserve">0.995009005069733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999029219150543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976917803287506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.974237680435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97021758556366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965527236461639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960837006568909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961506903171539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.964187204837799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980268120765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978927969932556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984958350658417</t>
   </si>
   <si>
     <t xml:space="preserve">0.972897708415985</t>
@@ -905,130 +905,130 @@
     <t xml:space="preserve">0.960166871547699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958826839923859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951456308364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955476701259613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949446141719818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963517010211945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950116276741028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953466534614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956816732883453</t>
+    <t xml:space="preserve">0.958826720714569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951456367969513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955476641654968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949446320533752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9635169506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950116336345673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953466415405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956816673278809</t>
   </si>
   <si>
     <t xml:space="preserve">0.958156704902649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952796399593353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962177097797394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944755911827087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931355059146881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948106110095978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954136669635773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957486689090729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939395487308502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946766078472137</t>
+    <t xml:space="preserve">0.952796578407288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962177157402039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944756090641022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931355237960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948106169700623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954136550426483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957486808300018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939395606517792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946766018867493</t>
   </si>
   <si>
     <t xml:space="preserve">0.934705436229706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.928674936294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92465478181839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932695209980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945425927639008</t>
+    <t xml:space="preserve">0.9286749958992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924654603004456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932695269584656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945425987243652</t>
   </si>
   <si>
     <t xml:space="preserve">0.959496974945068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973567605018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978257775306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993668913841248</t>
+    <t xml:space="preserve">0.973567724227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978258073329926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993668854236603</t>
   </si>
   <si>
     <t xml:space="preserve">0.984288334846497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.983618319034576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994338810443878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977587878704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980938196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972227513790131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966197192668915</t>
+    <t xml:space="preserve">0.983618438243866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994338989257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977587819099426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980938255786896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97222763299942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96619713306427</t>
   </si>
   <si>
     <t xml:space="preserve">0.96954745054245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96887731552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97155749797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995678961277008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992328584194183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966867327690125</t>
+    <t xml:space="preserve">0.96887743473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9715576171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995679020881653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992328763008118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96686726808548</t>
   </si>
   <si>
     <t xml:space="preserve">1.02114045619965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01041984558105</t>
+    <t xml:space="preserve">1.01041972637177</t>
   </si>
   <si>
     <t xml:space="preserve">1.01444017887115</t>
@@ -1037,61 +1037,61 @@
     <t xml:space="preserve">1.02181053161621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02382051944733</t>
+    <t xml:space="preserve">1.02382063865662</t>
   </si>
   <si>
     <t xml:space="preserve">1.02851092815399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03320121765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03923165798187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02650058269501</t>
+    <t xml:space="preserve">1.03320133686066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03923153877258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0265007019043</t>
   </si>
   <si>
     <t xml:space="preserve">1.05531251430511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05866253376007</t>
+    <t xml:space="preserve">1.05866277217865</t>
   </si>
   <si>
     <t xml:space="preserve">1.04459178447723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05330228805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0680433511734</t>
+    <t xml:space="preserve">1.05330240726471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06804323196411</t>
   </si>
   <si>
     <t xml:space="preserve">1.0727334022522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08613443374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0955148935318</t>
+    <t xml:space="preserve">1.08613431453705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09551501274109</t>
   </si>
   <si>
     <t xml:space="preserve">1.08345413208008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08211398124695</t>
+    <t xml:space="preserve">1.08211410045624</t>
   </si>
   <si>
     <t xml:space="preserve">1.05397248268127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06000280380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04392182826996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04861223697662</t>
+    <t xml:space="preserve">1.06000292301178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04392170906067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04861211776733</t>
   </si>
   <si>
     <t xml:space="preserve">1.04660201072693</t>
@@ -1100,22 +1100,22 @@
     <t xml:space="preserve">1.03990161418915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04258179664612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01980030536652</t>
+    <t xml:space="preserve">1.04258167743683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01980042457581</t>
   </si>
   <si>
     <t xml:space="preserve">1.01578009128571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05196237564087</t>
+    <t xml:space="preserve">1.05196225643158</t>
   </si>
   <si>
     <t xml:space="preserve">1.06737327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06603312492371</t>
+    <t xml:space="preserve">1.06603300571442</t>
   </si>
   <si>
     <t xml:space="preserve">1.02449071407318</t>
@@ -1127,22 +1127,22 @@
     <t xml:space="preserve">1.02784085273743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05665266513824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06134271621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07742393016815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07943391799927</t>
+    <t xml:space="preserve">1.05665254592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06134283542633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07742381095886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07943403720856</t>
   </si>
   <si>
     <t xml:space="preserve">1.06938326358795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05933284759521</t>
+    <t xml:space="preserve">1.05933272838593</t>
   </si>
   <si>
     <t xml:space="preserve">1.03856146335602</t>
@@ -1151,22 +1151,22 @@
     <t xml:space="preserve">1.02683579921722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03588128089905</t>
+    <t xml:space="preserve">1.03588140010834</t>
   </si>
   <si>
     <t xml:space="preserve">1.04191160202026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996348977088928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971222519874573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995343923568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94442081451416</t>
+    <t xml:space="preserve">0.996349036693573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971222579479218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995344042778015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944420993328094</t>
   </si>
   <si>
     <t xml:space="preserve">0.95313161611557</t>
@@ -1175,19 +1175,19 @@
     <t xml:space="preserve">0.941405773162842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959831893444061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946431040763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957821786403656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950451195240021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936380445957184</t>
+    <t xml:space="preserve">0.959831774234772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9464311003685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957821846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95045131444931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936380505561829</t>
   </si>
   <si>
     <t xml:space="preserve">0.967202365398407</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">0.991323709487915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975577771663666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993333876132965</t>
+    <t xml:space="preserve">0.975577890872955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993333756923676</t>
   </si>
   <si>
     <t xml:space="preserve">1.0000342130661</t>
@@ -1208,31 +1208,31 @@
     <t xml:space="preserve">1.00137436389923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991658806800842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00673460960388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999364197254181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04023671150208</t>
+    <t xml:space="preserve">0.991658866405487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00673472881317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999364256858826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04023659229279</t>
   </si>
   <si>
     <t xml:space="preserve">1.04157662391663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04224681854248</t>
+    <t xml:space="preserve">1.04224693775177</t>
   </si>
   <si>
     <t xml:space="preserve">1.04961705207825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04995226860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06268286705017</t>
+    <t xml:space="preserve">1.04995214939117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06268298625946</t>
   </si>
   <si>
     <t xml:space="preserve">1.07206356525421</t>
@@ -1244,25 +1244,25 @@
     <t xml:space="preserve">1.06335294246674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07407367229462</t>
+    <t xml:space="preserve">1.07407379150391</t>
   </si>
   <si>
     <t xml:space="preserve">1.08043897151947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08546447753906</t>
+    <t xml:space="preserve">1.08546411991119</t>
   </si>
   <si>
     <t xml:space="preserve">1.09048962593079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09484481811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09819519519806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0985301733017</t>
+    <t xml:space="preserve">1.09484493732452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09819507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09853005409241</t>
   </si>
   <si>
     <t xml:space="preserve">1.12198138237</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">1.11762619018555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1172913312912</t>
+    <t xml:space="preserve">1.11729121208191</t>
   </si>
   <si>
     <t xml:space="preserve">1.10724067687988</t>
@@ -1280,31 +1280,31 @@
     <t xml:space="preserve">1.10757577419281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12265145778656</t>
+    <t xml:space="preserve">1.12265157699585</t>
   </si>
   <si>
     <t xml:space="preserve">1.13002192974091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10992085933685</t>
+    <t xml:space="preserve">1.10992074012756</t>
   </si>
   <si>
     <t xml:space="preserve">1.11829626560211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05732250213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03387105464935</t>
+    <t xml:space="preserve">1.05732274055481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03387117385864</t>
   </si>
   <si>
     <t xml:space="preserve">1.03895282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05287516117096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04208540916443</t>
+    <t xml:space="preserve">1.05287528038025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04208528995514</t>
   </si>
   <si>
     <t xml:space="preserve">1.04730618000031</t>
@@ -1313,10 +1313,10 @@
     <t xml:space="preserve">1.02572667598724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00693154335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980827271938324</t>
+    <t xml:space="preserve">1.00693142414093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980827212333679</t>
   </si>
   <si>
     <t xml:space="preserve">0.998926222324371</t>
@@ -1325,19 +1325,19 @@
     <t xml:space="preserve">1.01076018810272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00484323501587</t>
+    <t xml:space="preserve">1.00484335422516</t>
   </si>
   <si>
     <t xml:space="preserve">1.02920734882355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00936782360077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00658333301544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999622464179993</t>
+    <t xml:space="preserve">1.00936794281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00658345222473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999622285366058</t>
   </si>
   <si>
     <t xml:space="preserve">0.968993246555328</t>
@@ -1346,28 +1346,28 @@
     <t xml:space="preserve">1.0159809589386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02398645877838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03164374828339</t>
+    <t xml:space="preserve">1.02398657798767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03164386749268</t>
   </si>
   <si>
     <t xml:space="preserve">1.02851116657257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01980972290039</t>
+    <t xml:space="preserve">1.0198096036911</t>
   </si>
   <si>
     <t xml:space="preserve">1.04382562637329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04660999774933</t>
+    <t xml:space="preserve">1.04661011695862</t>
   </si>
   <si>
     <t xml:space="preserve">1.02363836765289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02537858486176</t>
+    <t xml:space="preserve">1.02537882328033</t>
   </si>
   <si>
     <t xml:space="preserve">1.00588738918304</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">1.01250052452087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02120208740234</t>
+    <t xml:space="preserve">1.02120184898376</t>
   </si>
   <si>
     <t xml:space="preserve">1.02642285823822</t>
@@ -1388,19 +1388,19 @@
     <t xml:space="preserve">1.01389276981354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03860485553741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05113482475281</t>
+    <t xml:space="preserve">1.03860473632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0511349439621</t>
   </si>
   <si>
     <t xml:space="preserve">1.06122851371765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07236647605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06018435955048</t>
+    <t xml:space="preserve">1.07236635684967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06018424034119</t>
   </si>
   <si>
     <t xml:space="preserve">1.06262075901031</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">1.05600762367249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07375860214233</t>
+    <t xml:space="preserve">1.07375872135162</t>
   </si>
   <si>
     <t xml:space="preserve">1.06714558601379</t>
@@ -1421,19 +1421,19 @@
     <t xml:space="preserve">1.09290182590485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09429395198822</t>
+    <t xml:space="preserve">1.09429407119751</t>
   </si>
   <si>
     <t xml:space="preserve">1.10160326957703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08420050144196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04835033416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06157672405243</t>
+    <t xml:space="preserve">1.08420038223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04835045337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06157660484314</t>
   </si>
   <si>
     <t xml:space="preserve">1.07201826572418</t>
@@ -1448,22 +1448,22 @@
     <t xml:space="preserve">1.09394598007202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08106780052185</t>
+    <t xml:space="preserve">1.08106803894043</t>
   </si>
   <si>
     <t xml:space="preserve">1.09011733531952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0824601650238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10299551486969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12005031108856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12387895584106</t>
+    <t xml:space="preserve">1.08246004581451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1029953956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12005043029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12387907505035</t>
   </si>
   <si>
     <t xml:space="preserve">1.10473585128784</t>
@@ -1478,40 +1478,40 @@
     <t xml:space="preserve">1.10821640491486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10960876941681</t>
+    <t xml:space="preserve">1.10960865020752</t>
   </si>
   <si>
     <t xml:space="preserve">1.08837711811066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08802902698517</t>
+    <t xml:space="preserve">1.08802890777588</t>
   </si>
   <si>
     <t xml:space="preserve">1.08942139148712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0754988193512</t>
+    <t xml:space="preserve">1.07549893856049</t>
   </si>
   <si>
     <t xml:space="preserve">1.06540524959564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03338408470154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04243350028992</t>
+    <t xml:space="preserve">1.03338396549225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04243338108063</t>
   </si>
   <si>
     <t xml:space="preserve">1.02154994010925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03094732761383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04173719882965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05705189704895</t>
+    <t xml:space="preserve">1.03094744682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04173731803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05705177783966</t>
   </si>
   <si>
     <t xml:space="preserve">1.0789794921875</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">1.09116160869598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08454847335815</t>
+    <t xml:space="preserve">1.08454859256744</t>
   </si>
   <si>
     <t xml:space="preserve">1.08141613006592</t>
@@ -1541,13 +1541,13 @@
     <t xml:space="preserve">1.07445466518402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0587922334671</t>
+    <t xml:space="preserve">1.05879211425781</t>
   </si>
   <si>
     <t xml:space="preserve">1.07758724689484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06923389434814</t>
+    <t xml:space="preserve">1.06923401355743</t>
   </si>
   <si>
     <t xml:space="preserve">1.04069328308105</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">1.04417371749878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05183100700378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03616833686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05844402313232</t>
+    <t xml:space="preserve">1.05183112621307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03616845607758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05844414234161</t>
   </si>
   <si>
     <t xml:space="preserve">1.03442811965942</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">1.00310289859772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991617143154144</t>
+    <t xml:space="preserve">0.991616904735565</t>
   </si>
   <si>
     <t xml:space="preserve">1.00832378864288</t>
@@ -1589,13 +1589,13 @@
     <t xml:space="preserve">1.01772141456604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01354467868805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99370539188385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988136410713196</t>
+    <t xml:space="preserve">1.01354455947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993705451488495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988136351108551</t>
   </si>
   <si>
     <t xml:space="preserve">0.977346658706665</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">0.986048102378845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989528656005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992313265800476</t>
+    <t xml:space="preserve">0.989528715610504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992313206195831</t>
   </si>
   <si>
     <t xml:space="preserve">0.98291552066803</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">1.01319658756256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00414717197418</t>
+    <t xml:space="preserve">1.00414705276489</t>
   </si>
   <si>
     <t xml:space="preserve">1.02050590515137</t>
@@ -1634,10 +1634,10 @@
     <t xml:space="preserve">1.0351243019104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0393009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05252707004547</t>
+    <t xml:space="preserve">1.03930103778839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05252695083618</t>
   </si>
   <si>
     <t xml:space="preserve">1.05461549758911</t>
@@ -1646,19 +1646,19 @@
     <t xml:space="preserve">1.03721261024475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0271190404892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03999710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06610131263733</t>
+    <t xml:space="preserve">1.02711892127991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03999698162079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06610143184662</t>
   </si>
   <si>
     <t xml:space="preserve">1.06088054180145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04034507274628</t>
+    <t xml:space="preserve">1.04034531116486</t>
   </si>
   <si>
     <t xml:space="preserve">1.03233981132507</t>
@@ -1673,28 +1673,28 @@
     <t xml:space="preserve">1.07410657405853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10090708732605</t>
+    <t xml:space="preserve">1.10090720653534</t>
   </si>
   <si>
     <t xml:space="preserve">1.11761403083801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12701141834259</t>
+    <t xml:space="preserve">1.12701153755188</t>
   </si>
   <si>
     <t xml:space="preserve">1.11378538608551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10647594928741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12318301200867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13118827342987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11448132991791</t>
+    <t xml:space="preserve">1.1064760684967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12318289279938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13118815422058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1144814491272</t>
   </si>
   <si>
     <t xml:space="preserve">1.08872520923615</t>
@@ -1703,19 +1703,19 @@
     <t xml:space="preserve">1.094642162323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11622166633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11831021308899</t>
+    <t xml:space="preserve">1.11622178554535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11830997467041</t>
   </si>
   <si>
     <t xml:space="preserve">1.13501679897308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13675725460052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13814949989319</t>
+    <t xml:space="preserve">1.13675713539124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1381493806839</t>
   </si>
   <si>
     <t xml:space="preserve">1.14302217960358</t>
@@ -1727,55 +1727,55 @@
     <t xml:space="preserve">1.10891258716583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09951496124268</t>
+    <t xml:space="preserve">1.09951484203339</t>
   </si>
   <si>
     <t xml:space="preserve">1.10195124149323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09916687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09499025344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10578012466431</t>
+    <t xml:space="preserve">1.0991667509079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0949901342392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10577988624573</t>
   </si>
   <si>
     <t xml:space="preserve">1.09185767173767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07793533802032</t>
+    <t xml:space="preserve">1.07793521881104</t>
   </si>
   <si>
     <t xml:space="preserve">1.08071982860565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08663690090179</t>
+    <t xml:space="preserve">1.0866367816925</t>
   </si>
   <si>
     <t xml:space="preserve">1.06227278709412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08280825614929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09742677211761</t>
+    <t xml:space="preserve">1.08280813694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09742665290833</t>
   </si>
   <si>
     <t xml:space="preserve">1.10021114349365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09777474403381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10369157791138</t>
+    <t xml:space="preserve">1.09777462482452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10369169712067</t>
   </si>
   <si>
     <t xml:space="preserve">1.11100089550018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10543191432953</t>
+    <t xml:space="preserve">1.10543179512024</t>
   </si>
   <si>
     <t xml:space="preserve">1.08594071865082</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">1.09568619728088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08907318115234</t>
+    <t xml:space="preserve">1.08907330036163</t>
   </si>
   <si>
     <t xml:space="preserve">1.11726593971252</t>
@@ -1796,16 +1796,16 @@
     <t xml:space="preserve">1.10752022266388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1103048324585</t>
+    <t xml:space="preserve">1.11030471324921</t>
   </si>
   <si>
     <t xml:space="preserve">1.12179064750671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11935448646545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13571298122406</t>
+    <t xml:space="preserve">1.11935436725616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13571286201477</t>
   </si>
   <si>
     <t xml:space="preserve">1.13536489009857</t>
@@ -1817,28 +1817,28 @@
     <t xml:space="preserve">1.13223230838776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14754712581635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.063316822052</t>
+    <t xml:space="preserve">1.14754688739777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06331694126129</t>
   </si>
   <si>
     <t xml:space="preserve">1.05391931533813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04626202583313</t>
+    <t xml:space="preserve">1.04626190662384</t>
   </si>
   <si>
     <t xml:space="preserve">1.05426752567291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04869854450226</t>
+    <t xml:space="preserve">1.04869842529297</t>
   </si>
   <si>
     <t xml:space="preserve">1.02433454990387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0194616317749</t>
+    <t xml:space="preserve">1.01946151256561</t>
   </si>
   <si>
     <t xml:space="preserve">1.01632905006409</t>
@@ -1847,22 +1847,22 @@
     <t xml:space="preserve">1.0037989616394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997882127761841</t>
+    <t xml:space="preserve">0.997882068157196</t>
   </si>
   <si>
     <t xml:space="preserve">1.00727963447571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02015769481659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07654309272766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08517634868622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09720540046692</t>
+    <t xml:space="preserve">1.02015781402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07654297351837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08517646789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09720551967621</t>
   </si>
   <si>
     <t xml:space="preserve">1.09647643566132</t>
@@ -1883,13 +1883,13 @@
     <t xml:space="preserve">1.05127596855164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06403422355652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07168936729431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08043766021729</t>
+    <t xml:space="preserve">1.06403410434723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07168924808502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08043777942657</t>
   </si>
   <si>
     <t xml:space="preserve">1.0979346036911</t>
@@ -1901,19 +1901,19 @@
     <t xml:space="preserve">1.10449588298798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10048615932465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10230875015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09574747085571</t>
+    <t xml:space="preserve">1.10048639774323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1023086309433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09574735164642</t>
   </si>
   <si>
     <t xml:space="preserve">1.09829902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13219940662384</t>
+    <t xml:space="preserve">1.13219964504242</t>
   </si>
   <si>
     <t xml:space="preserve">1.12563812732697</t>
@@ -1931,13 +1931,13 @@
     <t xml:space="preserve">1.11944127082825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11543154716492</t>
+    <t xml:space="preserve">1.11543142795563</t>
   </si>
   <si>
     <t xml:space="preserve">1.10376691818237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11251533031464</t>
+    <t xml:space="preserve">1.11251544952393</t>
   </si>
   <si>
     <t xml:space="preserve">1.11069273948669</t>
@@ -1946,76 +1946,76 @@
     <t xml:space="preserve">1.13511574268341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15006101131439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15188348293304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.147873878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15261268615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16427719593048</t>
+    <t xml:space="preserve">1.1500608921051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15188360214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14787399768829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15261256694794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16427731513977</t>
   </si>
   <si>
     <t xml:space="preserve">1.1704740524292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17156755924225</t>
+    <t xml:space="preserve">1.17156767845154</t>
   </si>
   <si>
     <t xml:space="preserve">1.17229688167572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17849349975586</t>
+    <t xml:space="preserve">1.17849361896515</t>
   </si>
   <si>
     <t xml:space="preserve">1.17484831809998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1916161775589</t>
+    <t xml:space="preserve">1.19161641597748</t>
   </si>
   <si>
     <t xml:space="preserve">1.16318356990814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16609966754913</t>
+    <t xml:space="preserve">1.16609978675842</t>
   </si>
   <si>
     <t xml:space="preserve">1.17995166778564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18469047546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18104541301727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17120325565338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17375481128693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14969658851624</t>
+    <t xml:space="preserve">1.18469035625458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18104529380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1712030172348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17375469207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14969646930695</t>
   </si>
   <si>
     <t xml:space="preserve">1.15407061576843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17083859443665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16209018230438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16682910919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16755795478821</t>
+    <t xml:space="preserve">1.17083847522736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16209006309509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1668289899826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1675580739975</t>
   </si>
   <si>
     <t xml:space="preserve">1.17010962963104</t>
@@ -2024,43 +2024,43 @@
     <t xml:space="preserve">1.13183498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12418007850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12782526016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14277064800262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16099667549133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14459311962128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15297710895538</t>
+    <t xml:space="preserve">1.12418019771576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12782537937164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14277052879333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16099655628204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14459323883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15297722816467</t>
   </si>
   <si>
     <t xml:space="preserve">1.13985443115234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13475096225739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16391289234161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16938054561615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16573536396027</t>
+    <t xml:space="preserve">1.13475108146667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16391277313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16938066482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16573524475098</t>
   </si>
   <si>
     <t xml:space="preserve">1.16500639915466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18833553791046</t>
+    <t xml:space="preserve">1.18833565711975</t>
   </si>
   <si>
     <t xml:space="preserve">1.20473909378052</t>
@@ -2072,13 +2072,13 @@
     <t xml:space="preserve">1.1887001991272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1795871257782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16464185714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17922258377075</t>
+    <t xml:space="preserve">1.17958724498749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16464173793793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17922246456146</t>
   </si>
   <si>
     <t xml:space="preserve">1.18213880062103</t>
@@ -2090,13 +2090,13 @@
     <t xml:space="preserve">1.19599056243896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18979370594025</t>
+    <t xml:space="preserve">1.18979358673096</t>
   </si>
   <si>
     <t xml:space="preserve">1.22551667690277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21567463874817</t>
+    <t xml:space="preserve">1.21567475795746</t>
   </si>
   <si>
     <t xml:space="preserve">1.22770380973816</t>
@@ -2111,16 +2111,16 @@
     <t xml:space="preserve">1.21166479587555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23134899139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23025548458099</t>
+    <t xml:space="preserve">1.23134911060333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2302553653717</t>
   </si>
   <si>
     <t xml:space="preserve">1.21603918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21931982040405</t>
+    <t xml:space="preserve">1.21931993961334</t>
   </si>
   <si>
     <t xml:space="preserve">1.23791027069092</t>
@@ -2129,13 +2129,13 @@
     <t xml:space="preserve">1.23462963104248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22806823253632</t>
+    <t xml:space="preserve">1.22806835174561</t>
   </si>
   <si>
     <t xml:space="preserve">1.21640360355377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22187161445618</t>
+    <t xml:space="preserve">1.22187149524689</t>
   </si>
   <si>
     <t xml:space="preserve">1.22114241123199</t>
@@ -2147,10 +2147,10 @@
     <t xml:space="preserve">1.23061990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22843277454376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23645222187042</t>
+    <t xml:space="preserve">1.22843289375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23645234107971</t>
   </si>
   <si>
     <t xml:space="preserve">1.2287974357605</t>
@@ -2159,22 +2159,22 @@
     <t xml:space="preserve">1.22624576091766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27363324165344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27691411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31154334545135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3133659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30972075462341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30826270580292</t>
+    <t xml:space="preserve">1.27363336086273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27691400051117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31154346466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31336605548859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30972063541412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30826282501221</t>
   </si>
   <si>
     <t xml:space="preserve">1.31591761112213</t>
@@ -2186,19 +2186,19 @@
     <t xml:space="preserve">1.31518864631653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31445944309235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30862712860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29732704162598</t>
+    <t xml:space="preserve">1.31445956230164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30862724781036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29732716083527</t>
   </si>
   <si>
     <t xml:space="preserve">1.27873659133911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28857851028442</t>
+    <t xml:space="preserve">1.28857862949371</t>
   </si>
   <si>
     <t xml:space="preserve">1.28420436382294</t>
@@ -2210,16 +2210,16 @@
     <t xml:space="preserve">1.27509129047394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26452028751373</t>
+    <t xml:space="preserve">1.26452040672302</t>
   </si>
   <si>
     <t xml:space="preserve">1.24884593486786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24665868282318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25249099731445</t>
+    <t xml:space="preserve">1.24665880203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25249111652374</t>
   </si>
   <si>
     <t xml:space="preserve">1.24520063400269</t>
@@ -2228,25 +2228,25 @@
     <t xml:space="preserve">1.24483621120453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19052278995514</t>
+    <t xml:space="preserve">1.19052267074585</t>
   </si>
   <si>
     <t xml:space="preserve">1.19635510444641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19854211807251</t>
+    <t xml:space="preserve">1.1985422372818</t>
   </si>
   <si>
     <t xml:space="preserve">1.19343888759613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18068075180054</t>
+    <t xml:space="preserve">1.18068063259125</t>
   </si>
   <si>
     <t xml:space="preserve">1.20218741893768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18906462192535</t>
+    <t xml:space="preserve">1.18906474113464</t>
   </si>
   <si>
     <t xml:space="preserve">1.19270992279053</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">1.20656156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20729064941406</t>
+    <t xml:space="preserve">1.20729088783264</t>
   </si>
   <si>
     <t xml:space="preserve">1.22515213489532</t>
@@ -2264,34 +2264,34 @@
     <t xml:space="preserve">1.24155557155609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23353600502014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21895551681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21275842189789</t>
+    <t xml:space="preserve">1.23353612422943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21895527839661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21275854110718</t>
   </si>
   <si>
     <t xml:space="preserve">1.20838415622711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25504279136658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25066840648651</t>
+    <t xml:space="preserve">1.25504291057587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2506685256958</t>
   </si>
   <si>
     <t xml:space="preserve">1.25941693782806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25650072097778</t>
+    <t xml:space="preserve">1.25650084018707</t>
   </si>
   <si>
     <t xml:space="preserve">1.26853001117706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2998788356781</t>
+    <t xml:space="preserve">1.29987871646881</t>
   </si>
   <si>
     <t xml:space="preserve">1.30315947532654</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">1.29222393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30607557296753</t>
+    <t xml:space="preserve">1.30607545375824</t>
   </si>
   <si>
     <t xml:space="preserve">1.35200524330139</t>
@@ -2315,10 +2315,10 @@
     <t xml:space="preserve">1.33414363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31409513950348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3224790096283</t>
+    <t xml:space="preserve">1.31409502029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32247912883759</t>
   </si>
   <si>
     <t xml:space="preserve">1.32940495014191</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">1.34580826759338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33159208297729</t>
+    <t xml:space="preserve">1.33159196376801</t>
   </si>
   <si>
     <t xml:space="preserve">1.33013391494751</t>
@@ -2339,34 +2339,34 @@
     <t xml:space="preserve">1.34398567676544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3414341211319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34945333003998</t>
+    <t xml:space="preserve">1.34143400192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34945344924927</t>
   </si>
   <si>
     <t xml:space="preserve">1.35893106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36986672878265</t>
+    <t xml:space="preserve">1.36986660957336</t>
   </si>
   <si>
     <t xml:space="preserve">1.3822603225708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3603892326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3490891456604</t>
+    <t xml:space="preserve">1.36038911342621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34908902645111</t>
   </si>
   <si>
     <t xml:space="preserve">1.26524925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25613641738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13766717910767</t>
+    <t xml:space="preserve">1.25613629817963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13766729831696</t>
   </si>
   <si>
     <t xml:space="preserve">1.15589332580566</t>
@@ -2378,10 +2378,10 @@
     <t xml:space="preserve">1.11579608917236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996233522891998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924787402153015</t>
+    <t xml:space="preserve">0.996233463287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924787521362305</t>
   </si>
   <si>
     <t xml:space="preserve">0.905467987060547</t>
@@ -2393,13 +2393,13 @@
     <t xml:space="preserve">0.772782623767853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.750546991825104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775334358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751276016235352</t>
+    <t xml:space="preserve">0.750546932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775334417819977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751275956630707</t>
   </si>
   <si>
     <t xml:space="preserve">0.754556655883789</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">0.729040265083313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786269962787628</t>
+    <t xml:space="preserve">0.786270022392273</t>
   </si>
   <si>
     <t xml:space="preserve">0.797205567359924</t>
@@ -2420,16 +2420,16 @@
     <t xml:space="preserve">0.793195843696594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778250455856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824544548988342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826002538204193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816160619258881</t>
+    <t xml:space="preserve">0.778250515460968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824544489383698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826002597808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816160559654236</t>
   </si>
   <si>
     <t xml:space="preserve">0.841677010059357</t>
@@ -2438,70 +2438,70 @@
     <t xml:space="preserve">0.836209118366241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.869015991687775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869744956493378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855164170265198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876670956611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889429092407227</t>
+    <t xml:space="preserve">0.86901593208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869744896888733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855164110660553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876670897006989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889429032802582</t>
   </si>
   <si>
     <t xml:space="preserve">0.885783910751343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.897448539733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910935878753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91166478395462</t>
+    <t xml:space="preserve">0.897448480129242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910935938358307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911664843559265</t>
   </si>
   <si>
     <t xml:space="preserve">0.883961260318756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.888335645198822</t>
+    <t xml:space="preserve">0.888335525989532</t>
   </si>
   <si>
     <t xml:space="preserve">0.879587113857269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89015805721283</t>
+    <t xml:space="preserve">0.890158116817474</t>
   </si>
   <si>
     <t xml:space="preserve">0.906926035881042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.901458263397217</t>
+    <t xml:space="preserve">0.901458203792572</t>
   </si>
   <si>
     <t xml:space="preserve">0.899635672569275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.905832469463348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872296631336212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879951655864716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878128886222839</t>
+    <t xml:space="preserve">0.905832588672638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872296512126923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879951596260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878128945827484</t>
   </si>
   <si>
     <t xml:space="preserve">0.882138729095459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877764523029327</t>
+    <t xml:space="preserve">0.877764403820038</t>
   </si>
   <si>
     <t xml:space="preserve">0.914581060409546</t>
@@ -2510,10 +2510,10 @@
     <t xml:space="preserve">0.93426513671875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.911300420761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944332540035248</t>
+    <t xml:space="preserve">0.911300361156464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944332480430603</t>
   </si>
   <si>
     <t xml:space="preserve">0.902750730514526</t>
@@ -2528,10 +2528,10 @@
     <t xml:space="preserve">0.912854731082916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946275532245636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971146941184998</t>
+    <t xml:space="preserve">0.946275591850281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971147000789642</t>
   </si>
   <si>
     <t xml:space="preserve">0.950550377368927</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">0.981639444828033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00573348999023</t>
+    <t xml:space="preserve">1.00573360919952</t>
   </si>
   <si>
     <t xml:space="preserve">1.04265189170837</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">1.04342901706696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03060472011566</t>
+    <t xml:space="preserve">1.03060483932495</t>
   </si>
   <si>
     <t xml:space="preserve">1.05236709117889</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">0.960265636444092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.956379592418671</t>
+    <t xml:space="preserve">0.956379473209381</t>
   </si>
   <si>
     <t xml:space="preserve">0.978141903877258</t>
@@ -2606,10 +2606,10 @@
     <t xml:space="preserve">0.984359741210938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999904274940491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996795415878296</t>
+    <t xml:space="preserve">0.99990439414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996795535087585</t>
   </si>
   <si>
     <t xml:space="preserve">0.993686556816101</t>
@@ -2618,13 +2618,13 @@
     <t xml:space="preserve">0.983194053173065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982805252075195</t>
+    <t xml:space="preserve">0.982805371284485</t>
   </si>
   <si>
     <t xml:space="preserve">0.958322584629059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961431384086609</t>
+    <t xml:space="preserve">0.961431503295898</t>
   </si>
   <si>
     <t xml:space="preserve">0.960654199123383</t>
@@ -2645,16 +2645,16 @@
     <t xml:space="preserve">0.985525608062744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949773073196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954436421394348</t>
+    <t xml:space="preserve">0.949773132801056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954436540603638</t>
   </si>
   <si>
     <t xml:space="preserve">0.970758259296417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.928788065910339</t>
+    <t xml:space="preserve">0.928788006305695</t>
   </si>
   <si>
     <t xml:space="preserve">0.943166732788086</t>
@@ -2672,37 +2672,37 @@
     <t xml:space="preserve">0.965317666530609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982028067111969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01739192008972</t>
+    <t xml:space="preserve">0.982027947902679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01739203929901</t>
   </si>
   <si>
     <t xml:space="preserve">1.00612223148346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994852364063263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97930771112442</t>
+    <t xml:space="preserve">0.994852244853973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97930783033371</t>
   </si>
   <si>
     <t xml:space="preserve">0.989411771297455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987079977989197</t>
+    <t xml:space="preserve">0.987080097198486</t>
   </si>
   <si>
     <t xml:space="preserve">0.964929044246674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962597370147705</t>
+    <t xml:space="preserve">0.96259742975235</t>
   </si>
   <si>
     <t xml:space="preserve">0.958711266517639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.966094851493835</t>
+    <t xml:space="preserve">0.966094970703125</t>
   </si>
   <si>
     <t xml:space="preserve">0.951327502727509</t>
@@ -2726,52 +2726,52 @@
     <t xml:space="preserve">0.938503205776215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94200074672699</t>
+    <t xml:space="preserve">0.942000806331635</t>
   </si>
   <si>
     <t xml:space="preserve">0.933451235294342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971924006938934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948995769023895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953270554542542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9458869099617</t>
+    <t xml:space="preserve">0.971924126148224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94899582862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953270673751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945886969566345</t>
   </si>
   <si>
     <t xml:space="preserve">0.929565131664276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931119680404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900807797908783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903528034687042</t>
+    <t xml:space="preserve">0.931119561195374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900807738304138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903528094291687</t>
   </si>
   <si>
     <t xml:space="preserve">0.904693841934204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.898864567279816</t>
+    <t xml:space="preserve">0.898864507675171</t>
   </si>
   <si>
     <t xml:space="preserve">0.878656685352325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.886428892612457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90158486366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886040329933167</t>
+    <t xml:space="preserve">0.886428952217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901584804058075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886040270328522</t>
   </si>
   <si>
     <t xml:space="preserve">0.840961158275604</t>
@@ -2795,13 +2795,13 @@
     <t xml:space="preserve">0.892646729946136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.881376922130585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942778050899506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93928050994873</t>
+    <t xml:space="preserve">0.88137686252594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942777991294861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939280450344086</t>
   </si>
   <si>
     <t xml:space="preserve">0.955213606357574</t>
@@ -2810,22 +2810,22 @@
     <t xml:space="preserve">0.952493369579315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947441458702087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952104806900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959488451480865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976198971271515</t>
+    <t xml:space="preserve">0.947441399097443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95210474729538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959488570690155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976198852062225</t>
   </si>
   <si>
     <t xml:space="preserve">1.01700341701508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02205526828766</t>
+    <t xml:space="preserve">1.02205538749695</t>
   </si>
   <si>
     <t xml:space="preserve">0.993297874927521</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">0.975421667098999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.976587355136871</t>
+    <t xml:space="preserve">0.976587474346161</t>
   </si>
   <si>
     <t xml:space="preserve">0.997184038162231</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">0.990966200828552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988245844841003</t>
+    <t xml:space="preserve">0.988245964050293</t>
   </si>
   <si>
     <t xml:space="preserve">0.984748303890228</t>
@@ -2858,25 +2858,25 @@
     <t xml:space="preserve">0.954825043678284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0065108537674</t>
+    <t xml:space="preserve">1.00651073455811</t>
   </si>
   <si>
     <t xml:space="preserve">1.01583743095398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0138943195343</t>
+    <t xml:space="preserve">1.01389443874359</t>
   </si>
   <si>
     <t xml:space="preserve">1.03449094295502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02399837970734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04148614406586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0395427942276</t>
+    <t xml:space="preserve">1.02399826049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04148602485657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03954291343689</t>
   </si>
   <si>
     <t xml:space="preserve">1.03487956523895</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">1.0375999212265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03215932846069</t>
+    <t xml:space="preserve">1.0321592092514</t>
   </si>
   <si>
     <t xml:space="preserve">1.02050089836121</t>
@@ -2897,10 +2897,10 @@
     <t xml:space="preserve">1.03099346160889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06596887111664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0729638338089</t>
+    <t xml:space="preserve">1.06596875190735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07296371459961</t>
   </si>
   <si>
     <t xml:space="preserve">1.04653799533844</t>
@@ -2912,16 +2912,16 @@
     <t xml:space="preserve">1.05353307723999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06169390678406</t>
+    <t xml:space="preserve">1.06169402599335</t>
   </si>
   <si>
     <t xml:space="preserve">1.0449835062027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10871636867523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13630795478821</t>
+    <t xml:space="preserve">1.10871624946594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1363080739975</t>
   </si>
   <si>
     <t xml:space="preserve">1.15418410301208</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">1.14252579212189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17516922950745</t>
+    <t xml:space="preserve">1.17516911029816</t>
   </si>
   <si>
     <t xml:space="preserve">1.1619565486908</t>
@@ -2954,19 +2954,19 @@
     <t xml:space="preserve">1.12698113918304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11415684223175</t>
+    <t xml:space="preserve">1.11415696144104</t>
   </si>
   <si>
     <t xml:space="preserve">1.10366427898407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11221396923065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0931715965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08384501934052</t>
+    <t xml:space="preserve">1.11221385002136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09317171573639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08384490013123</t>
   </si>
   <si>
     <t xml:space="preserve">1.11493420600891</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">1.15262973308563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14874362945557</t>
+    <t xml:space="preserve">1.14874374866486</t>
   </si>
   <si>
     <t xml:space="preserve">1.15496134757996</t>
@@ -3023,16 +3023,16 @@
     <t xml:space="preserve">1.20664703845978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21558511257172</t>
+    <t xml:space="preserve">1.21558523178101</t>
   </si>
   <si>
     <t xml:space="preserve">1.2175281047821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20625841617584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20392680168152</t>
+    <t xml:space="preserve">1.20625829696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20392692089081</t>
   </si>
   <si>
     <t xml:space="preserve">1.20859003067017</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">1.19809758663177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21286475658417</t>
+    <t xml:space="preserve">1.21286487579346</t>
   </si>
   <si>
     <t xml:space="preserve">1.21597385406494</t>
@@ -3068,16 +3068,16 @@
     <t xml:space="preserve">1.21403074264526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23579323291779</t>
+    <t xml:space="preserve">1.2357931137085</t>
   </si>
   <si>
     <t xml:space="preserve">1.2381249666214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23851335048676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24278819561005</t>
+    <t xml:space="preserve">1.23851346969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24278807640076</t>
   </si>
   <si>
     <t xml:space="preserve">1.26105296611786</t>
@@ -3092,19 +3092,19 @@
     <t xml:space="preserve">1.26066446304321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2649393081665</t>
+    <t xml:space="preserve">1.26493918895721</t>
   </si>
   <si>
     <t xml:space="preserve">1.27892935276031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30457782745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31779074668884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29291939735413</t>
+    <t xml:space="preserve">1.3045779466629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31779086589813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29291951656342</t>
   </si>
   <si>
     <t xml:space="preserve">1.29874861240387</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">1.34382784366608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3484913110733</t>
+    <t xml:space="preserve">1.34849119186401</t>
   </si>
   <si>
     <t xml:space="preserve">1.35121154785156</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">1.391716837883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38438999652863</t>
+    <t xml:space="preserve">1.38438987731934</t>
   </si>
   <si>
     <t xml:space="preserve">1.39456629753113</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">1.38886749744415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41044127941132</t>
+    <t xml:space="preserve">1.41044139862061</t>
   </si>
   <si>
     <t xml:space="preserve">1.42306005954742</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">1.45847380161285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43852806091309</t>
+    <t xml:space="preserve">1.43852818012238</t>
   </si>
   <si>
     <t xml:space="preserve">1.43771398067474</t>
@@ -3188,19 +3188,19 @@
     <t xml:space="preserve">1.45765960216522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4552173614502</t>
+    <t xml:space="preserve">1.45521724224091</t>
   </si>
   <si>
     <t xml:space="preserve">1.43120110034943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44300556182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44422686100006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42713057994843</t>
+    <t xml:space="preserve">1.4430056810379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44422698020935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42713046073914</t>
   </si>
   <si>
     <t xml:space="preserve">1.41858243942261</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">1.41898941993713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41329073905945</t>
+    <t xml:space="preserve">1.41329061985016</t>
   </si>
   <si>
     <t xml:space="preserve">1.43527162075043</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">1.39945089817047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41736125946045</t>
+    <t xml:space="preserve">1.41736137866974</t>
   </si>
   <si>
     <t xml:space="preserve">1.403928399086</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">1.34734797477722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35915267467499</t>
+    <t xml:space="preserve">1.3591525554657</t>
   </si>
   <si>
     <t xml:space="preserve">1.38316881656647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.395787358284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4511467218399</t>
+    <t xml:space="preserve">1.39578747749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45114684104919</t>
   </si>
   <si>
     <t xml:space="preserve">1.47719812393188</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">1.47394180297852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47068536281586</t>
+    <t xml:space="preserve">1.47068524360657</t>
   </si>
   <si>
     <t xml:space="preserve">1.47923338413239</t>
@@ -3293,10 +3293,10 @@
     <t xml:space="preserve">1.54069864749908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55006086826324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58262503147125</t>
+    <t xml:space="preserve">1.55006098747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58262515068054</t>
   </si>
   <si>
     <t xml:space="preserve">1.58669567108154</t>
@@ -3305,13 +3305,13 @@
     <t xml:space="preserve">1.56593585014343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58384621143341</t>
+    <t xml:space="preserve">1.5838463306427</t>
   </si>
   <si>
     <t xml:space="preserve">1.5549453496933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53215026855469</t>
+    <t xml:space="preserve">1.53215038776398</t>
   </si>
   <si>
     <t xml:space="preserve">1.52726590633392</t>
@@ -3320,22 +3320,22 @@
     <t xml:space="preserve">1.52889406681061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52197396755219</t>
+    <t xml:space="preserve">1.52197408676147</t>
   </si>
   <si>
     <t xml:space="preserve">1.51424014568329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51912486553192</t>
+    <t xml:space="preserve">1.51912474632263</t>
   </si>
   <si>
     <t xml:space="preserve">1.50650596618652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49755084514618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52238118648529</t>
+    <t xml:space="preserve">1.49755072593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.522381067276</t>
   </si>
   <si>
     <t xml:space="preserve">1.49307322502136</t>
@@ -3362,16 +3362,16 @@
     <t xml:space="preserve">1.45155394077301</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46173012256622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46213710308075</t>
+    <t xml:space="preserve">1.46173000335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46213722229004</t>
   </si>
   <si>
     <t xml:space="preserve">1.4837110042572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47882640361786</t>
+    <t xml:space="preserve">1.47882628440857</t>
   </si>
   <si>
     <t xml:space="preserve">1.48411810398102</t>
@@ -3383,13 +3383,13 @@
     <t xml:space="preserve">1.45562422275543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43812108039856</t>
+    <t xml:space="preserve">1.43812096118927</t>
   </si>
   <si>
     <t xml:space="preserve">1.44544792175293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44015634059906</t>
+    <t xml:space="preserve">1.44015622138977</t>
   </si>
   <si>
     <t xml:space="preserve">1.45684552192688</t>
@@ -3407,10 +3407,10 @@
     <t xml:space="preserve">1.46417248249054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44504106044769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47475576400757</t>
+    <t xml:space="preserve">1.4450409412384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47475588321686</t>
   </si>
   <si>
     <t xml:space="preserve">1.49673676490784</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">1.502028465271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48696756362915</t>
+    <t xml:space="preserve">1.48696744441986</t>
   </si>
   <si>
     <t xml:space="preserve">1.50365662574768</t>
@@ -3452,43 +3452,43 @@
     <t xml:space="preserve">1.49022388458252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49225914478302</t>
+    <t xml:space="preserve">1.49225902557373</t>
   </si>
   <si>
     <t xml:space="preserve">1.510169506073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47760534286499</t>
+    <t xml:space="preserve">1.4776052236557</t>
   </si>
   <si>
     <t xml:space="preserve">1.50040030479431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50121438503265</t>
+    <t xml:space="preserve">1.50121426582336</t>
   </si>
   <si>
     <t xml:space="preserve">1.51301884651184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51953172683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51546132564545</t>
+    <t xml:space="preserve">1.51953184604645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51546120643616</t>
   </si>
   <si>
     <t xml:space="preserve">1.3921240568161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40596377849579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39538037776947</t>
+    <t xml:space="preserve">1.4059636592865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39538025856018</t>
   </si>
   <si>
     <t xml:space="preserve">1.40637075901031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45196080207825</t>
+    <t xml:space="preserve">1.45196068286896</t>
   </si>
   <si>
     <t xml:space="preserve">1.43079400062561</t>
@@ -3509,10 +3509,10 @@
     <t xml:space="preserve">1.39130985736847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32699537277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34531271457672</t>
+    <t xml:space="preserve">1.32699525356293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34531283378601</t>
   </si>
   <si>
     <t xml:space="preserve">1.34775507450104</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">1.37177121639252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39741563796997</t>
+    <t xml:space="preserve">1.39741575717926</t>
   </si>
   <si>
     <t xml:space="preserve">1.40026497840881</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">1.36770057678223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35589623451233</t>
+    <t xml:space="preserve">1.35589611530304</t>
   </si>
   <si>
     <t xml:space="preserve">1.35263979434967</t>
@@ -3563,16 +3563,16 @@
     <t xml:space="preserve">1.3530467748642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34164917469025</t>
+    <t xml:space="preserve">1.34164929389954</t>
   </si>
   <si>
     <t xml:space="preserve">1.30664265155792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3326940536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3652583360672</t>
+    <t xml:space="preserve">1.33269417285919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36525845527649</t>
   </si>
   <si>
     <t xml:space="preserve">1.41532599925995</t>
@@ -3590,13 +3590,13 @@
     <t xml:space="preserve">1.37624883651733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36973595619202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33513629436493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30949199199677</t>
+    <t xml:space="preserve">1.36973583698273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33513641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30949211120605</t>
   </si>
   <si>
     <t xml:space="preserve">1.28262650966644</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">1.30094397068024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30542159080505</t>
+    <t xml:space="preserve">1.30542147159576</t>
   </si>
   <si>
     <t xml:space="preserve">1.29036045074463</t>
@@ -3620,13 +3620,13 @@
     <t xml:space="preserve">1.28425467014313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2818124294281</t>
+    <t xml:space="preserve">1.28181231021881</t>
   </si>
   <si>
     <t xml:space="preserve">1.27652060985565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25413262844086</t>
+    <t xml:space="preserve">1.25413274765015</t>
   </si>
   <si>
     <t xml:space="preserve">1.22889542579651</t>
@@ -3638,16 +3638,16 @@
     <t xml:space="preserve">1.22482478618622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.281405210495</t>
+    <t xml:space="preserve">1.28140532970428</t>
   </si>
   <si>
     <t xml:space="preserve">1.3001297712326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25494682788849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2284882068634</t>
+    <t xml:space="preserve">1.2549467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22848832607269</t>
   </si>
   <si>
     <t xml:space="preserve">1.19918048381805</t>
@@ -3659,10 +3659,10 @@
     <t xml:space="preserve">1.20243692398071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25616788864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24639868736267</t>
+    <t xml:space="preserve">1.25616800785065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24639856815338</t>
   </si>
   <si>
     <t xml:space="preserve">1.24477052688599</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">1.22238254547119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22116148471832</t>
+    <t xml:space="preserve">1.22116136550903</t>
   </si>
   <si>
     <t xml:space="preserve">1.21464836597443</t>
@@ -3695,13 +3695,13 @@
     <t xml:space="preserve">1.23540818691254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25698220729828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27489244937897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25779604911804</t>
+    <t xml:space="preserve">1.25698208808899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27489233016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25779616832733</t>
   </si>
   <si>
     <t xml:space="preserve">1.26553010940552</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">1.25942444801331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28751111030579</t>
+    <t xml:space="preserve">1.2875109910965</t>
   </si>
   <si>
     <t xml:space="preserve">1.29768741130829</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">1.29809439182281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33554351329803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36281621456146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35223269462585</t>
+    <t xml:space="preserve">1.33554339408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36281609535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35223257541656</t>
   </si>
   <si>
     <t xml:space="preserve">1.3571172952652</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">1.34409153461456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36485135555267</t>
+    <t xml:space="preserve">1.36485123634338</t>
   </si>
   <si>
     <t xml:space="preserve">1.33961391448975</t>
@@ -3749,16 +3749,16 @@
     <t xml:space="preserve">1.3245530128479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33432233333588</t>
+    <t xml:space="preserve">1.33432221412659</t>
   </si>
   <si>
     <t xml:space="preserve">1.33106589317322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34002101421356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3286235332489</t>
+    <t xml:space="preserve">1.34002113342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32862341403961</t>
   </si>
   <si>
     <t xml:space="preserve">1.31193447113037</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">1.34327733516693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38561105728149</t>
+    <t xml:space="preserve">1.38561117649078</t>
   </si>
   <si>
     <t xml:space="preserve">1.33147287368774</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">1.36037373542786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34205627441406</t>
+    <t xml:space="preserve">1.34205639362335</t>
   </si>
   <si>
     <t xml:space="preserve">1.40272545814514</t>
@@ -5997,6 +5997,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.4300000667572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40499997138977</t>
   </si>
 </sst>
 </file>
@@ -71621,7 +71624,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6910416667</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>10982684</v>
@@ -71642,6 +71645,32 @@
         <v>1994</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6912847222</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>8845543</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>2.43799996376038</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>2.40100002288818</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>2.43400001525879</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>2.40499997138977</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>1995</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="1996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="1997">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,37 +44,37 @@
     <t xml:space="preserve">A2A.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774304032325745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76930046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77743124961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77242773771286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775554776191711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736151695251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728020906448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.708631932735443</t>
+    <t xml:space="preserve">0.7743039727211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769300401210785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777431070804596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772427618503571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775554716587067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73615175485611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728020846843719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.708631992340088</t>
   </si>
   <si>
     <t xml:space="preserve">0.701126635074615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.678610563278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.686115860939026</t>
+    <t xml:space="preserve">0.678610503673553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.686115741729736</t>
   </si>
   <si>
     <t xml:space="preserve">0.662974238395691</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">0.66985422372818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.673606932163239</t>
+    <t xml:space="preserve">0.673607051372528</t>
   </si>
   <si>
     <t xml:space="preserve">0.661723434925079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68986850976944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.667352497577667</t>
+    <t xml:space="preserve">0.689868628978729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.667352437973022</t>
   </si>
   <si>
     <t xml:space="preserve">0.688617646694183</t>
@@ -104,16 +104,16 @@
     <t xml:space="preserve">0.676108658313751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.671105086803436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.666727006435394</t>
+    <t xml:space="preserve">0.671105146408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.66672694683075</t>
   </si>
   <si>
     <t xml:space="preserve">0.643585443496704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612312972545624</t>
+    <t xml:space="preserve">0.612313032150269</t>
   </si>
   <si>
     <t xml:space="preserve">0.597927749156952</t>
@@ -122,52 +122,52 @@
     <t xml:space="preserve">0.605745851993561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610749423503876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614189386367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627323865890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617942094802856</t>
+    <t xml:space="preserve">0.610749363899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614189445972443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627323806285858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617941975593567</t>
   </si>
   <si>
     <t xml:space="preserve">0.624822020530701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646712720394135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.636080086231232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65671980381012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645461797714233</t>
+    <t xml:space="preserve">0.646712779998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.636080026626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.656719744205475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645461738109589</t>
   </si>
   <si>
     <t xml:space="preserve">0.641083598136902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647963523864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.657345354557037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661098003387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.672981560230255</t>
+    <t xml:space="preserve">0.647963464260101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.657345294952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661097943782806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.672981441020966</t>
   </si>
   <si>
     <t xml:space="preserve">0.666101574897766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.664850652217865</t>
+    <t xml:space="preserve">0.66485059261322</t>
   </si>
   <si>
     <t xml:space="preserve">0.658596158027649</t>
@@ -176,37 +176,37 @@
     <t xml:space="preserve">0.651716232299805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65484344959259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.669228792190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713010132312775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692995667457581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.691119492053986</t>
+    <t xml:space="preserve">0.65484356880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.669228911399841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71300995349884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69299578666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.691119432449341</t>
   </si>
   <si>
     <t xml:space="preserve">0.694246649742126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69799941778183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696123003959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70300281047821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692370235919952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.699250221252441</t>
+    <t xml:space="preserve">0.697999358177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696123063564301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692370414733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.699250280857086</t>
   </si>
   <si>
     <t xml:space="preserve">0.714260935783386</t>
@@ -215,28 +215,28 @@
     <t xml:space="preserve">0.714886426925659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.702377557754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705504596233368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735526204109192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.740529835224152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.744282424449921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748660624027252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.738027930259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750536978244781</t>
+    <t xml:space="preserve">0.702377498149872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705504834651947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735526263713837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.740529775619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.744282484054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748660504817963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.738027989864349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750536799430847</t>
   </si>
   <si>
     <t xml:space="preserve">0.754289627075195</t>
@@ -245,34 +245,34 @@
     <t xml:space="preserve">0.768049478530884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.757416784763336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766798615455627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.752413272857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781183838844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778056740760803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786187350749969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77930748462677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768674850463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755540430545807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.760544002056122</t>
+    <t xml:space="preserve">0.757416844367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766798496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.752413332462311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781183779239655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778056561946869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786187469959259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.779307544231415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768674910068512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755540490150452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.760544061660767</t>
   </si>
   <si>
     <t xml:space="preserve">0.76429682970047</t>
@@ -281,19 +281,19 @@
     <t xml:space="preserve">0.770551264286041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.759293079376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769925773143768</t>
+    <t xml:space="preserve">0.75929319858551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769925832748413</t>
   </si>
   <si>
     <t xml:space="preserve">0.761169612407684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.767423987388611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747409701347351</t>
+    <t xml:space="preserve">0.767424046993256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747409760951996</t>
   </si>
   <si>
     <t xml:space="preserve">0.751787841320038</t>
@@ -302,31 +302,31 @@
     <t xml:space="preserve">0.754915058612823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781809210777283</t>
+    <t xml:space="preserve">0.781809389591217</t>
   </si>
   <si>
     <t xml:space="preserve">0.801198244094849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804950833320618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799322009086609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785562038421631</t>
+    <t xml:space="preserve">0.804950952529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799321889877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785561919212341</t>
   </si>
   <si>
     <t xml:space="preserve">0.796820104122162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791816532611847</t>
+    <t xml:space="preserve">0.791816473007202</t>
   </si>
   <si>
     <t xml:space="preserve">0.801823675632477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.733649730682373</t>
+    <t xml:space="preserve">0.733649909496307</t>
   </si>
   <si>
     <t xml:space="preserve">0.725519120693207</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">0.759828746318817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.750760138034821</t>
+    <t xml:space="preserve">0.750760078430176</t>
   </si>
   <si>
     <t xml:space="preserve">0.778613984584808</t>
@@ -353,28 +353,28 @@
     <t xml:space="preserve">0.70541650056839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.730031549930573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763067543506622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762419879436493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769545316696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757885456085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742986798286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742339074611664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.758533179759979</t>
+    <t xml:space="preserve">0.730031609535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763067662715912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762419939041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769545257091522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75788551568985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742986857891083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742339193820953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758533298969269</t>
   </si>
   <si>
     <t xml:space="preserve">0.77731853723526</t>
@@ -383,25 +383,25 @@
     <t xml:space="preserve">0.774079620838165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776022970676422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78379613161087</t>
+    <t xml:space="preserve">0.776022851467133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783796191215515</t>
   </si>
   <si>
     <t xml:space="preserve">0.779909610748291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79027384519577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789625942707062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79416036605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805172502994537</t>
+    <t xml:space="preserve">0.790273785591125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789626002311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79416024684906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805172443389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.807763516902924</t>
@@ -410,22 +410,22 @@
     <t xml:space="preserve">0.822662055492401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817479968070984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820718824863434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.822014331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809706807136536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814241051673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816184401512146</t>
+    <t xml:space="preserve">0.817479908466339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820718705654144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.822014272212982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80970686674118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814241111278534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.816184520721436</t>
   </si>
   <si>
     <t xml:space="preserve">0.804524660110474</t>
@@ -434,43 +434,43 @@
     <t xml:space="preserve">0.801285743713379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812945604324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801933705806732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786387085914612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788330435752869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771488606929779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783148288726807</t>
+    <t xml:space="preserve">0.812945544719696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801933526992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786387205123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788330554962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771488666534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783148407936096</t>
   </si>
   <si>
     <t xml:space="preserve">0.782500505447388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781852722167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770193040370941</t>
+    <t xml:space="preserve">0.781852781772614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770193159580231</t>
   </si>
   <si>
     <t xml:space="preserve">0.785091638565063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.795455992221832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811002373695374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794808030128479</t>
+    <t xml:space="preserve">0.795455932617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811002254486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794808089733124</t>
   </si>
   <si>
     <t xml:space="preserve">0.796103656291962</t>
@@ -479,31 +479,31 @@
     <t xml:space="preserve">0.798694729804993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.802581310272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790921449661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796751499176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799342453479767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810354590415955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78055727481842</t>
+    <t xml:space="preserve">0.802581250667572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7909215092659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796751439571381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799342513084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810354471206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780557215213776</t>
   </si>
   <si>
     <t xml:space="preserve">0.784443855285645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785739541053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827196538448334</t>
+    <t xml:space="preserve">0.785739362239838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827196300029755</t>
   </si>
   <si>
     <t xml:space="preserve">0.81359338760376</t>
@@ -512,79 +512,79 @@
     <t xml:space="preserve">0.80063796043396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.797399163246155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803876936435699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807115733623505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7611243724823</t>
+    <t xml:space="preserve">0.797399282455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803876996040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80711567401886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761124432086945</t>
   </si>
   <si>
     <t xml:space="preserve">0.770840883255005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.731326997280121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735861539840698</t>
+    <t xml:space="preserve">0.731327056884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735861420631409</t>
   </si>
   <si>
     <t xml:space="preserve">0.720315098762512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.721610605716705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.719019591808319</t>
+    <t xml:space="preserve">0.72161066532135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.719019532203674</t>
   </si>
   <si>
     <t xml:space="preserve">0.696347892284393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696995615959167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.709950923919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713837385177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.711894154548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.707359910011292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728736042976379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715780794620514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722258388996124</t>
+    <t xml:space="preserve">0.696995556354523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.709950864315033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713837444782257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71189421415329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.707359790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728736102581024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715780854225159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722258508205414</t>
   </si>
   <si>
     <t xml:space="preserve">0.765010952949524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.7546466588974</t>
+    <t xml:space="preserve">0.754646599292755</t>
   </si>
   <si>
     <t xml:space="preserve">0.755294442176819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.78768265247345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776670813560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772136390209198</t>
+    <t xml:space="preserve">0.787682771682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776670694351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772136330604553</t>
   </si>
   <si>
     <t xml:space="preserve">0.787034928798676</t>
@@ -593,85 +593,85 @@
     <t xml:space="preserve">0.816832184791565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819423377513885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799990355968475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824605405330658</t>
+    <t xml:space="preserve">0.819423198699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799990236759186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824605345726013</t>
   </si>
   <si>
     <t xml:space="preserve">0.838856220245361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.831730902194977</t>
+    <t xml:space="preserve">0.831730782985687</t>
   </si>
   <si>
     <t xml:space="preserve">0.832378447055817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.84015166759491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.848572552204132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841447234153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844686090946198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830435335636139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798046886920929</t>
+    <t xml:space="preserve">0.840151786804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.848572611808777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.841447114944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844686210155487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830435276031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798046946525574</t>
   </si>
   <si>
     <t xml:space="preserve">0.815536499023438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.82007098197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806467950344086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811650037765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836265087127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844038188457489</t>
+    <t xml:space="preserve">0.820071041584015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806467831134796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811650097370148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83626526594162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844038307666779</t>
   </si>
   <si>
     <t xml:space="preserve">0.837560653686523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.836912989616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821366608142853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828492105007172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825900793075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829139828681946</t>
+    <t xml:space="preserve">0.836912870407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821366488933563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828491985797882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825900912284851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829139649868011</t>
   </si>
   <si>
     <t xml:space="preserve">0.846629440784454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849220395088196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864766657352448</t>
+    <t xml:space="preserve">0.849220454692841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864766776561737</t>
   </si>
   <si>
     <t xml:space="preserve">0.867357790470123</t>
@@ -680,58 +680,58 @@
     <t xml:space="preserve">0.868005573749542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.870596587657928</t>
+    <t xml:space="preserve">0.870596766471863</t>
   </si>
   <si>
     <t xml:space="preserve">0.857641458511353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.865414440631866</t>
+    <t xml:space="preserve">0.865414619445801</t>
   </si>
   <si>
     <t xml:space="preserve">0.866710245609283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85310697555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855698049068451</t>
+    <t xml:space="preserve">0.853107035160065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855697989463806</t>
   </si>
   <si>
     <t xml:space="preserve">0.858289182186127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860232472419739</t>
+    <t xml:space="preserve">0.860232293605804</t>
   </si>
   <si>
     <t xml:space="preserve">0.872539937496185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.874483227729797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887438595294952</t>
+    <t xml:space="preserve">0.874483346939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887438535690308</t>
   </si>
   <si>
     <t xml:space="preserve">0.893916249275208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.89262068271637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912701487541199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909462511539459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908167123794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919826924800873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91853129863739</t>
+    <t xml:space="preserve">0.892620742321014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.912701368331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909462809562683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908167064189911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919826865196228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918531358242035</t>
   </si>
   <si>
     <t xml:space="preserve">0.87577885389328</t>
@@ -743,49 +743,49 @@
     <t xml:space="preserve">0.891972899436951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.884847462177277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895211815834045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884199619293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876426696777344</t>
+    <t xml:space="preserve">0.884847581386566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895211696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884199857711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876426577568054</t>
   </si>
   <si>
     <t xml:space="preserve">0.862175703048706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85634583234787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882256388664246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899098455905914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.890677332878113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926952302455902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91529256105423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917235851287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966466069221497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958045125007629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965170443058014</t>
+    <t xml:space="preserve">0.856345951557159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88225656747818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899098336696625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890677392482758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926952362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91529244184494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917235791683197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966466009616852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958044946193695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965170502662659</t>
   </si>
   <si>
     <t xml:space="preserve">0.961283922195435</t>
@@ -794,64 +794,64 @@
     <t xml:space="preserve">0.963227152824402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941850960254669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941203057765961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958692908287048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982278048992157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988308668136597</t>
+    <t xml:space="preserve">0.94185084104538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941202998161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958692789077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982278227806091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988308429718018</t>
   </si>
   <si>
     <t xml:space="preserve">0.997019052505493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00036942958832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992998957633972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96820741891861</t>
+    <t xml:space="preserve">1.00036919116974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992998659610748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968207538127899</t>
   </si>
   <si>
     <t xml:space="preserve">0.981608271598816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986298620700836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988978683948517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989648699760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.974907755851746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999699354171753</t>
+    <t xml:space="preserve">0.986298263072968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988978624343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989648640155792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97490793466568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999699294567108</t>
   </si>
   <si>
     <t xml:space="preserve">1.00505936145782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998359203338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997689187526703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00170934200287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00706970691681</t>
+    <t xml:space="preserve">0.998359262943268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997689008712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00170946121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00706958770752</t>
   </si>
   <si>
     <t xml:space="preserve">1.02047049999237</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">1.0177903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995009005069733</t>
+    <t xml:space="preserve">0.995008945465088</t>
   </si>
   <si>
     <t xml:space="preserve">0.999029219150543</t>
@@ -872,10 +872,10 @@
     <t xml:space="preserve">0.976917803287506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.974237680435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97021758556366</t>
+    <t xml:space="preserve">0.974237620830536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97021746635437</t>
   </si>
   <si>
     <t xml:space="preserve">0.965527236461639</t>
@@ -884,61 +884,61 @@
     <t xml:space="preserve">0.960837006568909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.961506903171539</t>
+    <t xml:space="preserve">0.96150678396225</t>
   </si>
   <si>
     <t xml:space="preserve">0.964187204837799</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980268120765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978927969932556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984958350658417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.972897708415985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960166871547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958826720714569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951456367969513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955476641654968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949446320533752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9635169506073</t>
+    <t xml:space="preserve">0.980268061161041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978927850723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984958291053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97289776802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960166931152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958826839923859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951456308364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955476582050323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949446260929108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963517189025879</t>
   </si>
   <si>
     <t xml:space="preserve">0.950116336345673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953466415405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956816673278809</t>
+    <t xml:space="preserve">0.953466355800629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956816554069519</t>
   </si>
   <si>
     <t xml:space="preserve">0.958156704902649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952796578407288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962177157402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944756090641022</t>
+    <t xml:space="preserve">0.952796399593353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962177097797394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944755852222443</t>
   </si>
   <si>
     <t xml:space="preserve">0.931355237960815</t>
@@ -947,91 +947,91 @@
     <t xml:space="preserve">0.948106169700623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954136550426483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957486808300018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939395606517792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946766018867493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934705436229706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9286749958992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924654603004456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932695269584656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945425987243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959496974945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973567724227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978258073329926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993668854236603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984288334846497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983618438243866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994338989257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977587819099426</t>
+    <t xml:space="preserve">0.954136610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957486748695374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939395666122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946766078472137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934705376625061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928675055503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92465478181839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932695209980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945426106452942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959496915340424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973567605018616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.978257954120636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993668913841248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984288394451141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983618319034576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994338870048523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977587997913361</t>
   </si>
   <si>
     <t xml:space="preserve">0.980938255786896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97222763299942</t>
+    <t xml:space="preserve">0.972227513790131</t>
   </si>
   <si>
     <t xml:space="preserve">0.96619713306427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96954745054245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96887743473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9715576171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995679020881653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992328763008118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96686726808548</t>
+    <t xml:space="preserve">0.969547271728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968877375125885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971557557582855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995678961277008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992328703403473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966867208480835</t>
   </si>
   <si>
     <t xml:space="preserve">1.02114045619965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01041972637177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01444017887115</t>
+    <t xml:space="preserve">1.01041984558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01444005966187</t>
   </si>
   <si>
     <t xml:space="preserve">1.02181053161621</t>
@@ -1040,10 +1040,10 @@
     <t xml:space="preserve">1.02382063865662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02851092815399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03320133686066</t>
+    <t xml:space="preserve">1.0285108089447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03320121765137</t>
   </si>
   <si>
     <t xml:space="preserve">1.03923153877258</t>
@@ -1052,40 +1052,40 @@
     <t xml:space="preserve">1.0265007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05531251430511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05866277217865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04459178447723</t>
+    <t xml:space="preserve">1.05531239509583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05866253376007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04459202289581</t>
   </si>
   <si>
     <t xml:space="preserve">1.05330240726471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06804323196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0727334022522</t>
+    <t xml:space="preserve">1.06804311275482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07273352146149</t>
   </si>
   <si>
     <t xml:space="preserve">1.08613431453705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09551501274109</t>
+    <t xml:space="preserve">1.09551477432251</t>
   </si>
   <si>
     <t xml:space="preserve">1.08345413208008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08211410045624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05397248268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06000292301178</t>
+    <t xml:space="preserve">1.08211398124695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05397236347198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0600026845932</t>
   </si>
   <si>
     <t xml:space="preserve">1.04392170906067</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">1.03990161418915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04258167743683</t>
+    <t xml:space="preserve">1.04258179664612</t>
   </si>
   <si>
     <t xml:space="preserve">1.01980042457581</t>
@@ -1112,31 +1112,31 @@
     <t xml:space="preserve">1.05196225643158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06737327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06603300571442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02449071407318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01846015453339</t>
+    <t xml:space="preserve">1.06737315654755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06603312492371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02449059486389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01846027374268</t>
   </si>
   <si>
     <t xml:space="preserve">1.02784085273743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05665254592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06134283542633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07742381095886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07943403720856</t>
+    <t xml:space="preserve">1.05665266513824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06134271621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07742369174957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07943391799927</t>
   </si>
   <si>
     <t xml:space="preserve">1.06938326358795</t>
@@ -1145,13 +1145,13 @@
     <t xml:space="preserve">1.05933272838593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03856146335602</t>
+    <t xml:space="preserve">1.03856158256531</t>
   </si>
   <si>
     <t xml:space="preserve">1.02683579921722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03588140010834</t>
+    <t xml:space="preserve">1.03588163852692</t>
   </si>
   <si>
     <t xml:space="preserve">1.04191160202026</t>
@@ -1160,133 +1160,133 @@
     <t xml:space="preserve">0.996349036693573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.971222579479218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995344042778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944420993328094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95313161611557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941405773162842</t>
+    <t xml:space="preserve">0.971222460269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99534398317337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944420874118805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953131496906281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941405892372131</t>
   </si>
   <si>
     <t xml:space="preserve">0.959831774234772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9464311003685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957821846008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95045131444931</t>
+    <t xml:space="preserve">0.946431219577789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957821726799011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950451195240021</t>
   </si>
   <si>
     <t xml:space="preserve">0.936380505561829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967202365398407</t>
+    <t xml:space="preserve">0.967202305793762</t>
   </si>
   <si>
     <t xml:space="preserve">0.991323709487915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975577890872955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993333756923676</t>
+    <t xml:space="preserve">0.975577712059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993333876132965</t>
   </si>
   <si>
     <t xml:space="preserve">1.0000342130661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00137436389923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991658866405487</t>
+    <t xml:space="preserve">1.00137448310852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991658687591553</t>
   </si>
   <si>
     <t xml:space="preserve">1.00673472881317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999364256858826</t>
+    <t xml:space="preserve">0.99936431646347</t>
   </si>
   <si>
     <t xml:space="preserve">1.04023659229279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04157662391663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04224693775177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04961705207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04995214939117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06268298625946</t>
+    <t xml:space="preserve">1.04157674312592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04224681854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04961717128754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04995226860046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06268286705017</t>
   </si>
   <si>
     <t xml:space="preserve">1.07206356525421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05832767486572</t>
+    <t xml:space="preserve">1.05832755565643</t>
   </si>
   <si>
     <t xml:space="preserve">1.06335294246674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07407379150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08043897151947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08546411991119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09048962593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09484493732452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09819507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09853005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12198138237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11762619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11729121208191</t>
+    <t xml:space="preserve">1.07407367229462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08043885231018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08546435832977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09048974514008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09484469890594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09819519519806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09852993488312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12198150157928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11762607097626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11729109287262</t>
   </si>
   <si>
     <t xml:space="preserve">1.10724067687988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10757577419281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12265157699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13002192974091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10992074012756</t>
+    <t xml:space="preserve">1.10757565498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12265169620514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13002181053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10992085933685</t>
   </si>
   <si>
     <t xml:space="preserve">1.11829626560211</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">1.03895282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05287528038025</t>
+    <t xml:space="preserve">1.05287516117096</t>
   </si>
   <si>
     <t xml:space="preserve">1.04208528995514</t>
@@ -1313,49 +1313,49 @@
     <t xml:space="preserve">1.02572667598724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00693142414093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980827212333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998926222324371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01076018810272</t>
+    <t xml:space="preserve">1.00693154335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980827152729034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998926043510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01076030731201</t>
   </si>
   <si>
     <t xml:space="preserve">1.00484335422516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02920734882355</t>
+    <t xml:space="preserve">1.02920722961426</t>
   </si>
   <si>
     <t xml:space="preserve">1.00936794281006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00658345222473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999622285366058</t>
+    <t xml:space="preserve">1.00658333301544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999622344970703</t>
   </si>
   <si>
     <t xml:space="preserve">0.968993246555328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0159809589386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02398657798767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03164386749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02851116657257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0198096036911</t>
+    <t xml:space="preserve">1.01598107814789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02398645877838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0316436290741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02851104736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01980984210968</t>
   </si>
   <si>
     <t xml:space="preserve">1.04382562637329</t>
@@ -1367,10 +1367,10 @@
     <t xml:space="preserve">1.02363836765289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02537882328033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00588738918304</t>
+    <t xml:space="preserve">1.02537858486176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00588750839233</t>
   </si>
   <si>
     <t xml:space="preserve">1.01250052452087</t>
@@ -1382,13 +1382,13 @@
     <t xml:space="preserve">1.02642285823822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03373193740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01389276981354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03860473632812</t>
+    <t xml:space="preserve">1.03373205661774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01389265060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0386049747467</t>
   </si>
   <si>
     <t xml:space="preserve">1.0511349439621</t>
@@ -1397,16 +1397,16 @@
     <t xml:space="preserve">1.06122851371765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07236635684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06018424034119</t>
+    <t xml:space="preserve">1.07236659526825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06018435955048</t>
   </si>
   <si>
     <t xml:space="preserve">1.06262075901031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05600762367249</t>
+    <t xml:space="preserve">1.05600774288177</t>
   </si>
   <si>
     <t xml:space="preserve">1.07375872135162</t>
@@ -1424,13 +1424,13 @@
     <t xml:space="preserve">1.09429407119751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10160326957703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08420038223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04835045337677</t>
+    <t xml:space="preserve">1.10160338878632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08420026302338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04835057258606</t>
   </si>
   <si>
     <t xml:space="preserve">1.06157660484314</t>
@@ -1439,40 +1439,40 @@
     <t xml:space="preserve">1.07201826572418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07584702968597</t>
+    <t xml:space="preserve">1.07584714889526</t>
   </si>
   <si>
     <t xml:space="preserve">1.0713222026825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09394598007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08106803894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09011733531952</t>
+    <t xml:space="preserve">1.09394586086273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08106791973114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09011745452881</t>
   </si>
   <si>
     <t xml:space="preserve">1.08246004581451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1029953956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12005043029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12387907505035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10473585128784</t>
+    <t xml:space="preserve">1.10299551486969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12005031108856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12387895584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10473573207855</t>
   </si>
   <si>
     <t xml:space="preserve">1.10612797737122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11134910583496</t>
+    <t xml:space="preserve">1.11134898662567</t>
   </si>
   <si>
     <t xml:space="preserve">1.10821640491486</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">1.08837711811066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08802890777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08942139148712</t>
+    <t xml:space="preserve">1.08802902698517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08942127227783</t>
   </si>
   <si>
     <t xml:space="preserve">1.07549893856049</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">1.06540524959564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03338396549225</t>
+    <t xml:space="preserve">1.03338408470154</t>
   </si>
   <si>
     <t xml:space="preserve">1.04243338108063</t>
@@ -1514,31 +1514,31 @@
     <t xml:space="preserve">1.05705177783966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0789794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09220588207245</t>
+    <t xml:space="preserve">1.07897937297821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09220576286316</t>
   </si>
   <si>
     <t xml:space="preserve">1.09116160869598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08454859256744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08141613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09847068786621</t>
+    <t xml:space="preserve">1.08454835414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08141589164734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0984708070755</t>
   </si>
   <si>
     <t xml:space="preserve">1.09603440761566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07619500160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07445466518402</t>
+    <t xml:space="preserve">1.07619524002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07445478439331</t>
   </si>
   <si>
     <t xml:space="preserve">1.05879211425781</t>
@@ -1547,10 +1547,10 @@
     <t xml:space="preserve">1.07758724689484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06923401355743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04069328308105</t>
+    <t xml:space="preserve">1.06923377513885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04069316387177</t>
   </si>
   <si>
     <t xml:space="preserve">1.03199172019958</t>
@@ -1580,31 +1580,31 @@
     <t xml:space="preserve">0.991616904735565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00832378864288</t>
+    <t xml:space="preserve">1.00832390785217</t>
   </si>
   <si>
     <t xml:space="preserve">1.01424074172974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01772141456604</t>
+    <t xml:space="preserve">1.01772129535675</t>
   </si>
   <si>
     <t xml:space="preserve">1.01354455947876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.993705451488495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988136351108551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977346658706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00553929805756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986048102378845</t>
+    <t xml:space="preserve">0.993705332279205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98813658952713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97734671831131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00553941726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986047923564911</t>
   </si>
   <si>
     <t xml:space="preserve">0.989528715610504</t>
@@ -1613,19 +1613,19 @@
     <t xml:space="preserve">0.992313206195831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98291552066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991964995861053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01319658756256</t>
+    <t xml:space="preserve">0.982915580272675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991965055465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01319670677185</t>
   </si>
   <si>
     <t xml:space="preserve">1.00414705276489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02050590515137</t>
+    <t xml:space="preserve">1.02050578594208</t>
   </si>
   <si>
     <t xml:space="preserve">1.0156329870224</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">1.03930103778839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05252695083618</t>
+    <t xml:space="preserve">1.05252718925476</t>
   </si>
   <si>
     <t xml:space="preserve">1.05461549758911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03721261024475</t>
+    <t xml:space="preserve">1.03721272945404</t>
   </si>
   <si>
     <t xml:space="preserve">1.02711892127991</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">1.06610143184662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06088054180145</t>
+    <t xml:space="preserve">1.06088066101074</t>
   </si>
   <si>
     <t xml:space="preserve">1.04034531116486</t>
@@ -1664,19 +1664,19 @@
     <t xml:space="preserve">1.03233981132507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04278159141541</t>
+    <t xml:space="preserve">1.04278171062469</t>
   </si>
   <si>
     <t xml:space="preserve">1.04347765445709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07410657405853</t>
+    <t xml:space="preserve">1.07410669326782</t>
   </si>
   <si>
     <t xml:space="preserve">1.10090720653534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11761403083801</t>
+    <t xml:space="preserve">1.11761391162872</t>
   </si>
   <si>
     <t xml:space="preserve">1.12701153755188</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">1.12318289279938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13118815422058</t>
+    <t xml:space="preserve">1.13118827342987</t>
   </si>
   <si>
     <t xml:space="preserve">1.1144814491272</t>
@@ -1703,10 +1703,10 @@
     <t xml:space="preserve">1.094642162323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11622178554535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11830997467041</t>
+    <t xml:space="preserve">1.11622166633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1183100938797</t>
   </si>
   <si>
     <t xml:space="preserve">1.13501679897308</t>
@@ -1721,7 +1721,7 @@
     <t xml:space="preserve">1.14302217960358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10403966903687</t>
+    <t xml:space="preserve">1.10403978824615</t>
   </si>
   <si>
     <t xml:space="preserve">1.10891258716583</t>
@@ -1733,25 +1733,25 @@
     <t xml:space="preserve">1.10195124149323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0991667509079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0949901342392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10577988624573</t>
+    <t xml:space="preserve">1.09916687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09499025344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10578012466431</t>
   </si>
   <si>
     <t xml:space="preserve">1.09185767173767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07793521881104</t>
+    <t xml:space="preserve">1.07793545722961</t>
   </si>
   <si>
     <t xml:space="preserve">1.08071982860565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0866367816925</t>
+    <t xml:space="preserve">1.08663666248322</t>
   </si>
   <si>
     <t xml:space="preserve">1.06227278709412</t>
@@ -1775,25 +1775,25 @@
     <t xml:space="preserve">1.11100089550018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10543179512024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08594071865082</t>
+    <t xml:space="preserve">1.10543215274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08594059944153</t>
   </si>
   <si>
     <t xml:space="preserve">1.09568619728088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08907330036163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11726593971252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12074649333954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10752022266388</t>
+    <t xml:space="preserve">1.08907318115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11726582050323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12074673175812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10752034187317</t>
   </si>
   <si>
     <t xml:space="preserve">1.11030471324921</t>
@@ -1802,40 +1802,40 @@
     <t xml:space="preserve">1.12179064750671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11935436725616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13571286201477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13536489009857</t>
+    <t xml:space="preserve">1.11935424804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13571310043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13536500930786</t>
   </si>
   <si>
     <t xml:space="preserve">1.13084018230438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13223230838776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14754688739777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06331694126129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05391931533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04626190662384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05426752567291</t>
+    <t xml:space="preserve">1.13223242759705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14754700660706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06331706047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05391943454742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04626214504242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05426728725433</t>
   </si>
   <si>
     <t xml:space="preserve">1.04869842529297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02433454990387</t>
+    <t xml:space="preserve">1.02433443069458</t>
   </si>
   <si>
     <t xml:space="preserve">1.01946151256561</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">1.0037989616394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997882068157196</t>
+    <t xml:space="preserve">0.997882187366486</t>
   </si>
   <si>
     <t xml:space="preserve">1.00727963447571</t>
@@ -1883,13 +1883,13 @@
     <t xml:space="preserve">1.05127596855164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06403410434723</t>
+    <t xml:space="preserve">1.06403422355652</t>
   </si>
   <si>
     <t xml:space="preserve">1.07168924808502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08043777942657</t>
+    <t xml:space="preserve">1.08043766021729</t>
   </si>
   <si>
     <t xml:space="preserve">1.0979346036911</t>
@@ -1898,28 +1898,28 @@
     <t xml:space="preserve">1.0986635684967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10449588298798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10048639774323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1023086309433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09574735164642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09829902648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13219964504242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12563812732697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14021897315979</t>
+    <t xml:space="preserve">1.10449600219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10048615932465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10230875015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.095747590065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09829914569855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13219952583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12563824653625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1402188539505</t>
   </si>
   <si>
     <t xml:space="preserve">1.14750921726227</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">1.11944127082825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11543142795563</t>
+    <t xml:space="preserve">1.11543154716492</t>
   </si>
   <si>
     <t xml:space="preserve">1.10376691818237</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">1.11251544952393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11069273948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13511574268341</t>
+    <t xml:space="preserve">1.11069285869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13511562347412</t>
   </si>
   <si>
     <t xml:space="preserve">1.1500608921051</t>
@@ -1961,43 +1961,43 @@
     <t xml:space="preserve">1.16427731513977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1704740524292</t>
+    <t xml:space="preserve">1.17047417163849</t>
   </si>
   <si>
     <t xml:space="preserve">1.17156767845154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17229688167572</t>
+    <t xml:space="preserve">1.17229664325714</t>
   </si>
   <si>
     <t xml:space="preserve">1.17849361896515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17484831809998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19161641597748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16318356990814</t>
+    <t xml:space="preserve">1.17484843730927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19161629676819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16318368911743</t>
   </si>
   <si>
     <t xml:space="preserve">1.16609978675842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17995166778564</t>
+    <t xml:space="preserve">1.17995154857635</t>
   </si>
   <si>
     <t xml:space="preserve">1.18469035625458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18104529380798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1712030172348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17375469207764</t>
+    <t xml:space="preserve">1.18104517459869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17120325565338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17375481128693</t>
   </si>
   <si>
     <t xml:space="preserve">1.14969646930695</t>
@@ -2006,31 +2006,31 @@
     <t xml:space="preserve">1.15407061576843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17083847522736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16209006309509</t>
+    <t xml:space="preserve">1.17083859443665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16209018230438</t>
   </si>
   <si>
     <t xml:space="preserve">1.1668289899826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1675580739975</t>
+    <t xml:space="preserve">1.16755795478821</t>
   </si>
   <si>
     <t xml:space="preserve">1.17010962963104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13183498382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12418019771576</t>
+    <t xml:space="preserve">1.13183486461639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12418007850647</t>
   </si>
   <si>
     <t xml:space="preserve">1.12782537937164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14277052879333</t>
+    <t xml:space="preserve">1.14277064800262</t>
   </si>
   <si>
     <t xml:space="preserve">1.16099655628204</t>
@@ -2039,10 +2039,10 @@
     <t xml:space="preserve">1.14459323883057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15297722816467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13985443115234</t>
+    <t xml:space="preserve">1.15297710895538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13985455036163</t>
   </si>
   <si>
     <t xml:space="preserve">1.13475108146667</t>
@@ -2051,25 +2051,25 @@
     <t xml:space="preserve">1.16391277313232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16938066482544</t>
+    <t xml:space="preserve">1.16938054561615</t>
   </si>
   <si>
     <t xml:space="preserve">1.16573524475098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16500639915466</t>
+    <t xml:space="preserve">1.16500616073608</t>
   </si>
   <si>
     <t xml:space="preserve">1.18833565711975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20473909378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20036470890045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1887001991272</t>
+    <t xml:space="preserve">1.20473897457123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20036482810974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18870007991791</t>
   </si>
   <si>
     <t xml:space="preserve">1.17958724498749</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">1.16464173793793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17922246456146</t>
+    <t xml:space="preserve">1.17922270298004</t>
   </si>
   <si>
     <t xml:space="preserve">1.18213880062103</t>
@@ -2087,25 +2087,25 @@
     <t xml:space="preserve">1.17630648612976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19599056243896</t>
+    <t xml:space="preserve">1.19599044322968</t>
   </si>
   <si>
     <t xml:space="preserve">1.18979358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22551667690277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21567475795746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22770380973816</t>
+    <t xml:space="preserve">1.22551679611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21567463874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22770369052887</t>
   </si>
   <si>
     <t xml:space="preserve">1.23207807540894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21421658992767</t>
+    <t xml:space="preserve">1.21421670913696</t>
   </si>
   <si>
     <t xml:space="preserve">1.21166479587555</t>
@@ -2114,49 +2114,49 @@
     <t xml:space="preserve">1.23134911060333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2302553653717</t>
+    <t xml:space="preserve">1.23025548458099</t>
   </si>
   <si>
     <t xml:space="preserve">1.21603918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21931993961334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23791027069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23462963104248</t>
+    <t xml:space="preserve">1.21931982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23791038990021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23462975025177</t>
   </si>
   <si>
     <t xml:space="preserve">1.22806835174561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21640360355377</t>
+    <t xml:space="preserve">1.21640372276306</t>
   </si>
   <si>
     <t xml:space="preserve">1.22187149524689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22114241123199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22405850887299</t>
+    <t xml:space="preserve">1.22114229202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22405862808228</t>
   </si>
   <si>
     <t xml:space="preserve">1.23061990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22843289375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23645234107971</t>
+    <t xml:space="preserve">1.22843277454376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23645210266113</t>
   </si>
   <si>
     <t xml:space="preserve">1.2287974357605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22624576091766</t>
+    <t xml:space="preserve">1.22624564170837</t>
   </si>
   <si>
     <t xml:space="preserve">1.27363336086273</t>
@@ -2168,28 +2168,28 @@
     <t xml:space="preserve">1.31154346466064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31336605548859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30972063541412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30826282501221</t>
+    <t xml:space="preserve">1.3133659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30972075462341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30826270580292</t>
   </si>
   <si>
     <t xml:space="preserve">1.31591761112213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29331743717194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31518864631653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31445956230164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30862724781036</t>
+    <t xml:space="preserve">1.29331755638123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31518852710724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31445944309235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30862736701965</t>
   </si>
   <si>
     <t xml:space="preserve">1.29732716083527</t>
@@ -2201,16 +2201,16 @@
     <t xml:space="preserve">1.28857862949371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28420436382294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27727842330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27509129047394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26452040672302</t>
+    <t xml:space="preserve">1.28420448303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27727854251862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27509140968323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26452028751373</t>
   </si>
   <si>
     <t xml:space="preserve">1.24884593486786</t>
@@ -2219,25 +2219,25 @@
     <t xml:space="preserve">1.24665880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25249111652374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24520063400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24483621120453</t>
+    <t xml:space="preserve">1.25249099731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24520075321198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24483609199524</t>
   </si>
   <si>
     <t xml:space="preserve">1.19052267074585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19635510444641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1985422372818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19343888759613</t>
+    <t xml:space="preserve">1.19635498523712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19854235649109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19343876838684</t>
   </si>
   <si>
     <t xml:space="preserve">1.18068063259125</t>
@@ -2246,43 +2246,43 @@
     <t xml:space="preserve">1.20218741893768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18906474113464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19270992279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20656156539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20729088783264</t>
+    <t xml:space="preserve">1.18906462192535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19270980358124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20656168460846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20729064941406</t>
   </si>
   <si>
     <t xml:space="preserve">1.22515213489532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24155557155609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23353612422943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21895527839661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21275854110718</t>
+    <t xml:space="preserve">1.2415554523468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23353624343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2189553976059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21275842189789</t>
   </si>
   <si>
     <t xml:space="preserve">1.20838415622711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25504291057587</t>
+    <t xml:space="preserve">1.25504279136658</t>
   </si>
   <si>
     <t xml:space="preserve">1.2506685256958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25941693782806</t>
+    <t xml:space="preserve">1.25941705703735</t>
   </si>
   <si>
     <t xml:space="preserve">1.25650084018707</t>
@@ -2291,25 +2291,25 @@
     <t xml:space="preserve">1.26853001117706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29987871646881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30315947532654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29368185997009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29222393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30607545375824</t>
+    <t xml:space="preserve">1.2998788356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30315959453583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29368197917938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2922238111496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30607557296753</t>
   </si>
   <si>
     <t xml:space="preserve">1.35200524330139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34544384479523</t>
+    <t xml:space="preserve">1.34544372558594</t>
   </si>
   <si>
     <t xml:space="preserve">1.33414363861084</t>
@@ -2318,10 +2318,10 @@
     <t xml:space="preserve">1.31409502029419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32247912883759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32940495014191</t>
+    <t xml:space="preserve">1.3224790096283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32940483093262</t>
   </si>
   <si>
     <t xml:space="preserve">1.34580826759338</t>
@@ -2333,10 +2333,10 @@
     <t xml:space="preserve">1.33013391494751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34981799125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34398567676544</t>
+    <t xml:space="preserve">1.349818110466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34398579597473</t>
   </si>
   <si>
     <t xml:space="preserve">1.34143400192261</t>
@@ -2345,13 +2345,13 @@
     <t xml:space="preserve">1.34945344924927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35893106460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36986660957336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3822603225708</t>
+    <t xml:space="preserve">1.35893094539642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36986649036407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38226020336151</t>
   </si>
   <si>
     <t xml:space="preserve">1.36038911342621</t>
@@ -2360,16 +2360,16 @@
     <t xml:space="preserve">1.34908902645111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26524925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25613629817963</t>
+    <t xml:space="preserve">1.26524949073792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25613653659821</t>
   </si>
   <si>
     <t xml:space="preserve">1.13766729831696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15589332580566</t>
+    <t xml:space="preserve">1.15589320659637</t>
   </si>
   <si>
     <t xml:space="preserve">1.19708406925201</t>
@@ -2378,49 +2378,49 @@
     <t xml:space="preserve">1.11579608917236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996233463287354</t>
+    <t xml:space="preserve">0.996233344078064</t>
   </si>
   <si>
     <t xml:space="preserve">0.924787521362305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.905467987060547</t>
+    <t xml:space="preserve">0.905467927455902</t>
   </si>
   <si>
     <t xml:space="preserve">0.733049988746643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.772782623767853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750546932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775334417819977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751275956630707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754556655883789</t>
+    <t xml:space="preserve">0.772782564163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750546872615814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775334298610687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751276075839996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754556596279144</t>
   </si>
   <si>
     <t xml:space="preserve">0.741433918476105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.729040265083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786270022392273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797205567359924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793195843696594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778250515460968</t>
+    <t xml:space="preserve">0.729040205478668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786269962787628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79720550775528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.793195784091949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778250455856323</t>
   </si>
   <si>
     <t xml:space="preserve">0.824544489383698</t>
@@ -2429,145 +2429,145 @@
     <t xml:space="preserve">0.826002597808838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.816160559654236</t>
+    <t xml:space="preserve">0.816160619258881</t>
   </si>
   <si>
     <t xml:space="preserve">0.841677010059357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.836209118366241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86901593208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869744896888733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855164110660553</t>
+    <t xml:space="preserve">0.836209058761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869015991687775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.869745016098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855164170265198</t>
   </si>
   <si>
     <t xml:space="preserve">0.876670897006989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.889429032802582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.885783910751343</t>
+    <t xml:space="preserve">0.889429092407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885783851146698</t>
   </si>
   <si>
     <t xml:space="preserve">0.897448480129242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910935938358307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911664843559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.883961260318756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888335525989532</t>
+    <t xml:space="preserve">0.910935819149017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911664664745331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883961200714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888335585594177</t>
   </si>
   <si>
     <t xml:space="preserve">0.879587113857269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.890158116817474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906926035881042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901458203792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899635672569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905832588672638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872296512126923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879951596260071</t>
+    <t xml:space="preserve">0.89015805721283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906926155090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901458323001862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899635553359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905832409858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872296631336212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879951536655426</t>
   </si>
   <si>
     <t xml:space="preserve">0.878128945827484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.882138729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877764403820038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914581060409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93426513671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.911300361156464</t>
+    <t xml:space="preserve">0.882138609886169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877764463424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914581000804901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93426501750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.911300301551819</t>
   </si>
   <si>
     <t xml:space="preserve">0.944332480430603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.902750730514526</t>
+    <t xml:space="preserve">0.902750670909882</t>
   </si>
   <si>
     <t xml:space="preserve">0.914020538330078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910522997379303</t>
+    <t xml:space="preserve">0.910522937774658</t>
   </si>
   <si>
     <t xml:space="preserve">0.912854731082916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946275591850281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971147000789642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950550377368927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971535563468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969592273235321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981639444828033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00573360919952</t>
+    <t xml:space="preserve">0.946275532245636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971146881580353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950550258159637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971535444259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969592332839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981639504432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00573348999023</t>
   </si>
   <si>
     <t xml:space="preserve">1.04265189170837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04342901706696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03060483932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05236709117889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02710711956024</t>
+    <t xml:space="preserve">1.04342913627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03060472011566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05236732959747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02710747718811</t>
   </si>
   <si>
     <t xml:space="preserve">1.01195132732391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.960265636444092</t>
+    <t xml:space="preserve">0.960265576839447</t>
   </si>
   <si>
     <t xml:space="preserve">0.956379473209381</t>
@@ -2582,10 +2582,10 @@
     <t xml:space="preserve">1.01778054237366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0096195936203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01933491230011</t>
+    <t xml:space="preserve">1.00961983203888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0193350315094</t>
   </si>
   <si>
     <t xml:space="preserve">1.01467168331146</t>
@@ -2600,103 +2600,103 @@
     <t xml:space="preserve">0.977364778518677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979696393013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984359741210938</t>
+    <t xml:space="preserve">0.979696333408356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984359800815582</t>
   </si>
   <si>
     <t xml:space="preserve">0.99990439414978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996795535087585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993686556816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983194053173065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982805371284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958322584629059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961431503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960654199123383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973867237567902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973089814186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985137045383453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987857282161713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985525608062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949773132801056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954436540603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970758259296417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928788006305695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943166732788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95599091053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959877133369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953659236431122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965317666530609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982027947902679</t>
+    <t xml:space="preserve">0.996795415878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993686378002167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983193933963776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98280531167984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958322703838348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961431443691254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960654079914093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973867177963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973089933395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985136926174164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987857222557068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985525548458099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949773252010345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954436421394348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970758199691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92878794670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943166613578796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955990970134735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959877014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953659296035767</t>
+  </si>
+  <si>
+    <t xml